--- a/www/LENS_INDICATORS_DB.xlsx
+++ b/www/LENS_INDICATORS_DB.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L227"/>
+  <dimension ref="A1:L228"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -457,7 +457,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Access point type; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Access point type</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Digital channel type; Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Channel type; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Debit cards (volume)</t>
+          <t>Debit cards (number)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>An aggregate measure of the uptake of insurance. When expressed as a share of the population or in per capita terms, it is a measure of the prevalence of insurance adoption and facilitates comparison with other countries. !- Definitions and concepts: Insurance policy holders refers the total number of life and non-flie insurance policy holders from resident individuals or MSMEs. A customer holding more than one (life or non-life) insurance policy should be counted as one policy holder. !- Data requirements: Number of unique insurance policy holders at the end of a specific period (e.g. quarter or year);  Total adult population (official counts from recent census or estimates from national statistics agency). !- Limitations and considerations: If an individual or MSME holds insurance policies from multiple insurers, they may be counted more than once in aggregations of policyholders across institutions, unless a national ID can be used to track individual policyholders across institutions. !- Derivable indicators: Insurancy policy holders per 1,000 adults.</t>
+          <t>An aggregate measure of the uptake of insurance. When expressed as a share of the population or in per capita terms, it is a measure of the prevalence of insurance adoption and facilitates comparison with other countries. !- Definitions and concepts: Insurance policy holders refers the total number of life and non-flie insurance policy holders from resident individuals or MSMEs. A customer holding more than one (life or non-life) insurance policy should be counted as one policy holder. !- Data requirements: Number of unique insurance policy holders at the end of a specific period (e.g. quarter or year);  Total adult population (official counts from recent census or estimates from national statistics agency). !- Limitations and considerations: If an individual or MSME holds insurance policies from multiple insurers, they may be counted more than once in aggregations of policyholders across institutions, unless a national ID can be used to track individual policyholders across institutions. One policyholder's insurance policy may cover multiple persons (e.g. member-owned schemes, group plans) !- Derivable indicators: Insurance policy holders per 1,000 adults.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Customer gender; Customer type; Age of customer; Financial service provider (FSP) type; Product type</t>
+          <t>Customer type; Customer gender; Financial service provider (FSP) type; Product type; Age of customer</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="D58">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Customer gender; Customer type; Financial service provider (FSP) type; Product type; Transaction type</t>
+          <t>Customer type; Customer gender; Financial service provider (FSP) type; Product type; Transaction type</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Customer gender; Customer type; Financial service provider (FSP) type; Product type; Transaction type</t>
+          <t>Customer type; Customer gender; Financial service provider (FSP) type; Product type; Transaction type</t>
         </is>
       </c>
     </row>
@@ -4802,12 +4802,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Suitability, Depositor protection</t>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Customer type; Account type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Account type</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints resolution outcome; Complaints resolution time;</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints resolution outcome; Complaints resolution time</t>
         </is>
       </c>
     </row>
@@ -6258,60 +6258,51 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Consumer protection</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Suitability</t>
+          <t>Uptake (account ownership)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D112">
-        <v>103</v>
+        <v>395</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borrowers whose collateral was seized</t>
+          <t>Insured or lives covered</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>% of borrowers whose collateral was seized</t>
+          <t>Number of insured persons or lives covered by insurance</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>A measure of loan portfolio/credit risk assessment quality or financial distress among borrowers. !- Data requirements: Granular data that can yield (1) A count of unique borrowers of secured loans (those with collateral requirements) who subsequently had collateral seized by lender due to default over a specific period of time (e.g. past quarter or past year), (2) Total unique borrowers of secured loans over a specific period of time.</t>
+          <t>Refers to the total count of people covered by insurance, a key metric of coverage breadth and insurance uptake, complementary to the number of insurance policyholders. The policyholder and the insured can be different people -for example, if someone takes out a policy on another individual, the latter is the insured because the policy covers them, and the former is the policyholder, who purchases and owns the policy, and holds the right to make changes. An insurance policy can also cover several people, such as in member-owned schemes, group plans, and other variations. 
+When expressed as a share of the population or in per capita terms, it is a measure of the prevalence of insurance adoption and facilitates comparison with other countries. For microinsurance, a coverage ratio can reflect the number of lives covered expressed as a share of the target market or population participating in microinsurance programs  !- Definitions and concepts: Lives covered by insurance refers to the total number of people covered by life and non-life insurance policies. A customer covered by more than one (life or non-life) insurance policy should be counted as one life covered. !- Data requirements: Number of lives insured at the end of a specific period (e.g. quarter or year);  Total adult population (official counts from recent census or estimates from national statistics agency); Target population (number of people targeted by microinsurance, which may include segments of a community or clients from an MFI). !- Limitations and considerations: If an individual is covered by multiple insurers, they may be counted more than once in aggregations of lives covered across institutions, unless a national ID can be used . !- Derivable indicators: Lives covered by insurance per 1,000 adults; Lives covered by insurance as a share of the target population.</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>How does the share of customers whose collateral was seized due to default vary by gender and othe rkey sociodemographics? Are women more or less likely than men to have their collateral seized following loan default? How does the share differ by gender across different loan sizes, loan products,  types of financial service providers (FSP), collateral type (e.g., movable, immovable, alternative)? And how do any of these differences relate to seizure rates? Are women more likely to be subject to stricter collateral requirements or less flexible repayment terms that increase the likelihood of asset seizure?</t>
+          <t>Are there gender differences in the total number of lives covered by insurance, including across product types and providers? How do multiple insurance coverages and coverage amounts vary by gender, age, income, and location? To what extent do providers with higher gender diversity attract more gender-balanced portfolios of lives covered? Are gender disparities consistent or do they vary across life and non-life insurance within the overall market?</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>Outcomes, Credit risk</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator, it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered.</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Loan type; Collateral type; Loan size; Loan term; Interest rate category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -6323,35 +6314,35 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Complaints handling</t>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D113">
-        <v>239</v>
+        <v>103</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Customer complaints (number)</t>
+          <t>Borrowers whose collateral was seized</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Number of customer complaints (including processing status, channels, type)</t>
+          <t>% of borrowers whose collateral was seized</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>This indicator tallies the formal expressions of dissatisfaction that retail or MSME clients lodge with a financial-service provider (or an external ombudsman) about products, services, or staff conduct over a specified period and can be normalized by dividing by the customer basis to obtain an intensity metric (e.g. complaints per 1,000 active customers). A rising complaint count can signal service-quality gaps, mis-selling, opaque fees, or inadequate disclosure—issues that erode trust and may escalate into regulatory sanctions or litigation. Supervisors can track both the absolute number and complaint-to-account ratios to test consumer-protection frameworks, prioritise thematic reviews, and assess whether rapid product roll-outs (e.g., digital lending, mobile wallets) are being matched by robust after-sales support. Where granular data or more detailed reporting templates permit, customer complaints can be disaggregated by processing status (e.g. received, accepted/rejected, in process, resolved, escalated/disputed, withdrawn), product (e.g. consumer loan, deposit account, etc), channel (e.g. digital, phone, in-person), issue category (e.g. fraudulent or unauthorized transactions, unfair treatment, unexpected fees, errors on statements,  etc.), resolution status (open, resolved with monetary compensation, resolved without compensation, escalated to ombudsman/regulator, other). Combined with resolution-time, compensation and other metrics, the number of customer complaints provides a critical, early-warning lens on conduct risk and customer-experience health. !- Definitions and concepts:  Complaints are expressions of dissatisfaction by (or on behalf of) customers that are related to their experiences with FSPs and can include any written, digital or recorded verbal statement made through any available channel, such as a branch, call-centre, email, social media, chatbots and other portals. Complaints may relate to the quality of a product or service, treatment by an FSP (including its agents and other third parties), or suspected wrongdoing. Complaints are different from general inquiries (e.g., where can I find an ATM?) or legal disputes between parties that may require formal dispute resolution. For more information, see for example CGAP's toolkit on using complaints data for market conduct supervision: https://www.cgap.org/research/publication/market-monitoring-tool-analysis-complaints-data and the Alliance for Financial Inclusion's framework on 'Complaint handling in Central Banks': https://www.afi-global.org/sites/default/files/publications/2020-04/AFI_CEMC_framework_AW_digital%20v2.pdf. !- Data requirements:  Database or log of customer complaints, detailing date of complaint and additional information, such as channel through which complaint was lodged, associated product or account, details or brief description of the complaint, and resolution status. !- Limitations and considerations: Complaints processes differ across FSPs in terms of steps/levels for routing, hand-over, escalations to higher management levels and to external ombudsman. Customer details and demographics of complainants are not always capture/stored on FSPs' systems, or may be stored in fragmented data bases. Complaints logged at aggregator sites/portals may not request customer demographics. Limited to officially logged complaints and/or maintaining records of inbound customer communications. Dependent on having electronic complaints management system.  Reporting culture: firms with easy‐to‐use channels may record more complaints than peers, even if service quality is similar—benchmark using severity and uphold rates. Under-reporting bias: vulnerable customers may forgo formal complaints; mystery-shopping and survey data can complement administrative counts. Duplicate cases: the same issue voiced through multiple channels can inflate totals unless robust deduplication exists. Product mix effects: complaint propensity varies—e.g., complex investments draw more grievances than basic savings; segment analysis is essential. Regulatory divergence: definitions and mandatory reporting thresholds differ across jurisdictions, complicating cross-border comparisons.</t>
+          <t>A measure of loan portfolio/credit risk assessment quality or financial distress among borrowers. !- Data requirements: Granular data that can yield (1) A count of unique borrowers of secured loans (those with collateral requirements) who subsequently had collateral seized by lender due to default over a specific period of time (e.g. past quarter or past year), (2) Total unique borrowers of secured loans over a specific period of time.</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>How does the number of complaints at each processing stage vary by gender? Are complaints disproportionately concentrated at certain processing stages for any gender? How do FSPs compare to market averages in the number of complaints at each processing stage?"</t>
+          <t>How does the share of customers whose collateral was seized due to default vary by gender and othe rkey sociodemographics? Are women more or less likely than men to have their collateral seized following loan default? How does the share differ by gender across different loan sizes, loan products,  types of financial service providers (FSP), collateral type (e.g., movable, immovable, alternative)? And how do any of these differences relate to seizure rates? Are women more likely to be subject to stricter collateral requirements or less flexible repayment terms that increase the likelihood of asset seizure?</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -6366,12 +6357,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Quality, Reputational and legal risk</t>
+          <t>Outcomes, Credit risk</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints issue category; Complaints processing status; Complaints filing channel; Complaints resolution outcome; Complaints resolution time</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Loan type; Collateral type; Loan size; Loan term; Interest rate category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -6392,26 +6383,26 @@
         </is>
       </c>
       <c r="D114">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Customer complaints resolved in the customer's favor</t>
+          <t>Customer complaints (number)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>% of customer complaints that were solved in the customer's favor in the most recent period</t>
+          <t>Number of customer complaints (including processing status, channels, type)</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>This indicator shows the share of complaints closed in the reference period that were resolved in the customer’s favor. It is a direct outcome metric for fair treatment and service quality. A higher “uphold rate” can indicate strong remediation and customer-centric policies; a very low rate may suggest poor triage, overly narrow eligibility rules, or weak guidance to customers on evidence requirements. Supervisors use it to benchmark conduct outcomes across firms and products; boards track it alongside complaint volumes and resolution times to target root-cause fixes. Tracked with complaint volume, resolution time, and compensation totals, this indicator provides a balanced view of consumer outcomes and conduct risk. !- Definitions and concepts: Resolved in the customer’s favor (upheld): final decision grants redress—monetary (refund/compensation/fee reversal) or non-monetary (policy correction, contract change, apology with tangible remedy). Many firms also count partially upheld cases; disclose whether partials are included. Denominator: all complaints closed in the period. Segment results by product, channel, and severtiy to avoid masking problem areas. !- Data requirements: Central complaint-management records with unique IDs, receipt date, closure date, product, channel, allegation type, decision outcome (upheld/partially/declined), and compensation amount. Deduplication logic across channels; linkages to ombudsman/regulator portals for escalations and reversals. Customer-base denominator (for intensity metrics) and service level agreement (SLA) timestamps for parallel monitoring* (see note below). !- Limitations and considerations: Classification discretion: definitions of “partial uphold” vary; publish inclusion rules. Case mix effects: a surge in low-merit mass claims can depress the percentage; report severity-adjusted or line-of-business cuts. Gaming risk: chasing high uphold rates may encourage paying weak claims; pair with fraud flags, root-cause fixes, and cost-per-case. Timing bias: complex cases close later and differ in uphold propensity; use rolling averages and track median resolution time. External outcomes: include overturned-on-appeal adjustments to reflect true customer outcome. *With granular time-stamped complaints data, timeliness of key milestones in the complaints resolution process can be tracked, for example time to acknowledge complaint, time to first response, time to resolution. With this data, supervisors can track not just outcomes, but also whether providers are meeting required timeframes per their own SLA.</t>
+          <t>This indicator tallies the formal expressions of dissatisfaction that retail or MSME clients lodge with a financial-service provider (or an external ombudsman) about products, services, or staff conduct over a specified period and can be normalized by dividing by the customer basis to obtain an intensity metric (e.g. complaints per 1,000 active customers). A rising complaint count can signal service-quality gaps, mis-selling, opaque fees, or inadequate disclosure—issues that erode trust and may escalate into regulatory sanctions or litigation. Supervisors can track both the absolute number and complaint-to-account ratios to test consumer-protection frameworks, prioritise thematic reviews, and assess whether rapid product roll-outs (e.g., digital lending, mobile wallets) are being matched by robust after-sales support. Where granular data or more detailed reporting templates permit, customer complaints can be disaggregated by processing status (e.g. received, accepted/rejected, in process, resolved, escalated/disputed, withdrawn), product (e.g. consumer loan, deposit account, etc), channel (e.g. digital, phone, in-person), issue category (e.g. fraudulent or unauthorized transactions, unfair treatment, unexpected fees, errors on statements,  etc.), resolution status (open, resolved with monetary compensation, resolved without compensation, escalated to ombudsman/regulator, other). Combined with resolution-time, compensation and other metrics, the number of customer complaints provides a critical, early-warning lens on conduct risk and customer-experience health. !- Definitions and concepts:  Complaints are expressions of dissatisfaction by (or on behalf of) customers that are related to their experiences with FSPs and can include any written, digital or recorded verbal statement made through any available channel, such as a branch, call-centre, email, social media, chatbots and other portals. Complaints may relate to the quality of a product or service, treatment by an FSP (including its agents and other third parties), or suspected wrongdoing. Complaints are different from general inquiries (e.g., where can I find an ATM?) or legal disputes between parties that may require formal dispute resolution. For more information, see for example CGAP's toolkit on using complaints data for market conduct supervision: https://www.cgap.org/research/publication/market-monitoring-tool-analysis-complaints-data and the Alliance for Financial Inclusion's framework on 'Complaint handling in Central Banks': https://www.afi-global.org/sites/default/files/publications/2020-04/AFI_CEMC_framework_AW_digital%20v2.pdf. !- Data requirements:  Database or log of customer complaints, detailing date of complaint and additional information, such as channel through which complaint was lodged, associated product or account, details or brief description of the complaint, and resolution status. !- Limitations and considerations: Complaints processes differ across FSPs in terms of steps/levels for routing, hand-over, escalations to higher management levels and to external ombudsman. Customer details and demographics of complainants are not always capture/stored on FSPs' systems, or may be stored in fragmented data bases. Complaints logged at aggregator sites/portals may not request customer demographics. Limited to officially logged complaints and/or maintaining records of inbound customer communications. Dependent on having electronic complaints management system.  Reporting culture: firms with easy‐to‐use channels may record more complaints than peers, even if service quality is similar—benchmark using severity and uphold rates. Under-reporting bias: vulnerable customers may forgo formal complaints; mystery-shopping and survey data can complement administrative counts. Duplicate cases: the same issue voiced through multiple channels can inflate totals unless robust deduplication exists. Product mix effects: complaint propensity varies—e.g., complex investments draw more grievances than basic savings; segment analysis is essential. Regulatory divergence: definitions and mandatory reporting thresholds differ across jurisdictions, complicating cross-border comparisons.</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>How do the percentages of complaints resolved in favor of customers vary by gender? Are any genders more likely to receive favorable resolutions? How do FSPs rank in terms of favorable resolutions by gender?</t>
+          <t>How does the number of complaints at each processing stage vary by gender? Are complaints disproportionately concentrated at certain processing stages for any gender? How do FSPs compare to market averages in the number of complaints at each processing stage?"</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6426,12 +6417,12 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Quality, Reputational and legal risk</t>
+          <t>Quality,</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints issue category; Complaints processing status; Complaints filing channel; Complaints resolution outcome; Complaints resolution time</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints filing channel; Complaints issue category; Complaints processing status; Complaints resolution outcome; Complaints resolution time</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6434,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Data privacy and protection</t>
+          <t>Complaints handling</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6452,26 +6443,26 @@
         </is>
       </c>
       <c r="D115">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Consent rate for FSP contact</t>
+          <t>Customer complaints resolved in the customer's favor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>% of customers who provide consent to be contacted in the future by the FSP for sales, awareness and new offerings</t>
+          <t>% of customer complaints that were solved in the customer's favor in the most recent period</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Measures the percentage of customers who have provided explicit consent to be contacted in the future by their financial service provider (FSP) for purposes such as product marketing, customer awareness campaigns, or information on new offerings. This indicator reflects how institutions manage customer permissions for communication under applicable data privacy and marketing regulations. Captures the extent of customer consent and data-use transparency in the financial system, serving as a proxy for compliance with consent-based communication standards and the balance between customer engagement and data protection. Tracking customer contact consents helps regulators and providers: Monitor compliance with data protection and privacy laws (e.g., GDPR-like frameworks, data protection acts); Assess ethical marketing practices and responsible customer engagement; Evaluate trust and willingness of customers to maintain open communication with FSPs; Understand customer attitudes toward data sharing and digital outreach. For supervisors, it provides a measurable view of market conduct, customer empowerment, and institutional transparency. High consent rates suggest strong customer trust and engagement, but may require close monitoring to ensure non-coercive consent collection and ethical marketing practices. Low consent rates may reflect privacy concerns, limited digital literacy, or overly complex consent processes. Changes over time can signal shifts in consumer sentiment or compliance practices following new regulations. !- Definitions and concepts: Consent: A freely given, informed, and specific agreement by a customer allowing the FSP to contact them for defined purposes. Data privacy regulation: Legal framework governing the collection, storage, and use of personal data, including consent requirements for marketing communications. !- Data requirements: Administrative data from FSP customer relationship management (CRM) or consent-management systems to obtain the number of customers who provided consent to be contact and the total number of customers.</t>
+          <t>This indicator shows the share of complaints closed in the reference period that were resolved in the customer’s favor. It is a direct outcome metric for fair treatment and service quality. A higher “uphold rate” can indicate strong remediation and customer-centric policies; a very low rate may suggest poor triage, overly narrow eligibility rules, or weak guidance to customers on evidence requirements. Supervisors use it to benchmark conduct outcomes across firms and products; boards track it alongside complaint volumes and resolution times to target root-cause fixes. Tracked with complaint volume, resolution time, and compensation totals, this indicator provides a balanced view of consumer outcomes and conduct risk. !- Definitions and concepts: Resolved in the customer’s favor (upheld): final decision grants redress—monetary (refund/compensation/fee reversal) or non-monetary (policy correction, contract change, apology with tangible remedy). Many firms also count partially upheld cases; disclose whether partials are included. Denominator: all complaints closed in the period. Segment results by product, channel, and severtiy to avoid masking problem areas. !- Data requirements: Central complaint-management records with unique IDs, receipt date, closure date, product, channel, allegation type, decision outcome (upheld/partially/declined), and compensation amount. Deduplication logic across channels; linkages to ombudsman/regulator portals for escalations and reversals. Customer-base denominator (for intensity metrics) and service level agreement (SLA) timestamps for parallel monitoring* (see note below). !- Limitations and considerations: Classification discretion: definitions of “partial uphold” vary; publish inclusion rules. Case mix effects: a surge in low-merit mass claims can depress the percentage; report severity-adjusted or line-of-business cuts. Gaming risk: chasing high uphold rates may encourage paying weak claims; pair with fraud flags, root-cause fixes, and cost-per-case. Timing bias: complex cases close later and differ in uphold propensity; use rolling averages and track median resolution time. External outcomes: include overturned-on-appeal adjustments to reflect true customer outcome. *With granular time-stamped complaints data, timeliness of key milestones in the complaints resolution process can be tracked, for example time to acknowledge complaint, time to first response, time to resolution. With this data, supervisors can track not just outcomes, but also whether providers are meeting required timeframes per their own SLA.</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>How do consent rates for customer contact vary by gender? Are any genders more likely to provide consent to be contacted? How do FSPs rank in terms of consent rates by gender?</t>
+          <t>How do the percentages of complaints resolved in favor of customers vary by gender? Are any genders more likely to receive favorable resolutions? How do FSPs rank in terms of favorable resolutions by gender?</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6481,17 +6472,17 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Quality,</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints filing channel; Complaints issue category; Complaints processing status; Complaints resolution outcome; Complaints resolution time</t>
         </is>
       </c>
     </row>
@@ -6503,28 +6494,88 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
+          <t>Data privacy and protection</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D116">
+        <v>234</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Consent rate for FSP contact</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>% of customers who provide consent to be contacted in the future by the FSP for sales, awareness and new offerings</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Measures the percentage of customers who have provided explicit consent to be contacted in the future by their financial service provider (FSP) for purposes such as product marketing, customer awareness campaigns, or information on new offerings. This indicator reflects how institutions manage customer permissions for communication under applicable data privacy and marketing regulations. Captures the extent of customer consent and data-use transparency in the financial system, serving as a proxy for compliance with consent-based communication standards and the balance between customer engagement and data protection. Tracking customer contact consents helps regulators and providers: Monitor compliance with data protection and privacy laws (e.g., GDPR-like frameworks, data protection acts); Assess ethical marketing practices and responsible customer engagement; Evaluate trust and willingness of customers to maintain open communication with FSPs; Understand customer attitudes toward data sharing and digital outreach. For supervisors, it provides a measurable view of market conduct, customer empowerment, and institutional transparency. High consent rates suggest strong customer trust and engagement, but may require close monitoring to ensure non-coercive consent collection and ethical marketing practices. Low consent rates may reflect privacy concerns, limited digital literacy, or overly complex consent processes. Changes over time can signal shifts in consumer sentiment or compliance practices following new regulations. !- Definitions and concepts: Consent: A freely given, informed, and specific agreement by a customer allowing the FSP to contact them for defined purposes. Data privacy regulation: Legal framework governing the collection, storage, and use of personal data, including consent requirements for marketing communications. !- Data requirements: Administrative data from FSP customer relationship management (CRM) or consent-management systems to obtain the number of customers who provided consent to be contact and the total number of customers.</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>How do consent rates for customer contact vary by gender? Are any genders more likely to provide consent to be contacted? How do FSPs rank in terms of consent rates by gender?</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D116">
+      <c r="D117">
         <v>284</v>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="E117" t="inlineStr">
         <is>
           <t>Annual percentage rate (APR) for retail credit</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>Average cost of borrowing money, including fees to get the loan, as a% of the loan principal (except for credit cards)</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>APR is the standardized annualized cost of borrowing that incorporates the contractual interest rate plus certain up-front or periodic fees required to obtain and maintain the credit. It lets consumers compare offers across lenders and products on a like-for-like basis, and helps supervisors monitor pricing fairness and market competitiveness. Unlike a simple “nominal” rate, APR reflects timing of cash flows and required charges, so it better approximates the true price of credit. !- Definitions and concepts: Installment credit APR (actuarial method): the internal rate of return (IRR) that equates the amount advanced to the borrower with the present value of all required payments (principal, interest, and included fees), expressed on an annual basis.
 Revolving credit APR (cards/overdrafts): the periodic rate applied to the average daily balance, annualized (e.g., daily rate × 365 or monthly rate × 12), plus disclosure of any mandatory fees as prescribed. Scope of fees: typically includes origination/processing fees and compulsory charges; excludes penalty fees and optional add-ons (unless mandated). APR vs. EIR: APR is a consumer disclosure metric (jurisdiction-specific rules); EIR is an accounting yield used to recognize interest income.!- Data requirements: Contract terms: principal advanced, repayment schedule (dates/amounts), nominal rate, compounding frequency, and variable-rate index/margins. Included fees: origination/processing, mandatory maintenance or platform fees, financed vs. paid-in-cash. For revolving products: periodic rate(s), balance computation method (average daily balance), mandatory annual fees, grace-period rules, promotional/teaser rates.
@@ -6532,84 +6583,24 @@
 Promotions &amp; step-ups: teaser or deferred-interest offers can make snapshot APRs unrepresentative—show lifetime-effective examples when possible. Variable rates: APR at origination may understate future cost if reference rates rise. Loan term effects: fixed fees loom larger on short tenors; present both APR and the fee share of cost for transparency.</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>Are there gender disparities in the APR applied to loans disbursed to women and men, including MSMEs by gender of ownership? Do women borrowers systematically face higher average APRs than men within the same loan type, amount range, or provider category? Are higher APRs for women associated with smaller loan sizes, shorter maturities, or higher perceived credit risk? Do FSPs with greater gender diversity or stronger inclusion policies show smaller gender gaps in average APRs? How do APR differences relate to borrower profiles and do they suggest the presence of gender-based pricing bias or structural credit segmentation?</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
         <is>
           <t>Financial inclusion; Market development</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="K117" t="inlineStr">
         <is>
           <t>Quality, Competition</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Data privacy and protection</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D117">
-        <v>235</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Consents for sharing data with third-parties</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>% of customers who have given explicit consent for their data to be shared by FSPs with third parties, for various purposes</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>This indicator shows how many customers have actively opted in to let a financial service provider (FSP) share their data with external parties—for open-banking/aggregation, credit scoring, fraud prevention, marketing, analytics, etc. A higher share can reflect strong digital adoption and trust; low or falling rates may signal poor consent UX, unclear value propositions, or privacy concerns. It helps compliance teams evidence lawfulness, product teams gauge partner-integration reach, and supervisors assess the maturity of consent-based data-sharing ecosystems. !- Definitions and concepts: Explicit consent: a clear, affirmative action (e.g., checked box, strong-customer-authenticated authorization) tied to a specific purpose, with intelligible notice and the ability to withdraw at any time. Active consent: consent that is valid as of the reference date (not expired, not withdrawn, not superseded). Purpose taxonomy: e.g., account information services (AIS), payment initiation services (PIS), credit decisioning/bureau pulls, fraud/AML tools, personalised marketing, data portability. Metric: % of customer with active consent for purpose p = [# of unique customers with at least 1 active consent for p / # of active customers] x 100%. Indicator companions: Any-purpose consent, consents per consenting customer and revocation rate. !- Data requirements: Consent ledger that includes: customer ID, purpose(s) granted, third-party identity, channel, timestamp, expiry/refresh cycle, version of the privacy notice, proof of consent (hash, audit trail, SCA event). Status events: withdrawals, expiries, scope changes, third-party disconnects. Reference universe: deduplicated active-customer list (define “active”: e.g., ≥1 product in force or ≥1 login/transaction in last 12 months). !- Limitations and considerations: Granularity &amp; fragmentation: a customer may consent per app, per account, and per purpose; avoid double counting by using unique customers and report purpose-level cuts. Expiry &amp; refresh: open-banking tokens often have short authorizations; snapshot dates vs. rolling windows will yield different figures—disclose method. Consumer protection risk: high opt-ins driven by coercive UX can backfire (complaints, revocations); pair with revocation rate, time-to-revocation, and complaints about data sharing. Coverage gaps: legacy channels without digital capture may under-record historical consents; backfill or disclose limitations.</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>How do consent rates for data sharing with third parties vary by gender? Are any genders more likely to provide consent for data sharing? How do FSPs rank in terms of consent rates for data sharing by gender?</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Market development</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Competition</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -6626,35 +6617,35 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Fair treatment</t>
+          <t>Data privacy and protection</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D118">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Late penalty charges/fees on retail credit</t>
+          <t>Consents for sharing data with third-parties</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Income from penalty fees as % of total net interest income</t>
+          <t>% of customers who have given explicit consent for their data to be shared by FSPs with third parties, for various purposes</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>This indicator shows how much of a lender is relying on penalty fees for income. Revenue from penalty fees and other charges applied when a loan payment is late is compared with the total gross interest income. A high share could signal borrower stress and potential conduct risk (reliance on punitive pricing). Boards and supervisors use the metric to assess earnings quality, pricing fairness. !- Definitions and concepts: Penalty/default fees and charges: the fees and costs charged once a loan  is past due. Numerator (preferred “incremental” view): Penalty actually recognized as income on retail loans during the period. Denominator: Gross interest income. !- Data requirements: General-ledger mapping that identifies penalty income at product level. Period interest income totals for the denominator.  !- Limitations and considerations: Mix effects: card-heavy books show higher shares of penalty income; segment by product. Conduct lens: pair with % customers incurring penalty charges, related complaints.</t>
+          <t>This indicator shows how many customers have actively opted in to let a financial service provider (FSP) share their data with external parties—for open-banking/aggregation, credit scoring, fraud prevention, marketing, analytics, etc. A higher share can reflect strong digital adoption and trust; low or falling rates may signal poor consent UX, unclear value propositions, or privacy concerns. It helps compliance teams evidence lawfulness, product teams gauge partner-integration reach, and supervisors assess the maturity of consent-based data-sharing ecosystems. !- Definitions and concepts: Explicit consent: a clear, affirmative action (e.g., checked box, strong-customer-authenticated authorization) tied to a specific purpose, with intelligible notice and the ability to withdraw at any time. Active consent: consent that is valid as of the reference date (not expired, not withdrawn, not superseded). Purpose taxonomy: e.g., account information services (AIS), payment initiation services (PIS), credit decisioning/bureau pulls, fraud/AML tools, personalised marketing, data portability. Metric: % of customer with active consent for purpose p = [# of unique customers with at least 1 active consent for p / # of active customers] x 100%. Indicator companions: Any-purpose consent, consents per consenting customer and revocation rate. !- Data requirements: Consent ledger that includes: customer ID, purpose(s) granted, third-party identity, channel, timestamp, expiry/refresh cycle, version of the privacy notice, proof of consent (hash, audit trail, SCA event). Status events: withdrawals, expiries, scope changes, third-party disconnects. Reference universe: deduplicated active-customer list (define “active”: e.g., ≥1 product in force or ≥1 login/transaction in last 12 months). !- Limitations and considerations: Granularity &amp; fragmentation: a customer may consent per app, per account, and per purpose; avoid double counting by using unique customers and report purpose-level cuts. Expiry &amp; refresh: open-banking tokens often have short authorizations; snapshot dates vs. rolling windows will yield different figures—disclose method. Consumer protection risk: high opt-ins driven by coercive UX can backfire (complaints, revocations); pair with revocation rate, time-to-revocation, and complaints about data sharing. Coverage gaps: legacy channels without digital capture may under-record historical consents; backfill or disclose limitations.</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>What percentages of net interest income are attributable to penalties and other punitive charges earned from borrowers of unsecured loans/lines of credit, and how do these vary by gender across age bands and location types, at a total market level and by relevant FSP/type? How do these percentages compare across relevant FSPs/types and against market norms across age bands and location types? How do gender disparities manifest in these percentages at a total market level and by relevant FSP/type?</t>
+          <t>How do consent rates for data sharing with third parties vary by gender? Are any genders more likely to provide consent for data sharing? How do FSPs rank in terms of consent rates for data sharing by gender?</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6664,17 +6655,17 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Market development</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -6695,108 +6686,108 @@
         </is>
       </c>
       <c r="D119">
+        <v>260</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Late penalty charges/fees on retail credit</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Income from penalty fees as % of total net interest income</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>This indicator shows how much of a lender is relying on penalty fees for income. Revenue from penalty fees and other charges applied when a loan payment is late is compared with the total gross interest income. A high share could signal borrower stress and potential conduct risk (reliance on punitive pricing). Boards and supervisors use the metric to assess earnings quality, pricing fairness. !- Definitions and concepts: Penalty/default fees and charges: the fees and costs charged once a loan  is past due. Numerator (preferred “incremental” view): Penalty actually recognized as income on retail loans during the period. Denominator: Gross interest income. !- Data requirements: General-ledger mapping that identifies penalty income at product level. Period interest income totals for the denominator.  !- Limitations and considerations: Mix effects: card-heavy books show higher shares of penalty income; segment by product. Conduct lens: pair with % customers incurring penalty charges, related complaints.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>What percentages of net interest income are attributable to penalties and other punitive charges earned from borrowers of unsecured loans/lines of credit, and how do these vary by gender across age bands and location types, at a total market level and by relevant FSP/type? How do these percentages compare across relevant FSPs/types and against market norms across age bands and location types? How do gender disparities manifest in these percentages at a total market level and by relevant FSP/type?</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Fair treatment</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="D120">
         <v>185</v>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="E120" t="inlineStr">
         <is>
           <t>Processing and application fees or PAF (as % of loan principal)</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F120" t="inlineStr">
         <is>
           <t>PAF as % of loan principal in unsecured credit operations</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t>This indicator expresses the total up-front charges borrowers pay to originate an unsecured loan—processing fees, application fees, documentation charges—as a percentage of the loan’s principal amount. Because unsecured credit often targets price-sensitive segments and carries higher risk-based interest rates, excessive PAFs can materially raise the all-in cost of borrowing, undermine affordability tests, and trigger consumer-protection scrutiny. Tracking the ratio helps regulators detect predatory pricing, compare lenders’ transparency practices, and gauge competition in loan-origination services. For lenders, it is a barometer of non-interest revenue reliance and a lever for recouping acquisition costs. Processing &amp; Application Fees (PAF): any non-refundable charge levied at or before disbursement for administrative tasks (credit checks, KYC, documentation, platform usage). Late-payment or insurance fees are excluded.
 PAF ratio (simple): [Total PAF charged/Gross loan principal]×100%
 Where multiple partial disbursements occur, use the aggregate principal amount. Annualised impact: when PAFs are capitalised into the Effective Annual Percentage Rate (APR), their weight declines as term length rises—monitor both absolute and APR-embedded views. !- Data requirements: Loan-level records capturing principal, disbursement date, PAF amount, and any rebates for cancellations. Product codes distinguishing personal instalment loans, credit-card cash advances, payday/BNPL equivalents. Borrower demographics and channel identifiers (branch, mobile app, marketplace) for segmentation. Accounting entries showing whether fees are recognised up-front (IFRS 15 “contract costs”) or amortised via the effective-interest-rate (EIR) method. !- Limitations and considerations: Amortisation differences: Lenders using EIR spread PAFs over the loan’s life; comparing ratios on a cash basis versus amortised income can mislead. Bundled products: Cross-selling (e.g., credit-life insurance) may shift income from PAF to commissions, understating the ratio. Regulatory caps &amp; disclosures: Jurisdictions with fee ceilings or mandatory APR disclosures compress PAF ratios; cross-country benchmarking must control for such rules. Loan term effects: Short-tenor payday or BNPL loans show high PAF percentages even when absolute fees are small; interpret in context of maturity profile and APR. Waivers &amp; promotions: Temporary fee holidays for marketing campaigns can distort time-series trends—flag promotional periods separately. Should FSPs not be allowed/willing to share sensitive revenue data, ratios/percentages can be performed in-house and then shared with regulator.</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="H120" t="inlineStr">
         <is>
           <t>What are the origination fee percentages as a share of loan principal by gender? Are there gender disparities in the origination fee percentages incurred? How do FSPs rank in terms of origination fee percentages by gender?</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Data privacy and protection</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D120">
-        <v>232</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Data breaches</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>% of customers affected by data breaches</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>A measure of the depth of cyberattacks or other data security breach that result in unauthorized access to customer data. Definitions and concept: A data breach is any security incident in which unauthorized parties access sensitive or confidential information, including personal data (tax numbers, ID information, bank account numbers, healthcare data) and corporate data (customer records, intellectual property, financial information). Data requirement: Number of customers whose data was accessed without authorization during a specified period of time (e.g. quarter or year); Total number of customers at the beginning of the specified period (e.g. quarter or year).</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>How does the percentage of customers affected by data breaches vary by gender? Are any genders disproportionately affected by data breaches? Are data breaches more frequent in certain types of FSPs? Are data breaches more common in specific channels or interfaces?"</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>Quality, Operational risk</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -6808,35 +6799,35 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Depositor protection</t>
+          <t>Data privacy and protection</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Savings</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D121">
-        <v>15</v>
+        <v>232</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Deposit accounts covered by direct deposit insurance</t>
+          <t>Data breaches</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Volume and value (balances) of deposit accounts covered by direct deposit insurance</t>
+          <t>% of customers affected by data breaches</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>This indicator counts (or expresses as a percentage) the deposit accounts that fall within the scope of an explicit, statutory deposit insurance scheme (DIS) or deposit guarantee fund. It helps supervisors gauge how much of the retail/MSME funding base is protected against bank failure. This is key for financial stability monitoring, payout readiness, and for calibrating the deposit insurance/guarantee fund. High coverage supports confidence and can dampen run dynamics. Source: https://www.iadi.org/uploads/cprevised2014nov.pdf. !- Definitions and concepts: Covered (eligible) account: a deposit type included by law. Fully insured vs. partially insured: “Fully insured” balances are ≤ the coverage limit per depositor, per bank, per ownership category; “covered/eligible” may include accounts whose balances exceed the cap (partially insured). Ownership categories: individual, joint, trust/fiduciary, retirement—rules vary by jurisdiction and affect aggregation across accounts. Indicator variants: % Eligible accounts = eligible deposit accounts ÷ total deposit accounts. Insured balance share = insured amounts in eligible accounts ÷ total deposit balances in eligible accounts. Dormancy: dormant accounts may be treated differently in coverage statistics.</t>
+          <t>A measure of the depth of cyberattacks or other data security breach that result in unauthorized access to customer data. Definitions and concept: A data breach is any security incident in which unauthorized parties access sensitive or confidential information, including personal data (tax numbers, ID information, bank account numbers, healthcare data) and corporate data (customer records, intellectual property, financial information). Data requirement: Number of customers whose data was accessed without authorization during a specified period of time (e.g. quarter or year); Total number of customers at the beginning of the specified period (e.g. quarter or year).</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of deposit accounts covered by direct deposit insurance? How do these disparities vary by age, income level, and geographic location? Are certain gender groups, especially within vulnerable or low-income populations, less likely to hold insured deposit accounts? How do the average insured deposit account balances differ across genders, and what might this indicate about savings behavior, access to financial protection, or economic security? Do financial service providers with higher levels of gender diversity in leadership or staff tend to offer more equitable access to insured deposit accounts and balanced coverage across genders? Additionally, how do gender differences in insured deposit accounts relate to broader financial inclusion and resilience against financial shocks?</t>
+          <t>How does the percentage of customers affected by data breaches vary by gender? Are any genders disproportionately affected by data breaches? Are data breaches more frequent in certain types of FSPs? Are data breaches more common in specific channels or interfaces?"</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6846,17 +6837,17 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
+          <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Quality, Suitability, Depositor protection</t>
+          <t>Quality, Operational risk</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Deposit account type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -6877,19 +6868,79 @@
         </is>
       </c>
       <c r="D122">
+        <v>15</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Deposit accounts covered by direct deposit insurance</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Volume and value (balances) of deposit accounts covered by direct deposit insurance</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>This indicator counts (or expresses as a percentage) the deposit accounts that fall within the scope of an explicit, statutory deposit insurance scheme (DIS) or deposit guarantee fund. It helps supervisors gauge how much of the retail/MSME funding base is protected against bank failure. This is key for financial stability monitoring, payout readiness, and for calibrating the deposit insurance/guarantee fund. High coverage supports confidence and can dampen run dynamics. Source: https://www.iadi.org/uploads/cprevised2014nov.pdf. !- Definitions and concepts: Covered (eligible) account: a deposit type included by law. Fully insured vs. partially insured: “Fully insured” balances are ≤ the coverage limit per depositor, per bank, per ownership category; “covered/eligible” may include accounts whose balances exceed the cap (partially insured). Ownership categories: individual, joint, trust/fiduciary, retirement—rules vary by jurisdiction and affect aggregation across accounts. Indicator variants: % Eligible accounts = eligible deposit accounts ÷ total deposit accounts. Insured balance share = insured amounts in eligible accounts ÷ total deposit balances in eligible accounts. Dormancy: dormant accounts may be treated differently in coverage statistics.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in the number of deposit accounts covered by direct deposit insurance? How do these disparities vary by age, income level, and geographic location? Are certain gender groups, especially within vulnerable or low-income populations, less likely to hold insured deposit accounts? How do the average insured deposit account balances differ across genders, and what might this indicate about savings behavior, access to financial protection, or economic security? Do financial service providers with higher levels of gender diversity in leadership or staff tend to offer more equitable access to insured deposit accounts and balanced coverage across genders? Additionally, how do gender differences in insured deposit accounts relate to broader financial inclusion and resilience against financial shocks?</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Quality, Suitability,</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Deposit account type</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Depositor protection</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Savings</t>
+        </is>
+      </c>
+      <c r="D123">
         <v>16</v>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="E123" t="inlineStr">
         <is>
           <t>G2P accounts covered by deposit insurance</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>% of all accounts receiving G2P payments that are covered by deposit protection</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>This indicator helps analyze the extent to which low-value accounts are covered by deposit insurance or other protection. It focuses on account holders who are recipients of G2P programs. It quantifies how many of the government-to-person (G2P) payments recipients are protected by an explicit deposit insurance scheme or guarantee fund. It can be shown as (a) the share of G2P accounts that are eligible/fully insured and/or (b) the insured share of G2P balances. This indicator informs strategies for insurance/coverage payouts and the calibration of the deposit insurance fund. Definitions  and concepts: G2P account: an account that receives social transfers, government pensions, subsidies, or cash-benefit programs.
 Covered (eligible) vs. fully insured: “Eligible” products fall within the deposit insurance scope; “fully insured” means the balance per beneficiary per insured bank does not exceed the coverage cap. 
@@ -6898,197 +6949,137 @@
 Core-banking (and, where applicable, e-money) extracts: product code, ownership category, end-of-day balance, currency. Rules engine encoding national deposit-insurance scope, limits, and aggregation logic (per depositor—per bank). Sub-ledger data for pooled/FBO accounts to support pass-through eligibility. Timing sensitivity: balances spike on disbursement days; define the snapshot (e.g., month-end vs. T+2 after payout).</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="H123" t="inlineStr">
         <is>
           <t>Are there gender disparities in the number of G2P accounts covered by deposit insurance? How do these disparities vary across different age groups, income levels, and geographic locations? Are women and other gender groups within vulnerable populations less likely to have G2P accounts that are insured, potentially affecting their financial security? How do the average balances of insured G2P accounts compare across genders, and what does this imply about economic empowerment and financial resilience? Do government programs and financial service providers with greater gender diversity in design or delivery show more equitable insurance coverage of G2P accounts? Additionally, how do gender differences in insured G2P accounts influence overall inclusion and access to social safety nets?</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
+      <c r="K123" t="inlineStr">
         <is>
           <t>Quality, Suitability, Depositor protection</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+    <row r="124">
+      <c r="A124" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D123">
+      <c r="D124">
         <v>183</v>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>Average cost-to-borrower for unsecured retail lending</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>Average topline revenue earned from unsecured retail credit operations (as percentage of the average outstanding unsecured credit)</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>This indicator is a portfolio-level proxy for the all-in price actually paid by customers on unsecured retail credit during the period. It answers: How many currency units of revenue did the lender earn for each 100 units of average unpaid balance? Rising values may reflect higher base rates, heavier fee reliance (e.g., late/over-limit charges), or a shift toward shorter-tenor/high-yield products; falling values can indicate competitive pressure, promotional pricing, or relief programs. Boards, supervisors, and consumer-protection teams use it to benchmark pricing fairness, earnings quality, and sensitivity to interest-rate cycles. !- Definitions and concepts: Recommended numerator (topline revenue, P&amp;L-recognized): Interest income (EIR basis) + contractual fees (origination, servicing) + penalty/default interest actually recognized + punitive fees (late, over-limit, returned-payment) − waivers/reversals. Denominator: Average outstanding unsecured retail balances (use Average Daily Balance - ADB). Formula: Cost-to-customer yield = Topline revenue from unsecured retail credit divded by Average outstanding unsecured retail balances. This indicator can be reported separately for interest, contractual fees and penalities if the data is available and when the period is less than 12 months, report an annualized figure. !- Data requirements: General ledger and product-level revenue broken into interest, contractual fees, penalty interest, punitive fees; flags for waivers/reversals and non-accrual. Loan/card-level balances to compute ADB, segmented by product (cards, instalment, overdraft, BNPL), channel, and risk bucket. Accounting policies: EIR vs. cash, Stage-3/non-accrual treatment, capitalization rules.
 FX mapping for multi-currency portfolios. !- Limitations and considerations: Comparability: EIR vs. cash accounting and non-accrual practices differ; disclose methodology. Mix effects: more revolving/short-tenor loans inflate yields; always segment. Penalty bias: high ratios may be driven by a small cohort repeatedly paying fees—track % customers incurring penalties. Promotions/teasers: intro 0% and fee holidays distort short periods—show trailing-12-month and cohort views. Scope creep: exclude bundled insurance premiums or merchant discounts (BNPL) unless consistently included and disclosed.</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="H124" t="inlineStr">
         <is>
           <t>Are there gender disparities in the percentage of topline revenue relative to outstanding loan balances? Is there any gender paying comparatively more than market percentages for the same account types? How do FSPs rank in terms of these percentages by gender?</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
+    <row r="125">
+      <c r="A125" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D124">
+      <c r="D125">
         <v>181</v>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>Revenue generated by unsecured credit</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>% of total topline revenue attributable to unsecured credit operations and interest and non-interest revenue proportions</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>This indicator captures the total income that a lending institution earns from unsecured credit products—credit cards, personal instalment loans, overdrafts, payday and buy-now-pay-later (BNPL) facilities—over a reporting period. Because unsecured lending is typically high-yield and high-risk, tracking its revenue helps supervisors and management understand how much of the institution’s top line depends on products that are more sensitive to economic downturns, job-market shocks and aggressive competition. A rising share can boost short-term profitability, but it may also presage higher future credit losses and conduct-risk concerns if underwriting standards slip. !- Definitions and concepts: Unsecured credit – loans that are not backed by collateral; repayment relies on the borrower’s cash flow and creditworthiness.
 Revenue components – Interest income (accrued and collected) from outstanding balances. Fee income: annual fees, origination fees, late-payment charges, interchange on card transactions, BNPL merchant discount rates. Net insurance or payment-protection premiums (if bundled) may be included subject to local accounting rules.
 Revenue share metric: Unsecured-credit revenue ÷ Total lending revenue expresses concentration risk. Risk-adjusted yield – revenue net of credit-loss provisions gives a clearer view of economic profitability. !- Data requirements: Product-level general-ledger extracts segregating interest, fees and other income. Loan-level flags identifying collateral status (secured vs. unsecured). Average daily or month-end balances to compute effective yields. Associated credit-loss provisions and write-offs for risk-adjusted analysis. !- Limitations and considerations: Mixed products: Some personal loans are partially secured (e.g., salary-linked) or carry optional collateral; clear taxonomy is essential. Fee recognition rules: Capitalised origination fees amortised under effective-interest-rate (EIR) accounting may blur timing comparisons across banks or jurisdictions. Regulatory caps: Interest-rate or fee ceilings (e.g., usury limits) affect revenue potential and comparability. Promotional pricing: Introductory 0 % card offers or BNPL “pay-in-4” models generate deferred revenue; headline figures may understate future income. Economic cyclicality: Unsecured-credit revenue can fall sharply in recessions as balances contract and charge-offs rise; pairing with delinquency and provision metrics is crucial for a full risk-return picture.</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="H125" t="inlineStr">
         <is>
           <t>What proportion of total topline revenue comes from unsecured credit operations, and are there gender disparities in this distribution? How do FSPs rank in their reliance on unsecured credit revenue by gender?</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Fair treatment</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D125">
-        <v>198</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Insurance approved claims not paid</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>% of approved/accepted claims that remain unpaid to customers</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>This indicator shows the share of claims that have been approved (final liability accepted) but not yet disbursed to the claimant. A high rate flags operational bottlenecks or weak payout controls, directly impacting customer outcomes. Track alongside claims turnaround time, claims rejection rates, and complaints, to get a full picture of payout effectiveness and customer fairness. !- Definitions and concepts: Approved / accepted claim: a claim with a final decision to pay (post-analysis), a recorded payable, and no outstanding dispute. Unpaid status: no successful settlement to the beneficiary by period end. Formula: Amount weighted (unpaid approved amount ÷ approved amount) reveal economic impact. Count basis (# approved claims not paid by cut-off ÷ # claims approved in teh period). SLA variant: % not paid within X days of approval (e.g., 5/10/30 days) to neutralize end-period timing bias. Treatment of partial payments: disclose whether partially paid claims are counted as unpaid or excluded. The indicator may also track the reasons for non-payment, if these are standardized for reporting. !- Limitations and considerations: Cut-off effects: approvals late in the period will naturally be unpaid—use the SLA variant and report both snapshot and flow views. Reopened claims / appeals: specify whether reversals after approval are removed from both numerator and denominator. Segmentation: monitor by line of business, payment method, channel, and claim size to target fixes.</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>How do the average values of outstanding insurance claims compare by gender? Is there a gender group with consistently higher average unpaid claims? How do different FSPs rank in terms of outstanding claims by gender? Are vulnerable gender groups disproportionately affected by delayed or unpaid claims?</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>Quality, Reputational and legal risk</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -7109,164 +7100,164 @@
         </is>
       </c>
       <c r="D126">
+        <v>198</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Insurance approved claims not paid</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>% of approved/accepted claims that remain unpaid to customers</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>This indicator shows the share of claims that have been approved (final liability accepted) but not yet disbursed to the claimant. A high rate flags operational bottlenecks or weak payout controls, directly impacting customer outcomes. Track alongside claims turnaround time, claims rejection rates, and complaints, to get a full picture of payout effectiveness and customer fairness. !- Definitions and concepts: Approved / accepted claim: a claim with a final decision to pay (post-analysis), a recorded payable, and no outstanding dispute. Unpaid status: no successful settlement to the beneficiary by period end. Formula: Amount weighted (unpaid approved amount ÷ approved amount) reveal economic impact. Count basis (# approved claims not paid by cut-off ÷ # claims approved in teh period). SLA variant: % not paid within X days of approval (e.g., 5/10/30 days) to neutralize end-period timing bias. Treatment of partial payments: disclose whether partially paid claims are counted as unpaid or excluded. The indicator may also track the reasons for non-payment, if these are standardized for reporting. !- Limitations and considerations: Cut-off effects: approvals late in the period will naturally be unpaid—use the SLA variant and report both snapshot and flow views. Reopened claims / appeals: specify whether reversals after approval are removed from both numerator and denominator. Segmentation: monitor by line of business, payment method, channel, and claim size to target fixes.</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>How do the average values of outstanding insurance claims compare by gender? Is there a gender group with consistently higher average unpaid claims? How do different FSPs rank in terms of outstanding claims by gender? Are vulnerable gender groups disproportionately affected by delayed or unpaid claims?</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Quality, Reputational and legal risk</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Fair treatment</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D127">
         <v>256</v>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E127" t="inlineStr">
         <is>
           <t>Insurance claims declined</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>% of claims logged by policyholders that are declined prior to substantive analysis</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>This indicator captures the share of claim notifications the insurer does not accept for assessment at the front door—typically during first notice of loss (FNOL)/triage—because they are ineligible or incomplete. A high intake-decline rate can point to unclear policy wording, poor customer guidance, data-capture frictions, or overly strict gatekeeping. It is a key conduct-risk and customer-experience signal and, operationally, helps size avoidable workload versus genuinely assessable claims. Claim logged / FNOL: the moment a policyholder submits a claim or loss notice. Declined at intake (non-acceptance): the insurer refuses to open an assessable claim before investigation (e.g., policy not in force, peril not covered, waiting period, duplicate claim, claim below deductible/threshold, incomplete mandatory data not cured within a set window). Indicator formula (count basis): # claims declined at intake in period divided by # claim notifications received in period . Variants: exclude cured cases later resubmitted; report by product/channel. !- Data requirements: Claims-intake system fields: FNOL timestamp, policy ID/status at loss date, coverage/peril checks, deductible, mandatory-document checklist, triage outcome. Standardised reason codes (e.g., not covered, lapsed, duplicate, below excess, incomplete info). Deduplication logic (policyholder ID + incident date + peril). Linkage to resubmissions/appeals and to complaint records for outcome tracking. !- Limitations and considerations: Definition variance: what counts as “prior to analysis” differs; some firms place incomplete cases in “pending info” instead of “declined,” affecting comparability.
 Gaming risk: shifting cases to “withdrawn” or “pending” to improve this metric; require audit trails and age-off rules. Mix effects: products with low deductibles or mandatory documents (e.g., health) have different baseline rates—segment results. Customer fairness: high early declines may reflect confusing onboarding or exclusion wording; monitor alongside claims rejection rate (post-assessment), turnaround time, and complaints upheld. Resubmission policy: disclose whether cured resubmissions are excluded from the numerator to avoid double counting.</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>What percentage of claims logged by policyholders are declined, disaggregated by gender? How do these decline rates vary across FSPs, policy types, age groups, and locations? Are there notable gender disparities in claim declines at the market level or within specific providers? Are women or other gender groups more likely to face claim denial?</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
         <is>
           <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>Quality, Reputational and legal risk</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Quality,</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D127">
+      <c r="D128">
         <v>60</v>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>Insurance claims rejection rate</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>% of all insurance claims that are rejected by insurers (post-analysis)</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>The claims rejection rate shows the share of claims that an insurer declines to pay—fully or partially—relative to the total number (or value) of claims submitted in a period. Because denial directly affects customer trust, supervisors use the metric to monitor fair treatment outcomes, detect aggressive underwriting or opaque policy wording, and flag operational shortcomings. A sudden rise may presage reputational damage, regulatory sanctions, or litigation costs, while an unusually low rate can hint at lax fraud controls or inadequate claims processing. !- Definitions and concepts: Claims rejected (denied): claims for which the insurer issues a final communication refusing payment on contractual grounds (e.g., policy exclusions, lapsed cover, misrepresentation) or on fraud findings. !- Limitations and considerations: Definition divergence: Some regimes class “claims closed without payment” (due to missing documents) as rejections; others record them as pending, complicating cross-market comparison. Fraud vs. technical denial: Combining fraud rejections with contractual exclusions can blur very different issues. Separate reporting is best practice. Volume vs. value: A single large, legitimately denied loss can distort amount-based ratios; analysts should monitor both count and value metrics.
 Appeals and reversals: Denials overturned on review lower true rejection rates; timely data updates are essential.
 Incentive effects: Over-emphasis on low rejection rates may weaken fraud vigilance, whereas strict targets can push staff toward technical denials—pair the indicator with complaint ratios, turnaround times, and fraud-detection statistics for balanced oversight.</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="H128" t="inlineStr">
         <is>
           <t>Are there gender disparities in the rejection rates of insurance claims, including for MSMEs by owner gender? Which types of policies or claims see higher rejection rates, and do these differ by gender? How does claim rejection relate to coverage levels and turnaround times? Do FSPs with higher gender diversity have lower rejection rates for vulnerable gender groups?</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
         <is>
           <t>Quality</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Fair treatment</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D128">
-        <v>201</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Insurance claims settlement ratio</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>% of insurance claims logged by policyholders that have been paid by insurers</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Measures the percentage of insurance claims settled by an insurer out of the total claims it receives. It is a direct measure of an insurer's reliability and its commitment to fulfilling its primary promise to policyholders. This indicator is a cornerstone of conduct supervision, as it provides a quantitative view of how an insurer treats its customers at their most critical moment of need. For prudential supervisors, it could help analysis of operational and reputational risk. This indicator should be used together with other indicators on the performance of the claims process in the insurance sector.</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>How do claim settlement ratios vary by gender? Are any gender groups receiving lower settlement ratios compared to the market average? Are there FSPs with particularly low or high settlement ratios for certain genders? How do these ratios intersect with policy type and customer demographics?</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>Outcomes, Reputational and legal risk</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -7292,215 +7283,215 @@
         </is>
       </c>
       <c r="D129">
+        <v>201</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Insurance claims settlement ratio</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>% of insurance claims logged by policyholders that have been paid by insurers</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Measures the percentage of insurance claims settled by an insurer out of the total claims it receives. It is a direct measure of an insurer's reliability and its commitment to fulfilling its primary promise to policyholders. This indicator is a cornerstone of conduct supervision, as it provides a quantitative view of how an insurer treats its customers at their most critical moment of need. For prudential supervisors, it could help analysis of operational and reputational risk. This indicator should be used together with other indicators on the performance of the claims process in the insurance sector.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>How do claim settlement ratios vary by gender? Are any gender groups receiving lower settlement ratios compared to the market average? Are there FSPs with particularly low or high settlement ratios for certain genders? How do these ratios intersect with policy type and customer demographics?</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Outcomes, Reputational and legal risk</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Fair treatment</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D130">
         <v>59</v>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>Insurance claims turnaround time</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>Average number of days to process insurance claims</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>This indicator captures the average calendar days an insurer takes to settle a claim—from the claim filing date to the final payment or formal denial. It is a direct yard-stick of operational efficiency and customer experience. Shorter turnaround times (TATs) enhance policy-holder trust, limit reputational risk, and can lower claims handling expenses. Supervisors use the metric to enforce fair-treatment rules, while actuaries and underwriters link it to reserving accuracy—prolonged settlement can signal documentation bottlenecks, fraud investigations, policy transparency issues, or catastrophic complexity that may keep outstanding reserves elevated. !- Definitions and concepts:  Start point – the timestamp when the insurer first receives the claim request. End point – the date the insurer issues full payment, partial final payment, or a written denial. Average turnaround time (TAT) – arithmetic mean; many firms also monitor median and 90th-percentile to limit outlier masking.
 Segmented TATs – tracked by line of business, claim severity band, and distribution channel to isolate problem areas.
 !- Limitations and considerations: Partial settlements: Recording the date of first partial payment can understate full-and-final completion time. Dispute and litigation pauses: Regulatory or court‐mandated suspensions inflate TAT yet lie outside managerial control.</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="H130" t="inlineStr">
         <is>
           <t>Are there gender disparities in the average time taken to process and settle insurance claims? How does processing time vary by policy type, premium, claim amount, and customer demographics? Are insurers with lower gender diversity more likely to have longer turnaround times? Are vulnerable gender groups disproportionately affected by delays?</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="L130" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>Investments</t>
         </is>
       </c>
-      <c r="D130">
+      <c r="D131">
         <v>207</v>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>Net rate of return on investments</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>% point differential between the average rates of returns on investments and the average performance/administration fees charged</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>Measures the profitability of a financial institution's own investment portfolio after accounting for all associated costs. It reveals the actual, bottom-line gain or loss generated by the institution's securities, real estate, or other investments. This is a fundamental indicator of an institution's ability to effectively manage its own capital and generate profit from non-lending activities, of particular importance to prudential supervisors, including supervisors of insurance and pension administrators. Net Rate of Return (%)= 
 [(Market Value final-Market Value initial+Income−Expenses)/Market Value initial]×100</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="H131" t="inlineStr">
         <is>
           <t>How do net returns (% returns minus % performance fees and charges) on longer-term investments compare by gender? Do net returns for any gender differ from the overall market average for similar investment products? How do FSPs compare in terms of net returns earned by gender?</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr">
+      <c r="J131" t="inlineStr">
         <is>
           <t>Market development</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
+      <c r="K131" t="inlineStr">
         <is>
           <t>Capital markets development</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="L131" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>Savings</t>
         </is>
       </c>
-      <c r="D131">
+      <c r="D132">
         <v>159</v>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>Average cost-to-customer for transaction accounts</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>Average topline revenue earned per account holder as % of average account balances</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>This indicator estimates the effective price of holding and using a transaction account, expressed as a yield on the customer’s average balance. By computing it for each account type (e.g., basic/no-frills, standard retail, premium, SME, e-money wallet), it reveals where pricing and usage frictions are highest. It helps supervisors assess fairness, inclusion quality, and reliance on fee income. !- Definitions and concepts: Non-interest fees: maintenance/inactivity, ATM/network, FX/transfer, statement/card fees, overdraft &amp; returned-payment fees tied to the account. 
 Per account-holder basis: aggregate all accounts of the same type per customer, then average (also show balance-weighted results). !- Data requirements: Core-banking data: customer ID, account type tags, average daily balance by customer for each account type, interest credited, revenue by fee code linked to accounts; flags for waivers/refunds/chargebacks. Channel/product hierarchies (basic vs. premium, retail vs. SME, wallet vs. bank account) and currency/FX mapping. Optional: usage indicators (transactions per month) to explain differences across types.</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="H132" t="inlineStr">
         <is>
           <t>Are there gender disparities in the costs (fees, charges) borne by account holders of transaction accounts? Do women tend to hold transaction accounts with higher fee burdens (relative to income or transaction frequency) than men, particularly in certain regions or among lower‐income groups? How do costs compare across FSPs with different levels of gender diversity? Is fee structure or cost‐to‐customer a barrier to transaction usage for some gender/age/income cohorts?</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Financial service provider (FSP) type; Account type</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Fair treatment</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D132">
-        <v>226</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Rejections of product applications</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>% of all applications that are rejected by product type</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Measures the proportion of customer applications for financial products that are rejected by regulated financial institutions during the reporting period. The indicator is calculated as the percentage of total applications received—across products such as loans, credit cards, deposit accounts, or insurance policies—that were not approved or accepted. Captures the extent of unmet demand or access barriers in financial markets, as well as aspects of market conduct, underwriting practices, and risk appetite among providers. It provides insight into how easily consumers and businesses can obtain financial products. Monitoring rejection rates helps authorities: Identify potential access constraints or discriminatory lending or sales practices; Evaluate the tightness of credit or account-opening standards; Assess consumer protection outcomes and fair treatment; Detect sudden shifts in provider risk tolerance or macro-prudential conditions (e.g., post-crisis credit tightening). High rejection rates may indicate stringent eligibility criteria, weak applicant creditworthiness, or barriers to financial access. Declining rates may suggest improving inclusion or relaxation of underwriting standards. Cross-product comparisons reveal whether certain markets (e.g., credit vs. deposits) are more exclusionary. !- Definitions and concepts: Application: A formal request by a customer to obtain a financial product or service. Rejection: A decision by the provider not to approve, issue, or open the requested product, whether automated or manual. Product type: Category of financial service applied for (loan, deposit, insurance, card, etc.). !- Data requirements: Product application records from regulated financail institutions that can yield the total number of applications rejected and the total number of applications received during the reference period. Disaggregation variables for segmentation analysis: product type, applicant type (individual, MSME), gender etc.</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>How do rejection rates vary by gender? Are rejection rates higher for any gender in specific channels? How do rejection rates in physical channels compare to those in digital channels by gender? How do FSPs rank in terms of rejection rates by gender across available channels? For loans, when analyzed alongside the indicator "Customers by credit score," are there gender disparities in rejection rates by credit score?</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
         </is>
       </c>
     </row>
@@ -7512,35 +7503,40 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>Fair treatment</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D133">
-        <v>175</v>
+        <v>226</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Payroll loans</t>
+          <t>Rejections of product applications</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>% of all retail borrowers (or loans) that have payroll loans (repayments deducted directly of wages deposited into the customer's account)</t>
+          <t>% of all applications that are rejected by product type</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Measures the prevalence of payroll lending in the retail loan portfolio. !- Definitions and concepts: A payroll loan (also called a payroll-deducted loan, salary loan) is a personal consumer loan whose installments are automatically withheld from the borrower’s pay-check (or pension/social-security benefit) and remitted directly to the lender each pay period. Because repayment is taken “off the top” of the employee’s gross salary, the borrower’s future income effectively serves as collateral, giving lenders high repayment certainty and allowing them to charge lower rates than on unsecured personal loans. !- Data requirements:  Loan-level records with ability to identify payroll loans (e.g. product code or terms of loan that specify the repayment modality). Unique customer ID in order to extract unique number of borrowers with payroll loans.</t>
+          <t>Measures the proportion of customer applications for financial products that are rejected by regulated financial institutions during the reporting period. The indicator is calculated as the percentage of total applications received—across products such as loans, credit cards, deposit accounts, or insurance policies—that were not approved or accepted. Captures the extent of unmet demand or access barriers in financial markets, as well as aspects of market conduct, underwriting practices, and risk appetite among providers. It provides insight into how easily consumers and businesses can obtain financial products. Monitoring rejection rates helps authorities: Identify potential access constraints or discriminatory lending or sales practices; Evaluate the tightness of credit or account-opening standards; Assess consumer protection outcomes and fair treatment; Detect sudden shifts in provider risk tolerance or macro-prudential conditions (e.g., post-crisis credit tightening). High rejection rates may indicate stringent eligibility criteria, weak applicant creditworthiness, or barriers to financial access. Declining rates may suggest improving inclusion or relaxation of underwriting standards. Cross-product comparisons reveal whether certain markets (e.g., credit vs. deposits) are more exclusionary. !- Definitions and concepts: Application: A formal request by a customer to obtain a financial product or service. Rejection: A decision by the provider not to approve, issue, or open the requested product, whether automated or manual. Product type: Category of financial service applied for (loan, deposit, insurance, card, etc.). !- Data requirements: Product application records from regulated financail institutions that can yield the total number of applications rejected and the total number of applications received during the reference period. Disaggregation variables for segmentation analysis: product type, applicant type (individual, MSME), gender etc.</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of retail borrowers accessing payroll loans, and how do these differences vary by age, income, and location? Do women or other gender groups have equal access to payroll loan products compared to men, or are there structural or employment-related barriers affecting uptake? How does the prevalence of payroll loans among borrowers relate to their employment types and sectors, and are certain gender groups more represented in these segments? Are financial service providers with greater gender diversity more likely to offer payroll loans equitably across genders? How do repayment behaviors and default rates on payroll loans differ by gender, and what implications does this have for financial inclusion and debt sustainability?</t>
+          <t>How do rejection rates vary by gender? Are rejection rates higher for any gender in specific channels? How do rejection rates in physical channels compare to those in digital channels by gender? How do FSPs rank in terms of rejection rates by gender across available channels? For loans, when analyzed alongside the indicator "Customers by credit score," are there gender disparities in rejection rates by credit score?</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -7550,12 +7546,12 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Uptake (account ownership)</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
         </is>
       </c>
     </row>
@@ -7576,107 +7572,102 @@
         </is>
       </c>
       <c r="D134">
+        <v>175</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Payroll loans</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>% of all retail borrowers (or loans) that have payroll loans (repayments deducted directly of wages deposited into the customer's account)</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Measures the prevalence of payroll lending in the retail loan portfolio. !- Definitions and concepts: A payroll loan (also called a payroll-deducted loan, salary loan) is a personal consumer loan whose installments are automatically withheld from the borrower’s pay-check (or pension/social-security benefit) and remitted directly to the lender each pay period. Because repayment is taken “off the top” of the employee’s gross salary, the borrower’s future income effectively serves as collateral, giving lenders high repayment certainty and allowing them to charge lower rates than on unsecured personal loans. !- Data requirements:  Loan-level records with ability to identify payroll loans (e.g. product code or terms of loan that specify the repayment modality). Unique customer ID in order to extract unique number of borrowers with payroll loans.</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in the share of retail borrowers accessing payroll loans, and how do these differences vary by age, income, and location? Do women or other gender groups have equal access to payroll loan products compared to men, or are there structural or employment-related barriers affecting uptake? How does the prevalence of payroll loans among borrowers relate to their employment types and sectors, and are certain gender groups more represented in these segments? Are financial service providers with greater gender diversity more likely to offer payroll loans equitably across genders? How do repayment behaviors and default rates on payroll loans differ by gender, and what implications does this have for financial inclusion and debt sustainability?</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Uptake (account ownership)</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="D135">
         <v>172</v>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>First-time borrowers</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>% of borrowers who are first-time borrowers with the FSP (or in the financial system)</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>This indicator shows the share of active borrowing retail customers who are new to the lender (new-to-bank/FSP) or new to formal credit altogether (new-to-credit, NTC). It is a direct barometer of financial inclusion and retail credit growth. A higher share can signal effective onboarding and market expansion, but it also shifts portfolio risk: NTC borrowers may lack repayment histories, making underwriting more model-driven and subject to greater uncertainty. Supervisors and lenders can monitor this metric to balance inclusion objectives with prudent risk management and to evaluate the effectiveness of credit-bureau coverage. !- Definitions and concepts: First-time borrower (FSP scope): a customer with no prior loan or credit line ever booked by the FSP before the reference period. First-time borrower (system scope / NTC): a customer with no prior loan or credit line reported to the national credit registry/bureau within a defined historical look-back (commonly “ever,” or a long horizon such as 5–10 years). This indicator is obtained by dividing the number of first-time borrowers by the total number of borrowers. Variants of this indicator include: value-weighted (by origination amount), new originations only (versus the entire active book), and cohort-based analysis (by origination month or quarter). !- Data requirements: Customer master records with unique, reliable identifiers (national ID/tax ID; deduplicated across branches). Loan-booking history from the FSP’s core systems. Credit-bureau/registry match results (for system-wide NTC status). Product taxonomy (include/exclude credit cards, overdrafts, BNPL) and reference dates. Limitaitons and considerations: Coverage gaps: thin or partial bureau coverage, informal lenders, or non-reporting segments can misclassify NTC status.
 Identifier quality: name changes, multiple IDs, or data-entry errors cause false “first-time” flags; robust deduplication is essential. Look-back window choice: shorter windows inflate “first-time” shares; disclose methodology. Product scope: excluding revolving credit or microloans biases results.</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="H135" t="inlineStr">
         <is>
           <t>Do first-time borrowers reflect a balanced gender representation, or are there gender disparities? How do FSPs rank in onboarding typically underserved borrowers, and does this ranking change when analyzed by gender?</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
         <is>
           <t>Uptake (account ownership)</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Impact, Suitability</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D135">
-        <v>171</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Unsecured credit facilities per borrower</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Average volume and value (outstanding amount) of unsecured credit operations per borrower</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>This indicator shows, for each unsecured credit type (e.g., credit cards, personal instalment loans, overdrafts/lines, BNPL/pay-in-4, microcredit), how many active facilities the typical borrower holds (volume) and how much they owe on average (value). It reveals product stacking, utilisation intensity, and pockets of affordability risk. Rising volumes with flat values can indicate product fragmentation (e.g., multiple small BNPL plans), while high values per borrower point to concentration risk and potential loss severity. !- Definitions and concepts: Borrower universe per type (t): unique customers with ≥1 active unsecured facility of type (t) during the period. Average volume (holders-only) = [Total number of active contracts of type t for borrow b] / [Total number of unique borrowers with facility of type t]. Average value (holders only) = [Average daily outstanding balance across all of borrower b's facility of type t] / [Total number of unique borrowers with facility of type t]. Outstanding amount: Gross carrying amount before prvisions, exclude undrawn limits. Attribution rules: Define treatment of joint borrowers (full vs. proportional), refinances/restructures and charged-off accounts (exclude once written off, unless still on-book). !- Data requirements: Loan/line-level records with borrower ID, product/credit-type tag, status, origination date, limit (revolving), currency, and daily balances. Deduped customer master across subsidiaries/channels; joint-borrower flags. FX rates for multi-currency portfolios; calendar to compute ADB over the period. !- Limitations and considerations: Seasonality: cards/overdrafts spike around holidays—use ADB and rolling windows. Mix effects: comparing cards (revolving) with instalments needs a utilisation companion metric. Policy choices: inclusion of dormant but open lines, re-aged accounts, or post-charge-off recoveries changes results—document choices. Distribution matters: report median and percentiles per type alongside means to avoid high-balance skew.</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>How does the average number of outstanding loans per borrower vary by gender? Are outstanding balances more concentrated in long- or short-term loans, and does this differ by gender? Have gender disparities in loan terms evolved over time?</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>Outcomes, Credit risk</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
         </is>
       </c>
     </row>
@@ -7688,35 +7679,35 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Safety and security</t>
+          <t>Suitability, Impact</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D136">
-        <v>231</v>
+        <v>171</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Frauds faced by customers</t>
+          <t>Unsecured credit facilities per borrower</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>% of customers affected by fraud</t>
+          <t>Average volume and value (outstanding amount) of unsecured credit operations per borrower</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Fraud directly erodes consumer confidence, trust in financial institutions and can trigger liquidity or solvency stress for institutions, tracking its incidence lets supervisors spot emerging threats before they undermine financial stability. Consistent monitoring also reveals control weaknesses, helping authorities direct enforcement, bolster preventive regulation, and keep the payments and deposit system trusted and resilient. This indicator measures the share of customers of financial services that have been victims of fraud over a specific period. !- Definitions and concepts: Several definitions of fraud exist and vary depending on the jurisdiction, local definitions of fraud for statistical reporting purposes should be used. For example, the European Banking Authority splits fraudelent payment transactions into two categories: (1) Unauthorised payment transactions: transfers made “as a result of the loss, theft or misappropriation of sensitive payment data or a payment instrument … executed in the absence of consent by the payer.” and (2) Manipulation of the payer: transactions “made as a result of the payer being manipulated … to issue a payment order … in good faith, to a payment account it believes belongs to a legitimate payee.” This definition anchors EU-wide fraud statistics and stresses both technical compromise (e.g., stolen credentials) and social-engineering scams (e.g., authorised push-payment fraud). !- Data requirements: Transactions initiated and executed during a specified period that are flagged as fraudulent linked to a unique customer ID; Total number of customer at the beginning of the specified period.</t>
+          <t>This indicator shows, for each unsecured credit type (e.g., credit cards, personal instalment loans, overdrafts/lines, BNPL/pay-in-4, microcredit), how many active facilities the typical borrower holds (volume) and how much they owe on average (value). It reveals product stacking, utilisation intensity, and pockets of affordability risk. Rising volumes with flat values can indicate product fragmentation (e.g., multiple small BNPL plans), while high values per borrower point to concentration risk and potential loss severity. !- Definitions and concepts: Borrower universe per type (t): unique customers with ≥1 active unsecured facility of type (t) during the period. Average volume (holders-only) = [Total number of active contracts of type t for borrow b] / [Total number of unique borrowers with facility of type t]. Average value (holders only) = [Average daily outstanding balance across all of borrower b's facility of type t] / [Total number of unique borrowers with facility of type t]. Outstanding amount: Gross carrying amount before prvisions, exclude undrawn limits. Attribution rules: Define treatment of joint borrowers (full vs. proportional), refinances/restructures and charged-off accounts (exclude once written off, unless still on-book). !- Data requirements: Loan/line-level records with borrower ID, product/credit-type tag, status, origination date, limit (revolving), currency, and daily balances. Deduped customer master across subsidiaries/channels; joint-borrower flags. FX rates for multi-currency portfolios; calendar to compute ADB over the period. !- Limitations and considerations: Seasonality: cards/overdrafts spike around holidays—use ADB and rolling windows. Mix effects: comparing cards (revolving) with instalments needs a utilisation companion metric. Policy choices: inclusion of dormant but open lines, re-aged accounts, or post-charge-off recoveries changes results—document choices. Distribution matters: report median and percentiles per type alongside means to avoid high-balance skew.</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>How does the number of fraud cases vary by gender? Are any genders disproportionately affected by fraud? Are fraud cases more frequent in certain types of FSPs?</t>
+          <t>How does the average number of outstanding loans per borrower vary by gender? Are outstanding balances more concentrated in long- or short-term loans, and does this differ by gender? Have gender disparities in loan terms evolved over time?</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -7726,17 +7717,17 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Outcomes, Credit risk</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
         </is>
       </c>
     </row>
@@ -7757,26 +7748,26 @@
         </is>
       </c>
       <c r="D137">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Frauds resulting in costumers losses</t>
+          <t>Frauds faced by customers</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Average volume and value (losses incurred) of frauds experienced by customers</t>
+          <t>% of customers affected by fraud</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Fraud directly erodes consumer confidence, trust in financial institutions and can trigger liquidity or solvency stress for institutions, tracking its incidence lets supervisors spot emerging threats before they undermine financial stability. Consistent monitoring also reveals control weaknesses, helping authorities direct enforcement, bolster preventive regulation, and keep the payments and deposit system trusted and resilient. This indicator measures the number of transactions that have been flagged as fraudulent and their corresponding value in currency.  !- Definitions and concepts: Several definitions of fraud exist and vary depending on the jurisdiction, local definitions of fraud for statistical reporting purposes should be used. For example, the European Banking Authority splits fraudelent payment transactions into two categories: (1) Unauthorised payment transactions: transfers made “as a result of the loss, theft or misappropriation of sensitive payment data or a payment instrument … executed in the absence of consent by the payer.” and (2) Manipulation of the payer: transactions “made as a result of the payer being manipulated … to issue a payment order … in good faith, to a payment account it believes belongs to a legitimate payee.” This definition anchors EU-wide fraud statistics and stresses both technical compromise (e.g., stolen credentials) and social-engineering scams (e.g., authorised push-payment fraud). !- Data requirements: Total number of transactions initiated and executed during a specified period that are flagged as fraudulent;  Total value of transactions initiated and executed during a specified period that are flagged as fraudulent.</t>
+          <t>Fraud directly erodes consumer confidence, trust in financial institutions and can trigger liquidity or solvency stress for institutions, tracking its incidence lets supervisors spot emerging threats before they undermine financial stability. Consistent monitoring also reveals control weaknesses, helping authorities direct enforcement, bolster preventive regulation, and keep the payments and deposit system trusted and resilient. This indicator measures the share of customers of financial services that have been victims of fraud over a specific period. !- Definitions and concepts: Several definitions of fraud exist and vary depending on the jurisdiction, local definitions of fraud for statistical reporting purposes should be used. For example, the European Banking Authority splits fraudelent payment transactions into two categories: (1) Unauthorised payment transactions: transfers made “as a result of the loss, theft or misappropriation of sensitive payment data or a payment instrument … executed in the absence of consent by the payer.” and (2) Manipulation of the payer: transactions “made as a result of the payer being manipulated … to issue a payment order … in good faith, to a payment account it believes belongs to a legitimate payee.” This definition anchors EU-wide fraud statistics and stresses both technical compromise (e.g., stolen credentials) and social-engineering scams (e.g., authorised push-payment fraud). !- Data requirements: Transactions initiated and executed during a specified period that are flagged as fraudulent linked to a unique customer ID; Total number of customer at the beginning of the specified period.</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>How do financial loss-related fraud cases impact genders differently? Are any genders disproportionately affected by frauds that result in financial losses? Are fraud cases involving financial losses more common in certain types of FSPs?</t>
+          <t>How does the number of fraud cases vary by gender? Are any genders disproportionately affected by fraud? Are fraud cases more frequent in certain types of FSPs?</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -7817,102 +7808,102 @@
         </is>
       </c>
       <c r="D138">
+        <v>233</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Frauds resulting in costumers losses</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Average volume and value (losses incurred) of frauds experienced by customers</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Fraud directly erodes consumer confidence, trust in financial institutions and can trigger liquidity or solvency stress for institutions, tracking its incidence lets supervisors spot emerging threats before they undermine financial stability. Consistent monitoring also reveals control weaknesses, helping authorities direct enforcement, bolster preventive regulation, and keep the payments and deposit system trusted and resilient. This indicator measures the number of transactions that have been flagged as fraudulent and their corresponding value in currency.  !- Definitions and concepts: Several definitions of fraud exist and vary depending on the jurisdiction, local definitions of fraud for statistical reporting purposes should be used. For example, the European Banking Authority splits fraudelent payment transactions into two categories: (1) Unauthorised payment transactions: transfers made “as a result of the loss, theft or misappropriation of sensitive payment data or a payment instrument … executed in the absence of consent by the payer.” and (2) Manipulation of the payer: transactions “made as a result of the payer being manipulated … to issue a payment order … in good faith, to a payment account it believes belongs to a legitimate payee.” This definition anchors EU-wide fraud statistics and stresses both technical compromise (e.g., stolen credentials) and social-engineering scams (e.g., authorised push-payment fraud). !- Data requirements: Total number of transactions initiated and executed during a specified period that are flagged as fraudulent;  Total value of transactions initiated and executed during a specified period that are flagged as fraudulent.</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>How do financial loss-related fraud cases impact genders differently? Are any genders disproportionately affected by frauds that result in financial losses? Are fraud cases involving financial losses more common in certain types of FSPs?</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Safety and security</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D139">
         <v>230</v>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E139" t="inlineStr">
         <is>
           <t>Physical safety</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>Number of physical security incidents and number of customers affected</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t>This indicator captures the total number of reported physical security incidents that occur in connection with the operations of financial service providers (FSPs) — including banks, microfinance institutions, payment service providers, and other regulated entities — as well as the number of customers directly affected by such incidents. Physical security incidents include events such as armed robberies, thefts, assaults, vandalism, or damage to property occurring at branches, ATMs, cash-in-transit vehicles, or other service delivery points. The “number of customers affected” reflects individuals who have experienced harm, loss, or disruption of service as a result of these events.This indicator measures the operational risk exposure of the financial sector to physical threats and criminal activity, and the extent to which such incidents impact customers and public trust. It forms part of the broader construct of operational resilience and consumer protection, providing insights into the safety of physical access points within the financial system. Supervisory reporting could record:
 Number of incidents = Total count of reported physical security incidents during the reference period (e.g., quarterly or annually). Number of customers affected = Total number of customers who suffered loss, injury, or service disruption due to those incidents. !- Derivable indicators: Incident rate = (Number of incidents / Total number of service points) × 1,000; Customer impact rate = (Number of customers affected / Total number of customers) × 100</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
+      <c r="H139" t="inlineStr">
         <is>
           <t>How does the number of physical security incidents vary by gender? Are any genders disproportionately affected? Are physical security incidents more common in certain types of FSPs?</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr">
+      <c r="J139" t="inlineStr">
         <is>
           <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
+      <c r="K139" t="inlineStr">
         <is>
           <t>Outcomes, Reputational and legal risk</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
+      <c r="L139" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Suitability</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D139">
-        <v>152</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Deposit account holders qualifying for credit</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>% of all deposit account holders that meet the minimum qualifying criteria for a loan or line of credit</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>A measure of the assessed creditworthiness of depositors. Digital financial tools such as mobile money and e-wallets have opened up access to financal services to millions around the world. This indicator tries to measure the degree to which users of accounts can unlock access to addiitonal services, in the case credit. !- Definitions and concepts: Deposit accounts include transaction and non-transaction deposit accounts, for example: Checking/demand, savings, time/term deposit accounts, pensions. !- Data requirements: Total number of unique deposit account holders that also either have (1) an open loan account, (2) do not have an open loan account but would be approved for a loan or line of credit given their current credit history, credit score or other basic requirements (such as minimum balance or savings history); Total number of unique deposit account holders (i.e. an individual must be counted as one depositor irrespective of the number of deposit accounts held) at the end of a specified period (e.g. quarter or year).  !- Limitations and considerations: If individuals or MSMEs own deposit accounts across multiple different financial institutions, sector or system wide aggregates which add up accounts across institutions will, as a result, overstate the degree of financial inclusion unless granular data and unique national IDs can be used to identify individuals with multiple accounts across financial institutions.</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>What are the credit-qualifying rates for transaction account holders by gender? How do these rates compare? Which FSPs rank highest and lowest in credit-qualifying rates for typically underserved groups, and does this ranking change when analyzed by gender?</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>Outcomes, Credit risk</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
         </is>
       </c>
     </row>
@@ -7933,26 +7924,26 @@
         </is>
       </c>
       <c r="D140">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Early loan payoff</t>
+          <t>Deposit account holders qualifying for credit</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>% of borrowers who paid loans in full before due date</t>
+          <t>% of all deposit account holders that meet the minimum qualifying criteria for a loan or line of credit</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>The early-loan-payoff (or prepayment) indicator tracks the share of outstanding loans that borrowers settle—partly or fully—before the contractually scheduled maturity. High prepayment activity can squeeze interest income, change expected cash-flow profiles that underpin asset-liability management, and distort credit-loss models. For lenders, rising early payoffs may flag aggressive refinancing campaigns by competitors, interest rate declines that make refinancing attractive, or borrowers’ improved liquidity. Supervisors and investors monitor the metric to evaluate revenue volatility, among others. !- Definitions and concepts: Early payoff / prepayment: any unscheduled principal reduction exceeding the contractual amortisation, including full settlement (loan closed) and partial prepayments (lump-sum curtailments).</t>
+          <t>A measure of the assessed creditworthiness of depositors. Digital financial tools such as mobile money and e-wallets have opened up access to financal services to millions around the world. This indicator tries to measure the degree to which users of accounts can unlock access to addiitonal services, in the case credit. !- Definitions and concepts: Deposit accounts include transaction and non-transaction deposit accounts, for example: Checking/demand, savings, time/term deposit accounts, pensions. !- Data requirements: Total number of unique deposit account holders that also either have (1) an open loan account, (2) do not have an open loan account but would be approved for a loan or line of credit given their current credit history, credit score or other basic requirements (such as minimum balance or savings history); Total number of unique deposit account holders (i.e. an individual must be counted as one depositor irrespective of the number of deposit accounts held) at the end of a specified period (e.g. quarter or year).  !- Limitations and considerations: If individuals or MSMEs own deposit accounts across multiple different financial institutions, sector or system wide aggregates which add up accounts across institutions will, as a result, overstate the degree of financial inclusion unless granular data and unique national IDs can be used to identify individuals with multiple accounts across financial institutions.</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the likelihood of making early payments before due dates? Which credit products are most frequently paid early by each gender?</t>
+          <t>What are the credit-qualifying rates for transaction account holders by gender? How do these rates compare? Which FSPs rank highest and lowest in credit-qualifying rates for typically underserved groups, and does this ranking change when analyzed by gender?</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7993,26 +7984,26 @@
         </is>
       </c>
       <c r="D141">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Grace period/payment leeway</t>
+          <t>Early loan payoff</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>% of borrowers using payment holidays, grace periods and other relief measures</t>
+          <t>% of borrowers who paid loans in full before due date</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Shows how many borrowers are under temporary repayment relief, signalling household stress, policy effectiveness, and potential payment cliffs when relief ends. Rising usage can reduce near-term delinquencies but may defer (not eliminate) credit risk and revenue. !- Definitions and concepts: Relief measures (forbearance): payment holiday/deferral, interest-only period, reduced instalment, term extension, fee/penalty waiver, capitalization of arrears, hardship programs.Borrower-based indicator: % of borrowers on relief = [Total unique borrowers with at least 1 active relief measure in period]/[Total unique active borrowing customers] x 100%. Account-based variant uses loan count instead of borrowers. Status: Active (relief in effect), Approved but not started, Expired. Intensity companions: % of balances under relief, avg. relief days used, new entrants to relief ÷ active borrowers. !- Data requirements: Loan-level flags: relief type, start/end dates, approval date, terms (interest accrual, capitalization), reason code (income loss, disaster, medical), product type. Borrower ID (deduplicated across products/entities). !- Limitations and considerations: Definition variance: some programs auto-enrol; others require hardship evidence—harmful to cross-bank comparisons. Double counting: a borrower may receive multiple reliefs across loans—use borrower-level dedupe and report per-loan as a companion. Masking effect: relief suppresses DPD/NPL temporarily; pair with balances under relief and post-exit performance. Cohort effects &amp; timing: shocks (e.g., disasters) create spikes; use cohort tracking (by approval month) and rolling windows. Conduct risk: prolonged or opaque relief terms can mislead customers; monitor complaints and repeat relief rates. Segment by product (mortgage, card, personal, SME), risk grade, tenure, and demographics to pinpoint vulnerability and program effectiveness.</t>
+          <t>The early-loan-payoff (or prepayment) indicator tracks the share of outstanding loans that borrowers settle—partly or fully—before the contractually scheduled maturity. High prepayment activity can squeeze interest income, change expected cash-flow profiles that underpin asset-liability management, and distort credit-loss models. For lenders, rising early payoffs may flag aggressive refinancing campaigns by competitors, interest rate declines that make refinancing attractive, or borrowers’ improved liquidity. Supervisors and investors monitor the metric to evaluate revenue volatility, among others. !- Definitions and concepts: Early payoff / prepayment: any unscheduled principal reduction exceeding the contractual amortisation, including full settlement (loan closed) and partial prepayments (lump-sum curtailments).</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>How do the percentages of borrowers using grace periods or payment leeways compare by gender? Is there any gender more likely to use them? How does the use of grace periods or payment leeways vary by credit product and gender?</t>
+          <t>Are there gender disparities in the likelihood of making early payments before due dates? Which credit products are most frequently paid early by each gender?</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8053,102 +8044,102 @@
         </is>
       </c>
       <c r="D142">
+        <v>189</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Grace period/payment leeway</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>% of borrowers using payment holidays, grace periods and other relief measures</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Shows how many borrowers are under temporary repayment relief, signalling household stress, policy effectiveness, and potential payment cliffs when relief ends. Rising usage can reduce near-term delinquencies but may defer (not eliminate) credit risk and revenue. !- Definitions and concepts: Relief measures (forbearance): payment holiday/deferral, interest-only period, reduced instalment, term extension, fee/penalty waiver, capitalization of arrears, hardship programs.Borrower-based indicator: % of borrowers on relief = [Total unique borrowers with at least 1 active relief measure in period]/[Total unique active borrowing customers] x 100%. Account-based variant uses loan count instead of borrowers. Status: Active (relief in effect), Approved but not started, Expired. Intensity companions: % of balances under relief, avg. relief days used, new entrants to relief ÷ active borrowers. !- Data requirements: Loan-level flags: relief type, start/end dates, approval date, terms (interest accrual, capitalization), reason code (income loss, disaster, medical), product type. Borrower ID (deduplicated across products/entities). !- Limitations and considerations: Definition variance: some programs auto-enrol; others require hardship evidence—harmful to cross-bank comparisons. Double counting: a borrower may receive multiple reliefs across loans—use borrower-level dedupe and report per-loan as a companion. Masking effect: relief suppresses DPD/NPL temporarily; pair with balances under relief and post-exit performance. Cohort effects &amp; timing: shocks (e.g., disasters) create spikes; use cohort tracking (by approval month) and rolling windows. Conduct risk: prolonged or opaque relief terms can mislead customers; monitor complaints and repeat relief rates. Segment by product (mortgage, card, personal, SME), risk grade, tenure, and demographics to pinpoint vulnerability and program effectiveness.</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>How do the percentages of borrowers using grace periods or payment leeways compare by gender? Is there any gender more likely to use them? How does the use of grace periods or payment leeways vary by credit product and gender?</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Outcomes, Credit risk</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Suitability</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="D143">
         <v>190</v>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>Borrowers in debt counselling and rehabilitation</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>% of borrowers participating in debt counselling and/or debt rehabilitation progams</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>This indicator tracks the prevalence of individuals formally enrolled in debt-counselling or rehabilitation programmes: legal or contractual processes that restructure debt, impose spending plans, or provide financial-literacy support. A rising level signals household over-indebtedness pressures, tighter monetary or labour-market conditions, or aggressive credit expansion in the recent past. Regulators, consumer-protection agencies, and lenders track the metric to gauge systemic consumer-credit risk, calibrate responsible-lending rules and supervision, and anticipate write-off or provisioning needs. !- Definitions and concepts: Borrowers refers to individuals that have obtained any type of credit from financial institutions. Individuals are counted as one borrower, irrespective of the number of loan accounts held. Debt-counselling / debt-review: A court-sanctioned or regulator-approved process (e.g., South Africa’s National Credit Act, UK Debt Management Plans) where a certified counsellor assesses affordability, negotiates new payment schedules with all creditors, and disburses consolidated instalments. Debt rehabilitation / discharge: The stage at which the borrower has completed the plan, obtained a clearance certificate, or been legally discharged from remaining obligations (analogous to Chapter 13 completion in the US). Indicator forms:
 Stock measure: number of active borrowers under counselling ÷ total number of retail borrowers. Flow measure: new counselling entrants during the period ÷ new defaults. !- Data requirements: Registry or court filings identifying unique borrowers, start and end dates, original and restructured debt balances, and counsellor accreditation. Credit-bureau data to link counselling status with credit scores, delinquency buckets, and new credit enquiries. !- Limitations and considerations: Coverage gaps: Informal or NGO-led advice services may not report centrally, understating prevalence. Regime differences: Some jurisdictions treat insolvency, debt management, and bankruptcy as separate processes; harmonising counts is non-trivial. Multiple enrolments: Borrowers can exit and re-enter counselling; deduplicating unique individuals is essential for accurate stock figures. Moral-hazard concerns: Easy access to rehabilitation might weaken repayment discipline; analysts pair this indicator with post-rehabilitation re-default rates.Privacy restrictions: Personally identifiable data are often masked, limiting segmentation by income, gender, or geography unless aggregated extracts are provided. Used alongside delinquency trends, restructuring volumes, and loan-loss provisions, the “borrowers in debt counselling and rehabilitation” metric offers a forward-looking lens on household financial stress and the effectiveness of consumer-protection frameworks.</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t>How do the percentages of borrowers in debt counseling or rehabilitation compare by gender? Is there any gender more likely to enroll in debt counseling or rehabilitation? How do FSPs compare in terms of debt counseling or rehabilitation enrollment by gender?</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
         <is>
           <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="K143" t="inlineStr">
         <is>
           <t>Outcomes, Credit risk</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Suitability</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D143">
-        <v>27</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Borrowers in risky indebtedness (risk of over-indebtedness)</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Number of borrowers classified as at risk of over-indebtedness, as per risk-indebtedness calculation</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Tracking over-indebtedness gives authorities a measure of systemic distress: when large segments of retail borrowers can’t meet their obligations, it highlights consumer-protection gaps. Persistent debt burdens signal predatory lending or inadequate affordability assessments. The indicator helps calibrate market-conduct supervision and regulation. This particular indicator that identifies borrowers at risk of overindebtedness was developed by the Central Bank of Brazil: https://www.bcb.gov.br/content/cidadaniafinanceira/documentos_cidadania/serie_cidadania/serie_cidadania_financeira_8_endividamento_risco_2ed.pdf ad https://www.researchgate.net/publication/376634051_Risky_Indebtedness_Behavior_Impacts_on_Financial_Preparation_for_Retirement_and_Perceived_Financial_Well-Being. It is a composite of four components. A borrower is flagged as being in "risky indebtedness" when any two of the following four criteria are met: (1) Has defaulted on credit installments, that is, has had payment delays of more than 90 days in meeting credit obligations, (2) Monthly income devoted to debt-service payments exceeds 50 percent, (3) Has simultaneous exposure to the following forms of credit: overdraft, unsecured personal loan, and revolving credit card debt, (4) Monthly disposable income (after debt-service payments) that falls below the poverty line. Generating this indicator at the system level requires a unique national ID in order to match granular loan data to unique borrowers. The indicator also requires access to income data. !- Derivable indicators: Percent of borrowers in risky indebtendess; Percent of adults in risky indebtedness.</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in the classification of risky indebtedness? Are low-income borrowers more at risk of risky indebtedness and how does it compare across genders? Comparing this indicator with gender diversity, do FSPs with higher levels of gender diversity present lower levels of risky indebtedness?</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>Credit risk</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -8174,26 +8165,26 @@
         </is>
       </c>
       <c r="D144">
-        <v>285</v>
+        <v>27</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Debt service-to-income ratio</t>
+          <t>Borrowers in risky indebtedness (risk of over-indebtedness)</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>% of income allocated to retail credit debt repayment</t>
+          <t>Number of borrowers classified as at risk of over-indebtedness, as per risk-indebtedness calculation</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>The debt service-to-Income ratio,  sometimes referred to more concisely as the debt service ratio (DSR) expresses a borrower’s (or household’s) total debt-service burden relative to recurring income, answering a simple question: How much of each income unit is already pledged to repay existing debt? At the micro level, lenders use DSR to assess repayment capacity, price credit, and comply with responsible-lending rules. At the macro level, supervisors track average or distributional DSR to gauge household vulnerability to interest-rate shocks and to calibrate macro-prudential tools such as loan-to-income caps. !- Definitions and concepts: Debt payments include principal, interest, mandatory insurance on retail credit facilities;  Income can be defined in gross terms (pre-tax income (salary) plus verifiable recurring earning) or net terms (income after taxes and social-security contributions). !- Data requirements: Current loan statements or credit-bureau/registry reports detailing payment amounts, remaiming term, and interest rate for all obligations; Recent payslips, audited financial statements (self-fmployed), tax returns, and verified rental or pension income. !- Limitations and considerations: Income volatility: informal or gig-economy or commission-based earnings make future cash flows uncertain; Undisclosed liabilities: informal or unreported debts escape bureau coverage, understating true DSR. Household composition: shared living expenses and co-borrower support can distort individual ratios; some frameworks use household disposable income instead. Interest-rate path: fixed-rate loans keep payments stable, while floating-rate debt can raise DSR sharply when policy rates rise. Cross-country comparability: tax structures, social-welfare benefits, and healthcare costs influence disposable income, so identical DSR thresholds may imply different real affordability across jurisdictions.</t>
+          <t>Tracking over-indebtedness gives authorities a measure of systemic distress: when large segments of retail borrowers can’t meet their obligations, it highlights consumer-protection gaps. Persistent debt burdens signal predatory lending or inadequate affordability assessments. The indicator helps calibrate market-conduct supervision and regulation. This particular indicator that identifies borrowers at risk of overindebtedness was developed by the Central Bank of Brazil: https://www.bcb.gov.br/content/cidadaniafinanceira/documentos_cidadania/serie_cidadania/serie_cidadania_financeira_8_endividamento_risco_2ed.pdf ad https://www.researchgate.net/publication/376634051_Risky_Indebtedness_Behavior_Impacts_on_Financial_Preparation_for_Retirement_and_Perceived_Financial_Well-Being. It is a composite of four components. A borrower is flagged as being in "risky indebtedness" when any two of the following four criteria are met: (1) Has defaulted on credit installments, that is, has had payment delays of more than 90 days in meeting credit obligations, (2) Monthly income devoted to debt-service payments exceeds 50 percent, (3) Has simultaneous exposure to the following forms of credit: overdraft, unsecured personal loan, and revolving credit card debt, (4) Monthly disposable income (after debt-service payments) that falls below the poverty line. Generating this indicator at the system level requires a unique national ID in order to match granular loan data to unique borrowers. The indicator also requires access to income data. !- Derivable indicators: Percent of borrowers in risky indebtendess; Percent of adults in risky indebtedness.</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>How do debt service-to-income ratios vary by gender and across different loan sizes and terms? Do loans with higher rates and shorter terms show gender disparities in ratios? Comparing this indicator with gender diversity, do FSPs with higher levels of gender diversity present lower debt-service to income ratios?</t>
+          <t>Are there gender disparities in the classification of risky indebtedness? Are low-income borrowers more at risk of risky indebtedness and how does it compare across genders? Comparing this indicator with gender diversity, do FSPs with higher levels of gender diversity present lower levels of risky indebtedness?</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8203,12 +8194,12 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
+          <t>Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Quality,Credit risk</t>
+          <t>Credit risk</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -8230,30 +8221,30 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D145">
-        <v>194</v>
+        <v>285</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Insurance lapse rates</t>
+          <t>Debt service-to-income ratio</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>% of all insurance policies (or policyholders) that have lapsed</t>
+          <t>% of income allocated to retail credit debt repayment</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>This indicator measures the number of policies discontinued due to non-payment of premiums by the policyholder relative to the total number of policies at the beginning of the period. It is a key indicator to assess quality of advice, quality of service, product appropriateness, and mis-selling risk in the insurance sector. https://www.iais.org/uploads/2022/06/Report-on-Supervisors-Use-of-Key-Indicators-to-Assess-Insurer-Conduct.pdf</t>
+          <t>The debt service-to-Income ratio,  sometimes referred to more concisely as the debt service ratio (DSR) expresses a borrower’s (or household’s) total debt-service burden relative to recurring income, answering a simple question: How much of each income unit is already pledged to repay existing debt? At the micro level, lenders use DSR to assess repayment capacity, price credit, and comply with responsible-lending rules. At the macro level, supervisors track average or distributional DSR to gauge household vulnerability to interest-rate shocks and to calibrate macro-prudential tools such as loan-to-income caps. !- Definitions and concepts: Debt payments include principal, interest, mandatory insurance on retail credit facilities;  Income can be defined in gross terms (pre-tax income (salary) plus verifiable recurring earning) or net terms (income after taxes and social-security contributions). !- Data requirements: Current loan statements or credit-bureau/registry reports detailing payment amounts, remaiming term, and interest rate for all obligations; Recent payslips, audited financial statements (self-fmployed), tax returns, and verified rental or pension income. !- Limitations and considerations: Income volatility: informal or gig-economy or commission-based earnings make future cash flows uncertain; Undisclosed liabilities: informal or unreported debts escape bureau coverage, understating true DSR. Household composition: shared living expenses and co-borrower support can distort individual ratios; some frameworks use household disposable income instead. Interest-rate path: fixed-rate loans keep payments stable, while floating-rate debt can raise DSR sharply when policy rates rise. Cross-country comparability: tax structures, social-welfare benefits, and healthcare costs influence disposable income, so identical DSR thresholds may imply different real affordability across jurisdictions.</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>How do insurance lapse rates differ by gender? Are certain types of insurance policies associated with higher lapse rates among specific genders, suggesting potential issues with product suitability? How do different financial service providers (FSPs) compare in terms of lapse rates across genders? Are there notable differences when considering age, location, or income alongside gender?</t>
+          <t>How do debt service-to-income ratios vary by gender and across different loan sizes and terms? Do loans with higher rates and shorter terms show gender disparities in ratios? Comparing this indicator with gender diversity, do FSPs with higher levels of gender diversity present lower debt-service to income ratios?</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8268,12 +8259,12 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Outcomes, Credit risk</t>
+          <t>Quality, Credit risk</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -8294,26 +8285,26 @@
         </is>
       </c>
       <c r="D146">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Reinstatement of lapsed insurance policies</t>
+          <t>Insurance lapse rates</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>% of lapsed insurance policies that have been re-instated after customer made back-payments</t>
+          <t>% of all insurance policies (or policyholders) that have lapsed</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>This indicator shows the share of policies that lapsed for non-payment and were later reinstated after the customer cleared arrears (and, where required, satisfied evidence-of-insurability). A higher reinstatement rate can indicate effective retention outreach and product value to customers; very low rates may signal affordability stress, weak follow-up, or poor customer experience. From a risk perspective, reinstatements affect cash flows, reserve dynamics, and anti-selection (customers may reinstate when risk has increased). Pair this indicator with persistency, tenure of cancellations, and complaint metrics to diagnose retention quality and customer outcomes. !- Definitions and concepts: Lapse (non-payment): policy terminated after the grace period due to unpaid premium (distinct from surrender, maturity, or death). Reinstatement: restoration of coverage after lapse once back-premiums (and any interest/fees) are paid and underwriting/administrative conditions are met. Coverage may be backdated or resume prospectively per policy terms. Measurement window: define a fixed look-back (e.g., reinstated within 90/180 days of lapse). Formula (cohort basis): # policies that lapsed in period and were reinstated within {days} divided by the # policies that lapsed in period. Variants: policyholder-level (deduplicated), premium-weighted share, and calendar-period “reinstatements ÷ lapses” with a stated window. !- Data requirements: Policy-level: product/LOB, activation date, lapse date, grace-period end, arrears amount, reinstatement date, back-payment amount, underwriting outcome (medical/financial), and whether coverage backdated. Channel, geography, tenure at lapse, and prior claims/loan status. Cohort tags (issue or lapse month) for like-for-like tracking. !- Limitations and considerations: Window sensitivity: longer window raises the rate; disclose and keep constant. Classification noise: grace-period statuses mis-tagged as lapses depress apparent reinstatement. Anti-selection: reinstated policies may have higher subsequent claims—monitor post-reinstatement loss experience. Operational variance: some firms “rewrite” new policies rather than reinstate, understating the metric. Coverage basis: backdated vs. prospective reinstatement changes exposure and reserve treatment—report the split if material.</t>
+          <t>This indicator measures the number of policies discontinued due to non-payment of premiums by the policyholder relative to the total number of policies at the beginning of the period. It is a key indicator to assess quality of advice, quality of service, product appropriateness, and mis-selling risk in the insurance sector. https://www.iais.org/uploads/2022/06/Report-on-Supervisors-Use-of-Key-Indicators-to-Assess-Insurer-Conduct.pdf</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>How do rates of reinstating lapsed insurance policies vary by gender? Is any gender more likely to make back payments and reinstate their policies? How do these reinstatement patterns differ across FSPs, policy types, and demographic groups such as age or income? What might these patterns indicate about barriers to maintaining continuous coverage?</t>
+          <t>How do insurance lapse rates differ by gender? Are certain types of insurance policies associated with higher lapse rates among specific genders, suggesting potential issues with product suitability? How do different financial service providers (FSPs) compare in terms of lapse rates across genders? Are there notable differences when considering age, location, or income alongside gender?</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8323,12 +8314,12 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Outcomes, Credit risk</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -8354,26 +8345,26 @@
         </is>
       </c>
       <c r="D147">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Risk of insurance coverage lapse</t>
+          <t>Reinstatement of lapsed insurance policies</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>% of all insurance policies (or policyholders) that missed one or more premium payments (depending on product rules and polcies) but are still within the grace period</t>
+          <t>% of lapsed insurance policies that have been re-instated after customer made back-payments</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Measures the percentage of active insurance policies (or policyholders) that have missed one or more scheduled premium payments but remain within the contractual grace period before formal lapse or cancellation takes effect. It reflects the proportion of insurance coverage that is at risk of lapsing due to non-payment but still eligible for reinstatement under product rules. Captures policyholder payment continuity risk and the vulnerability of insurance coverage within a given portfolio. It serves as an early-warning measure of potential lapse rates, affordability pressures, and retention dynamics in insurance markets. Monitoring the risk of coverage lapse helps regulators, supervisors, and insurers to: Identify emerging risks to policy continuity and financial protection coverage; Assess household liquidity stress and premium affordability; Evaluate insurer risk management practices regarding collections and grace-period handling; Strengthen consumer protection and financial health monitoring, especially in low-income or microinsurance segments. It provides an early signal of future lapse or surrender trends, which can affect both household resilience and insurer liquidity. Higher values indicate rising vulnerability to policy lapse, which may reflect household financial strain, ineffective premium collection, or weak payment reminders.Persistent high rates suggest potential issues in affordability or product suitability. Declining values reflect improved payment discipline, automatic premium collection mechanisms, or targeted retention strategies. !- Definitions and concepts: Grace period: A contractually defined period after a missed premium during which coverage remains active and can be reinstated upon payment. Lapse: Termination of an insurance policy due to non-payment of premiums after the grace period expires. !- Data requirements: Administrative data from licensed insurance companies or supervisory reporting systems. Disaggregation by product type (life, health, motor, microinsurance, etc.), customer segment (individual, group), and insurer type. Definition of grace period based on product category (e.g., 30 days for life insurance, 7–15 days for general insurance).</t>
+          <t>This indicator shows the share of policies that lapsed for non-payment and were later reinstated after the customer cleared arrears (and, where required, satisfied evidence-of-insurability). A higher reinstatement rate can indicate effective retention outreach and product value to customers; very low rates may signal affordability stress, weak follow-up, or poor customer experience. From a risk perspective, reinstatements affect cash flows, reserve dynamics, and anti-selection (customers may reinstate when risk has increased). Pair this indicator with persistency, tenure of cancellations, and complaint metrics to diagnose retention quality and customer outcomes. !- Definitions and concepts: Lapse (non-payment): policy terminated after the grace period due to unpaid premium (distinct from surrender, maturity, or death). Reinstatement: restoration of coverage after lapse once back-premiums (and any interest/fees) are paid and underwriting/administrative conditions are met. Coverage may be backdated or resume prospectively per policy terms. Measurement window: define a fixed look-back (e.g., reinstated within 90/180 days of lapse). Formula (cohort basis): # policies that lapsed in period and were reinstated within {days} divided by the # policies that lapsed in period. Variants: policyholder-level (deduplicated), premium-weighted share, and calendar-period “reinstatements ÷ lapses” with a stated window. !- Data requirements: Policy-level: product/LOB, activation date, lapse date, grace-period end, arrears amount, reinstatement date, back-payment amount, underwriting outcome (medical/financial), and whether coverage backdated. Channel, geography, tenure at lapse, and prior claims/loan status. Cohort tags (issue or lapse month) for like-for-like tracking. !- Limitations and considerations: Window sensitivity: longer window raises the rate; disclose and keep constant. Classification noise: grace-period statuses mis-tagged as lapses depress apparent reinstatement. Anti-selection: reinstated policies may have higher subsequent claims—monitor post-reinstatement loss experience. Operational variance: some firms “rewrite” new policies rather than reinstate, understating the metric. Coverage basis: backdated vs. prospective reinstatement changes exposure and reserve treatment—report the split if material.</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>How well does the non-life insurance policy market reflect gender-based differences in policyholding and insured benefits? How do the types of non-life insurance policies held compare by gender? How are gender disparities evolving in the distribution of non-life insurance policies across different FSPs?</t>
+          <t>How do rates of reinstating lapsed insurance policies vary by gender? Is any gender more likely to make back payments and reinstate their policies? How do these reinstatement patterns differ across FSPs, policy types, and demographic groups such as age or income? What might these patterns indicate about barriers to maintaining continuous coverage?</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -8388,7 +8379,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Outcomes</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -8414,19 +8405,79 @@
         </is>
       </c>
       <c r="D148">
+        <v>193</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Risk of insurance coverage lapse</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>% of all insurance policies (or policyholders) that missed one or more premium payments (depending on product rules and polcies) but are still within the grace period</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Measures the percentage of active insurance policies (or policyholders) that have missed one or more scheduled premium payments but remain within the contractual grace period before formal lapse or cancellation takes effect. It reflects the proportion of insurance coverage that is at risk of lapsing due to non-payment but still eligible for reinstatement under product rules. Captures policyholder payment continuity risk and the vulnerability of insurance coverage within a given portfolio. It serves as an early-warning measure of potential lapse rates, affordability pressures, and retention dynamics in insurance markets. Monitoring the risk of coverage lapse helps regulators, supervisors, and insurers to: Identify emerging risks to policy continuity and financial protection coverage; Assess household liquidity stress and premium affordability; Evaluate insurer risk management practices regarding collections and grace-period handling; Strengthen consumer protection and financial health monitoring, especially in low-income or microinsurance segments. It provides an early signal of future lapse or surrender trends, which can affect both household resilience and insurer liquidity. Higher values indicate rising vulnerability to policy lapse, which may reflect household financial strain, ineffective premium collection, or weak payment reminders.Persistent high rates suggest potential issues in affordability or product suitability. Declining values reflect improved payment discipline, automatic premium collection mechanisms, or targeted retention strategies. !- Definitions and concepts: Grace period: A contractually defined period after a missed premium during which coverage remains active and can be reinstated upon payment. Lapse: Termination of an insurance policy due to non-payment of premiums after the grace period expires. !- Data requirements: Administrative data from licensed insurance companies or supervisory reporting systems. Disaggregation by product type (life, health, motor, microinsurance, etc.), customer segment (individual, group), and insurer type. Definition of grace period based on product category (e.g., 30 days for life insurance, 7–15 days for general insurance).</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>How well does the non-life insurance policy market reflect gender-based differences in policyholding and insured benefits? How do the types of non-life insurance policies held compare by gender? How are gender disparities evolving in the distribution of non-life insurance policies across different FSPs?</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Outcomes</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Suitability</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D149">
         <v>196</v>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="E149" t="inlineStr">
         <is>
           <t>Surrendered insurance policies</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>% of eligible insurance policies (or policyholders) de-activated/lapsed that paid-out surrender values</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="G149" t="inlineStr">
         <is>
           <t>This indicator shows the share of terminated policies that generated a cash surrender payout. It helps distinguish benign expiries or non-cash lapses from value-bearing exits that can strain liquidity, depress embedded value, and signal product-fit or conduct issues (e.g., early surrenders after aggressive sales). Supervisors and boards use it to gauge customer outcomes, the health of savings-type books, and potential mis-selling or affordability problems. !- Definitions and concepts: Eligible policy: contracts with a cash value (e.g., whole life, endowment, unit-linked). Pure risk covers (term, many GI lines) are ineligible. Surrender vs. lapse: a surrender pays cash value on termination; a lapse ends cover without payout. De-activatd here excludes natural maturaties and deaths. Full vs. partial surrender: count full surrenders tied to termination; report partial withdrawals separately unless they trigger de-activation.
 Indicator (count basis): Policies terminated in period with a surrender payout divided by the number of eligible policies terminated (non-maturity) in period. Variants: policyholder-based (unique customers), and amount-based (surrender amounts ÷ cash values of terminated policies). Segment by tenure (&lt;1y, 1–3y, &gt;3y), product, and channel. Data requirements
@@ -8434,71 +8485,9 @@
 Data granularity: partial withdrawals that don’t terminate cover should be excluded or separately disclosed. Conduct lens: high early-tenure surrender shares point to mis-selling or affordability issues—pair with complaints, persistency, and tenure-of-cancellation indicators.</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
+      <c r="H149" t="inlineStr">
         <is>
           <t>Are surrender values and payouts equitably distributed by gender among eligible policyholders? Is there any gender that is less likely to receive surrender payouts, and does this vary by policy type or FSP? How do surrender rates differ by gender when combined with other demographics like income or location?</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Suitability</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D149">
-        <v>195</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Tenure of cancelled insurance policies</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Average time between policy activation and cancellation, by chosen time periods (e.g., &lt;3 months, 3-6 months, 6-12 months, etc)</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>This indicator captures how long policies stay in force before they are cancelled (or lapse mid-term). A concentration of early-tenure cancellations is a red flag for mis-selling, poor onboarding, pricing/friction issues, or product-fit problems. It also matters for economics: early lapses strand acquisition costs, depress embedded value, and erode persistency. Tracking tenure by product and channel helps target remediation (e.g., agent training, cooling-off disclosures, claim-time communications). !- Definitions and concepts: Cancellation: termination of cover before the natural renewal/expiry date—may be customer-initiated (voluntary), insurer-initiated (non-payment, underwriting, fraud), or regulatory. Activation (policy start): the in-force date (not the issue date, if different). Tenure (days/months) = cancellation date – activation date.
-Buckets: choose stable, business-meaningful bands (e.g., &lt;3m, 3–6m, 6–12m, 12–24m, &gt;24m). Report count-weighted and premium-weighted shares. Scope: life and non-life; clarify whether non-renewals at anniversary are counted (usually not) and how cooling-off/free-look rescissions are treated (often reported separately). Data requirements Policy-level fields: policy ID, product/LOB, distribution channel, activation date, cancellation date, cancellation reason code, written premium/sum assured, payment mode, and claim history. Status logic to exclude simple expiries and to de-duplicate reinstated policies (see below). Calendar and cohort views (by issue month/quarter) to remove seasonality. !- Limitations and considerations: Selection bias: averaging only cancelled policies ignores still-active ones. For a fuller view of lifetime behaviour, complement with survival analysis (e.g., Kaplan–Meier) and standard persistency ratios (13/25/61-month). Reinstatements: define whether a reinstated policy’s earlier cancellation is (a) ignored, (b) treated as a separate episode, or (c) measured to the first cancellation only.
-Reason codes matter: split results (voluntary, non-payment, underwriting, fraud). Early non-payment suggests billing/channel issues; early voluntary points to product fit. Channel &amp; product mix: bancassurance, digital, and agency books have distinct early-tenure profiles—always segment. Cooling-off: report &lt;30-day rescissions separately to avoid overstating issues that are procedural rather than structural.</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>At what tenure points do insurance policies tend to be canceled, and do these patterns vary by gender? Is there a gender more likely to cancel policies earlier? How do cancellation patterns differ across policy types, age groups, locations, or income levels? What might early cancellations suggest about policy suitability or customer experience for different genders?</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -8530,7 +8519,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Suitability, Fair treatment</t>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8539,26 +8528,28 @@
         </is>
       </c>
       <c r="D150">
-        <v>61</v>
+        <v>195</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Insurance policy downgrade rate</t>
+          <t>Tenure of  insurance policies</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>% of policies downgraded at the customer's request (e.g.,  lower coverage, higher deductiblees, removal of riders, switch to a lower tier plan)</t>
+          <t>Average time elapsed since policy activation, by chosen time periods (e.g., &lt;3 months, 3-6 months, 6-12 months, etc)</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>This indicator tracks the share of in-force policies that customers voluntarily reduce in coverage during the period. Elevated downgrade activity can signal affordability stress, product misfit, or competitive pressure (customers trading down to cheaper plans). It affects revenue (lower premiums), risk mix (higher deductibles shift loss ratios), and persistency (downgrades may precede lapses or surrenders). Supervisors and boards use the metric to monitor customer outcomes and pricing adequacy, and to gauge the effectiveness of retention strategies that preserve cover while easing budgets. !- Definitions and concepts: Downgrade (customer-initiated): a mid-term endorsement or renewal change that reduces coverage level—e.g., lower sum assured/benefit limits, higher deductibles/co-pays, downgrade of plan tier. Formula (count basis): # policies with customer-requested downgrades in period divided by # active (or renewing) policies in period. !- Limitations and considerations: Multiple events: the same policy may downgrade more than once—decide event vs. policy-unique counting. Product mapping: ensure consistent tier/benefit taxonomy across products. Group policies: member-level downgrades may not map cleanly to master policy counts—state scope.</t>
+          <t>This indicator measures how long policies have stayed in force -including policies that were cancelled or lapsed mid-term. It captures the stability, maturity, and longevity of customer relationships with insurers, distinguishing recently opened accounts from those that have remained active and in use over time, and identifying which policies were cancelled after a short period of activity. A concentration of early-tenure cancellations is a red flag for mis-selling, poor onboarding, pricing/friction issues, or product-fit problems. It also matters for economics: early lapses strand acquisition costs, depress embedded value, and erode persistency. Tracking tenure helps regulators and financial institutions to: Assess policyholder retention and churn rates; Identify short-lived policies that may inflate access statistics; Evaluate the depth and continuity of customer engagement; Analyze cancellations by product and channel to target remediation measures (e.g., agent training, cooling-off disclosures, claim-time communications). From a supervisory perspective, it provides insights into stability, consumer loyalty, and the effectiveness of insurance acquisition campaigns. A longer average tenure indicates stable customer relationships, active usage, and mature market penetration. A high share of new policies may suggest recent inclusion initiatives, but also potential fragility if those policies are cancelled quickly. Monitoring shifts over time can reveal trends in account retention and digital adoption maturity !- Definitions and concepts: Activation (policy start): the in-force date (not the issue date, if different). Cancellation: termination of cover before the natural renewal/expiry date—may be customer-initiated (voluntary), insurer-initiated (non-payment, underwriting, fraud), or regulatory. Tenure of active policies (days/months) = date at the end of the reference period – activation date. Tenure of cancelled policies (days/months) = cancelation date – activation date.
+Buckets: choose stable, business-meaningful bands (e.g., &lt;3m, 3–6m, 6–12m, 12–24m, &gt;24m). Report count-weighted and premium-weighted shares. Scope: life and non-life.  Clarify whether non-renewals at anniversary are counted (usually not) and how cooling-off/free-look rescissions are treated (often reported separately). Data requirements: Policy-level fields: policy ID, product/LOB, distribution channel, activation date, cancellation date, cancellation reason code, written premium/sum assured, payment mode, and claim history. Status logic to exclude simple expiries and to de-duplicate reinstated policies (see below). Calendar and cohort views (by issue month/quarter) to remove seasonality. !- Limitations and considerations: Selection bias: averaging only cancelled policies ignores still-active ones. For a fuller view of lifetime behaviour, complement with survival analysis (e.g., Kaplan–Meier) and standard persistency ratios (13/25/61-month). Reinstatements: define whether a reinstated policy’s earlier cancellation is (a) ignored, (b) treated as a separate episode, or (c) measured to the first cancellation only.
+For cancelled policies, consider including reason codes and analyze results by product type (voluntary, non-payment, underwriting, fraud). Early non-payment suggests billing/channel issues; early voluntary points to product fit. Channel &amp; product mix: bancassurance, digital, and agency books have distinct early-tenure profiles—always segment. Cooling-off: report &lt;30-day rescissions separately to avoid overstating issues that are procedural rather than structural.</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Are there gender disparities in policy downgrade rates, including for MSMEs based on owner gender? Which types of policies experience higher downgrade rates, and could this reflect issues like unsuitable product features or unfavorable premium-to-coverage ratios? How might these downgrade rates relate to claims rejection rates and coverage ratios? Could poor claims experiences or misunderstandings about coverage terms contribute to downgrades? Do FSPs with greater gender diversity exhibit lower downgrade rates?</t>
+          <t>Do genders differ in how long they hold their policies? Are there disproportionate gender differences in longer, medium, or shorter tenures? Does any gender show higher loyalty across different insurers/types? At what tenure points do insurance policies tend to be canceled, and do these patterns vary by gender? Is there a gender more likely to cancel policies earlier? How do cancellation patterns differ across policy types, age groups, locations, or income levels? What might early cancellations suggest about policy suitability or customer experience for different genders?</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -8590,30 +8581,35 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Suitability</t>
+          <t>Suitability, Fair treatment</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D151">
-        <v>206</v>
+        <v>61</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Unpaid matured long-term investments</t>
+          <t>Insurance policy downgrade rate</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>% of long-term investments that have matured but have not yet been paid to investors</t>
+          <t>% of policies downgraded at the customer's request (e.g.,  lower coverage, higher deductiblees, removal of riders, switch to a lower tier plan)</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>This indicator tracks the share of in-force policies that customers voluntarily reduce in coverage during the period. Elevated downgrade activity can signal affordability stress, product misfit, or competitive pressure (customers trading down to cheaper plans). It affects revenue (lower premiums), risk mix (higher deductibles shift loss ratios), and persistency (downgrades may precede lapses or surrenders). Supervisors and boards use the metric to monitor customer outcomes and pricing adequacy, and to gauge the effectiveness of retention strategies that preserve cover while easing budgets. !- Definitions and concepts: Downgrade (customer-initiated): a mid-term endorsement or renewal change that reduces coverage level—e.g., lower sum assured/benefit limits, higher deductibles/co-pays, downgrade of plan tier. Formula (count basis): # policies with customer-requested downgrades in period divided by # active (or renewing) policies in period. !- Limitations and considerations: Multiple events: the same policy may downgrade more than once—decide event vs. policy-unique counting. Product mapping: ensure consistent tier/benefit taxonomy across products. Group policies: member-level downgrades may not map cleanly to master policy counts—state scope.</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>What percentage of unpaid matured longer-term investments is attributable to each gender? Are unpaid amounts disproportionately concentrated in any gender? How do FSPs rank in terms of unpaid proportions of matured longer-term investments by gender?</t>
+          <t>Are there gender disparities in policy downgrade rates, including for MSMEs based on owner gender? Which types of policies experience higher downgrade rates, and could this reflect issues like unsuitable product features or unfavorable premium-to-coverage ratios? How might these downgrade rates relate to claims rejection rates and coverage ratios? Could poor claims experiences or misunderstandings about coverage terms contribute to downgrades? Do FSPs with greater gender diversity exhibit lower downgrade rates?</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -8623,17 +8619,17 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Market development</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Capital markets development</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -8645,35 +8641,30 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Suitability, Fair treatment</t>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Pensions</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="D152">
-        <v>34</v>
+        <v>206</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Pension fund switching rate</t>
+          <t>Unpaid matured long-term investments</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>% of all pension accounts that have switched to another pension fund administrator</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>An indicator of switching rates among pension recipients is a metric used to measure the frequency or volume of pension fund members who transfer their accumulated savings from one pension fund administrator (PFA) to another within a specific timeframe. This indicator can be used in countries where there is a private pension fund adminsitration industry, but not in countries where the entirety of the pension system is publicly-funded. This indicator serves as a key barometer of competition, customer satisfaction, and market dynamics within the pension industry. It can signal trends to administrators, regulators, and members themselves.  Switching Rate (%) = Total average number of members in the system / number of members who switched pension fund administrators  ×100</t>
+          <t>% of long-term investments that have matured but have not yet been paid to investors</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>How do transfers of pension fund balances to a different pension fund administrator vary by gender? Does this vary according to the level of FSP gender diversity? What percentage of contributors transferred funds compared to all customers, and are there gender disparities in this proportion? Are certain customer segments, such as women, women-owned MSMEs, and low-value accounts, more likely to make high-to-low transfers (switching to a fund administrator that has been paying lower returns)? Are FSPs with higher levels of gender diversity less likely to receive savers coming from an administrator that previously paid higher returns?</t>
+          <t>What percentage of unpaid matured longer-term investments is attributable to each gender? Are unpaid amounts disproportionately concentrated in any gender? How do FSPs rank in terms of unpaid proportions of matured longer-term investments by gender?</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -8683,17 +8674,17 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Market development</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Capital markets development</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Pension type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -8705,35 +8696,35 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Suitability</t>
+          <t>Suitability, Fair treatment</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Savings</t>
+          <t>Pensions</t>
         </is>
       </c>
       <c r="D153">
-        <v>151</v>
+        <v>34</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Tenure of deposit and payment accounts</t>
+          <t>Pension fund switching rate</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Average time elapsed since account opening</t>
+          <t>% of all pension accounts that have switched to another pension fund administrator</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Measures the length of time that deposit and payment accounts have been open, can be expressed as an average or as the share of accounts in tenure categories such as &lt;3 months, 3–6 months, 6–12 months, 1–3 years, &gt;3 years, etc. It reflects the age profile of active accounts held by customers at regulated financial institutions and payment service providers. Captures the stability, maturity, and longevity of customer relationships with financial institutions. It is a key behavioral measure of financial inclusion sustainability, distinguishing recently opened accounts from those that have remained active and in use over time. Tracking account tenure helps regulators and financial institutions to: Assess account retention and churn rates in deposit and payment systems; Monitor sustained usage versus one-off account openings, especially under inclusion programs; Identify short-lived or dormant accounts that may inflate access statistics; Evaluate the depth and continuity of customer engagement with the financial system. From a supervisory perspective, it provides insights into financial system stability, consumer loyalty, and the effectiveness of account-opening campaigns. A longer average tenure indicates stable customer relationships, active usage, and mature market penetration. A high share of newly opened accounts may suggest recent inclusion initiatives, but also potential fragility if those accounts become inactive. Monitoring shifts over time can reveal trends in account retention and digital adoption maturity. !- Definitions and concepts: Deposit accounts: Savings, current, or term accounts offered by regulated deposit-taking institutions. Payment accounts: Accounts used to execute payment transactions or access funds on demand, including e-money and digital wallets. !- Data requirements: Account-level data from administrative records containing the account opening date; Total number of accounts. The tenure is calculated as the difference between the data of the end of the reference period and the account opening data (expressed in years or months).</t>
+          <t>An indicator of switching rates among pension recipients is a metric used to measure the frequency or volume of pension fund members who transfer their accumulated savings from one pension fund administrator (PFA) to another within a specific timeframe. This indicator can be used in countries where there is a private pension fund adminsitration industry, but not in countries where the entirety of the pension system is publicly-funded. This indicator serves as a key barometer of competition, customer satisfaction, and market dynamics within the pension industry. It can signal trends to administrators, regulators, and members themselves.  Switching Rate (%) = Total average number of members in the system / number of members who switched pension fund administrators  ×100</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Do genders differ in how long they hold their transaction accounts? Are some genders disproportionately represented in longer, medium, or shorter account tenures? Which genders show higher account loyalty across different FSPs/types, and which tend to close accounts sooner?</t>
+          <t>How do transfers of pension fund balances to a different pension fund administrator vary by gender? Does this vary according to the level of FSP gender diversity? What percentage of contributors transferred funds compared to all customers, and are there gender disparities in this proportion? Are certain customer segments, such as women, women-owned MSMEs, and low-value accounts, more likely to make high-to-low transfers (switching to a fund administrator that has been paying lower returns)? Are FSPs with higher levels of gender diversity less likely to receive savers coming from an administrator that previously paid higher returns?</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -8743,17 +8734,17 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Stability, safety and soundness</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Liquidity risk</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Pension type</t>
         </is>
       </c>
     </row>
@@ -8770,91 +8761,91 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
+          <t>Savings</t>
+        </is>
+      </c>
+      <c r="D154">
+        <v>151</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Tenure of deposit and payment accounts</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Average time elapsed since account opening</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Measures the length of time that deposit and payment accounts have been open, can be expressed as an average or as the share of accounts in tenure categories such as &lt;3 months, 3–6 months, 6–12 months, 1–3 years, &gt;3 years, etc. It reflects the age profile of active accounts held by customers at regulated financial institutions and payment service providers. Captures the stability, maturity, and longevity of customer relationships with financial institutions. It is a key behavioral measure of financial inclusion sustainability, distinguishing recently opened accounts from those that have remained active and in use over time. Tracking account tenure helps regulators and financial institutions to: Assess account retention and churn rates in deposit and payment systems; Monitor sustained usage versus one-off account openings, especially under inclusion programs; Identify short-lived or dormant accounts that may inflate access statistics; Evaluate the depth and continuity of customer engagement with the financial system. From a supervisory perspective, it provides insights into financial system stability, consumer loyalty, and the effectiveness of account-opening campaigns. A longer average tenure indicates stable customer relationships, active usage, and mature market penetration. A high share of newly opened accounts may suggest recent inclusion initiatives, but also potential fragility if those accounts become inactive. Monitoring shifts over time can reveal trends in account retention and digital adoption maturity. !- Definitions and concepts: Deposit accounts: Savings, current, or term accounts offered by regulated deposit-taking institutions. Payment accounts: Accounts used to execute payment transactions or access funds on demand, including e-money and digital wallets. !- Data requirements: Account-level data from administrative records containing the account opening date; Total number of accounts. The tenure is calculated as the difference between the data of the end of the reference period and the account opening data (expressed in years or months).</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Do genders differ in how long they hold their transaction accounts? Are some genders disproportionately represented in longer, medium, or shorter account tenures? Which genders show higher account loyalty across different FSPs/types, and which tend to close accounts sooner?</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Liquidity risk</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Suitability</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
           <t>Payments, Savings, Pensions, Investments</t>
         </is>
       </c>
-      <c r="D154">
+      <c r="D155">
         <v>158</v>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E155" t="inlineStr">
         <is>
           <t>Inactive and dormant accounts (balance)</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>% of total account balances that are held in inactive and dormant accounts</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t>This indicator shows the share of funds sitting in deposit and payment accounts (excluding term deposits) that are not actively used by customers. High concentrations of idle balances can signal weak customer engagement, poor product fit, or frictions in account usage—important for financial-inclusion quality, liquidity management, and conduct risk. From a prudential angle, large dormant balances may look “stable” but can reverse if reactivation drives or policy changes prompt withdrawals. For consumer protection, persistent dormancy raises risks around unclaimed funds, fees, and fraud. Recommended to analyze of this indicator by product type (e.g. current/checking, mobile money, etc). !- Definitions and concepts: Accounts: demand/current accounts and other payment-capable deposit accounts. Inactive account: no customer-initiated debit/credit (card use, cash withdrawal/deposit, transfer) for a defined window (e.g., ≥90 or 180 days). System entries (interest, fees, bank corrections) don’t count. Dormant account: extended inactivity beyond a longer threshold (commonly ≥12 months) that may trigger special handling (restricted access, outreach, escheatment). Indicator formula: Balances in inactive + dormant transaction accounts divided by total transaction-account balances. Reporting the split (inactive vs. dormant) can provide further detail. !- Data requirements: Core-banking ledger with end-of-day balances, product codes, and last customer-initiated activity timestamp per account. Classification rules reflecting local definitions (inactive/dormant thresholds; treatment of standing orders/auto-debits). Ownership segment (retail/SME), currency, and insured/uninsured flags. Optional: outreach attempts, reactivation outcomes, and fee assessments to monitor conduct risk. Limitations &amp; considerations: Definition divergence: thresholds and what counts as “activity” vary by jurisdiction and even by institution—state methodology clearly. Data quality: some channels (agents, fintech front-ends) may not update the core “last activity” field, overstating dormancy.
 Seasonality &amp; cycles: balances can spike around payroll/tax periods; use consistent month-end or averages. Policy effects: dormancy fees, auto-closures, and unclaimed-funds rules materially affect trends. Coverage scope: exclude escrow, trust, and suspense ledgers to avoid inflating inactive balances.</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
+      <c r="H155" t="inlineStr">
         <is>
           <t>What proportion of balances held in inactive/dormant/suspense accounts is attributable to each gender? Are these balances disproportionately skewed by gender? Which FSPs have notable skews (higher than market averages) in balances held in inactive/dormant/suspense accounts by gender?</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Account type</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Suitability</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D155">
-        <v>161</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Revenue from inactive and dormant accounts</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Average non-interest revenue earned on inactive and dormant accounts per account holder</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>This indicator estimates how much fee income a provider earns, on average, from customers whose transaction accounts are inactive or dormant. It highlights potential conduct-risk hotspots (“junk fees”), tests whether inclusion policies translate into active use, and helps gauge earnings reliance on non-usage charges. Regulators often scrutinize such revenue because it may disproportionately affect vulnerable or low-balance customers and can conflict with fair-treatment principles or local dormancy rules. Used alongside % balances in inactive/dormant accounts, reactivation rates, and complaints upheld about fees, this metric provides a balanced view of inclusion quality and earnings fairness. !- Definitions and concepts: Inactive account: no customer-initiated transaction over a defined window (e.g., ≥90/180 days). Dormant account: extended inactivity (e.g., ≥12 months) triggering special handling (restricted access, outreach, or escheatment). Non-interest revenue: maintenance/inactivity fees, SMS/statement charges, card fees, ATM/network fees, account closure fees—exclude interest, FX spreads, and lending-related fees. Metric (per holder): Avg. fee per inactive/dormant holder = [Non interest fees charged to inactive+dormant accounts in period (net of waivers/refunds)] divided by unique customers with ≥1 inactive or dormant account in period. Report per-account as a companion view, and show inactive vs dormant separately. !- Data requirements: Core-banking extracts: account status, last customer-initiated activity timestamp, balances, product code. General-ledger fee income by fee code with identifiers to tie fees to specific accounts/customers; flags for waivers/refunds/chargebacks. Customer master data to deduplicate holders with multiple accounts. Policy tables: inactivity/dormancy thresholds, fee schedules, and escheatment rules; time-at-risk (days classified as inactive/dormant). !- Limitations and considerations: Definition variance: thresholds and what counts as “activity” differ—state methodology. Partial-period bias: accounts turning dormant late in the period face fewer fee days; consider normalizing by days inactive/dormant. Outliers &amp; distribution: averages can be skewed; also report median, 90th percentile, and % of affected customers. Conduct/regulatory constraints: some jurisdictions cap or ban dormancy fees or require fee cessation before escheatment—track compliance and annotate series breaks after rule changes. Mix effects: product/channel mixes (e.g., basic accounts, youth or social-transfer accounts) drive fee propensity—segment results by product and customer segment.</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>How does the average revenue earned from inactive and dormant accounts compare by gender? Are there gender disparities in the charges applied to these accounts compared to the overall market average? How do relevant FSPs rank in terms of the average revenue earned from these accounts, and does this ranking change when analyzed by gender?</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -8891,30 +8882,30 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Payments, Savings, Pensions, Investments</t>
         </is>
       </c>
       <c r="D156">
-        <v>229</v>
+        <v>161</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Product take-up ratio</t>
+          <t>Revenue from inactive and dormant accounts</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>% of approved applicants who take-up the approved products by product type</t>
+          <t>Average non-interest revenue earned on inactive and dormant accounts per account holder</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Share of applicants that are approved for a specific product type that take-up the product. This indicator can be viewed together with the product application indicator to allow for a more comprehensive analysis of the demand for financial products. Product categoreis to consider for analysis include: deposits, investments, insurance, credit.</t>
+          <t>This indicator estimates how much fee income a provider earns, on average, from customers whose transaction accounts are inactive or dormant. It highlights potential conduct-risk hotspots (“junk fees”), tests whether inclusion policies translate into active use, and helps gauge earnings reliance on non-usage charges. Regulators often scrutinize such revenue because it may disproportionately affect vulnerable or low-balance customers and can conflict with fair-treatment principles or local dormancy rules. Used alongside % balances in inactive/dormant accounts, reactivation rates, and complaints upheld about fees, this metric provides a balanced view of inclusion quality and earnings fairness. !- Definitions and concepts: Inactive account: no customer-initiated transaction over a defined window (e.g., ≥90/180 days). Dormant account: extended inactivity (e.g., ≥12 months) triggering special handling (restricted access, outreach, or escheatment). Non-interest revenue: maintenance/inactivity fees, SMS/statement charges, card fees, ATM/network fees, account closure fees—exclude interest, FX spreads, and lending-related fees. Metric (per holder): Avg. fee per inactive/dormant holder = [Non interest fees charged to inactive+dormant accounts in period (net of waivers/refunds)] divided by unique customers with ≥1 inactive or dormant account in period. Report per-account as a companion view, and show inactive vs dormant separately. !- Data requirements: Core-banking extracts: account status, last customer-initiated activity timestamp, balances, product code. General-ledger fee income by fee code with identifiers to tie fees to specific accounts/customers; flags for waivers/refunds/chargebacks. Customer master data to deduplicate holders with multiple accounts. Policy tables: inactivity/dormancy thresholds, fee schedules, and escheatment rules; time-at-risk (days classified as inactive/dormant). !- Limitations and considerations: Definition variance: thresholds and what counts as “activity” differ—state methodology. Partial-period bias: accounts turning dormant late in the period face fewer fee days; consider normalizing by days inactive/dormant. Outliers &amp; distribution: averages can be skewed; also report median, 90th percentile, and % of affected customers. Conduct/regulatory constraints: some jurisdictions cap or ban dormancy fees or require fee cessation before escheatment—track compliance and annotate series breaks after rule changes. Mix effects: product/channel mixes (e.g., basic accounts, youth or social-transfer accounts) drive fee propensity—segment results by product and customer segment.</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>How do take-up rates vary by gender? Do any genders have higher take-up rates than the overall market average? How do FSPs compare in terms of take-up rates by gender?</t>
+          <t>How does the average revenue earned from inactive and dormant accounts compare by gender? Are there gender disparities in the charges applied to these accounts compared to the overall market average? How do relevant FSPs rank in terms of the average revenue earned from these accounts, and does this ranking change when analyzed by gender?</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -8929,12 +8920,12 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Uptake (account ownership)</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Product type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Account type</t>
         </is>
       </c>
     </row>
@@ -8946,35 +8937,35 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Fair treatment</t>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Savings</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D157">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Account closure costs paid by customers</t>
+          <t>Product take-up ratio</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Average customer-paid account closure charges</t>
+          <t>% of approved applicants who take-up the approved products by product type</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>This indicator captures the out-of-pocket costs borne by customers when they close their transaction account(s). It focuses on fees directly tied to the closure process (not ongoing usage fees). High averages or wide dispersion can signal unfair fee structures, poor process design (e.g., costly payout rails), or weak disclosures—issues that draw conduct-risk scrutiny and harm inclusion goals. Tracking this metric alongside complaints upheld about closure, time to close, and payout failure/return rates gives a rounded view of off-boarding fairness and efficiency. !- Definitions and concepts: Transaction accounts are broadly defined as an account held with a bank or other authorised and/or regulated service provider (including a non-bank) which can be used to make and receive payments. Transaction accounts can be further differentiated into deposit transaction accounts and e-money accounts. Customer-paid closure charges: amounts debited to the customer because of closure, including: explicit closure fees, final statement/document fees, card/cheque deactivation fees, balance-refund/payout charges (e.g., wire/RTGS, cheque issuance, e-money cash-out), account package early-termination fees, statutory taxes/levies linked to these items, and FX/transfer margins if required to remit funds. Exclusions: regular monthly maintenance already charged prior to the closure request, penalty interest on unrelated lending, and third-party fees not passed through. !- Data requirements: Event log with closure request date and closure completion date; customer ID (deduplicated), number of accounts closed, channel, reason code. Transaction-level fee taxonomy to flag closure-related charges; payout transactions (method, amount, fees, FX). Reversal/waiver flags and timestamps to net back rescinded charges. Recommended charge window: from request date through T+30 days after completion to catch settlement/payout fees. Number of customers who closed at least 1 account in period. !- Limitations and considerations: Attribution: define the fee list upfront to avoid counting routine usage fees; publish the measurement window.</t>
+          <t>Share of applicants that are approved for a specific product type that take-up the product. This indicator can be viewed together with the product application indicator to allow for a more comprehensive analysis of the demand for financial products. Product categoreis to consider for analysis include: deposits, investments, insurance, credit.</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>How do relevant FSPs rank in terms of closing costs (from highest to lowest), and does this ranking change when the average is computed by gender? Are women and men equally likely to incur account closure fees, or are there gendered patterns in the types of financial service providers (FSPs) they use that influence the likelihood or amount of such fees? How might account closure costs act as a barrier to financial flexibility or mobility? Are women more likely to avoid formal financial services due to concerns over the cost of exiting the system? Additionally, are FSPs that charge lower or no closure fees more accessible to certain gender groups, and does this vary by geography or provider type?</t>
+          <t>How do take-up rates vary by gender? Do any genders have higher take-up rates than the overall market average? How do FSPs compare in terms of take-up rates by gender?</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -8984,17 +8975,17 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Financial inclusion; Market development</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Outcomes, Capital markets development</t>
+          <t>Uptake (account ownership)</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Product type</t>
         </is>
       </c>
     </row>
@@ -9006,35 +8997,35 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Suitability</t>
+          <t>Fair treatment</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Savings</t>
         </is>
       </c>
       <c r="D158">
-        <v>389</v>
+        <v>162</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Insurance claims (number)</t>
+          <t>Account closure costs paid by customers</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Number of insurance claims</t>
+          <t>Average customer-paid account closure charges</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>The total count of insurance claims formally submitted by policyholders, beneficiaries, or authorized third parties to an insurer within a defined reporting period, regardless of whether the claims are accepted, rejected, paid, or still under review. Denominator for several key inclusion, consumer protection and prudential insurance ratios. !- Data requirements: Claim identifier, (unique ID per claim), Policyholder identifier, Date of claim submission.</t>
+          <t>This indicator captures the out-of-pocket costs borne by customers when they close their transaction account(s). It focuses on fees directly tied to the closure process (not ongoing usage fees). High averages or wide dispersion can signal unfair fee structures, poor process design (e.g., costly payout rails), or weak disclosures—issues that draw conduct-risk scrutiny and harm inclusion goals. Tracking this metric alongside complaints upheld about closure, time to close, and payout failure/return rates gives a rounded view of off-boarding fairness and efficiency. !- Definitions and concepts: Transaction accounts are broadly defined as an account held with a bank or other authorised and/or regulated service provider (including a non-bank) which can be used to make and receive payments. Transaction accounts can be further differentiated into deposit transaction accounts and e-money accounts. Customer-paid closure charges: amounts debited to the customer because of closure, including: explicit closure fees, final statement/document fees, card/cheque deactivation fees, balance-refund/payout charges (e.g., wire/RTGS, cheque issuance, e-money cash-out), account package early-termination fees, statutory taxes/levies linked to these items, and FX/transfer margins if required to remit funds. Exclusions: regular monthly maintenance already charged prior to the closure request, penalty interest on unrelated lending, and third-party fees not passed through. !- Data requirements: Event log with closure request date and closure completion date; customer ID (deduplicated), number of accounts closed, channel, reason code. Transaction-level fee taxonomy to flag closure-related charges; payout transactions (method, amount, fees, FX). Reversal/waiver flags and timestamps to net back rescinded charges. Recommended charge window: from request date through T+30 days after completion to catch settlement/payout fees. Number of customers who closed at least 1 account in period. !- Limitations and considerations: Attribution: define the fee list upfront to avoid counting routine usage fees; publish the measurement window.</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>How do claim numbers vary by gender? Are there any gender groups logging fewer claims compared to the market average? Are there FSPs with particularly low or high claim numbers for certain genders? How do claim statistics intersect with policy type and customer demographics?</t>
+          <t>How do relevant FSPs rank in terms of closing costs (from highest to lowest), and does this ranking change when the average is computed by gender? Are women and men equally likely to incur account closure fees, or are there gendered patterns in the types of financial service providers (FSPs) they use that influence the likelihood or amount of such fees? How might account closure costs act as a barrier to financial flexibility or mobility? Are women more likely to avoid formal financial services due to concerns over the cost of exiting the system? Additionally, are FSPs that charge lower or no closure fees more accessible to certain gender groups, and does this vary by geography or provider type?</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9044,17 +9035,17 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
+          <t>Financial inclusion; Market development</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Usage, Soundness</t>
+          <t>Outcomes, Capital markets development</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9057,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Fair treatment</t>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9075,26 +9066,26 @@
         </is>
       </c>
       <c r="D159">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Insurance claims paid</t>
+          <t>Insurance claims (number)</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Value of insurance claims paid</t>
+          <t>Number of insurance claims</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>"Claims paid" represents the total cash outflow or settled obligations by an insurer to policyholders or beneficiaries for claims events during a reporting period. It includes only claims for which payment has been disbursed, regardless of whether additional claims are still outstanding or whether reserves were previously established. Tracking claims paid helps supervisors monitor liquidity, operational efficiency, and consumer protection outcomes. It provides a concrete measure of the insurer’s fulfillment of contractual obligations and complements other claims indicators (e.g., claims incurred, claims outstanding, unpaid approved claims). !- Data requirements: Claim identifier, (unique ID per claim), Policyholder identifier, Date of claim submission, Date of payment, Amount paid (full or partial), Product / policy type; . !- Limitations and considerations: paid claims may lag claims incurred due to reporting delays or extended claims handling processes; some claims are paid in installments, methodology must specify whether to include full or partial amounts; severe events can cause sudden increases in paid claims, interpretation should consider context. Segmentation by product line or policy type is recommended for supervisory analysis.</t>
+          <t>The total count of insurance claims formally submitted by policyholders, beneficiaries, or authorized third parties to an insurer within a defined reporting period, regardless of whether the claims are accepted, rejected, paid, or still under review. Denominator for several key inclusion, consumer protection and prudential insurance ratios. !- Data requirements: Claim identifier, (unique ID per claim), Policyholder identifier, Date of claim submission.</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>How do claim payments vary by gender? Are there any gender groups receiving fewer/lower payments compared to the market average? Are there FSPs with particularly low or high payment rate for certain genders? How do claim payment statistics intersect with policy type and customer demographics?</t>
+          <t>How do claim numbers vary by gender? Are there any gender groups logging fewer claims compared to the market average? Are there FSPs with particularly low or high claim numbers for certain genders? How do claim statistics intersect with policy type and customer demographics?</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9121,40 +9112,40 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Stability, safety and soundness</t>
+          <t>Consumer protection</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>AML/CFT</t>
+          <t>Fair treatment</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D160">
-        <v>64</v>
+        <v>390</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Suspicious transaction reports</t>
+          <t>Insurance claims paid</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Number of suspicious transaction reports</t>
+          <t>Value of insurance claims paid</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>The indicator tallies the suspicious transaction reports (STRs)  financial service providers file with the Financial Intelligence Unit (FIU) when they suspect financial crimes such as money-laundering and terrorism financing. A rising count can signal stronger transaction monitoring systems or higher level of potentially criminal activities. Policymakers use STR volumes, in combination with other data (e.g., investigations), to allocate investigative resources. !- Definitions and concepts: Suspicious Transaction Report (STR): a mandatory report filed when a transaction is known, suspected, or has reasonable grounds to be suspected of involving criminal proceeds or terrorist funds (FATF Rec. 20). Reporting entities: broadly, all institutions covered by the AML/CFT law, including all finacial financial service providers. !- Data requirements: FIU registry of incoming STRs, ideally tagged by date, reporting institution, sector, transaction channel, predicate crime category, and outcome (e.g., disseminated to law-enforcement), and customer gender. Data quality: Duplicate submissions, incomplete narratives, or vague suspicion reasons hamper analysis and inflate reported numbers without real value. Confidentiality constraints: Detailed STR data including customer gender may be restricted.</t>
+          <t>"Claims paid" represents the total cash outflow or settled obligations by an insurer to policyholders or beneficiaries for claims events during a reporting period. It includes only claims for which payment has been disbursed, regardless of whether additional claims are still outstanding or whether reserves were previously established. Tracking claims paid helps supervisors monitor liquidity, operational efficiency, and consumer protection outcomes. It provides a concrete measure of the insurer’s fulfillment of contractual obligations and complements other claims indicators (e.g., claims incurred, claims outstanding, unpaid approved claims). !- Data requirements: Claim identifier, (unique ID per claim), Policyholder identifier, Date of claim submission, Date of payment, Amount paid (full or partial), Product / policy type; . !- Limitations and considerations: paid claims may lag claims incurred due to reporting delays or extended claims handling processes; some claims are paid in installments, methodology must specify whether to include full or partial amounts; severe events can cause sudden increases in paid claims, interpretation should consider context. Segmentation by product line or policy type is recommended for supervisory analysis.</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the volume of Suspiciou transaction reports (STRs) generated, including for MSMEs by the owner's gender? Are there disparities in STR statistics across FSPs with different levels of gender diversity?</t>
+          <t>How do claim payments vary by gender? Are there any gender groups receiving fewer/lower payments compared to the market average? Are there FSPs with particularly low or high payment rate for certain genders? How do claim payment statistics intersect with policy type and customer demographics?</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9162,9 +9153,19 @@
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Usage, Soundness</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -9185,26 +9186,26 @@
         </is>
       </c>
       <c r="D161">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Systematic reporting to financial intelligence unit/office (FIU)</t>
+          <t>Suspicious transaction reports</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Number of transactions reported (excluding suspicious transaction reports) to FIU</t>
+          <t>Number of suspicious transaction reports</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>This indicator counts all objective anti-money-laundering (AML) disclosures that reporting institutions file with the FIU other than Suspicious Transaction Reports (STRs)—for example Cash / Large-Value Transaction Reports (CTRs/LCTRs), Cross-Border Currency Reports (CBCRs), Electronic Funds Transfer Reports (EFTIs), and threshold-based filings. Tracking the volume highlights how much potentially risky activity flows through the regulated system, tests the reach and effectiveness of automated monitoring engines, and helps the FIU size analytical workloads and allocate investigative resources. When combined with STR counts and outcome statistics, this indicator offers a comprehensive perspective on the preventive arm of the AML/CFT framework. !- Definitions and concepts: Objective reports: filings triggered automatically when a transaction exceeds a statutory threshold or meets a predefined typology—irrespective of suspicion. Thresholds are set at national level and vary across countries. Reporting entities: all AML-obliged financial institutions. Optional denominator metrics to enable intensity ratios: total transactions processed or number of active customers. !- Data requirements: FIU registry of objective-report filings with unique identifiers. Data-quality variance: Missing customer identifiers or incorrect codes hinder FIU analytics; robust validation routines are essential.</t>
+          <t>The indicator tallies the suspicious transaction reports (STRs)  financial service providers file with the Financial Intelligence Unit (FIU) when they suspect financial crimes such as money-laundering and terrorism financing. A rising count can signal stronger transaction monitoring systems or higher level of potentially criminal activities. Policymakers use STR volumes, in combination with other data (e.g., investigations), to allocate investigative resources. !- Definitions and concepts: Suspicious Transaction Report (STR): a mandatory report filed when a transaction is known, suspected, or has reasonable grounds to be suspected of involving criminal proceeds or terrorist funds (FATF Rec. 20). Reporting entities: broadly, all institutions covered by the AML/CFT law, including all finacial financial service providers. !- Data requirements: FIU registry of incoming STRs, ideally tagged by date, reporting institution, sector, transaction channel, predicate crime category, and outcome (e.g., disseminated to law-enforcement), and customer gender. Data quality: Duplicate submissions, incomplete narratives, or vague suspicion reasons hamper analysis and inflate reported numbers without real value. Confidentiality constraints: Detailed STR data including customer gender may be restricted.</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Are there customer gender disparities in the volume of systematic transaction reports (transactions that are not suspicious but reach regulatory thresholds for reporting) to the FIU, including for MSMEs by the owner's gender? Is there a correlation between the volume of these reports and the composition of the FSP customer base by gender? For example, do FSPs with a higher proportion of women in their customer base report a lower volume of systematic transaction reports, including those involving women? How do FSPs with different levels of gender diversity differ in the patterns of systematic reporting to the FIU?</t>
+          <t>Are there gender disparities in the volume of Suspiciou transaction reports (STRs) generated, including for MSMEs by the owner's gender? Are there disparities in STR statistics across FSPs with different levels of gender diversity?</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9214,7 +9215,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Transaction type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -9226,35 +9227,35 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Credit risk</t>
+          <t>AML/CFT</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D162">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Gender composition of loan guarantors</t>
+          <t>Systematic reporting to financial intelligence unit/office (FIU)</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Gender composition of guarantors in the retail loan portfolio</t>
+          <t>Number of transactions reported (excluding suspicious transaction reports) to FIU</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Measures the representation of different genders among the individuals who act as loan guarantors--pledge to repay a loan if the borrower defaults. It offers a sophisticated lens through which to view credit risk, gender-based economic disparities, and the social dynamics that underpin a loan portfolio. It can reveal hidden concentration risks. For example, if a large portion of a bank's small business loans are guaranteed by the male spouses of female entrepreneurs, the portfolio's risk profile becomes heavily correlated with the financial health and stability of that specific demographic.  This metric also provides insights into the structural barriers different genders face when seeking credit. If the data shows that female borrowers disproportionately require male guarantors (while the reverse is not true), it can signal underlying biases in credit assessment or a disparity in asset ownership. Prudential supervisors may also be interested in finding out whether the different permutations of borrower's and guarantor's gender could relate to loan performance. Conduct supervisors would use it to scrutinize lending practices for fairness and equity.</t>
+          <t>This indicator counts all objective anti-money-laundering (AML) disclosures that reporting institutions file with the FIU other than Suspicious Transaction Reports (STRs)—for example Cash / Large-Value Transaction Reports (CTRs/LCTRs), Cross-Border Currency Reports (CBCRs), Electronic Funds Transfer Reports (EFTIs), and threshold-based filings. Tracking the volume highlights how much potentially risky activity flows through the regulated system, tests the reach and effectiveness of automated monitoring engines, and helps the FIU size analytical workloads and allocate investigative resources. When combined with STR counts and outcome statistics, this indicator offers a comprehensive perspective on the preventive arm of the AML/CFT framework. !- Definitions and concepts: Objective reports: filings triggered automatically when a transaction exceeds a statutory threshold or meets a predefined typology—irrespective of suspicion. Thresholds are set at national level and vary across countries. Reporting entities: all AML-obliged financial institutions. Optional denominator metrics to enable intensity ratios: total transactions processed or number of active customers. !- Data requirements: FIU registry of objective-report filings with unique identifiers. Data-quality variance: Missing customer identifiers or incorrect codes hinder FIU analytics; robust validation routines are essential.</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the representation of loan guarantors? What types of loans and borrowers, across different FSP types, are more likely to show gender disparities in the use of guarantors? Are there disparities in loan performance (NPLs, delinquency, interest income) depending on the gender of the guarantor?</t>
+          <t>Are there customer gender disparities in the volume of systematic transaction reports (transactions that are not suspicious but reach regulatory thresholds for reporting) to the FIU, including for MSMEs by the owner's gender? Is there a correlation between the volume of these reports and the composition of the FSP customer base by gender? For example, do FSPs with a higher proportion of women in their customer base report a lower volume of systematic transaction reports, including those involving women? How do FSPs with different levels of gender diversity differ in the patterns of systematic reporting to the FIU?</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -9262,19 +9263,9 @@
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>Fair treatment</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Product type</t>
+          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Transaction type</t>
         </is>
       </c>
     </row>
@@ -9295,26 +9286,26 @@
         </is>
       </c>
       <c r="D163">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Delinquency rate in the retail loan portfolio</t>
+          <t>Gender composition of loan guarantors</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Volume and value of delinquent retail loans as a proportion of total retail portfolio</t>
+          <t>Gender composition of guarantors in the retail loan portfolio</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>The delinquency rate tracks the share of consumer loans—mortgages, credit-cards, instalment loans, auto, buy-now-pay-later, qualifying MSEs—that have fallen past due but have not yet crossed the “non-performing” threshold or been written off. Rising early-stage arrears are an early-warning signal of household stress and of future spikes in non-performing loans (NPLs), provisions and write-offs. Paired with NPL, restructuring and write-off metrics, the delinquency rate provides a forward-looking barometer of retail credit health. Supervisors and risk managers use the metric to test the effectiveness of underwriting standards, consumer disclosure, customer interfaces (for digital loans), and pricing for credit risk. !- Definitions and concepts: Loan delinquency refers to a situation in which borrowed money is not paid back as agreed. A loan becomes delinquent when a borrower misses a regular installment payment. A delinquent loan is any kind of loan that has past due payments but has yet to go into default. On a value basis, this indicator measures the total outstanding balances past due (for example greater than 1 day past due) as a share of gross retail loan balances at the end of a specified period. Operational cut-offs: Inconsistent days past due calculation (calendar days vs. business days, partial payments) hinders cross-lender comparability.</t>
+          <t>Measures the representation of different genders among the individuals who act as loan guarantors--pledge to repay a loan if the borrower defaults. It offers a sophisticated lens through which to view credit risk, gender-based economic disparities, and the social dynamics that underpin a loan portfolio. It can reveal hidden concentration risks. For example, if a large portion of a bank's small business loans are guaranteed by the male spouses of female entrepreneurs, the portfolio's risk profile becomes heavily correlated with the financial health and stability of that specific demographic.  This metric also provides insights into the structural barriers different genders face when seeking credit. If the data shows that female borrowers disproportionately require male guarantors (while the reverse is not true), it can signal underlying biases in credit assessment or a disparity in asset ownership. Prudential supervisors may also be interested in finding out whether the different permutations of borrower's and guarantor's gender could relate to loan performance. Conduct supervisors would use it to scrutinize lending practices for fairness and equity.</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Are there gender disparities (including for MSMEs based on the gender of ownership) in delinquency rates (also considering the number of unpaid installments) for loans of different types, terms and sizes? Do smaller loans have lower delinquency rates and how does this vary across genders? Do FSPs with higher levels of gender diversity present lower delinquency rates?</t>
+          <t>Are there gender disparities in the representation of loan guarantors? What types of loans and borrowers, across different FSP types, are more likely to show gender disparities in the use of guarantors? Are there disparities in loan performance (NPLs, delinquency, interest income) depending on the gender of the guarantor?</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -9324,12 +9315,12 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
+          <t>Consumer protection</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Outcomes, Suitability, Credit risk</t>
+          <t>Fair treatment</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -9355,26 +9346,26 @@
         </is>
       </c>
       <c r="D164">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Non performing loans (NPLs) in the retail portfolio</t>
+          <t>Delinquency rate in the retail loan portfolio</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Non performing loans rate in the retail/MSME loan portfolio</t>
+          <t>Volume and value of delinquent retail loans as a proportion of total retail portfolio</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>The NPL indicator for the retail loan portfolio quantifies the share (or absolute value) of consumer and MSE loans that are unlikely to be fully repaid. Because retail credit typically involves high volumes of granular, often unsecured exposures, a build-up of NPLs signals mounting credit risk costs, pressure on provisioning, and potential stress. Supervisors track this metric to assess lenders' underwriting standards, resilience to economic shocks, and the effectiveness of arrears management. !- Definitions and concepts: An NPL is defined as a loan that is past-due for a minimum amount of days (e.g., 90 days). The definition can vary across countries but the Basel Committee has set common standards. The retail portfolio encompasses exposures to individuals and qualifying MSMEs treated under the retail asset class. The most common ratio is Gross NPLs ÷ Gross retail loans. Aggressive charge-offs or “evergreening” can temporarily lower the NPL ratio without improving underlying asset quality. Seasonality and relief measures: Payment holidays or pandemic moratoria may defer delinquencies, masking latent credit risk.</t>
+          <t>The delinquency rate tracks the share of consumer loans—mortgages, credit-cards, instalment loans, auto, buy-now-pay-later, qualifying MSEs—that have fallen past due but have not yet crossed the “non-performing” threshold or been written off. Rising early-stage arrears are an early-warning signal of household stress and of future spikes in non-performing loans (NPLs), provisions and write-offs. Paired with NPL, restructuring and write-off metrics, the delinquency rate provides a forward-looking barometer of retail credit health. Supervisors and risk managers use the metric to test the effectiveness of underwriting standards, consumer disclosure, customer interfaces (for digital loans), and pricing for credit risk. !- Definitions and concepts: Loan delinquency refers to a situation in which borrowed money is not paid back as agreed. A loan becomes delinquent when a borrower misses a regular installment payment. A delinquent loan is any kind of loan that has past due payments but has yet to go into default. On a value basis, this indicator measures the total outstanding balances past due (for example greater than 1 day past due) as a share of gross retail loan balances at the end of a specified period. Operational cut-offs: Inconsistent days past due calculation (calendar days vs. business days, partial payments) hinders cross-lender comparability.</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the rates of non-performing loans (NPL) within retail/MSME portfolios, and how do these differences vary by age, income levels, geographic location, and types of financial service providers? Do women or other gender groups exhibit different patterns of loan repayment and default compared to men, and what factors might explain these variations? How do NPL rates differ across loan types, and are portfolios with higher female borrower participation associated with lower or higher NPL ratios? Are financial service providers with greater gender diversity in their workforce or leadership more effective at managing NPLs equitably across genders? What insights do gender-disaggregated NPL data provide regarding credit risk, financial resilience, and inclusion of vulnerable or underserved gender groups?</t>
+          <t>Are there gender disparities (including for MSMEs based on the gender of ownership) in delinquency rates (also considering the number of unpaid installments) for loans of different types, terms and sizes? Do smaller loans have lower delinquency rates and how does this vary across genders? Do FSPs with higher levels of gender diversity present lower delinquency rates?</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -9389,12 +9380,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Quality, Suitability, Stability</t>
+          <t>Outcomes, Suitability, Credit risk</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Customer type; Customer gender; Financial service provider (FSP) type; Financial service provider (FSP) gender diversity; Product type</t>
         </is>
       </c>
     </row>
@@ -9415,26 +9406,26 @@
         </is>
       </c>
       <c r="D165">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Restructured loans</t>
+          <t>Non performing loans (NPLs) in the retail portfolio</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Volume and value of restructured loans as a proportion of total retail/MSME portfolio</t>
+          <t>Non performing loans rate in the retail/MSME loan portfolio</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>The restructured loans indicator tracks the portion of a lender's credit portfolio whose contractual terms have been modified to relieve a borrower in financial difficulty—by lowering the interest rate, extending maturity, granting grace periods, converting currency, or partially forgiving principal, or a mix of these. A rising stock signals mounting credit stress, latent loss risk, or even internal frauds or mismagement. While restructurings can help viable borrowers bridge a temporary shock, they may defer recognition of non-performing loans (NPLs). Supervisors watch both the level and the flow of restructurings to detect “ever-greening”. !- Definitions and concepts: Restructured (or renegotiated / forborne) loan: an exposure whose cash-flow terms have been modified for credit risk reasons and would not have been granted under comparable market conditions. Local definitions vary, while standard setting bodies such as the Basel Committe and IFRS have provided common standards. Indicator formula: Restructured loans ÷ Gross loans (stock measure). !- Limitations and considerations: Regulatory divergence: Some jurisdictions treat any concession as a restructuring; others exclude purely administrative changes, hampering cross-country comparisons. Forbearance episodes: Crisis-era moratoria or government-mandated payment holidays may inflate restructuring volumes temporarily, masking true borrower weakness. Portfolio mix effects: High-yield consumer portfolios often show higher restructuring rates than collateralised mortgages; segment analysis is essential.</t>
+          <t>The NPL indicator for the retail loan portfolio quantifies the share (or absolute value) of consumer and MSE loans that are unlikely to be fully repaid. Because retail credit typically involves high volumes of granular, often unsecured exposures, a build-up of NPLs signals mounting credit risk costs, pressure on provisioning, and potential stress. Supervisors track this metric to assess lenders' underwriting standards, resilience to economic shocks, and the effectiveness of arrears management. !- Definitions and concepts: An NPL is defined as a loan that is past-due for a minimum amount of days (e.g., 90 days). The definition can vary across countries but the Basel Committee has set common standards. The retail portfolio encompasses exposures to individuals and qualifying MSMEs treated under the retail asset class. The most common ratio is Gross NPLs ÷ Gross retail loans. Aggressive charge-offs or “evergreening” can temporarily lower the NPL ratio without improving underlying asset quality. Seasonality and relief measures: Payment holidays or pandemic moratoria may defer delinquencies, masking latent credit risk.</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of restructured loans within retail/MSME loan portfolios, and how do these differences vary by age, income levels, and geographic location? Are women or other gender groups more likely to have loans restructured, potentially reflecting differences in financial vulnerability or repayment capacity? How do patterns of loan restructuring differ across loan types and sectors by gender? Do financial service providers with greater gender diversity in their workforce or leadership demonstrate more equitable practices in loan restructuring across gender groups? What do gender-disaggregated data on restructured loans reveal about the resilience and support available to borrowers facing financial stress?</t>
+          <t>Are there gender disparities in the rates of non-performing loans (NPL) within retail/MSME portfolios, and how do these differences vary by age, income levels, geographic location, and types of financial service providers? Do women or other gender groups exhibit different patterns of loan repayment and default compared to men, and what factors might explain these variations? How do NPL rates differ across loan types, and are portfolios with higher female borrower participation associated with lower or higher NPL ratios? Are financial service providers with greater gender diversity in their workforce or leadership more effective at managing NPLs equitably across genders? What insights do gender-disaggregated NPL data provide regarding credit risk, financial resilience, and inclusion of vulnerable or underserved gender groups?</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -9449,7 +9440,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Quality, Suitability</t>
+          <t>Quality, Suitability,</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -9475,26 +9466,31 @@
         </is>
       </c>
       <c r="D166">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Large exposures</t>
+          <t>Restructured loans</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Large exposures as % of total capital</t>
+          <t>Volume and value of restructured loans as a proportion of total retail/MSME portfolio</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Tracks a lender's credit exposures to single counterparties or groups that exceed a threshold (e.g., a % of capital) and ensures none breach the regulatory cap. !- Definitions and concepts: Exposure includes on- and off-balance-sheet items. !- Data requirements: Counterparty-level exposure data, eligible capital base.</t>
+          <t>The restructured loans indicator tracks the portion of a lender's credit portfolio whose contractual terms have been modified to relieve a borrower in financial difficulty—by lowering the interest rate, extending maturity, granting grace periods, converting currency, or partially forgiving principal, or a mix of these. A rising stock signals mounting credit stress, latent loss risk, or even internal frauds or mismagement. While restructurings can help viable borrowers bridge a temporary shock, they may defer recognition of non-performing loans (NPLs). Supervisors watch both the level and the flow of restructurings to detect “ever-greening”. !- Definitions and concepts: Restructured (or renegotiated / forborne) loan: an exposure whose cash-flow terms have been modified for credit risk reasons and would not have been granted under comparable market conditions. Local definitions vary, while standard setting bodies such as the Basel Committe and IFRS have provided common standards. Indicator formula: Restructured loans ÷ Gross loans (stock measure). !- Limitations and considerations: Regulatory divergence: Some jurisdictions treat any concession as a restructuring; others exclude purely administrative changes, hampering cross-country comparisons. Forbearance episodes: Crisis-era moratoria or government-mandated payment holidays may inflate restructuring volumes temporarily, masking true borrower weakness. Portfolio mix effects: High-yield consumer portfolios often show higher restructuring rates than collateralised mortgages; segment analysis is essential.</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Are higher levels of gender diversity at FSPs and in their customer base correlated with lower levels of large exposures in loan operations? How are large exposures distributed across different products, gender, and locations? Do large exposures show different delinquency and NPL levels based on gender?</t>
+          <t>Are there gender disparities in the share of restructured loans within retail/MSME loan portfolios, and how do these differences vary by age, income levels, and geographic location? Are women or other gender groups more likely to have loans restructured, potentially reflecting differences in financial vulnerability or repayment capacity? How do patterns of loan restructuring differ across loan types and sectors by gender? Do financial service providers with greater gender diversity in their workforce or leadership demonstrate more equitable practices in loan restructuring across gender groups? What do gender-disaggregated data on restructured loans reveal about the resilience and support available to borrowers facing financial stress?</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9504,12 +9500,12 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Outcomes, Safety and security, Credit risk</t>
+          <t>Quality, Suitability,</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -9521,7 +9517,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Credit risk, Soundness</t>
+          <t>Credit risk</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9530,26 +9526,26 @@
         </is>
       </c>
       <c r="D167">
-        <v>262</v>
+        <v>118</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Write-offs ratio</t>
+          <t>Large exposures</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Volume and value of written off retail loans as a proportion of retail/MSME portfolio</t>
+          <t>Large exposures as % of total capital</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>The write-offs ratio tracks the portion of the retail loan portfolio that a lender permanently removes from its balance sheet within a period because collection is deemed impossible or uneconomic. It is a forward-looking credit-risk barometer: rising write-offs shrink the loan book, erode earnings through higher impairment charges, and may reveal weaknesses in underwriting or collections. Supervisors examine the indicator alongside NPL and provisioning coverage to judge whether lenders are recognising losses promptly or postponing them through restructurings. !- Definitions and concepts: Write-offs ratio is usually expressed as (Gross retail loan write-offs during period ÷ Average gross retail loans outstanding). Write-off: an accounting action that derecognises the unrecoverable portion of a loan’s amortised cost. It does not preclude further collections, which are recognised as recoveries. !- Limitations and considerations:  Timing disparities: Institutions with aggressive 180-day charge-off policies show higher ratios than peers that delay write-offs until legal exhaustion, complicating comparisons..</t>
+          <t>Tracks a lender's credit exposures to single counterparties or groups that exceed a threshold (e.g., a % of capital) and ensures none breach the regulatory cap. !- Definitions and concepts: Exposure includes on- and off-balance-sheet items. !- Data requirements: Counterparty-level exposure data, eligible capital base.</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the incidence of loan write-offs among retail/MSME borrowers? How do these disparities shift when further disaggregated by age, income, loan size, and geographic location? Do women or other gender groups experience higher or lower write-off rates compared to men, and what factors might explain these patterns? When analyzed in relation to the gender diversity of financial service providers’ leadership or top management, is higher gender diversity associated with more equitable write-off rates across customer genders? What insights do gender-disaggregated write-off data provide about risk assessment, financial inclusion, and borrower resilience?</t>
+          <t>Are higher levels of gender diversity at FSPs and in their customer base correlated with lower levels of large exposures in loan operations? How are large exposures distributed across different products, gender, and locations? Do large exposures show different delinquency and NPL levels based on gender?</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -9559,12 +9555,12 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Outcomes, Suitability, Credit risk</t>
+          <t>Outcomes, Safety and security, Credit risk</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -9585,31 +9581,26 @@
         </is>
       </c>
       <c r="D168">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Loan loss provisions</t>
+          <t>Write-offs ratio</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>% of the outstanding loan portfolio set aside as provisions for expected credit losses</t>
+          <t>Volume and value of written off retail loans as a proportion of retail/MSME portfolio</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Loan loss provisions (LLPs) are the expenses a lender records to cover expected credit losses on its loan portfolio. They represent management’s best estimate of future cash shortfalls arising from borrower defaults or deteriorating credit quality. Adequate provisioning is critical for portraying true earnings, maintaining solvency, and sustaining market confidence. Monitoring LLP trends alongside non-performing loan inflows, write-offs, and capital ratios provides a holistic view of a bank’s credit-risk resilience and earnings quality. Definitions &amp; concepts: Loan Loss Provision (expense) – the profit-and-loss charge that increases the Allowance for Expected Credit Losses (ECL) on the balance sheet. !- Data requirements: LLP expenses segmented by product, geography, collateral type. Total loan portfolio value.</t>
+          <t>The write-offs ratio tracks the portion of the retail loan portfolio that a lender permanently removes from its balance sheet within a period because collection is deemed impossible or uneconomic. It is a forward-looking credit-risk barometer: rising write-offs shrink the loan book, erode earnings through higher impairment charges, and may reveal weaknesses in underwriting or collections. Supervisors examine the indicator alongside NPL and provisioning coverage to judge whether lenders are recognising losses promptly or postponing them through restructurings. !- Definitions and concepts: Write-offs ratio is usually expressed as (Gross retail loan write-offs during period ÷ Average gross retail loans outstanding). Write-off: an accounting action that derecognises the unrecoverable portion of a loan’s amortised cost. It does not preclude further collections, which are recognised as recoveries. !- Limitations and considerations:  Timing disparities: Institutions with aggressive 180-day charge-off policies show higher ratios than peers that delay write-offs until legal exhaustion, complicating comparisons..</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the provisioning level allocated to customers? When disaggregated by other demographics such as age and location, do the observed gender-based differences change? Do vulnerable customers tend to have loans with higher provisioning levels, and are there gender differences in these patterns? When analyzed in relation to the gender diversity of FSPs' top management, is a higher level of gender diversity associated with differences in provisioning levels? And how does this relationship compare when considering gender diversity across other staff levels?</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>Are there gender disparities in the incidence of loan write-offs among retail/MSME borrowers? How do these disparities shift when further disaggregated by age, income, loan size, and geographic location? Do women or other gender groups experience higher or lower write-off rates compared to men, and what factors might explain these patterns? When analyzed in relation to the gender diversity of financial service providers’ leadership or top management, is higher gender diversity associated with more equitable write-off rates across customer genders? What insights do gender-disaggregated write-off data provide about risk assessment, financial inclusion, and borrower resilience?</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -9619,12 +9610,12 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Outcomes, Suitability, Credit risk, Soundness, Stability</t>
+          <t>Outcomes, Suitability, Credit risk</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Product type; Loan size</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -9636,7 +9627,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Credit risk</t>
+          <t>Credit risk, Soundness</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9645,21 +9636,26 @@
         </is>
       </c>
       <c r="D169">
-        <v>125</v>
+        <v>263</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Physical risk in the credit portfolio</t>
+          <t>Loan loss provisions</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Exposure of the credit portfolio to customers/industries with high physical risk related to climate change</t>
+          <t>% of the outstanding loan portfolio set aside as provisions for expected credit losses</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>This indicator quantifies how much of the loan book is exposed to climate-related physical risks, specifically. These risks materialize through direct damage to assets, disruptions in business operations, or negative impacts on local economies, all of which can lead to higher rates of loan defaults and losses for the lender. This indicator should complement the all-encompassing indicator that measures climate-related risks (both physical and transition risks). Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, including physical risks, while the NGFS provides a range of additional defintions, including nature-related financial risks.</t>
+          <t>Loan loss provisions (LLPs) are the expenses a lender records to cover expected credit losses on its loan portfolio. They represent management’s best estimate of future cash shortfalls arising from borrower defaults or deteriorating credit quality. Adequate provisioning is critical for portraying true earnings, maintaining solvency, and sustaining market confidence. Monitoring LLP trends alongside non-performing loan inflows, write-offs, and capital ratios provides a holistic view of a bank’s credit-risk resilience and earnings quality. Definitions &amp; concepts: Loan Loss Provision (expense) – the profit-and-loss charge that increases the Allowance for Expected Credit Losses (ECL) on the balance sheet. !- Data requirements: LLP expenses segmented by product, geography, collateral type. Total loan portfolio value.</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in the provisioning level allocated to customers? When disaggregated by other demographics such as age and location, do the observed gender-based differences change? Do vulnerable customers tend to have loans with higher provisioning levels, and are there gender differences in these patterns? When analyzed in relation to the gender diversity of FSPs' top management, is a higher level of gender diversity associated with differences in provisioning levels? And how does this relationship compare when considering gender diversity across other staff levels?</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -9667,9 +9663,19 @@
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Outcomes, Suitability, Credit risk, Soundness, Stability</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>Customer gender; Customer type; Financial service provider (FSP) type; Product type; Loan size; Loan term</t>
+          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Product type; Loan size</t>
         </is>
       </c>
     </row>
@@ -9681,40 +9687,40 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Liquidity risk</t>
+          <t>Credit risk</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D170">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Liquidity ratio</t>
+          <t>Physical risk in the credit portfolio</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Liquidity ratio</t>
+          <t>Exposure of the credit portfolio to customers/industries with high physical risk related to climate change</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>The liquidity ratio tests whether an entity holds enough high quality liquid assets to survive a 30-day stress scenario. !- Definitions and concepts: definition of liquidity ratios can vary across countries. The Basel Committee has provided definitions for the Liquidity Coverage Ratio and the Net Stable Funding, but many countries use simpler liquidity ratio definitions. For the insurance sector, the International Association of Insurance Supervisors has also proposed liquidity metrics using an exposure approach (Insurance Liquidity Ratio) and a company projection approach (based on cash flows).</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>How are FSP gender diversity and the gender composition of the customer base correlated with liquidity risk?</t>
+          <t>This indicator quantifies how much of the loan book is exposed to climate-related physical risks, specifically. These risks materialize through direct damage to assets, disruptions in business operations, or negative impacts on local economies, all of which can lead to higher rates of loan defaults and losses for the lender. This indicator should complement the all-encompassing indicator that measures climate-related risks (both physical and transition risks). Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, including physical risks, while the NGFS provides a range of additional defintions, including nature-related financial risks.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity</t>
+          <t>Customer gender; Customer type; Financial service provider (FSP) type; Product type; Loan size; Loan term</t>
         </is>
       </c>
     </row>
@@ -9726,50 +9732,40 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Market risk</t>
+          <t>Liquidity risk</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Insurance, Pensions, Investments</t>
+          <t>Payments, Savings, Credit, Insurance, Investments</t>
         </is>
       </c>
       <c r="D171">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Value at Risk (VaR)</t>
+          <t>Liquidity ratio</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Exposure to market risk (value volatility in the trading book)</t>
+          <t>Liquidity ratio</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>VaR estimates the maximum potential trading-book loss over a specified horizon at a given confidence level (e.g., one-day 99%). It informs market risk limits and capital requirements for market risk. !- Definitions and concepts: market risk definition and standardized calculations vary across jurisdictions. Standards are provided by international standard setting bodies such as the Basel Committee.</t>
+          <t>The liquidity ratio tests whether an entity holds enough high quality liquid assets to survive a 30-day stress scenario. !- Definitions and concepts: definition of liquidity ratios can vary across countries. The Basel Committee has provided definitions for the Liquidity Coverage Ratio and the Net Stable Funding, but many countries use simpler liquidity ratio definitions. For the insurance sector, the International Association of Insurance Supervisors has also proposed liquidity metrics using an exposure approach (Insurance Liquidity Ratio) and a company projection approach (based on cash flows).</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Is there a correlation between higher levels of gender diversity in FSPs and lower risk levels?</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>Statistics and research</t>
+          <t>How are FSP gender diversity and the gender composition of the customer base correlated with liquidity risk?</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity</t>
         </is>
       </c>
     </row>
@@ -9781,50 +9777,50 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Operational risk</t>
+          <t>Market risk</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Payments, Savings</t>
+          <t>Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D172">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Balance of suspense accounts</t>
+          <t>Value at Risk (VaR)</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Value of balances of suspense accounts</t>
+          <t>Exposure to market risk (value volatility in the trading book)</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Suspense accounts are temporary holding ledgers used when a transaction cannot be posted to its final customer account because critical details are missing or disputed or due to any technical issues. The balance of suspense accounts aggregates the outstanding debit or credit amounts awaiting resolution. Persistently high or growing balances signal weaknesses in reconciliation, client on-boarding, Know-Your-Customer (KYC) data quality, payment-processing controls, or even internal fraud. Ageing buckets: some regulators require ageing of reported balances (0-30, 31-90, 91-180, &gt;180 days) to identify balances that exceed tolerance windows. !- Limitations and considerations: Accounting practices vary: some institutions clear items by moving them to internal “parking” accounts that may not be labelled suspense, understating the indicator. Standardization is needed to ensure reporting of balances in similar accounts that are not labelled "suspense accounts". Regulatory treatment: in certain jurisdictions, long-dated unresolved credits are treated as unclaimed funds.</t>
+          <t>VaR estimates the maximum potential trading-book loss over a specified horizon at a given confidence level (e.g., one-day 99%). It informs market risk limits and capital requirements for market risk. !- Definitions and concepts: market risk definition and standardized calculations vary across jurisdictions. Standards are provided by international standard setting bodies such as the Basel Committee.</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the average amount of funds in suspense accounts, including for low-income customers and MSMEs based on the ownership gender? Are there gender disparities in the distribution of low-income customers with suspense accounts (and for which types of accounts?) compared to the whole customer base? Comparing this indicator with failed transactions and customer losses (if available), are there gender disparities in financial losses after funds remain in suspense or temporary accounts, which could indicate potential internal frauds? Comparing this indicator with FSP gender diversity, does higher gender diversity correlate with lower amounts in suspense accounts or customer losses after funds are temporarily placed in suspense accounts?</t>
+          <t>Is there a correlation between higher levels of gender diversity in FSPs and lower risk levels?</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Usage, Suitability</t>
+          <t>Statistics and research</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -9841,30 +9837,30 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Payments, Savings</t>
         </is>
       </c>
       <c r="D173">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Incomplete/failed transactions</t>
+          <t>Balance of suspense accounts</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>% of all initiated transactions that are incomplete or failed</t>
+          <t>Value of balances of suspense accounts</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Measures the percentage of transactions that users initiate but that do not successfully complete as intended. It's a metric for assessing the reliability, usability, and accessibility of a digital financial service. A high rate of incomplete or failed transactions points to a poor user experience, and may lead to financial loss if funds are temporarily held and not returned. A sudden spike in this indicator can be an early warning of technical problems, cybersecurity attacks, or capacity issues. Incomplete transactions: transactions that are started by the user but are never fully processed to a conclusion. They are often "timed out" or abandoned. Failed transactions: transactions that are fully processed by the system but are ultimately rejected. The system actively returns an error message confirming the failure.</t>
+          <t>Suspense accounts are temporary holding ledgers used when a transaction cannot be posted to its final customer account because critical details are missing or disputed or due to any technical issues. The balance of suspense accounts aggregates the outstanding debit or credit amounts awaiting resolution. Persistently high or growing balances signal weaknesses in reconciliation, client on-boarding, Know-Your-Customer (KYC) data quality, payment-processing controls, or even internal fraud. Ageing buckets: some regulators require ageing of reported balances (0-30, 31-90, 91-180, &gt;180 days) to identify balances that exceed tolerance windows. !- Limitations and considerations: Accounting practices vary: some institutions clear items by moving them to internal “parking” accounts that may not be labelled suspense, understating the indicator. Standardization is needed to ensure reporting of balances in similar accounts that are not labelled "suspense accounts". Regulatory treatment: in certain jurisdictions, long-dated unresolved credits are treated as unclaimed funds.</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Do incomplete/failed transactions impact different genders differently, including low-income customers and MSMEs based on the ownership gender? Comparing this indicator with the amount of losses suffered by customers (if available), are there gender disparities in financial losses due to failed transactions? How does this indicator compare with indicators on values maintained in suspense accounts and their variation by gender? Do different types of FSPs and accounts perform differently across the gender in terms of failed transactions? Comparing this indicator with gender diversity, does higher gender diversity correlate with a lower prevalence of failed transactions?</t>
+          <t>Are there gender disparities in the average amount of funds in suspense accounts, including for low-income customers and MSMEs based on the ownership gender? Are there gender disparities in the distribution of low-income customers with suspense accounts (and for which types of accounts?) compared to the whole customer base? Comparing this indicator with failed transactions and customer losses (if available), are there gender disparities in financial losses after funds remain in suspense or temporary accounts, which could indicate potential internal frauds? Comparing this indicator with FSP gender diversity, does higher gender diversity correlate with lower amounts in suspense accounts or customer losses after funds are temporarily placed in suspense accounts?</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -9879,7 +9875,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Transaction type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -9900,98 +9896,98 @@
         </is>
       </c>
       <c r="D174">
+        <v>29</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Incomplete/failed transactions</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>% of all initiated transactions that are incomplete or failed</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Measures the percentage of transactions that users initiate but that do not successfully complete as intended. It's a metric for assessing the reliability, usability, and accessibility of a digital financial service. A high rate of incomplete or failed transactions points to a poor user experience, and may lead to financial loss if funds are temporarily held and not returned. A sudden spike in this indicator can be an early warning of technical problems, cybersecurity attacks, or capacity issues. Incomplete transactions: transactions that are started by the user but are never fully processed to a conclusion. They are often "timed out" or abandoned. Failed transactions: transactions that are fully processed by the system but are ultimately rejected. The system actively returns an error message confirming the failure.</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Do incomplete/failed transactions impact different genders differently, including low-income customers and MSMEs based on the ownership gender? Comparing this indicator with the amount of losses suffered by customers (if available), are there gender disparities in financial losses due to failed transactions? How does this indicator compare with indicators on values maintained in suspense accounts and their variation by gender? Do different types of FSPs and accounts perform differently across the gender in terms of failed transactions? Comparing this indicator with gender diversity, does higher gender diversity correlate with a lower prevalence of failed transactions?</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Usage, Suitability</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Transaction type</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D175">
         <v>106</v>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="E175" t="inlineStr">
         <is>
           <t>Operational disruption incidents</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
+      <c r="F175" t="inlineStr">
         <is>
           <t>Number of operational disruption incidents</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
+      <c r="G175" t="inlineStr">
         <is>
           <t>This indicator counts and classifies events that interrupt an institution’s ability to deliver financial services—whether due to IT failures, cyber-attacks, power outages, third-party breakdowns, or physical events (e.g., fire, pandemic lockdowns). Regulators track both the frequency and severity (e.g., service-unavailable minutes, customers affected, monetary losses) to judge the resilience of regulated services. A rising trend can erode confidence and expose the system to contagion if multiple firms rely on the same outsourced providers or infrastructure.
 !- Definitions and concepts: Operational disruption incident: an unplanned event that prevents or materially degrades the delivery of a critical business service beyond a defined tolerance. Definitions, including of critical services, vary across countries. Standard setting bodies including the Basel Committee provide standardized definitions that can be used. 
 Impact metrics: duration, peak concurrent users affected, transaction backlog, financial loss, data-integrity impact, customer detriment, others. Root-cause categories: hardware/software failure, cyber-intrusion, third-party outage, human error, environmental event, others. !- Limitations and considerations: Firms may fear reputational damage so there is a risk of under-reporting. Heterogeneous critical-service definitions may be used across firm, so regulatory standardization is needed.</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
+      <c r="H175" t="inlineStr">
         <is>
           <t>How are FSP gender diversity and gender composition of customer base correlated with the frequency of operational disruption incidents?</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr">
+      <c r="J175" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>Quality, Data privacy and protection, Safety and security</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type; Transaction type</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Operational risk</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D175">
-        <v>107</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Successful cyber attacks</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Number of successful cyber attacks</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>A measure of the frequency of cyberattacks on regulated financial institutions over a specified period. !- Definitions and concepts: A cyberattack is any intentional effort to steal, expose, alter, disable, or destroy data, applications, or other assets through unauthorized access to a network, computer system or digital device. Cyberattacks can disrupt and damage businesses and often carry high costs, including the costs of discovering and responding to the violation, downtime and lost revenue, and the long-term reputational damage to a business and its brand. Data requirement: Self-reporting of the number of successful cyberattacks by FSPs or data from other parties that track the incidence and severity of cyberattacks.</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Are higher levels of gender diversity at FSPs correlated with the frequency of successful cyber attacks?</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection</t>
-        </is>
-      </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Outcomes, Safety and security</t>
+          <t>Quality, Data privacy and protection</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type; Transaction type</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity; Transaction type</t>
         </is>
       </c>
     </row>
@@ -10003,35 +9999,35 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Soundness</t>
+          <t>Operational risk</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D176">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Cost of reinsurance</t>
+          <t>Successful cyber attacks</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Premiums ceded to reinsurers as % of gross premium written</t>
+          <t>Number of successful cyber attacks</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>The cost of reinsurance indicator quantifies the price an insurer pays to transfer part of its underwriting risk to reinsurers. Tracked as either an absolute expense or as a ratio—most often Reinsurance premium ceded ÷ Gross premiums written (GPW)—it shows how much earnings capacity the insurer surrenders for balance-sheet protection. Rising costs may stem from hardening global reinsurance markets, high catastrophe exposures, deteriorating loss experience or weakened credit quality of the insurer. Supervisors and rating agencies watch for excessive reliance on expensive reinsurance cover which can compress margins, while under-spending may leave the insurer over-exposed to shocks. Evaluated over time and in tandem with retention ratios, claims ratio and solvency coverage, the cost of reinsurance reveals whether an insurer’s risk transfer strategy is adequate. !- Definitions and concepts: Reinsurance premium ceded: contractual payments (net of commissions) made to reinsurers for proportional (quota-share, surplus) or non-proportional (excess-of-loss, stop-loss) treaties, booked at treaty inception. Net cost of reinsurance: ceded premium minus ceding commission plus profit-commission adjustments and reinstatement premiums. Timing mismatches: Premiums are typically paid up-front, while recoveries occur post-loss, so annual cost ratios can spike in growth years and dip after large events.</t>
+          <t>A measure of the frequency of cyberattacks on regulated financial institutions over a specified period. !- Definitions and concepts: A cyberattack is any intentional effort to steal, expose, alter, disable, or destroy data, applications, or other assets through unauthorized access to a network, computer system or digital device. Cyberattacks can disrupt and damage businesses and often carry high costs, including the costs of discovering and responding to the violation, downtime and lost revenue, and the long-term reputational damage to a business and its brand. Data requirement: Self-reporting of the number of successful cyberattacks by FSPs or data from other parties that track the incidence and severity of cyberattacks.</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>How do FSPs’ gender diversity and the gender composition of their customer base correlate with the costs incurred from reinsurance? Are there gendered patterns in how reinsurance expenses impact insurers and their customers?</t>
+          <t>Are higher levels of gender diversity at FSPs correlated with the frequency of successful cyber attacks?</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10041,12 +10037,12 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Quality,Suitability</t>
+          <t>Outcomes, Safety and security</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type; Transaction type</t>
         </is>
       </c>
     </row>
@@ -10067,26 +10063,26 @@
         </is>
       </c>
       <c r="D177">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Insurance claims (loss) ratio</t>
+          <t>Cost of reinsurance</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>% of total premium income paid out as claims</t>
+          <t>Premiums ceded to reinsurers as % of gross premium written</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>The claims paid ratio compares the amount of benefits and claims an insurer actually disburses during a period with the premium income it records for the same portfolio. It answers a basic question for supervisors, policy-holders, and analysts: How much of each premium dollar flows back to customers in the form of claims? Persistently low ratios may flag overly aggressive pricing, onerous exclusions, or servicing bottlenecks, while very high ratios can foreshadow reserve inadequacy, under-pricing, or a spike in catastrophe losses. In combination with the expense ratio, the indicator feeds into the overall loss or combined ratio that underpins solvency and profitability assessments. !- Definitions and concepts: Claims paid: cash actually settled with policy-holders and claimants in the accounting period, including partial payments and salvage recoveries netted where local GAAP allows. It excludes outstanding claims reserves and IBNR, which are captured by “claims incurred.” Gross vs. net basis: gross claims ignore reinsurance recoveries; net claims deduct them, better reflecting the insurer’s retained risk. Segmented ratios (e.g., motor, health, property) pinpoint product-level profitability. !- Data requirements: Extracts from the claims-management system showing paid amounts, dates, line of business, and reinsurance cessions. Premium registers (written or earned, depending on supervisory preference) reconciled to the general ledger. Catastrophe tags, legal-settlement flags, and large-loss registers to isolate one-off distortions. Limitations &amp; considerations: Timing mismatch: annual premiums are often received up-front, whereas claim payments can lag; using earned premiums mitigates, but does not eliminate, this distortion. Claims-handling practices: delayed settlement or dispute escalation depresses the ratio without improving true risk experience. Reinsurance structure: quota-share vs. excess-of-loss treaties change the net ratio dramatically; analysts should review both gross and net perspectives. Regulatory definitions: some jurisdictions fold surrenders of savings-type contracts into claims, inflating comparability. Trend analysis should therefore pair the claims paid ratio with claims-incurred and reserve-adequacy metrics, catastrophe-loss disclosures, and expense dynamics to obtain a holistic view of underwriting performance and solvency resilience.</t>
+          <t>The cost of reinsurance indicator quantifies the price an insurer pays to transfer part of its underwriting risk to reinsurers. Tracked as either an absolute expense or as a ratio—most often Reinsurance premium ceded ÷ Gross premiums written (GPW)—it shows how much earnings capacity the insurer surrenders for balance-sheet protection. Rising costs may stem from hardening global reinsurance markets, high catastrophe exposures, deteriorating loss experience or weakened credit quality of the insurer. Supervisors and rating agencies watch for excessive reliance on expensive reinsurance cover which can compress margins, while under-spending may leave the insurer over-exposed to shocks. Evaluated over time and in tandem with retention ratios, claims ratio and solvency coverage, the cost of reinsurance reveals whether an insurer’s risk transfer strategy is adequate. !- Definitions and concepts: Reinsurance premium ceded: contractual payments (net of commissions) made to reinsurers for proportional (quota-share, surplus) or non-proportional (excess-of-loss, stop-loss) treaties, booked at treaty inception. Net cost of reinsurance: ceded premium minus ceding commission plus profit-commission adjustments and reinstatement premiums. Timing mismatches: Premiums are typically paid up-front, while recoveries occur post-loss, so annual cost ratios can spike in growth years and dip after large events.</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Are there gender disparities in claims ratios for insurance products, including for MSMEs based on the owner's gender? Are excessively low claims ratios correlated with low premiums (a proxy for targeting lower-income segments)? Are women more likely to be targeted by products with low claims ratios, potentially indicating lower-value offerings? Are FSPs with higher levels of gender diversity less likely to have excessively low claims ratios for insurance sold to vulnerable segments, such as women and women-owned MSMEs? When comparing with coverage ratios (amount of claims paid relative to the claim value), how do gender disparities in coverage ratios compare with claims paid?</t>
+          <t>How do FSPs’ gender diversity and the gender composition of their customer base correlate with the costs incurred from reinsurance? Are there gendered patterns in how reinsurance expenses impact insurers and their customers?</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10096,7 +10092,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Usage, Suitability</t>
+          <t>Quality,Suitability</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -10122,26 +10118,26 @@
         </is>
       </c>
       <c r="D178">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Insurance claims incurred</t>
+          <t>Insurance claims (loss) ratio</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Value of insurance claims incurred</t>
+          <t>% of total premium income paid out as claims</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>“Claims incurred” represents the total cost an insurer recognises for claims events during a reporting period, regardless of whether they have been paid yet. Tracking the level and trend of incurred claims helps supervisors monitor the financial health of insurers such as by detecting emerging risk clusters (e.g., climate-driven catastrophes). !- Definitions and concepts: Claims incurred = Claims paid + Change in outstanding claims reserves + Change in IBNR (incurred-but-not-reported) reserves ± Claims-handling expense reserve movements. !- Data requirements: Total claims incurred.  !- Limitations and considerations: Catastrophe volatility: Single severe events cause spikes. Used alongside premium growth, claims-ratio components, and reserve-adequacy studies, “claims incurred” provides a cornerstone view of underwriting performance and balance-sheet resilience.</t>
+          <t>The claims paid ratio compares the amount of benefits and claims an insurer actually disburses during a period with the premium income it records for the same portfolio. It answers a basic question for supervisors, policy-holders, and analysts: How much of each premium dollar flows back to customers in the form of claims? Persistently low ratios may flag overly aggressive pricing, onerous exclusions, or servicing bottlenecks, while very high ratios can foreshadow reserve inadequacy, under-pricing, or a spike in catastrophe losses. In combination with the expense ratio, the indicator feeds into the overall loss or combined ratio that underpins solvency and profitability assessments. !- Definitions and concepts: Claims paid: cash actually settled with policy-holders and claimants in the accounting period, including partial payments and salvage recoveries netted where local GAAP allows. It excludes outstanding claims reserves and IBNR, which are captured by “claims incurred.” Gross vs. net basis: gross claims ignore reinsurance recoveries; net claims deduct them, better reflecting the insurer’s retained risk. Segmented ratios (e.g., motor, health, property) pinpoint product-level profitability. !- Data requirements: Extracts from the claims-management system showing paid amounts, dates, line of business, and reinsurance cessions. Premium registers (written or earned, depending on supervisory preference) reconciled to the general ledger. Catastrophe tags, legal-settlement flags, and large-loss registers to isolate one-off distortions. Limitations &amp; considerations: Timing mismatch: annual premiums are often received up-front, whereas claim payments can lag; using earned premiums mitigates, but does not eliminate, this distortion. Claims-handling practices: delayed settlement or dispute escalation depresses the ratio without improving true risk experience. Reinsurance structure: quota-share vs. excess-of-loss treaties change the net ratio dramatically; analysts should review both gross and net perspectives. Regulatory definitions: some jurisdictions fold surrenders of savings-type contracts into claims, inflating comparability. Trend analysis should therefore pair the claims paid ratio with claims-incurred and reserve-adequacy metrics, catastrophe-loss disclosures, and expense dynamics to obtain a holistic view of underwriting performance and solvency resilience.</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>How has the participation of different genders in incurred insurance claims evolved over time, both for individuals and MSMEs by owner’s gender? Are there gender differences in the types of claims incurred? How does the level of gender diversity within FSPs relate to these patterns?</t>
+          <t>Are there gender disparities in claims ratios for insurance products, including for MSMEs based on the owner's gender? Are excessively low claims ratios correlated with low premiums (a proxy for targeting lower-income segments)? Are women more likely to be targeted by products with low claims ratios, potentially indicating lower-value offerings? Are FSPs with higher levels of gender diversity less likely to have excessively low claims ratios for insurance sold to vulnerable segments, such as women and women-owned MSMEs? When comparing with coverage ratios (amount of claims paid relative to the claim value), how do gender disparities in coverage ratios compare with claims paid?</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10151,7 +10147,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Quality, Suitability</t>
+          <t>Usage, Suitability</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -10177,82 +10173,92 @@
         </is>
       </c>
       <c r="D179">
+        <v>8</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Insurance claims incurred</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Value of insurance claims incurred</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>“Claims incurred” represents the total cost an insurer recognises for claims events during a reporting period, regardless of whether they have been paid yet. Tracking the level and trend of incurred claims helps supervisors monitor the financial health of insurers such as by detecting emerging risk clusters (e.g., climate-driven catastrophes). !- Definitions and concepts: Claims incurred = Claims paid + Change in outstanding claims reserves + Change in IBNR (incurred-but-not-reported) reserves ± Claims-handling expense reserve movements. !- Data requirements: Total claims incurred.  !- Limitations and considerations: Catastrophe volatility: Single severe events cause spikes. Used alongside premium growth, claims-ratio components, and reserve-adequacy studies, “claims incurred” provides a cornerstone view of underwriting performance and balance-sheet resilience.</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>How has the participation of different genders in incurred insurance claims evolved over time, both for individuals and MSMEs by owner’s gender? Are there gender differences in the types of claims incurred? How does the level of gender diversity within FSPs relate to these patterns?</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Quality, Suitability</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Soundness</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D180">
         <v>57</v>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="E180" t="inlineStr">
         <is>
           <t>Insurance policy renewal (persistency) ratio</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>% of all policies up for renewal that are renewed</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
+      <c r="G180" t="inlineStr">
         <is>
           <t>The renewal- or persistency-ratio gauges the proportion of in-force insurance policies (or premium) that remain active after a specified period—typically the 13th, 25th, or 61st month following issuance. High persistency signals strong customer satisfaction, effective servicing, and accurate underwriting assumptions; it underpins stable cash-flow projections, lowers acquisition-cost amortisation strain, and enhances embedded value. Conversely, rapid lapses may expose product-design weaknesses or mis-selling. Supervisors review persistency alongside surrender-value payouts and complaint levels to detect conduct risk and solvency concerns. !- Definitions and concepts: Persistency ratio (policy-count basis) = Policies renewed at month t / Policies eligible for renewal at month t
 Premium-weighted persistency uses renewal premium divided by original premium to capture face-amount shifts. Cohort vs. calendar method: Cohort traces a single issue-year block through time; calendar aggregates all cohorts renewing in a given period. !- Limitations and considerations: Measurement horizon: 13-month persistency suits annual-premium life products; short-tailed general-insurance policies need annual or shorter retention ratios. Channel mix: Bancassurance and digital pathways often show different lapse behaviours—segment analysis is essential.</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
+      <c r="H180" t="inlineStr">
         <is>
           <t>Are there gender disparities in insurance policy renewal rates, including among MSMEs by owner gender? Do certain policy types have lower renewal rates among specific gender groups? Could these differences signal mismatches between products and customer needs, posing strategic risks for insurers?</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr">
+      <c r="J180" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="K180" t="inlineStr">
         <is>
           <t>Quality, Suitability</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Soundness</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D180">
-        <v>114</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Risk retention ratio (dependency on reinsurance)</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>% of gross written premium that is net (as a measure of the level of dependency on reinsurance)</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Also known as the net retention ratio, this indicator shows the proportion of insurance risk an insurer keeps on its own balance sheet after ceding portions to reinsurers. It is usually expressed as Net premiums written ÷ Gross premiums written. A high ratio signals greater self-reliance (and potentially higher earnings volatility), while a low ratio points to heavy dependence on reinsurance, which may reduce earnings swings but create counter-party risks. Supervisors monitor the metric to ensure that ceded volumes are commensurate with the insurer’s capital strength, product mix, and risk appetite. !- Definitions and concepts: Gross premiums written (GPW): Total premium income before reinsurance ceded. Net premiums written (NPW): GPW minus premiums ceded plus reinsurance recoveries on ceded unearned premiums. !- Data requirements: Line-of-business breakdown of GPW and NPW for the period. Details of outward reinsurance treaties. Counter-party concentration: high concentration risk may offset the benefits of resinsurance.</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>What is the relationship between FSP gender diversity, customer gender composition, and the degree of dependency on reinsurance? Are there gender-based patterns in insurers’ risk retention strategies?</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -10278,31 +10284,31 @@
         </is>
       </c>
       <c r="D181">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Technical provisions</t>
+          <t>Risk retention ratio (dependency on reinsurance)</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Level of technical provisions to cover actuarial liabilities</t>
+          <t>% of gross written premium that is net (as a measure of the level of dependency on reinsurance)</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Technical provisions represent the present-value estimate of all future cash outflows that an insurer expects to incur on written policies, including claims not yet reported (IBNR), claims reported but not settled, and future policyholder benefits. Adequate provisions are the cornerstone of insurance solvency and a key indicator for prudential supervisors. Definitions &amp; concepts: Technical provisions comprise two main blocks: Best-Estimate Liabilities (BEL), the probability-weighted expected value of future cash flows (claims, benefits, expenses) discounted using risk-free or prescribed curves; and Risk Margins, an additional amount reflecting the cost of holding capital to run off the liabilities (Solvency II) or a prudential margin (IFRS 17, LAT).</t>
+          <t>Also known as the net retention ratio, this indicator shows the proportion of insurance risk an insurer keeps on its own balance sheet after ceding portions to reinsurers. It is usually expressed as Net premiums written ÷ Gross premiums written. A high ratio signals greater self-reliance (and potentially higher earnings volatility), while a low ratio points to heavy dependence on reinsurance, which may reduce earnings swings but create counter-party risks. Supervisors monitor the metric to ensure that ceded volumes are commensurate with the insurer’s capital strength, product mix, and risk appetite. !- Definitions and concepts: Gross premiums written (GPW): Total premium income before reinsurance ceded. Net premiums written (NPW): GPW minus premiums ceded plus reinsurance recoveries on ceded unearned premiums. !- Data requirements: Line-of-business breakdown of GPW and NPW for the period. Details of outward reinsurance treaties. Counter-party concentration: high concentration risk may offset the benefits of resinsurance.</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the adequacy of technical provisions maintained by FSPs? How do FSPs with higher gender diversity in management and governance compare in maintaining technical provisions that fairly reflect risks associated with serving diverse gender groups? Are provisions sufficiently accounting for potential differences in claims or defaults related to gender segments in the portfolio?</t>
+          <t>What is the relationship between FSP gender diversity, customer gender composition, and the degree of dependency on reinsurance? Are there gender-based patterns in insurers’ risk retention strategies?</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -10323,31 +10329,31 @@
         </is>
       </c>
       <c r="D182">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Physical risk in the insurance portfolio</t>
+          <t>Technical provisions</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Exposure of the insurance portfolio to written policies to physical risk related to climate change</t>
+          <t>Level of technical provisions to cover actuarial liabilities</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Metric used to quantify an insurer's financial exposure to losses caused by the direct physical impacts of climate change. This includes both event-driven acute risks and longer-term chronic risks. This indicator is essential for measuring an insurer's vulnerability to climate-related claims, which can impact its profitability, solvency, and ability to provide affordable coverage. Hence, it is an important metric for prudential supervisors from the perspective of capital adequacy, solvency and risk management. Definitions and concepts of climate-related risks vary across countries. The NGFS provides a range of additional defintions, including nature-related financial risks.</t>
+          <t>Technical provisions represent the present-value estimate of all future cash outflows that an insurer expects to incur on written policies, including claims not yet reported (IBNR), claims reported but not settled, and future policyholder benefits. Adequate provisions are the cornerstone of insurance solvency and a key indicator for prudential supervisors. Definitions &amp; concepts: Technical provisions comprise two main blocks: Best-Estimate Liabilities (BEL), the probability-weighted expected value of future cash flows (claims, benefits, expenses) discounted using risk-free or prescribed curves; and Risk Margins, an additional amount reflecting the cost of holding capital to run off the liabilities (Solvency II) or a prudential margin (IFRS 17, LAT).</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>How do FSP gender diversity and customer gender composition correlate with exposure to climate-related physical risks in insurance portfolios? Are there gender disparities in financial risk exposure due to climate impacts, including among MSMEs by owner gender?</t>
+          <t>Are there gender disparities in the adequacy of technical provisions maintained by FSPs? How do FSPs with higher gender diversity in management and governance compare in maintaining technical provisions that fairly reflect risks associated with serving diverse gender groups? Are provisions sufficiently accounting for potential differences in claims or defaults related to gender segments in the portfolio?</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -10364,35 +10370,35 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Investments</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D183">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Capital adequacy ratio (CAR)</t>
+          <t>Physical risk in the insurance portfolio</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Total regulatory capital relative as % of risk weighted assets (RWAs)</t>
+          <t>Exposure of the insurance portfolio to written policies to physical risk related to climate change</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Capital Adequacy Rario (CAR) shows the total qualifying capital relative to risk-weighted assets (RWA). It captures the full loss-absorbing cushion. !-Definitions and concepts: Capital tiers to include in the CAR formula are provided by the Basel Capital Accords and adapted in each jurisdiction. !- Data requirements: Full breakdown of regulatory capital components, and total RWA. For the insurance sector, the equivalent is the Solvency Ratio calculated as own funds divided by the minimum capital that insurers are required to hold to cover unexpected losses.</t>
+          <t>Metric used to quantify an insurer's financial exposure to losses caused by the direct physical impacts of climate change. This includes both event-driven acute risks and longer-term chronic risks. This indicator is essential for measuring an insurer's vulnerability to climate-related claims, which can impact its profitability, solvency, and ability to provide affordable coverage. Hence, it is an important metric for prudential supervisors from the perspective of capital adequacy, solvency and risk management. Definitions and concepts of climate-related risks vary across countries. The NGFS provides a range of additional defintions, including nature-related financial risks.</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>How are FSP gender diversity and the gender composition of the customer base correlated with CAR levels?</t>
+          <t>How do FSP gender diversity and customer gender composition correlate with exposure to climate-related physical risks in insurance portfolios? Are there gender disparities in financial risk exposure due to climate impacts, including among MSMEs by owner gender?</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -10409,35 +10415,35 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Payments, Savings, Credit, Insurance, Investments</t>
         </is>
       </c>
       <c r="D184">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Tier 1 capital ratio</t>
+          <t>Capital adequacy ratio (CAR)</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tier 1 regulatory capital as % of risk weighted assets (RWAs)</t>
+          <t>Total regulatory capital relative as % of risk weighted assets (RWAs)</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>The Tier 1 ratio shows the core loss-absorbing capital relative to risk-weighted assets (RWA). It is a cornerstone of the Basel Capital Accords and a trigger point for supervisory intervention. !- Definitions and concepts: Tier 1 capital comprises common equity tier 1 (CET1) plus additional tier 1 (perpetual, non-cumulative instruments). RWA adjust asset values for credit, market, and operational risk weights. Local definitions vary, but the Basel Committee has provided common standards.</t>
+          <t>Capital Adequacy Rario (CAR) shows the total qualifying capital relative to risk-weighted assets (RWA). It captures the full loss-absorbing cushion. !-Definitions and concepts: Capital tiers to include in the CAR formula are provided by the Basel Capital Accords and adapted in each jurisdiction. !- Data requirements: Full breakdown of regulatory capital components, and total RWA. For the insurance sector, the equivalent is the Solvency Ratio calculated as own funds divided by the minimum capital that insurers are required to hold to cover unexpected losses.</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Do FSPs with greater gender diversity in leadership and customer base tend to maintain stronger Tier 1 capital ratios? Is there any evidence that gender-inclusive governance correlates with improved capital adequacy and financial resilience? How might gender-related risk factors influence the calculation or management of Tier 1 capital?</t>
+          <t>How are FSP gender diversity and the gender composition of the customer base correlated with CAR levels?</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity</t>
         </is>
       </c>
     </row>
@@ -10454,45 +10460,35 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D185">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Interest margin ratio</t>
+          <t>Tier 1 capital ratio</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Net interest income as % of total earning assets</t>
+          <t>Tier 1 regulatory capital as % of risk weighted assets (RWAs)</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Also known as Net Interest Margin (NIM), is a metric that measures a lender's profitability by calculating difference between the interest it earns on its assets (like loans) and the interest it pays on liabilities, divided by the total earning assets. !- Definitions and concepts: NIM = (Net Interest income – Interest expense) ÷ Average earning assets. !- Data requirements: Total interest income, total interest expenses, total earning assets.</t>
+          <t>The Tier 1 ratio shows the core loss-absorbing capital relative to risk-weighted assets (RWA). It is a cornerstone of the Basel Capital Accords and a trigger point for supervisory intervention. !- Definitions and concepts: Tier 1 capital comprises common equity tier 1 (CET1) plus additional tier 1 (perpetual, non-cumulative instruments). RWA adjust asset values for credit, market, and operational risk weights. Local definitions vary, but the Basel Committee has provided common standards.</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Do financial service providers (FSPs) with higher gender diversity in leadership or governance report different interest margin ratios compared to less gender‑diverse peers? Are there associations between the gender composition of the customer base (e.g. share of women borrowers/depositors) and margin outcomes? Could gendered pricing—such as differential rates offered to male vs. female clients—impact FSP interest margins? Over time, do changes in margin ratios correlate with shifts in gender inclusion (e.g. more women customers or staff)?</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>Impact</t>
+          <t>Do FSPs with greater gender diversity in leadership and customer base tend to maintain stronger Tier 1 capital ratios? Is there any evidence that gender-inclusive governance correlates with improved capital adequacy and financial resilience? How might gender-related risk factors influence the calculation or management of Tier 1 capital?</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -10509,45 +10505,45 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D186">
-        <v>7</v>
+        <v>113</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Insurance premiums written</t>
+          <t>Interest margin ratio</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Value of insurance premiums writen in the insurance sector</t>
+          <t>Net interest income as % of total earning assets</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Premiums written represent the contractual revenue an insurer books when it underwrites new or renewal policies during a given period, irrespective of when coverage is provided or cash is received. Rising written-premium volumes can indicate growth, improved pricing power, or inflation-driven sum-assured increases; declining volumes may flag competitive pressures or tighter underwriting standards. !- Definitions and concepts: Gross premiums written (GPW): All premiums on policies incepted or renewed during the period before ceding to reinsurers. Net premiums written (NPW): GPW minus premiums ceded plus any reinsurance assumed—reflects the risk the insurer retains. Earned premiums: Portion of written premiums recognised as revenue in proportion to expired coverage—crucial for claims-ratio analysis. !- Data requirements: total premium written. For granular data: Policy-level underwriting feeds: issue/renewal dates, premium amounts, payment mode, product line, distribution channel, currency.</t>
+          <t>Also known as Net Interest Margin (NIM), is a metric that measures a lender's profitability by calculating difference between the interest it earns on its assets (like loans) and the interest it pays on liabilities, divided by the total earning assets. !- Definitions and concepts: NIM = (Net Interest income – Interest expense) ÷ Average earning assets. !- Data requirements: Total interest income, total interest expenses, total earning assets.</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>How do insurance premiums written vary by gender of the policyholder, including for individuals and MSMEs based on owner gender? Are there gender disparities in the types and values of insurance products purchased, reflected in premiums collected? Do women or other gender groups pay systematically higher or lower premiums, and what might this indicate about risk assessment or product suitability? How do FSPs with higher gender diversity compare in the total premiums written to different gender segments? Are trends in premiums written by gender evolving over time, and do these trends vary by product type or geographic region?</t>
+          <t>Do financial service providers (FSPs) with higher gender diversity in leadership or governance report different interest margin ratios compared to less gender‑diverse peers? Are there associations between the gender composition of the customer base (e.g. share of women borrowers/depositors) and margin outcomes? Could gendered pricing—such as differential rates offered to male vs. female clients—impact FSP interest margins? Over time, do changes in margin ratios correlate with shifts in gender inclusion (e.g. more women customers or staff)?</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Financial inclusion; Other</t>
+          <t>Consumer protection</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Outcomes, Statistics and research</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -10564,35 +10560,45 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D187">
-        <v>112</v>
+        <v>7</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Efficiency ratio</t>
+          <t>Insurance premiums written</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Effciency ratio</t>
+          <t>Value of insurance premiums writen in the insurance sector</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Indicates operating efficiency by comparing non-interest expenses to operating income. Lower ratios signal better cost control, a key driver of sustainable profitability, especially in low-margin environments. Definitions &amp; concepts – Efficiency Ratio = Operating expenses ÷ (Net interest income + Non-interest income). Some variants exclude litigation or restructuring charges. !- Data requirements: Detailed income statement with breakdowns of personnel, IT, and occupancy costs; segment reporting helps pinpoint inefficiencies. !- Limitations and considerations: Cost cuts that impair risk management or customer service may improve the ratio temporarily but raise long-run risks. Cross-country comparisons should adjust for labour cost levels and digitalisation stages. One-off income (e.g., asset sales) can distort the denominator.</t>
+          <t>Premiums written represent the contractual revenue an insurer books when it underwrites new or renewal policies during a given period, irrespective of when coverage is provided or cash is received. Rising written-premium volumes can indicate growth, improved pricing power, or inflation-driven sum-assured increases; declining volumes may flag competitive pressures or tighter underwriting standards. !- Definitions and concepts: Gross premiums written (GPW): All premiums on policies incepted or renewed during the period before ceding to reinsurers. Net premiums written (NPW): GPW minus premiums ceded plus any reinsurance assumed—reflects the risk the insurer retains. Earned premiums: Portion of written premiums recognised as revenue in proportion to expired coverage—crucial for claims-ratio analysis. !- Data requirements: total premium written. For granular data: Policy-level underwriting feeds: issue/renewal dates, premium amounts, payment mode, product line, distribution channel, currency.</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Are there gender-related differences in the efficiency of FSP operations, for example, in cost-to-income ratios? Do FSPs with more gender-diverse teams or client bases demonstrate better operational efficiency? How do gender dynamics in product design, customer service, and outreach impact overall institutional efficiency?</t>
+          <t>How do insurance premiums written vary by gender of the policyholder, including for individuals and MSMEs based on owner gender? Are there gender disparities in the types and values of insurance products purchased, reflected in premiums collected? Do women or other gender groups pay systematically higher or lower premiums, and what might this indicate about risk assessment or product suitability? How do FSPs with higher gender diversity compare in the total premiums written to different gender segments? Are trends in premiums written by gender evolving over time, and do these trends vary by product type or geographic region?</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Other</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Outcomes, Statistics and research</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -10613,31 +10619,31 @@
         </is>
       </c>
       <c r="D188">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Personnel expenses per customer/contract</t>
+          <t>Efficiency ratio</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Total personnel expenses per customer or contract</t>
+          <t>Effciency ratio</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>This indicator measures the total cost of personnel (wages, salaries, benefits, etc.) divided by the total number of customers a financial service provider serves, revealing how much is spent on staff to support each individual customer. This metric helps assess a company's operational efficiency and cost-effectiveness in managing its customer base, with a lower figure typically indicating better efficiency.</t>
+          <t>Indicates operating efficiency by comparing non-interest expenses to operating income. Lower ratios signal better cost control, a key driver of sustainable profitability, especially in low-margin environments. Definitions &amp; concepts – Efficiency Ratio = Operating expenses ÷ (Net interest income + Non-interest income). Some variants exclude litigation or restructuring charges. !- Data requirements: Detailed income statement with breakdowns of personnel, IT, and occupancy costs; segment reporting helps pinpoint inefficiencies. !- Limitations and considerations: Cost cuts that impair risk management or customer service may improve the ratio temporarily but raise long-run risks. Cross-country comparisons should adjust for labour cost levels and digitalisation stages. One-off income (e.g., asset sales) can distort the denominator.</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Is there a gender dimension in personnel cost efficiency—that is, do FSPs with more balanced or female‑inclusive staff structures show lower personnel expenses per customer or contract? Are personnel expense ratios correlated with the gender composition of staff and how services are delivered to different gender groups? Do FSPs serving a higher proportion of women customers incur different per-customer personnel costs (e.g. due to agent outreach, financial literacy support)? How does this metric evolve over time in relation to efforts to promote gender inclusion in staffing and service models?</t>
+          <t>Are there gender-related differences in the efficiency of FSP operations, for example, in cost-to-income ratios? Do FSPs with more gender-diverse teams or client bases demonstrate better operational efficiency? How do gender dynamics in product design, customer service, and outreach impact overall institutional efficiency?</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -10658,31 +10664,31 @@
         </is>
       </c>
       <c r="D189">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>ROA</t>
+          <t>Personnel expenses per customer/contract</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Return on assets</t>
+          <t>Total personnel expenses per customer or contract</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>ROA gauges how efficiently a financial service provider turns every unit of assets under its control into net profit. !- Definitions and concepts: ROA = Net income after tax ÷ Average total assets (opening + closing assets ÷ 2). !- Data requirements: net income and total assets at two balance-sheet dates, preferably quarterly to smooth seasonality. !- Limitations and considerations: ROA ignores off-balance-sheet exposures such as guarantees or derivatives.</t>
+          <t>This indicator measures the total cost of personnel (wages, salaries, benefits, etc.) divided by the total number of customers a financial service provider serves, revealing how much is spent on staff to support each individual customer. This metric helps assess a company's operational efficiency and cost-effectiveness in managing its customer base, with a lower figure typically indicating better efficiency.</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Do FSPs with greater gender diversity in their workforce, management, or boards tend to achieve higher or more stable ROA? Is there evidence that the gender composition of the customer base (e.g. more female clients) affects asset returns, for instance through differences in risk, lending, or deposit behaviors? When comparing across FSPs, does ROA differ systematically in institutions with stronger gender inclusion strategies? How have ROA trends shifted over time relative to changes in gender diversity (staffing or customer composition)?</t>
+          <t>Is there a gender dimension in personnel cost efficiency—that is, do FSPs with more balanced or female‑inclusive staff structures show lower personnel expenses per customer or contract? Are personnel expense ratios correlated with the gender composition of staff and how services are delivered to different gender groups? Do FSPs serving a higher proportion of women customers incur different per-customer personnel costs (e.g. due to agent outreach, financial literacy support)? How does this metric evolve over time in relation to efforts to promote gender inclusion in staffing and service models?</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -10703,36 +10709,26 @@
         </is>
       </c>
       <c r="D190">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>ROE</t>
+          <t>ROA</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Return on equity</t>
+          <t>Return on assets</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>ROE indicates the earnings available to common shareholders per unit of book equity. !- Definitions and concepts: ROE = Net income ÷ Average shareholders’ equity. !- Data requirements: Consolidated net income and shareholders’ equity.</t>
+          <t>ROA gauges how efficiently a financial service provider turns every unit of assets under its control into net profit. !- Definitions and concepts: ROA = Net income after tax ÷ Average total assets (opening + closing assets ÷ 2). !- Data requirements: net income and total assets at two balance-sheet dates, preferably quarterly to smooth seasonality. !- Limitations and considerations: ROA ignores off-balance-sheet exposures such as guarantees or derivatives.</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Is there a relationship between gender diversity in leadership or equity ownership and ROE performance across FSPs? Are FSPs that prioritize gender inclusion more likely to achieve higher equity returns, possibly through broader market reach or more balanced risk management? How does the gender mix of customers, especially depositors and borrowers, relate to ROE outcomes? Over time, do improvements in gender inclusion (in staffing or customer base) precede or follow changes in ROE?</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>Other; Consumer protection; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>Statistics and research, Impact, Credit risk</t>
+          <t>Do FSPs with greater gender diversity in their workforce, management, or boards tend to achieve higher or more stable ROA? Is there evidence that the gender composition of the customer base (e.g. more female clients) affects asset returns, for instance through differences in risk, lending, or deposit behaviors? When comparing across FSPs, does ROA differ systematically in institutions with stronger gender inclusion strategies? How have ROA trends shifted over time relative to changes in gender diversity (staffing or customer composition)?</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -10749,50 +10745,50 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Credit risk</t>
+          <t>Soundness</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D191">
-        <v>6</v>
+        <v>116</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Financial system credit operations</t>
+          <t>ROE</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Volume and value of credit operations in the total financial sector portfolio</t>
+          <t>Return on equity</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>This indicator captures the breadth of formal lending with two perspectives: the number of credit contracts (volume) and their aggregate outstanding balance (value) across all regulated lenders. Tracking it offers a panoramic view of credit provision, enabling supervisors to (i) gauge financial deepening, (ii) assess systemic leverage of the banking sector, (iii) monitor shifts in portfolio composition (e.g., rise of consumer or MSME lending), and (iv) feed macro-prudential stress tests and monetary policy models. Sharp expansions may indicate rapid financial inclusion or overheating; contractions can herald credit crunches that dampen growth. !- Definitions and concepts: Credit operation – any legally binding loan, line of credit, hire-purchase, lease, or other. Off-balance-sheet commitments (e.g., undrawn credit lines, guarantees) are usually excluded or reported separately. Volume (count): unique credit contracts outstanding at the reporting date; renewals/extensions count as new operations if a fresh contract is signed. Segmentation by sector (household, corporate, government), product type, currency, and residual maturity enriches analysis. !- Data requirements: Supervisory returns or call-reports detailing credit operations contract count by institution and product. Standardised product and sector taxononies to avoid double counting.</t>
+          <t>ROE indicates the earnings available to common shareholders per unit of book equity. !- Definitions and concepts: ROE = Net income ÷ Average shareholders’ equity. !- Data requirements: Consolidated net income and shareholders’ equity.</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>How does the gender composition of borrowers in the total financial sector credit portfolio compare across the number and value of outstanding credit operations? Are there gender disparities in both the frequency (number) of credit operations and the total credit amounts extended? How do these disparities vary by loan type, sector, or borrower demographics such as age, income, and location? Are women or other gender groups underrepresented in certain types of credit or regions within the overall portfolio? How do FSPs with higher levels of gender diversity compare in terms of the balance and number of credit operations granted to different genders? Are portfolios with more balanced gender representation associated with differences in credit performance, such as lower default rates or more stable repayment patterns?</t>
+          <t>Is there a relationship between gender diversity in leadership or equity ownership and ROE performance across FSPs? Are FSPs that prioritize gender inclusion more likely to achieve higher equity returns, possibly through broader market reach or more balanced risk management? How does the gender mix of customers, especially depositors and borrowers, relate to ROE outcomes? Over time, do improvements in gender inclusion (in staffing or customer base) precede or follow changes in ROE?</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Other; Consumer protection; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>Statistics and research, Impact, Credit risk</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -10804,74 +10800,129 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
+          <t>Credit risk</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="D192">
+        <v>6</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Financial system credit operations</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Volume and value of credit operations in the total financial sector portfolio</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>This indicator captures the breadth of formal lending with two perspectives: the number of credit contracts (volume) and their aggregate outstanding balance (value) across all regulated lenders. Tracking it offers a panoramic view of credit provision, enabling supervisors to (i) gauge financial deepening, (ii) assess systemic leverage of the banking sector, (iii) monitor shifts in portfolio composition (e.g., rise of consumer or MSME lending), and (iv) feed macro-prudential stress tests and monetary policy models. Sharp expansions may indicate rapid financial inclusion or overheating; contractions can herald credit crunches that dampen growth. !- Definitions and concepts: Credit operation – any legally binding loan, line of credit, hire-purchase, lease, or other. Off-balance-sheet commitments (e.g., undrawn credit lines, guarantees) are usually excluded or reported separately. Volume (count): unique credit contracts outstanding at the reporting date; renewals/extensions count as new operations if a fresh contract is signed. Segmentation by sector (household, corporate, government), product type, currency, and residual maturity enriches analysis. !- Data requirements: Supervisory returns or call-reports detailing credit operations contract count by institution and product. Standardised product and sector taxononies to avoid double counting.</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>How does the gender composition of borrowers in the total financial sector credit portfolio compare across the number and value of outstanding credit operations? Are there gender disparities in both the frequency (number) of credit operations and the total credit amounts extended? How do these disparities vary by loan type, sector, or borrower demographics such as age, income, and location? Are women or other gender groups underrepresented in certain types of credit or regions within the overall portfolio? How do FSPs with higher levels of gender diversity compare in terms of the balance and number of credit operations granted to different genders? Are portfolios with more balanced gender representation associated with differences in credit performance, such as lower default rates or more stable repayment patterns?</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
           <t>Liquidity risk</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
+      <c r="C193" t="inlineStr">
         <is>
           <t>Savings</t>
         </is>
       </c>
-      <c r="D192">
+      <c r="D193">
         <v>17</v>
       </c>
-      <c r="E192" t="inlineStr">
+      <c r="E193" t="inlineStr">
         <is>
           <t>Deposit stability/volatility</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr">
+      <c r="F193" t="inlineStr">
         <is>
           <t>Stability/volatility of retail deposits (deposit stickness, deposit stability, deposit flows)</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
+      <c r="G193" t="inlineStr">
         <is>
           <t>The deposit stability (or deposit-volatility) indicator assesses how predictable an FSP's funding base is by tracking the fluctuation and “stickiness” of customer deposits over time. Sudden, correlated outflows—whether triggered by market rumours, rate competition or digital bank runs—can force a bank to liquidate assets at fire-sale prices or draw on emergency facilities. Prudential supervisors monitor deposit volatility alongside liquidity ratios to judge an institution’s ability to withstand funding shocks and to calibrate run-off assumptions in stress tests and the Liquidity Coverage Ratio (LCR). Definitions &amp; concepts: Core / stable deposits: retail balances judged unlikely to flee under stress; often defined by balance size, relationship depth, and whether the account is transactional rather than rate-sensitive. Volatility metrics: standard deviation of daily balances divided by the mean (coefficient of variation), maximum one-day net outflow over a look-back window, or elasticity (beta) to market rates. Calculation methods vary across countries. !- Data requirements: High-frequency (daily or intraday) deposit-balance time series, tagged by customer type, product, and currency. Interest-rate history to estimate betas. Customer identifiers for relationship tenure, cross-selling, and concentration analysis. 
 Digital channel dynamics: mobile app withdrawals can accelerate run speed beyond historical norms; backward-looking volatility measures may understate future risk.</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
+      <c r="H193" t="inlineStr">
         <is>
           <t>Are there gender disparities in deposit stability or volatility, and do accounts held by different gender groups show distinct patterns in the frequency or magnitude of balance fluctuations? Could these differences reflect varying income regularity, saving habits, or financial resilience? How do these patterns vary across age, income level, or geographic location? Are there notable differences in deposit stability between FSPs with higher or lower levels of gender diversity in their customer base? Do FSPs with greater gender diversity among their clients tend to experience greater deposit stickiness overall?</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
+      <c r="L193" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
+    <row r="194">
+      <c r="A194" t="inlineStr">
         <is>
           <t>Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B194" t="inlineStr">
         <is>
           <t>Soundness</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
+      <c r="C194" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D193">
+      <c r="D194">
         <v>392</v>
       </c>
-      <c r="E193" t="inlineStr">
+      <c r="E194" t="inlineStr">
         <is>
           <t>Combined ratio</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
+      <c r="F194" t="inlineStr">
         <is>
           <t>% of total premium income used in paying expenses and claims</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
+      <c r="G194" t="inlineStr">
         <is>
           <t>The combined ratio is a key measure of underwriting profitability in the insurance industry. It indicates the proportion of each unit of premium earned that an insurer uses to cover claims-related losses and operating expenses. A combined ratio below 100% signals an underwriting profit, meaning the insurer is collecting more in premiums than it pays out in claims and expenses, while a ratio above 100% indicates an underwriting loss. This indicator is widely used by insurance supervisors as an early warning signal for assessing the financial health and operational efficiency of insurers, and it supports prudential oversight by helping to identify companies that may be underpricing risk or operating with excessive costs. Monitoring this indicator over time and across different types of insurers can reveal structural patterns in the sustainability of insurance business models and inform supervisory responses.
 !-Definitions and concepts: The combined ratio is calculated as the sum of two components: the loss ratio and the expense ratio. The loss ratio measures claims-related costs (incurred losses plus loss adjustment expenses) as a proportion of earned premiums. The expense ratio measures underwriting and administrative expenses (such as commissions, salaries, and other operational costs) as a proportion of earned or written premiums. The general formula is: Combined Ratio = Loss Ratio + Expense Ratio, or equivalently, Combined Ratio = (Incurred Losses + Loss Adjustment Expenses + Underwriting Expenses) / Earned Premiums. Earned premiums refer to the portion of written premiums corresponding to the coverage period that has elapsed, ensuring proper matching between income recognized and associated claims obligations. A combined ratio of exactly 100% represents the break-even point for underwriting operations.
@@ -10880,36 +10931,36 @@
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
+    <row r="195">
+      <c r="A195" t="inlineStr">
         <is>
           <t>Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="B195" t="inlineStr">
         <is>
           <t>Soundness</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
+      <c r="C195" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D194">
+      <c r="D195">
         <v>394</v>
       </c>
-      <c r="E194" t="inlineStr">
+      <c r="E195" t="inlineStr">
         <is>
           <t>Expense ratio</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
+      <c r="F195" t="inlineStr">
         <is>
           <t>% of earned premiums that an insurance company spends on underwriting and administrative expenses (excluding claims)</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
+      <c r="G195" t="inlineStr">
         <is>
           <t>The expense ratio measures the proportion of earned premiums that an insurance company spends on underwriting and administrative expenses, excluding claims-related costs. It is a key indicator of operational efficiency, reflecting how effectively an insurer manages the costs associated with acquiring, underwriting, and servicing insurance policies. Financial sector authorities use this indicator to assess whether insurers are operating within sustainable cost structures and to identify potential inefficiencies that could affect policyholder value or long-term solvency. Together with the loss ratio, the expense ratio is one of the two components of the combined ratio, providing a complementary view that isolates operational cost management from claims experience. Monitoring the expense ratio across providers and over time can help supervisors detect trends in market competitiveness, evaluate the impact of new distribution models (such as digital or agent-based channels) on cost structures, and assess whether high acquisition or administrative costs may be eroding the value delivered to policyholders.
 !-Definitions and concepts: The expense ratio is calculated by dividing total underwriting and administrative expenses by premiums for a given reporting period. The formula is: Expense Ratio (%) = (Underwriting and Administrative Expenses / Premiums) × 100. Underwriting and administrative expenses typically include acquisition costs (such as agent and broker commissions, marketing expenses, and premium taxes), as well as operational costs associated with policy administration, underwriting staff salaries, technology, licensing fees, and general overhead. These expenses exclude claims payments and loss adjustment expenses, which are captured separately in the loss ratio. An important distinction exists in the choice of denominator: under statutory accounting conventions, the expense ratio often uses written premiums, since acquisition costs are recognized at the time a policy is written rather than spread over its duration. Under other accounting frameworks, earned premiums may be used. This difference can affect comparability across jurisdictions and should be noted when interpreting the ratio.
@@ -10918,66 +10969,6 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Sustainability</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Climate and environmental objectives</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D195">
-        <v>330</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Rural credit (volume)</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>Number of loans in the retail loan portfolio designated as rural credit</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector, such as the volume of loans disbursed as a % of the total loan portfolio. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis.</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in participation in the rural credit portfolio, when measured by number of loans and disaggregated by loan type and type of borrower (individual or MSME)? Are these disparities more pronounced in certain types of financial service providers or geographic regions? Do FSPs with higher levels of gender diversity tend to allocate a greater share of loan volume to rural women or women-led MSMEs? Does the proportion of rural credit within the total number of loans granted to women differ significantly from that of men, and what does this reveal about access to credit by gender and location?</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>Usage</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
-        </is>
-      </c>
-    </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
@@ -10995,41 +10986,46 @@
         </is>
       </c>
       <c r="D196">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Climate and other environmental risk in the credit portfolio</t>
+          <t>Rural credit (volume)</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Exposure of the credit portfolio to customers or industries with high climate (physical and transition risks) and other environmental risk</t>
+          <t>Number of loans in the retail loan portfolio designated as rural credit</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>This indicator quantifies how much of the loan book is exposed to climate-related risks (physical and transition) and broader environmental risks (e.g., water stress, biodiversity loss, pollution). It helps firms and supervisors judge vulnerability to asset impairment, collateral devaluation, cash-flow shocks, and regulatory change. It also informs pricing, sector limits, and strategic portfolio alignment. Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, while the NGFS provides a range of additional defintions, including nature-related financial risks.</t>
+          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector, such as the volume of loans disbursed as a % of the total loan portfolio. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis.</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>How is FSP gender diversity and the gender composition of the customer base correlated with climate-related financial risks (physical and transition) and other environmental risks?</t>
+          <t>Are there gender disparities in participation in the rural credit portfolio, when measured by number of loans and disaggregated by loan type and type of borrower (individual or MSME)? Are these disparities more pronounced in certain types of financial service providers or geographic regions? Do FSPs with higher levels of gender diversity tend to allocate a greater share of loan volume to rural women or women-led MSMEs? Does the proportion of rural credit within the total number of loans granted to women differ significantly from that of men, and what does this reveal about access to credit by gender and location?</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Other; Stability, safety and soundness</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Statistics and research, Credit risk, Stability</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -11050,36 +11046,36 @@
         </is>
       </c>
       <c r="D197">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Exposure to polluting firms/industries</t>
+          <t>Climate and other environmental risk in the credit portfolio</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Number of loans and total exposure of the credit portfolio to pollutting firms/industries</t>
+          <t>Exposure of the credit portfolio to customers or industries with high climate (physical and transition risks) and other environmental risk</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>This indicator quantifies how much of the loan book is exposed to borrowers classified as big polluters (e.g., fossil fuel industry). The definition of polluting borrowers or activity varies widely across countries and the indicator should be aligned with national definitions. The EU uses a range of similar indicators: https://www.ecb.europa.eu/stats/all-key-statistics/horizontal-indicators/sustainability-indicators/data/html/ecb.climate_indicators_carbon_emissions.en.html</t>
+          <t>This indicator quantifies how much of the loan book is exposed to climate-related risks (physical and transition) and broader environmental risks (e.g., water stress, biodiversity loss, pollution). It helps firms and supervisors judge vulnerability to asset impairment, collateral devaluation, cash-flow shocks, and regulatory change. It also informs pricing, sector limits, and strategic portfolio alignment. Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, while the NGFS provides a range of additional defintions, including nature-related financial risks.</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>How is FSP gender diversity correlated with lending to high polluters?</t>
+          <t>How is FSP gender diversity and the gender composition of the customer base correlated with climate-related financial risks (physical and transition) and other environmental risks?</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Stability, safety and soundness</t>
+          <t>Other; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Credit risk, Stability</t>
+          <t>Statistics and research, Credit risk, Stability</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -11105,26 +11101,26 @@
         </is>
       </c>
       <c r="D198">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Financed emissions (Carbon footprint of credit portfolio)</t>
+          <t>Exposure to polluting firms/industries</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Contribution of the financial sector to emissions (debtor's emissions financed by the financial sector via loan and securities portfolios)</t>
+          <t>Number of loans and total exposure of the credit portfolio to pollutting firms/industries</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>This indicator, also known as carbon footprint, quantifies how much carbon emission the loan book is financing, by estimating the carbon emissions of financed activities and clients. The standardized calculations of emissions vary across countries and the indicator should align with national practices. In the EU, ther financed emissions (FE) indicator provides information on the financing of high-emitting economic activities. It tracks the amount of total carbon emissions from non-financial corporations (borrowers) that can be linked to funding from financial institutions, based on a set of identifiable securities and loan portfolios. See https://www.ecb.europa.eu/stats/all-key-statistics/horizontal-indicators/sustainability-indicators/data/html/ecb.climate_indicators_carbon_emissions.en.html</t>
+          <t>This indicator quantifies how much of the loan book is exposed to borrowers classified as big polluters (e.g., fossil fuel industry). The definition of polluting borrowers or activity varies widely across countries and the indicator should be aligned with national definitions. The EU uses a range of similar indicators: https://www.ecb.europa.eu/stats/all-key-statistics/horizontal-indicators/sustainability-indicators/data/html/ecb.climate_indicators_carbon_emissions.en.html</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>How is FSP gender diversity correlated with financed emissions of the loan and securities portfolio?</t>
+          <t>How is FSP gender diversity correlated with lending to high polluters?</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -11160,41 +11156,41 @@
         </is>
       </c>
       <c r="D199">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Green/sustainable loans</t>
+          <t>Financed emissions (Carbon footprint of credit portfolio)</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>% of all loans labelled as green or sustainable</t>
+          <t>Contribution of the financial sector to emissions (debtor's emissions financed by the financial sector via loan and securities portfolios)</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>This indicator shows the share of a regulated lender’s aggregate loan book that is formally designated green, social, or sustainable. A higher percentage signals that credit is being channelled toward activities aligned with climate-transition and inclusive-growth objectives, helping regulators gauge progress against national or international sustainable-finance targets and identify institutions with elevated exposure to taxonomy-related reputation or compliance risks. The indicator is an input for green-asset-ratio disclosures and climate-stress-testing frameworks. !- Definitions and concepts: definition of green / sustainable loan varies widely across countries and should align with local frameworks. !- Data requirements: Loan-level tagging for use-of-proceeds or sustainability-performance targets, mapped to the applicable taxonomy code. Up-to-date balances to build the numerator and denominator. Dynamic criteria: Ongoing revisions to reference taxonomies may reclassify loans ex-post, creating series breaks.</t>
+          <t>This indicator, also known as carbon footprint, quantifies how much carbon emission the loan book is financing, by estimating the carbon emissions of financed activities and clients. The standardized calculations of emissions vary across countries and the indicator should align with national practices. In the EU, ther financed emissions (FE) indicator provides information on the financing of high-emitting economic activities. It tracks the amount of total carbon emissions from non-financial corporations (borrowers) that can be linked to funding from financial institutions, based on a set of identifiable securities and loan portfolios. See https://www.ecb.europa.eu/stats/all-key-statistics/horizontal-indicators/sustainability-indicators/data/html/ecb.climate_indicators_carbon_emissions.en.html</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Are there gender, location, and income disparities in access to green and sustainable loans, including those aimed at climate adaptation and resilience? How do these disparities intersect with factors such as age and sector of activity? Are women or other gender groups underrepresented among borrowers of green loans, and what barriers might contribute to this? Do financial service providers with higher levels of gender diversity tend to have relatively larger and more inclusive green/sustainable loan portfolios? How do repayment patterns and loan terms for green loans differ by gender, and what implications do these have for promoting equitable access to climate finance?</t>
+          <t>How is FSP gender diversity correlated with financed emissions of the loan and securities portfolio?</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Financial inclusion; Other; Stability, safety and soundness</t>
+          <t>Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Uptake, Statistics and research, Impact</t>
+          <t>Credit risk, Stability</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -11215,41 +11211,36 @@
         </is>
       </c>
       <c r="D200">
-        <v>331</v>
+        <v>21</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Rural credit (outstanding balance)</t>
+          <t>Green/sustainable loans</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>% of the total retail loan portfolio that is rural credit based on outstanding balance</t>
+          <t>% of all loans labelled as green or sustainable</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis. !- Data requirements: Loan account level data, with details on date of disbursements, size of loan, payment schedule and repayments to date. Loan-level detail should have an existing agricultural classification or description of loan to enable classification.</t>
+          <t>This indicator shows the share of a regulated lender’s aggregate loan book that is formally designated green, social, or sustainable. A higher percentage signals that credit is being channelled toward activities aligned with climate-transition and inclusive-growth objectives, helping regulators gauge progress against national or international sustainable-finance targets and identify institutions with elevated exposure to taxonomy-related reputation or compliance risks. The indicator is an input for green-asset-ratio disclosures and climate-stress-testing frameworks. !- Definitions and concepts: definition of green / sustainable loan varies widely across countries and should align with local frameworks. !- Data requirements: Loan-level tagging for use-of-proceeds or sustainability-performance targets, mapped to the applicable taxonomy code. Up-to-date balances to build the numerator and denominator. Dynamic criteria: Ongoing revisions to reference taxonomies may reclassify loans ex-post, creating series breaks.</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of the outstanding retail loan portfolio held by rural borrowers, disaggregated by gender and type of borrower? Are these disparities more significant in specific regions or FSP types? Do rural women hold a lower share of outstanding balances, and could this reflect differences in loan size, duration, or repayment behavior? How does the share of rural credit within the total outstanding credit held by women compare to that of men, and what does it suggest about the gendered distribution of long-term credit in rural areas?</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>Are there gender, location, and income disparities in access to green and sustainable loans, including those aimed at climate adaptation and resilience? How do these disparities intersect with factors such as age and sector of activity? Are women or other gender groups underrepresented among borrowers of green loans, and what barriers might contribute to this? Do financial service providers with higher levels of gender diversity tend to have relatively larger and more inclusive green/sustainable loan portfolios? How do repayment patterns and loan terms for green loans differ by gender, and what implications do these have for promoting equitable access to climate finance?</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection</t>
+          <t>Financial inclusion; Other; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Uptake, Impact</t>
+          <t>Uptake, Statistics and research, Impact</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -11275,16 +11266,16 @@
         </is>
       </c>
       <c r="D201">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Rural credit (principal disbursed)</t>
+          <t>Rural credit (outstanding balance)</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>% of the total retail loan portfolio that is rural credit based on principal disbursed</t>
+          <t>% of the total retail loan portfolio that is rural credit based on outstanding balance</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -11294,7 +11285,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the value of new rural credit disbursed to borrowers, disaggregated by gender and borrower type? Are these disparities more evident in certain regions or financial service providers, particularly among those with less gender diversity? Do women in rural areas systematically receive smaller disbursements compared to men in similar loan categories or activities? Does the share of rural credit within the total disbursed credit to women differ significantly from that of men, and what does it indicate about access to productive credit for rural women? Has the share of credit disbursed to rural women changed over time in proportion to their role in the rural economy?</t>
+          <t>Are there gender disparities in the share of the outstanding retail loan portfolio held by rural borrowers, disaggregated by gender and type of borrower? Are these disparities more significant in specific regions or FSP types? Do rural women hold a lower share of outstanding balances, and could this reflect differences in loan size, duration, or repayment behavior? How does the share of rural credit within the total outstanding credit held by women compare to that of men, and what does it suggest about the gendered distribution of long-term credit in rural areas?</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -11309,7 +11300,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Usage, Impact</t>
+          <t>Uptake, Impact</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -11331,45 +11322,50 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D202">
-        <v>58</v>
+        <v>332</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Green/sustainable insurance</t>
+          <t>Rural credit (principal disbursed)</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>% of all insurance policies that are green or sustainable</t>
+          <t>% of the total retail loan portfolio that is rural credit based on principal disbursed</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>This indicator shows the share of an insurer's aggregate policy portfolio that is formally designated green, social, or sustainable. A higher percentage signals that insurance being channelled toward activities aligned with climate-transition and inclusive-growth objectives (e.g., crop insurance for agroforestry), helping regulators gauge progress against national or international sustainable-finance targets. !- Definitions and concepts: definition of green / sustainable insurance varies widely across countries and should align with local frameworks. !- Data requirements: Policy-level tagging for sustainability-performance targets, mapped to the applicable taxonomy code.</t>
+          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis. !- Data requirements: Loan account level data, with details on date of disbursements, size of loan, payment schedule and repayments to date. Loan-level detail should have an existing agricultural classification or description of loan to enable classification.</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Are there disparities by gender, income, and location in the likelihood of acquiring green or sustainable insurance products, including climate resilience coverage? Are certain gender groups underserved in this market? Do financial service providers (FSPs) with higher levels of gender diversity tend to maintain larger or more diverse green/sustainable insurance portfolios?</t>
+          <t>Are there gender disparities in the value of new rural credit disbursed to borrowers, disaggregated by gender and borrower type? Are these disparities more evident in certain regions or financial service providers, particularly among those with less gender diversity? Do women in rural areas systematically receive smaller disbursements compared to men in similar loan categories or activities? Does the share of rural credit within the total disbursed credit to women differ significantly from that of men, and what does it indicate about access to productive credit for rural women? Has the share of credit disbursed to rural women changed over time in proportion to their role in the rural economy?</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Financial inclusion; Other</t>
+          <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Usage, Statistics and research</t>
+          <t>Usage, Impact</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -11386,40 +11382,40 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D203">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Holdings of green/sustainable bonds</t>
+          <t>Green/sustainable insurance</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Volume (holdings) and value (amount outstanding) of sustainable/green bonds</t>
+          <t>% of all insurance policies that are green or sustainable</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>The indicator measures the aggregate value and volume of green and/or sustainability bonds held by investors, reflecting capital directed towards projects and activities with positive environmental or social impacts. It is a measure of sustainable finance. The definition of sustainable or green bond varies widely across countries and the indicator should align with local practices. An example of definition is provided by the Green Bond Principles (GBP), by the International Capital Markets Association (ICMA) https://www.icmagroup.org/sustainable-finance/the-principles-guidelines-and-handbooks/green-bond-principles-gbp/</t>
+          <t>This indicator shows the share of an insurer's aggregate policy portfolio that is formally designated green, social, or sustainable. A higher percentage signals that insurance being channelled toward activities aligned with climate-transition and inclusive-growth objectives (e.g., crop insurance for agroforestry), helping regulators gauge progress against national or international sustainable-finance targets. !- Definitions and concepts: definition of green / sustainable insurance varies widely across countries and should align with local frameworks. !- Data requirements: Policy-level tagging for sustainability-performance targets, mapped to the applicable taxonomy code.</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the acquisition/holding of green/sustainable bonds? Are FSPs with higher levels of gender diversity more likely to distribute sustainable or green bonds to a more diverse investor base?  Comparing this with gender diversity at FSPs, are institutions with higher levels of gender diversity more likely to have larger green/sustainable portfolios?</t>
+          <t>Are there disparities by gender, income, and location in the likelihood of acquiring green or sustainable insurance products, including climate resilience coverage? Are certain gender groups underserved in this market? Do financial service providers (FSPs) with higher levels of gender diversity tend to maintain larger or more diverse green/sustainable insurance portfolios?</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Other; Market development</t>
+          <t>Financial inclusion; Other</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Statistics and research, Sustainability</t>
+          <t>Usage, Statistics and research</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -11445,41 +11441,41 @@
         </is>
       </c>
       <c r="D204">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Issuances of green/sustainable bonds</t>
+          <t>Holdings of green/sustainable bonds</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Volume (issuances) and value (amount outstanding) of sustainable/green bonds</t>
+          <t>Volume (holdings) and value (amount outstanding) of sustainable/green bonds</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>This indicator tracks the number and, more commonly, the face value (in USD, EUR or local currency) of bonds labelled green, social, sustainability or sustainability-linked that reach primary markets in a given period. By capturing how much fresh capital is being channelled explicitly toward environmentally and/or socially beneficial projects, it offers a tangible gauge of the financial sector’s contribution to the transition to a low-carbon, inclusive economy. Policymakers use the series to monitor progress against climate-finance targets, assess the effectiveness of incentives such as tax exemptions or regulatory relief, and spot market slow-downs that could jeopardise net-zero pathways. The definition of sustainable or green bond varies widely across countries and the indicator should align with local practices. An example of definition is provided by the Green Bond Principles (GBP), by the International Capital Markets Association (ICMA) https://www.icmagroup.org/sustainable-finance/the-principles-guidelines-and-handbooks/green-bond-principles-gbp/</t>
+          <t>The indicator measures the aggregate value and volume of green and/or sustainability bonds held by investors, reflecting capital directed towards projects and activities with positive environmental or social impacts. It is a measure of sustainable finance. The definition of sustainable or green bond varies widely across countries and the indicator should align with local practices. An example of definition is provided by the Green Bond Principles (GBP), by the International Capital Markets Association (ICMA) https://www.icmagroup.org/sustainable-finance/the-principles-guidelines-and-handbooks/green-bond-principles-gbp/</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Do companies with higher levels of gender diversity issue more green bonds? Are FSPs with higher levels of gender diversity more likely to distribute sustainable or green bonds?</t>
+          <t>Are there gender disparities in the acquisition/holding of green/sustainable bonds? Are FSPs with higher levels of gender diversity more likely to distribute sustainable or green bonds to a more diverse investor base?  Comparing this with gender diversity at FSPs, are institutions with higher levels of gender diversity more likely to have larger green/sustainable portfolios?</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>Financial inclusion; Other; Market development</t>
+          <t>Other; Market development</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Usage, Statistics and research, Sustainability</t>
+          <t>Statistics and research, Sustainability</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -11496,45 +11492,45 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Savings, Credit, Insurance, Pensions</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="D205">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Climate and other environmental risks in the investment portoflio</t>
+          <t>Issuances of green/sustainable bonds</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Exposure of the investment portfolio to industries with high climate and other environmental risks</t>
+          <t>Volume (issuances) and value (amount outstanding) of sustainable/green bonds</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>This indicator quantifies how much of the investment book is exposed to climate-related risks (physical and transition) and broader environmental risks (e.g., water stress, biodiversity loss, pollution). It helps firms and supervisors judge vulnerability to asset impairment and regulatory change. Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, while the NGFS provides a range of additional definitions, including nature-related financial risks.</t>
+          <t>This indicator tracks the number and, more commonly, the face value (in USD, EUR or local currency) of bonds labelled green, social, sustainability or sustainability-linked that reach primary markets in a given period. By capturing how much fresh capital is being channelled explicitly toward environmentally and/or socially beneficial projects, it offers a tangible gauge of the financial sector’s contribution to the transition to a low-carbon, inclusive economy. Policymakers use the series to monitor progress against climate-finance targets, assess the effectiveness of incentives such as tax exemptions or regulatory relief, and spot market slow-downs that could jeopardise net-zero pathways. The definition of sustainable or green bond varies widely across countries and the indicator should align with local practices. An example of definition is provided by the Green Bond Principles (GBP), by the International Capital Markets Association (ICMA) https://www.icmagroup.org/sustainable-finance/the-principles-guidelines-and-handbooks/green-bond-principles-gbp/</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>How is FSP gender diversity correlated with climate-related financial risks and other environmental risks arising from the investment portfolio of insurers and banks?</t>
+          <t>Do companies with higher levels of gender diversity issue more green bonds? Are FSPs with higher levels of gender diversity more likely to distribute sustainable or green bonds?</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Stability, safety and soundness</t>
+          <t>Financial inclusion; Other; Market development</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Market risk, Credit risk</t>
+          <t>Usage, Statistics and research, Sustainability</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -11546,40 +11542,45 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Gender equality</t>
+          <t>Climate and environmental objectives</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Savings, Credit, Insurance, Pensions</t>
         </is>
       </c>
       <c r="D206">
-        <v>11</v>
+        <v>126</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Gender diversity at FSP (by reference workforce group)</t>
+          <t>Climate and other environmental risks in the investment portoflio</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Gender composition of FSP workforce by level of responsibility (Board, management, staff)</t>
+          <t>Exposure of the investment portfolio to industries with high climate and other environmental risks</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Measure used to assess the representation of different genders within a financial institution. It serves as a critical tool for evaluating a firm's commitment to inclusivity and is increasingly correlated with enhanced financial performance, risk management, and innovation. This indicator is not a single metric but a suite of measurements that can be applied across various levels of an organization. Ideally, it would be calculated at the board level, the senior management level (C suite), and the staff level. In some occasions, it can also be useful to calculate it for specific roles within the financial institution, such as branch managers, or agents, when analyzing differences in performance related to specific issues, such as consumer protection and conduct issues. In addition to being useful to monitor diversity at the system level, and its alignment with national gender equality policies, this indicator can also be used by prudential and conduct supervisors, as a growing body of knowledge points to improved financial and conduct performance of financial institutions that have a greater level of diversity. For prudential supervisors, this indicator serves as a valuable proxy for assessing a firm's health, as greater gender diversity is often correlated with stronger corporate governance, more prudent risk management, and enhanced financial stability.</t>
+          <t>This indicator quantifies how much of the investment book is exposed to climate-related risks (physical and transition) and broader environmental risks (e.g., water stress, biodiversity loss, pollution). It helps firms and supervisors judge vulnerability to asset impairment and regulatory change. Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, while the NGFS provides a range of additional definitions, including nature-related financial risks.</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Are there gender disparities in workforce participation across different types of FSPs? At what responsibility levels? How does gender diversity in FSP management correlate with key financial indicators (e.g., Stability, Financial Inclusion, Customer Protection, Sustainability)? Comparing with climate-related financial data (e.g., green loan portfolios, green insurance), does gender diversity in FSPs correlate with the growth of these portfolios? If legal or regulatory gender equity requirements exist for FSPs, are they being met? Does gender diversity correlate with variations in supervisory risk scores? How does gender diversity correlate with staff turnover (if data is available)? How does gender diversity correlate with enforcement and other supervisory actions?</t>
+          <t>How is FSP gender diversity correlated with climate-related financial risks and other environmental risks arising from the investment portfolio of insurers and banks?</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection; Stability, safety and soundness; Market development</t>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Market risk, Credit risk</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -11605,26 +11606,26 @@
         </is>
       </c>
       <c r="D207">
-        <v>341</v>
+        <v>11</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Gender diversity of customer base</t>
+          <t>Gender diversity at FSP (by reference workforce group)</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Gender composition of FSP customer base</t>
+          <t>Gender composition of FSP workforce by level of responsibility (Board, management, staff)</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Measures the representation of different genders—women, men, and non-binary individuals—among a financial institution's clients. This metric provides insights into a firm's market reach, product inclusiveness, and potential exposure to social and economic trends. This indicator can be used to monitor implementaton of gender equality targets and national policies, but also by prudential and conduct supervisors, to compare performance in other metrics, such as basic consumer risk indicators and prudential risk indicators, with the level of gender diversity of the customer base, with the purpose of finding any possible correlation.</t>
+          <t>Measure used to assess the representation of different genders within a financial institution. It serves as a critical tool for evaluating a firm's commitment to inclusivity and is increasingly correlated with enhanced financial performance, risk management, and innovation. This indicator is not a single metric but a suite of measurements that can be applied across various levels of an organization. Ideally, it would be calculated at the board level, the senior management level (C suite), and the staff level. In some occasions, it can also be useful to calculate it for specific roles within the financial institution, such as branch managers, or agents, when analyzing differences in performance related to specific issues, such as consumer protection and conduct issues. In addition to being useful to monitor diversity at the system level, and its alignment with national gender equality policies, this indicator can also be used by prudential and conduct supervisors, as a growing body of knowledge points to improved financial and conduct performance of financial institutions that have a greater level of diversity. For prudential supervisors, this indicator serves as a valuable proxy for assessing a firm's health, as greater gender diversity is often correlated with stronger corporate governance, more prudent risk management, and enhanced financial stability.</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Are there significant gender disparities in the composition of customers across different types of financial service providers (FSPs)? How does the gender diversity of the FSP customer base vary by institution size, sector, and geographic region? What correlations exist between the gender diversity of the customer base and key financial inclusion metrics such as account ownership, loan uptake, and insurance coverage? How does greater gender diversity among customers relate to customer protection outcomes, including complaint resolution and fair treatment? Are FSPs with more gender-diverse customer bases also demonstrating stronger prudential performance and sustainability indicators? How do gender disparities in the customer base influencefinancila outcomes such as Financial Health? And broader social and economic outcomes, such as women's economic empowerment, MSME growth, climate change, jobs creation or poverty reduction?</t>
+          <t>Are there gender disparities in workforce participation across different types of FSPs? At what responsibility levels? How does gender diversity in FSP management correlate with key financial indicators (e.g., Stability, Financial Inclusion, Customer Protection, Sustainability)? Comparing with climate-related financial data (e.g., green loan portfolios, green insurance), does gender diversity in FSPs correlate with the growth of these portfolios? If legal or regulatory gender equity requirements exist for FSPs, are they being met? Does gender diversity correlate with variations in supervisory risk scores? How does gender diversity correlate with staff turnover (if data is available)? How does gender diversity correlate with enforcement and other supervisory actions?</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -11655,26 +11656,26 @@
         </is>
       </c>
       <c r="D208">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Gender pay gap at FSPs</t>
+          <t>Gender diversity of customer base</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Gender pay gap at FSPs</t>
+          <t>Gender composition of FSP customer base</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Metric that measures the difference in average (or median) earnings between genders across similar functions and roles at financial institutions. Typically calculated to spot differences across men and women, but it could be expanded to include other genders. It's typically expressed as a percentage of the higher earner gender (usually men's earnings), for a given role or hierarchical level at the financial institution. Prudential supervisors can use this indicator with a focus on the safety and soundness of financial institutions. A significant gender pay gap can be an indicator of underlying governance and operational risks. for conduct supervisors, a significant gender pay gap could be an indication of potential misconduct and unfairness that could affect customers. The gender pay gap is most commonly calculated as the mean or median difference in gross earnings between all male and female employees, expressed as a percentage of the male earnings.</t>
+          <t>Measures the representation of different genders—women, men, and non-binary individuals—among a financial institution's clients. This metric provides insights into a firm's market reach, product inclusiveness, and potential exposure to social and economic trends. This indicator can be used to monitor implementaton of gender equality targets and national policies, but also by prudential and conduct supervisors, to compare performance in other metrics, such as basic consumer risk indicators and prudential risk indicators, with the level of gender diversity of the customer base, with the purpose of finding any possible correlation.</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Are there gender disparities in compensation for similar positions or responsibilities (Board, management, staff)? How does this compare with other macro indicators related to financial stability and portfolio performance across FSPs (credit, insurance, investment funds, pensions)? Are FSPs with greater gender diversity in the Board more likely to present lower gender pay gap?</t>
+          <t>Are there significant gender disparities in the composition of customers across different types of financial service providers (FSPs)? How does the gender diversity of the FSP customer base vary by institution size, sector, and geographic region? What correlations exist between the gender diversity of the customer base and key financial inclusion metrics such as account ownership, loan uptake, and insurance coverage? How does greater gender diversity among customers relate to customer protection outcomes, including complaint resolution and fair treatment? Are FSPs with more gender-diverse customer bases also demonstrating stronger prudential performance and sustainability indicators? How do gender disparities in the customer base influencefinancila outcomes such as Financial Health? And broader social and economic outcomes, such as women's economic empowerment, MSME growth, climate change, jobs creation or poverty reduction?</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -11705,92 +11706,87 @@
         </is>
       </c>
       <c r="D209">
+        <v>131</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Gender pay gap at FSPs</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Gender pay gap at FSPs</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Metric that measures the difference in average (or median) earnings between genders across similar functions and roles at financial institutions. Typically calculated to spot differences across men and women, but it could be expanded to include other genders. It's typically expressed as a percentage of the higher earner gender (usually men's earnings), for a given role or hierarchical level at the financial institution. Prudential supervisors can use this indicator with a focus on the safety and soundness of financial institutions. A significant gender pay gap can be an indicator of underlying governance and operational risks. for conduct supervisors, a significant gender pay gap could be an indication of potential misconduct and unfairness that could affect customers. The gender pay gap is most commonly calculated as the mean or median difference in gross earnings between all male and female employees, expressed as a percentage of the male earnings.</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in compensation for similar positions or responsibilities (Board, management, staff)? How does this compare with other macro indicators related to financial stability and portfolio performance across FSPs (credit, insurance, investment funds, pensions)? Are FSPs with greater gender diversity in the Board more likely to present lower gender pay gap?</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection; Stability, safety and soundness; Market development</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Sustainability</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Gender equality</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D210">
         <v>18</v>
       </c>
-      <c r="E209" t="inlineStr">
+      <c r="E210" t="inlineStr">
         <is>
           <t>Human Resources Gender Index (HRGI)</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
+      <c r="F210" t="inlineStr">
         <is>
           <t>Index based on FSPs' gender diversity policies, covering gender and employment, gender earnings, leave and work arrangements, childcare, and other benefits</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
+      <c r="G210" t="inlineStr">
         <is>
           <t>The Human Resources Gender Index (HRGI) is a composite index that consolidates multiple HR data points to provide a holistic score of gender equality within an institution, throughout the employee lifecycle. It is not a standardized indicator. It can be defined as a weighted score that measures a financial institution's gender equality across key HR areas, including representation, remuneration, recruitment, promotion, and retention, going way beyond headcount. Potential indicator components include: representation score (gender diversity at different corporate levels), pay equality score (mean and median pay gap), gender gap in performance-based bonuses, progression score (promotion rate gender gap, recruitment score (% of women among new hires, especially at senior levels), retention score (gender gap in turnover rate).  This indicator can be used to monitor implementaton of gender equality targets and national policies, but also by prudential and conduct supervisors, to compare performance in other metrics, such as basic consumer risk indicators and prudential risk indicators, with the level of gender diversity of the customer base, with the purpose of finding any possible correlation. https://www.elibrary.imf.org/view/journals/001/2023/091/article-A001-en.xml
 .</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
+      <c r="H210" t="inlineStr">
         <is>
           <t>How do financial service providers (FSPs) compare in their Human Resources Gender Index (HRGI) scores? Are FSPs with higher levels of gender diversity in their workforce more likely to perform better across the various HRGI dimensions, such as recruitment, retention, promotion, and leadership representation? When comparing HRGI scores with key performance indicators (e.g., capital and liquidity, profitability, efficiency, customer satisfaction, innovation), is there evidence of a positive correlation? How do HRGI scores vary by FSP type, size, or region, and what best practices can be identified from top performers? How does HRGI performance relate to gender-related outcomes, such as gender-balanced customer bases or inclusive product offerings?</t>
         </is>
       </c>
-      <c r="J209" t="inlineStr">
+      <c r="J210" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection; Stability, safety and soundness; Market development</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
+      <c r="L210" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Sustainability</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Gender equality</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D210">
-        <v>12</v>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>New licenses granted to diverse FSPs</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>% of all new licenses that are issued to diverse FSPs</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>This indicator is a measure of the gender composition of newly licensed financial institutions. It helps regulators and policy makers identify trends in the gender diversity in the financial sector by looking at the leadership of financial institutions. For fuller more complete analysis, this indicator can be complemented by an indicator of the success rate of licensing applications, considering the gender of the lead sponsor.</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>What are the trends in the number of new licenses issued to diverse FSPs?</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>Other; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>Statistics and research,  Stability</t>
-        </is>
-      </c>
-      <c r="L210" t="inlineStr">
-        <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -11811,26 +11807,36 @@
         </is>
       </c>
       <c r="D211">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Success rate of license applications by diverse FSPs</t>
+          <t>New licenses granted to diverse FSPs</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>% of all license applications by diverse FSPs that are issued</t>
+          <t>% of all new licenses that are issued to diverse FSPs</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>This indicator is a measure of potential gender biases in licensing decisions by the financial authority. It helps authorities analyze the success rate of license pplications by segmenting applications by their final oucome (rejection/approval), and the gender of the lead sponsor of the application (e.g., the majority individual shareholder). The definition of lead sponsor will vary across countries and the indicator should align with local practices.</t>
+          <t>This indicator is a measure of the gender composition of newly licensed financial institutions. It helps regulators and policy makers identify trends in the gender diversity in the financial sector by looking at the leadership of financial institutions. For fuller more complete analysis, this indicator can be complemented by an indicator of the success rate of licensing applications, considering the gender of the lead sponsor.</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>To what extent does the gender of individuals in leadership or control positions within the proposed FSPs influence the likelihood of obtaining a license from the regulatory authority?</t>
+          <t>What are the trends in the number of new licenses issued to diverse FSPs?</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Other; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Statistics and research,  Stability</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -11842,55 +11848,45 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Market development</t>
+          <t>Sustainability</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Capital markets development</t>
+          <t>Gender equality</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D212">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Crowdfunding - Differential rate of return (equity)</t>
+          <t>Success rate of license applications by diverse FSPs</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Difference between the advertised/promised rate of return and the actual rate of return of equity in crowdfunding projects</t>
+          <t>% of all license applications by diverse FSPs that are issued</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Measures the gap between the projected or advertised rate of return presented to investors before a project is funded and the actual rate of return realized after the project is completed. This is a critical conduct indicator that measures the accuracy of a project's promises versus its real-world performance. For investors, this metric is a tool for due diligence. For conduct supervisors, it can be used to detect mis-selling and fraud. A large and persistent negative differential (where actual returns are consistently far below promised returns) is a red flag. it could flag issues such as inadequate risk disclosure and fraud. When gender disaggregated by the gender of the main sponsor or lead executive, the indicator can provide additional information. If projects led by women consistently show a smaller negative "reality gap" (meaning their actual returns are closer to their promised returns), it could suggest they are more conservative or accurate in their financial projections. This would be a crucial data point in assessing risk and investor protection. Using this indicator together with the indicator on rejected crowddfunding projects could strenghten the identification of gender bias inside the securities authority. Return Differential (%) = Actual Rate of Return - Advertised/Promised Rate of Return.</t>
+          <t>This indicator is a measure of potential gender biases in licensing decisions by the financial authority. It helps authorities analyze the success rate of license pplications by segmenting applications by their final oucome (rejection/approval), and the gender of the lead sponsor of the application (e.g., the majority individual shareholder). The definition of lead sponsor will vary across countries and the indicator should align with local practices.</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Are there differences in the rates of return for crowdfunding projects depending on the gender assigned to the MSME seeking funding?</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Other</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>Uptake (account ownership), Statistics and research</t>
+          <t>To what extent does the gender of individuals in leadership or control positions within the proposed FSPs influence the likelihood of obtaining a license from the regulatory authority?</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -11911,26 +11907,36 @@
         </is>
       </c>
       <c r="D213">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Crowdfunding - Authorization rejection rate</t>
+          <t>Crowdfunding - Differential rate of return (equity)</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>% of all crowfunding applications that are rejected (not authorized by the securities authority)</t>
+          <t>Difference between the advertised/promised rate of return and the actual rate of return of equity in crowdfunding projects</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Measures the percentage of all crowdfunding applications submitted to a securities authority that are denied or not authorized to proceed with fundraising. This is a key regulatory indicator that reflects the quality of applications being submitted and the stringency of the regulator's vetting process, which is designed to protect investors from fraud and non-viable projects. When disaggregated by the gender of the main sponsor, the lead executive of the company, it could draw insights into potential gender biases working within the securities authority.</t>
+          <t>Measures the gap between the projected or advertised rate of return presented to investors before a project is funded and the actual rate of return realized after the project is completed. This is a critical conduct indicator that measures the accuracy of a project's promises versus its real-world performance. For investors, this metric is a tool for due diligence. For conduct supervisors, it can be used to detect mis-selling and fraud. A large and persistent negative differential (where actual returns are consistently far below promised returns) is a red flag. it could flag issues such as inadequate risk disclosure and fraud. When gender disaggregated by the gender of the main sponsor or lead executive, the indicator can provide additional information. If projects led by women consistently show a smaller negative "reality gap" (meaning their actual returns are closer to their promised returns), it could suggest they are more conservative or accurate in their financial projections. This would be a crucial data point in assessing risk and investor protection. Using this indicator together with the indicator on rejected crowddfunding projects could strenghten the identification of gender bias inside the securities authority. Return Differential (%) = Actual Rate of Return - Advertised/Promised Rate of Return.</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the rejection rates and the reasons for rejection of crowdfunding projects presented for authorization by the securities regulator?</t>
+          <t>Are there differences in the rates of return for crowdfunding projects depending on the gender assigned to the MSME seeking funding?</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Other</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Uptake (account ownership), Statistics and research</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -11956,36 +11962,26 @@
         </is>
       </c>
       <c r="D214">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Crowdfunding - Success rate</t>
+          <t>Crowdfunding - Authorization rejection rate</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>% of all crowfunding projects that are successful in raising the asked amount</t>
+          <t>% of all crowfunding applications that are rejected (not authorized by the securities authority)</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>The indicator is a metric that measures the proportion of projects on a crowdfunding platform (or the sum of all crowdfunding platforms) that successfully reach their predetermined funding goal within a specified timeframe. This indicator is a vital sign of a platform's effectiveness, credibility, and the overall health of its ecosystem. It helps gauge the ability of a platform to connect viable projects with interested backers. For MSMEs, crowdfunding can be a viable and less onerous funding source, so the indicator provids important information for monitoring development of MSME finance markets. From a market conduct perspective, while a high success rate is generally positive, an unusually high or artificially inflated rate could be a red flag for misconduct. Platforms could be setting trivially low funding goals to boost statistics,  failing to conduct proper due diligence on projects, or not being transparent about how the success rate is calculated. Successful projects is the number of projects that met or exceeded their funding target during a specific period (e.g., a month, quarter, or year).</t>
+          <t>Measures the percentage of all crowdfunding applications submitted to a securities authority that are denied or not authorized to proceed with fundraising. This is a key regulatory indicator that reflects the quality of applications being submitted and the stringency of the regulator's vetting process, which is designed to protect investors from fraud and non-viable projects. When disaggregated by the gender of the main sponsor, the lead executive of the company, it could draw insights into potential gender biases working within the securities authority.</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the success rates of crowdfunding projects? Are smaller or younger MSMEs headed by women more likely to face challenges in crowdfunding?</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Other</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>Usage, Statistics and research</t>
+          <t>Are there gender disparities in the rejection rates and the reasons for rejection of crowdfunding projects presented for authorization by the securities regulator?</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -12011,26 +12007,36 @@
         </is>
       </c>
       <c r="D215">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Crowdfunding - Transactions</t>
+          <t>Crowdfunding - Success rate</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Volume (number of offerings) and value (amount raised) of crowdfunding transactions</t>
+          <t>% of all crowfunding projects that are successful in raising the asked amount</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Metric that measures the total volume of individual investments or pledges made across all projects on a crowdfunding platform or in the entire market (across multiple platforms) over a specific period. This indicator is a direct measure of market activity and investor engagement with crowdfunding, which is increasingly important for MSME finance.</t>
+          <t>The indicator is a metric that measures the proportion of projects on a crowdfunding platform (or the sum of all crowdfunding platforms) that successfully reach their predetermined funding goal within a specified timeframe. This indicator is a vital sign of a platform's effectiveness, credibility, and the overall health of its ecosystem. It helps gauge the ability of a platform to connect viable projects with interested backers. For MSMEs, crowdfunding can be a viable and less onerous funding source, so the indicator provids important information for monitoring development of MSME finance markets. From a market conduct perspective, while a high success rate is generally positive, an unusually high or artificially inflated rate could be a red flag for misconduct. Platforms could be setting trivially low funding goals to boost statistics,  failing to conduct proper due diligence on projects, or not being transparent about how the success rate is calculated. Successful projects is the number of projects that met or exceeded their funding target during a specific period (e.g., a month, quarter, or year).</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Are there disparities in crowdfunding volumes and values raised, according to the gender of the MSMEs asking for funds? Are there disparities in terms of funding periods? Among women-owned MSMEs, which types and ages (years in operation) are driving growth in crowdfunding transactions? Are crowdfunding platforms operated by diverse management more likely to attract women-owned MSMEs, and young MSMEs headed by women?</t>
+          <t>Are there gender disparities in the success rates of crowdfunding projects? Are smaller or younger MSMEs headed by women more likely to face challenges in crowdfunding?</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Other</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Usage, Statistics and research</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -12056,26 +12062,26 @@
         </is>
       </c>
       <c r="D216">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>P2P - Investors</t>
+          <t>Crowdfunding - Transactions</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Number of P2P investors</t>
+          <t>Volume (number of offerings) and value (amount raised) of crowdfunding transactions</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>This indicator counts the number of investors registered in P2P lending platforms, as a measure of development of digital finance, and specifically P2P lending, which can potentially benefit MSMEs. It is a key metric to monitor market development in platform lending. It helps assess the effectiveness of marketing campaigns, measure market reach, and forecast potential loan demand or the ability of platforms to meet demand. A growing investor base indicates increased trust and interest, enabling the business to scale and optimize revenue generation. The indicator should be segmented by type of investor (e.g., retail investor, institutional investor), according to local regulatory definitions.</t>
+          <t>Metric that measures the total volume of individual investments or pledges made across all projects on a crowdfunding platform or in the entire market (across multiple platforms) over a specific period. This indicator is a direct measure of market activity and investor engagement with crowdfunding, which is increasingly important for MSME finance.</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the growth of reatil investors in P2P lending platforms? How do invested amounts and types vary by investor gender and other demographics? For example, do women prefer to invest in women-led MSMEs, smaller projects, or younger enterprises? Do P2P platforms operated by diverse management more likely to attract a more diverse investor base?</t>
+          <t>Are there disparities in crowdfunding volumes and values raised, according to the gender of the MSMEs asking for funds? Are there disparities in terms of funding periods? Among women-owned MSMEs, which types and ages (years in operation) are driving growth in crowdfunding transactions? Are crowdfunding platforms operated by diverse management more likely to attract women-owned MSMEs, and young MSMEs headed by women?</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -12101,36 +12107,26 @@
         </is>
       </c>
       <c r="D217">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Total investment fund shares</t>
+          <t>P2P - Investors</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Number of investment fund shares held by retail investors in the system</t>
+          <t>Number of P2P investors</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Market-wide metric that quantifies the volume of investment fund shares owned by individual, non-professional investors within a financial system. This market develoment indicator serves as a crucial gauge of retail investor participation in the capital markets, and their overall exposure to market risks. Companion indicators include the share of investment fund shares held by retail investors as percentage of total investment fund shares, and the average holding size by retail investors.</t>
+          <t>This indicator counts the number of investors registered in P2P lending platforms, as a measure of development of digital finance, and specifically P2P lending, which can potentially benefit MSMEs. It is a key metric to monitor market development in platform lending. It helps assess the effectiveness of marketing campaigns, measure market reach, and forecast potential loan demand or the ability of platforms to meet demand. A growing investor base indicates increased trust and interest, enabling the business to scale and optimize revenue generation. The indicator should be segmented by type of investor (e.g., retail investor, institutional investor), according to local regulatory definitions.</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>How has participation in investment funds evolved by gender, both for individuals and MSMEs considering the gender of their owners? What types of investment funds show growing participation by women?</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Statistics &amp; research</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>Uptake (account ownership), Other</t>
+          <t>Are there gender disparities in the growth of reatil investors in P2P lending platforms? How do invested amounts and types vary by investor gender and other demographics? For example, do women prefer to invest in women-led MSMEs, smaller projects, or younger enterprises? Do P2P platforms operated by diverse management more likely to attract a more diverse investor base?</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -12147,50 +12143,45 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Capital markets development</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Savings</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="D218">
-        <v>156</v>
+        <v>9</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Depositors who actively close deposit accounts</t>
+          <t>Total investment fund shares</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>% of retail depositors who actively closed a deposit account</t>
+          <t>Number of investment fund shares held by retail investors in the system</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>A measure of the incidence of account closing among depositors, if the measure is high, it could potentially signal issues with the quality of accounts or concerns about the safety of funds. !- Definitions and concepts: Deposit accounts include transaction and non-transaction deposit accounts, for example: Checking/demand, savings, time/term deposit accounts, pensions. 'Active' closure of an account refers to cases where the closure is initiated at the request of the customer, and not due to inactivity or dormancy. !- Data requirements: List of unique deposit account holders (i.e. an individual  must be counted as one depositor irrespective of the number of deposit accounts held) who actively close any of their accounts over a specified period of time (e.g. quarter or year); Total number of unique depositors at the beginning of the specified period.</t>
+          <t>Market-wide metric that quantifies the volume of investment fund shares owned by individual, non-professional investors within a financial system. This market develoment indicator serves as a crucial gauge of retail investor participation in the capital markets, and their overall exposure to market risks. Companion indicators include the share of investment fund shares held by retail investors as percentage of total investment fund shares, and the average holding size by retail investors.</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>How do active closure rates compare by gender? Which types of accounts are most frequently closed by each gender? How do FSPs rank in active account closures, and does this ranking change when analyzed by gender?</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>How has participation in investment funds evolved by gender, both for individuals and MSMEs considering the gender of their owners? What types of investment funds show growing participation by women?</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
+          <t>Financial inclusion; Statistics &amp; research</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Quality, Fair treatment, Soundness, Stability</t>
+          <t>Uptake (account ownership), Other</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -12212,30 +12203,30 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Savings, Credit</t>
+          <t>Savings</t>
         </is>
       </c>
       <c r="D219">
-        <v>267</v>
+        <v>156</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Interest rate spreads (loans)</t>
+          <t>Depositors who actively close deposit accounts</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Difference between the average lending rate and a reference rate (e.g. deposit rate or external reference rate)</t>
+          <t>% of retail depositors who actively closed a deposit account</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>The interest-rate spread on loans captures the margin between the average contractual rate a lender charges borrowers and an external reference rate—typically the policy rate. It is a concise gauge of (i) lenders’ credit-risk pricing, (ii) competitive conditions in the lending market, and (iii) monetary-policy transmission. Wider spreads may reflect higher perceived borrower risk, limited competition, or funding-cost pressures; persistently narrow spreads can point to aggressive underwriting or excess liquidity that may undermine future asset quality. Tracked over time and across peer institutions, interest-rate spreads provide insights into credit-cycle turning points, profitability dynamics, and the effectiveness of monetary-policy signals reaching the real economy. !- Definitions and concepts:  Loan interest rate spread (simple): Average contractual loan rate minus Reference rate measured for new originations or for the stock of loans. Net lending spread: average loan rate minus average deposit rate, often used when policy benchmarks are volatile. Segmented spreads: calculated by product (e.g., mortgages, SMEs, credit cards). Non-interest charges: fees and cross-selling income are excluded; the true all-in lending margin may be higher.</t>
+          <t>A measure of the incidence of account closing among depositors, if the measure is high, it could potentially signal issues with the quality of accounts or concerns about the safety of funds. !- Definitions and concepts: Deposit accounts include transaction and non-transaction deposit accounts, for example: Checking/demand, savings, time/term deposit accounts, pensions. 'Active' closure of an account refers to cases where the closure is initiated at the request of the customer, and not due to inactivity or dormancy. !- Data requirements: List of unique deposit account holders (i.e. an individual  must be counted as one depositor irrespective of the number of deposit accounts held) who actively close any of their accounts over a specified period of time (e.g. quarter or year); Total number of unique depositors at the beginning of the specified period.</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Are there gender disparities in interest rate spreads offered to borrowers, and how do these differences vary across regions, income levels, and types of financial service providers? Do women or other gender groups consistently face higher lending rates relative to reference rates compared to men, potentially indicating unequal credit costs? How do interest rate spreads differ by loan type or sector, and are there gender patterns in these variations? Are financial service providers with higher gender diversity more likely to offer more equitable interest rate spreads across gender groups? How do differences in interest rate spreads impact borrowing behavior and access to credit for different gender groups?</t>
+          <t>How do active closure rates compare by gender? Which types of accounts are most frequently closed by each gender? How do FSPs rank in active account closures, and does this ranking change when analyzed by gender?</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -12250,12 +12241,12 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>Data privacy and protection, Operational risk</t>
+          <t>Quality, Fair treatment, Soundness, Stability</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -12272,30 +12263,30 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Savings, Credit</t>
         </is>
       </c>
       <c r="D220">
-        <v>35</v>
+        <v>267</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Open finance - % of customers that have given data sharing consent to FSPs</t>
+          <t>Interest rate spreads (loans)</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>% of all customers that have given consent to participate in the open finance scheme</t>
+          <t>Difference between the average lending rate and a reference rate (e.g. deposit rate or external reference rate)</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>The indicator shows how many customers have actively opted in to share their data via the open finance rails (e.g., with account information service providers or payment initiation service providers). A higher share signals trust, clear value propositions, and mature consent customer interfaces (mobile apps); a low or falling rate may reflect friction in UX or Strong Customer Authentication (SCA), poor messaging, or privacy concerns. It’s a headline adoption KPI for open finance schemes. !- Definitions and concepts: Explicit consent: a clear, affirmative action tied to a specific purpose with the ability to manage and withdraw. Active consent: valid as of the reference date (not expired/withdrawn). Open finance consenting customers (%) = [# unique customers with at least 1 open finance consent / # eligible customers] x 100%. Denominator options: all active retail/MSME customers (preferred) or customers with eligible accounts (state choice). Segment by purpose of consent, scope (accounts included), and channel (mobile/web). Duplication &amp; scope: a customer may hold multiple consents across TPPs; count unique customers, and compare with total count of consents. Lawful-basis nuance: exclude sharing done under contractual necessity or legal obligation (e.g., consultation to credit bureaus for a loan application)—this metric is about explicit consent only.</t>
+          <t>The interest-rate spread on loans captures the margin between the average contractual rate a lender charges borrowers and an external reference rate—typically the policy rate. It is a concise gauge of (i) lenders’ credit-risk pricing, (ii) competitive conditions in the lending market, and (iii) monetary-policy transmission. Wider spreads may reflect higher perceived borrower risk, limited competition, or funding-cost pressures; persistently narrow spreads can point to aggressive underwriting or excess liquidity that may undermine future asset quality. Tracked over time and across peer institutions, interest-rate spreads provide insights into credit-cycle turning points, profitability dynamics, and the effectiveness of monetary-policy signals reaching the real economy. !- Definitions and concepts:  Loan interest rate spread (simple): Average contractual loan rate minus Reference rate measured for new originations or for the stock of loans. Net lending spread: average loan rate minus average deposit rate, often used when policy benchmarks are volatile. Segmented spreads: calculated by product (e.g., mortgages, SMEs, credit cards). Non-interest charges: fees and cross-selling income are excluded; the true all-in lending margin may be higher.</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Are there gender disparities in data-sharing consent within the open finance scheme, including for MSMEs based on the ownership gender and low-value accounts? What types of accounts are more commonly subject to data-sharing consents? Which types of FSPs have a higher percentage of customers who have given data-sharing consent, and do these percentages vary by gender? If the information is available, what are the most common types and terms for these consents?</t>
+          <t>Are there gender disparities in interest rate spreads offered to borrowers, and how do these differences vary across regions, income levels, and types of financial service providers? Do women or other gender groups consistently face higher lending rates relative to reference rates compared to men, potentially indicating unequal credit costs? How do interest rate spreads differ by loan type or sector, and are there gender patterns in these variations? Are financial service providers with higher gender diversity more likely to offer more equitable interest rate spreads across gender groups? How do differences in interest rate spreads impact borrowing behavior and access to credit for different gender groups?</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -12305,17 +12296,17 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Consumer protection; Stability, safety and soundness</t>
+          <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Data privacy and protection, Reputational and legal risk</t>
+          <t>Data privacy and protection, Operational risk</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -12336,26 +12327,26 @@
         </is>
       </c>
       <c r="D221">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Open finance - API availability</t>
+          <t>Open finance - % of customers that have given data sharing consent to FSPs</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Average % of time APIs are available</t>
+          <t>% of all customers that have given consent to participate in the open finance scheme</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Shows the proportion of clock time that open finance endpoints can successfully serve requests. High availability is critical for data users such as third-party providers (TPPs) to deliver reliable account information and payment initiation; poor uptime breaks customer journeys, breaches SLAs/SLOs, and can trigger regulatory scrutiny in open finance schemes. !- Definitions and concepts: Availability (uptime):  time-weighted share of intervals in which an endpoint meets both reachability and success criteria. Scope — include account information service, payment initiation service, consent/token endpoints, and webhooks if they’re required for completion. Planned vs. unplanned:  exclude planned maintenance time; report maintenance windows separately. SLO period: availability is usually measured monthly/quarterly (e.g., 99.9% per calendar month), but preferably in shorter periods (e.g., weekly, daily). Granularity: overall availability, by endpoint family, region/zone, and time of day. Example indicator: Availability = 1 - [Downtime / Total scheduled time] where Downtime aggregates intervals failing the success criterion (5xx gateway/network timeouts, auth outages, or latency breaches). !- Limitations and considerations: Including latency SLOs will lower availability vs. status-only measurements. Publish thresholds.</t>
+          <t>The indicator shows how many customers have actively opted in to share their data via the open finance rails (e.g., with account information service providers or payment initiation service providers). A higher share signals trust, clear value propositions, and mature consent customer interfaces (mobile apps); a low or falling rate may reflect friction in UX or Strong Customer Authentication (SCA), poor messaging, or privacy concerns. It’s a headline adoption KPI for open finance schemes. !- Definitions and concepts: Explicit consent: a clear, affirmative action tied to a specific purpose with the ability to manage and withdraw. Active consent: valid as of the reference date (not expired/withdrawn). Open finance consenting customers (%) = [# unique customers with at least 1 open finance consent / # eligible customers] x 100%. Denominator options: all active retail/MSME customers (preferred) or customers with eligible accounts (state choice). Segment by purpose of consent, scope (accounts included), and channel (mobile/web). Duplication &amp; scope: a customer may hold multiple consents across TPPs; count unique customers, and compare with total count of consents. Lawful-basis nuance: exclude sharing done under contractual necessity or legal obligation (e.g., consultation to credit bureaus for a loan application)—this metric is about explicit consent only.</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Open finance performance will vary across FSPs for a range of reasons such as their current data architecture and other firm-specific aspects. The objective of looking into this indicator from a gender perspective is to identify whether FSPs that concentrate underserved, low-income women and women-led MSMEs also present poor open finance performance. This indicator can be analyzed together with other open finance performance indicators (Unsuccessful API calls, API response time), and open finance adoption indicators (% customer that have given consent, payment initiation transactions)</t>
+          <t>Are there gender disparities in data-sharing consent within the open finance scheme, including for MSMEs based on the ownership gender and low-value accounts? What types of accounts are more commonly subject to data-sharing consents? Which types of FSPs have a higher percentage of customers who have given data-sharing consent, and do these percentages vary by gender? If the information is available, what are the most common types and terms for these consents?</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -12365,12 +12356,12 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
+          <t>Consumer protection; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Quality, Suitability, Operational risk</t>
+          <t>Data privacy and protection, Reputational and legal risk</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -12396,21 +12387,21 @@
         </is>
       </c>
       <c r="D222">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Open finance - API error rate</t>
+          <t>Open finance - API availability</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>% of all API calls that are unsuccessful</t>
+          <t>Average % of time APIs are available</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>This indicator tracks the reliability of open-finance interfaces by showing what share of API requests do not complete successfully due to errors. It is a key API performance indicator monitored by financial authorities implementing open finance. High failure rates degrade customer journeys (consent, data retrieval, payment initiation), inflate support costs, and can breach SLA/SLO commitments. !- Definitions and concepts: API call (request): one HTTP request to a documented endpoint, for example: Account Information Services (AIS) data, Payment Initiatiion Services (PIS) payment, consent, token, webhook, etc. Unsuccessful call: define as per local regulation. This indicator can be collected segmented by types of errors, to be defined as per local regulation (e.g., gateway/network timeouts, invalid/expired token/consent, error in validation, authentication failures. It should also be segmented by type of endpoint, as per local categorization (e.g., account information request, payment initiation request, other). Example indicator: [# of errors  /  # total API calls] x 100%.</t>
+          <t>Shows the proportion of clock time that open finance endpoints can successfully serve requests. High availability is critical for data users such as third-party providers (TPPs) to deliver reliable account information and payment initiation; poor uptime breaks customer journeys, breaches SLAs/SLOs, and can trigger regulatory scrutiny in open finance schemes. !- Definitions and concepts: Availability (uptime):  time-weighted share of intervals in which an endpoint meets both reachability and success criteria. Scope — include account information service, payment initiation service, consent/token endpoints, and webhooks if they’re required for completion. Planned vs. unplanned:  exclude planned maintenance time; report maintenance windows separately. SLO period: availability is usually measured monthly/quarterly (e.g., 99.9% per calendar month), but preferably in shorter periods (e.g., weekly, daily). Granularity: overall availability, by endpoint family, region/zone, and time of day. Example indicator: Availability = 1 - [Downtime / Total scheduled time] where Downtime aggregates intervals failing the success criterion (5xx gateway/network timeouts, auth outages, or latency breaches). !- Limitations and considerations: Including latency SLOs will lower availability vs. status-only measurements. Publish thresholds.</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -12430,7 +12421,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Quality, Operational risk</t>
+          <t>Quality, Suitability, Operational risk</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -12456,21 +12447,21 @@
         </is>
       </c>
       <c r="D223">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Open finance - API response time</t>
+          <t>Open finance - API error rate</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Average API response time</t>
+          <t>% of all API calls that are unsuccessful</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Shows how quickly open-finance endpoints answer requests. Faster responses improve user experience during consent, account-information retrieval, and payment initiation, reducing frictions and drop-offs. Response time is a core performance KPI that complements availability and error rate. !- Definitions and concepts: Response time (latency): elapsed time between request start and final byte received (client-observed) or gateway in → gateway out (server-observed). Track both when possible. Averages vs. tails: report p50/median, p95, p99, and the mean; tails (p95/p99) best reflect user pain. Track both. Granularity: report by endpoint family (types of APIs), potentially segmented into priority levels (see https://www.cdr.gov.au/performance). Units &amp; window: milliseconds, by calendar month (preferably shorter SLO period, such as weekly or daily).</t>
+          <t>This indicator tracks the reliability of open-finance interfaces by showing what share of API requests do not complete successfully due to errors. It is a key API performance indicator monitored by financial authorities implementing open finance. High failure rates degrade customer journeys (consent, data retrieval, payment initiation), inflate support costs, and can breach SLA/SLO commitments. !- Definitions and concepts: API call (request): one HTTP request to a documented endpoint, for example: Account Information Services (AIS) data, Payment Initiatiion Services (PIS) payment, consent, token, webhook, etc. Unsuccessful call: define as per local regulation. This indicator can be collected segmented by types of errors, to be defined as per local regulation (e.g., gateway/network timeouts, invalid/expired token/consent, error in validation, authentication failures. It should also be segmented by type of endpoint, as per local categorization (e.g., account information request, payment initiation request, other). Example indicator: [# of errors  /  # total API calls] x 100%.</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -12516,31 +12507,41 @@
         </is>
       </c>
       <c r="D224">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Open finance - Payment initiation transactions</t>
+          <t>Open finance - API response time</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Number of payment initiation transactions conducted in the open finance scheme</t>
+          <t>Average API response time</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Counts how many account-to-account (A2A) payment orders were successfully initiated via open-finance rails in the period. It’s a core adoption and usage KPI for Payment Initiation Services (PIS): more transactions imply growing merchant and P2P acceptance of openb finance, customer trust, and TPP–bank interoperability. !- Definitions and concepts: Payment initiation transaction (PIT): a payment order created via an authorized PISP/TPP and accepted by the ASPSP (account holder) for processing. Companion counts: Failed payment initiation transactions. Refunds/returns/chargebacks tracked separately. Sub-types: single immediate payments, scheduled payments, recurring/VRP (variable recurring payments), instant vs. ACH/batch. !- Data requirements: Total number of successful payment initiation transactions. !- Limitations and considerations: Duplicates: avoid double counting by using operation IDs.</t>
+          <t>Shows how quickly open-finance endpoints answer requests. Faster responses improve user experience during consent, account-information retrieval, and payment initiation, reducing frictions and drop-offs. Response time is a core performance KPI that complements availability and error rate. !- Definitions and concepts: Response time (latency): elapsed time between request start and final byte received (client-observed) or gateway in → gateway out (server-observed). Track both when possible. Averages vs. tails: report p50/median, p95, p99, and the mean; tails (p95/p99) best reflect user pain. Track both. Granularity: report by endpoint family (types of APIs), potentially segmented into priority levels (see https://www.cdr.gov.au/performance). Units &amp; window: milliseconds, by calendar month (preferably shorter SLO period, such as weekly or daily).</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the adoption of payment initiation transactions within the open finance scheme, including for MSMEs by the owner's gender? Do FSPs with higher levels of gender diversity tend to have a larger share of diverse customers conducting payment initiation transactions?</t>
+          <t>Open finance performance will vary across FSPs for a range of reasons such as their current data architecture and other firm-specific aspects. The objective of looking into this indicator from a gender perspective is to identify whether FSPs that concentrate underserved, low-income women and women-led MSMEs also present poor open finance performance. This indicator can be analyzed together with other open finance performance indicators (Unsuccessful API calls, API response time), and open finance adoption indicators (% customer that have given consent, payment initiation transactions)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Quality, Operational risk</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -12566,107 +12567,97 @@
         </is>
       </c>
       <c r="D225">
+        <v>68</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Open finance - Payment initiation transactions</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Number of payment initiation transactions conducted in the open finance scheme</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Counts how many account-to-account (A2A) payment orders were successfully initiated via open-finance rails in the period. It’s a core adoption and usage KPI for Payment Initiation Services (PIS): more transactions imply growing merchant and P2P acceptance of openb finance, customer trust, and TPP–bank interoperability. !- Definitions and concepts: Payment initiation transaction (PIT): a payment order created via an authorized PISP/TPP and accepted by the ASPSP (account holder) for processing. Companion counts: Failed payment initiation transactions. Refunds/returns/chargebacks tracked separately. Sub-types: single immediate payments, scheduled payments, recurring/VRP (variable recurring payments), instant vs. ACH/batch. !- Data requirements: Total number of successful payment initiation transactions. !- Limitations and considerations: Duplicates: avoid double counting by using operation IDs.</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in the adoption of payment initiation transactions within the open finance scheme, including for MSMEs by the owner's gender? Do FSPs with higher levels of gender diversity tend to have a larger share of diverse customers conducting payment initiation transactions?</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Market development</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D226">
         <v>150</v>
       </c>
-      <c r="E225" t="inlineStr">
+      <c r="E226" t="inlineStr">
         <is>
           <t>Bundled product uptake rate</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
+      <c r="F226" t="inlineStr">
         <is>
           <t>% of customers taking up additional products during onboarding</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
+      <c r="G226" t="inlineStr">
         <is>
           <t>Measures the percentage of customers who acquire one or more additional financial products or services at the time of onboarding (i.e., when opening their primary account or initiating a new relationship with a financial service provider). These additional products may include insurance, savings, credit, or investment add-ons linked to the initial product. Captures the prevalence of product bundling and cross-selling practices during customer onboarding. It provides insight into market behavior, product integration, and the extent to which customers are being offered or encouraged to take multiple products simultaneously. Monitoring product bundling helps regulators and providers:
 Assess consumer choice and informed consent during onboarding; Identify potential coercive or mis-selling practices; Evaluate financial literacy and customer understanding of product combinations; Analyze the integration of complementary services (e.g., savings plus micro-insurance); Support efforts to ensure responsible cross-selling and transparent disclosure. Bundling can enhance value and convenience when responsibly designed, but may also raise conduct or affordability risks if customers are not well-informed. High bundling rates may reflect integrated product offerings or effective cross-selling, but warrant review for consent and suitability. Low rates may indicate limited product integration or narrow customer engagement at onboarding. Trends can reveal shifts in market strategy, regulatory compliance, or consumer protection outcomes. !- Definitions and concepts: Bundled product: A package of two or more financial services offered together at onboarding (e.g., transaction account + insurance or credit line). Onboarding: The process of establishing a new customer relationship, including account opening and KYC verification. Cross-selling: Offering additional, often related, financial products to a new or existing customer. Informed consent: The customer’s clear understanding and voluntary acceptance of each product taken. !- Data requirements: Bundled product uptake rate (%)=Number of customers who acquired ≥1 additional product at onboarding​/Total number of new customers onboarded. Administrative or CRM data from financial institutions on new customer onboarding and product uptake. Disaggregation by institution type, customer segment (individual, SME), region, and product category. !- Derivable indicators: Average number of products per new customer; Distribution of additional products (e.g., % taking insurance, credit, savings add-ons)</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
+      <c r="H226" t="inlineStr">
         <is>
           <t>How many products does each gender take up on average during the onboarding stage, and how do these numbers compare? What are the gender disparities in the likelihood of adopting multiple products? Which FSPs stand out in multi-product onboarding, and does their ranking change when analyzed by gender? Note: Active usage of products should also be assessed for multiple products taken up during onboarding.</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr">
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
         <is>
           <t>Uptake</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr">
+      <c r="L226" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Market development</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D226">
-        <v>32</v>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>Product portability requests</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>Number of product portability requests</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>Measures the volume of formal requests initiated by customers to transfer their financial product or relationship from one provider to another within a specific period. This includes activities like switching a mortgage, transferring a loan to a new lender, or moving a current account to a new bank. This indicator is a gauge of market competition, consumer empowerment, and potential frictions or risks within the financial system. Very low switching rates can indicate significant barriers to entry or anti-competitive behavior, suggesting that customers are "trapped" with their current providers due to high exit fees, complex processes, or a lack of clear alternatives. This indicator is even more important in countries where product switching platforms or open finance exist and whose effectiveness should be monitored. A companion indicator to the total number of product switch requests is the total number of switches effected in the period, in comparison to the total number of requests. Another companion indicator is the total number of requests (or successful requests) relative to the number of active customers. The central bank of Brazil has calculated the number of loan portability requests relative to the number of loans with an interest rate above the market average rates, using the number of loans with above-market interest rates as a proxy for the untapped potential of the portability system. https://www.bcb.gov.br/content/publicacoes/Documents/reb/boxesreb2020/boxe_2_evolucao_portabilidade_credito_brasil.pdf</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Are there customer gender, income and location disparities in account and loan portability or FSP switching requests? Are FSPs with higher levels of gender diversity more likely to receive portability or switching requests or be the destination FSP (rather than the origin) for such requests?</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>Usage, Suitability</t>
-        </is>
-      </c>
-      <c r="L226" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
         </is>
       </c>
     </row>
@@ -12687,44 +12678,104 @@
         </is>
       </c>
       <c r="D227">
+        <v>32</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Product portability requests</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Number of product portability requests</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Measures the volume of formal requests initiated by customers to transfer their financial product or relationship from one provider to another within a specific period. This includes activities like switching a mortgage, transferring a loan to a new lender, or moving a current account to a new bank. This indicator is a gauge of market competition, consumer empowerment, and potential frictions or risks within the financial system. Very low switching rates can indicate significant barriers to entry or anti-competitive behavior, suggesting that customers are "trapped" with their current providers due to high exit fees, complex processes, or a lack of clear alternatives. This indicator is even more important in countries where product switching platforms or open finance exist and whose effectiveness should be monitored. A companion indicator to the total number of product switch requests is the total number of switches effected in the period, in comparison to the total number of requests. Another companion indicator is the total number of requests (or successful requests) relative to the number of active customers. The central bank of Brazil has calculated the number of loan portability requests relative to the number of loans with an interest rate above the market average rates, using the number of loans with above-market interest rates as a proxy for the untapped potential of the portability system. https://www.bcb.gov.br/content/publicacoes/Documents/reb/boxesreb2020/boxe_2_evolucao_portabilidade_credito_brasil.pdf</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Are there customer gender, income and location disparities in account and loan portability or FSP switching requests? Are FSPs with higher levels of gender diversity more likely to receive portability or switching requests or be the destination FSP (rather than the origin) for such requests?</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Usage, Suitability</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Market development</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D228">
         <v>33</v>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="E228" t="inlineStr">
         <is>
           <t>Rejected product portability requests</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
+      <c r="F228" t="inlineStr">
         <is>
           <t>% of all product portability requests that are rejected</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
+      <c r="G228" t="inlineStr">
         <is>
           <t>Measures the volume of formal portability requests initiated by customers to transfer their financial product or relationship from one provider to another within a specific period, which are rejected by the financial service provider. Product portability includes activities like switching a mortgage, transferring a loan to a new lender, or moving a current account to a new bank. This indicator is a gauge of market competition, consumer empowerment, and potential frictions or risks within the financial system. Very low switching rates can indicate significant barriers to entry or anti-competitive behavior, suggesting that customers are "trapped" with their current providers due to high exit fees, complex processes, or a lack of clear alternatives. This indicator is even more important in countries where product switching platforms or open finance exist and whose effectiveness should be monitored. When providers reject too many portability requests, this could be a sign of anti-competitive practices. This indicator should be analyzed together with the indicator on the total number of portability requests.</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
+      <c r="H228" t="inlineStr">
         <is>
           <t>Are there customer gender, income, and location disparities in the approval of portability requests? Are FSPs with higher levels of gender diversity more likely to approve portability requests?</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
+      <c r="K228" t="inlineStr">
         <is>
           <t>Usage, Suitability</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr">
+      <c r="L228" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
         </is>

--- a/www/LENS_INDICATORS_DB.xlsx
+++ b/www/LENS_INDICATORS_DB.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L228"/>
+  <dimension ref="A1:L226"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -655,16 +655,6 @@
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Channel type; Financial service provider (FSP) type</t>
@@ -1682,12 +1672,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Consumer protection; Market development</t>
+          <t>Market development</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Impact, Capital markets development</t>
+          <t>Capital markets development</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1743,12 +1733,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Consumer protection; Market development</t>
+          <t>Market development</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Impact, Capital markets development</t>
+          <t>Capital markets development</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2688,16 +2678,6 @@
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
@@ -2798,16 +2778,6 @@
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
@@ -3053,16 +3023,6 @@
           <t>Are there gender disparities in the likelihood of engaging in e-commerce transactions, including for MSMEs based on the gender of the owner? Do transaction patterns—such as frequency and average ticket size—differ by gender, and how do these vary across income groups, age brackets, and locations? Are e-commerce transactions concentrated within specific financial service providers (FSPs) or market segments, and does this concentration reflect gender imbalances? Could differences in transaction volumes by gender indicate limited access to e-commerce payment channels or the unsuitability of available solutions for certain groups? Are FSPs with higher levels of gender diversity more likely to support inclusive e-commerce participation across genders?</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
@@ -3299,16 +3259,6 @@
           <t>What are the gender dynamics in remittance transactions? Is there a gender that is the predominant recipient of international remittances? What are the gender differences in the size and frequency of remittances? Are remittances concentrated in certain geographical areas, FSP types, and account types? Which channels are mostly used to receive remittances? Are these areas considered low-income locations or locations with low cash access point density? Comparing with indicators on transaction channel locations, how do they compare with remittance reception? Are remittance recipients particularly underserved by access points? Is there any correlation between the gender of recipients and FSP gender diversity? Which countries originate the most remittances to low-income locations and populations? Do these coincide with countries with higher remittance costs?</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Other; Consumer protection</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Statistics and research, Impact</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Channel type; Transaction type</t>
@@ -3354,16 +3304,6 @@
           <t>What are the gender dynamics in remittance transactions? Is there a gender that is the predominant recipient of international remittances? What are the gender differences in the size and frequency of remittances? Are remittances concentrated in certain geographical areas, FSP types, and account types? Which channels are mostly used to receive remittances? Are these areas considered low-income locations or locations with low cash access point density? Comparing with indicators on transaction channel locations, how do they compare with remittance reception? Are remittance recipients particularly underserved by access points? Is there any correlation between the gender of recipients and FSP gender diversity? Which countries originate the most remittances to low-income locations and populations? Do these coincide with countries with higher remittance costs?</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Other; Consumer protection</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Statistics and research, Impact</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Channel type; Transaction type</t>
@@ -3409,16 +3349,6 @@
           <t>How do genders differ in how much and how often they transact through different channels (cash, ATM, digital, agents, mobile, etc.), by transaction value and frequency? Are there gender differences in the choice of channels associated with high‐value vs low‐value transactions? How have channel usage patterns for different genders evolved over time, especially for younger, lower‐income, or rural women? Do providers who are more gender‐inclusive tend to offer or promote more equitable access and usage across channels?</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Financial service provider (FSP) type; Product type; Transaction type</t>
@@ -3464,16 +3394,6 @@
           <t>How do genders differ in how much and how often they transact through different channels (cash, ATM, digital, agents, mobile, etc.)? How have channel usage patterns for different genders evolved over time, especially for younger, lower‐income, or rural women? Do providers who are more gender‐inclusive tend to offer or promote more equitable access and usage across channels?</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Financial service provider (FSP) type; Product type; Transaction type</t>
@@ -3744,16 +3664,6 @@
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
@@ -4186,12 +4096,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Total outstanding balances in active deposit accounts</t>
+          <t>Total balances in active deposit accounts</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Measures the total outstanding balance in all active deposit accounts at the end of the reporting period. It represents the aggregate value of deposits held in accounts that are actively used, distinguishing them from dormant or inactive balances. Captures the volume of mobilized deposits that are linked to active financial relationships, providing insight into financial depth, liquidity, and the stability of deposit funding within the banking system. Tracking the balance of active accounts helps regulators and analysts: Evaluate effective deposit mobilization and financial intermediation; Identify the share of deposits that are transactionally relevant versus idle; Monitor liquidity risks and customer engagement in deposit markets; Assess financial inclusion quality and trust in the formal system. Higher balances indicate stronger deposit mobilization and customer trust in institutions. Declining balances may reflect economic stress, withdrawals, or shift toward alternative financial instruments. Stable ratios of active to total balances indicate healthy engagement and liquidity management. !- Definitions and concepts: Active deposit account: An account with at least one transaction or a positive balance during the reporting period. Outstanding balance: The total value of deposits held in those accounts as of the reference date. !- Derivable indicators: Average balance per active account = (Total active deposit balances / Number of active deposit accounts); Weighted deposit activity rate = (Active deposit balances / Total deposit balances) × 100</t>
+          <t>Measures the total balance in all active deposit accounts at the end of the reporting period. It represents the aggregate value of deposits held in accounts that are actively used, distinguishing them from dormant or inactive balances. Captures the volume of mobilized deposits that are linked to active financial relationships, providing insight into financial depth, liquidity, and the stability of deposit funding within the banking system. Tracking the balance of active accounts helps regulators and analysts: Evaluate effective deposit mobilization and financial intermediation; Identify the share of deposits that are transactionally relevant versus idle; Monitor liquidity risks and customer engagement in deposit markets; Assess financial inclusion quality and trust in the formal system. Higher balances indicate stronger deposit mobilization and customer trust in institutions. Declining balances may reflect economic stress, withdrawals, or shift toward alternative financial instruments. Stable ratios of active to total balances indicate healthy engagement and liquidity management. !- Definitions and concepts: Active deposit account: An account with at least one transaction or a positive balance during the reporting period. Balance: The total value of deposits held in those accounts as of the reference date. !- Derivable indicators: Average balance per active account = (Total active deposit balances / Number of active deposit accounts); Weighted deposit activity rate = (Active deposit balances / Total deposit balances) × 100</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4523,17 +4433,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>E-money accounts (outstanding balance)</t>
+          <t>E-money accounts (balance)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Outstanding balances in e-money accounts</t>
+          <t>Balances in e-money accounts</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Measures the total outstanding value of e-money issued and held in customer accounts at a given point in time. It represents the monetary value of customer funds stored electronically and redeemable on demand. Captures the stock of e-money in circulation, serving as an indicator of digital liquidity, trust in electronic value storage, and systemic importance of e-money issuers within the payments landscape. The total e-money float helps supervisors monitor: System-wide liquidity exposure of e-money issuers, customer fund safeguarding and segregation compliance, the role of e-money in monetary aggregates and financial stability. It is also a key input to assessing digital financial inclusion and payment ecosystem growth. Higher balances indicate increased usage and confidence in e-money as a store of value. Rapid increases may reflect accelerating digital adoption or limited conversion to cash; Declines could signal withdrawals or regulatory tightening. !- Definitions and concepts: E-money is prepaid value stored electronically, which represents a liability of the e-money issuer (a bank, an e-money institution or any other entity authorised or allowed to issue e-money in the local jurisdiction) and which is denominated in a currency backed by an authority. Outstanding balance: The monetary value of all e-money not yet redeemed or withdrawn by customers. E-money float: The total value of customer funds corresponding to issued e-money liabilities, typically held in trust or custodial accounts with regulated financial institutions. !- Data requirements: Sum of all outstanding e-money balances across customer accounts at the end of the reference period, based on account-level data from licensed e-money issuers with additional disaggregation for segmentation analysis (e.g. age, gender, location of customer). !- Derivable indicators: Average balance per account = (Total e-money balances / Number of e-money accounts); Average balance per account holder = (Total e-money balances / Number of e-money account holders).</t>
+          <t>Measures the total value (balance) of e-money issued and held in customer accounts at a given point in time. It represents the monetary value of customer funds stored electronically and redeemable on demand. Captures the stock of e-money in circulation, serving as an indicator of digital liquidity, trust in electronic value storage, and systemic importance of e-money issuers within the payments landscape. The total e-money float helps supervisors monitor: System-wide liquidity exposure of e-money issuers, customer fund safeguarding and segregation compliance, the role of e-money in monetary aggregates and financial stability. It is also a key input to assessing digital financial inclusion and payment ecosystem growth. Higher balances indicate increased usage and confidence in e-money as a store of value. Rapid increases may reflect accelerating digital adoption or limited conversion to cash; Declines could signal withdrawals or regulatory tightening. !- Definitions and concepts: E-money is prepaid value stored electronically, which represents a liability of the e-money issuer (a bank, an e-money institution or any other entity authorised or allowed to issue e-money in the local jurisdiction) and which is denominated in a currency backed by an authority. Balance: The monetary value of all e-money not yet redeemed or withdrawn by customers. E-money float: The total value of customer funds corresponding to issued e-money liabilities, typically held in trust or custodial accounts with regulated financial institutions. !- Data requirements: Sum of all e-money balances across customer accounts at the end of the reference period, based on account-level data from licensed e-money issuers with additional disaggregation for segmentation analysis (e.g. age, gender, location of customer). !- Derivable indicators: Average balance per account = (Total e-money balances / Number of e-money accounts); Average balance per account holder = (Total e-money balances / Number of e-money account holders).</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4569,17 +4479,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Mobile money accounts (outstanding balance)</t>
+          <t>Mobile money accounts (balance)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Outstanding balances in mobile money accounts</t>
+          <t>Balances in mobile money accounts</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Measures the total outstanding value of mobile-money issued and held in customer accounts at a given point in time. It represents the monetary value of customer funds stored electronically and redeemable on demand. Captures the stock of mobile money in circulation, serving as an indicator of digital liquidity, trust in electronic value storage, and systemic importance of mobile money issuers within the payments landscape. The total mobile money float helps supervisors monitor: System-wide liquidity exposure of mobile money issuers, customer fund safeguarding and segregation compliance, the role of mobile money in monetary aggregates and financial stability. It is also a key input to assessing digital financial inclusion and payment ecosystem growth. Higher balances indicate increased usage and confidence in mobile money as a store of value. Rapid increases may reflect accelerating digital adoption or limited conversion to cash; Declines could signal withdrawals or regulatory tightening. !- Definitions and concepts: Mobile money accounts are a type of e-money account. Mobile money refers to a form of e-money where funds are stored in a mobile money account linked to a phone number accessible through a mobile phone, or any SIM-enabled device, and facilitated by a network of mobile money agents (IMF FAS). It is a financial service offered to its clients by a mobile network operator or another entity that partners with mobile network operators, independent of the traditional banking network. Outstanding balance: The monetary value of all mobile money not yet redeemed or withdrawn by customers. !- Data requirements: Sum of all outstanding mobile money balances across customer accounts at the end of the reference period, based on account-level data from licensed mobile money issuers with additional disaggregation for segmentation analysis (e.g. age, gender, location of customer). !- Derivable indicators: Average balance per account = (Total mobile money balances / Number of mobile money accounts); Average balance per account holder = (Total mobile money balances / Number of mobile money account holders).</t>
+          <t>Measures the total outstanding value of mobile-money issued and held in customer accounts at a given point in time. It represents the monetary value of customer funds stored electronically and redeemable on demand. Captures the stock of mobile money in circulation, serving as an indicator of digital liquidity, trust in electronic value storage, and systemic importance of mobile money issuers within the payments landscape. The total mobile money float helps supervisors monitor: System-wide liquidity exposure of mobile money issuers, customer fund safeguarding and segregation compliance, the role of mobile money in monetary aggregates and financial stability. It is also a key input to assessing digital financial inclusion and payment ecosystem growth. Higher balances indicate increased usage and confidence in mobile money as a store of value. Rapid increases may reflect accelerating digital adoption or limited conversion to cash; Declines could signal withdrawals or regulatory tightening. !- Definitions and concepts: Mobile money accounts are a type of e-money account. Mobile money refers to a form of e-money where funds are stored in a mobile money account linked to a phone number accessible through a mobile phone, or any SIM-enabled device, and facilitated by a network of mobile money agents (IMF FAS). It is a financial service offered to its clients by a mobile network operator or another entity that partners with mobile network operators, independent of the traditional banking network. Outstanding balance: The monetary value of all mobile money not yet redeemed or withdrawn by customers. !- Data requirements: Sum of all mobile money balances across customer accounts at the end of the reference period, based on account-level data from licensed mobile money issuers with additional disaggregation for segmentation analysis (e.g. age, gender, location of customer). !- Derivable indicators: Average balance per account = (Total mobile money balances / Number of mobile money accounts); Average balance per account holder = (Total mobile money balances / Number of mobile money account holders).</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4590,7 +4500,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Customer type; Account type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Account type</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4609,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4742,7 +4652,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Uptake (account ownership)</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -4832,17 +4742,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Investment accounts (outstanding balance)</t>
+          <t>Investment accounts (balance)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Outstanding balance in investment accounts</t>
+          <t>Balance in investment accounts</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Measures the total value of financial assets held by individuals in all investment accounts at the end of the reference period. Captures the aggregate stock of investment wealth intermediated through formal financial channels, reflecting financial market depth, asset accumulation, and portfolio diversification. The outstanding balance in investment accounts provides insights into: The size and composition of retail investments; Trends in wealth accumulation and capital-market development; The contribution of investment activity to domestic financial stability and savings mobilization. For supervisory analysis, it informs monitoring of asset-price exposure, systemic linkages, and investor concentration. Higher values indicate growing household and institutional asset holdings and deepening financial markets. Volatility may reflect market valuation changes or shifts in investor behavior. Persistent growth signals increasing intermediation through formal channels. !- Definitions and concepts: Investment accounts: An account used to hold, trade, or manage financial assets through a licensed intermediary and can include securities trading accounts, collective investment scheme accounts, mutual fund accounts, retirement investment sub-accounts, and other regulated investment products. They can be held in banks, brokerage firms, asset managers, investment platforms and other financial institutions. They are different from deposit accounts, as their returns are not guaranteed and their value can fluctuate. Outstanding balance (investment accounts): The total market value of financial assets held in investment accounts at the reporting date, net of withdrawals or redemptions. Financial assets: Tradable or redeemable instruments such as equities, bonds, units in mutual funds, ETFs, or money-market funds. !- Data requirements: Sum of all balanes in investment accounts (market value of assets held) at the end of the reference period. Aggregated balance-sheet or custodial data from brokers, asset managers, fund administrators, and investment platforms. Disaggregation by product type (equities, fixed income, mutual funds, etc.). !- Derivable indicators: Average investment account balance = (Total investment account balances / Number of investment accounts)</t>
+          <t>Measures the total value (balance) of financial assets held by individuals in all investment accounts at the end of the reference period. Captures the aggregate stock of investment wealth intermediated through formal financial channels, reflecting financial market depth, asset accumulation, and portfolio diversification. The balance in investment accounts provides insights into: The size and composition of retail investments; Trends in wealth accumulation and capital-market development; The contribution of investment activity to domestic financial stability and savings mobilization. For supervisory analysis, it informs monitoring of asset-price exposure, systemic linkages, and investor concentration. Higher values indicate growing household and institutional asset holdings and deepening financial markets. Volatility may reflect market valuation changes or shifts in investor behavior. Persistent growth signals increasing intermediation through formal channels. !- Definitions and concepts: Investment accounts: An account used to hold, trade, or manage financial assets through a licensed intermediary and can include securities trading accounts, collective investment scheme accounts, mutual fund accounts, retirement investment sub-accounts, and other regulated investment products. They can be held in banks, brokerage firms, asset managers, investment platforms and other financial institutions. They are different from deposit accounts, as their returns are not guaranteed and their value can fluctuate. Balance (investment accounts): The total market value of financial assets held in investment accounts at the reporting date, net of withdrawals or redemptions. Financial assets: Tradable or redeemable instruments such as equities, bonds, units in mutual funds, ETFs, or money-market funds. !- Data requirements: Sum of all balances in investment accounts (market value of assets held) at the end of the reference period. Aggregated balance-sheet or custodial data from brokers, asset managers, fund administrators, and investment platforms. Disaggregation by product type (equities, fixed income, mutual funds, etc.). !- Derivable indicators: Average investment account balance = (Total investment account balances / Number of investment accounts)</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4857,17 +4767,17 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Consumer protection; Market development</t>
+          <t>Market development</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Impact, Capital markets development</t>
+          <t>Capital markets development</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Customer type; Account type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Account type</t>
         </is>
       </c>
     </row>
@@ -4912,12 +4822,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Consumer protection; Stability, safety and soundness</t>
+          <t>Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Impact, Operational risk</t>
+          <t>Operational risk</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5044,7 +4954,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>Usage, Outcomes</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5087,7 +4997,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Suitability,</t>
+          <t>Suitability, Stability</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5262,12 +5172,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Other; Consumer protection</t>
+          <t>Consumer protection</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Statistics and research, Suitability</t>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5322,12 +5232,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Other; Consumer protection</t>
+          <t>Consumer protection</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Statistics and research, Quality</t>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -5438,16 +5348,6 @@
       <c r="I96" t="inlineStr">
         <is>
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Statistics and research</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -5763,7 +5663,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Fair treatment</t>
+          <t>Fair treatment, Complaints handling</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -5823,7 +5723,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Fair treatment</t>
+          <t>Fair treatment, Complaints handling</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -5840,35 +5740,35 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Outcomes</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Savings</t>
         </is>
       </c>
       <c r="D104">
-        <v>322</v>
+        <v>164</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Fraud prevalence in complaints</t>
+          <t>Early extraction of term deposits</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Portion and volume of complaints received by providers, regulators, and ombuds that are fraud-related.</t>
+          <t>% of term deposit account holders who extracted funds before reaching maturity</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tracks how much of the complaint landscape is driven by fraud—both the count (volume) and the share (portion) of total complaints. Rising prevalence of frauds signals elevated customer harm, control weaknesses (KYC/AML, authentication, data security), or new attack vectors (social engineering). It helps guide supervision, consumer protection responses, reimbursement policies, and investment in fraud controls. !- Definitions and concepts: Fraud-related complaint: a case alleging unauthorised or deceptive activity resulting in loss or attempted loss—e.g., account takeover, card-not-present, phishing/SMiShing, SIM-swap, mule accounts, synthetic identity, merchant fraud, insider abuse, and authorised push payment (APP) scams. Volume: number of fraud-related complaints received in the period. Share: [# of fraud complaints / # of all complaints] x 100%. Intensity companions: fraud complaints per 1,000 customers or per 1 million transactions, value lens using claimed or confirmed loss amounts. Outcome cuts: upheld rate, reimbursement rate, median loss, time-to-resolution. A standard taxonomy for fraud types is needed, including the differentiation between fraud and disputed transaction. !- Limitations and considerations:  Under-reporting: many victims never complain or only contact the bank—triangulate with dispute/chargeback data and incident logs.</t>
+          <t>A measure of unplanned demand for liquidity, potentially indicating financial distress. !- Definitions and concepts: Term deposit accounts (such as certificates of deposit) are interest-bearing accounts whose funds can be withdrawn (without penalty) at the maturity date. !- Data requirements: Transaction level information or system flag that can produce a list of term deposit accounts with an early, full extraction of funds over a specific period. To the extent that for a given reporting institution customers can open more than one term-deposit account, unique customer IDs can de-duplicate account-level records to produce a list of unique term-deposit customers that extracted funds before maturity. In addition, the total number of term-deposit accounts (or unique account-holders) is required to compute the percentage.</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Are there gender differences in the proportion of fraud-related complaints submitted to providers, regulators, or ombuds services?  Do individuals of different genders tend to report different types of fraud, such as identity theft, phishing, or agent misconduct, and are specific delivery channels more commonly associated with these complaints? Is the volume of fraud-related complaints disproportionately high among certain gender groups when compared to their levels of account ownership or usage? Do complaint resolution rates and timeframes differ by gender across various FSP or reporting channels?</t>
+          <t>Are there gender disparities in savings discipline, particularly in whether term deposits are retained until maturity or withdrawn early? Is there evidence that term deposit savings serve as coping mechanisms differently by gender? How do term deposit savings behaviors differ among more vulnerable or underserved individuals by gender?</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5876,19 +5776,9 @@
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>Fair treatment</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints resolution outcome; Complaints resolution time</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -5909,26 +5799,26 @@
         </is>
       </c>
       <c r="D105">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Early extraction of term deposits</t>
+          <t>Resumption of savings after early extraction from term deposits</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>% of term deposit account holders who extracted funds before reaching maturity</t>
+          <t>% of term deposit account holders who resumed savings after extracting funds prior to maturity</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>A measure of unplanned demand for liquidity, potentially indicating financial distress. !- Definitions and concepts: Term deposit accounts (such as certificates of deposit) are interest-bearing accounts whose funds can be withdrawn (without penalty) at the maturity date. !- Data requirements: Transaction level information or system flag that can produce a list of term deposit accounts with an early, full extraction of funds over a specific period. To the extent that for a given reporting institution customers can open more than one term-deposit account, unique customer IDs can de-duplicate account-level records to produce a list of unique term-deposit customers that extracted funds before maturity. In addition, the total number of term-deposit accounts (or unique account-holders) is required to compute the percentage.</t>
+          <t>A measure of financial resilience or the ability to bounce back after an unplanned use of committed resources.  !- Definitions and concepts: Term deposit accounts (such as certificates of deposit) are interest-bearing accounts whose funds can be withdrawn (without penalty) at the maturity date. !- Data requirements: Transaction level information or system flag that can produce a list of term deposit accounts that had an early, full extraction of funds over a specific period, and of those, the number that made subsquent repleneshing deposits to the account. To the extent that for a given reporting institution customers can open more than one term-deposit account, unique customer IDs can de-duplicate account-level records to produce a list of unique term-deposit customers that extracted funds before maturity. In addition, the total number of term-deposit accounts (or unique account-holders) is required as the denominator to compute the percentage.</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Are there gender disparities in savings discipline, particularly in whether term deposits are retained until maturity or withdrawn early? Is there evidence that term deposit savings serve as coping mechanisms differently by gender? How do term deposit savings behaviors differ among more vulnerable or underserved individuals by gender?</t>
+          <t>Are there gender disparities in the likelihood of resuming term deposit savings after withdrawing them before maturity? What are the characteristics of individuals who resume term deposit savings by gender? Which FSPs rank highest and lowest in the resumption of term deposit savings, and does this ranking change when analyzed by gender?</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5959,26 +5849,26 @@
         </is>
       </c>
       <c r="D106">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Resumption of savings after early extraction from term deposits</t>
+          <t>Deposit and payment account holders who also hold term deposits</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>% of term deposit account holders who resumed savings after extracting funds prior to maturity</t>
+          <t>% of deposit and payment account holders who also have term deposits</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>A measure of financial resilience or the ability to bounce back after an unplanned use of committed resources.  !- Definitions and concepts: Term deposit accounts (such as certificates of deposit) are interest-bearing accounts whose funds can be withdrawn (without penalty) at the maturity date. !- Data requirements: Transaction level information or system flag that can produce a list of term deposit accounts that had an early, full extraction of funds over a specific period, and of those, the number that made subsquent repleneshing deposits to the account. To the extent that for a given reporting institution customers can open more than one term-deposit account, unique customer IDs can de-duplicate account-level records to produce a list of unique term-deposit customers that extracted funds before maturity. In addition, the total number of term-deposit accounts (or unique account-holders) is required as the denominator to compute the percentage.</t>
+          <t>A measure of the demand for long-term savings instruments among account holders. !- Data requirements: List of customers with deposit or payment accounts over a specific period of time, List of customers with time or term-deposit accounts over a specific period of time. Both lists should be linkable with a unique customer ID. When the lists are merged, the number of unique customers with both a deposit or payment account and a term deposit account can be counted and reported. For a system-wide count, the number of unique customers with both a deposit or payment account and term account across all reporting institutions can be summed up  and divided by the total number of unique customers and multiplied by 100 to obtain a percentage.  At the system level, there is a risk of counting individuals more than once in the numerator and denominator, unless national IDs can be used to de-duplicate records across FSPs.</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the likelihood of resuming term deposit savings after withdrawing them before maturity? What are the characteristics of individuals who resume term deposit savings by gender? Which FSPs rank highest and lowest in the resumption of term deposit savings, and does this ranking change when analyzed by gender?</t>
+          <t>How common is it for individuals holding transaction accounts to also maintain interest-bearing term deposit accounts? Are there gender disparities in the multiple ownership and distribution of these different account types across age groups and location types, both at the total market level and by relevant FSP/type? How prevalent is the cross-sell of term deposit accounts among vulnerable customer segments, and are there gender disparities within these segments? How do average balances differ between transaction and term deposit accounts across gender, age groups, and location types, both at the total market level and by relevant FSP/type? Are there gender disparities in average balances across these account types? How do average balances vary among vulnerable customer segments, and are there gender disparities within these segments? What are the gender disparities in cross-selling and average balances of transaction accounts and term deposit accounts across age groups and location types, both at the total market level and by relevant FSP/type?</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6005,35 +5895,45 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Savings</t>
+          <t>Savings, Credit</t>
         </is>
       </c>
       <c r="D107">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Deposit and payment account holders who also hold term deposits</t>
+          <t>Depositors-borrowers ratio</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>% of deposit and payment account holders who also have term deposits</t>
+          <t>% of unsecured borrowers who also have a deposit account</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>A measure of the demand for long-term savings instruments among account holders. !- Data requirements: List of customers with deposit or payment accounts over a specific period of time, List of customers with time or term-deposit accounts over a specific period of time. Both lists should be linkable with a unique customer ID. When the lists are merged, the number of unique customers with both a deposit or payment account and a term deposit account can be counted and reported. For a system-wide count, the number of unique customers with both a deposit or payment account and term account across all reporting institutions can be summed up  and divided by the total number of unique customers and multiplied by 100 to obtain a percentage.  At the system level, there is a risk of counting individuals more than once in the numerator and denominator, unless national IDs can be used to de-duplicate records across FSPs.</t>
+          <t>A measure of cross-selling additional financial services to borrowers (alternatively, a measure of the demand for deposit accounts among short-term borrowers). !- Data requirements: Granular data or data systems that can produce (1) A list of unique customers of any (at least one) unsecured loan or line of credit (e.g. credit card, personal loan) and (2) A list of unique customers of any (at least one) type of deposit account (e.g. current/checking, savings, time deposit). A unique customer ID to identify customers that are in both list (1) AND list (2). The total number of unique borrowers meeting this condition (also having a deposit account) is then divided by the total number of borrowers and multiplied by 100 to obtain the ratio.</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>How common is it for individuals holding transaction accounts to also maintain interest-bearing term deposit accounts? Are there gender disparities in the multiple ownership and distribution of these different account types across age groups and location types, both at the total market level and by relevant FSP/type? How prevalent is the cross-sell of term deposit accounts among vulnerable customer segments, and are there gender disparities within these segments? How do average balances differ between transaction and term deposit accounts across gender, age groups, and location types, both at the total market level and by relevant FSP/type? Are there gender disparities in average balances across these account types? How do average balances vary among vulnerable customer segments, and are there gender disparities within these segments? What are the gender disparities in cross-selling and average balances of transaction accounts and term deposit accounts across age groups and location types, both at the total market level and by relevant FSP/type?</t>
+          <t>Are there sociodemographic (gender, age, location, income) disparities in borrowers' cross-sell ratios of deposit accounts and in the likelihood of being a stand-alone borrower? Have gender disparities in cross-sell ratios changed over time, particularly for underserved borrowers?</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6059,41 +5959,31 @@
         </is>
       </c>
       <c r="D108">
-        <v>173</v>
+        <v>261</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Depositors-borrowers ratio</t>
+          <t>Savings to borrowings ratio</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>% of unsecured borrowers who also have a deposit account</t>
+          <t>% of outstanding balances of unsecured credit in relation to savings balances, for borrowers who also have a savings account</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>A measure of cross-selling additional financial services to borrowers (alternatively, a measure of the demand for deposit accounts among short-term borrowers). !- Data requirements: Granular data or data systems that can produce (1) A list of unique customers of any (at least one) unsecured loan or line of credit (e.g. credit card, personal loan) and (2) A list of unique customers of any (at least one) type of deposit account (e.g. current/checking, savings, time deposit). A unique customer ID to identify customers that are in both list (1) AND list (2). The total number of unique borrowers meeting this condition (also having a deposit account) is then divided by the total number of borrowers and multiplied by 100 to obtain the ratio.</t>
+          <t>This indicator measures the degree to which outstanding balances on unsecured loans or lines of credit (such as credit card debt, digital loans or other personal loans) can be covered with savings balances at a specific point in time, potentially providing insights on the financial health of the borrower. !- Data requirements: Granular data that can enable identifiction of (1) list of unique borrowers using any unsecured credit product AND a savings account, (2) total outstanding balances across all unsecured credit products at a specific point in time (e.g. end of quarter) by unique borrower, (3) total balances in savings accounts at a specific point in time by unique borrower. Among the borrowers who meet the conditions in (1) the indicator can be computed by taking the sum of total outstanding debt divided by the sum of total savings balances.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Are there sociodemographic (gender, age, location, income) disparities in borrowers' cross-sell ratios of deposit accounts and in the likelihood of being a stand-alone borrower? Have gender disparities in cross-sell ratios changed over time, particularly for underserved borrowers?</t>
+          <t>Are there disparities in borrowers' cross-sell ratios of deposit accounts by gender, and/or age, location or income?? And in the likelihood of being a stand-alone borrower? Have gender disparities in cross-sell ratios changed over time, particularly for underserved borrowers?</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Suitability</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -6110,35 +6000,36 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Outcomes</t>
+          <t>Uptake (account ownership)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Savings, Credit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D109">
-        <v>261</v>
+        <v>172</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Savings to borrowings ratio</t>
+          <t>First-time borrowers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>% of outstanding balances of unsecured credit in relation to savings balances, for borrowers who also have a savings account</t>
+          <t>% of borrowers who are first-time borrowers with the FSP (or in the financial system)</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>This indicator measures the degree to which outstanding balances on unsecured loans or lines of credit (such as credit card debt, digital loans or other personal loans) can be covered with savings balances at a specific point in time, potentially providing insights on the financial health of the borrower. !- Data requirements: Granular data that can enable identifiction of (1) list of unique borrowers using any unsecured credit product AND a savings account, (2) total outstanding balances across all unsecured credit products at a specific point in time (e.g. end of quarter) by unique borrower, (3) total balances in savings accounts at a specific point in time by unique borrower. Among the borrowers who meet the conditions in (1) the indicator can be computed by taking the sum of total outstanding debt divided by the sum of total savings balances.</t>
+          <t>This indicator shows the share of active borrowing retail customers who are new to the lender (new-to-bank/FSP) or new to formal credit altogether (new-to-credit, NTC). It is a direct barometer of financial inclusion and retail credit growth. A higher share can signal effective onboarding and market expansion, but it also shifts portfolio risk: NTC borrowers may lack repayment histories, making underwriting more model-driven and subject to greater uncertainty. Supervisors and lenders can monitor this metric to balance inclusion objectives with prudent risk management and to evaluate the effectiveness of credit-bureau coverage. !- Definitions and concepts: First-time borrower (FSP scope): a customer with no prior loan or credit line ever booked by the FSP before the reference period. First-time borrower (system scope / NTC): a customer with no prior loan or credit line reported to the national credit registry/bureau within a defined historical look-back (commonly “ever,” or a long horizon such as 5–10 years). This indicator is obtained by dividing the number of first-time borrowers by the total number of borrowers. Variants of this indicator include: value-weighted (by origination amount), new originations only (versus the entire active book), and cohort-based analysis (by origination month or quarter). !- Data requirements: Customer master records with unique, reliable identifiers (national ID/tax ID; deduplicated across branches). Loan-booking history from the FSP’s core systems. Credit-bureau/registry match results (for system-wide NTC status). Product taxonomy (include/exclude credit cards, overdrafts, BNPL) and reference dates. Limitaitons and considerations: Coverage gaps: thin or partial bureau coverage, informal lenders, or non-reporting segments can misclassify NTC status.
+Identifier quality: name changes, multiple IDs, or data-entry errors cause false “first-time” flags; robust deduplication is essential. Look-back window choice: shorter windows inflate “first-time” shares; disclose methodology. Product scope: excluding revolving credit or microloans biases results.</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Are there disparities in borrowers' cross-sell ratios of deposit accounts by gender, and/or age, location or income?? And in the likelihood of being a stand-alone borrower? Have gender disparities in cross-sell ratios changed over time, particularly for underserved borrowers?</t>
+          <t>Do first-time borrowers reflect a balanced gender representation, or are there gender disparities? How do FSPs rank in onboarding typically underserved borrowers, and does this ranking change when analyzed by gender?</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6160,7 +6051,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Suitability</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6196,16 +6087,6 @@
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>Central banking</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>Currency management and cash handling</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
@@ -6220,28 +6101,88 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
+          <t>Outcomes</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Savings</t>
+        </is>
+      </c>
+      <c r="D111">
+        <v>156</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Depositors who actively close deposit accounts</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>% of retail depositors who actively closed a deposit account</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>A measure of the incidence of account closing among depositors, if the measure is high, it could potentially signal issues with the quality of accounts or concerns about the safety of funds. !- Definitions and concepts: Deposit accounts include transaction and non-transaction deposit accounts, for example: Checking/demand, savings, time/term deposit accounts, pensions. 'Active' closure of an account refers to cases where the closure is initiated at the request of the customer, and not due to inactivity or dormancy. !- Data requirements: List of unique deposit account holders (i.e. an individual  must be counted as one depositor irrespective of the number of deposit accounts held) who actively close any of their accounts over a specified period of time (e.g. quarter or year); Total number of unique depositors at the beginning of the specified period.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>How do active closure rates compare by gender? Which types of accounts are most frequently closed by each gender? How do FSPs rank in active account closures, and does this ranking change when analyzed by gender?</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Consumer protection; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Fair treatment, Stability</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
           <t>Access</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D111">
+      <c r="D112">
         <v>393</v>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="E112" t="inlineStr">
         <is>
           <t>Access to inclusive insurance products</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>% of financial service providers offering inclusive or micro insurance products</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>This indicator measures the proportion of licensed insurance providers (or other entities authorized to underwrite insurance) that offer inclusive insurance or microinsurance products. It provides a supply-side measure of the extent to which the insurance market is serving un- or underserved populations, including low-income individuals and communities that face specific risks but have traditionally been excluded from formal insurance coverage. Tracking this indicator over time allows financial sector authorities to assess whether regulatory frameworks and market conditions are effectively encouraging providers to develop and distribute products that address the protection gap. It is particularly relevant for supervisors pursuing financial inclusion objectives and for evaluating the impact of proportionate regulatory approaches, such as dedicated microinsurance licensing frameworks or regulatory sandboxes, on the breadth of product offerings in the market.
 !-Definitions and concepts: Inclusive insurance, as defined in the IAIS Issues Paper on Conduct of Business in Inclusive Insurance (2015), refers broadly to all insurance products aimed at the excluded or underserved market, rather than only those targeted at the poor or a narrow conception of the low-income population. Microinsurance is a subset of inclusive insurance, defined by the IAIS (2007) as insurance that is accessed by the low-income population, provided by a variety of different entities, but run in accordance with generally accepted insurance practices and funded by premiums. Each jurisdiction should adapt this definition to its own context, considering national regulatory frameworks, market characteristics, and the specific populations identified as underserved. The formula is: Access to inclusive insurance products (%) = (Number of FSPs offering at least one inclusive or microinsurance product / Total number of licensed insurance providers) × 100.
@@ -6249,120 +6190,60 @@
 !-Limitations and considerations: The meaningfulness of this indicator depends heavily on how inclusive insurance or microinsurance is defined in each jurisdiction. In countries without a dedicated regulatory framework or formal product classification, identifying which providers offer qualifying products may require subjective judgments or additional data collection efforts. The indicator captures the share of providers offering inclusive products but does not measure the depth, quality, or uptake of those products; a provider may offer a single inclusive product with very limited reach. Complementary indicators such as the number of inclusive insurance policies in force, premiums written, or claims settlement ratios for inclusive products would provide a fuller picture of market development. The indicator also does not distinguish between providers for whom inclusive insurance is a core business versus those for whom it is a marginal product line. Cross-country comparisons should be made cautiously due to differences in regulatory definitions, market structures, and the types of entities authorized to offer insurance. Finally, because this indicator focuses on the supply side, it should be interpreted alongside demand-side measures to understand whether available products are actually reaching and benefiting the intended populations.</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
         <is>
           <t>Uptake (account ownership)</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D112">
+      <c r="D113">
         <v>395</v>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>Insured or lives covered</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>Number of insured persons or lives covered by insurance</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t>Refers to the total count of people covered by insurance, a key metric of coverage breadth and insurance uptake, complementary to the number of insurance policyholders. The policyholder and the insured can be different people -for example, if someone takes out a policy on another individual, the latter is the insured because the policy covers them, and the former is the policyholder, who purchases and owns the policy, and holds the right to make changes. An insurance policy can also cover several people, such as in member-owned schemes, group plans, and other variations. 
 When expressed as a share of the population or in per capita terms, it is a measure of the prevalence of insurance adoption and facilitates comparison with other countries. For microinsurance, a coverage ratio can reflect the number of lives covered expressed as a share of the target market or population participating in microinsurance programs  !- Definitions and concepts: Lives covered by insurance refers to the total number of people covered by life and non-life insurance policies. A customer covered by more than one (life or non-life) insurance policy should be counted as one life covered. !- Data requirements: Number of lives insured at the end of a specific period (e.g. quarter or year);  Total adult population (official counts from recent census or estimates from national statistics agency); Target population (number of people targeted by microinsurance, which may include segments of a community or clients from an MFI). !- Limitations and considerations: If an individual is covered by multiple insurers, they may be counted more than once in aggregations of lives covered across institutions, unless a national ID can be used . !- Derivable indicators: Lives covered by insurance per 1,000 adults; Lives covered by insurance as a share of the target population.</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t>Are there gender differences in the total number of lives covered by insurance, including across product types and providers? How do multiple insurance coverages and coverage amounts vary by gender, age, income, and location? To what extent do providers with higher gender diversity attract more gender-balanced portfolios of lives covered? Are gender disparities consistent or do they vary across life and non-life insurance within the overall market?</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t>For analyses with a primary focus on financial inclusion, for this indicator, it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered.</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t>Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Suitability</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D113">
-        <v>103</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Borrowers whose collateral was seized</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>% of borrowers whose collateral was seized</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>A measure of loan portfolio/credit risk assessment quality or financial distress among borrowers. !- Data requirements: Granular data that can yield (1) A count of unique borrowers of secured loans (those with collateral requirements) who subsequently had collateral seized by lender due to default over a specific period of time (e.g. past quarter or past year), (2) Total unique borrowers of secured loans over a specific period of time.</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>How does the share of customers whose collateral was seized due to default vary by gender and othe rkey sociodemographics? Are women more or less likely than men to have their collateral seized following loan default? How does the share differ by gender across different loan sizes, loan products,  types of financial service providers (FSP), collateral type (e.g., movable, immovable, alternative)? And how do any of these differences relate to seizure rates? Are women more likely to be subject to stricter collateral requirements or less flexible repayment terms that increase the likelihood of asset seizure?</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Outcomes, Credit risk</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Loan type; Collateral type; Loan size; Loan term; Interest rate category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6255,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Complaints handling</t>
+          <t>Complaints handling, Safety and security</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6383,26 +6264,26 @@
         </is>
       </c>
       <c r="D114">
-        <v>239</v>
+        <v>322</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Customer complaints (number)</t>
+          <t>Fraud prevalence in complaints</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Number of customer complaints (including processing status, channels, type)</t>
+          <t>Portion and volume of complaints received by providers, regulators, and ombuds that are fraud-related.</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>This indicator tallies the formal expressions of dissatisfaction that retail or MSME clients lodge with a financial-service provider (or an external ombudsman) about products, services, or staff conduct over a specified period and can be normalized by dividing by the customer basis to obtain an intensity metric (e.g. complaints per 1,000 active customers). A rising complaint count can signal service-quality gaps, mis-selling, opaque fees, or inadequate disclosure—issues that erode trust and may escalate into regulatory sanctions or litigation. Supervisors can track both the absolute number and complaint-to-account ratios to test consumer-protection frameworks, prioritise thematic reviews, and assess whether rapid product roll-outs (e.g., digital lending, mobile wallets) are being matched by robust after-sales support. Where granular data or more detailed reporting templates permit, customer complaints can be disaggregated by processing status (e.g. received, accepted/rejected, in process, resolved, escalated/disputed, withdrawn), product (e.g. consumer loan, deposit account, etc), channel (e.g. digital, phone, in-person), issue category (e.g. fraudulent or unauthorized transactions, unfair treatment, unexpected fees, errors on statements,  etc.), resolution status (open, resolved with monetary compensation, resolved without compensation, escalated to ombudsman/regulator, other). Combined with resolution-time, compensation and other metrics, the number of customer complaints provides a critical, early-warning lens on conduct risk and customer-experience health. !- Definitions and concepts:  Complaints are expressions of dissatisfaction by (or on behalf of) customers that are related to their experiences with FSPs and can include any written, digital or recorded verbal statement made through any available channel, such as a branch, call-centre, email, social media, chatbots and other portals. Complaints may relate to the quality of a product or service, treatment by an FSP (including its agents and other third parties), or suspected wrongdoing. Complaints are different from general inquiries (e.g., where can I find an ATM?) or legal disputes between parties that may require formal dispute resolution. For more information, see for example CGAP's toolkit on using complaints data for market conduct supervision: https://www.cgap.org/research/publication/market-monitoring-tool-analysis-complaints-data and the Alliance for Financial Inclusion's framework on 'Complaint handling in Central Banks': https://www.afi-global.org/sites/default/files/publications/2020-04/AFI_CEMC_framework_AW_digital%20v2.pdf. !- Data requirements:  Database or log of customer complaints, detailing date of complaint and additional information, such as channel through which complaint was lodged, associated product or account, details or brief description of the complaint, and resolution status. !- Limitations and considerations: Complaints processes differ across FSPs in terms of steps/levels for routing, hand-over, escalations to higher management levels and to external ombudsman. Customer details and demographics of complainants are not always capture/stored on FSPs' systems, or may be stored in fragmented data bases. Complaints logged at aggregator sites/portals may not request customer demographics. Limited to officially logged complaints and/or maintaining records of inbound customer communications. Dependent on having electronic complaints management system.  Reporting culture: firms with easy‐to‐use channels may record more complaints than peers, even if service quality is similar—benchmark using severity and uphold rates. Under-reporting bias: vulnerable customers may forgo formal complaints; mystery-shopping and survey data can complement administrative counts. Duplicate cases: the same issue voiced through multiple channels can inflate totals unless robust deduplication exists. Product mix effects: complaint propensity varies—e.g., complex investments draw more grievances than basic savings; segment analysis is essential. Regulatory divergence: definitions and mandatory reporting thresholds differ across jurisdictions, complicating cross-border comparisons.</t>
+          <t>Tracks how much of the complaint landscape is driven by fraud—both the count (volume) and the share (portion) of total complaints. Rising prevalence of frauds signals elevated customer harm, control weaknesses (KYC/AML, authentication, data security), or new attack vectors (social engineering). It helps guide supervision, consumer protection responses, reimbursement policies, and investment in fraud controls. !- Definitions and concepts: Fraud-related complaint: a case alleging unauthorised or deceptive activity resulting in loss or attempted loss—e.g., account takeover, card-not-present, phishing/SMiShing, SIM-swap, mule accounts, synthetic identity, merchant fraud, insider abuse, and authorised push payment (APP) scams. Volume: number of fraud-related complaints received in the period. Share: [# of fraud complaints / # of all complaints] x 100%. Intensity companions: fraud complaints per 1,000 customers or per 1 million transactions, value lens using claimed or confirmed loss amounts. Outcome cuts: upheld rate, reimbursement rate, median loss, time-to-resolution. A standard taxonomy for fraud types is needed, including the differentiation between fraud and disputed transaction. !- Limitations and considerations:  Under-reporting: many victims never complain or only contact the bank—triangulate with dispute/chargeback data and incident logs.</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>How does the number of complaints at each processing stage vary by gender? Are complaints disproportionately concentrated at certain processing stages for any gender? How do FSPs compare to market averages in the number of complaints at each processing stage?"</t>
+          <t>Are there gender differences in the proportion of fraud-related complaints submitted to providers, regulators, or ombuds services?  Do individuals of different genders tend to report different types of fraud, such as identity theft, phishing, or agent misconduct, and are specific delivery channels more commonly associated with these complaints? Is the volume of fraud-related complaints disproportionately high among certain gender groups when compared to their levels of account ownership or usage? Do complaint resolution rates and timeframes differ by gender across various FSP or reporting channels?</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6412,17 +6293,17 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Quality,</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints filing channel; Complaints issue category; Complaints processing status; Complaints resolution outcome; Complaints resolution time</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints resolution outcome; Complaints resolution time</t>
         </is>
       </c>
     </row>
@@ -6434,35 +6315,35 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Complaints handling</t>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D115">
-        <v>243</v>
+        <v>103</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Customer complaints resolved in the customer's favor</t>
+          <t>Borrowers whose collateral was seized</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>% of customer complaints that were solved in the customer's favor in the most recent period</t>
+          <t>% of borrowers whose collateral was seized</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>This indicator shows the share of complaints closed in the reference period that were resolved in the customer’s favor. It is a direct outcome metric for fair treatment and service quality. A higher “uphold rate” can indicate strong remediation and customer-centric policies; a very low rate may suggest poor triage, overly narrow eligibility rules, or weak guidance to customers on evidence requirements. Supervisors use it to benchmark conduct outcomes across firms and products; boards track it alongside complaint volumes and resolution times to target root-cause fixes. Tracked with complaint volume, resolution time, and compensation totals, this indicator provides a balanced view of consumer outcomes and conduct risk. !- Definitions and concepts: Resolved in the customer’s favor (upheld): final decision grants redress—monetary (refund/compensation/fee reversal) or non-monetary (policy correction, contract change, apology with tangible remedy). Many firms also count partially upheld cases; disclose whether partials are included. Denominator: all complaints closed in the period. Segment results by product, channel, and severtiy to avoid masking problem areas. !- Data requirements: Central complaint-management records with unique IDs, receipt date, closure date, product, channel, allegation type, decision outcome (upheld/partially/declined), and compensation amount. Deduplication logic across channels; linkages to ombudsman/regulator portals for escalations and reversals. Customer-base denominator (for intensity metrics) and service level agreement (SLA) timestamps for parallel monitoring* (see note below). !- Limitations and considerations: Classification discretion: definitions of “partial uphold” vary; publish inclusion rules. Case mix effects: a surge in low-merit mass claims can depress the percentage; report severity-adjusted or line-of-business cuts. Gaming risk: chasing high uphold rates may encourage paying weak claims; pair with fraud flags, root-cause fixes, and cost-per-case. Timing bias: complex cases close later and differ in uphold propensity; use rolling averages and track median resolution time. External outcomes: include overturned-on-appeal adjustments to reflect true customer outcome. *With granular time-stamped complaints data, timeliness of key milestones in the complaints resolution process can be tracked, for example time to acknowledge complaint, time to first response, time to resolution. With this data, supervisors can track not just outcomes, but also whether providers are meeting required timeframes per their own SLA.</t>
+          <t>A measure of loan portfolio/credit risk assessment quality or financial distress among borrowers. !- Data requirements: Granular data that can yield (1) A count of unique borrowers of secured loans (those with collateral requirements) who subsequently had collateral seized by lender due to default over a specific period of time (e.g. past quarter or past year), (2) Total unique borrowers of secured loans over a specific period of time.</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>How do the percentages of complaints resolved in favor of customers vary by gender? Are any genders more likely to receive favorable resolutions? How do FSPs rank in terms of favorable resolutions by gender?</t>
+          <t>How does the share of customers whose collateral was seized due to default vary by gender and othe rkey sociodemographics? Are women more or less likely than men to have their collateral seized following loan default? How does the share differ by gender across different loan sizes, loan products,  types of financial service providers (FSP), collateral type (e.g., movable, immovable, alternative)? And how do any of these differences relate to seizure rates? Are women more likely to be subject to stricter collateral requirements or less flexible repayment terms that increase the likelihood of asset seizure?</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6477,12 +6358,12 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Quality,</t>
+          <t>Outcomes, Credit risk</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints filing channel; Complaints issue category; Complaints processing status; Complaints resolution outcome; Complaints resolution time</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Loan type; Collateral type; Loan size; Loan term; Interest rate category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6375,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Data privacy and protection</t>
+          <t>Complaints handling</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6503,26 +6384,26 @@
         </is>
       </c>
       <c r="D116">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Consent rate for FSP contact</t>
+          <t>Customer complaints (number)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>% of customers who provide consent to be contacted in the future by the FSP for sales, awareness and new offerings</t>
+          <t>Number of customer complaints (including processing status, channels, type)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Measures the percentage of customers who have provided explicit consent to be contacted in the future by their financial service provider (FSP) for purposes such as product marketing, customer awareness campaigns, or information on new offerings. This indicator reflects how institutions manage customer permissions for communication under applicable data privacy and marketing regulations. Captures the extent of customer consent and data-use transparency in the financial system, serving as a proxy for compliance with consent-based communication standards and the balance between customer engagement and data protection. Tracking customer contact consents helps regulators and providers: Monitor compliance with data protection and privacy laws (e.g., GDPR-like frameworks, data protection acts); Assess ethical marketing practices and responsible customer engagement; Evaluate trust and willingness of customers to maintain open communication with FSPs; Understand customer attitudes toward data sharing and digital outreach. For supervisors, it provides a measurable view of market conduct, customer empowerment, and institutional transparency. High consent rates suggest strong customer trust and engagement, but may require close monitoring to ensure non-coercive consent collection and ethical marketing practices. Low consent rates may reflect privacy concerns, limited digital literacy, or overly complex consent processes. Changes over time can signal shifts in consumer sentiment or compliance practices following new regulations. !- Definitions and concepts: Consent: A freely given, informed, and specific agreement by a customer allowing the FSP to contact them for defined purposes. Data privacy regulation: Legal framework governing the collection, storage, and use of personal data, including consent requirements for marketing communications. !- Data requirements: Administrative data from FSP customer relationship management (CRM) or consent-management systems to obtain the number of customers who provided consent to be contact and the total number of customers.</t>
+          <t>This indicator tallies the formal expressions of dissatisfaction that retail or MSME clients lodge with a financial-service provider (or an external ombudsman) about products, services, or staff conduct over a specified period and can be normalized by dividing by the customer basis to obtain an intensity metric (e.g. complaints per 1,000 active customers). A rising complaint count can signal service-quality gaps, mis-selling, opaque fees, or inadequate disclosure—issues that erode trust and may escalate into regulatory sanctions or litigation. Supervisors can track both the absolute number and complaint-to-account ratios to test consumer-protection frameworks, prioritise thematic reviews, and assess whether rapid product roll-outs (e.g., digital lending, mobile wallets) are being matched by robust after-sales support. Where granular data or more detailed reporting templates permit, customer complaints can be disaggregated by processing status (e.g. received, accepted/rejected, in process, resolved, escalated/disputed, withdrawn), product (e.g. consumer loan, deposit account, etc), channel (e.g. digital, phone, in-person), issue category (e.g. fraudulent or unauthorized transactions, unfair treatment, unexpected fees, errors on statements,  etc.), resolution status (open, resolved with monetary compensation, resolved without compensation, escalated to ombudsman/regulator, other). Combined with resolution-time, compensation and other metrics, the number of customer complaints provides a critical, early-warning lens on conduct risk and customer-experience health. !- Definitions and concepts:  Complaints are expressions of dissatisfaction by (or on behalf of) customers that are related to their experiences with FSPs and can include any written, digital or recorded verbal statement made through any available channel, such as a branch, call-centre, email, social media, chatbots and other portals. Complaints may relate to the quality of a product or service, treatment by an FSP (including its agents and other third parties), or suspected wrongdoing. Complaints are different from general inquiries (e.g., where can I find an ATM?) or legal disputes between parties that may require formal dispute resolution. For more information, see for example CGAP's toolkit on using complaints data for market conduct supervision: https://www.cgap.org/research/publication/market-monitoring-tool-analysis-complaints-data and the Alliance for Financial Inclusion's framework on 'Complaint handling in Central Banks': https://www.afi-global.org/sites/default/files/publications/2020-04/AFI_CEMC_framework_AW_digital%20v2.pdf. !- Data requirements:  Database or log of customer complaints, detailing date of complaint and additional information, such as channel through which complaint was lodged, associated product or account, details or brief description of the complaint, and resolution status. !- Limitations and considerations: Complaints processes differ across FSPs in terms of steps/levels for routing, hand-over, escalations to higher management levels and to external ombudsman. Customer details and demographics of complainants are not always capture/stored on FSPs' systems, or may be stored in fragmented data bases. Complaints logged at aggregator sites/portals may not request customer demographics. Limited to officially logged complaints and/or maintaining records of inbound customer communications. Dependent on having electronic complaints management system.  Reporting culture: firms with easy‐to‐use channels may record more complaints than peers, even if service quality is similar—benchmark using severity and uphold rates. Under-reporting bias: vulnerable customers may forgo formal complaints; mystery-shopping and survey data can complement administrative counts. Duplicate cases: the same issue voiced through multiple channels can inflate totals unless robust deduplication exists. Product mix effects: complaint propensity varies—e.g., complex investments draw more grievances than basic savings; segment analysis is essential. Regulatory divergence: definitions and mandatory reporting thresholds differ across jurisdictions, complicating cross-border comparisons.</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>How do consent rates for customer contact vary by gender? Are any genders more likely to provide consent to be contacted? How do FSPs rank in terms of consent rates by gender?</t>
+          <t>How does the number of complaints at each processing stage vary by gender? Are complaints disproportionately concentrated at certain processing stages for any gender? How do FSPs compare to market averages in the number of complaints at each processing stage?"</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -6542,7 +6423,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints filing channel; Complaints issue category; Complaints processing status; Complaints resolution outcome; Complaints resolution time</t>
         </is>
       </c>
     </row>
@@ -6554,28 +6435,148 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>Complaints handling</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D117">
+        <v>243</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Customer complaints resolved in the customer's favor</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>% of customer complaints that were solved in the customer's favor in the most recent period</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>This indicator shows the share of complaints closed in the reference period that were resolved in the customer’s favor. It is a direct outcome metric for fair treatment and service quality. A higher “uphold rate” can indicate strong remediation and customer-centric policies; a very low rate may suggest poor triage, overly narrow eligibility rules, or weak guidance to customers on evidence requirements. Supervisors use it to benchmark conduct outcomes across firms and products; boards track it alongside complaint volumes and resolution times to target root-cause fixes. Tracked with complaint volume, resolution time, and compensation totals, this indicator provides a balanced view of consumer outcomes and conduct risk. !- Definitions and concepts: Resolved in the customer’s favor (upheld): final decision grants redress—monetary (refund/compensation/fee reversal) or non-monetary (policy correction, contract change, apology with tangible remedy). Many firms also count partially upheld cases; disclose whether partials are included. Denominator: all complaints closed in the period. Segment results by product, channel, and severtiy to avoid masking problem areas. !- Data requirements: Central complaint-management records with unique IDs, receipt date, closure date, product, channel, allegation type, decision outcome (upheld/partially/declined), and compensation amount. Deduplication logic across channels; linkages to ombudsman/regulator portals for escalations and reversals. Customer-base denominator (for intensity metrics) and service level agreement (SLA) timestamps for parallel monitoring* (see note below). !- Limitations and considerations: Classification discretion: definitions of “partial uphold” vary; publish inclusion rules. Case mix effects: a surge in low-merit mass claims can depress the percentage; report severity-adjusted or line-of-business cuts. Gaming risk: chasing high uphold rates may encourage paying weak claims; pair with fraud flags, root-cause fixes, and cost-per-case. Timing bias: complex cases close later and differ in uphold propensity; use rolling averages and track median resolution time. External outcomes: include overturned-on-appeal adjustments to reflect true customer outcome. *With granular time-stamped complaints data, timeliness of key milestones in the complaints resolution process can be tracked, for example time to acknowledge complaint, time to first response, time to resolution. With this data, supervisors can track not just outcomes, but also whether providers are meeting required timeframes per their own SLA.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>How do the percentages of complaints resolved in favor of customers vary by gender? Are any genders more likely to receive favorable resolutions? How do FSPs rank in terms of favorable resolutions by gender?</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints filing channel; Complaints issue category; Complaints processing status; Complaints resolution outcome; Complaints resolution time</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Data privacy and protection</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D118">
+        <v>234</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Consent rate for FSP contact</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>% of customers who provide consent to be contacted in the future by the FSP for sales, awareness and new offerings</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Measures the percentage of customers who have provided explicit consent to be contacted in the future by their financial service provider (FSP) for purposes such as product marketing, customer awareness campaigns, or information on new offerings. This indicator reflects how institutions manage customer permissions for communication under applicable data privacy and marketing regulations. Captures the extent of customer consent and data-use transparency in the financial system, serving as a proxy for compliance with consent-based communication standards and the balance between customer engagement and data protection. Tracking customer contact consents helps regulators and providers: Monitor compliance with data protection and privacy laws (e.g., GDPR-like frameworks, data protection acts); Assess ethical marketing practices and responsible customer engagement; Evaluate trust and willingness of customers to maintain open communication with FSPs; Understand customer attitudes toward data sharing and digital outreach. For supervisors, it provides a measurable view of market conduct, customer empowerment, and institutional transparency. High consent rates suggest strong customer trust and engagement, but may require close monitoring to ensure non-coercive consent collection and ethical marketing practices. Low consent rates may reflect privacy concerns, limited digital literacy, or overly complex consent processes. Changes over time can signal shifts in consumer sentiment or compliance practices following new regulations. !- Definitions and concepts: Consent: A freely given, informed, and specific agreement by a customer allowing the FSP to contact them for defined purposes. Data privacy regulation: Legal framework governing the collection, storage, and use of personal data, including consent requirements for marketing communications. !- Data requirements: Administrative data from FSP customer relationship management (CRM) or consent-management systems to obtain the number of customers who provided consent to be contact and the total number of customers.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>How do consent rates for customer contact vary by gender? Are any genders more likely to provide consent to be contacted? How do FSPs rank in terms of consent rates by gender?</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D117">
+      <c r="D119">
         <v>284</v>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>Annual percentage rate (APR) for retail credit</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>Average cost of borrowing money, including fees to get the loan, as a% of the loan principal (except for credit cards)</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t>APR is the standardized annualized cost of borrowing that incorporates the contractual interest rate plus certain up-front or periodic fees required to obtain and maintain the credit. It lets consumers compare offers across lenders and products on a like-for-like basis, and helps supervisors monitor pricing fairness and market competitiveness. Unlike a simple “nominal” rate, APR reflects timing of cash flows and required charges, so it better approximates the true price of credit. !- Definitions and concepts: Installment credit APR (actuarial method): the internal rate of return (IRR) that equates the amount advanced to the borrower with the present value of all required payments (principal, interest, and included fees), expressed on an annual basis.
 Revolving credit APR (cards/overdrafts): the periodic rate applied to the average daily balance, annualized (e.g., daily rate × 365 or monthly rate × 12), plus disclosure of any mandatory fees as prescribed. Scope of fees: typically includes origination/processing fees and compulsory charges; excludes penalty fees and optional add-ons (unless mandated). APR vs. EIR: APR is a consumer disclosure metric (jurisdiction-specific rules); EIR is an accounting yield used to recognize interest income.!- Data requirements: Contract terms: principal advanced, repayment schedule (dates/amounts), nominal rate, compounding frequency, and variable-rate index/margins. Included fees: origination/processing, mandatory maintenance or platform fees, financed vs. paid-in-cash. For revolving products: periodic rate(s), balance computation method (average daily balance), mandatory annual fees, grace-period rules, promotional/teaser rates.
@@ -6583,149 +6584,29 @@
 Promotions &amp; step-ups: teaser or deferred-interest offers can make snapshot APRs unrepresentative—show lifetime-effective examples when possible. Variable rates: APR at origination may understate future cost if reference rates rise. Loan term effects: fixed fees loom larger on short tenors; present both APR and the fee share of cost for transparency.</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="H119" t="inlineStr">
         <is>
           <t>Are there gender disparities in the APR applied to loans disbursed to women and men, including MSMEs by gender of ownership? Do women borrowers systematically face higher average APRs than men within the same loan type, amount range, or provider category? Are higher APRs for women associated with smaller loan sizes, shorter maturities, or higher perceived credit risk? Do FSPs with greater gender diversity or stronger inclusion policies show smaller gender gaps in average APRs? How do APR differences relate to borrower profiles and do they suggest the presence of gender-based pricing bias or structural credit segmentation?</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
         <is>
           <t>Financial inclusion; Market development</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="K119" t="inlineStr">
         <is>
           <t>Quality, Competition</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Data privacy and protection</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D118">
-        <v>235</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Consents for sharing data with third-parties</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>% of customers who have given explicit consent for their data to be shared by FSPs with third parties, for various purposes</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>This indicator shows how many customers have actively opted in to let a financial service provider (FSP) share their data with external parties—for open-banking/aggregation, credit scoring, fraud prevention, marketing, analytics, etc. A higher share can reflect strong digital adoption and trust; low or falling rates may signal poor consent UX, unclear value propositions, or privacy concerns. It helps compliance teams evidence lawfulness, product teams gauge partner-integration reach, and supervisors assess the maturity of consent-based data-sharing ecosystems. !- Definitions and concepts: Explicit consent: a clear, affirmative action (e.g., checked box, strong-customer-authenticated authorization) tied to a specific purpose, with intelligible notice and the ability to withdraw at any time. Active consent: consent that is valid as of the reference date (not expired, not withdrawn, not superseded). Purpose taxonomy: e.g., account information services (AIS), payment initiation services (PIS), credit decisioning/bureau pulls, fraud/AML tools, personalised marketing, data portability. Metric: % of customer with active consent for purpose p = [# of unique customers with at least 1 active consent for p / # of active customers] x 100%. Indicator companions: Any-purpose consent, consents per consenting customer and revocation rate. !- Data requirements: Consent ledger that includes: customer ID, purpose(s) granted, third-party identity, channel, timestamp, expiry/refresh cycle, version of the privacy notice, proof of consent (hash, audit trail, SCA event). Status events: withdrawals, expiries, scope changes, third-party disconnects. Reference universe: deduplicated active-customer list (define “active”: e.g., ≥1 product in force or ≥1 login/transaction in last 12 months). !- Limitations and considerations: Granularity &amp; fragmentation: a customer may consent per app, per account, and per purpose; avoid double counting by using unique customers and report purpose-level cuts. Expiry &amp; refresh: open-banking tokens often have short authorizations; snapshot dates vs. rolling windows will yield different figures—disclose method. Consumer protection risk: high opt-ins driven by coercive UX can backfire (complaints, revocations); pair with revocation rate, time-to-revocation, and complaints about data sharing. Coverage gaps: legacy channels without digital capture may under-record historical consents; backfill or disclose limitations.</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>How do consent rates for data sharing with third parties vary by gender? Are any genders more likely to provide consent for data sharing? How do FSPs rank in terms of consent rates for data sharing by gender?</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>Market development</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Fair treatment</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D119">
-        <v>260</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Late penalty charges/fees on retail credit</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Income from penalty fees as % of total net interest income</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>This indicator shows how much of a lender is relying on penalty fees for income. Revenue from penalty fees and other charges applied when a loan payment is late is compared with the total gross interest income. A high share could signal borrower stress and potential conduct risk (reliance on punitive pricing). Boards and supervisors use the metric to assess earnings quality, pricing fairness. !- Definitions and concepts: Penalty/default fees and charges: the fees and costs charged once a loan  is past due. Numerator (preferred “incremental” view): Penalty actually recognized as income on retail loans during the period. Denominator: Gross interest income. !- Data requirements: General-ledger mapping that identifies penalty income at product level. Period interest income totals for the denominator.  !- Limitations and considerations: Mix effects: card-heavy books show higher shares of penalty income; segment by product. Conduct lens: pair with % customers incurring penalty charges, related complaints.</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>What percentages of net interest income are attributable to penalties and other punitive charges earned from borrowers of unsecured loans/lines of credit, and how do these vary by gender across age bands and location types, at a total market level and by relevant FSP/type? How do these percentages compare across relevant FSPs/types and against market norms across age bands and location types? How do gender disparities manifest in these percentages at a total market level and by relevant FSP/type?</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
         </is>
       </c>
     </row>
@@ -6737,177 +6618,177 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
+          <t>Data privacy and protection</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D120">
+        <v>235</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Consents for sharing data with third-parties</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>% of customers who have given explicit consent for their data to be shared by FSPs with third parties, for various purposes</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>This indicator shows how many customers have actively opted in to let a financial service provider (FSP) share their data with external parties—for open-banking/aggregation, credit scoring, fraud prevention, marketing, analytics, etc. A higher share can reflect strong digital adoption and trust; low or falling rates may signal poor consent UX, unclear value propositions, or privacy concerns. It helps compliance teams evidence lawfulness, product teams gauge partner-integration reach, and supervisors assess the maturity of consent-based data-sharing ecosystems. !- Definitions and concepts: Explicit consent: a clear, affirmative action (e.g., checked box, strong-customer-authenticated authorization) tied to a specific purpose, with intelligible notice and the ability to withdraw at any time. Active consent: consent that is valid as of the reference date (not expired, not withdrawn, not superseded). Purpose taxonomy: e.g., account information services (AIS), payment initiation services (PIS), credit decisioning/bureau pulls, fraud/AML tools, personalised marketing, data portability. Metric: % of customer with active consent for purpose p = [# of unique customers with at least 1 active consent for p / # of active customers] x 100%. Indicator companions: Any-purpose consent, consents per consenting customer and revocation rate. !- Data requirements: Consent ledger that includes: customer ID, purpose(s) granted, third-party identity, channel, timestamp, expiry/refresh cycle, version of the privacy notice, proof of consent (hash, audit trail, SCA event). Status events: withdrawals, expiries, scope changes, third-party disconnects. Reference universe: deduplicated active-customer list (define “active”: e.g., ≥1 product in force or ≥1 login/transaction in last 12 months). !- Limitations and considerations: Granularity &amp; fragmentation: a customer may consent per app, per account, and per purpose; avoid double counting by using unique customers and report purpose-level cuts. Expiry &amp; refresh: open-banking tokens often have short authorizations; snapshot dates vs. rolling windows will yield different figures—disclose method. Consumer protection risk: high opt-ins driven by coercive UX can backfire (complaints, revocations); pair with revocation rate, time-to-revocation, and complaints about data sharing. Coverage gaps: legacy channels without digital capture may under-record historical consents; backfill or disclose limitations.</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>How do consent rates for data sharing with third parties vary by gender? Are any genders more likely to provide consent for data sharing? How do FSPs rank in terms of consent rates for data sharing by gender?</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Market development</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D120">
+      <c r="D121">
+        <v>260</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Late penalty charges/fees on retail credit</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Income from penalty fees as % of total net interest income</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>This indicator shows how much of a lender is relying on penalty fees for income. Revenue from penalty fees and other charges applied when a loan payment is late is compared with the total gross interest income. A high share could signal borrower stress and potential conduct risk (reliance on punitive pricing). Boards and supervisors use the metric to assess earnings quality, pricing fairness. !- Definitions and concepts: Penalty/default fees and charges: the fees and costs charged once a loan  is past due. Numerator (preferred “incremental” view): Penalty actually recognized as income on retail loans during the period. Denominator: Gross interest income. !- Data requirements: General-ledger mapping that identifies penalty income at product level. Period interest income totals for the denominator.  !- Limitations and considerations: Mix effects: card-heavy books show higher shares of penalty income; segment by product. Conduct lens: pair with % customers incurring penalty charges, related complaints.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>What percentages of net interest income are attributable to penalties and other punitive charges earned from borrowers of unsecured loans/lines of credit, and how do these vary by gender across age bands and location types, at a total market level and by relevant FSP/type? How do these percentages compare across relevant FSPs/types and against market norms across age bands and location types? How do gender disparities manifest in these percentages at a total market level and by relevant FSP/type?</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Fair treatment</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="D122">
         <v>185</v>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="E122" t="inlineStr">
         <is>
           <t>Processing and application fees or PAF (as % of loan principal)</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>PAF as % of loan principal in unsecured credit operations</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t>This indicator expresses the total up-front charges borrowers pay to originate an unsecured loan—processing fees, application fees, documentation charges—as a percentage of the loan’s principal amount. Because unsecured credit often targets price-sensitive segments and carries higher risk-based interest rates, excessive PAFs can materially raise the all-in cost of borrowing, undermine affordability tests, and trigger consumer-protection scrutiny. Tracking the ratio helps regulators detect predatory pricing, compare lenders’ transparency practices, and gauge competition in loan-origination services. For lenders, it is a barometer of non-interest revenue reliance and a lever for recouping acquisition costs. Processing &amp; Application Fees (PAF): any non-refundable charge levied at or before disbursement for administrative tasks (credit checks, KYC, documentation, platform usage). Late-payment or insurance fees are excluded.
 PAF ratio (simple): [Total PAF charged/Gross loan principal]×100%
 Where multiple partial disbursements occur, use the aggregate principal amount. Annualised impact: when PAFs are capitalised into the Effective Annual Percentage Rate (APR), their weight declines as term length rises—monitor both absolute and APR-embedded views. !- Data requirements: Loan-level records capturing principal, disbursement date, PAF amount, and any rebates for cancellations. Product codes distinguishing personal instalment loans, credit-card cash advances, payday/BNPL equivalents. Borrower demographics and channel identifiers (branch, mobile app, marketplace) for segmentation. Accounting entries showing whether fees are recognised up-front (IFRS 15 “contract costs”) or amortised via the effective-interest-rate (EIR) method. !- Limitations and considerations: Amortisation differences: Lenders using EIR spread PAFs over the loan’s life; comparing ratios on a cash basis versus amortised income can mislead. Bundled products: Cross-selling (e.g., credit-life insurance) may shift income from PAF to commissions, understating the ratio. Regulatory caps &amp; disclosures: Jurisdictions with fee ceilings or mandatory APR disclosures compress PAF ratios; cross-country benchmarking must control for such rules. Loan term effects: Short-tenor payday or BNPL loans show high PAF percentages even when absolute fees are small; interpret in context of maturity profile and APR. Waivers &amp; promotions: Temporary fee holidays for marketing campaigns can distort time-series trends—flag promotional periods separately. Should FSPs not be allowed/willing to share sensitive revenue data, ratios/percentages can be performed in-house and then shared with regulator.</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="H122" t="inlineStr">
         <is>
           <t>What are the origination fee percentages as a share of loan principal by gender? Are there gender disparities in the origination fee percentages incurred? How do FSPs rank in terms of origination fee percentages by gender?</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="L122" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Data privacy and protection</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D121">
-        <v>232</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Data breaches</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>% of customers affected by data breaches</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>A measure of the depth of cyberattacks or other data security breach that result in unauthorized access to customer data. Definitions and concept: A data breach is any security incident in which unauthorized parties access sensitive or confidential information, including personal data (tax numbers, ID information, bank account numbers, healthcare data) and corporate data (customer records, intellectual property, financial information). Data requirement: Number of customers whose data was accessed without authorization during a specified period of time (e.g. quarter or year); Total number of customers at the beginning of the specified period (e.g. quarter or year).</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>How does the percentage of customers affected by data breaches vary by gender? Are any genders disproportionately affected by data breaches? Are data breaches more frequent in certain types of FSPs? Are data breaches more common in specific channels or interfaces?"</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>Quality, Operational risk</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Depositor protection</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Savings</t>
-        </is>
-      </c>
-      <c r="D122">
-        <v>15</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Deposit accounts covered by direct deposit insurance</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Volume and value (balances) of deposit accounts covered by direct deposit insurance</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>This indicator counts (or expresses as a percentage) the deposit accounts that fall within the scope of an explicit, statutory deposit insurance scheme (DIS) or deposit guarantee fund. It helps supervisors gauge how much of the retail/MSME funding base is protected against bank failure. This is key for financial stability monitoring, payout readiness, and for calibrating the deposit insurance/guarantee fund. High coverage supports confidence and can dampen run dynamics. Source: https://www.iadi.org/uploads/cprevised2014nov.pdf. !- Definitions and concepts: Covered (eligible) account: a deposit type included by law. Fully insured vs. partially insured: “Fully insured” balances are ≤ the coverage limit per depositor, per bank, per ownership category; “covered/eligible” may include accounts whose balances exceed the cap (partially insured). Ownership categories: individual, joint, trust/fiduciary, retirement—rules vary by jurisdiction and affect aggregation across accounts. Indicator variants: % Eligible accounts = eligible deposit accounts ÷ total deposit accounts. Insured balance share = insured amounts in eligible accounts ÷ total deposit balances in eligible accounts. Dormancy: dormant accounts may be treated differently in coverage statistics.</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in the number of deposit accounts covered by direct deposit insurance? How do these disparities vary by age, income level, and geographic location? Are certain gender groups, especially within vulnerable or low-income populations, less likely to hold insured deposit accounts? How do the average insured deposit account balances differ across genders, and what might this indicate about savings behavior, access to financial protection, or economic security? Do financial service providers with higher levels of gender diversity in leadership or staff tend to offer more equitable access to insured deposit accounts and balanced coverage across genders? Additionally, how do gender differences in insured deposit accounts relate to broader financial inclusion and resilience against financial shocks?</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>Quality, Suitability,</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Deposit account type</t>
         </is>
       </c>
     </row>
@@ -6919,28 +6800,148 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
+          <t>Data privacy and protection</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D123">
+        <v>232</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Data breaches</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>% of customers affected by data breaches</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>A measure of the depth of cyberattacks or other data security breach that result in unauthorized access to customer data. Definitions and concept: A data breach is any security incident in which unauthorized parties access sensitive or confidential information, including personal data (tax numbers, ID information, bank account numbers, healthcare data) and corporate data (customer records, intellectual property, financial information). Data requirement: Number of customers whose data was accessed without authorization during a specified period of time (e.g. quarter or year); Total number of customers at the beginning of the specified period (e.g. quarter or year).</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>How does the percentage of customers affected by data breaches vary by gender? Are any genders disproportionately affected by data breaches? Are data breaches more frequent in certain types of FSPs? Are data breaches more common in specific channels or interfaces?"</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Quality, Operational risk</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
           <t>Depositor protection</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>Savings</t>
         </is>
       </c>
-      <c r="D123">
+      <c r="D124">
+        <v>15</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Deposit accounts covered by direct deposit insurance</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Volume and value (balances) of deposit accounts covered by direct deposit insurance</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>This indicator counts (or expresses as a percentage) the deposit accounts that fall within the scope of an explicit, statutory deposit insurance scheme (DIS) or deposit guarantee fund. It helps supervisors gauge how much of the retail/MSME funding base is protected against bank failure. This is key for financial stability monitoring, payout readiness, and for calibrating the deposit insurance/guarantee fund. High coverage supports confidence and can dampen run dynamics. Source: https://www.iadi.org/uploads/cprevised2014nov.pdf. !- Definitions and concepts: Covered (eligible) account: a deposit type included by law. Fully insured vs. partially insured: “Fully insured” balances are ≤ the coverage limit per depositor, per bank, per ownership category; “covered/eligible” may include accounts whose balances exceed the cap (partially insured). Ownership categories: individual, joint, trust/fiduciary, retirement—rules vary by jurisdiction and affect aggregation across accounts. Indicator variants: % Eligible accounts = eligible deposit accounts ÷ total deposit accounts. Insured balance share = insured amounts in eligible accounts ÷ total deposit balances in eligible accounts. Dormancy: dormant accounts may be treated differently in coverage statistics.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in the number of deposit accounts covered by direct deposit insurance? How do these disparities vary by age, income level, and geographic location? Are certain gender groups, especially within vulnerable or low-income populations, less likely to hold insured deposit accounts? How do the average insured deposit account balances differ across genders, and what might this indicate about savings behavior, access to financial protection, or economic security? Do financial service providers with higher levels of gender diversity in leadership or staff tend to offer more equitable access to insured deposit accounts and balanced coverage across genders? Additionally, how do gender differences in insured deposit accounts relate to broader financial inclusion and resilience against financial shocks?</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Quality, Suitability</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Deposit account type</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Depositor protection</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Savings</t>
+        </is>
+      </c>
+      <c r="D125">
         <v>16</v>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>G2P accounts covered by deposit insurance</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>% of all accounts receiving G2P payments that are covered by deposit protection</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>This indicator helps analyze the extent to which low-value accounts are covered by deposit insurance or other protection. It focuses on account holders who are recipients of G2P programs. It quantifies how many of the government-to-person (G2P) payments recipients are protected by an explicit deposit insurance scheme or guarantee fund. It can be shown as (a) the share of G2P accounts that are eligible/fully insured and/or (b) the insured share of G2P balances. This indicator informs strategies for insurance/coverage payouts and the calibration of the deposit insurance fund. Definitions  and concepts: G2P account: an account that receives social transfers, government pensions, subsidies, or cash-benefit programs.
 Covered (eligible) vs. fully insured: “Eligible” products fall within the deposit insurance scope; “fully insured” means the balance per beneficiary per insured bank does not exceed the coverage cap. 
@@ -6949,664 +6950,549 @@
 Core-banking (and, where applicable, e-money) extracts: product code, ownership category, end-of-day balance, currency. Rules engine encoding national deposit-insurance scope, limits, and aggregation logic (per depositor—per bank). Sub-ledger data for pooled/FBO accounts to support pass-through eligibility. Timing sensitivity: balances spike on disbursement days; define the snapshot (e.g., month-end vs. T+2 after payout).</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="H125" t="inlineStr">
         <is>
           <t>Are there gender disparities in the number of G2P accounts covered by deposit insurance? How do these disparities vary across different age groups, income levels, and geographic locations? Are women and other gender groups within vulnerable populations less likely to have G2P accounts that are insured, potentially affecting their financial security? How do the average balances of insured G2P accounts compare across genders, and what does this imply about economic empowerment and financial resilience? Do government programs and financial service providers with greater gender diversity in design or delivery show more equitable insurance coverage of G2P accounts? Additionally, how do gender differences in insured G2P accounts influence overall inclusion and access to social safety nets?</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>Quality, Suitability, Depositor protection</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Quality, Suitability, Stability</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
+    <row r="126">
+      <c r="A126" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D124">
+      <c r="D126">
         <v>183</v>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E126" t="inlineStr">
         <is>
           <t>Average cost-to-borrower for unsecured retail lending</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>Average topline revenue earned from unsecured retail credit operations (as percentage of the average outstanding unsecured credit)</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>This indicator is a portfolio-level proxy for the all-in price actually paid by customers on unsecured retail credit during the period. It answers: How many currency units of revenue did the lender earn for each 100 units of average unpaid balance? Rising values may reflect higher base rates, heavier fee reliance (e.g., late/over-limit charges), or a shift toward shorter-tenor/high-yield products; falling values can indicate competitive pressure, promotional pricing, or relief programs. Boards, supervisors, and consumer-protection teams use it to benchmark pricing fairness, earnings quality, and sensitivity to interest-rate cycles. !- Definitions and concepts: Recommended numerator (topline revenue, P&amp;L-recognized): Interest income (EIR basis) + contractual fees (origination, servicing) + penalty/default interest actually recognized + punitive fees (late, over-limit, returned-payment) − waivers/reversals. Denominator: Average outstanding unsecured retail balances (use Average Daily Balance - ADB). Formula: Cost-to-customer yield = Topline revenue from unsecured retail credit divded by Average outstanding unsecured retail balances. This indicator can be reported separately for interest, contractual fees and penalities if the data is available and when the period is less than 12 months, report an annualized figure. !- Data requirements: General ledger and product-level revenue broken into interest, contractual fees, penalty interest, punitive fees; flags for waivers/reversals and non-accrual. Loan/card-level balances to compute ADB, segmented by product (cards, instalment, overdraft, BNPL), channel, and risk bucket. Accounting policies: EIR vs. cash, Stage-3/non-accrual treatment, capitalization rules.
 FX mapping for multi-currency portfolios. !- Limitations and considerations: Comparability: EIR vs. cash accounting and non-accrual practices differ; disclose methodology. Mix effects: more revolving/short-tenor loans inflate yields; always segment. Penalty bias: high ratios may be driven by a small cohort repeatedly paying fees—track % customers incurring penalties. Promotions/teasers: intro 0% and fee holidays distort short periods—show trailing-12-month and cohort views. Scope creep: exclude bundled insurance premiums or merchant discounts (BNPL) unless consistently included and disclosed.</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="H126" t="inlineStr">
         <is>
           <t>Are there gender disparities in the percentage of topline revenue relative to outstanding loan balances? Is there any gender paying comparatively more than market percentages for the same account types? How do FSPs rank in terms of these percentages by gender?</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="L126" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
+    <row r="127">
+      <c r="A127" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D125">
+      <c r="D127">
         <v>181</v>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E127" t="inlineStr">
         <is>
           <t>Revenue generated by unsecured credit</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>% of total topline revenue attributable to unsecured credit operations and interest and non-interest revenue proportions</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>This indicator captures the total income that a lending institution earns from unsecured credit products—credit cards, personal instalment loans, overdrafts, payday and buy-now-pay-later (BNPL) facilities—over a reporting period. Because unsecured lending is typically high-yield and high-risk, tracking its revenue helps supervisors and management understand how much of the institution’s top line depends on products that are more sensitive to economic downturns, job-market shocks and aggressive competition. A rising share can boost short-term profitability, but it may also presage higher future credit losses and conduct-risk concerns if underwriting standards slip. !- Definitions and concepts: Unsecured credit – loans that are not backed by collateral; repayment relies on the borrower’s cash flow and creditworthiness.
 Revenue components – Interest income (accrued and collected) from outstanding balances. Fee income: annual fees, origination fees, late-payment charges, interchange on card transactions, BNPL merchant discount rates. Net insurance or payment-protection premiums (if bundled) may be included subject to local accounting rules.
 Revenue share metric: Unsecured-credit revenue ÷ Total lending revenue expresses concentration risk. Risk-adjusted yield – revenue net of credit-loss provisions gives a clearer view of economic profitability. !- Data requirements: Product-level general-ledger extracts segregating interest, fees and other income. Loan-level flags identifying collateral status (secured vs. unsecured). Average daily or month-end balances to compute effective yields. Associated credit-loss provisions and write-offs for risk-adjusted analysis. !- Limitations and considerations: Mixed products: Some personal loans are partially secured (e.g., salary-linked) or carry optional collateral; clear taxonomy is essential. Fee recognition rules: Capitalised origination fees amortised under effective-interest-rate (EIR) accounting may blur timing comparisons across banks or jurisdictions. Regulatory caps: Interest-rate or fee ceilings (e.g., usury limits) affect revenue potential and comparability. Promotional pricing: Introductory 0 % card offers or BNPL “pay-in-4” models generate deferred revenue; headline figures may understate future income. Economic cyclicality: Unsecured-credit revenue can fall sharply in recessions as balances contract and charge-offs rise; pairing with delinquency and provision metrics is crucial for a full risk-return picture.</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>What proportion of total topline revenue comes from unsecured credit operations, and are there gender disparities in this distribution? How do FSPs rank in their reliance on unsecured credit revenue by gender?</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D126">
+      <c r="D128">
         <v>198</v>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>Insurance approved claims not paid</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>% of approved/accepted claims that remain unpaid to customers</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>This indicator shows the share of claims that have been approved (final liability accepted) but not yet disbursed to the claimant. A high rate flags operational bottlenecks or weak payout controls, directly impacting customer outcomes. Track alongside claims turnaround time, claims rejection rates, and complaints, to get a full picture of payout effectiveness and customer fairness. !- Definitions and concepts: Approved / accepted claim: a claim with a final decision to pay (post-analysis), a recorded payable, and no outstanding dispute. Unpaid status: no successful settlement to the beneficiary by period end. Formula: Amount weighted (unpaid approved amount ÷ approved amount) reveal economic impact. Count basis (# approved claims not paid by cut-off ÷ # claims approved in teh period). SLA variant: % not paid within X days of approval (e.g., 5/10/30 days) to neutralize end-period timing bias. Treatment of partial payments: disclose whether partially paid claims are counted as unpaid or excluded. The indicator may also track the reasons for non-payment, if these are standardized for reporting. !- Limitations and considerations: Cut-off effects: approvals late in the period will naturally be unpaid—use the SLA variant and report both snapshot and flow views. Reopened claims / appeals: specify whether reversals after approval are removed from both numerator and denominator. Segmentation: monitor by line of business, payment method, channel, and claim size to target fixes.</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="H128" t="inlineStr">
         <is>
           <t>How do the average values of outstanding insurance claims compare by gender? Is there a gender group with consistently higher average unpaid claims? How do different FSPs rank in terms of outstanding claims by gender? Are vulnerable gender groups disproportionately affected by delayed or unpaid claims?</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
         <is>
           <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
+      <c r="K128" t="inlineStr">
         <is>
           <t>Quality, Reputational and legal risk</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
+      <c r="L128" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D127">
+      <c r="D129">
         <v>256</v>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E129" t="inlineStr">
         <is>
           <t>Insurance claims declined</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>% of claims logged by policyholders that are declined prior to substantive analysis</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>This indicator captures the share of claim notifications the insurer does not accept for assessment at the front door—typically during first notice of loss (FNOL)/triage—because they are ineligible or incomplete. A high intake-decline rate can point to unclear policy wording, poor customer guidance, data-capture frictions, or overly strict gatekeeping. It is a key conduct-risk and customer-experience signal and, operationally, helps size avoidable workload versus genuinely assessable claims. Claim logged / FNOL: the moment a policyholder submits a claim or loss notice. Declined at intake (non-acceptance): the insurer refuses to open an assessable claim before investigation (e.g., policy not in force, peril not covered, waiting period, duplicate claim, claim below deductible/threshold, incomplete mandatory data not cured within a set window). Indicator formula (count basis): # claims declined at intake in period divided by # claim notifications received in period . Variants: exclude cured cases later resubmitted; report by product/channel. !- Data requirements: Claims-intake system fields: FNOL timestamp, policy ID/status at loss date, coverage/peril checks, deductible, mandatory-document checklist, triage outcome. Standardised reason codes (e.g., not covered, lapsed, duplicate, below excess, incomplete info). Deduplication logic (policyholder ID + incident date + peril). Linkage to resubmissions/appeals and to complaint records for outcome tracking. !- Limitations and considerations: Definition variance: what counts as “prior to analysis” differs; some firms place incomplete cases in “pending info” instead of “declined,” affecting comparability.
 Gaming risk: shifting cases to “withdrawn” or “pending” to improve this metric; require audit trails and age-off rules. Mix effects: products with low deductibles or mandatory documents (e.g., health) have different baseline rates—segment results. Customer fairness: high early declines may reflect confusing onboarding or exclusion wording; monitor alongside claims rejection rate (post-assessment), turnaround time, and complaints upheld. Resubmission policy: disclose whether cured resubmissions are excluded from the numerator to avoid double counting.</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>What percentage of claims logged by policyholders are declined, disaggregated by gender? How do these decline rates vary across FSPs, policy types, age groups, and locations? Are there notable gender disparities in claim declines at the market level or within specific providers? Are women or other gender groups more likely to face claim denial?</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>Quality,</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D128">
+      <c r="D130">
         <v>60</v>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>Insurance claims rejection rate</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>% of all insurance claims that are rejected by insurers (post-analysis)</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>The claims rejection rate shows the share of claims that an insurer declines to pay—fully or partially—relative to the total number (or value) of claims submitted in a period. Because denial directly affects customer trust, supervisors use the metric to monitor fair treatment outcomes, detect aggressive underwriting or opaque policy wording, and flag operational shortcomings. A sudden rise may presage reputational damage, regulatory sanctions, or litigation costs, while an unusually low rate can hint at lax fraud controls or inadequate claims processing. !- Definitions and concepts: Claims rejected (denied): claims for which the insurer issues a final communication refusing payment on contractual grounds (e.g., policy exclusions, lapsed cover, misrepresentation) or on fraud findings. !- Limitations and considerations: Definition divergence: Some regimes class “claims closed without payment” (due to missing documents) as rejections; others record them as pending, complicating cross-market comparison. Fraud vs. technical denial: Combining fraud rejections with contractual exclusions can blur very different issues. Separate reporting is best practice. Volume vs. value: A single large, legitimately denied loss can distort amount-based ratios; analysts should monitor both count and value metrics.
 Appeals and reversals: Denials overturned on review lower true rejection rates; timely data updates are essential.
 Incentive effects: Over-emphasis on low rejection rates may weaken fraud vigilance, whereas strict targets can push staff toward technical denials—pair the indicator with complaint ratios, turnaround times, and fraud-detection statistics for balanced oversight.</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="H130" t="inlineStr">
         <is>
           <t>Are there gender disparities in the rejection rates of insurance claims, including for MSMEs by owner gender? Which types of policies or claims see higher rejection rates, and do these differ by gender? How does claim rejection relate to coverage levels and turnaround times? Do FSPs with higher gender diversity have lower rejection rates for vulnerable gender groups?</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="L130" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D129">
+      <c r="D131">
         <v>201</v>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>Insurance claims settlement ratio</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>% of insurance claims logged by policyholders that have been paid by insurers</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>Measures the percentage of insurance claims settled by an insurer out of the total claims it receives. It is a direct measure of an insurer's reliability and its commitment to fulfilling its primary promise to policyholders. This indicator is a cornerstone of conduct supervision, as it provides a quantitative view of how an insurer treats its customers at their most critical moment of need. For prudential supervisors, it could help analysis of operational and reputational risk. This indicator should be used together with other indicators on the performance of the claims process in the insurance sector.</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="H131" t="inlineStr">
         <is>
           <t>How do claim settlement ratios vary by gender? Are any gender groups receiving lower settlement ratios compared to the market average? Are there FSPs with particularly low or high settlement ratios for certain genders? How do these ratios intersect with policy type and customer demographics?</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
         <is>
           <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="K131" t="inlineStr">
         <is>
           <t>Outcomes, Reputational and legal risk</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="L131" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D130">
+      <c r="D132">
         <v>59</v>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>Insurance claims turnaround time</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>Average number of days to process insurance claims</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>This indicator captures the average calendar days an insurer takes to settle a claim—from the claim filing date to the final payment or formal denial. It is a direct yard-stick of operational efficiency and customer experience. Shorter turnaround times (TATs) enhance policy-holder trust, limit reputational risk, and can lower claims handling expenses. Supervisors use the metric to enforce fair-treatment rules, while actuaries and underwriters link it to reserving accuracy—prolonged settlement can signal documentation bottlenecks, fraud investigations, policy transparency issues, or catastrophic complexity that may keep outstanding reserves elevated. !- Definitions and concepts:  Start point – the timestamp when the insurer first receives the claim request. End point – the date the insurer issues full payment, partial final payment, or a written denial. Average turnaround time (TAT) – arithmetic mean; many firms also monitor median and 90th-percentile to limit outlier masking.
 Segmented TATs – tracked by line of business, claim severity band, and distribution channel to isolate problem areas.
 !- Limitations and considerations: Partial settlements: Recording the date of first partial payment can understate full-and-final completion time. Dispute and litigation pauses: Regulatory or court‐mandated suspensions inflate TAT yet lie outside managerial control.</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="H132" t="inlineStr">
         <is>
           <t>Are there gender disparities in the average time taken to process and settle insurance claims? How does processing time vary by policy type, premium, claim amount, and customer demographics? Are insurers with lower gender diversity more likely to have longer turnaround times? Are vulnerable gender groups disproportionately affected by delays?</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>Investments</t>
         </is>
       </c>
-      <c r="D131">
+      <c r="D133">
         <v>207</v>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E133" t="inlineStr">
         <is>
           <t>Net rate of return on investments</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>% point differential between the average rates of returns on investments and the average performance/administration fees charged</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>Measures the profitability of a financial institution's own investment portfolio after accounting for all associated costs. It reveals the actual, bottom-line gain or loss generated by the institution's securities, real estate, or other investments. This is a fundamental indicator of an institution's ability to effectively manage its own capital and generate profit from non-lending activities, of particular importance to prudential supervisors, including supervisors of insurance and pension administrators. Net Rate of Return (%)= 
 [(Market Value final-Market Value initial+Income−Expenses)/Market Value initial]×100</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>How do net returns (% returns minus % performance fees and charges) on longer-term investments compare by gender? Do net returns for any gender differ from the overall market average for similar investment products? How do FSPs compare in terms of net returns earned by gender?</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr">
+      <c r="J133" t="inlineStr">
         <is>
           <t>Market development</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
+      <c r="K133" t="inlineStr">
         <is>
           <t>Capital markets development</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
+      <c r="L133" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>Savings</t>
         </is>
       </c>
-      <c r="D132">
+      <c r="D134">
         <v>159</v>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>Average cost-to-customer for transaction accounts</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>Average topline revenue earned per account holder as % of average account balances</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>This indicator estimates the effective price of holding and using a transaction account, expressed as a yield on the customer’s average balance. By computing it for each account type (e.g., basic/no-frills, standard retail, premium, SME, e-money wallet), it reveals where pricing and usage frictions are highest. It helps supervisors assess fairness, inclusion quality, and reliance on fee income. !- Definitions and concepts: Non-interest fees: maintenance/inactivity, ATM/network, FX/transfer, statement/card fees, overdraft &amp; returned-payment fees tied to the account. 
 Per account-holder basis: aggregate all accounts of the same type per customer, then average (also show balance-weighted results). !- Data requirements: Core-banking data: customer ID, account type tags, average daily balance by customer for each account type, interest credited, revenue by fee code linked to accounts; flags for waivers/refunds/chargebacks. Channel/product hierarchies (basic vs. premium, retail vs. SME, wallet vs. bank account) and currency/FX mapping. Optional: usage indicators (transactions per month) to explain differences across types.</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="H134" t="inlineStr">
         <is>
           <t>Are there gender disparities in the costs (fees, charges) borne by account holders of transaction accounts? Do women tend to hold transaction accounts with higher fee burdens (relative to income or transaction frequency) than men, particularly in certain regions or among lower‐income groups? How do costs compare across FSPs with different levels of gender diversity? Is fee structure or cost‐to‐customer a barrier to transaction usage for some gender/age/income cohorts?</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
+      <c r="L134" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Financial service provider (FSP) type; Account type</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Fair treatment</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D133">
-        <v>226</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Rejections of product applications</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>% of all applications that are rejected by product type</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Measures the proportion of customer applications for financial products that are rejected by regulated financial institutions during the reporting period. The indicator is calculated as the percentage of total applications received—across products such as loans, credit cards, deposit accounts, or insurance policies—that were not approved or accepted. Captures the extent of unmet demand or access barriers in financial markets, as well as aspects of market conduct, underwriting practices, and risk appetite among providers. It provides insight into how easily consumers and businesses can obtain financial products. Monitoring rejection rates helps authorities: Identify potential access constraints or discriminatory lending or sales practices; Evaluate the tightness of credit or account-opening standards; Assess consumer protection outcomes and fair treatment; Detect sudden shifts in provider risk tolerance or macro-prudential conditions (e.g., post-crisis credit tightening). High rejection rates may indicate stringent eligibility criteria, weak applicant creditworthiness, or barriers to financial access. Declining rates may suggest improving inclusion or relaxation of underwriting standards. Cross-product comparisons reveal whether certain markets (e.g., credit vs. deposits) are more exclusionary. !- Definitions and concepts: Application: A formal request by a customer to obtain a financial product or service. Rejection: A decision by the provider not to approve, issue, or open the requested product, whether automated or manual. Product type: Category of financial service applied for (loan, deposit, insurance, card, etc.). !- Data requirements: Product application records from regulated financail institutions that can yield the total number of applications rejected and the total number of applications received during the reference period. Disaggregation variables for segmentation analysis: product type, applicant type (individual, MSME), gender etc.</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>How do rejection rates vary by gender? Are rejection rates higher for any gender in specific channels? How do rejection rates in physical channels compare to those in digital channels by gender? How do FSPs rank in terms of rejection rates by gender across available channels? For loans, when analyzed alongside the indicator "Customers by credit score," are there gender disparities in rejection rates by credit score?</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D134">
-        <v>175</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Payroll loans</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>% of all retail borrowers (or loans) that have payroll loans (repayments deducted directly of wages deposited into the customer's account)</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Measures the prevalence of payroll lending in the retail loan portfolio. !- Definitions and concepts: A payroll loan (also called a payroll-deducted loan, salary loan) is a personal consumer loan whose installments are automatically withheld from the borrower’s pay-check (or pension/social-security benefit) and remitted directly to the lender each pay period. Because repayment is taken “off the top” of the employee’s gross salary, the borrower’s future income effectively serves as collateral, giving lenders high repayment certainty and allowing them to charge lower rates than on unsecured personal loans. !- Data requirements:  Loan-level records with ability to identify payroll loans (e.g. product code or terms of loan that specify the repayment modality). Unique customer ID in order to extract unique number of borrowers with payroll loans.</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in the share of retail borrowers accessing payroll loans, and how do these differences vary by age, income, and location? Do women or other gender groups have equal access to payroll loan products compared to men, or are there structural or employment-related barriers affecting uptake? How does the prevalence of payroll loans among borrowers relate to their employment types and sectors, and are certain gender groups more represented in these segments? Are financial service providers with greater gender diversity more likely to offer payroll loans equitably across genders? How do repayment behaviors and default rates on payroll loans differ by gender, and what implications does this have for financial inclusion and debt sustainability?</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>Uptake (account ownership)</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -7618,36 +7504,35 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>Fair treatment</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D135">
-        <v>172</v>
+        <v>226</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>First-time borrowers</t>
+          <t>Rejections of product applications</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>% of borrowers who are first-time borrowers with the FSP (or in the financial system)</t>
+          <t>% of all applications that are rejected by product type</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>This indicator shows the share of active borrowing retail customers who are new to the lender (new-to-bank/FSP) or new to formal credit altogether (new-to-credit, NTC). It is a direct barometer of financial inclusion and retail credit growth. A higher share can signal effective onboarding and market expansion, but it also shifts portfolio risk: NTC borrowers may lack repayment histories, making underwriting more model-driven and subject to greater uncertainty. Supervisors and lenders can monitor this metric to balance inclusion objectives with prudent risk management and to evaluate the effectiveness of credit-bureau coverage. !- Definitions and concepts: First-time borrower (FSP scope): a customer with no prior loan or credit line ever booked by the FSP before the reference period. First-time borrower (system scope / NTC): a customer with no prior loan or credit line reported to the national credit registry/bureau within a defined historical look-back (commonly “ever,” or a long horizon such as 5–10 years). This indicator is obtained by dividing the number of first-time borrowers by the total number of borrowers. Variants of this indicator include: value-weighted (by origination amount), new originations only (versus the entire active book), and cohort-based analysis (by origination month or quarter). !- Data requirements: Customer master records with unique, reliable identifiers (national ID/tax ID; deduplicated across branches). Loan-booking history from the FSP’s core systems. Credit-bureau/registry match results (for system-wide NTC status). Product taxonomy (include/exclude credit cards, overdrafts, BNPL) and reference dates. Limitaitons and considerations: Coverage gaps: thin or partial bureau coverage, informal lenders, or non-reporting segments can misclassify NTC status.
-Identifier quality: name changes, multiple IDs, or data-entry errors cause false “first-time” flags; robust deduplication is essential. Look-back window choice: shorter windows inflate “first-time” shares; disclose methodology. Product scope: excluding revolving credit or microloans biases results.</t>
+          <t>Measures the proportion of customer applications for financial products that are rejected by regulated financial institutions during the reporting period. The indicator is calculated as the percentage of total applications received—across products such as loans, credit cards, deposit accounts, or insurance policies—that were not approved or accepted. Captures the extent of unmet demand or access barriers in financial markets, as well as aspects of market conduct, underwriting practices, and risk appetite among providers. It provides insight into how easily consumers and businesses can obtain financial products. Monitoring rejection rates helps authorities: Identify potential access constraints or discriminatory lending or sales practices; Evaluate the tightness of credit or account-opening standards; Assess consumer protection outcomes and fair treatment; Detect sudden shifts in provider risk tolerance or macro-prudential conditions (e.g., post-crisis credit tightening). High rejection rates may indicate stringent eligibility criteria, weak applicant creditworthiness, or barriers to financial access. Declining rates may suggest improving inclusion or relaxation of underwriting standards. Cross-product comparisons reveal whether certain markets (e.g., credit vs. deposits) are more exclusionary. !- Definitions and concepts: Application: A formal request by a customer to obtain a financial product or service. Rejection: A decision by the provider not to approve, issue, or open the requested product, whether automated or manual. Product type: Category of financial service applied for (loan, deposit, insurance, card, etc.). !- Data requirements: Product application records from regulated financail institutions that can yield the total number of applications rejected and the total number of applications received during the reference period. Disaggregation variables for segmentation analysis: product type, applicant type (individual, MSME), gender etc.</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Do first-time borrowers reflect a balanced gender representation, or are there gender disparities? How do FSPs rank in onboarding typically underserved borrowers, and does this ranking change when analyzed by gender?</t>
+          <t>How do rejection rates vary by gender? Are rejection rates higher for any gender in specific channels? How do rejection rates in physical channels compare to those in digital channels by gender? How do FSPs rank in terms of rejection rates by gender across available channels? For loans, when analyzed alongside the indicator "Customers by credit score," are there gender disparities in rejection rates by credit score?</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7662,12 +7547,12 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Uptake (account ownership)</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7564,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Suitability, Impact</t>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9375,12 +9260,12 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
+          <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Outcomes, Suitability, Credit risk</t>
+          <t>Outcomes, Suitability</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -9435,12 +9320,12 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
+          <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Quality, Suitability,</t>
+          <t>Quality, Suitability</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -9495,12 +9380,12 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
+          <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Quality, Suitability,</t>
+          <t>Quality, Suitability</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -9550,12 +9435,12 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
+          <t>Consumer protection</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Outcomes, Safety and security, Credit risk</t>
+          <t>Safety and security</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -9605,12 +9490,12 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
+          <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Outcomes, Suitability, Credit risk</t>
+          <t>Outcomes, Suitability</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -9665,12 +9550,12 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
+          <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Outcomes, Suitability, Credit risk, Soundness, Stability</t>
+          <t>Outcomes, Suitability</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -9806,16 +9691,6 @@
       <c r="H172" t="inlineStr">
         <is>
           <t>Is there a correlation between higher levels of gender diversity in FSPs and lower risk levels?</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>Statistics and research</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -10092,7 +9967,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Quality,Suitability</t>
+          <t>Quality, Suitability</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -10531,16 +10406,6 @@
           <t>Do financial service providers (FSPs) with higher gender diversity in leadership or governance report different interest margin ratios compared to less gender‑diverse peers? Are there associations between the gender composition of the customer base (e.g. share of women borrowers/depositors) and margin outcomes? Could gendered pricing—such as differential rates offered to male vs. female clients—impact FSP interest margins? Over time, do changes in margin ratios correlate with shifts in gender inclusion (e.g. more women customers or staff)?</t>
         </is>
       </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
@@ -10588,12 +10453,12 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Financial inclusion; Other</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Outcomes, Statistics and research</t>
+          <t>Outcomes</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -10745,7 +10610,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Soundness</t>
+          <t>Soundness, Credit risk</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -10774,16 +10639,6 @@
       <c r="H191" t="inlineStr">
         <is>
           <t>Is there a relationship between gender diversity in leadership or equity ownership and ROE performance across FSPs? Are FSPs that prioritize gender inclusion more likely to achieve higher equity returns, possibly through broader market reach or more balanced risk management? How does the gender mix of customers, especially depositors and borrowers, relate to ROE outcomes? Over time, do improvements in gender inclusion (in staffing or customer base) precede or follow changes in ROE?</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>Other; Consumer protection; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>Statistics and research, Impact, Credit risk</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -11070,12 +10925,12 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Other; Stability, safety and soundness</t>
+          <t>Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Statistics and research, Credit risk, Stability</t>
+          <t>Credit risk, Stability</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -11235,12 +11090,12 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Financial inclusion; Other; Stability, safety and soundness</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Uptake, Statistics and research, Impact</t>
+          <t>Uptake (account ownership)</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -11295,12 +11150,12 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Uptake, Impact</t>
+          <t>Uptake (account ownership)</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -11355,12 +11210,12 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Usage, Impact</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -11410,12 +11265,12 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Financial inclusion; Other</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Usage, Statistics and research</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -11463,16 +11318,6 @@
           <t>Are there gender disparities in the acquisition/holding of green/sustainable bonds? Are FSPs with higher levels of gender diversity more likely to distribute sustainable or green bonds to a more diverse investor base?  Comparing this with gender diversity at FSPs, are institutions with higher levels of gender diversity more likely to have larger green/sustainable portfolios?</t>
         </is>
       </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>Other; Market development</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>Statistics and research, Sustainability</t>
-        </is>
-      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
@@ -11520,12 +11365,12 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Financial inclusion; Other; Market development</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Usage, Statistics and research, Sustainability</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -11628,11 +11473,6 @@
           <t>Are there gender disparities in workforce participation across different types of FSPs? At what responsibility levels? How does gender diversity in FSP management correlate with key financial indicators (e.g., Stability, Financial Inclusion, Customer Protection, Sustainability)? Comparing with climate-related financial data (e.g., green loan portfolios, green insurance), does gender diversity in FSPs correlate with the growth of these portfolios? If legal or regulatory gender equity requirements exist for FSPs, are they being met? Does gender diversity correlate with variations in supervisory risk scores? How does gender diversity correlate with staff turnover (if data is available)? How does gender diversity correlate with enforcement and other supervisory actions?</t>
         </is>
       </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection; Stability, safety and soundness; Market development</t>
-        </is>
-      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
@@ -11678,11 +11518,6 @@
           <t>Are there significant gender disparities in the composition of customers across different types of financial service providers (FSPs)? How does the gender diversity of the FSP customer base vary by institution size, sector, and geographic region? What correlations exist between the gender diversity of the customer base and key financial inclusion metrics such as account ownership, loan uptake, and insurance coverage? How does greater gender diversity among customers relate to customer protection outcomes, including complaint resolution and fair treatment? Are FSPs with more gender-diverse customer bases also demonstrating stronger prudential performance and sustainability indicators? How do gender disparities in the customer base influencefinancila outcomes such as Financial Health? And broader social and economic outcomes, such as women's economic empowerment, MSME growth, climate change, jobs creation or poverty reduction?</t>
         </is>
       </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection; Stability, safety and soundness; Market development</t>
-        </is>
-      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
@@ -11728,11 +11563,6 @@
           <t>Are there gender disparities in compensation for similar positions or responsibilities (Board, management, staff)? How does this compare with other macro indicators related to financial stability and portfolio performance across FSPs (credit, insurance, investment funds, pensions)? Are FSPs with greater gender diversity in the Board more likely to present lower gender pay gap?</t>
         </is>
       </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection; Stability, safety and soundness; Market development</t>
-        </is>
-      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
@@ -11779,11 +11609,6 @@
           <t>How do financial service providers (FSPs) compare in their Human Resources Gender Index (HRGI) scores? Are FSPs with higher levels of gender diversity in their workforce more likely to perform better across the various HRGI dimensions, such as recruitment, retention, promotion, and leadership representation? When comparing HRGI scores with key performance indicators (e.g., capital and liquidity, profitability, efficiency, customer satisfaction, innovation), is there evidence of a positive correlation? How do HRGI scores vary by FSP type, size, or region, and what best practices can be identified from top performers? How does HRGI performance relate to gender-related outcomes, such as gender-balanced customer bases or inclusive product offerings?</t>
         </is>
       </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection; Stability, safety and soundness; Market development</t>
-        </is>
-      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
@@ -11807,36 +11632,26 @@
         </is>
       </c>
       <c r="D211">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>New licenses granted to diverse FSPs</t>
+          <t>Success rate of license applications by diverse FSPs</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>% of all new licenses that are issued to diverse FSPs</t>
+          <t>% of all license applications by diverse FSPs that are issued</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>This indicator is a measure of the gender composition of newly licensed financial institutions. It helps regulators and policy makers identify trends in the gender diversity in the financial sector by looking at the leadership of financial institutions. For fuller more complete analysis, this indicator can be complemented by an indicator of the success rate of licensing applications, considering the gender of the lead sponsor.</t>
+          <t>This indicator is a measure of potential gender biases in licensing decisions by the financial authority. It helps authorities analyze the success rate of license pplications by segmenting applications by their final oucome (rejection/approval), and the gender of the lead sponsor of the application (e.g., the majority individual shareholder). The definition of lead sponsor will vary across countries and the indicator should align with local practices.</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>What are the trends in the number of new licenses issued to diverse FSPs?</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>Other; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>Statistics and research,  Stability</t>
+          <t>To what extent does the gender of individuals in leadership or control positions within the proposed FSPs influence the likelihood of obtaining a license from the regulatory authority?</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -11848,45 +11663,55 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Sustainability</t>
+          <t>Market development</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Gender equality</t>
+          <t>Capital markets development</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="D212">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Success rate of license applications by diverse FSPs</t>
+          <t>Crowdfunding - Differential rate of return (equity)</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>% of all license applications by diverse FSPs that are issued</t>
+          <t>Difference between the advertised/promised rate of return and the actual rate of return of equity in crowdfunding projects</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>This indicator is a measure of potential gender biases in licensing decisions by the financial authority. It helps authorities analyze the success rate of license pplications by segmenting applications by their final oucome (rejection/approval), and the gender of the lead sponsor of the application (e.g., the majority individual shareholder). The definition of lead sponsor will vary across countries and the indicator should align with local practices.</t>
+          <t>Measures the gap between the projected or advertised rate of return presented to investors before a project is funded and the actual rate of return realized after the project is completed. This is a critical conduct indicator that measures the accuracy of a project's promises versus its real-world performance. For investors, this metric is a tool for due diligence. For conduct supervisors, it can be used to detect mis-selling and fraud. A large and persistent negative differential (where actual returns are consistently far below promised returns) is a red flag. it could flag issues such as inadequate risk disclosure and fraud. When gender disaggregated by the gender of the main sponsor or lead executive, the indicator can provide additional information. If projects led by women consistently show a smaller negative "reality gap" (meaning their actual returns are closer to their promised returns), it could suggest they are more conservative or accurate in their financial projections. This would be a crucial data point in assessing risk and investor protection. Using this indicator together with the indicator on rejected crowddfunding projects could strenghten the identification of gender bias inside the securities authority. Return Differential (%) = Actual Rate of Return - Advertised/Promised Rate of Return.</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>To what extent does the gender of individuals in leadership or control positions within the proposed FSPs influence the likelihood of obtaining a license from the regulatory authority?</t>
+          <t>Are there differences in the rates of return for crowdfunding projects depending on the gender assigned to the MSME seeking funding?</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Uptake (account ownership)</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -11907,36 +11732,26 @@
         </is>
       </c>
       <c r="D213">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Crowdfunding - Differential rate of return (equity)</t>
+          <t>Crowdfunding - Authorization rejection rate</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Difference between the advertised/promised rate of return and the actual rate of return of equity in crowdfunding projects</t>
+          <t>% of all crowfunding applications that are rejected (not authorized by the securities authority)</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Measures the gap between the projected or advertised rate of return presented to investors before a project is funded and the actual rate of return realized after the project is completed. This is a critical conduct indicator that measures the accuracy of a project's promises versus its real-world performance. For investors, this metric is a tool for due diligence. For conduct supervisors, it can be used to detect mis-selling and fraud. A large and persistent negative differential (where actual returns are consistently far below promised returns) is a red flag. it could flag issues such as inadequate risk disclosure and fraud. When gender disaggregated by the gender of the main sponsor or lead executive, the indicator can provide additional information. If projects led by women consistently show a smaller negative "reality gap" (meaning their actual returns are closer to their promised returns), it could suggest they are more conservative or accurate in their financial projections. This would be a crucial data point in assessing risk and investor protection. Using this indicator together with the indicator on rejected crowddfunding projects could strenghten the identification of gender bias inside the securities authority. Return Differential (%) = Actual Rate of Return - Advertised/Promised Rate of Return.</t>
+          <t>Measures the percentage of all crowdfunding applications submitted to a securities authority that are denied or not authorized to proceed with fundraising. This is a key regulatory indicator that reflects the quality of applications being submitted and the stringency of the regulator's vetting process, which is designed to protect investors from fraud and non-viable projects. When disaggregated by the gender of the main sponsor, the lead executive of the company, it could draw insights into potential gender biases working within the securities authority.</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Are there differences in the rates of return for crowdfunding projects depending on the gender assigned to the MSME seeking funding?</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Other</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>Uptake (account ownership), Statistics and research</t>
+          <t>Are there gender disparities in the rejection rates and the reasons for rejection of crowdfunding projects presented for authorization by the securities regulator?</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -11962,26 +11777,36 @@
         </is>
       </c>
       <c r="D214">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Crowdfunding - Authorization rejection rate</t>
+          <t>Crowdfunding - Success rate</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>% of all crowfunding applications that are rejected (not authorized by the securities authority)</t>
+          <t>% of all crowfunding projects that are successful in raising the asked amount</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Measures the percentage of all crowdfunding applications submitted to a securities authority that are denied or not authorized to proceed with fundraising. This is a key regulatory indicator that reflects the quality of applications being submitted and the stringency of the regulator's vetting process, which is designed to protect investors from fraud and non-viable projects. When disaggregated by the gender of the main sponsor, the lead executive of the company, it could draw insights into potential gender biases working within the securities authority.</t>
+          <t>The indicator is a metric that measures the proportion of projects on a crowdfunding platform (or the sum of all crowdfunding platforms) that successfully reach their predetermined funding goal within a specified timeframe. This indicator is a vital sign of a platform's effectiveness, credibility, and the overall health of its ecosystem. It helps gauge the ability of a platform to connect viable projects with interested backers. For MSMEs, crowdfunding can be a viable and less onerous funding source, so the indicator provids important information for monitoring development of MSME finance markets. From a market conduct perspective, while a high success rate is generally positive, an unusually high or artificially inflated rate could be a red flag for misconduct. Platforms could be setting trivially low funding goals to boost statistics,  failing to conduct proper due diligence on projects, or not being transparent about how the success rate is calculated. Successful projects is the number of projects that met or exceeded their funding target during a specific period (e.g., a month, quarter, or year).</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the rejection rates and the reasons for rejection of crowdfunding projects presented for authorization by the securities regulator?</t>
+          <t>Are there gender disparities in the success rates of crowdfunding projects? Are smaller or younger MSMEs headed by women more likely to face challenges in crowdfunding?</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Usage</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -12007,36 +11832,26 @@
         </is>
       </c>
       <c r="D215">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Crowdfunding - Success rate</t>
+          <t>Crowdfunding - Transactions</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>% of all crowfunding projects that are successful in raising the asked amount</t>
+          <t>Volume (number of offerings) and value (amount raised) of crowdfunding transactions</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>The indicator is a metric that measures the proportion of projects on a crowdfunding platform (or the sum of all crowdfunding platforms) that successfully reach their predetermined funding goal within a specified timeframe. This indicator is a vital sign of a platform's effectiveness, credibility, and the overall health of its ecosystem. It helps gauge the ability of a platform to connect viable projects with interested backers. For MSMEs, crowdfunding can be a viable and less onerous funding source, so the indicator provids important information for monitoring development of MSME finance markets. From a market conduct perspective, while a high success rate is generally positive, an unusually high or artificially inflated rate could be a red flag for misconduct. Platforms could be setting trivially low funding goals to boost statistics,  failing to conduct proper due diligence on projects, or not being transparent about how the success rate is calculated. Successful projects is the number of projects that met or exceeded their funding target during a specific period (e.g., a month, quarter, or year).</t>
+          <t>Metric that measures the total volume of individual investments or pledges made across all projects on a crowdfunding platform or in the entire market (across multiple platforms) over a specific period. This indicator is a direct measure of market activity and investor engagement with crowdfunding, which is increasingly important for MSME finance.</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the success rates of crowdfunding projects? Are smaller or younger MSMEs headed by women more likely to face challenges in crowdfunding?</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Other</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>Usage, Statistics and research</t>
+          <t>Are there disparities in crowdfunding volumes and values raised, according to the gender of the MSMEs asking for funds? Are there disparities in terms of funding periods? Among women-owned MSMEs, which types and ages (years in operation) are driving growth in crowdfunding transactions? Are crowdfunding platforms operated by diverse management more likely to attract women-owned MSMEs, and young MSMEs headed by women?</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -12062,26 +11877,26 @@
         </is>
       </c>
       <c r="D216">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Crowdfunding - Transactions</t>
+          <t>P2P - Investors</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Volume (number of offerings) and value (amount raised) of crowdfunding transactions</t>
+          <t>Number of P2P investors</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Metric that measures the total volume of individual investments or pledges made across all projects on a crowdfunding platform or in the entire market (across multiple platforms) over a specific period. This indicator is a direct measure of market activity and investor engagement with crowdfunding, which is increasingly important for MSME finance.</t>
+          <t>This indicator counts the number of investors registered in P2P lending platforms, as a measure of development of digital finance, and specifically P2P lending, which can potentially benefit MSMEs. It is a key metric to monitor market development in platform lending. It helps assess the effectiveness of marketing campaigns, measure market reach, and forecast potential loan demand or the ability of platforms to meet demand. A growing investor base indicates increased trust and interest, enabling the business to scale and optimize revenue generation. The indicator should be segmented by type of investor (e.g., retail investor, institutional investor), according to local regulatory definitions.</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Are there disparities in crowdfunding volumes and values raised, according to the gender of the MSMEs asking for funds? Are there disparities in terms of funding periods? Among women-owned MSMEs, which types and ages (years in operation) are driving growth in crowdfunding transactions? Are crowdfunding platforms operated by diverse management more likely to attract women-owned MSMEs, and young MSMEs headed by women?</t>
+          <t>Are there gender disparities in the growth of reatil investors in P2P lending platforms? How do invested amounts and types vary by investor gender and other demographics? For example, do women prefer to invest in women-led MSMEs, smaller projects, or younger enterprises? Do P2P platforms operated by diverse management more likely to attract a more diverse investor base?</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -12107,26 +11922,36 @@
         </is>
       </c>
       <c r="D217">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>P2P - Investors</t>
+          <t>Total investment fund shares</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Number of P2P investors</t>
+          <t>Number of investment fund shares held by retail investors in the system</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>This indicator counts the number of investors registered in P2P lending platforms, as a measure of development of digital finance, and specifically P2P lending, which can potentially benefit MSMEs. It is a key metric to monitor market development in platform lending. It helps assess the effectiveness of marketing campaigns, measure market reach, and forecast potential loan demand or the ability of platforms to meet demand. A growing investor base indicates increased trust and interest, enabling the business to scale and optimize revenue generation. The indicator should be segmented by type of investor (e.g., retail investor, institutional investor), according to local regulatory definitions.</t>
+          <t>Market-wide metric that quantifies the volume of investment fund shares owned by individual, non-professional investors within a financial system. This market develoment indicator serves as a crucial gauge of retail investor participation in the capital markets, and their overall exposure to market risks. Companion indicators include the share of investment fund shares held by retail investors as percentage of total investment fund shares, and the average holding size by retail investors.</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the growth of reatil investors in P2P lending platforms? How do invested amounts and types vary by investor gender and other demographics? For example, do women prefer to invest in women-led MSMEs, smaller projects, or younger enterprises? Do P2P platforms operated by diverse management more likely to attract a more diverse investor base?</t>
+          <t>How has participation in investment funds evolved by gender, both for individuals and MSMEs considering the gender of their owners? What types of investment funds show growing participation by women?</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Uptake (account ownership)</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -12143,50 +11968,55 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Capital markets development</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Savings, Credit</t>
         </is>
       </c>
       <c r="D218">
-        <v>9</v>
+        <v>267</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Total investment fund shares</t>
+          <t>Interest rate spreads (loans)</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Number of investment fund shares held by retail investors in the system</t>
+          <t>Difference between the average lending rate and a reference rate (e.g. deposit rate or external reference rate)</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Market-wide metric that quantifies the volume of investment fund shares owned by individual, non-professional investors within a financial system. This market develoment indicator serves as a crucial gauge of retail investor participation in the capital markets, and their overall exposure to market risks. Companion indicators include the share of investment fund shares held by retail investors as percentage of total investment fund shares, and the average holding size by retail investors.</t>
+          <t>The interest-rate spread on loans captures the margin between the average contractual rate a lender charges borrowers and an external reference rate—typically the policy rate. It is a concise gauge of (i) lenders’ credit-risk pricing, (ii) competitive conditions in the lending market, and (iii) monetary-policy transmission. Wider spreads may reflect higher perceived borrower risk, limited competition, or funding-cost pressures; persistently narrow spreads can point to aggressive underwriting or excess liquidity that may undermine future asset quality. Tracked over time and across peer institutions, interest-rate spreads provide insights into credit-cycle turning points, profitability dynamics, and the effectiveness of monetary-policy signals reaching the real economy. !- Definitions and concepts:  Loan interest rate spread (simple): Average contractual loan rate minus Reference rate measured for new originations or for the stock of loans. Net lending spread: average loan rate minus average deposit rate, often used when policy benchmarks are volatile. Segmented spreads: calculated by product (e.g., mortgages, SMEs, credit cards). Non-interest charges: fees and cross-selling income are excluded; the true all-in lending margin may be higher.</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>How has participation in investment funds evolved by gender, both for individuals and MSMEs considering the gender of their owners? What types of investment funds show growing participation by women?</t>
+          <t>Are there gender disparities in interest rate spreads offered to borrowers, and how do these differences vary across regions, income levels, and types of financial service providers? Do women or other gender groups consistently face higher lending rates relative to reference rates compared to men, potentially indicating unequal credit costs? How do interest rate spreads differ by loan type or sector, and are there gender patterns in these variations? Are financial service providers with higher gender diversity more likely to offer more equitable interest rate spreads across gender groups? How do differences in interest rate spreads impact borrowing behavior and access to credit for different gender groups?</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Financial inclusion; Statistics &amp; research</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Uptake (account ownership), Other</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -12203,30 +12033,30 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Savings</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D219">
-        <v>156</v>
+        <v>35</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Depositors who actively close deposit accounts</t>
+          <t>Open finance - % of customers that have given data sharing consent to FSPs</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>% of retail depositors who actively closed a deposit account</t>
+          <t>% of all customers that have given consent to participate in the open finance scheme</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>A measure of the incidence of account closing among depositors, if the measure is high, it could potentially signal issues with the quality of accounts or concerns about the safety of funds. !- Definitions and concepts: Deposit accounts include transaction and non-transaction deposit accounts, for example: Checking/demand, savings, time/term deposit accounts, pensions. 'Active' closure of an account refers to cases where the closure is initiated at the request of the customer, and not due to inactivity or dormancy. !- Data requirements: List of unique deposit account holders (i.e. an individual  must be counted as one depositor irrespective of the number of deposit accounts held) who actively close any of their accounts over a specified period of time (e.g. quarter or year); Total number of unique depositors at the beginning of the specified period.</t>
+          <t>The indicator shows how many customers have actively opted in to share their data via the open finance rails (e.g., with account information service providers or payment initiation service providers). A higher share signals trust, clear value propositions, and mature consent customer interfaces (mobile apps); a low or falling rate may reflect friction in UX or Strong Customer Authentication (SCA), poor messaging, or privacy concerns. It’s a headline adoption KPI for open finance schemes. !- Definitions and concepts: Explicit consent: a clear, affirmative action tied to a specific purpose with the ability to manage and withdraw. Active consent: valid as of the reference date (not expired/withdrawn). Open finance consenting customers (%) = [# unique customers with at least 1 open finance consent / # eligible customers] x 100%. Denominator options: all active retail/MSME customers (preferred) or customers with eligible accounts (state choice). Segment by purpose of consent, scope (accounts included), and channel (mobile/web). Duplication &amp; scope: a customer may hold multiple consents across TPPs; count unique customers, and compare with total count of consents. Lawful-basis nuance: exclude sharing done under contractual necessity or legal obligation (e.g., consultation to credit bureaus for a loan application)—this metric is about explicit consent only.</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>How do active closure rates compare by gender? Which types of accounts are most frequently closed by each gender? How do FSPs rank in active account closures, and does this ranking change when analyzed by gender?</t>
+          <t>Are there gender disparities in data-sharing consent within the open finance scheme, including for MSMEs based on the ownership gender and low-value accounts? What types of accounts are more commonly subject to data-sharing consents? Which types of FSPs have a higher percentage of customers who have given data-sharing consent, and do these percentages vary by gender? If the information is available, what are the most common types and terms for these consents?</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -12236,17 +12066,17 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
+          <t>Consumer protection; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>Quality, Fair treatment, Soundness, Stability</t>
+          <t>Data privacy and protection, Reputational and legal risk</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -12263,30 +12093,30 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Savings, Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D220">
-        <v>267</v>
+        <v>36</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Interest rate spreads (loans)</t>
+          <t>Open finance - API availability</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Difference between the average lending rate and a reference rate (e.g. deposit rate or external reference rate)</t>
+          <t>Average % of time APIs are available</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>The interest-rate spread on loans captures the margin between the average contractual rate a lender charges borrowers and an external reference rate—typically the policy rate. It is a concise gauge of (i) lenders’ credit-risk pricing, (ii) competitive conditions in the lending market, and (iii) monetary-policy transmission. Wider spreads may reflect higher perceived borrower risk, limited competition, or funding-cost pressures; persistently narrow spreads can point to aggressive underwriting or excess liquidity that may undermine future asset quality. Tracked over time and across peer institutions, interest-rate spreads provide insights into credit-cycle turning points, profitability dynamics, and the effectiveness of monetary-policy signals reaching the real economy. !- Definitions and concepts:  Loan interest rate spread (simple): Average contractual loan rate minus Reference rate measured for new originations or for the stock of loans. Net lending spread: average loan rate minus average deposit rate, often used when policy benchmarks are volatile. Segmented spreads: calculated by product (e.g., mortgages, SMEs, credit cards). Non-interest charges: fees and cross-selling income are excluded; the true all-in lending margin may be higher.</t>
+          <t>Shows the proportion of clock time that open finance endpoints can successfully serve requests. High availability is critical for data users such as third-party providers (TPPs) to deliver reliable account information and payment initiation; poor uptime breaks customer journeys, breaches SLAs/SLOs, and can trigger regulatory scrutiny in open finance schemes. !- Definitions and concepts: Availability (uptime):  time-weighted share of intervals in which an endpoint meets both reachability and success criteria. Scope — include account information service, payment initiation service, consent/token endpoints, and webhooks if they’re required for completion. Planned vs. unplanned:  exclude planned maintenance time; report maintenance windows separately. SLO period: availability is usually measured monthly/quarterly (e.g., 99.9% per calendar month), but preferably in shorter periods (e.g., weekly, daily). Granularity: overall availability, by endpoint family, region/zone, and time of day. Example indicator: Availability = 1 - [Downtime / Total scheduled time] where Downtime aggregates intervals failing the success criterion (5xx gateway/network timeouts, auth outages, or latency breaches). !- Limitations and considerations: Including latency SLOs will lower availability vs. status-only measurements. Publish thresholds.</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Are there gender disparities in interest rate spreads offered to borrowers, and how do these differences vary across regions, income levels, and types of financial service providers? Do women or other gender groups consistently face higher lending rates relative to reference rates compared to men, potentially indicating unequal credit costs? How do interest rate spreads differ by loan type or sector, and are there gender patterns in these variations? Are financial service providers with higher gender diversity more likely to offer more equitable interest rate spreads across gender groups? How do differences in interest rate spreads impact borrowing behavior and access to credit for different gender groups?</t>
+          <t>Open finance performance will vary across FSPs for a range of reasons such as their current data architecture and other firm-specific aspects. The objective of looking into this indicator from a gender perspective is to identify whether FSPs that concentrate underserved, low-income women and women-led MSMEs also present poor open finance performance. This indicator can be analyzed together with other open finance performance indicators (Unsuccessful API calls, API response time), and open finance adoption indicators (% customer that have given consent, payment initiation transactions)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -12296,17 +12126,17 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
+          <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Data privacy and protection, Operational risk</t>
+          <t>Quality, Operational risk</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -12327,26 +12157,26 @@
         </is>
       </c>
       <c r="D221">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Open finance - % of customers that have given data sharing consent to FSPs</t>
+          <t>Open finance - API error rate</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>% of all customers that have given consent to participate in the open finance scheme</t>
+          <t>% of all API calls that are unsuccessful</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>The indicator shows how many customers have actively opted in to share their data via the open finance rails (e.g., with account information service providers or payment initiation service providers). A higher share signals trust, clear value propositions, and mature consent customer interfaces (mobile apps); a low or falling rate may reflect friction in UX or Strong Customer Authentication (SCA), poor messaging, or privacy concerns. It’s a headline adoption KPI for open finance schemes. !- Definitions and concepts: Explicit consent: a clear, affirmative action tied to a specific purpose with the ability to manage and withdraw. Active consent: valid as of the reference date (not expired/withdrawn). Open finance consenting customers (%) = [# unique customers with at least 1 open finance consent / # eligible customers] x 100%. Denominator options: all active retail/MSME customers (preferred) or customers with eligible accounts (state choice). Segment by purpose of consent, scope (accounts included), and channel (mobile/web). Duplication &amp; scope: a customer may hold multiple consents across TPPs; count unique customers, and compare with total count of consents. Lawful-basis nuance: exclude sharing done under contractual necessity or legal obligation (e.g., consultation to credit bureaus for a loan application)—this metric is about explicit consent only.</t>
+          <t>This indicator tracks the reliability of open-finance interfaces by showing what share of API requests do not complete successfully due to errors. It is a key API performance indicator monitored by financial authorities implementing open finance. High failure rates degrade customer journeys (consent, data retrieval, payment initiation), inflate support costs, and can breach SLA/SLO commitments. !- Definitions and concepts: API call (request): one HTTP request to a documented endpoint, for example: Account Information Services (AIS) data, Payment Initiatiion Services (PIS) payment, consent, token, webhook, etc. Unsuccessful call: define as per local regulation. This indicator can be collected segmented by types of errors, to be defined as per local regulation (e.g., gateway/network timeouts, invalid/expired token/consent, error in validation, authentication failures. It should also be segmented by type of endpoint, as per local categorization (e.g., account information request, payment initiation request, other). Example indicator: [# of errors  /  # total API calls] x 100%.</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Are there gender disparities in data-sharing consent within the open finance scheme, including for MSMEs based on the ownership gender and low-value accounts? What types of accounts are more commonly subject to data-sharing consents? Which types of FSPs have a higher percentage of customers who have given data-sharing consent, and do these percentages vary by gender? If the information is available, what are the most common types and terms for these consents?</t>
+          <t>Open finance performance will vary across FSPs for a range of reasons such as their current data architecture and other firm-specific aspects. The objective of looking into this indicator from a gender perspective is to identify whether FSPs that concentrate underserved, low-income women and women-led MSMEs also present poor open finance performance. This indicator can be analyzed together with other open finance performance indicators (Unsuccessful API calls, API response time), and open finance adoption indicators (% customer that have given consent, payment initiation transactions)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -12356,12 +12186,12 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Consumer protection; Stability, safety and soundness</t>
+          <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Data privacy and protection, Reputational and legal risk</t>
+          <t>Quality, Operational risk</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -12387,21 +12217,21 @@
         </is>
       </c>
       <c r="D222">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Open finance - API availability</t>
+          <t>Open finance - API response time</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Average % of time APIs are available</t>
+          <t>Average API response time</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Shows the proportion of clock time that open finance endpoints can successfully serve requests. High availability is critical for data users such as third-party providers (TPPs) to deliver reliable account information and payment initiation; poor uptime breaks customer journeys, breaches SLAs/SLOs, and can trigger regulatory scrutiny in open finance schemes. !- Definitions and concepts: Availability (uptime):  time-weighted share of intervals in which an endpoint meets both reachability and success criteria. Scope — include account information service, payment initiation service, consent/token endpoints, and webhooks if they’re required for completion. Planned vs. unplanned:  exclude planned maintenance time; report maintenance windows separately. SLO period: availability is usually measured monthly/quarterly (e.g., 99.9% per calendar month), but preferably in shorter periods (e.g., weekly, daily). Granularity: overall availability, by endpoint family, region/zone, and time of day. Example indicator: Availability = 1 - [Downtime / Total scheduled time] where Downtime aggregates intervals failing the success criterion (5xx gateway/network timeouts, auth outages, or latency breaches). !- Limitations and considerations: Including latency SLOs will lower availability vs. status-only measurements. Publish thresholds.</t>
+          <t>Shows how quickly open-finance endpoints answer requests. Faster responses improve user experience during consent, account-information retrieval, and payment initiation, reducing frictions and drop-offs. Response time is a core performance KPI that complements availability and error rate. !- Definitions and concepts: Response time (latency): elapsed time between request start and final byte received (client-observed) or gateway in → gateway out (server-observed). Track both when possible. Averages vs. tails: report p50/median, p95, p99, and the mean; tails (p95/p99) best reflect user pain. Track both. Granularity: report by endpoint family (types of APIs), potentially segmented into priority levels (see https://www.cdr.gov.au/performance). Units &amp; window: milliseconds, by calendar month (preferably shorter SLO period, such as weekly or daily).</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -12421,7 +12251,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Quality, Suitability, Operational risk</t>
+          <t>Quality, Operational risk</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -12447,41 +12277,31 @@
         </is>
       </c>
       <c r="D223">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Open finance - API error rate</t>
+          <t>Open finance - Payment initiation transactions</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>% of all API calls that are unsuccessful</t>
+          <t>Number of payment initiation transactions conducted in the open finance scheme</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>This indicator tracks the reliability of open-finance interfaces by showing what share of API requests do not complete successfully due to errors. It is a key API performance indicator monitored by financial authorities implementing open finance. High failure rates degrade customer journeys (consent, data retrieval, payment initiation), inflate support costs, and can breach SLA/SLO commitments. !- Definitions and concepts: API call (request): one HTTP request to a documented endpoint, for example: Account Information Services (AIS) data, Payment Initiatiion Services (PIS) payment, consent, token, webhook, etc. Unsuccessful call: define as per local regulation. This indicator can be collected segmented by types of errors, to be defined as per local regulation (e.g., gateway/network timeouts, invalid/expired token/consent, error in validation, authentication failures. It should also be segmented by type of endpoint, as per local categorization (e.g., account information request, payment initiation request, other). Example indicator: [# of errors  /  # total API calls] x 100%.</t>
+          <t>Counts how many account-to-account (A2A) payment orders were successfully initiated via open-finance rails in the period. It’s a core adoption and usage KPI for Payment Initiation Services (PIS): more transactions imply growing merchant and P2P acceptance of openb finance, customer trust, and TPP–bank interoperability. !- Definitions and concepts: Payment initiation transaction (PIT): a payment order created via an authorized PISP/TPP and accepted by the ASPSP (account holder) for processing. Companion counts: Failed payment initiation transactions. Refunds/returns/chargebacks tracked separately. Sub-types: single immediate payments, scheduled payments, recurring/VRP (variable recurring payments), instant vs. ACH/batch. !- Data requirements: Total number of successful payment initiation transactions. !- Limitations and considerations: Duplicates: avoid double counting by using operation IDs.</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Open finance performance will vary across FSPs for a range of reasons such as their current data architecture and other firm-specific aspects. The objective of looking into this indicator from a gender perspective is to identify whether FSPs that concentrate underserved, low-income women and women-led MSMEs also present poor open finance performance. This indicator can be analyzed together with other open finance performance indicators (Unsuccessful API calls, API response time), and open finance adoption indicators (% customer that have given consent, payment initiation transactions)</t>
+          <t>Are there gender disparities in the adoption of payment initiation transactions within the open finance scheme, including for MSMEs by the owner's gender? Do FSPs with higher levels of gender diversity tend to have a larger share of diverse customers conducting payment initiation transactions?</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>Quality, Operational risk</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -12507,26 +12327,27 @@
         </is>
       </c>
       <c r="D224">
-        <v>69</v>
+        <v>150</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Open finance - API response time</t>
+          <t>Bundled product uptake rate</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Average API response time</t>
+          <t>% of customers taking up additional products during onboarding</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Shows how quickly open-finance endpoints answer requests. Faster responses improve user experience during consent, account-information retrieval, and payment initiation, reducing frictions and drop-offs. Response time is a core performance KPI that complements availability and error rate. !- Definitions and concepts: Response time (latency): elapsed time between request start and final byte received (client-observed) or gateway in → gateway out (server-observed). Track both when possible. Averages vs. tails: report p50/median, p95, p99, and the mean; tails (p95/p99) best reflect user pain. Track both. Granularity: report by endpoint family (types of APIs), potentially segmented into priority levels (see https://www.cdr.gov.au/performance). Units &amp; window: milliseconds, by calendar month (preferably shorter SLO period, such as weekly or daily).</t>
+          <t>Measures the percentage of customers who acquire one or more additional financial products or services at the time of onboarding (i.e., when opening their primary account or initiating a new relationship with a financial service provider). These additional products may include insurance, savings, credit, or investment add-ons linked to the initial product. Captures the prevalence of product bundling and cross-selling practices during customer onboarding. It provides insight into market behavior, product integration, and the extent to which customers are being offered or encouraged to take multiple products simultaneously. Monitoring product bundling helps regulators and providers:
+Assess consumer choice and informed consent during onboarding; Identify potential coercive or mis-selling practices; Evaluate financial literacy and customer understanding of product combinations; Analyze the integration of complementary services (e.g., savings plus micro-insurance); Support efforts to ensure responsible cross-selling and transparent disclosure. Bundling can enhance value and convenience when responsibly designed, but may also raise conduct or affordability risks if customers are not well-informed. High bundling rates may reflect integrated product offerings or effective cross-selling, but warrant review for consent and suitability. Low rates may indicate limited product integration or narrow customer engagement at onboarding. Trends can reveal shifts in market strategy, regulatory compliance, or consumer protection outcomes. !- Definitions and concepts: Bundled product: A package of two or more financial services offered together at onboarding (e.g., transaction account + insurance or credit line). Onboarding: The process of establishing a new customer relationship, including account opening and KYC verification. Cross-selling: Offering additional, often related, financial products to a new or existing customer. Informed consent: The customer’s clear understanding and voluntary acceptance of each product taken. !- Data requirements: Bundled product uptake rate (%)=Number of customers who acquired ≥1 additional product at onboarding​/Total number of new customers onboarded. Administrative or CRM data from financial institutions on new customer onboarding and product uptake. Disaggregation by institution type, customer segment (individual, SME), region, and product category. !- Derivable indicators: Average number of products per new customer; Distribution of additional products (e.g., % taking insurance, credit, savings add-ons)</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Open finance performance will vary across FSPs for a range of reasons such as their current data architecture and other firm-specific aspects. The objective of looking into this indicator from a gender perspective is to identify whether FSPs that concentrate underserved, low-income women and women-led MSMEs also present poor open finance performance. This indicator can be analyzed together with other open finance performance indicators (Unsuccessful API calls, API response time), and open finance adoption indicators (% customer that have given consent, payment initiation transactions)</t>
+          <t>How many products does each gender take up on average during the onboarding stage, and how do these numbers compare? What are the gender disparities in the likelihood of adopting multiple products? Which FSPs stand out in multi-product onboarding, and does their ranking change when analyzed by gender? Note: Active usage of products should also be assessed for multiple products taken up during onboarding.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -12536,17 +12357,17 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Quality, Operational risk</t>
+          <t>Uptake (account ownership)</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -12567,26 +12388,26 @@
         </is>
       </c>
       <c r="D225">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Open finance - Payment initiation transactions</t>
+          <t>Product portability requests</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Number of payment initiation transactions conducted in the open finance scheme</t>
+          <t>Number of product portability requests</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Counts how many account-to-account (A2A) payment orders were successfully initiated via open-finance rails in the period. It’s a core adoption and usage KPI for Payment Initiation Services (PIS): more transactions imply growing merchant and P2P acceptance of openb finance, customer trust, and TPP–bank interoperability. !- Definitions and concepts: Payment initiation transaction (PIT): a payment order created via an authorized PISP/TPP and accepted by the ASPSP (account holder) for processing. Companion counts: Failed payment initiation transactions. Refunds/returns/chargebacks tracked separately. Sub-types: single immediate payments, scheduled payments, recurring/VRP (variable recurring payments), instant vs. ACH/batch. !- Data requirements: Total number of successful payment initiation transactions. !- Limitations and considerations: Duplicates: avoid double counting by using operation IDs.</t>
+          <t>Measures the volume of formal requests initiated by customers to transfer their financial product or relationship from one provider to another within a specific period. This includes activities like switching a mortgage, transferring a loan to a new lender, or moving a current account to a new bank. This indicator is a gauge of market competition, consumer empowerment, and potential frictions or risks within the financial system. Very low switching rates can indicate significant barriers to entry or anti-competitive behavior, suggesting that customers are "trapped" with their current providers due to high exit fees, complex processes, or a lack of clear alternatives. This indicator is even more important in countries where product switching platforms or open finance exist and whose effectiveness should be monitored. A companion indicator to the total number of product switch requests is the total number of switches effected in the period, in comparison to the total number of requests. Another companion indicator is the total number of requests (or successful requests) relative to the number of active customers. The central bank of Brazil has calculated the number of loan portability requests relative to the number of loans with an interest rate above the market average rates, using the number of loans with above-market interest rates as a proxy for the untapped potential of the portability system. https://www.bcb.gov.br/content/publicacoes/Documents/reb/boxesreb2020/boxe_2_evolucao_portabilidade_credito_brasil.pdf</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the adoption of payment initiation transactions within the open finance scheme, including for MSMEs by the owner's gender? Do FSPs with higher levels of gender diversity tend to have a larger share of diverse customers conducting payment initiation transactions?</t>
+          <t>Are there customer gender, income and location disparities in account and loan portability or FSP switching requests? Are FSPs with higher levels of gender diversity more likely to receive portability or switching requests or be the destination FSP (rather than the origin) for such requests?</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -12594,9 +12415,19 @@
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Usage, Suitability</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
         </is>
       </c>
     </row>
@@ -12617,27 +12448,26 @@
         </is>
       </c>
       <c r="D226">
-        <v>150</v>
+        <v>33</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Bundled product uptake rate</t>
+          <t>Rejected product portability requests</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>% of customers taking up additional products during onboarding</t>
+          <t>% of all product portability requests that are rejected</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Measures the percentage of customers who acquire one or more additional financial products or services at the time of onboarding (i.e., when opening their primary account or initiating a new relationship with a financial service provider). These additional products may include insurance, savings, credit, or investment add-ons linked to the initial product. Captures the prevalence of product bundling and cross-selling practices during customer onboarding. It provides insight into market behavior, product integration, and the extent to which customers are being offered or encouraged to take multiple products simultaneously. Monitoring product bundling helps regulators and providers:
-Assess consumer choice and informed consent during onboarding; Identify potential coercive or mis-selling practices; Evaluate financial literacy and customer understanding of product combinations; Analyze the integration of complementary services (e.g., savings plus micro-insurance); Support efforts to ensure responsible cross-selling and transparent disclosure. Bundling can enhance value and convenience when responsibly designed, but may also raise conduct or affordability risks if customers are not well-informed. High bundling rates may reflect integrated product offerings or effective cross-selling, but warrant review for consent and suitability. Low rates may indicate limited product integration or narrow customer engagement at onboarding. Trends can reveal shifts in market strategy, regulatory compliance, or consumer protection outcomes. !- Definitions and concepts: Bundled product: A package of two or more financial services offered together at onboarding (e.g., transaction account + insurance or credit line). Onboarding: The process of establishing a new customer relationship, including account opening and KYC verification. Cross-selling: Offering additional, often related, financial products to a new or existing customer. Informed consent: The customer’s clear understanding and voluntary acceptance of each product taken. !- Data requirements: Bundled product uptake rate (%)=Number of customers who acquired ≥1 additional product at onboarding​/Total number of new customers onboarded. Administrative or CRM data from financial institutions on new customer onboarding and product uptake. Disaggregation by institution type, customer segment (individual, SME), region, and product category. !- Derivable indicators: Average number of products per new customer; Distribution of additional products (e.g., % taking insurance, credit, savings add-ons)</t>
+          <t>Measures the volume of formal portability requests initiated by customers to transfer their financial product or relationship from one provider to another within a specific period, which are rejected by the financial service provider. Product portability includes activities like switching a mortgage, transferring a loan to a new lender, or moving a current account to a new bank. This indicator is a gauge of market competition, consumer empowerment, and potential frictions or risks within the financial system. Very low switching rates can indicate significant barriers to entry or anti-competitive behavior, suggesting that customers are "trapped" with their current providers due to high exit fees, complex processes, or a lack of clear alternatives. This indicator is even more important in countries where product switching platforms or open finance exist and whose effectiveness should be monitored. When providers reject too many portability requests, this could be a sign of anti-competitive practices. This indicator should be analyzed together with the indicator on the total number of portability requests.</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>How many products does each gender take up on average during the onboarding stage, and how do these numbers compare? What are the gender disparities in the likelihood of adopting multiple products? Which FSPs stand out in multi-product onboarding, and does their ranking change when analyzed by gender? Note: Active usage of products should also be assessed for multiple products taken up during onboarding.</t>
+          <t>Are there customer gender, income, and location disparities in the approval of portability requests? Are FSPs with higher levels of gender diversity more likely to approve portability requests?</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -12647,135 +12477,15 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>Uptake</t>
+          <t>Usage, Suitability</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Market development</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D227">
-        <v>32</v>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>Product portability requests</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>Number of product portability requests</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>Measures the volume of formal requests initiated by customers to transfer their financial product or relationship from one provider to another within a specific period. This includes activities like switching a mortgage, transferring a loan to a new lender, or moving a current account to a new bank. This indicator is a gauge of market competition, consumer empowerment, and potential frictions or risks within the financial system. Very low switching rates can indicate significant barriers to entry or anti-competitive behavior, suggesting that customers are "trapped" with their current providers due to high exit fees, complex processes, or a lack of clear alternatives. This indicator is even more important in countries where product switching platforms or open finance exist and whose effectiveness should be monitored. A companion indicator to the total number of product switch requests is the total number of switches effected in the period, in comparison to the total number of requests. Another companion indicator is the total number of requests (or successful requests) relative to the number of active customers. The central bank of Brazil has calculated the number of loan portability requests relative to the number of loans with an interest rate above the market average rates, using the number of loans with above-market interest rates as a proxy for the untapped potential of the portability system. https://www.bcb.gov.br/content/publicacoes/Documents/reb/boxesreb2020/boxe_2_evolucao_portabilidade_credito_brasil.pdf</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Are there customer gender, income and location disparities in account and loan portability or FSP switching requests? Are FSPs with higher levels of gender diversity more likely to receive portability or switching requests or be the destination FSP (rather than the origin) for such requests?</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>Usage, Suitability</t>
-        </is>
-      </c>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Market development</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D228">
-        <v>33</v>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>Rejected product portability requests</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>% of all product portability requests that are rejected</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>Measures the volume of formal portability requests initiated by customers to transfer their financial product or relationship from one provider to another within a specific period, which are rejected by the financial service provider. Product portability includes activities like switching a mortgage, transferring a loan to a new lender, or moving a current account to a new bank. This indicator is a gauge of market competition, consumer empowerment, and potential frictions or risks within the financial system. Very low switching rates can indicate significant barriers to entry or anti-competitive behavior, suggesting that customers are "trapped" with their current providers due to high exit fees, complex processes, or a lack of clear alternatives. This indicator is even more important in countries where product switching platforms or open finance exist and whose effectiveness should be monitored. When providers reject too many portability requests, this could be a sign of anti-competitive practices. This indicator should be analyzed together with the indicator on the total number of portability requests.</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Are there customer gender, income, and location disparities in the approval of portability requests? Are FSPs with higher levels of gender diversity more likely to approve portability requests?</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>Usage, Suitability</t>
-        </is>
-      </c>
-      <c r="L228" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
         </is>

--- a/www/LENS_INDICATORS_DB.xlsx
+++ b/www/LENS_INDICATORS_DB.xlsx
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Are there gender-based disparities in access to providers that offer free account opening for basic deposit or payment accounts? Do individuals of different genders tend to rely on providers that are more or less likely to charge account opening fees? Are there geographic or institutional patterns—such as rural areas or certain FSP types, with more or less gender diversity—that disproportionately affect access to no-cost accounts by gender? How might the availability of free account opening across FSP types influence formal account uptake among different gender groups?</t>
+          <t>How does the gender composition of the customer base of the FSPs correlate with the level of access to free accounts?, Are FSPs with higher levels of gender diversity more likely to offer free accounts?”</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the availability of complaints channels that align with women’s communication preferences or access patterns (e.g., lower access to digital channels, higher reliance on in-person options)? Are FSPs with higher levels of gender diversity more likely to offer a broader range of accessible complaints channels? Do women face more limited access to certain complaints channels due to geographic, digital, or literacy-related barriers?</t>
+          <t>How does the gender composition of the customer base of the FSPs correlate with the level of access to complaints channels?</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints filing channel</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints filing channel</t>
         </is>
       </c>
     </row>
@@ -12006,12 +12006,12 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Quality, Fair treatment</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">

--- a/www/LENS_INDICATORS_DB.xlsx
+++ b/www/LENS_INDICATORS_DB.xlsx
@@ -9090,7 +9090,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the volume of Suspiciou transaction reports (STRs) generated, including for MSMEs by the owner's gender? Are there disparities in STR statistics across FSPs with different levels of gender diversity?</t>
+          <t>Are there gender disparities in the volume of Suspiciou transaction reports (STRs) generated, including for MSMEs by the owner's gender? Is there a correlation between the volume of these reports and the composition of the FSP customer base by gender? For example, do FSPs with a higher proportion of women in their customer base report a lower volume of STR? Are there disparities in STR statistics across FSPs with different levels of gender diversity?</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">

--- a/www/LENS_INDICATORS_DB.xlsx
+++ b/www/LENS_INDICATORS_DB.xlsx
@@ -6997,7 +6997,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Average cost-to-borrower for unsecured retail lending</t>
+          <t>Average cost-to-borrower for unsecured lending</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Delinquency rate in the retail loan portfolio</t>
+          <t>Delinquency rate in the loan portfolio</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -9295,17 +9295,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Non performing loans (NPLs) in the retail portfolio</t>
+          <t>Non performing loans (NPLs)</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Non performing loans rate in the retail/MSME loan portfolio</t>
+          <t>Non performing loans rate in the retail loan portfolio</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>The NPL indicator for the retail loan portfolio quantifies the share (or absolute value) of consumer and MSE loans that are unlikely to be fully repaid. Because retail credit typically involves high volumes of granular, often unsecured exposures, a build-up of NPLs signals mounting credit risk costs, pressure on provisioning, and potential stress. Supervisors track this metric to assess lenders' underwriting standards, resilience to economic shocks, and the effectiveness of arrears management. !- Definitions and concepts: An NPL is defined as a loan that is past-due for a minimum amount of days (e.g., 90 days). The definition can vary across countries but the Basel Committee has set common standards. The retail portfolio encompasses exposures to individuals and qualifying MSMEs treated under the retail asset class. The most common ratio is Gross NPLs ÷ Gross retail loans. Aggressive charge-offs or “evergreening” can temporarily lower the NPL ratio without improving underlying asset quality. Seasonality and relief measures: Payment holidays or pandemic moratoria may defer delinquencies, masking latent credit risk.</t>
+          <t>The NPL indicator for the retail loan portfolio quantifies the share (or absolute value) of consumer and MSME loans that are unlikely to be fully repaid. Because retail credit typically involves high volumes of granular, often unsecured exposures, a build-up of NPLs signals mounting credit risk costs, pressure on provisioning, and potential stress. Supervisors track this metric to assess lenders' underwriting standards, resilience to economic shocks, and the effectiveness of arrears management. !- Definitions and concepts: An NPL is defined as a loan that is past-due for a minimum amount of days (e.g., 90 days). The definition can vary across countries but the Basel Committee has set common standards. The retail portfolio encompasses exposures to individuals and qualifying MSMEs treated under the retail asset class. The most common ratio is Gross NPLs ÷ Gross retail loans. Aggressive charge-offs or “evergreening” can temporarily lower the NPL ratio without improving underlying asset quality. Seasonality and relief measures: Payment holidays or pandemic moratoria may defer delinquencies, masking latent credit risk.</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">

--- a/www/LENS_INDICATORS_DB.xlsx
+++ b/www/LENS_INDICATORS_DB.xlsx
@@ -897,7 +897,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Represents the total number of current (checking or demand deposit) accounts maintained by regulated financial service providers for individuals or MSEs. Measures the volume of current accounts in the financial system, serving as a proxy for usage intensity and liquidity management capacity within the banking sector. Tracking the number of current accounts helps supervisors understand the depth of account usage, the scale of banking activity, and potential duplication or concentration of accounts across the system. !- Data requirements: Aggregated institutional data on current accounts.
+          <t>Represents the total number of current (checking or demand deposit) accounts maintained by regulated financial service providers for individuals or MSMEs. Measures the volume of current accounts in the financial system, serving as a proxy for usage intensity and liquidity management capacity within the banking sector. Tracking the number of current accounts helps supervisors understand the depth of account usage, the scale of banking activity, and potential duplication or concentration of accounts across the system. !- Data requirements: Aggregated institutional data on current accounts.
 Customer level disaggregation variables for segmentation analysis, for example, by institution type, gender, age, and sub-national administrative units. !- Derivable indicators: Average accounts per holder = (Number of current accounts / Number of current account holders).</t>
         </is>
       </c>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Measures the number of individuals or entities that hold at least one payment account with a regulated payment service provider or financial institution. Each holder is counted once, regardless of the number of accounts they maintain. Captures the extent of access to formal payment infrastructure, indicating the proportion of the population or firms that can send, receive, and store funds electronically through regulated accounts. Payment account ownership is a core measure of financial inclusion and digital financial participation. It helps assess: the reach of cashless transaction systems, the effectiveness instant payment schemes, and the integration of individuals and SMEs into formal payment networks. Higher values indicate wider participation in the digital payment ecosystem; low values suggest barriers to access, especially in underserved regions or demographics. !- Definitions and concepts: Payment account: An account that allows customers to execute payment transactions (deposits, withdrawals, transfers) and access funds on demand. Includes current accounts, e-money accounts, mobile money accounts, and other regulated transaction accounts. !- Data requirements: Administrative or supervisory data from banks, mobile money operators, e-money issuers, and payment service providers. Disaggregation variables for segmentation analysis, for example, customer type, product type, gender. !- Derivable indicators: Payment account ownership rate = (Number of payment account holders / Adult population) × 100</t>
+          <t>Measures the number of individuals or entities that hold at least one payment account with a regulated payment service provider or financial institution. Each holder is counted once, regardless of the number of accounts they maintain. Captures the extent of access to formal payment infrastructure, indicating the proportion of the population or firms that can send, receive, and store funds electronically through regulated accounts. Payment account ownership is a core measure of financial inclusion and digital financial participation. It helps assess: the reach of cashless transaction systems, the effectiveness instant payment schemes, and the integration of individuals and MSMEs into formal payment networks. Higher values indicate wider participation in the digital payment ecosystem; low values suggest barriers to access, especially in underserved regions or demographics. !- Definitions and concepts: Payment account: An account that allows customers to execute payment transactions (deposits, withdrawals, transfers) and access funds on demand. Includes current accounts, e-money accounts, mobile money accounts, and other regulated transaction accounts. !- Data requirements: Administrative or supervisory data from banks, mobile money operators, e-money issuers, and payment service providers. Disaggregation variables for segmentation analysis, for example, customer type, product type, gender. !- Derivable indicators: Payment account ownership rate = (Number of payment account holders / Adult population) × 100</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>An aggregate measure of the uptake of loans (volume) from financial institutions. When expressed in per capita terms, it is a measure of the intensity of borrowing and the depth of the credit market. This is a core indicator in the IMF Financial Access Survey which collects financial access and usage indicators from 192 economies, for a number of financial institution types, enabling cross-country comparisons and benchmarking (https://data.imf.org/en/datasets/IMF.STA:FAS). !- Definitions and concepts: Loans referes to a specific loan account held by resident individuals or MSMEs and could encompass one of many types, such as a mortgage, a revolving line of credit (e.g. credit card), an overdraft account, a personal loan or a loan to purchase a vehicle. MSMEs are defined variably across countries using thresholds of either total number of employees, assets or annual revenue (sales). If none of these characteristics are available, loan size can be used as a proxy for firm size. The International Finance Corporation (IFC) has a standard definition which can be consulted as a guideline if there is no local definition. !- Data requirements: Total number of loans received by indidivuals or MSMEs over a specified period of time (e.g. last quarter, last year); Total adult population (official count from recent census or estimate from national satistics agency); Total borrowers. !- Derivable indicators: Number of loans per 1,000 adults; Number of loans per borrower, Share of all loan accounts represented by MSEs</t>
+          <t>An aggregate measure of the uptake of loans (volume) from financial institutions. When expressed in per capita terms, it is a measure of the intensity of borrowing and the depth of the credit market. This is a core indicator in the IMF Financial Access Survey which collects financial access and usage indicators from 192 economies, for a number of financial institution types, enabling cross-country comparisons and benchmarking (https://data.imf.org/en/datasets/IMF.STA:FAS). !- Definitions and concepts: Loans referes to a specific loan account held by resident individuals or MSMEs and could encompass one of many types, such as a mortgage, a revolving line of credit (e.g. credit card), an overdraft account, a personal loan or a loan to purchase a vehicle. MSMEs are defined variably across countries using thresholds of either total number of employees, assets or annual revenue (sales). If none of these characteristics are available, loan size can be used as a proxy for firm size. The International Finance Corporation (IFC) has a standard definition which can be consulted as a guideline if there is no local definition. !- Data requirements: Total number of loans received by indidivuals or MSMEs over a specified period of time (e.g. last quarter, last year); Total adult population (official count from recent census or estimate from national satistics agency); Total borrowers. !- Derivable indicators: Number of loans per 1,000 adults; Number of loans per borrower, Share of all loan accounts represented by MSMEs</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Measures the number of individuals or entities that hold at least one active life insurance policy with a licensed insurance company during the reporting period. Each policyholder is counted once, regardless of the number of life insurance policies they own. Captures the breadth of participation in the life insurance market, reflecting financial protection, long-term savings, and risk management coverage among households and MSEs. Life insurance policy ownership indicates the extent to which individuals and families are protected against income loss or death-related shocks, and contributes to broader measures of financial resilience and inclusion. For regulators, it provides insight into market penetration, consumer protection coverage, and the development of the insurance sector. !- Data requirements: Total number of unique policyholders with active life insurance policies at the end of the reporting period using: Administrative data reported by licensed life insurance companies and disaggregation variables, for example, by type of policy (term, whole, group, etc.), gender, age group, and sub-national administrative area where available. !- Derivable indicators: Coverage rate = (Number of life insurance policy holders / Adult population) × 100</t>
+          <t>Measures the number of individuals or entities that hold at least one active life insurance policy with a licensed insurance company during the reporting period. Each policyholder is counted once, regardless of the number of life insurance policies they own. Captures the breadth of participation in the life insurance market, reflecting financial protection, long-term savings, and risk management coverage among households and MSMEs. Life insurance policy ownership indicates the extent to which individuals and families are protected against income loss or death-related shocks, and contributes to broader measures of financial resilience and inclusion. For regulators, it provides insight into market penetration, consumer protection coverage, and the development of the insurance sector. !- Data requirements: Total number of unique policyholders with active life insurance policies at the end of the reporting period using: Administrative data reported by licensed life insurance companies and disaggregation variables, for example, by type of policy (term, whole, group, etc.), gender, age group, and sub-national administrative area where available. !- Derivable indicators: Coverage rate = (Number of life insurance policy holders / Adult population) × 100</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Measures the total number of active non-life (general) insurance policies in force with licensed insurance companies during the reporting period. This includes all forms of insurance other than life insurance, such as motor, property, health, travel, fire, marine, and liability insurance. Captures the depth and reach of risk protection provided by the non-life insurance market, serving as a measure of both market development and household or business financial resilience to unexpected shocks. The number of non-life insurance policies reflects the extent to which households and firms are insured against everyday risks (e.g., accidents, property damage, medical emergencies). For regulators, it indicates: The penetration and diversification of the non-life insurance market; the distribution of insurance coverage across sectors and population groups and the potential exposure of the uninsured to catastrophic losses. Higher values indicate greater risk coverage and insurance market depth, while stagnation or decline may suggest low affordability, weak market development, or limited consumer trust in insurance products. !- Definitions and concepts: Non-life (general) insurance: Covers financial losses from events other than death, typically over a one-year term. It provides indemnity rather than a savings component, distinguishing it from life insurance. !- Data requirements: Total count of active non-life insurance policies recorded by licensed insurers at the end of the reporting period, derived from: Administrative data from licensed non-life insurance companies; disaggregation variables for segmentation analysis such as by type of product (vehicle, property, health, etc.), customer segment (individual, SME), and sub-national administrative areas. !- Derivable indicators: Policy coverage rate = (Number of non-life policies / Adult population or number of firms) × 100</t>
+          <t>Measures the total number of active non-life (general) insurance policies in force with licensed insurance companies during the reporting period. This includes all forms of insurance other than life insurance, such as motor, property, health, travel, fire, marine, and liability insurance. Captures the depth and reach of risk protection provided by the non-life insurance market, serving as a measure of both market development and household or business financial resilience to unexpected shocks. The number of non-life insurance policies reflects the extent to which households and firms are insured against everyday risks (e.g., accidents, property damage, medical emergencies). For regulators, it indicates: The penetration and diversification of the non-life insurance market; the distribution of insurance coverage across sectors and population groups and the potential exposure of the uninsured to catastrophic losses. Higher values indicate greater risk coverage and insurance market depth, while stagnation or decline may suggest low affordability, weak market development, or limited consumer trust in insurance products. !- Definitions and concepts: Non-life (general) insurance: Covers financial losses from events other than death, typically over a one-year term. It provides indemnity rather than a savings component, distinguishing it from life insurance. !- Data requirements: Total count of active non-life insurance policies recorded by licensed insurers at the end of the reporting period, derived from: Administrative data from licensed non-life insurance companies; disaggregation variables for segmentation analysis such as by type of product (vehicle, property, health, etc.), customer segment (individual, MSMEs), and sub-national administrative areas. !- Derivable indicators: Policy coverage rate = (Number of non-life policies / Adult population or number of firms) × 100</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Measures the number (volume) and average monetary value of transfers made from mobile money, e-money, or prepaid card accounts into savings accounts held with regulated financial institutions during the reporting period. It captures the movement of funds from transactional platforms into formal savings instruments. Captures the integration between digital payment systems and formal deposit-taking institutions, serving as a proxy for digitally enabled savings behavior. It reflects both financial ecosystem interoperability and user intent to save via digital channels. This indicator provides insight into how digital financial services support asset building and liquidity management among consumers and small businesses. For regulators and policymakers, it helps: Assess the linkages between payment and savings ecosystems; Evaluate the role of digital finance in mobilizing deposits; Monitor consumer behavioral shifts from cash or digital wallets to formal savings; Identify bottlenecks in interoperability or settlement infrastructure. It is also a useful measure of financial inclusion quality, going beyond access to capture productive financial usage. Higher transfer volumes indicate strong integration and frequent saving behaviors via digital platforms. Higher average values may reflect larger or more intentional savings transfers. Low or stagnant values may suggest limited interoperability, low trust, or lack of linked savings products. !- Definitions and concepts: Mobile money / e-money account: A digital store-of-value account allowing electronic payments, transfers, and withdrawals via mobile or prepaid platforms. Savings account: A regulated deposit account designed primarily for storing value and earning interest. !- Data requirements: Transaction-level or aggregated data from e-money issuers, mobile money operators, and deposit-taking institutions; Disaggregation by sending channel, receiving institution type, customer segment (individual, SME), and region.</t>
+          <t>Measures the number (volume) and average monetary value of transfers made from mobile money, e-money, or prepaid card accounts into savings accounts held with regulated financial institutions during the reporting period. It captures the movement of funds from transactional platforms into formal savings instruments. Captures the integration between digital payment systems and formal deposit-taking institutions, serving as a proxy for digitally enabled savings behavior. It reflects both financial ecosystem interoperability and user intent to save via digital channels. This indicator provides insight into how digital financial services support asset building and liquidity management among consumers and small businesses. For regulators and policymakers, it helps: Assess the linkages between payment and savings ecosystems; Evaluate the role of digital finance in mobilizing deposits; Monitor consumer behavioral shifts from cash or digital wallets to formal savings; Identify bottlenecks in interoperability or settlement infrastructure. It is also a useful measure of financial inclusion quality, going beyond access to capture productive financial usage. Higher transfer volumes indicate strong integration and frequent saving behaviors via digital platforms. Higher average values may reflect larger or more intentional savings transfers. Low or stagnant values may suggest limited interoperability, low trust, or lack of linked savings products. !- Definitions and concepts: Mobile money / e-money account: A digital store-of-value account allowing electronic payments, transfers, and withdrawals via mobile or prepaid platforms. Savings account: A regulated deposit account designed primarily for storing value and earning interest. !- Data requirements: Transaction-level or aggregated data from e-money issuers, mobile money operators, and deposit-taking institutions; Disaggregation by sending channel, receiving institution type, customer segment (individual, MSMEs), and region.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4152,7 +4152,7 @@
       <c r="G74" t="inlineStr">
         <is>
           <t>Measures the total number of deposit accounts that were active during the reporting period — that is, accounts that recorded at least one transaction (deposit, withdrawal, transfer, or interest accrual) or maintained a positive balance within the reference period. Captures the extent of active engagement with deposit products, providing insight into the usage and vitality of the deposit base within the formal financial system. It differentiates between accounts merely opened and those that are operational and regularly used. Monitoring active deposit accounts allows authorities to: Assess the sustainability of financial inclusion (beyond access); Identify dormancy trends and inactive balances; Evaluate the breadth of active financial relationships with customers; Support liquidity management and deposit insurance analysis. It helps ensure that reported account growth translates into meaningful usage rather than inactive accounts. Higher values indicate broad and sustained account usage. Low activity ratios may signal dormant accounts, limited engagement, or inclusion fatigue. Trends over time reveal patterns of customer retention, financial health, and economic activity. !- Definitions and concepts: Active deposit account: An account that has had at least one financial transaction or maintained a positive balance within the reference period (commonly 90 days or 12 months). Deposit account: Savings, current, or term deposit accounts held with regulated deposit-taking institutions. !- Data requirements: 
-Administrative data from licensed deposit-taking institutions (banks, microfinance institutions, cooperatives); Disaggregation by institution type, account type (savings, current, term), customer type (individual, SME), and region. !- Derivable indicators: Activity rate = (Number of active deposit accounts / Total number of deposit accounts) × 100</t>
+Administrative data from licensed deposit-taking institutions (banks, microfinance institutions, cooperatives); Disaggregation by institution type, account type (savings, current, term), customer type (individual, MSMEs), and region. !- Derivable indicators: Activity rate = (Number of active deposit accounts / Total number of deposit accounts) × 100</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>This indicator shows how widespread truly no-minimum (“zero-balance”) deposit offerings are across regulated providers. A higher share signals stronger inclusion and fewer barriers to entry for low-income or newly banked customers. It also benchmarks market competitiveness and the effectiveness of policy nudges (fee caps, basic-account mandates). !- Definitions and concepts: Provider: a licensed bank or regulated deposit-taking institution (count each legal entity once; brand-level cuts optional). Qualifying product: a demand/current or other payment-capable deposit account that (a) has no required minimum balance to open or maintain, and (b) does not levy any fee or penalty for falling below any balance threshold (unconditional—no “waived if direct deposit” clauses). Metric: [# of providers with at least 1 qualifying product] / [# of providers offering retail transaction accounts] x 100%. Companion indicators: product-based share (% of products that quality) and coverage share (% of active custoemrs eligible for a zero-minimum product at their provider). !- Data requirements: Public product disclosures and fee schedules (account opening requirements, minimum-balance rules, below-minimum penalties, waiver conditions). Product taxonomy (basic/no-frills, standard, premium, student/youth, SME). Provider registry (licensed DTIs) to define the denominator. Optional: account-holder counts per provider to compute customer coverage. !- Limitations and considerations: Conditional waivers: “no fee if direct deposit/average balance ≥ X” do not qualify—document this to avoid overstatement. Promotional periods: temporary fee holidays should be excluded or footnoted.
+          <t>This indicator shows how widespread truly no-minimum (“zero-balance”) deposit offerings are across regulated providers. A higher share signals stronger inclusion and fewer barriers to entry for low-income or newly banked customers. It also benchmarks market competitiveness and the effectiveness of policy nudges (fee caps, basic-account mandates). !- Definitions and concepts: Provider: a licensed bank or regulated deposit-taking institution (count each legal entity once; brand-level cuts optional). Qualifying product: a demand/current or other payment-capable deposit account that (a) has no required minimum balance to open or maintain, and (b) does not levy any fee or penalty for falling below any balance threshold (unconditional—no “waived if direct deposit” clauses). Metric: [# of providers with at least 1 qualifying product] / [# of providers offering retail transaction accounts] x 100%. Companion indicators: product-based share (% of products that quality) and coverage share (% of active custoemrs eligible for a zero-minimum product at their provider). !- Data requirements: Public product disclosures and fee schedules (account opening requirements, minimum-balance rules, below-minimum penalties, waiver conditions). Product taxonomy (basic/no-frills, standard, premium, student/youth, MSMEs). Provider registry (licensed DTIs) to define the denominator. Optional: account-holder counts per provider to compute customer coverage. !- Limitations and considerations: Conditional waivers: “no fee if direct deposit/average balance ≥ X” do not qualify—document this to avoid overstatement. Promotional periods: temporary fee holidays should be excluded or footnoted.
 Scope: prepaid/e-money wallets may not be “deposits” in some regimes; state inclusion rules. Comparability: some providers bundle packages where zero-minimum applies only to youth/senior accounts—segment by customer type. Mystery-shop vs. policy: actual onboarding practices may diverge from posted terms; periodic verification improves accuracy.</t>
         </is>
       </c>
@@ -7471,8 +7471,8 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>This indicator estimates the effective price of holding and using a transaction account, expressed as a yield on the customer’s average balance. By computing it for each account type (e.g., basic/no-frills, standard retail, premium, SME, e-money wallet), it reveals where pricing and usage frictions are highest. It helps supervisors assess fairness, inclusion quality, and reliance on fee income. !- Definitions and concepts: Non-interest fees: maintenance/inactivity, ATM/network, FX/transfer, statement/card fees, overdraft &amp; returned-payment fees tied to the account. 
-Per account-holder basis: aggregate all accounts of the same type per customer, then average (also show balance-weighted results). !- Data requirements: Core-banking data: customer ID, account type tags, average daily balance by customer for each account type, interest credited, revenue by fee code linked to accounts; flags for waivers/refunds/chargebacks. Channel/product hierarchies (basic vs. premium, retail vs. SME, wallet vs. bank account) and currency/FX mapping. Optional: usage indicators (transactions per month) to explain differences across types.</t>
+          <t>This indicator estimates the effective price of holding and using a transaction account, expressed as a yield on the customer’s average balance. By computing it for each account type (e.g., basic/no-frills, standard retail, premium, MSMEs, e-money wallet), it reveals where pricing and usage frictions are highest. It helps supervisors assess fairness, inclusion quality, and reliance on fee income. !- Definitions and concepts: Non-interest fees: maintenance/inactivity, ATM/network, FX/transfer, statement/card fees, overdraft &amp; returned-payment fees tied to the account. 
+Per account-holder basis: aggregate all accounts of the same type per customer, then average (also show balance-weighted results). !- Data requirements: Core-banking data: customer ID, account type tags, average daily balance by customer for each account type, interest credited, revenue by fee code linked to accounts; flags for waivers/refunds/chargebacks. Channel/product hierarchies (basic vs. premium, retail vs. MSMEs, wallet vs. bank account) and currency/FX mapping. Optional: usage indicators (transactions per month) to explain differences across types.</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Shows how many borrowers are under temporary repayment relief, signalling household stress, policy effectiveness, and potential payment cliffs when relief ends. Rising usage can reduce near-term delinquencies but may defer (not eliminate) credit risk and revenue. !- Definitions and concepts: Relief measures (forbearance): payment holiday/deferral, interest-only period, reduced instalment, term extension, fee/penalty waiver, capitalization of arrears, hardship programs.Borrower-based indicator: % of borrowers on relief = [Total unique borrowers with at least 1 active relief measure in period]/[Total unique active borrowing customers] x 100%. Account-based variant uses loan count instead of borrowers. Status: Active (relief in effect), Approved but not started, Expired. Intensity companions: % of balances under relief, avg. relief days used, new entrants to relief ÷ active borrowers. !- Data requirements: Loan-level flags: relief type, start/end dates, approval date, terms (interest accrual, capitalization), reason code (income loss, disaster, medical), product type. Borrower ID (deduplicated across products/entities). !- Limitations and considerations: Definition variance: some programs auto-enrol; others require hardship evidence—harmful to cross-bank comparisons. Double counting: a borrower may receive multiple reliefs across loans—use borrower-level dedupe and report per-loan as a companion. Masking effect: relief suppresses DPD/NPL temporarily; pair with balances under relief and post-exit performance. Cohort effects &amp; timing: shocks (e.g., disasters) create spikes; use cohort tracking (by approval month) and rolling windows. Conduct risk: prolonged or opaque relief terms can mislead customers; monitor complaints and repeat relief rates. Segment by product (mortgage, card, personal, SME), risk grade, tenure, and demographics to pinpoint vulnerability and program effectiveness.</t>
+          <t>Shows how many borrowers are under temporary repayment relief, signalling household stress, policy effectiveness, and potential payment cliffs when relief ends. Rising usage can reduce near-term delinquencies but may defer (not eliminate) credit risk and revenue. !- Definitions and concepts: Relief measures (forbearance): payment holiday/deferral, interest-only period, reduced instalment, term extension, fee/penalty waiver, capitalization of arrears, hardship programs.Borrower-based indicator: % of borrowers on relief = [Total unique borrowers with at least 1 active relief measure in period]/[Total unique active borrowing customers] x 100%. Account-based variant uses loan count instead of borrowers. Status: Active (relief in effect), Approved but not started, Expired. Intensity companions: % of balances under relief, avg. relief days used, new entrants to relief ÷ active borrowers. !- Data requirements: Loan-level flags: relief type, start/end dates, approval date, terms (interest accrual, capitalization), reason code (income loss, disaster, medical), product type. Borrower ID (deduplicated across products/entities). !- Limitations and considerations: Definition variance: some programs auto-enrol; others require hardship evidence—harmful to cross-bank comparisons. Double counting: a borrower may receive multiple reliefs across loans—use borrower-level dedupe and report per-loan as a companion. Masking effect: relief suppresses DPD/NPL temporarily; pair with balances under relief and post-exit performance. Cohort effects &amp; timing: shocks (e.g., disasters) create spikes; use cohort tracking (by approval month) and rolling windows. Conduct risk: prolonged or opaque relief terms can mislead customers; monitor complaints and repeat relief rates. Segment by product (mortgage, card, personal, MSMEs), risk grade, tenure, and demographics to pinpoint vulnerability and program effectiveness.</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>This indicator shows the share of funds sitting in deposit and payment accounts (excluding term deposits) that are not actively used by customers. High concentrations of idle balances can signal weak customer engagement, poor product fit, or frictions in account usage—important for financial-inclusion quality, liquidity management, and conduct risk. From a prudential angle, large dormant balances may look “stable” but can reverse if reactivation drives or policy changes prompt withdrawals. For consumer protection, persistent dormancy raises risks around unclaimed funds, fees, and fraud. Recommended to analyze of this indicator by product type (e.g. current/checking, mobile money, etc). !- Definitions and concepts: Accounts: demand/current accounts and other payment-capable deposit accounts. Inactive account: no customer-initiated debit/credit (card use, cash withdrawal/deposit, transfer) for a defined window (e.g., ≥90 or 180 days). System entries (interest, fees, bank corrections) don’t count. Dormant account: extended inactivity beyond a longer threshold (commonly ≥12 months) that may trigger special handling (restricted access, outreach, escheatment). Indicator formula: Balances in inactive + dormant transaction accounts divided by total transaction-account balances. Reporting the split (inactive vs. dormant) can provide further detail. !- Data requirements: Core-banking ledger with end-of-day balances, product codes, and last customer-initiated activity timestamp per account. Classification rules reflecting local definitions (inactive/dormant thresholds; treatment of standing orders/auto-debits). Ownership segment (retail/SME), currency, and insured/uninsured flags. Optional: outreach attempts, reactivation outcomes, and fee assessments to monitor conduct risk. Limitations &amp; considerations: Definition divergence: thresholds and what counts as “activity” vary by jurisdiction and even by institution—state methodology clearly. Data quality: some channels (agents, fintech front-ends) may not update the core “last activity” field, overstating dormancy.
+          <t>This indicator shows the share of funds sitting in deposit and payment accounts (excluding term deposits) that are not actively used by customers. High concentrations of idle balances can signal weak customer engagement, poor product fit, or frictions in account usage—important for financial-inclusion quality, liquidity management, and conduct risk. From a prudential angle, large dormant balances may look “stable” but can reverse if reactivation drives or policy changes prompt withdrawals. For consumer protection, persistent dormancy raises risks around unclaimed funds, fees, and fraud. Recommended to analyze of this indicator by product type (e.g. current/checking, mobile money, etc). !- Definitions and concepts: Accounts: demand/current accounts and other payment-capable deposit accounts. Inactive account: no customer-initiated debit/credit (card use, cash withdrawal/deposit, transfer) for a defined window (e.g., ≥90 or 180 days). System entries (interest, fees, bank corrections) don’t count. Dormant account: extended inactivity beyond a longer threshold (commonly ≥12 months) that may trigger special handling (restricted access, outreach, escheatment). Indicator formula: Balances in inactive + dormant transaction accounts divided by total transaction-account balances. Reporting the split (inactive vs. dormant) can provide further detail. !- Data requirements: Core-banking ledger with end-of-day balances, product codes, and last customer-initiated activity timestamp per account. Classification rules reflecting local definitions (inactive/dormant thresholds; treatment of standing orders/auto-debits). Ownership segment (retail/MSMEs), currency, and insured/uninsured flags. Optional: outreach attempts, reactivation outcomes, and fee assessments to monitor conduct risk. Limitations &amp; considerations: Definition divergence: thresholds and what counts as “activity” vary by jurisdiction and even by institution—state methodology clearly. Data quality: some channels (agents, fintech front-ends) may not update the core “last activity” field, overstating dormancy.
 Seasonality &amp; cycles: balances can spike around payroll/tax periods; use consistent month-end or averages. Policy effects: dormancy fees, auto-closures, and unclaimed-funds rules materially affect trends. Coverage scope: exclude escrow, trust, and suspense ledgers to avoid inflating inactive balances.</t>
         </is>
       </c>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>The delinquency rate tracks the share of consumer loans—mortgages, credit-cards, instalment loans, auto, buy-now-pay-later, qualifying MSEs—that have fallen past due but have not yet crossed the “non-performing” threshold or been written off. Rising early-stage arrears are an early-warning signal of household stress and of future spikes in non-performing loans (NPLs), provisions and write-offs. Paired with NPL, restructuring and write-off metrics, the delinquency rate provides a forward-looking barometer of retail credit health. Supervisors and risk managers use the metric to test the effectiveness of underwriting standards, consumer disclosure, customer interfaces (for digital loans), and pricing for credit risk. !- Definitions and concepts: Loan delinquency refers to a situation in which borrowed money is not paid back as agreed. A loan becomes delinquent when a borrower misses a regular installment payment. A delinquent loan is any kind of loan that has past due payments but has yet to go into default. On a value basis, this indicator measures the total outstanding balances past due (for example greater than 1 day past due) as a share of gross retail loan balances at the end of a specified period. Operational cut-offs: Inconsistent days past due calculation (calendar days vs. business days, partial payments) hinders cross-lender comparability.</t>
+          <t>The delinquency rate tracks the share of consumer loans—mortgages, credit-cards, instalment loans, auto, buy-now-pay-later, qualifying MSMEs—that have fallen past due but have not yet crossed the “non-performing” threshold or been written off. Rising early-stage arrears are an early-warning signal of household stress and of future spikes in non-performing loans (NPLs), provisions and write-offs. Paired with NPL, restructuring and write-off metrics, the delinquency rate provides a forward-looking barometer of retail credit health. Supervisors and risk managers use the metric to test the effectiveness of underwriting standards, consumer disclosure, customer interfaces (for digital loans), and pricing for credit risk. !- Definitions and concepts: Loan delinquency refers to a situation in which borrowed money is not paid back as agreed. A loan becomes delinquent when a borrower misses a regular installment payment. A delinquent loan is any kind of loan that has past due payments but has yet to go into default. On a value basis, this indicator measures the total outstanding balances past due (for example greater than 1 day past due) as a share of gross retail loan balances at the end of a specified period. Operational cut-offs: Inconsistent days past due calculation (calendar days vs. business days, partial payments) hinders cross-lender comparability.</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>The interest-rate spread on loans captures the margin between the average contractual rate a lender charges borrowers and an external reference rate—typically the policy rate. It is a concise gauge of (i) lenders’ credit-risk pricing, (ii) competitive conditions in the lending market, and (iii) monetary-policy transmission. Wider spreads may reflect higher perceived borrower risk, limited competition, or funding-cost pressures; persistently narrow spreads can point to aggressive underwriting or excess liquidity that may undermine future asset quality. Tracked over time and across peer institutions, interest-rate spreads provide insights into credit-cycle turning points, profitability dynamics, and the effectiveness of monetary-policy signals reaching the real economy. !- Definitions and concepts:  Loan interest rate spread (simple): Average contractual loan rate minus Reference rate measured for new originations or for the stock of loans. Net lending spread: average loan rate minus average deposit rate, often used when policy benchmarks are volatile. Segmented spreads: calculated by product (e.g., mortgages, SMEs, credit cards). Non-interest charges: fees and cross-selling income are excluded; the true all-in lending margin may be higher.</t>
+          <t>The interest-rate spread on loans captures the margin between the average contractual rate a lender charges borrowers and an external reference rate—typically the policy rate. It is a concise gauge of (i) lenders’ credit-risk pricing, (ii) competitive conditions in the lending market, and (iii) monetary-policy transmission. Wider spreads may reflect higher perceived borrower risk, limited competition, or funding-cost pressures; persistently narrow spreads can point to aggressive underwriting or excess liquidity that may undermine future asset quality. Tracked over time and across peer institutions, interest-rate spreads provide insights into credit-cycle turning points, profitability dynamics, and the effectiveness of monetary-policy signals reaching the real economy. !- Definitions and concepts:  Loan interest rate spread (simple): Average contractual loan rate minus Reference rate measured for new originations or for the stock of loans. Net lending spread: average loan rate minus average deposit rate, often used when policy benchmarks are volatile. Segmented spreads: calculated by product (e.g., mortgages, MSMEs, credit cards). Non-interest charges: fees and cross-selling income are excluded; the true all-in lending margin may be higher.</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -12342,7 +12342,7 @@
       <c r="G224" t="inlineStr">
         <is>
           <t>Measures the percentage of customers who acquire one or more additional financial products or services at the time of onboarding (i.e., when opening their primary account or initiating a new relationship with a financial service provider). These additional products may include insurance, savings, credit, or investment add-ons linked to the initial product. Captures the prevalence of product bundling and cross-selling practices during customer onboarding. It provides insight into market behavior, product integration, and the extent to which customers are being offered or encouraged to take multiple products simultaneously. Monitoring product bundling helps regulators and providers:
-Assess consumer choice and informed consent during onboarding; Identify potential coercive or mis-selling practices; Evaluate financial literacy and customer understanding of product combinations; Analyze the integration of complementary services (e.g., savings plus micro-insurance); Support efforts to ensure responsible cross-selling and transparent disclosure. Bundling can enhance value and convenience when responsibly designed, but may also raise conduct or affordability risks if customers are not well-informed. High bundling rates may reflect integrated product offerings or effective cross-selling, but warrant review for consent and suitability. Low rates may indicate limited product integration or narrow customer engagement at onboarding. Trends can reveal shifts in market strategy, regulatory compliance, or consumer protection outcomes. !- Definitions and concepts: Bundled product: A package of two or more financial services offered together at onboarding (e.g., transaction account + insurance or credit line). Onboarding: The process of establishing a new customer relationship, including account opening and KYC verification. Cross-selling: Offering additional, often related, financial products to a new or existing customer. Informed consent: The customer’s clear understanding and voluntary acceptance of each product taken. !- Data requirements: Bundled product uptake rate (%)=Number of customers who acquired ≥1 additional product at onboarding​/Total number of new customers onboarded. Administrative or CRM data from financial institutions on new customer onboarding and product uptake. Disaggregation by institution type, customer segment (individual, SME), region, and product category. !- Derivable indicators: Average number of products per new customer; Distribution of additional products (e.g., % taking insurance, credit, savings add-ons)</t>
+Assess consumer choice and informed consent during onboarding; Identify potential coercive or mis-selling practices; Evaluate financial literacy and customer understanding of product combinations; Analyze the integration of complementary services (e.g., savings plus micro-insurance); Support efforts to ensure responsible cross-selling and transparent disclosure. Bundling can enhance value and convenience when responsibly designed, but may also raise conduct or affordability risks if customers are not well-informed. High bundling rates may reflect integrated product offerings or effective cross-selling, but warrant review for consent and suitability. Low rates may indicate limited product integration or narrow customer engagement at onboarding. Trends can reveal shifts in market strategy, regulatory compliance, or consumer protection outcomes. !- Definitions and concepts: Bundled product: A package of two or more financial services offered together at onboarding (e.g., transaction account + insurance or credit line). Onboarding: The process of establishing a new customer relationship, including account opening and KYC verification. Cross-selling: Offering additional, often related, financial products to a new or existing customer. Informed consent: The customer’s clear understanding and voluntary acceptance of each product taken. !- Data requirements: Bundled product uptake rate (%)=Number of customers who acquired ≥1 additional product at onboarding​/Total number of new customers onboarded. Administrative or CRM data from financial institutions on new customer onboarding and product uptake. Disaggregation by institution type, customer segment (individual, MSMEs), region, and product category. !- Derivable indicators: Average number of products per new customer; Distribution of additional products (e.g., % taking insurance, credit, savings add-ons)</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">

--- a/www/LENS_INDICATORS_DB.xlsx
+++ b/www/LENS_INDICATORS_DB.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L226"/>
+  <dimension ref="A1:L230"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6250,240 +6250,200 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Consumer protection</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Complaints handling, Safety and security</t>
+          <t>Outcomes</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Payments, Savings, Credit</t>
         </is>
       </c>
       <c r="D114">
-        <v>322</v>
+        <v>397</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Fraud prevalence in complaints</t>
+          <t>Account overdrafts and/or non-sufficient funds events</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Portion and volume of complaints received by providers, regulators, and ombuds that are fraud-related.</t>
+          <t>Frequency of account overdrafts, bounced payments, or non-sufficient funds (NSF) events over a defined period</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tracks how much of the complaint landscape is driven by fraud—both the count (volume) and the share (portion) of total complaints. Rising prevalence of frauds signals elevated customer harm, control weaknesses (KYC/AML, authentication, data security), or new attack vectors (social engineering). It helps guide supervision, consumer protection responses, reimbursement policies, and investment in fraud controls. !- Definitions and concepts: Fraud-related complaint: a case alleging unauthorised or deceptive activity resulting in loss or attempted loss—e.g., account takeover, card-not-present, phishing/SMiShing, SIM-swap, mule accounts, synthetic identity, merchant fraud, insider abuse, and authorised push payment (APP) scams. Volume: number of fraud-related complaints received in the period. Share: [# of fraud complaints / # of all complaints] x 100%. Intensity companions: fraud complaints per 1,000 customers or per 1 million transactions, value lens using claimed or confirmed loss amounts. Outcome cuts: upheld rate, reimbursement rate, median loss, time-to-resolution. A standard taxonomy for fraud types is needed, including the differentiation between fraud and disputed transaction. !- Limitations and considerations:  Under-reporting: many victims never complain or only contact the bank—triangulate with dispute/chargeback data and incident logs.</t>
+          <t>Measures how frequently individuals experience overdrafts, bounced payments, or fees resulting from insufficient account balances. These events are observable indicators of cashflow mismatches, where outgoing payments exceed available funds at the moment they are due. Higher frequency indicates more severe or persistent cashflow problems, and cumulative fees compound financial strain. !- Rationale: Overdrafts and NSF events are observable, objective markers of cashflow. Unlike subjective measures, these events are verifiable through bank records. Occasional overdrafts may reflect timing gaps, but frequent overdrafts indicate that a person is routinely unable to maintain sufficient liquidity. Assessed fees compound financial strain as a household already short on funds loses additional resources to penalty charges, potentially triggering a cycle of further shortfalls. For financial sector authorities, tracking overdraft incidence reveals the prevalence of acute liquidity stress and can inform policies on fee structures, consumer protection, and financial inclusion. !- Administrative data: Number of overdraft/NSF events per account per period; share of accounts experiencing one or more overdraft/NSF events; total fees charged per account due to overdrafts/NSF; average account balance at time of overdraft; repeat overdraft incidence (accounts with 3+ events). Aggregate NSF/overdraft fee revenue and payment system rejection rates can serve as system-level proxies where individual data is unavailable. !- Interpretation: This metric applies only to populations with transaction accounts. In mobile money-dominant markets, equivalent concepts include failed transactions due to insufficient balance or declined payments. Overdraft practices and fee structures vary across jurisdictions and must be understood when interpreting prevalence data.</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Are there gender differences in the proportion of fraud-related complaints submitted to providers, regulators, or ombuds services?  Do individuals of different genders tend to report different types of fraud, such as identity theft, phishing, or agent misconduct, and are specific delivery channels more commonly associated with these complaints? Is the volume of fraud-related complaints disproportionately high among certain gender groups when compared to their levels of account ownership or usage? Do complaint resolution rates and timeframes differ by gender across various FSP or reporting channels?</t>
+          <t>Do overdraft/NSF event rates differ between women and men? Are women more likely to incur repeated overdrafts due to income volatility or lower average balances? Do fee structures disproportionately burden lower-balance accounts, which may be more prevalent among women?</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>Quality</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered.</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints resolution outcome; Complaints resolution time</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Account type; Channel type</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Consumer protection</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Suitability</t>
+          <t>Outcomes</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings</t>
         </is>
       </c>
       <c r="D115">
-        <v>103</v>
+        <v>398</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Borrowers whose collateral was seized</t>
+          <t>Liquid savings (cash) buffer</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>% of borrowers whose collateral was seized</t>
+          <t>Availability of liquid financial resources that can be accessed quickly to cover unexpected expenses or income disruptions</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>A measure of loan portfolio/credit risk assessment quality or financial distress among borrowers. !- Data requirements: Granular data that can yield (1) A count of unique borrowers of secured loans (those with collateral requirements) who subsequently had collateral seized by lender due to default over a specific period of time (e.g. past quarter or past year), (2) Total unique borrowers of secured loans over a specific period of time.</t>
+          <t>Measures the availability of liquid financial resources (cash, bank account balances, money market funds and other cash-equivalent assets) that individuals or households can access quickly without needing to borrow or sell assets. Buffer adequacy is typically quantified in terms of months of living expenses or income that could be covered. Excludes retirement accounts with withdrawal restrictions or illiquid assets like property. !- Rationale: Emergency savings buffers represent the first line of defense against financial shocks such as job loss, medical emergencies, or economic downturns. Research consistently shows that emergency savings are associated with lower financial stress, better bill payment behavior, and reduced likelihood of material hardship following shocks. Without liquid reserves, even moderate financial shocks can cascade into missed payments, utility disconnections, asset fire sales, or dependence on high-cost credit. For financial sector authorities, tracking buffer adequacy reveals population vulnerability to economic disruptions and informs policies on savings incentives, emergency lending, and financial inclusion. !- Administrative data: Average and median liquid account balances (current + savings accounts); share of account holders with balances covering 1 month, 3 months, or 6+ months of expenses; distribution of balance-to-income or balance-to-expense ratios. Where regulators have balance data but not income or expense data, fixed reference amounts (such as GNI per capita/12 or the national poverty line) can be used as denominators. !- Interpretation: Administrative data captures only formal account balances and may miss informal savings (savings groups, cash at home). Living expenses vary month to month and may spike during emergencies. A buffer sufficient for normal months may be inadequate for large shocks.</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>How does the share of customers whose collateral was seized due to default vary by gender and othe rkey sociodemographics? Are women more or less likely than men to have their collateral seized following loan default? How does the share differ by gender across different loan sizes, loan products,  types of financial service providers (FSP), collateral type (e.g., movable, immovable, alternative)? And how do any of these differences relate to seizure rates? Are women more likely to be subject to stricter collateral requirements or less flexible repayment terms that increase the likelihood of asset seizure?</t>
+          <t>Do women maintain lower liquid savings buffers than men? Is the gender gap in savings buffers widening or narrowing over time? Are there differences in savings patterns by account type (e.g., mobile money vs. bank) that affect gendered buffer adequacy?</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Outcomes, Credit risk</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered.</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Loan type; Collateral type; Loan size; Loan term; Interest rate category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Account type; Deposit account type</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Consumer protection</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Complaints handling</t>
+          <t>Outcomes</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Savings, Pensions, Investments</t>
         </is>
       </c>
       <c r="D116">
-        <v>239</v>
+        <v>399</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Customer complaints (number)</t>
+          <t>Long-term saving and/or financial asset accumulation</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Number of customer complaints (including processing status, channels, type)</t>
+          <t>Whether individuals are actively setting aside money or accumulating financial assets for long-term purposes</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>This indicator tallies the formal expressions of dissatisfaction that retail or MSME clients lodge with a financial-service provider (or an external ombudsman) about products, services, or staff conduct over a specified period and can be normalized by dividing by the customer basis to obtain an intensity metric (e.g. complaints per 1,000 active customers). A rising complaint count can signal service-quality gaps, mis-selling, opaque fees, or inadequate disclosure—issues that erode trust and may escalate into regulatory sanctions or litigation. Supervisors can track both the absolute number and complaint-to-account ratios to test consumer-protection frameworks, prioritise thematic reviews, and assess whether rapid product roll-outs (e.g., digital lending, mobile wallets) are being matched by robust after-sales support. Where granular data or more detailed reporting templates permit, customer complaints can be disaggregated by processing status (e.g. received, accepted/rejected, in process, resolved, escalated/disputed, withdrawn), product (e.g. consumer loan, deposit account, etc), channel (e.g. digital, phone, in-person), issue category (e.g. fraudulent or unauthorized transactions, unfair treatment, unexpected fees, errors on statements,  etc.), resolution status (open, resolved with monetary compensation, resolved without compensation, escalated to ombudsman/regulator, other). Combined with resolution-time, compensation and other metrics, the number of customer complaints provides a critical, early-warning lens on conduct risk and customer-experience health. !- Definitions and concepts:  Complaints are expressions of dissatisfaction by (or on behalf of) customers that are related to their experiences with FSPs and can include any written, digital or recorded verbal statement made through any available channel, such as a branch, call-centre, email, social media, chatbots and other portals. Complaints may relate to the quality of a product or service, treatment by an FSP (including its agents and other third parties), or suspected wrongdoing. Complaints are different from general inquiries (e.g., where can I find an ATM?) or legal disputes between parties that may require formal dispute resolution. For more information, see for example CGAP's toolkit on using complaints data for market conduct supervision: https://www.cgap.org/research/publication/market-monitoring-tool-analysis-complaints-data and the Alliance for Financial Inclusion's framework on 'Complaint handling in Central Banks': https://www.afi-global.org/sites/default/files/publications/2020-04/AFI_CEMC_framework_AW_digital%20v2.pdf. !- Data requirements:  Database or log of customer complaints, detailing date of complaint and additional information, such as channel through which complaint was lodged, associated product or account, details or brief description of the complaint, and resolution status. !- Limitations and considerations: Complaints processes differ across FSPs in terms of steps/levels for routing, hand-over, escalations to higher management levels and to external ombudsman. Customer details and demographics of complainants are not always capture/stored on FSPs' systems, or may be stored in fragmented data bases. Complaints logged at aggregator sites/portals may not request customer demographics. Limited to officially logged complaints and/or maintaining records of inbound customer communications. Dependent on having electronic complaints management system.  Reporting culture: firms with easy‐to‐use channels may record more complaints than peers, even if service quality is similar—benchmark using severity and uphold rates. Under-reporting bias: vulnerable customers may forgo formal complaints; mystery-shopping and survey data can complement administrative counts. Duplicate cases: the same issue voiced through multiple channels can inflate totals unless robust deduplication exists. Product mix effects: complaint propensity varies—e.g., complex investments draw more grievances than basic savings; segment analysis is essential. Regulatory divergence: definitions and mandatory reporting thresholds differ across jurisdictions, complicating cross-border comparisons.</t>
+          <t>Measures whether individuals are actively setting aside money or accumulating financial assets for long-term purposes such as retirement, education, home purchase, business investment, or other life goals. Captures both participation (whether saving or investing is occurring) and, where possible, stock (balances of long-term financial assets). The focus is on forward-looking, wealth-building behavior rather than precautionary savings. Key asset types include pension/retirement accounts, investment or brokerage accounts, and long-term savings or time-deposit accounts. !- Rationale: The ability to pursue aspirations, goals, and capture opportunities is a core dimension of financial wellbeing. Long-term saving and investing is the primary mechanism through which this is achieved. Without systematic wealth accumulation, individuals face precarious retirements, inability to invest in opportunities, and dependence on costly borrowing or social safety nets. For financial sector authorities, tracking participation in long-term saving and investment reveals the extent to which populations are building financial security and can inform policies on pension coverage, savings incentives, and inclusion in retail investment products. !- Administrative data: Number/share of adults with active long-term savings or investment accounts; net inflows to long-term savings and investment products; average and median balances in long-term accounts; pension active contributor counts relative to working-age population; retail investor account counts from securities regulators or central depositories. !- Interpretation: Appropriate benchmarks vary by age: young adults may appropriately have lower balances, while those near retirement should have accumulated significant assets. In many contexts, long-term saving takes the form of physical assets (land, livestock) rather than financial instruments and administrative data may not capture these.</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>How does the number of complaints at each processing stage vary by gender? Are complaints disproportionately concentrated at certain processing stages for any gender? How do FSPs compare to market averages in the number of complaints at each processing stage?"</t>
+          <t>Do women show lower rates of long-term savings and investment participation than men? At what age do women versus men begin accumulating long-term financial assets? Are gender gaps in long-term savings driven by income differences, access barriers, or product design?</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Quality</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered.</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints filing channel; Complaints issue category; Complaints processing status; Complaints resolution outcome; Complaints resolution time</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Account type; Product type</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Consumer protection</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Complaints handling</t>
+          <t>Outcomes</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Payments, Savings, Credit</t>
         </is>
       </c>
       <c r="D117">
-        <v>243</v>
+        <v>400</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Customer complaints resolved in the customer's favor</t>
+          <t>Positive net cashflow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>% of customer complaints that were solved in the customer's favor in the most recent period</t>
+          <t>Whether total income exceeds total expenses over a defined period, indicating ability to build savings and reduce debt</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>This indicator shows the share of complaints closed in the reference period that were resolved in the customer’s favor. It is a direct outcome metric for fair treatment and service quality. A higher “uphold rate” can indicate strong remediation and customer-centric policies; a very low rate may suggest poor triage, overly narrow eligibility rules, or weak guidance to customers on evidence requirements. Supervisors use it to benchmark conduct outcomes across firms and products; boards track it alongside complaint volumes and resolution times to target root-cause fixes. Tracked with complaint volume, resolution time, and compensation totals, this indicator provides a balanced view of consumer outcomes and conduct risk. !- Definitions and concepts: Resolved in the customer’s favor (upheld): final decision grants redress—monetary (refund/compensation/fee reversal) or non-monetary (policy correction, contract change, apology with tangible remedy). Many firms also count partially upheld cases; disclose whether partials are included. Denominator: all complaints closed in the period. Segment results by product, channel, and severtiy to avoid masking problem areas. !- Data requirements: Central complaint-management records with unique IDs, receipt date, closure date, product, channel, allegation type, decision outcome (upheld/partially/declined), and compensation amount. Deduplication logic across channels; linkages to ombudsman/regulator portals for escalations and reversals. Customer-base denominator (for intensity metrics) and service level agreement (SLA) timestamps for parallel monitoring* (see note below). !- Limitations and considerations: Classification discretion: definitions of “partial uphold” vary; publish inclusion rules. Case mix effects: a surge in low-merit mass claims can depress the percentage; report severity-adjusted or line-of-business cuts. Gaming risk: chasing high uphold rates may encourage paying weak claims; pair with fraud flags, root-cause fixes, and cost-per-case. Timing bias: complex cases close later and differ in uphold propensity; use rolling averages and track median resolution time. External outcomes: include overturned-on-appeal adjustments to reflect true customer outcome. *With granular time-stamped complaints data, timeliness of key milestones in the complaints resolution process can be tracked, for example time to acknowledge complaint, time to first response, time to resolution. With this data, supervisors can track not just outcomes, but also whether providers are meeting required timeframes per their own SLA.</t>
+          <t>Net cashflow measures the difference between an individual's or household's total income and total expenses over a defined period. A positive net cashflow indicates money left over after meeting expenses; a negative net cashflow indicates a shortfall that must be covered by drawing down savings or taking on debt. Total income includes wages, self-employment earnings, transfers, and remittances; total expenses include consumption, bills, loan repayments, and other obligations. With administrative data, income may be proxied by total account inflows and expenses by total outflows, requiring careful treatment of inter-account transfers. !- Rationale: Positive net cashflow is a foundational indicator of financial health. The ability to spend less than income directly determines whether an individual can build savings, reduce debt, invest for the future, or absorb unexpected expenses. When expenses chronically exceed income, households are forced to deplete savings or accumulate debt, eroding resilience over time. For financial sector authorities, tracking population-level net cashflow trends provides early warning of emerging financial stress: declining cashflow margins may precede rising delinquencies, increased reliance on high-cost credit, and deteriorating savings buffers. !- Administrative data: Net inflows minus net outflows per account per period (excluding inter-account transfers); share of accounts with positive net cashflow; expense-to-income ratio distribution; count of months where spending exceeds 90% of inflows; minimum liquid balance over the measurement period. Inter-account transfers must be excluded to avoid double-counting. If only partial account data is available, net cashflow will be incomplete. !- Interpretation: The time period is a critical design choice. Monthly net cashflow can be volatile due to timing of income and expenses. Longer measurement periods (3-12 months) smooth seasonal and idiosyncratic variation. Life-cycle factors (students, retirees) produce legitimately negative cashflow that does not necessarily indicate distress.</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>How do the percentages of complaints resolved in favor of customers vary by gender? Are any genders more likely to receive favorable resolutions? How do FSPs rank in terms of favorable resolutions by gender?</t>
+          <t>Do women show systematically lower net cashflow than men? Is the gender gap in net cashflow driven by income differences, expense patterns, or both? How does net cashflow vary by household type (single vs. dual income) and how does this affect gendered financial health outcomes?</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Quality</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered.</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints filing channel; Complaints issue category; Complaints processing status; Complaints resolution outcome; Complaints resolution time</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Account type; Channel type</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6455,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Data privacy and protection</t>
+          <t>Complaints handling, Safety and security</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6504,26 +6464,26 @@
         </is>
       </c>
       <c r="D118">
-        <v>234</v>
+        <v>322</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Consent rate for FSP contact</t>
+          <t>Fraud prevalence in complaints</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>% of customers who provide consent to be contacted in the future by the FSP for sales, awareness and new offerings</t>
+          <t>Portion and volume of complaints received by providers, regulators, and ombuds that are fraud-related.</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Measures the percentage of customers who have provided explicit consent to be contacted in the future by their financial service provider (FSP) for purposes such as product marketing, customer awareness campaigns, or information on new offerings. This indicator reflects how institutions manage customer permissions for communication under applicable data privacy and marketing regulations. Captures the extent of customer consent and data-use transparency in the financial system, serving as a proxy for compliance with consent-based communication standards and the balance between customer engagement and data protection. Tracking customer contact consents helps regulators and providers: Monitor compliance with data protection and privacy laws (e.g., GDPR-like frameworks, data protection acts); Assess ethical marketing practices and responsible customer engagement; Evaluate trust and willingness of customers to maintain open communication with FSPs; Understand customer attitudes toward data sharing and digital outreach. For supervisors, it provides a measurable view of market conduct, customer empowerment, and institutional transparency. High consent rates suggest strong customer trust and engagement, but may require close monitoring to ensure non-coercive consent collection and ethical marketing practices. Low consent rates may reflect privacy concerns, limited digital literacy, or overly complex consent processes. Changes over time can signal shifts in consumer sentiment or compliance practices following new regulations. !- Definitions and concepts: Consent: A freely given, informed, and specific agreement by a customer allowing the FSP to contact them for defined purposes. Data privacy regulation: Legal framework governing the collection, storage, and use of personal data, including consent requirements for marketing communications. !- Data requirements: Administrative data from FSP customer relationship management (CRM) or consent-management systems to obtain the number of customers who provided consent to be contact and the total number of customers.</t>
+          <t>Tracks how much of the complaint landscape is driven by fraud—both the count (volume) and the share (portion) of total complaints. Rising prevalence of frauds signals elevated customer harm, control weaknesses (KYC/AML, authentication, data security), or new attack vectors (social engineering). It helps guide supervision, consumer protection responses, reimbursement policies, and investment in fraud controls. !- Definitions and concepts: Fraud-related complaint: a case alleging unauthorised or deceptive activity resulting in loss or attempted loss—e.g., account takeover, card-not-present, phishing/SMiShing, SIM-swap, mule accounts, synthetic identity, merchant fraud, insider abuse, and authorised push payment (APP) scams. Volume: number of fraud-related complaints received in the period. Share: [# of fraud complaints / # of all complaints] x 100%. Intensity companions: fraud complaints per 1,000 customers or per 1 million transactions, value lens using claimed or confirmed loss amounts. Outcome cuts: upheld rate, reimbursement rate, median loss, time-to-resolution. A standard taxonomy for fraud types is needed, including the differentiation between fraud and disputed transaction. !- Limitations and considerations:  Under-reporting: many victims never complain or only contact the bank—triangulate with dispute/chargeback data and incident logs.</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>How do consent rates for customer contact vary by gender? Are any genders more likely to provide consent to be contacted? How do FSPs rank in terms of consent rates by gender?</t>
+          <t>Are there gender differences in the proportion of fraud-related complaints submitted to providers, regulators, or ombuds services?  Do individuals of different genders tend to report different types of fraud, such as identity theft, phishing, or agent misconduct, and are specific delivery channels more commonly associated with these complaints? Is the volume of fraud-related complaints disproportionately high among certain gender groups when compared to their levels of account ownership or usage? Do complaint resolution rates and timeframes differ by gender across various FSP or reporting channels?</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6543,7 +6503,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints resolution outcome; Complaints resolution time</t>
         </is>
       </c>
     </row>
@@ -6555,28 +6515,268 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
+          <t>Suitability</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="D119">
+        <v>103</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Borrowers whose collateral was seized</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>% of borrowers whose collateral was seized</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>A measure of loan portfolio/credit risk assessment quality or financial distress among borrowers. !- Data requirements: Granular data that can yield (1) A count of unique borrowers of secured loans (those with collateral requirements) who subsequently had collateral seized by lender due to default over a specific period of time (e.g. past quarter or past year), (2) Total unique borrowers of secured loans over a specific period of time.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>How does the share of customers whose collateral was seized due to default vary by gender and othe rkey sociodemographics? Are women more or less likely than men to have their collateral seized following loan default? How does the share differ by gender across different loan sizes, loan products,  types of financial service providers (FSP), collateral type (e.g., movable, immovable, alternative)? And how do any of these differences relate to seizure rates? Are women more likely to be subject to stricter collateral requirements or less flexible repayment terms that increase the likelihood of asset seizure?</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Outcomes, Credit risk</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Loan type; Collateral type; Loan size; Loan term; Interest rate category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Complaints handling</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D120">
+        <v>239</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Customer complaints (number)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Number of customer complaints (including processing status, channels, type)</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>This indicator tallies the formal expressions of dissatisfaction that retail or MSME clients lodge with a financial-service provider (or an external ombudsman) about products, services, or staff conduct over a specified period and can be normalized by dividing by the customer basis to obtain an intensity metric (e.g. complaints per 1,000 active customers). A rising complaint count can signal service-quality gaps, mis-selling, opaque fees, or inadequate disclosure—issues that erode trust and may escalate into regulatory sanctions or litigation. Supervisors can track both the absolute number and complaint-to-account ratios to test consumer-protection frameworks, prioritise thematic reviews, and assess whether rapid product roll-outs (e.g., digital lending, mobile wallets) are being matched by robust after-sales support. Where granular data or more detailed reporting templates permit, customer complaints can be disaggregated by processing status (e.g. received, accepted/rejected, in process, resolved, escalated/disputed, withdrawn), product (e.g. consumer loan, deposit account, etc), channel (e.g. digital, phone, in-person), issue category (e.g. fraudulent or unauthorized transactions, unfair treatment, unexpected fees, errors on statements,  etc.), resolution status (open, resolved with monetary compensation, resolved without compensation, escalated to ombudsman/regulator, other). Combined with resolution-time, compensation and other metrics, the number of customer complaints provides a critical, early-warning lens on conduct risk and customer-experience health. !- Definitions and concepts:  Complaints are expressions of dissatisfaction by (or on behalf of) customers that are related to their experiences with FSPs and can include any written, digital or recorded verbal statement made through any available channel, such as a branch, call-centre, email, social media, chatbots and other portals. Complaints may relate to the quality of a product or service, treatment by an FSP (including its agents and other third parties), or suspected wrongdoing. Complaints are different from general inquiries (e.g., where can I find an ATM?) or legal disputes between parties that may require formal dispute resolution. For more information, see for example CGAP's toolkit on using complaints data for market conduct supervision: https://www.cgap.org/research/publication/market-monitoring-tool-analysis-complaints-data and the Alliance for Financial Inclusion's framework on 'Complaint handling in Central Banks': https://www.afi-global.org/sites/default/files/publications/2020-04/AFI_CEMC_framework_AW_digital%20v2.pdf. !- Data requirements:  Database or log of customer complaints, detailing date of complaint and additional information, such as channel through which complaint was lodged, associated product or account, details or brief description of the complaint, and resolution status. !- Limitations and considerations: Complaints processes differ across FSPs in terms of steps/levels for routing, hand-over, escalations to higher management levels and to external ombudsman. Customer details and demographics of complainants are not always capture/stored on FSPs' systems, or may be stored in fragmented data bases. Complaints logged at aggregator sites/portals may not request customer demographics. Limited to officially logged complaints and/or maintaining records of inbound customer communications. Dependent on having electronic complaints management system.  Reporting culture: firms with easy‐to‐use channels may record more complaints than peers, even if service quality is similar—benchmark using severity and uphold rates. Under-reporting bias: vulnerable customers may forgo formal complaints; mystery-shopping and survey data can complement administrative counts. Duplicate cases: the same issue voiced through multiple channels can inflate totals unless robust deduplication exists. Product mix effects: complaint propensity varies—e.g., complex investments draw more grievances than basic savings; segment analysis is essential. Regulatory divergence: definitions and mandatory reporting thresholds differ across jurisdictions, complicating cross-border comparisons.</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>How does the number of complaints at each processing stage vary by gender? Are complaints disproportionately concentrated at certain processing stages for any gender? How do FSPs compare to market averages in the number of complaints at each processing stage?"</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints filing channel; Complaints issue category; Complaints processing status; Complaints resolution outcome; Complaints resolution time</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Complaints handling</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D121">
+        <v>243</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Customer complaints resolved in the customer's favor</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>% of customer complaints that were solved in the customer's favor in the most recent period</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>This indicator shows the share of complaints closed in the reference period that were resolved in the customer’s favor. It is a direct outcome metric for fair treatment and service quality. A higher “uphold rate” can indicate strong remediation and customer-centric policies; a very low rate may suggest poor triage, overly narrow eligibility rules, or weak guidance to customers on evidence requirements. Supervisors use it to benchmark conduct outcomes across firms and products; boards track it alongside complaint volumes and resolution times to target root-cause fixes. Tracked with complaint volume, resolution time, and compensation totals, this indicator provides a balanced view of consumer outcomes and conduct risk. !- Definitions and concepts: Resolved in the customer’s favor (upheld): final decision grants redress—monetary (refund/compensation/fee reversal) or non-monetary (policy correction, contract change, apology with tangible remedy). Many firms also count partially upheld cases; disclose whether partials are included. Denominator: all complaints closed in the period. Segment results by product, channel, and severtiy to avoid masking problem areas. !- Data requirements: Central complaint-management records with unique IDs, receipt date, closure date, product, channel, allegation type, decision outcome (upheld/partially/declined), and compensation amount. Deduplication logic across channels; linkages to ombudsman/regulator portals for escalations and reversals. Customer-base denominator (for intensity metrics) and service level agreement (SLA) timestamps for parallel monitoring* (see note below). !- Limitations and considerations: Classification discretion: definitions of “partial uphold” vary; publish inclusion rules. Case mix effects: a surge in low-merit mass claims can depress the percentage; report severity-adjusted or line-of-business cuts. Gaming risk: chasing high uphold rates may encourage paying weak claims; pair with fraud flags, root-cause fixes, and cost-per-case. Timing bias: complex cases close later and differ in uphold propensity; use rolling averages and track median resolution time. External outcomes: include overturned-on-appeal adjustments to reflect true customer outcome. *With granular time-stamped complaints data, timeliness of key milestones in the complaints resolution process can be tracked, for example time to acknowledge complaint, time to first response, time to resolution. With this data, supervisors can track not just outcomes, but also whether providers are meeting required timeframes per their own SLA.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>How do the percentages of complaints resolved in favor of customers vary by gender? Are any genders more likely to receive favorable resolutions? How do FSPs rank in terms of favorable resolutions by gender?</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints filing channel; Complaints issue category; Complaints processing status; Complaints resolution outcome; Complaints resolution time</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Data privacy and protection</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D122">
+        <v>234</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Consent rate for FSP contact</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>% of customers who provide consent to be contacted in the future by the FSP for sales, awareness and new offerings</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Measures the percentage of customers who have provided explicit consent to be contacted in the future by their financial service provider (FSP) for purposes such as product marketing, customer awareness campaigns, or information on new offerings. This indicator reflects how institutions manage customer permissions for communication under applicable data privacy and marketing regulations. Captures the extent of customer consent and data-use transparency in the financial system, serving as a proxy for compliance with consent-based communication standards and the balance between customer engagement and data protection. Tracking customer contact consents helps regulators and providers: Monitor compliance with data protection and privacy laws (e.g., GDPR-like frameworks, data protection acts); Assess ethical marketing practices and responsible customer engagement; Evaluate trust and willingness of customers to maintain open communication with FSPs; Understand customer attitudes toward data sharing and digital outreach. For supervisors, it provides a measurable view of market conduct, customer empowerment, and institutional transparency. High consent rates suggest strong customer trust and engagement, but may require close monitoring to ensure non-coercive consent collection and ethical marketing practices. Low consent rates may reflect privacy concerns, limited digital literacy, or overly complex consent processes. Changes over time can signal shifts in consumer sentiment or compliance practices following new regulations. !- Definitions and concepts: Consent: A freely given, informed, and specific agreement by a customer allowing the FSP to contact them for defined purposes. Data privacy regulation: Legal framework governing the collection, storage, and use of personal data, including consent requirements for marketing communications. !- Data requirements: Administrative data from FSP customer relationship management (CRM) or consent-management systems to obtain the number of customers who provided consent to be contact and the total number of customers.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>How do consent rates for customer contact vary by gender? Are any genders more likely to provide consent to be contacted? How do FSPs rank in terms of consent rates by gender?</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D119">
+      <c r="D123">
         <v>284</v>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="E123" t="inlineStr">
         <is>
           <t>Annual percentage rate (APR) for retail credit</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>Average cost of borrowing money, including fees to get the loan, as a% of the loan principal (except for credit cards)</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>APR is the standardized annualized cost of borrowing that incorporates the contractual interest rate plus certain up-front or periodic fees required to obtain and maintain the credit. It lets consumers compare offers across lenders and products on a like-for-like basis, and helps supervisors monitor pricing fairness and market competitiveness. Unlike a simple “nominal” rate, APR reflects timing of cash flows and required charges, so it better approximates the true price of credit. !- Definitions and concepts: Installment credit APR (actuarial method): the internal rate of return (IRR) that equates the amount advanced to the borrower with the present value of all required payments (principal, interest, and included fees), expressed on an annual basis.
 Revolving credit APR (cards/overdrafts): the periodic rate applied to the average daily balance, annualized (e.g., daily rate × 365 or monthly rate × 12), plus disclosure of any mandatory fees as prescribed. Scope of fees: typically includes origination/processing fees and compulsory charges; excludes penalty fees and optional add-ons (unless mandated). APR vs. EIR: APR is a consumer disclosure metric (jurisdiction-specific rules); EIR is an accounting yield used to recognize interest income.!- Data requirements: Contract terms: principal advanced, repayment schedule (dates/amounts), nominal rate, compounding frequency, and variable-rate index/margins. Included fees: origination/processing, mandatory maintenance or platform fees, financed vs. paid-in-cash. For revolving products: periodic rate(s), balance computation method (average daily balance), mandatory annual fees, grace-period rules, promotional/teaser rates.
@@ -6584,364 +6784,364 @@
 Promotions &amp; step-ups: teaser or deferred-interest offers can make snapshot APRs unrepresentative—show lifetime-effective examples when possible. Variable rates: APR at origination may understate future cost if reference rates rise. Loan term effects: fixed fees loom larger on short tenors; present both APR and the fee share of cost for transparency.</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="H123" t="inlineStr">
         <is>
           <t>Are there gender disparities in the APR applied to loans disbursed to women and men, including MSMEs by gender of ownership? Do women borrowers systematically face higher average APRs than men within the same loan type, amount range, or provider category? Are higher APRs for women associated with smaller loan sizes, shorter maturities, or higher perceived credit risk? Do FSPs with greater gender diversity or stronger inclusion policies show smaller gender gaps in average APRs? How do APR differences relate to borrower profiles and do they suggest the presence of gender-based pricing bias or structural credit segmentation?</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
         <is>
           <t>Financial inclusion; Market development</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="K123" t="inlineStr">
         <is>
           <t>Quality, Competition</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+    <row r="124">
+      <c r="A124" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>Data privacy and protection</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
-      <c r="D120">
+      <c r="D124">
         <v>235</v>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>Consents for sharing data with third-parties</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>% of customers who have given explicit consent for their data to be shared by FSPs with third parties, for various purposes</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>This indicator shows how many customers have actively opted in to let a financial service provider (FSP) share their data with external parties—for open-banking/aggregation, credit scoring, fraud prevention, marketing, analytics, etc. A higher share can reflect strong digital adoption and trust; low or falling rates may signal poor consent UX, unclear value propositions, or privacy concerns. It helps compliance teams evidence lawfulness, product teams gauge partner-integration reach, and supervisors assess the maturity of consent-based data-sharing ecosystems. !- Definitions and concepts: Explicit consent: a clear, affirmative action (e.g., checked box, strong-customer-authenticated authorization) tied to a specific purpose, with intelligible notice and the ability to withdraw at any time. Active consent: consent that is valid as of the reference date (not expired, not withdrawn, not superseded). Purpose taxonomy: e.g., account information services (AIS), payment initiation services (PIS), credit decisioning/bureau pulls, fraud/AML tools, personalised marketing, data portability. Metric: % of customer with active consent for purpose p = [# of unique customers with at least 1 active consent for p / # of active customers] x 100%. Indicator companions: Any-purpose consent, consents per consenting customer and revocation rate. !- Data requirements: Consent ledger that includes: customer ID, purpose(s) granted, third-party identity, channel, timestamp, expiry/refresh cycle, version of the privacy notice, proof of consent (hash, audit trail, SCA event). Status events: withdrawals, expiries, scope changes, third-party disconnects. Reference universe: deduplicated active-customer list (define “active”: e.g., ≥1 product in force or ≥1 login/transaction in last 12 months). !- Limitations and considerations: Granularity &amp; fragmentation: a customer may consent per app, per account, and per purpose; avoid double counting by using unique customers and report purpose-level cuts. Expiry &amp; refresh: open-banking tokens often have short authorizations; snapshot dates vs. rolling windows will yield different figures—disclose method. Consumer protection risk: high opt-ins driven by coercive UX can backfire (complaints, revocations); pair with revocation rate, time-to-revocation, and complaints about data sharing. Coverage gaps: legacy channels without digital capture may under-record historical consents; backfill or disclose limitations.</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="H124" t="inlineStr">
         <is>
           <t>How do consent rates for data sharing with third parties vary by gender? Are any genders more likely to provide consent for data sharing? How do FSPs rank in terms of consent rates for data sharing by gender?</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
         <is>
           <t>Market development</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="K124" t="inlineStr">
         <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+    <row r="125">
+      <c r="A125" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D121">
+      <c r="D125">
         <v>260</v>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>Late penalty charges/fees on retail credit</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>Income from penalty fees as % of total net interest income</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>This indicator shows how much of a lender is relying on penalty fees for income. Revenue from penalty fees and other charges applied when a loan payment is late is compared with the total gross interest income. A high share could signal borrower stress and potential conduct risk (reliance on punitive pricing). Boards and supervisors use the metric to assess earnings quality, pricing fairness. !- Definitions and concepts: Penalty/default fees and charges: the fees and costs charged once a loan  is past due. Numerator (preferred “incremental” view): Penalty actually recognized as income on retail loans during the period. Denominator: Gross interest income. !- Data requirements: General-ledger mapping that identifies penalty income at product level. Period interest income totals for the denominator.  !- Limitations and considerations: Mix effects: card-heavy books show higher shares of penalty income; segment by product. Conduct lens: pair with % customers incurring penalty charges, related complaints.</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="H125" t="inlineStr">
         <is>
           <t>What percentages of net interest income are attributable to penalties and other punitive charges earned from borrowers of unsecured loans/lines of credit, and how do these vary by gender across age bands and location types, at a total market level and by relevant FSP/type? How do these percentages compare across relevant FSPs/types and against market norms across age bands and location types? How do gender disparities manifest in these percentages at a total market level and by relevant FSP/type?</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+    <row r="126">
+      <c r="A126" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D122">
+      <c r="D126">
         <v>185</v>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="E126" t="inlineStr">
         <is>
           <t>Processing and application fees or PAF (as % of loan principal)</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>PAF as % of loan principal in unsecured credit operations</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>This indicator expresses the total up-front charges borrowers pay to originate an unsecured loan—processing fees, application fees, documentation charges—as a percentage of the loan’s principal amount. Because unsecured credit often targets price-sensitive segments and carries higher risk-based interest rates, excessive PAFs can materially raise the all-in cost of borrowing, undermine affordability tests, and trigger consumer-protection scrutiny. Tracking the ratio helps regulators detect predatory pricing, compare lenders’ transparency practices, and gauge competition in loan-origination services. For lenders, it is a barometer of non-interest revenue reliance and a lever for recouping acquisition costs. Processing &amp; Application Fees (PAF): any non-refundable charge levied at or before disbursement for administrative tasks (credit checks, KYC, documentation, platform usage). Late-payment or insurance fees are excluded.
 PAF ratio (simple): [Total PAF charged/Gross loan principal]×100%
 Where multiple partial disbursements occur, use the aggregate principal amount. Annualised impact: when PAFs are capitalised into the Effective Annual Percentage Rate (APR), their weight declines as term length rises—monitor both absolute and APR-embedded views. !- Data requirements: Loan-level records capturing principal, disbursement date, PAF amount, and any rebates for cancellations. Product codes distinguishing personal instalment loans, credit-card cash advances, payday/BNPL equivalents. Borrower demographics and channel identifiers (branch, mobile app, marketplace) for segmentation. Accounting entries showing whether fees are recognised up-front (IFRS 15 “contract costs”) or amortised via the effective-interest-rate (EIR) method. !- Limitations and considerations: Amortisation differences: Lenders using EIR spread PAFs over the loan’s life; comparing ratios on a cash basis versus amortised income can mislead. Bundled products: Cross-selling (e.g., credit-life insurance) may shift income from PAF to commissions, understating the ratio. Regulatory caps &amp; disclosures: Jurisdictions with fee ceilings or mandatory APR disclosures compress PAF ratios; cross-country benchmarking must control for such rules. Loan term effects: Short-tenor payday or BNPL loans show high PAF percentages even when absolute fees are small; interpret in context of maturity profile and APR. Waivers &amp; promotions: Temporary fee holidays for marketing campaigns can distort time-series trends—flag promotional periods separately. Should FSPs not be allowed/willing to share sensitive revenue data, ratios/percentages can be performed in-house and then shared with regulator.</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="H126" t="inlineStr">
         <is>
           <t>What are the origination fee percentages as a share of loan principal by gender? Are there gender disparities in the origination fee percentages incurred? How do FSPs rank in terms of origination fee percentages by gender?</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="L126" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+    <row r="127">
+      <c r="A127" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>Data privacy and protection</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
-      <c r="D123">
+      <c r="D127">
         <v>232</v>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E127" t="inlineStr">
         <is>
           <t>Data breaches</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>% of customers affected by data breaches</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>A measure of the depth of cyberattacks or other data security breach that result in unauthorized access to customer data. Definitions and concept: A data breach is any security incident in which unauthorized parties access sensitive or confidential information, including personal data (tax numbers, ID information, bank account numbers, healthcare data) and corporate data (customer records, intellectual property, financial information). Data requirement: Number of customers whose data was accessed without authorization during a specified period of time (e.g. quarter or year); Total number of customers at the beginning of the specified period (e.g. quarter or year).</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>How does the percentage of customers affected by data breaches vary by gender? Are any genders disproportionately affected by data breaches? Are data breaches more frequent in certain types of FSPs? Are data breaches more common in specific channels or interfaces?"</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
         <is>
           <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="K127" t="inlineStr">
         <is>
           <t>Quality, Operational risk</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="L127" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>Depositor protection</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>Savings</t>
         </is>
       </c>
-      <c r="D124">
+      <c r="D128">
         <v>15</v>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>Deposit accounts covered by direct deposit insurance</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>Volume and value (balances) of deposit accounts covered by direct deposit insurance</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>This indicator counts (or expresses as a percentage) the deposit accounts that fall within the scope of an explicit, statutory deposit insurance scheme (DIS) or deposit guarantee fund. It helps supervisors gauge how much of the retail/MSME funding base is protected against bank failure. This is key for financial stability monitoring, payout readiness, and for calibrating the deposit insurance/guarantee fund. High coverage supports confidence and can dampen run dynamics. Source: https://www.iadi.org/uploads/cprevised2014nov.pdf. !- Definitions and concepts: Covered (eligible) account: a deposit type included by law. Fully insured vs. partially insured: “Fully insured” balances are ≤ the coverage limit per depositor, per bank, per ownership category; “covered/eligible” may include accounts whose balances exceed the cap (partially insured). Ownership categories: individual, joint, trust/fiduciary, retirement—rules vary by jurisdiction and affect aggregation across accounts. Indicator variants: % Eligible accounts = eligible deposit accounts ÷ total deposit accounts. Insured balance share = insured amounts in eligible accounts ÷ total deposit balances in eligible accounts. Dormancy: dormant accounts may be treated differently in coverage statistics.</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="H128" t="inlineStr">
         <is>
           <t>Are there gender disparities in the number of deposit accounts covered by direct deposit insurance? How do these disparities vary by age, income level, and geographic location? Are certain gender groups, especially within vulnerable or low-income populations, less likely to hold insured deposit accounts? How do the average insured deposit account balances differ across genders, and what might this indicate about savings behavior, access to financial protection, or economic security? Do financial service providers with higher levels of gender diversity in leadership or staff tend to offer more equitable access to insured deposit accounts and balanced coverage across genders? Additionally, how do gender differences in insured deposit accounts relate to broader financial inclusion and resilience against financial shocks?</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="K128" t="inlineStr">
         <is>
           <t>Quality, Suitability</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="L128" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Deposit account type</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Depositor protection</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Savings</t>
         </is>
       </c>
-      <c r="D125">
+      <c r="D129">
         <v>16</v>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E129" t="inlineStr">
         <is>
           <t>G2P accounts covered by deposit insurance</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>% of all accounts receiving G2P payments that are covered by deposit protection</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>This indicator helps analyze the extent to which low-value accounts are covered by deposit insurance or other protection. It focuses on account holders who are recipients of G2P programs. It quantifies how many of the government-to-person (G2P) payments recipients are protected by an explicit deposit insurance scheme or guarantee fund. It can be shown as (a) the share of G2P accounts that are eligible/fully insured and/or (b) the insured share of G2P balances. This indicator informs strategies for insurance/coverage payouts and the calibration of the deposit insurance fund. Definitions  and concepts: G2P account: an account that receives social transfers, government pensions, subsidies, or cash-benefit programs.
 Covered (eligible) vs. fully insured: “Eligible” products fall within the deposit insurance scope; “fully insured” means the balance per beneficiary per insured bank does not exceed the coverage cap. 
@@ -6950,789 +7150,549 @@
 Core-banking (and, where applicable, e-money) extracts: product code, ownership category, end-of-day balance, currency. Rules engine encoding national deposit-insurance scope, limits, and aggregation logic (per depositor—per bank). Sub-ledger data for pooled/FBO accounts to support pass-through eligibility. Timing sensitivity: balances spike on disbursement days; define the snapshot (e.g., month-end vs. T+2 after payout).</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>Are there gender disparities in the number of G2P accounts covered by deposit insurance? How do these disparities vary across different age groups, income levels, and geographic locations? Are women and other gender groups within vulnerable populations less likely to have G2P accounts that are insured, potentially affecting their financial security? How do the average balances of insured G2P accounts compare across genders, and what does this imply about economic empowerment and financial resilience? Do government programs and financial service providers with greater gender diversity in design or delivery show more equitable insurance coverage of G2P accounts? Additionally, how do gender differences in insured G2P accounts influence overall inclusion and access to social safety nets?</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
+      <c r="K129" t="inlineStr">
         <is>
           <t>Quality, Suitability, Stability</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
+      <c r="L129" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D126">
+      <c r="D130">
         <v>183</v>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>Average cost-to-borrower for unsecured lending</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>Average topline revenue earned from unsecured retail credit operations (as percentage of the average outstanding unsecured credit)</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>This indicator is a portfolio-level proxy for the all-in price actually paid by customers on unsecured retail credit during the period. It answers: How many currency units of revenue did the lender earn for each 100 units of average unpaid balance? Rising values may reflect higher base rates, heavier fee reliance (e.g., late/over-limit charges), or a shift toward shorter-tenor/high-yield products; falling values can indicate competitive pressure, promotional pricing, or relief programs. Boards, supervisors, and consumer-protection teams use it to benchmark pricing fairness, earnings quality, and sensitivity to interest-rate cycles. !- Definitions and concepts: Recommended numerator (topline revenue, P&amp;L-recognized): Interest income (EIR basis) + contractual fees (origination, servicing) + penalty/default interest actually recognized + punitive fees (late, over-limit, returned-payment) − waivers/reversals. Denominator: Average outstanding unsecured retail balances (use Average Daily Balance - ADB). Formula: Cost-to-customer yield = Topline revenue from unsecured retail credit divded by Average outstanding unsecured retail balances. This indicator can be reported separately for interest, contractual fees and penalities if the data is available and when the period is less than 12 months, report an annualized figure. !- Data requirements: General ledger and product-level revenue broken into interest, contractual fees, penalty interest, punitive fees; flags for waivers/reversals and non-accrual. Loan/card-level balances to compute ADB, segmented by product (cards, instalment, overdraft, BNPL), channel, and risk bucket. Accounting policies: EIR vs. cash, Stage-3/non-accrual treatment, capitalization rules.
 FX mapping for multi-currency portfolios. !- Limitations and considerations: Comparability: EIR vs. cash accounting and non-accrual practices differ; disclose methodology. Mix effects: more revolving/short-tenor loans inflate yields; always segment. Penalty bias: high ratios may be driven by a small cohort repeatedly paying fees—track % customers incurring penalties. Promotions/teasers: intro 0% and fee holidays distort short periods—show trailing-12-month and cohort views. Scope creep: exclude bundled insurance premiums or merchant discounts (BNPL) unless consistently included and disclosed.</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="H130" t="inlineStr">
         <is>
           <t>Are there gender disparities in the percentage of topline revenue relative to outstanding loan balances? Is there any gender paying comparatively more than market percentages for the same account types? How do FSPs rank in terms of these percentages by gender?</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
+      <c r="L130" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D127">
+      <c r="D131">
         <v>181</v>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>Revenue generated by unsecured credit</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>% of total topline revenue attributable to unsecured credit operations and interest and non-interest revenue proportions</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>This indicator captures the total income that a lending institution earns from unsecured credit products—credit cards, personal instalment loans, overdrafts, payday and buy-now-pay-later (BNPL) facilities—over a reporting period. Because unsecured lending is typically high-yield and high-risk, tracking its revenue helps supervisors and management understand how much of the institution’s top line depends on products that are more sensitive to economic downturns, job-market shocks and aggressive competition. A rising share can boost short-term profitability, but it may also presage higher future credit losses and conduct-risk concerns if underwriting standards slip. !- Definitions and concepts: Unsecured credit – loans that are not backed by collateral; repayment relies on the borrower’s cash flow and creditworthiness.
 Revenue components – Interest income (accrued and collected) from outstanding balances. Fee income: annual fees, origination fees, late-payment charges, interchange on card transactions, BNPL merchant discount rates. Net insurance or payment-protection premiums (if bundled) may be included subject to local accounting rules.
 Revenue share metric: Unsecured-credit revenue ÷ Total lending revenue expresses concentration risk. Risk-adjusted yield – revenue net of credit-loss provisions gives a clearer view of economic profitability. !- Data requirements: Product-level general-ledger extracts segregating interest, fees and other income. Loan-level flags identifying collateral status (secured vs. unsecured). Average daily or month-end balances to compute effective yields. Associated credit-loss provisions and write-offs for risk-adjusted analysis. !- Limitations and considerations: Mixed products: Some personal loans are partially secured (e.g., salary-linked) or carry optional collateral; clear taxonomy is essential. Fee recognition rules: Capitalised origination fees amortised under effective-interest-rate (EIR) accounting may blur timing comparisons across banks or jurisdictions. Regulatory caps: Interest-rate or fee ceilings (e.g., usury limits) affect revenue potential and comparability. Promotional pricing: Introductory 0 % card offers or BNPL “pay-in-4” models generate deferred revenue; headline figures may understate future income. Economic cyclicality: Unsecured-credit revenue can fall sharply in recessions as balances contract and charge-offs rise; pairing with delinquency and provision metrics is crucial for a full risk-return picture.</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="H131" t="inlineStr">
         <is>
           <t>What proportion of total topline revenue comes from unsecured credit operations, and are there gender disparities in this distribution? How do FSPs rank in their reliance on unsecured credit revenue by gender?</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D128">
+      <c r="D132">
         <v>198</v>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>Insurance approved claims not paid</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>% of approved/accepted claims that remain unpaid to customers</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>This indicator shows the share of claims that have been approved (final liability accepted) but not yet disbursed to the claimant. A high rate flags operational bottlenecks or weak payout controls, directly impacting customer outcomes. Track alongside claims turnaround time, claims rejection rates, and complaints, to get a full picture of payout effectiveness and customer fairness. !- Definitions and concepts: Approved / accepted claim: a claim with a final decision to pay (post-analysis), a recorded payable, and no outstanding dispute. Unpaid status: no successful settlement to the beneficiary by period end. Formula: Amount weighted (unpaid approved amount ÷ approved amount) reveal economic impact. Count basis (# approved claims not paid by cut-off ÷ # claims approved in teh period). SLA variant: % not paid within X days of approval (e.g., 5/10/30 days) to neutralize end-period timing bias. Treatment of partial payments: disclose whether partially paid claims are counted as unpaid or excluded. The indicator may also track the reasons for non-payment, if these are standardized for reporting. !- Limitations and considerations: Cut-off effects: approvals late in the period will naturally be unpaid—use the SLA variant and report both snapshot and flow views. Reopened claims / appeals: specify whether reversals after approval are removed from both numerator and denominator. Segmentation: monitor by line of business, payment method, channel, and claim size to target fixes.</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="H132" t="inlineStr">
         <is>
           <t>How do the average values of outstanding insurance claims compare by gender? Is there a gender group with consistently higher average unpaid claims? How do different FSPs rank in terms of outstanding claims by gender? Are vulnerable gender groups disproportionately affected by delayed or unpaid claims?</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
         <is>
           <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
+      <c r="K132" t="inlineStr">
         <is>
           <t>Quality, Reputational and legal risk</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D129">
+      <c r="D133">
         <v>256</v>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E133" t="inlineStr">
         <is>
           <t>Insurance claims declined</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>% of claims logged by policyholders that are declined prior to substantive analysis</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>This indicator captures the share of claim notifications the insurer does not accept for assessment at the front door—typically during first notice of loss (FNOL)/triage—because they are ineligible or incomplete. A high intake-decline rate can point to unclear policy wording, poor customer guidance, data-capture frictions, or overly strict gatekeeping. It is a key conduct-risk and customer-experience signal and, operationally, helps size avoidable workload versus genuinely assessable claims. Claim logged / FNOL: the moment a policyholder submits a claim or loss notice. Declined at intake (non-acceptance): the insurer refuses to open an assessable claim before investigation (e.g., policy not in force, peril not covered, waiting period, duplicate claim, claim below deductible/threshold, incomplete mandatory data not cured within a set window). Indicator formula (count basis): # claims declined at intake in period divided by # claim notifications received in period . Variants: exclude cured cases later resubmitted; report by product/channel. !- Data requirements: Claims-intake system fields: FNOL timestamp, policy ID/status at loss date, coverage/peril checks, deductible, mandatory-document checklist, triage outcome. Standardised reason codes (e.g., not covered, lapsed, duplicate, below excess, incomplete info). Deduplication logic (policyholder ID + incident date + peril). Linkage to resubmissions/appeals and to complaint records for outcome tracking. !- Limitations and considerations: Definition variance: what counts as “prior to analysis” differs; some firms place incomplete cases in “pending info” instead of “declined,” affecting comparability.
 Gaming risk: shifting cases to “withdrawn” or “pending” to improve this metric; require audit trails and age-off rules. Mix effects: products with low deductibles or mandatory documents (e.g., health) have different baseline rates—segment results. Customer fairness: high early declines may reflect confusing onboarding or exclusion wording; monitor alongside claims rejection rate (post-assessment), turnaround time, and complaints upheld. Resubmission policy: disclose whether cured resubmissions are excluded from the numerator to avoid double counting.</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>What percentage of claims logged by policyholders are declined, disaggregated by gender? How do these decline rates vary across FSPs, policy types, age groups, and locations? Are there notable gender disparities in claim declines at the market level or within specific providers? Are women or other gender groups more likely to face claim denial?</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="L133" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D130">
+      <c r="D134">
         <v>60</v>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>Insurance claims rejection rate</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>% of all insurance claims that are rejected by insurers (post-analysis)</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>The claims rejection rate shows the share of claims that an insurer declines to pay—fully or partially—relative to the total number (or value) of claims submitted in a period. Because denial directly affects customer trust, supervisors use the metric to monitor fair treatment outcomes, detect aggressive underwriting or opaque policy wording, and flag operational shortcomings. A sudden rise may presage reputational damage, regulatory sanctions, or litigation costs, while an unusually low rate can hint at lax fraud controls or inadequate claims processing. !- Definitions and concepts: Claims rejected (denied): claims for which the insurer issues a final communication refusing payment on contractual grounds (e.g., policy exclusions, lapsed cover, misrepresentation) or on fraud findings. !- Limitations and considerations: Definition divergence: Some regimes class “claims closed without payment” (due to missing documents) as rejections; others record them as pending, complicating cross-market comparison. Fraud vs. technical denial: Combining fraud rejections with contractual exclusions can blur very different issues. Separate reporting is best practice. Volume vs. value: A single large, legitimately denied loss can distort amount-based ratios; analysts should monitor both count and value metrics.
 Appeals and reversals: Denials overturned on review lower true rejection rates; timely data updates are essential.
 Incentive effects: Over-emphasis on low rejection rates may weaken fraud vigilance, whereas strict targets can push staff toward technical denials—pair the indicator with complaint ratios, turnaround times, and fraud-detection statistics for balanced oversight.</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="H134" t="inlineStr">
         <is>
           <t>Are there gender disparities in the rejection rates of insurance claims, including for MSMEs by owner gender? Which types of policies or claims see higher rejection rates, and do these differ by gender? How does claim rejection relate to coverage levels and turnaround times? Do FSPs with higher gender diversity have lower rejection rates for vulnerable gender groups?</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="L134" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D131">
+      <c r="D135">
         <v>201</v>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>Insurance claims settlement ratio</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>% of insurance claims logged by policyholders that have been paid by insurers</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>Measures the percentage of insurance claims settled by an insurer out of the total claims it receives. It is a direct measure of an insurer's reliability and its commitment to fulfilling its primary promise to policyholders. This indicator is a cornerstone of conduct supervision, as it provides a quantitative view of how an insurer treats its customers at their most critical moment of need. For prudential supervisors, it could help analysis of operational and reputational risk. This indicator should be used together with other indicators on the performance of the claims process in the insurance sector.</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="H135" t="inlineStr">
         <is>
           <t>How do claim settlement ratios vary by gender? Are any gender groups receiving lower settlement ratios compared to the market average? Are there FSPs with particularly low or high settlement ratios for certain genders? How do these ratios intersect with policy type and customer demographics?</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
         <is>
           <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
+      <c r="K135" t="inlineStr">
         <is>
           <t>Outcomes, Reputational and legal risk</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D132">
+      <c r="D136">
         <v>59</v>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E136" t="inlineStr">
         <is>
           <t>Insurance claims turnaround time</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>Average number of days to process insurance claims</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t>This indicator captures the average calendar days an insurer takes to settle a claim—from the claim filing date to the final payment or formal denial. It is a direct yard-stick of operational efficiency and customer experience. Shorter turnaround times (TATs) enhance policy-holder trust, limit reputational risk, and can lower claims handling expenses. Supervisors use the metric to enforce fair-treatment rules, while actuaries and underwriters link it to reserving accuracy—prolonged settlement can signal documentation bottlenecks, fraud investigations, policy transparency issues, or catastrophic complexity that may keep outstanding reserves elevated. !- Definitions and concepts:  Start point – the timestamp when the insurer first receives the claim request. End point – the date the insurer issues full payment, partial final payment, or a written denial. Average turnaround time (TAT) – arithmetic mean; many firms also monitor median and 90th-percentile to limit outlier masking.
 Segmented TATs – tracked by line of business, claim severity band, and distribution channel to isolate problem areas.
 !- Limitations and considerations: Partial settlements: Recording the date of first partial payment can understate full-and-final completion time. Dispute and litigation pauses: Regulatory or court‐mandated suspensions inflate TAT yet lie outside managerial control.</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="H136" t="inlineStr">
         <is>
           <t>Are there gender disparities in the average time taken to process and settle insurance claims? How does processing time vary by policy type, premium, claim amount, and customer demographics? Are insurers with lower gender diversity more likely to have longer turnaround times? Are vulnerable gender groups disproportionately affected by delays?</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
+      <c r="L136" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
+    <row r="137">
+      <c r="A137" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>Investments</t>
         </is>
       </c>
-      <c r="D133">
+      <c r="D137">
         <v>207</v>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="E137" t="inlineStr">
         <is>
           <t>Net rate of return on investments</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>% point differential between the average rates of returns on investments and the average performance/administration fees charged</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>Measures the profitability of a financial institution's own investment portfolio after accounting for all associated costs. It reveals the actual, bottom-line gain or loss generated by the institution's securities, real estate, or other investments. This is a fundamental indicator of an institution's ability to effectively manage its own capital and generate profit from non-lending activities, of particular importance to prudential supervisors, including supervisors of insurance and pension administrators. Net Rate of Return (%)= 
 [(Market Value final-Market Value initial+Income−Expenses)/Market Value initial]×100</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="H137" t="inlineStr">
         <is>
           <t>How do net returns (% returns minus % performance fees and charges) on longer-term investments compare by gender? Do net returns for any gender differ from the overall market average for similar investment products? How do FSPs compare in terms of net returns earned by gender?</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr">
+      <c r="J137" t="inlineStr">
         <is>
           <t>Market development</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
+      <c r="K137" t="inlineStr">
         <is>
           <t>Capital markets development</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>Savings</t>
         </is>
       </c>
-      <c r="D134">
+      <c r="D138">
         <v>159</v>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="E138" t="inlineStr">
         <is>
           <t>Average cost-to-customer for transaction accounts</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>Average topline revenue earned per account holder as % of average account balances</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t>This indicator estimates the effective price of holding and using a transaction account, expressed as a yield on the customer’s average balance. By computing it for each account type (e.g., basic/no-frills, standard retail, premium, MSMEs, e-money wallet), it reveals where pricing and usage frictions are highest. It helps supervisors assess fairness, inclusion quality, and reliance on fee income. !- Definitions and concepts: Non-interest fees: maintenance/inactivity, ATM/network, FX/transfer, statement/card fees, overdraft &amp; returned-payment fees tied to the account. 
 Per account-holder basis: aggregate all accounts of the same type per customer, then average (also show balance-weighted results). !- Data requirements: Core-banking data: customer ID, account type tags, average daily balance by customer for each account type, interest credited, revenue by fee code linked to accounts; flags for waivers/refunds/chargebacks. Channel/product hierarchies (basic vs. premium, retail vs. MSMEs, wallet vs. bank account) and currency/FX mapping. Optional: usage indicators (transactions per month) to explain differences across types.</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="H138" t="inlineStr">
         <is>
           <t>Are there gender disparities in the costs (fees, charges) borne by account holders of transaction accounts? Do women tend to hold transaction accounts with higher fee burdens (relative to income or transaction frequency) than men, particularly in certain regions or among lower‐income groups? How do costs compare across FSPs with different levels of gender diversity? Is fee structure or cost‐to‐customer a barrier to transaction usage for some gender/age/income cohorts?</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="L138" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Financial service provider (FSP) type; Account type</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Fair treatment</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D135">
-        <v>226</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Rejections of product applications</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>% of all applications that are rejected by product type</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Measures the proportion of customer applications for financial products that are rejected by regulated financial institutions during the reporting period. The indicator is calculated as the percentage of total applications received—across products such as loans, credit cards, deposit accounts, or insurance policies—that were not approved or accepted. Captures the extent of unmet demand or access barriers in financial markets, as well as aspects of market conduct, underwriting practices, and risk appetite among providers. It provides insight into how easily consumers and businesses can obtain financial products. Monitoring rejection rates helps authorities: Identify potential access constraints or discriminatory lending or sales practices; Evaluate the tightness of credit or account-opening standards; Assess consumer protection outcomes and fair treatment; Detect sudden shifts in provider risk tolerance or macro-prudential conditions (e.g., post-crisis credit tightening). High rejection rates may indicate stringent eligibility criteria, weak applicant creditworthiness, or barriers to financial access. Declining rates may suggest improving inclusion or relaxation of underwriting standards. Cross-product comparisons reveal whether certain markets (e.g., credit vs. deposits) are more exclusionary. !- Definitions and concepts: Application: A formal request by a customer to obtain a financial product or service. Rejection: A decision by the provider not to approve, issue, or open the requested product, whether automated or manual. Product type: Category of financial service applied for (loan, deposit, insurance, card, etc.). !- Data requirements: Product application records from regulated financail institutions that can yield the total number of applications rejected and the total number of applications received during the reference period. Disaggregation variables for segmentation analysis: product type, applicant type (individual, MSME), gender etc.</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>How do rejection rates vary by gender? Are rejection rates higher for any gender in specific channels? How do rejection rates in physical channels compare to those in digital channels by gender? How do FSPs rank in terms of rejection rates by gender across available channels? For loans, when analyzed alongside the indicator "Customers by credit score," are there gender disparities in rejection rates by credit score?</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Suitability</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D136">
-        <v>171</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Unsecured credit facilities per borrower</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Average volume and value (outstanding amount) of unsecured credit operations per borrower</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>This indicator shows, for each unsecured credit type (e.g., credit cards, personal instalment loans, overdrafts/lines, BNPL/pay-in-4, microcredit), how many active facilities the typical borrower holds (volume) and how much they owe on average (value). It reveals product stacking, utilisation intensity, and pockets of affordability risk. Rising volumes with flat values can indicate product fragmentation (e.g., multiple small BNPL plans), while high values per borrower point to concentration risk and potential loss severity. !- Definitions and concepts: Borrower universe per type (t): unique customers with ≥1 active unsecured facility of type (t) during the period. Average volume (holders-only) = [Total number of active contracts of type t for borrow b] / [Total number of unique borrowers with facility of type t]. Average value (holders only) = [Average daily outstanding balance across all of borrower b's facility of type t] / [Total number of unique borrowers with facility of type t]. Outstanding amount: Gross carrying amount before prvisions, exclude undrawn limits. Attribution rules: Define treatment of joint borrowers (full vs. proportional), refinances/restructures and charged-off accounts (exclude once written off, unless still on-book). !- Data requirements: Loan/line-level records with borrower ID, product/credit-type tag, status, origination date, limit (revolving), currency, and daily balances. Deduped customer master across subsidiaries/channels; joint-borrower flags. FX rates for multi-currency portfolios; calendar to compute ADB over the period. !- Limitations and considerations: Seasonality: cards/overdrafts spike around holidays—use ADB and rolling windows. Mix effects: comparing cards (revolving) with instalments needs a utilisation companion metric. Policy choices: inclusion of dormant but open lines, re-aged accounts, or post-charge-off recoveries changes results—document choices. Distribution matters: report median and percentiles per type alongside means to avoid high-balance skew.</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>How does the average number of outstanding loans per borrower vary by gender? Are outstanding balances more concentrated in long- or short-term loans, and does this differ by gender? Have gender disparities in loan terms evolved over time?</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>Outcomes, Credit risk</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Safety and security</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D137">
-        <v>231</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Frauds faced by customers</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>% of customers affected by fraud</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Fraud directly erodes consumer confidence, trust in financial institutions and can trigger liquidity or solvency stress for institutions, tracking its incidence lets supervisors spot emerging threats before they undermine financial stability. Consistent monitoring also reveals control weaknesses, helping authorities direct enforcement, bolster preventive regulation, and keep the payments and deposit system trusted and resilient. This indicator measures the share of customers of financial services that have been victims of fraud over a specific period. !- Definitions and concepts: Several definitions of fraud exist and vary depending on the jurisdiction, local definitions of fraud for statistical reporting purposes should be used. For example, the European Banking Authority splits fraudelent payment transactions into two categories: (1) Unauthorised payment transactions: transfers made “as a result of the loss, theft or misappropriation of sensitive payment data or a payment instrument … executed in the absence of consent by the payer.” and (2) Manipulation of the payer: transactions “made as a result of the payer being manipulated … to issue a payment order … in good faith, to a payment account it believes belongs to a legitimate payee.” This definition anchors EU-wide fraud statistics and stresses both technical compromise (e.g., stolen credentials) and social-engineering scams (e.g., authorised push-payment fraud). !- Data requirements: Transactions initiated and executed during a specified period that are flagged as fraudulent linked to a unique customer ID; Total number of customer at the beginning of the specified period.</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>How does the number of fraud cases vary by gender? Are any genders disproportionately affected by fraud? Are fraud cases more frequent in certain types of FSPs?</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Safety and security</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D138">
-        <v>233</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Frauds resulting in costumers losses</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Average volume and value (losses incurred) of frauds experienced by customers</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Fraud directly erodes consumer confidence, trust in financial institutions and can trigger liquidity or solvency stress for institutions, tracking its incidence lets supervisors spot emerging threats before they undermine financial stability. Consistent monitoring also reveals control weaknesses, helping authorities direct enforcement, bolster preventive regulation, and keep the payments and deposit system trusted and resilient. This indicator measures the number of transactions that have been flagged as fraudulent and their corresponding value in currency.  !- Definitions and concepts: Several definitions of fraud exist and vary depending on the jurisdiction, local definitions of fraud for statistical reporting purposes should be used. For example, the European Banking Authority splits fraudelent payment transactions into two categories: (1) Unauthorised payment transactions: transfers made “as a result of the loss, theft or misappropriation of sensitive payment data or a payment instrument … executed in the absence of consent by the payer.” and (2) Manipulation of the payer: transactions “made as a result of the payer being manipulated … to issue a payment order … in good faith, to a payment account it believes belongs to a legitimate payee.” This definition anchors EU-wide fraud statistics and stresses both technical compromise (e.g., stolen credentials) and social-engineering scams (e.g., authorised push-payment fraud). !- Data requirements: Total number of transactions initiated and executed during a specified period that are flagged as fraudulent;  Total value of transactions initiated and executed during a specified period that are flagged as fraudulent.</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>How do financial loss-related fraud cases impact genders differently? Are any genders disproportionately affected by frauds that result in financial losses? Are fraud cases involving financial losses more common in certain types of FSPs?</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -7744,532 +7704,532 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
+          <t>Fair treatment</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D139">
+        <v>226</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Rejections of product applications</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>% of all applications that are rejected by product type</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Measures the proportion of customer applications for financial products that are rejected by regulated financial institutions during the reporting period. The indicator is calculated as the percentage of total applications received—across products such as loans, credit cards, deposit accounts, or insurance policies—that were not approved or accepted. Captures the extent of unmet demand or access barriers in financial markets, as well as aspects of market conduct, underwriting practices, and risk appetite among providers. It provides insight into how easily consumers and businesses can obtain financial products. Monitoring rejection rates helps authorities: Identify potential access constraints or discriminatory lending or sales practices; Evaluate the tightness of credit or account-opening standards; Assess consumer protection outcomes and fair treatment; Detect sudden shifts in provider risk tolerance or macro-prudential conditions (e.g., post-crisis credit tightening). High rejection rates may indicate stringent eligibility criteria, weak applicant creditworthiness, or barriers to financial access. Declining rates may suggest improving inclusion or relaxation of underwriting standards. Cross-product comparisons reveal whether certain markets (e.g., credit vs. deposits) are more exclusionary. !- Definitions and concepts: Application: A formal request by a customer to obtain a financial product or service. Rejection: A decision by the provider not to approve, issue, or open the requested product, whether automated or manual. Product type: Category of financial service applied for (loan, deposit, insurance, card, etc.). !- Data requirements: Product application records from regulated financail institutions that can yield the total number of applications rejected and the total number of applications received during the reference period. Disaggregation variables for segmentation analysis: product type, applicant type (individual, MSME), gender etc.</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>How do rejection rates vary by gender? Are rejection rates higher for any gender in specific channels? How do rejection rates in physical channels compare to those in digital channels by gender? How do FSPs rank in terms of rejection rates by gender across available channels? For loans, when analyzed alongside the indicator "Customers by credit score," are there gender disparities in rejection rates by credit score?</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Suitability</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="D140">
+        <v>171</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Unsecured credit facilities per borrower</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Average volume and value (outstanding amount) of unsecured credit operations per borrower</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>This indicator shows, for each unsecured credit type (e.g., credit cards, personal instalment loans, overdrafts/lines, BNPL/pay-in-4, microcredit), how many active facilities the typical borrower holds (volume) and how much they owe on average (value). It reveals product stacking, utilisation intensity, and pockets of affordability risk. Rising volumes with flat values can indicate product fragmentation (e.g., multiple small BNPL plans), while high values per borrower point to concentration risk and potential loss severity. !- Definitions and concepts: Borrower universe per type (t): unique customers with ≥1 active unsecured facility of type (t) during the period. Average volume (holders-only) = [Total number of active contracts of type t for borrow b] / [Total number of unique borrowers with facility of type t]. Average value (holders only) = [Average daily outstanding balance across all of borrower b's facility of type t] / [Total number of unique borrowers with facility of type t]. Outstanding amount: Gross carrying amount before prvisions, exclude undrawn limits. Attribution rules: Define treatment of joint borrowers (full vs. proportional), refinances/restructures and charged-off accounts (exclude once written off, unless still on-book). !- Data requirements: Loan/line-level records with borrower ID, product/credit-type tag, status, origination date, limit (revolving), currency, and daily balances. Deduped customer master across subsidiaries/channels; joint-borrower flags. FX rates for multi-currency portfolios; calendar to compute ADB over the period. !- Limitations and considerations: Seasonality: cards/overdrafts spike around holidays—use ADB and rolling windows. Mix effects: comparing cards (revolving) with instalments needs a utilisation companion metric. Policy choices: inclusion of dormant but open lines, re-aged accounts, or post-charge-off recoveries changes results—document choices. Distribution matters: report median and percentiles per type alongside means to avoid high-balance skew.</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>How does the average number of outstanding loans per borrower vary by gender? Are outstanding balances more concentrated in long- or short-term loans, and does this differ by gender? Have gender disparities in loan terms evolved over time?</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Outcomes, Credit risk</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
           <t>Safety and security</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
-      <c r="D139">
+      <c r="D141">
+        <v>231</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Frauds faced by customers</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>% of customers affected by fraud</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Fraud directly erodes consumer confidence, trust in financial institutions and can trigger liquidity or solvency stress for institutions, tracking its incidence lets supervisors spot emerging threats before they undermine financial stability. Consistent monitoring also reveals control weaknesses, helping authorities direct enforcement, bolster preventive regulation, and keep the payments and deposit system trusted and resilient. This indicator measures the share of customers of financial services that have been victims of fraud over a specific period. !- Definitions and concepts: Several definitions of fraud exist and vary depending on the jurisdiction, local definitions of fraud for statistical reporting purposes should be used. For example, the European Banking Authority splits fraudelent payment transactions into two categories: (1) Unauthorised payment transactions: transfers made “as a result of the loss, theft or misappropriation of sensitive payment data or a payment instrument … executed in the absence of consent by the payer.” and (2) Manipulation of the payer: transactions “made as a result of the payer being manipulated … to issue a payment order … in good faith, to a payment account it believes belongs to a legitimate payee.” This definition anchors EU-wide fraud statistics and stresses both technical compromise (e.g., stolen credentials) and social-engineering scams (e.g., authorised push-payment fraud). !- Data requirements: Transactions initiated and executed during a specified period that are flagged as fraudulent linked to a unique customer ID; Total number of customer at the beginning of the specified period.</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>How does the number of fraud cases vary by gender? Are any genders disproportionately affected by fraud? Are fraud cases more frequent in certain types of FSPs?</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Safety and security</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D142">
+        <v>233</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Frauds resulting in costumer losses</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Average volume and value (losses incurred) of frauds experienced by customers</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Fraud directly erodes consumer confidence, trust in financial institutions and can trigger liquidity or solvency stress for institutions, tracking its incidence lets supervisors spot emerging threats before they undermine financial stability. Consistent monitoring also reveals control weaknesses, helping authorities direct enforcement, bolster preventive regulation, and keep the payments and deposit system trusted and resilient. This indicator measures the number of transactions that have been flagged as fraudulent and their corresponding value in currency.  !- Definitions and concepts: Several definitions of fraud exist and vary depending on the jurisdiction, local definitions of fraud for statistical reporting purposes should be used. For example, the European Banking Authority splits fraudelent payment transactions into two categories: (1) Unauthorised payment transactions: transfers made “as a result of the loss, theft or misappropriation of sensitive payment data or a payment instrument … executed in the absence of consent by the payer.” and (2) Manipulation of the payer: transactions “made as a result of the payer being manipulated … to issue a payment order … in good faith, to a payment account it believes belongs to a legitimate payee.” This definition anchors EU-wide fraud statistics and stresses both technical compromise (e.g., stolen credentials) and social-engineering scams (e.g., authorised push-payment fraud). !- Data requirements: Total number of transactions initiated and executed during a specified period that are flagged as fraudulent;  Total value of transactions initiated and executed during a specified period that are flagged as fraudulent.</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>How do financial loss-related fraud cases impact genders differently? Are any genders disproportionately affected by frauds that result in financial losses? Are fraud cases involving financial losses more common in certain types of FSPs?</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Safety and security</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D143">
         <v>230</v>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>Physical safety</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>Number of physical security incidents and number of customers affected</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>This indicator captures the total number of reported physical security incidents that occur in connection with the operations of financial service providers (FSPs) — including banks, microfinance institutions, payment service providers, and other regulated entities — as well as the number of customers directly affected by such incidents. Physical security incidents include events such as armed robberies, thefts, assaults, vandalism, or damage to property occurring at branches, ATMs, cash-in-transit vehicles, or other service delivery points. The “number of customers affected” reflects individuals who have experienced harm, loss, or disruption of service as a result of these events.This indicator measures the operational risk exposure of the financial sector to physical threats and criminal activity, and the extent to which such incidents impact customers and public trust. It forms part of the broader construct of operational resilience and consumer protection, providing insights into the safety of physical access points within the financial system. Supervisory reporting could record:
 Number of incidents = Total count of reported physical security incidents during the reference period (e.g., quarterly or annually). Number of customers affected = Total number of customers who suffered loss, injury, or service disruption due to those incidents. !- Derivable indicators: Incident rate = (Number of incidents / Total number of service points) × 1,000; Customer impact rate = (Number of customers affected / Total number of customers) × 100</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t>How does the number of physical security incidents vary by gender? Are any genders disproportionately affected? Are physical security incidents more common in certain types of FSPs?</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr">
+      <c r="J143" t="inlineStr">
         <is>
           <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
+      <c r="K143" t="inlineStr">
         <is>
           <t>Outcomes, Reputational and legal risk</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
+      <c r="L143" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>Suitability</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D140">
+      <c r="D144">
         <v>152</v>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>Deposit account holders qualifying for credit</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>% of all deposit account holders that meet the minimum qualifying criteria for a loan or line of credit</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t>A measure of the assessed creditworthiness of depositors. Digital financial tools such as mobile money and e-wallets have opened up access to financal services to millions around the world. This indicator tries to measure the degree to which users of accounts can unlock access to addiitonal services, in the case credit. !- Definitions and concepts: Deposit accounts include transaction and non-transaction deposit accounts, for example: Checking/demand, savings, time/term deposit accounts, pensions. !- Data requirements: Total number of unique deposit account holders that also either have (1) an open loan account, (2) do not have an open loan account but would be approved for a loan or line of credit given their current credit history, credit score or other basic requirements (such as minimum balance or savings history); Total number of unique deposit account holders (i.e. an individual must be counted as one depositor irrespective of the number of deposit accounts held) at the end of a specified period (e.g. quarter or year).  !- Limitations and considerations: If individuals or MSMEs own deposit accounts across multiple different financial institutions, sector or system wide aggregates which add up accounts across institutions will, as a result, overstate the degree of financial inclusion unless granular data and unique national IDs can be used to identify individuals with multiple accounts across financial institutions.</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
+      <c r="H144" t="inlineStr">
         <is>
           <t>What are the credit-qualifying rates for transaction account holders by gender? How do these rates compare? Which FSPs rank highest and lowest in credit-qualifying rates for typically underserved groups, and does this ranking change when analyzed by gender?</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
         <is>
           <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
+      <c r="K144" t="inlineStr">
         <is>
           <t>Outcomes, Credit risk</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>Suitability</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D141">
+      <c r="D145">
         <v>176</v>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E145" t="inlineStr">
         <is>
           <t>Early loan payoff</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F145" t="inlineStr">
         <is>
           <t>% of borrowers who paid loans in full before due date</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="G145" t="inlineStr">
         <is>
           <t>The early-loan-payoff (or prepayment) indicator tracks the share of outstanding loans that borrowers settle—partly or fully—before the contractually scheduled maturity. High prepayment activity can squeeze interest income, change expected cash-flow profiles that underpin asset-liability management, and distort credit-loss models. For lenders, rising early payoffs may flag aggressive refinancing campaigns by competitors, interest rate declines that make refinancing attractive, or borrowers’ improved liquidity. Supervisors and investors monitor the metric to evaluate revenue volatility, among others. !- Definitions and concepts: Early payoff / prepayment: any unscheduled principal reduction exceeding the contractual amortisation, including full settlement (loan closed) and partial prepayments (lump-sum curtailments).</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="H145" t="inlineStr">
         <is>
           <t>Are there gender disparities in the likelihood of making early payments before due dates? Which credit products are most frequently paid early by each gender?</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
         <is>
           <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
+      <c r="K145" t="inlineStr">
         <is>
           <t>Outcomes, Credit risk</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
+      <c r="L145" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>Suitability</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D142">
+      <c r="D146">
         <v>189</v>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E146" t="inlineStr">
         <is>
           <t>Grace period/payment leeway</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F146" t="inlineStr">
         <is>
           <t>% of borrowers using payment holidays, grace periods and other relief measures</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="G146" t="inlineStr">
         <is>
           <t>Shows how many borrowers are under temporary repayment relief, signalling household stress, policy effectiveness, and potential payment cliffs when relief ends. Rising usage can reduce near-term delinquencies but may defer (not eliminate) credit risk and revenue. !- Definitions and concepts: Relief measures (forbearance): payment holiday/deferral, interest-only period, reduced instalment, term extension, fee/penalty waiver, capitalization of arrears, hardship programs.Borrower-based indicator: % of borrowers on relief = [Total unique borrowers with at least 1 active relief measure in period]/[Total unique active borrowing customers] x 100%. Account-based variant uses loan count instead of borrowers. Status: Active (relief in effect), Approved but not started, Expired. Intensity companions: % of balances under relief, avg. relief days used, new entrants to relief ÷ active borrowers. !- Data requirements: Loan-level flags: relief type, start/end dates, approval date, terms (interest accrual, capitalization), reason code (income loss, disaster, medical), product type. Borrower ID (deduplicated across products/entities). !- Limitations and considerations: Definition variance: some programs auto-enrol; others require hardship evidence—harmful to cross-bank comparisons. Double counting: a borrower may receive multiple reliefs across loans—use borrower-level dedupe and report per-loan as a companion. Masking effect: relief suppresses DPD/NPL temporarily; pair with balances under relief and post-exit performance. Cohort effects &amp; timing: shocks (e.g., disasters) create spikes; use cohort tracking (by approval month) and rolling windows. Conduct risk: prolonged or opaque relief terms can mislead customers; monitor complaints and repeat relief rates. Segment by product (mortgage, card, personal, MSMEs), risk grade, tenure, and demographics to pinpoint vulnerability and program effectiveness.</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="H146" t="inlineStr">
         <is>
           <t>How do the percentages of borrowers using grace periods or payment leeways compare by gender? Is there any gender more likely to use them? How does the use of grace periods or payment leeways vary by credit product and gender?</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
         <is>
           <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="K146" t="inlineStr">
         <is>
           <t>Outcomes, Credit risk</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
+      <c r="L146" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>Suitability</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D143">
+      <c r="D147">
         <v>190</v>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="E147" t="inlineStr">
         <is>
           <t>Borrowers in debt counselling and rehabilitation</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>% of borrowers participating in debt counselling and/or debt rehabilitation progams</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>This indicator tracks the prevalence of individuals formally enrolled in debt-counselling or rehabilitation programmes: legal or contractual processes that restructure debt, impose spending plans, or provide financial-literacy support. A rising level signals household over-indebtedness pressures, tighter monetary or labour-market conditions, or aggressive credit expansion in the recent past. Regulators, consumer-protection agencies, and lenders track the metric to gauge systemic consumer-credit risk, calibrate responsible-lending rules and supervision, and anticipate write-off or provisioning needs. !- Definitions and concepts: Borrowers refers to individuals that have obtained any type of credit from financial institutions. Individuals are counted as one borrower, irrespective of the number of loan accounts held. Debt-counselling / debt-review: A court-sanctioned or regulator-approved process (e.g., South Africa’s National Credit Act, UK Debt Management Plans) where a certified counsellor assesses affordability, negotiates new payment schedules with all creditors, and disburses consolidated instalments. Debt rehabilitation / discharge: The stage at which the borrower has completed the plan, obtained a clearance certificate, or been legally discharged from remaining obligations (analogous to Chapter 13 completion in the US). Indicator forms:
 Stock measure: number of active borrowers under counselling ÷ total number of retail borrowers. Flow measure: new counselling entrants during the period ÷ new defaults. !- Data requirements: Registry or court filings identifying unique borrowers, start and end dates, original and restructured debt balances, and counsellor accreditation. Credit-bureau data to link counselling status with credit scores, delinquency buckets, and new credit enquiries. !- Limitations and considerations: Coverage gaps: Informal or NGO-led advice services may not report centrally, understating prevalence. Regime differences: Some jurisdictions treat insolvency, debt management, and bankruptcy as separate processes; harmonising counts is non-trivial. Multiple enrolments: Borrowers can exit and re-enter counselling; deduplicating unique individuals is essential for accurate stock figures. Moral-hazard concerns: Easy access to rehabilitation might weaken repayment discipline; analysts pair this indicator with post-rehabilitation re-default rates.Privacy restrictions: Personally identifiable data are often masked, limiting segmentation by income, gender, or geography unless aggregated extracts are provided. Used alongside delinquency trends, restructuring volumes, and loan-loss provisions, the “borrowers in debt counselling and rehabilitation” metric offers a forward-looking lens on household financial stress and the effectiveness of consumer-protection frameworks.</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="H147" t="inlineStr">
         <is>
           <t>How do the percentages of borrowers in debt counseling or rehabilitation compare by gender? Is there any gender more likely to enroll in debt counseling or rehabilitation? How do FSPs compare in terms of debt counseling or rehabilitation enrollment by gender?</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
         <is>
           <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
+      <c r="K147" t="inlineStr">
         <is>
           <t>Outcomes, Credit risk</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
+      <c r="L147" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Suitability</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D144">
-        <v>27</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Borrowers in risky indebtedness (risk of over-indebtedness)</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Number of borrowers classified as at risk of over-indebtedness, as per risk-indebtedness calculation</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Tracking over-indebtedness gives authorities a measure of systemic distress: when large segments of retail borrowers can’t meet their obligations, it highlights consumer-protection gaps. Persistent debt burdens signal predatory lending or inadequate affordability assessments. The indicator helps calibrate market-conduct supervision and regulation. This particular indicator that identifies borrowers at risk of overindebtedness was developed by the Central Bank of Brazil: https://www.bcb.gov.br/content/cidadaniafinanceira/documentos_cidadania/serie_cidadania/serie_cidadania_financeira_8_endividamento_risco_2ed.pdf ad https://www.researchgate.net/publication/376634051_Risky_Indebtedness_Behavior_Impacts_on_Financial_Preparation_for_Retirement_and_Perceived_Financial_Well-Being. It is a composite of four components. A borrower is flagged as being in "risky indebtedness" when any two of the following four criteria are met: (1) Has defaulted on credit installments, that is, has had payment delays of more than 90 days in meeting credit obligations, (2) Monthly income devoted to debt-service payments exceeds 50 percent, (3) Has simultaneous exposure to the following forms of credit: overdraft, unsecured personal loan, and revolving credit card debt, (4) Monthly disposable income (after debt-service payments) that falls below the poverty line. Generating this indicator at the system level requires a unique national ID in order to match granular loan data to unique borrowers. The indicator also requires access to income data. !- Derivable indicators: Percent of borrowers in risky indebtendess; Percent of adults in risky indebtedness.</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in the classification of risky indebtedness? Are low-income borrowers more at risk of risky indebtedness and how does it compare across genders? Comparing this indicator with gender diversity, do FSPs with higher levels of gender diversity present lower levels of risky indebtedness?</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>Credit risk</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Suitability</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D145">
-        <v>285</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Debt service-to-income ratio</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>% of income allocated to retail credit debt repayment</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>The debt service-to-Income ratio,  sometimes referred to more concisely as the debt service ratio (DSR) expresses a borrower’s (or household’s) total debt-service burden relative to recurring income, answering a simple question: How much of each income unit is already pledged to repay existing debt? At the micro level, lenders use DSR to assess repayment capacity, price credit, and comply with responsible-lending rules. At the macro level, supervisors track average or distributional DSR to gauge household vulnerability to interest-rate shocks and to calibrate macro-prudential tools such as loan-to-income caps. !- Definitions and concepts: Debt payments include principal, interest, mandatory insurance on retail credit facilities;  Income can be defined in gross terms (pre-tax income (salary) plus verifiable recurring earning) or net terms (income after taxes and social-security contributions). !- Data requirements: Current loan statements or credit-bureau/registry reports detailing payment amounts, remaiming term, and interest rate for all obligations; Recent payslips, audited financial statements (self-fmployed), tax returns, and verified rental or pension income. !- Limitations and considerations: Income volatility: informal or gig-economy or commission-based earnings make future cash flows uncertain; Undisclosed liabilities: informal or unreported debts escape bureau coverage, understating true DSR. Household composition: shared living expenses and co-borrower support can distort individual ratios; some frameworks use household disposable income instead. Interest-rate path: fixed-rate loans keep payments stable, while floating-rate debt can raise DSR sharply when policy rates rise. Cross-country comparability: tax structures, social-welfare benefits, and healthcare costs influence disposable income, so identical DSR thresholds may imply different real affordability across jurisdictions.</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>How do debt service-to-income ratios vary by gender and across different loan sizes and terms? Do loans with higher rates and shorter terms show gender disparities in ratios? Comparing this indicator with gender diversity, do FSPs with higher levels of gender diversity present lower debt-service to income ratios?</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>Quality, Credit risk</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Suitability</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D146">
-        <v>194</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Insurance lapse rates</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>% of all insurance policies (or policyholders) that have lapsed</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>This indicator measures the number of policies discontinued due to non-payment of premiums by the policyholder relative to the total number of policies at the beginning of the period. It is a key indicator to assess quality of advice, quality of service, product appropriateness, and mis-selling risk in the insurance sector. https://www.iais.org/uploads/2022/06/Report-on-Supervisors-Use-of-Key-Indicators-to-Assess-Insurer-Conduct.pdf</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>How do insurance lapse rates differ by gender? Are certain types of insurance policies associated with higher lapse rates among specific genders, suggesting potential issues with product suitability? How do different financial service providers (FSPs) compare in terms of lapse rates across genders? Are there notable differences when considering age, location, or income alongside gender?</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>Outcomes, Credit risk</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Suitability</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D147">
-        <v>197</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Reinstatement of lapsed insurance policies</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>% of lapsed insurance policies that have been re-instated after customer made back-payments</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>This indicator shows the share of policies that lapsed for non-payment and were later reinstated after the customer cleared arrears (and, where required, satisfied evidence-of-insurability). A higher reinstatement rate can indicate effective retention outreach and product value to customers; very low rates may signal affordability stress, weak follow-up, or poor customer experience. From a risk perspective, reinstatements affect cash flows, reserve dynamics, and anti-selection (customers may reinstate when risk has increased). Pair this indicator with persistency, tenure of cancellations, and complaint metrics to diagnose retention quality and customer outcomes. !- Definitions and concepts: Lapse (non-payment): policy terminated after the grace period due to unpaid premium (distinct from surrender, maturity, or death). Reinstatement: restoration of coverage after lapse once back-premiums (and any interest/fees) are paid and underwriting/administrative conditions are met. Coverage may be backdated or resume prospectively per policy terms. Measurement window: define a fixed look-back (e.g., reinstated within 90/180 days of lapse). Formula (cohort basis): # policies that lapsed in period and were reinstated within {days} divided by the # policies that lapsed in period. Variants: policyholder-level (deduplicated), premium-weighted share, and calendar-period “reinstatements ÷ lapses” with a stated window. !- Data requirements: Policy-level: product/LOB, activation date, lapse date, grace-period end, arrears amount, reinstatement date, back-payment amount, underwriting outcome (medical/financial), and whether coverage backdated. Channel, geography, tenure at lapse, and prior claims/loan status. Cohort tags (issue or lapse month) for like-for-like tracking. !- Limitations and considerations: Window sensitivity: longer window raises the rate; disclose and keep constant. Classification noise: grace-period statuses mis-tagged as lapses depress apparent reinstatement. Anti-selection: reinstated policies may have higher subsequent claims—monitor post-reinstatement loss experience. Operational variance: some firms “rewrite” new policies rather than reinstate, understating the metric. Coverage basis: backdated vs. prospective reinstatement changes exposure and reserve treatment—report the split if material.</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>How do rates of reinstating lapsed insurance policies vary by gender? Is any gender more likely to make back payments and reinstate their policies? How do these reinstatement patterns differ across FSPs, policy types, and demographic groups such as age or income? What might these patterns indicate about barriers to maintaining continuous coverage?</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -8286,30 +8246,30 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D148">
-        <v>193</v>
+        <v>27</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Risk of insurance coverage lapse</t>
+          <t>Borrowers in risky indebtedness (risk of over-indebtedness)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>% of all insurance policies (or policyholders) that missed one or more premium payments (depending on product rules and polcies) but are still within the grace period</t>
+          <t>Number of borrowers classified as at risk of over-indebtedness, as per risk-indebtedness calculation</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Measures the percentage of active insurance policies (or policyholders) that have missed one or more scheduled premium payments but remain within the contractual grace period before formal lapse or cancellation takes effect. It reflects the proportion of insurance coverage that is at risk of lapsing due to non-payment but still eligible for reinstatement under product rules. Captures policyholder payment continuity risk and the vulnerability of insurance coverage within a given portfolio. It serves as an early-warning measure of potential lapse rates, affordability pressures, and retention dynamics in insurance markets. Monitoring the risk of coverage lapse helps regulators, supervisors, and insurers to: Identify emerging risks to policy continuity and financial protection coverage; Assess household liquidity stress and premium affordability; Evaluate insurer risk management practices regarding collections and grace-period handling; Strengthen consumer protection and financial health monitoring, especially in low-income or microinsurance segments. It provides an early signal of future lapse or surrender trends, which can affect both household resilience and insurer liquidity. Higher values indicate rising vulnerability to policy lapse, which may reflect household financial strain, ineffective premium collection, or weak payment reminders.Persistent high rates suggest potential issues in affordability or product suitability. Declining values reflect improved payment discipline, automatic premium collection mechanisms, or targeted retention strategies. !- Definitions and concepts: Grace period: A contractually defined period after a missed premium during which coverage remains active and can be reinstated upon payment. Lapse: Termination of an insurance policy due to non-payment of premiums after the grace period expires. !- Data requirements: Administrative data from licensed insurance companies or supervisory reporting systems. Disaggregation by product type (life, health, motor, microinsurance, etc.), customer segment (individual, group), and insurer type. Definition of grace period based on product category (e.g., 30 days for life insurance, 7–15 days for general insurance).</t>
+          <t>Tracking over-indebtedness gives authorities a measure of systemic distress: when large segments of retail borrowers can’t meet their obligations, it highlights consumer-protection gaps. Persistent debt burdens signal predatory lending or inadequate affordability assessments. The indicator helps calibrate market-conduct supervision and regulation. This particular indicator that identifies borrowers at risk of overindebtedness was developed by the Central Bank of Brazil: https://www.bcb.gov.br/content/cidadaniafinanceira/documentos_cidadania/serie_cidadania/serie_cidadania_financeira_8_endividamento_risco_2ed.pdf ad https://www.researchgate.net/publication/376634051_Risky_Indebtedness_Behavior_Impacts_on_Financial_Preparation_for_Retirement_and_Perceived_Financial_Well-Being. It is a composite of four components. A borrower is flagged as being in "risky indebtedness" when any two of the following four criteria are met: (1) Has defaulted on credit installments, that is, has had payment delays of more than 90 days in meeting credit obligations, (2) Monthly income devoted to debt-service payments exceeds 50 percent, (3) Has simultaneous exposure to the following forms of credit: overdraft, unsecured personal loan, and revolving credit card debt, (4) Monthly disposable income (after debt-service payments) that falls below the poverty line. Generating this indicator at the system level requires a unique national ID in order to match granular loan data to unique borrowers. The indicator also requires access to income data. !- Derivable indicators: Percent of borrowers in risky indebtendess; Percent of adults in risky indebtedness.</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>How well does the non-life insurance policy market reflect gender-based differences in policyholding and insured benefits? How do the types of non-life insurance policies held compare by gender? How are gender disparities evolving in the distribution of non-life insurance policies across different FSPs?</t>
+          <t>Are there gender disparities in the classification of risky indebtedness? Are low-income borrowers more at risk of risky indebtedness and how does it compare across genders? Comparing this indicator with gender diversity, do FSPs with higher levels of gender diversity present lower levels of risky indebtedness?</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -8319,17 +8279,17 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Outcomes</t>
+          <t>Credit risk</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -8346,23 +8306,263 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="D149">
+        <v>285</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Debt service-to-income ratio</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>% of income allocated to retail credit debt repayment</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>The debt service-to-Income ratio,  sometimes referred to more concisely as the debt service ratio (DSR) expresses a borrower’s (or household’s) total debt-service burden relative to recurring income, answering a simple question: How much of each income unit is already pledged to repay existing debt? At the micro level, lenders use DSR to assess repayment capacity, price credit, and comply with responsible-lending rules. At the macro level, supervisors track average or distributional DSR to gauge household vulnerability to interest-rate shocks and to calibrate macro-prudential tools such as loan-to-income caps. !- Definitions and concepts: Debt payments include principal, interest, mandatory insurance on retail credit facilities;  Income can be defined in gross terms (pre-tax income (salary) plus verifiable recurring earning) or net terms (income after taxes and social-security contributions). !- Data requirements: Current loan statements or credit-bureau/registry reports detailing payment amounts, remaiming term, and interest rate for all obligations; Recent payslips, audited financial statements (self-fmployed), tax returns, and verified rental or pension income. !- Limitations and considerations: Income volatility: informal or gig-economy or commission-based earnings make future cash flows uncertain; Undisclosed liabilities: informal or unreported debts escape bureau coverage, understating true DSR. Household composition: shared living expenses and co-borrower support can distort individual ratios; some frameworks use household disposable income instead. Interest-rate path: fixed-rate loans keep payments stable, while floating-rate debt can raise DSR sharply when policy rates rise. Cross-country comparability: tax structures, social-welfare benefits, and healthcare costs influence disposable income, so identical DSR thresholds may imply different real affordability across jurisdictions.</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>How do debt service-to-income ratios vary by gender and across different loan sizes and terms? Do loans with higher rates and shorter terms show gender disparities in ratios? Comparing this indicator with gender diversity, do FSPs with higher levels of gender diversity present lower debt-service to income ratios?</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Quality, Credit risk</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Suitability</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D149">
+      <c r="D150">
+        <v>194</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Insurance lapse rates</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>% of all insurance policies (or policyholders) that have lapsed</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>This indicator measures the number of policies discontinued due to non-payment of premiums by the policyholder relative to the total number of policies at the beginning of the period. It is a key indicator to assess quality of advice, quality of service, product appropriateness, and mis-selling risk in the insurance sector. https://www.iais.org/uploads/2022/06/Report-on-Supervisors-Use-of-Key-Indicators-to-Assess-Insurer-Conduct.pdf</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>How do insurance lapse rates differ by gender? Are certain types of insurance policies associated with higher lapse rates among specific genders, suggesting potential issues with product suitability? How do different financial service providers (FSPs) compare in terms of lapse rates across genders? Are there notable differences when considering age, location, or income alongside gender?</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Outcomes, Credit risk</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Suitability</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D151">
+        <v>197</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Reinstatement of lapsed insurance policies</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>% of lapsed insurance policies that have been re-instated after customer made back-payments</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>This indicator shows the share of policies that lapsed for non-payment and were later reinstated after the customer cleared arrears (and, where required, satisfied evidence-of-insurability). A higher reinstatement rate can indicate effective retention outreach and product value to customers; very low rates may signal affordability stress, weak follow-up, or poor customer experience. From a risk perspective, reinstatements affect cash flows, reserve dynamics, and anti-selection (customers may reinstate when risk has increased). Pair this indicator with persistency, tenure of cancellations, and complaint metrics to diagnose retention quality and customer outcomes. !- Definitions and concepts: Lapse (non-payment): policy terminated after the grace period due to unpaid premium (distinct from surrender, maturity, or death). Reinstatement: restoration of coverage after lapse once back-premiums (and any interest/fees) are paid and underwriting/administrative conditions are met. Coverage may be backdated or resume prospectively per policy terms. Measurement window: define a fixed look-back (e.g., reinstated within 90/180 days of lapse). Formula (cohort basis): # policies that lapsed in period and were reinstated within {days} divided by the # policies that lapsed in period. Variants: policyholder-level (deduplicated), premium-weighted share, and calendar-period “reinstatements ÷ lapses” with a stated window. !- Data requirements: Policy-level: product/LOB, activation date, lapse date, grace-period end, arrears amount, reinstatement date, back-payment amount, underwriting outcome (medical/financial), and whether coverage backdated. Channel, geography, tenure at lapse, and prior claims/loan status. Cohort tags (issue or lapse month) for like-for-like tracking. !- Limitations and considerations: Window sensitivity: longer window raises the rate; disclose and keep constant. Classification noise: grace-period statuses mis-tagged as lapses depress apparent reinstatement. Anti-selection: reinstated policies may have higher subsequent claims—monitor post-reinstatement loss experience. Operational variance: some firms “rewrite” new policies rather than reinstate, understating the metric. Coverage basis: backdated vs. prospective reinstatement changes exposure and reserve treatment—report the split if material.</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>How do rates of reinstating lapsed insurance policies vary by gender? Is any gender more likely to make back payments and reinstate their policies? How do these reinstatement patterns differ across FSPs, policy types, and demographic groups such as age or income? What might these patterns indicate about barriers to maintaining continuous coverage?</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Suitability</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D152">
+        <v>193</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Risk of insurance coverage lapse</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>% of all insurance policies (or policyholders) that missed one or more premium payments (depending on product rules and polcies) but are still within the grace period</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Measures the percentage of active insurance policies (or policyholders) that have missed one or more scheduled premium payments but remain within the contractual grace period before formal lapse or cancellation takes effect. It reflects the proportion of insurance coverage that is at risk of lapsing due to non-payment but still eligible for reinstatement under product rules. Captures policyholder payment continuity risk and the vulnerability of insurance coverage within a given portfolio. It serves as an early-warning measure of potential lapse rates, affordability pressures, and retention dynamics in insurance markets. Monitoring the risk of coverage lapse helps regulators, supervisors, and insurers to: Identify emerging risks to policy continuity and financial protection coverage; Assess household liquidity stress and premium affordability; Evaluate insurer risk management practices regarding collections and grace-period handling; Strengthen consumer protection and financial health monitoring, especially in low-income or microinsurance segments. It provides an early signal of future lapse or surrender trends, which can affect both household resilience and insurer liquidity. Higher values indicate rising vulnerability to policy lapse, which may reflect household financial strain, ineffective premium collection, or weak payment reminders.Persistent high rates suggest potential issues in affordability or product suitability. Declining values reflect improved payment discipline, automatic premium collection mechanisms, or targeted retention strategies. !- Definitions and concepts: Grace period: A contractually defined period after a missed premium during which coverage remains active and can be reinstated upon payment. Lapse: Termination of an insurance policy due to non-payment of premiums after the grace period expires. !- Data requirements: Administrative data from licensed insurance companies or supervisory reporting systems. Disaggregation by product type (life, health, motor, microinsurance, etc.), customer segment (individual, group), and insurer type. Definition of grace period based on product category (e.g., 30 days for life insurance, 7–15 days for general insurance).</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>How well does the non-life insurance policy market reflect gender-based differences in policyholding and insured benefits? How do the types of non-life insurance policies held compare by gender? How are gender disparities evolving in the distribution of non-life insurance policies across different FSPs?</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Outcomes</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Suitability</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D153">
         <v>196</v>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="E153" t="inlineStr">
         <is>
           <t>Surrendered insurance policies</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>% of eligible insurance policies (or policyholders) de-activated/lapsed that paid-out surrender values</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="G153" t="inlineStr">
         <is>
           <t>This indicator shows the share of terminated policies that generated a cash surrender payout. It helps distinguish benign expiries or non-cash lapses from value-bearing exits that can strain liquidity, depress embedded value, and signal product-fit or conduct issues (e.g., early surrenders after aggressive sales). Supervisors and boards use it to gauge customer outcomes, the health of savings-type books, and potential mis-selling or affordability problems. !- Definitions and concepts: Eligible policy: contracts with a cash value (e.g., whole life, endowment, unit-linked). Pure risk covers (term, many GI lines) are ineligible. Surrender vs. lapse: a surrender pays cash value on termination; a lapse ends cover without payout. De-activatd here excludes natural maturaties and deaths. Full vs. partial surrender: count full surrenders tied to termination; report partial withdrawals separately unless they trigger de-activation.
 Indicator (count basis): Policies terminated in period with a surrender payout divided by the number of eligible policies terminated (non-maturity) in period. Variants: policyholder-based (unique customers), and amount-based (surrender amounts ÷ cash values of terminated policies). Segment by tenure (&lt;1y, 1–3y, &gt;3y), product, and channel. Data requirements
@@ -8370,326 +8570,91 @@
 Data granularity: partial withdrawals that don’t terminate cover should be excluded or separately disclosed. Conduct lens: high early-tenure surrender shares point to mis-selling or affordability issues—pair with complaints, persistency, and tenure-of-cancellation indicators.</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
+      <c r="H153" t="inlineStr">
         <is>
           <t>Are surrender values and payouts equitably distributed by gender among eligible policyholders? Is there any gender that is less likely to receive surrender payouts, and does this vary by policy type or FSP? How do surrender rates differ by gender when combined with other demographics like income or location?</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
+      <c r="L153" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
+    <row r="154">
+      <c r="A154" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>Suitability</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D150">
+      <c r="D154">
         <v>195</v>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E154" t="inlineStr">
         <is>
           <t>Tenure of  insurance policies</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>Average time elapsed since policy activation, by chosen time periods (e.g., &lt;3 months, 3-6 months, 6-12 months, etc)</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t>This indicator measures how long policies have stayed in force -including policies that were cancelled or lapsed mid-term. It captures the stability, maturity, and longevity of customer relationships with insurers, distinguishing recently opened accounts from those that have remained active and in use over time, and identifying which policies were cancelled after a short period of activity. A concentration of early-tenure cancellations is a red flag for mis-selling, poor onboarding, pricing/friction issues, or product-fit problems. It also matters for economics: early lapses strand acquisition costs, depress embedded value, and erode persistency. Tracking tenure helps regulators and financial institutions to: Assess policyholder retention and churn rates; Identify short-lived policies that may inflate access statistics; Evaluate the depth and continuity of customer engagement; Analyze cancellations by product and channel to target remediation measures (e.g., agent training, cooling-off disclosures, claim-time communications). From a supervisory perspective, it provides insights into stability, consumer loyalty, and the effectiveness of insurance acquisition campaigns. A longer average tenure indicates stable customer relationships, active usage, and mature market penetration. A high share of new policies may suggest recent inclusion initiatives, but also potential fragility if those policies are cancelled quickly. Monitoring shifts over time can reveal trends in account retention and digital adoption maturity !- Definitions and concepts: Activation (policy start): the in-force date (not the issue date, if different). Cancellation: termination of cover before the natural renewal/expiry date—may be customer-initiated (voluntary), insurer-initiated (non-payment, underwriting, fraud), or regulatory. Tenure of active policies (days/months) = date at the end of the reference period – activation date. Tenure of cancelled policies (days/months) = cancelation date – activation date.
 Buckets: choose stable, business-meaningful bands (e.g., &lt;3m, 3–6m, 6–12m, 12–24m, &gt;24m). Report count-weighted and premium-weighted shares. Scope: life and non-life.  Clarify whether non-renewals at anniversary are counted (usually not) and how cooling-off/free-look rescissions are treated (often reported separately). Data requirements: Policy-level fields: policy ID, product/LOB, distribution channel, activation date, cancellation date, cancellation reason code, written premium/sum assured, payment mode, and claim history. Status logic to exclude simple expiries and to de-duplicate reinstated policies (see below). Calendar and cohort views (by issue month/quarter) to remove seasonality. !- Limitations and considerations: Selection bias: averaging only cancelled policies ignores still-active ones. For a fuller view of lifetime behaviour, complement with survival analysis (e.g., Kaplan–Meier) and standard persistency ratios (13/25/61-month). Reinstatements: define whether a reinstated policy’s earlier cancellation is (a) ignored, (b) treated as a separate episode, or (c) measured to the first cancellation only.
 For cancelled policies, consider including reason codes and analyze results by product type (voluntary, non-payment, underwriting, fraud). Early non-payment suggests billing/channel issues; early voluntary points to product fit. Channel &amp; product mix: bancassurance, digital, and agency books have distinct early-tenure profiles—always segment. Cooling-off: report &lt;30-day rescissions separately to avoid overstating issues that are procedural rather than structural.</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
+      <c r="H154" t="inlineStr">
         <is>
           <t>Do genders differ in how long they hold their policies? Are there disproportionate gender differences in longer, medium, or shorter tenures? Does any gender show higher loyalty across different insurers/types? At what tenure points do insurance policies tend to be canceled, and do these patterns vary by gender? Is there a gender more likely to cancel policies earlier? How do cancellation patterns differ across policy types, age groups, locations, or income levels? What might early cancellations suggest about policy suitability or customer experience for different genders?</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
+      <c r="L154" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Suitability, Fair treatment</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D151">
-        <v>61</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Insurance policy downgrade rate</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>% of policies downgraded at the customer's request (e.g.,  lower coverage, higher deductiblees, removal of riders, switch to a lower tier plan)</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>This indicator tracks the share of in-force policies that customers voluntarily reduce in coverage during the period. Elevated downgrade activity can signal affordability stress, product misfit, or competitive pressure (customers trading down to cheaper plans). It affects revenue (lower premiums), risk mix (higher deductibles shift loss ratios), and persistency (downgrades may precede lapses or surrenders). Supervisors and boards use the metric to monitor customer outcomes and pricing adequacy, and to gauge the effectiveness of retention strategies that preserve cover while easing budgets. !- Definitions and concepts: Downgrade (customer-initiated): a mid-term endorsement or renewal change that reduces coverage level—e.g., lower sum assured/benefit limits, higher deductibles/co-pays, downgrade of plan tier. Formula (count basis): # policies with customer-requested downgrades in period divided by # active (or renewing) policies in period. !- Limitations and considerations: Multiple events: the same policy may downgrade more than once—decide event vs. policy-unique counting. Product mapping: ensure consistent tier/benefit taxonomy across products. Group policies: member-level downgrades may not map cleanly to master policy counts—state scope.</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in policy downgrade rates, including for MSMEs based on owner gender? Which types of policies experience higher downgrade rates, and could this reflect issues like unsuitable product features or unfavorable premium-to-coverage ratios? How might these downgrade rates relate to claims rejection rates and coverage ratios? Could poor claims experiences or misunderstandings about coverage terms contribute to downgrades? Do FSPs with greater gender diversity exhibit lower downgrade rates?</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Suitability</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Investments</t>
-        </is>
-      </c>
-      <c r="D152">
-        <v>206</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Unpaid matured long-term investments</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>% of long-term investments that have matured but have not yet been paid to investors</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>What percentage of unpaid matured longer-term investments is attributable to each gender? Are unpaid amounts disproportionately concentrated in any gender? How do FSPs rank in terms of unpaid proportions of matured longer-term investments by gender?</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>Market development</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>Capital markets development</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Suitability, Fair treatment</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Pensions</t>
-        </is>
-      </c>
-      <c r="D153">
-        <v>34</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Pension fund switching rate</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>% of all pension accounts that have switched to another pension fund administrator</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>An indicator of switching rates among pension recipients is a metric used to measure the frequency or volume of pension fund members who transfer their accumulated savings from one pension fund administrator (PFA) to another within a specific timeframe. This indicator can be used in countries where there is a private pension fund adminsitration industry, but not in countries where the entirety of the pension system is publicly-funded. This indicator serves as a key barometer of competition, customer satisfaction, and market dynamics within the pension industry. It can signal trends to administrators, regulators, and members themselves.  Switching Rate (%) = Total average number of members in the system / number of members who switched pension fund administrators  ×100</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>How do transfers of pension fund balances to a different pension fund administrator vary by gender? Does this vary according to the level of FSP gender diversity? What percentage of contributors transferred funds compared to all customers, and are there gender disparities in this proportion? Are certain customer segments, such as women, women-owned MSMEs, and low-value accounts, more likely to make high-to-low transfers (switching to a fund administrator that has been paying lower returns)? Are FSPs with higher levels of gender diversity less likely to receive savers coming from an administrator that previously paid higher returns?</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Pension type</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Suitability</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Savings</t>
-        </is>
-      </c>
-      <c r="D154">
-        <v>151</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Tenure of deposit and payment accounts</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Average time elapsed since account opening</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Measures the length of time that deposit and payment accounts have been open, can be expressed as an average or as the share of accounts in tenure categories such as &lt;3 months, 3–6 months, 6–12 months, 1–3 years, &gt;3 years, etc. It reflects the age profile of active accounts held by customers at regulated financial institutions and payment service providers. Captures the stability, maturity, and longevity of customer relationships with financial institutions. It is a key behavioral measure of financial inclusion sustainability, distinguishing recently opened accounts from those that have remained active and in use over time. Tracking account tenure helps regulators and financial institutions to: Assess account retention and churn rates in deposit and payment systems; Monitor sustained usage versus one-off account openings, especially under inclusion programs; Identify short-lived or dormant accounts that may inflate access statistics; Evaluate the depth and continuity of customer engagement with the financial system. From a supervisory perspective, it provides insights into financial system stability, consumer loyalty, and the effectiveness of account-opening campaigns. A longer average tenure indicates stable customer relationships, active usage, and mature market penetration. A high share of newly opened accounts may suggest recent inclusion initiatives, but also potential fragility if those accounts become inactive. Monitoring shifts over time can reveal trends in account retention and digital adoption maturity. !- Definitions and concepts: Deposit accounts: Savings, current, or term accounts offered by regulated deposit-taking institutions. Payment accounts: Accounts used to execute payment transactions or access funds on demand, including e-money and digital wallets. !- Data requirements: Account-level data from administrative records containing the account opening date; Total number of accounts. The tenure is calculated as the difference between the data of the end of the reference period and the account opening data (expressed in years or months).</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Do genders differ in how long they hold their transaction accounts? Are some genders disproportionately represented in longer, medium, or shorter account tenures? Which genders show higher account loyalty across different FSPs/types, and which tend to close accounts sooner?</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>Liquidity risk</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -8701,296 +8666,291 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
+          <t>Suitability, Fair treatment</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D155">
+        <v>61</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Insurance policy downgrade rate</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>% of policies downgraded at the customer's request (e.g.,  lower coverage, higher deductiblees, removal of riders, switch to a lower tier plan)</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>This indicator tracks the share of in-force policies that customers voluntarily reduce in coverage during the period. Elevated downgrade activity can signal affordability stress, product misfit, or competitive pressure (customers trading down to cheaper plans). It affects revenue (lower premiums), risk mix (higher deductibles shift loss ratios), and persistency (downgrades may precede lapses or surrenders). Supervisors and boards use the metric to monitor customer outcomes and pricing adequacy, and to gauge the effectiveness of retention strategies that preserve cover while easing budgets. !- Definitions and concepts: Downgrade (customer-initiated): a mid-term endorsement or renewal change that reduces coverage level—e.g., lower sum assured/benefit limits, higher deductibles/co-pays, downgrade of plan tier. Formula (count basis): # policies with customer-requested downgrades in period divided by # active (or renewing) policies in period. !- Limitations and considerations: Multiple events: the same policy may downgrade more than once—decide event vs. policy-unique counting. Product mapping: ensure consistent tier/benefit taxonomy across products. Group policies: member-level downgrades may not map cleanly to master policy counts—state scope.</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in policy downgrade rates, including for MSMEs based on owner gender? Which types of policies experience higher downgrade rates, and could this reflect issues like unsuitable product features or unfavorable premium-to-coverage ratios? How might these downgrade rates relate to claims rejection rates and coverage ratios? Could poor claims experiences or misunderstandings about coverage terms contribute to downgrades? Do FSPs with greater gender diversity exhibit lower downgrade rates?</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
           <t>Suitability</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="D156">
+        <v>206</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Unpaid matured long-term investments</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>% of long-term investments that have matured but have not yet been paid to investors</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>What percentage of unpaid matured longer-term investments is attributable to each gender? Are unpaid amounts disproportionately concentrated in any gender? How do FSPs rank in terms of unpaid proportions of matured longer-term investments by gender?</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Market development</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Capital markets development</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Suitability, Fair treatment</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Pensions</t>
+        </is>
+      </c>
+      <c r="D157">
+        <v>34</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Pension fund switching rate</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>% of all pension accounts that have switched to another pension fund administrator</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>An indicator of switching rates among pension recipients is a metric used to measure the frequency or volume of pension fund members who transfer their accumulated savings from one pension fund administrator (PFA) to another within a specific timeframe. This indicator can be used in countries where there is a private pension fund adminsitration industry, but not in countries where the entirety of the pension system is publicly-funded. This indicator serves as a key barometer of competition, customer satisfaction, and market dynamics within the pension industry. It can signal trends to administrators, regulators, and members themselves.  Switching Rate (%) = Total average number of members in the system / number of members who switched pension fund administrators  ×100</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>How do transfers of pension fund balances to a different pension fund administrator vary by gender? Does this vary according to the level of FSP gender diversity? What percentage of contributors transferred funds compared to all customers, and are there gender disparities in this proportion? Are certain customer segments, such as women, women-owned MSMEs, and low-value accounts, more likely to make high-to-low transfers (switching to a fund administrator that has been paying lower returns)? Are FSPs with higher levels of gender diversity less likely to receive savers coming from an administrator that previously paid higher returns?</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Pension type</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Suitability</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Savings</t>
+        </is>
+      </c>
+      <c r="D158">
+        <v>151</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Tenure of deposit and payment accounts</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Average time elapsed since account opening</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Measures the length of time that deposit and payment accounts have been open, can be expressed as an average or as the share of accounts in tenure categories such as &lt;3 months, 3–6 months, 6–12 months, 1–3 years, &gt;3 years, etc. It reflects the age profile of active accounts held by customers at regulated financial institutions and payment service providers. Captures the stability, maturity, and longevity of customer relationships with financial institutions. It is a key behavioral measure of financial inclusion sustainability, distinguishing recently opened accounts from those that have remained active and in use over time. Tracking account tenure helps regulators and financial institutions to: Assess account retention and churn rates in deposit and payment systems; Monitor sustained usage versus one-off account openings, especially under inclusion programs; Identify short-lived or dormant accounts that may inflate access statistics; Evaluate the depth and continuity of customer engagement with the financial system. From a supervisory perspective, it provides insights into financial system stability, consumer loyalty, and the effectiveness of account-opening campaigns. A longer average tenure indicates stable customer relationships, active usage, and mature market penetration. A high share of newly opened accounts may suggest recent inclusion initiatives, but also potential fragility if those accounts become inactive. Monitoring shifts over time can reveal trends in account retention and digital adoption maturity. !- Definitions and concepts: Deposit accounts: Savings, current, or term accounts offered by regulated deposit-taking institutions. Payment accounts: Accounts used to execute payment transactions or access funds on demand, including e-money and digital wallets. !- Data requirements: Account-level data from administrative records containing the account opening date; Total number of accounts. The tenure is calculated as the difference between the data of the end of the reference period and the account opening data (expressed in years or months).</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Do genders differ in how long they hold their transaction accounts? Are some genders disproportionately represented in longer, medium, or shorter account tenures? Which genders show higher account loyalty across different FSPs/types, and which tend to close accounts sooner?</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Liquidity risk</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Suitability</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
         <is>
           <t>Payments, Savings, Pensions, Investments</t>
         </is>
       </c>
-      <c r="D155">
+      <c r="D159">
         <v>158</v>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="E159" t="inlineStr">
         <is>
           <t>Inactive and dormant accounts (balance)</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t>% of total account balances that are held in inactive and dormant accounts</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t>This indicator shows the share of funds sitting in deposit and payment accounts (excluding term deposits) that are not actively used by customers. High concentrations of idle balances can signal weak customer engagement, poor product fit, or frictions in account usage—important for financial-inclusion quality, liquidity management, and conduct risk. From a prudential angle, large dormant balances may look “stable” but can reverse if reactivation drives or policy changes prompt withdrawals. For consumer protection, persistent dormancy raises risks around unclaimed funds, fees, and fraud. Recommended to analyze of this indicator by product type (e.g. current/checking, mobile money, etc). !- Definitions and concepts: Accounts: demand/current accounts and other payment-capable deposit accounts. Inactive account: no customer-initiated debit/credit (card use, cash withdrawal/deposit, transfer) for a defined window (e.g., ≥90 or 180 days). System entries (interest, fees, bank corrections) don’t count. Dormant account: extended inactivity beyond a longer threshold (commonly ≥12 months) that may trigger special handling (restricted access, outreach, escheatment). Indicator formula: Balances in inactive + dormant transaction accounts divided by total transaction-account balances. Reporting the split (inactive vs. dormant) can provide further detail. !- Data requirements: Core-banking ledger with end-of-day balances, product codes, and last customer-initiated activity timestamp per account. Classification rules reflecting local definitions (inactive/dormant thresholds; treatment of standing orders/auto-debits). Ownership segment (retail/MSMEs), currency, and insured/uninsured flags. Optional: outreach attempts, reactivation outcomes, and fee assessments to monitor conduct risk. Limitations &amp; considerations: Definition divergence: thresholds and what counts as “activity” vary by jurisdiction and even by institution—state methodology clearly. Data quality: some channels (agents, fintech front-ends) may not update the core “last activity” field, overstating dormancy.
 Seasonality &amp; cycles: balances can spike around payroll/tax periods; use consistent month-end or averages. Policy effects: dormancy fees, auto-closures, and unclaimed-funds rules materially affect trends. Coverage scope: exclude escrow, trust, and suspense ledgers to avoid inflating inactive balances.</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
+      <c r="H159" t="inlineStr">
         <is>
           <t>What proportion of balances held in inactive/dormant/suspense accounts is attributable to each gender? Are these balances disproportionately skewed by gender? Which FSPs have notable skews (higher than market averages) in balances held in inactive/dormant/suspense accounts by gender?</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
+      <c r="L159" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Account type</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Suitability</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D156">
-        <v>161</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Revenue from inactive and dormant accounts</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Average non-interest revenue earned on inactive and dormant accounts per account holder</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>This indicator estimates how much fee income a provider earns, on average, from customers whose transaction accounts are inactive or dormant. It highlights potential conduct-risk hotspots (“junk fees”), tests whether inclusion policies translate into active use, and helps gauge earnings reliance on non-usage charges. Regulators often scrutinize such revenue because it may disproportionately affect vulnerable or low-balance customers and can conflict with fair-treatment principles or local dormancy rules. Used alongside % balances in inactive/dormant accounts, reactivation rates, and complaints upheld about fees, this metric provides a balanced view of inclusion quality and earnings fairness. !- Definitions and concepts: Inactive account: no customer-initiated transaction over a defined window (e.g., ≥90/180 days). Dormant account: extended inactivity (e.g., ≥12 months) triggering special handling (restricted access, outreach, or escheatment). Non-interest revenue: maintenance/inactivity fees, SMS/statement charges, card fees, ATM/network fees, account closure fees—exclude interest, FX spreads, and lending-related fees. Metric (per holder): Avg. fee per inactive/dormant holder = [Non interest fees charged to inactive+dormant accounts in period (net of waivers/refunds)] divided by unique customers with ≥1 inactive or dormant account in period. Report per-account as a companion view, and show inactive vs dormant separately. !- Data requirements: Core-banking extracts: account status, last customer-initiated activity timestamp, balances, product code. General-ledger fee income by fee code with identifiers to tie fees to specific accounts/customers; flags for waivers/refunds/chargebacks. Customer master data to deduplicate holders with multiple accounts. Policy tables: inactivity/dormancy thresholds, fee schedules, and escheatment rules; time-at-risk (days classified as inactive/dormant). !- Limitations and considerations: Definition variance: thresholds and what counts as “activity” differ—state methodology. Partial-period bias: accounts turning dormant late in the period face fewer fee days; consider normalizing by days inactive/dormant. Outliers &amp; distribution: averages can be skewed; also report median, 90th percentile, and % of affected customers. Conduct/regulatory constraints: some jurisdictions cap or ban dormancy fees or require fee cessation before escheatment—track compliance and annotate series breaks after rule changes. Mix effects: product/channel mixes (e.g., basic accounts, youth or social-transfer accounts) drive fee propensity—segment results by product and customer segment.</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>How does the average revenue earned from inactive and dormant accounts compare by gender? Are there gender disparities in the charges applied to these accounts compared to the overall market average? How do relevant FSPs rank in terms of the average revenue earned from these accounts, and does this ranking change when analyzed by gender?</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Account type</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Suitability</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D157">
-        <v>229</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Product take-up ratio</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>% of approved applicants who take-up the approved products by product type</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Share of applicants that are approved for a specific product type that take-up the product. This indicator can be viewed together with the product application indicator to allow for a more comprehensive analysis of the demand for financial products. Product categoreis to consider for analysis include: deposits, investments, insurance, credit.</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>How do take-up rates vary by gender? Do any genders have higher take-up rates than the overall market average? How do FSPs compare in terms of take-up rates by gender?</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>Uptake (account ownership)</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Product type</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Fair treatment</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Savings</t>
-        </is>
-      </c>
-      <c r="D158">
-        <v>162</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Account closure costs paid by customers</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Average customer-paid account closure charges</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>This indicator captures the out-of-pocket costs borne by customers when they close their transaction account(s). It focuses on fees directly tied to the closure process (not ongoing usage fees). High averages or wide dispersion can signal unfair fee structures, poor process design (e.g., costly payout rails), or weak disclosures—issues that draw conduct-risk scrutiny and harm inclusion goals. Tracking this metric alongside complaints upheld about closure, time to close, and payout failure/return rates gives a rounded view of off-boarding fairness and efficiency. !- Definitions and concepts: Transaction accounts are broadly defined as an account held with a bank or other authorised and/or regulated service provider (including a non-bank) which can be used to make and receive payments. Transaction accounts can be further differentiated into deposit transaction accounts and e-money accounts. Customer-paid closure charges: amounts debited to the customer because of closure, including: explicit closure fees, final statement/document fees, card/cheque deactivation fees, balance-refund/payout charges (e.g., wire/RTGS, cheque issuance, e-money cash-out), account package early-termination fees, statutory taxes/levies linked to these items, and FX/transfer margins if required to remit funds. Exclusions: regular monthly maintenance already charged prior to the closure request, penalty interest on unrelated lending, and third-party fees not passed through. !- Data requirements: Event log with closure request date and closure completion date; customer ID (deduplicated), number of accounts closed, channel, reason code. Transaction-level fee taxonomy to flag closure-related charges; payout transactions (method, amount, fees, FX). Reversal/waiver flags and timestamps to net back rescinded charges. Recommended charge window: from request date through T+30 days after completion to catch settlement/payout fees. Number of customers who closed at least 1 account in period. !- Limitations and considerations: Attribution: define the fee list upfront to avoid counting routine usage fees; publish the measurement window.</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>How do relevant FSPs rank in terms of closing costs (from highest to lowest), and does this ranking change when the average is computed by gender? Are women and men equally likely to incur account closure fees, or are there gendered patterns in the types of financial service providers (FSPs) they use that influence the likelihood or amount of such fees? How might account closure costs act as a barrier to financial flexibility or mobility? Are women more likely to avoid formal financial services due to concerns over the cost of exiting the system? Additionally, are FSPs that charge lower or no closure fees more accessible to certain gender groups, and does this vary by geography or provider type?</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Market development</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>Outcomes, Capital markets development</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Suitability</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D159">
-        <v>389</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Insurance claims (number)</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Number of insurance claims</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>The total count of insurance claims formally submitted by policyholders, beneficiaries, or authorized third parties to an insurer within a defined reporting period, regardless of whether the claims are accepted, rejected, paid, or still under review. Denominator for several key inclusion, consumer protection and prudential insurance ratios. !- Data requirements: Claim identifier, (unique ID per claim), Policyholder identifier, Date of claim submission.</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>How do claim numbers vary by gender? Are there any gender groups logging fewer claims compared to the market average? Are there FSPs with particularly low or high claim numbers for certain genders? How do claim statistics intersect with policy type and customer demographics?</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>Usage, Soundness</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -9002,35 +8962,35 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Fair treatment</t>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Payments, Savings, Pensions, Investments</t>
         </is>
       </c>
       <c r="D160">
-        <v>390</v>
+        <v>161</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Insurance claims paid</t>
+          <t>Revenue from inactive and dormant accounts</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Value of insurance claims paid</t>
+          <t>Average non-interest revenue earned on inactive and dormant accounts per account holder</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>"Claims paid" represents the total cash outflow or settled obligations by an insurer to policyholders or beneficiaries for claims events during a reporting period. It includes only claims for which payment has been disbursed, regardless of whether additional claims are still outstanding or whether reserves were previously established. Tracking claims paid helps supervisors monitor liquidity, operational efficiency, and consumer protection outcomes. It provides a concrete measure of the insurer’s fulfillment of contractual obligations and complements other claims indicators (e.g., claims incurred, claims outstanding, unpaid approved claims). !- Data requirements: Claim identifier, (unique ID per claim), Policyholder identifier, Date of claim submission, Date of payment, Amount paid (full or partial), Product / policy type; . !- Limitations and considerations: paid claims may lag claims incurred due to reporting delays or extended claims handling processes; some claims are paid in installments, methodology must specify whether to include full or partial amounts; severe events can cause sudden increases in paid claims, interpretation should consider context. Segmentation by product line or policy type is recommended for supervisory analysis.</t>
+          <t>This indicator estimates how much fee income a provider earns, on average, from customers whose transaction accounts are inactive or dormant. It highlights potential conduct-risk hotspots (“junk fees”), tests whether inclusion policies translate into active use, and helps gauge earnings reliance on non-usage charges. Regulators often scrutinize such revenue because it may disproportionately affect vulnerable or low-balance customers and can conflict with fair-treatment principles or local dormancy rules. Used alongside % balances in inactive/dormant accounts, reactivation rates, and complaints upheld about fees, this metric provides a balanced view of inclusion quality and earnings fairness. !- Definitions and concepts: Inactive account: no customer-initiated transaction over a defined window (e.g., ≥90/180 days). Dormant account: extended inactivity (e.g., ≥12 months) triggering special handling (restricted access, outreach, or escheatment). Non-interest revenue: maintenance/inactivity fees, SMS/statement charges, card fees, ATM/network fees, account closure fees—exclude interest, FX spreads, and lending-related fees. Metric (per holder): Avg. fee per inactive/dormant holder = [Non interest fees charged to inactive+dormant accounts in period (net of waivers/refunds)] divided by unique customers with ≥1 inactive or dormant account in period. Report per-account as a companion view, and show inactive vs dormant separately. !- Data requirements: Core-banking extracts: account status, last customer-initiated activity timestamp, balances, product code. General-ledger fee income by fee code with identifiers to tie fees to specific accounts/customers; flags for waivers/refunds/chargebacks. Customer master data to deduplicate holders with multiple accounts. Policy tables: inactivity/dormancy thresholds, fee schedules, and escheatment rules; time-at-risk (days classified as inactive/dormant). !- Limitations and considerations: Definition variance: thresholds and what counts as “activity” differ—state methodology. Partial-period bias: accounts turning dormant late in the period face fewer fee days; consider normalizing by days inactive/dormant. Outliers &amp; distribution: averages can be skewed; also report median, 90th percentile, and % of affected customers. Conduct/regulatory constraints: some jurisdictions cap or ban dormancy fees or require fee cessation before escheatment—track compliance and annotate series breaks after rule changes. Mix effects: product/channel mixes (e.g., basic accounts, youth or social-transfer accounts) drive fee propensity—segment results by product and customer segment.</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>How do claim payments vary by gender? Are there any gender groups receiving fewer/lower payments compared to the market average? Are there FSPs with particularly low or high payment rate for certain genders? How do claim payment statistics intersect with policy type and customer demographics?</t>
+          <t>How does the average revenue earned from inactive and dormant accounts compare by gender? Are there gender disparities in the charges applied to these accounts compared to the overall market average? How do relevant FSPs rank in terms of the average revenue earned from these accounts, and does this ranking change when analyzed by gender?</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9040,29 +9000,29 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Usage, Soundness</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Account type</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Stability, safety and soundness</t>
+          <t>Consumer protection</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>AML/CFT</t>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9071,26 +9031,26 @@
         </is>
       </c>
       <c r="D161">
-        <v>64</v>
+        <v>229</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Suspicious transaction reports</t>
+          <t>Product take-up ratio</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Number of suspicious transaction reports</t>
+          <t>% of approved applicants who take-up the approved products by product type</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>The indicator tallies the suspicious transaction reports (STRs)  financial service providers file with the Financial Intelligence Unit (FIU) when they suspect financial crimes such as money-laundering and terrorism financing. A rising count can signal stronger transaction monitoring systems or higher level of potentially criminal activities. Policymakers use STR volumes, in combination with other data (e.g., investigations), to allocate investigative resources. !- Definitions and concepts: Suspicious Transaction Report (STR): a mandatory report filed when a transaction is known, suspected, or has reasonable grounds to be suspected of involving criminal proceeds or terrorist funds (FATF Rec. 20). Reporting entities: broadly, all institutions covered by the AML/CFT law, including all finacial financial service providers. !- Data requirements: FIU registry of incoming STRs, ideally tagged by date, reporting institution, sector, transaction channel, predicate crime category, and outcome (e.g., disseminated to law-enforcement), and customer gender. Data quality: Duplicate submissions, incomplete narratives, or vague suspicion reasons hamper analysis and inflate reported numbers without real value. Confidentiality constraints: Detailed STR data including customer gender may be restricted.</t>
+          <t>Share of applicants that are approved for a specific product type that take-up the product. This indicator can be viewed together with the product application indicator to allow for a more comprehensive analysis of the demand for financial products. Product categoreis to consider for analysis include: deposits, investments, insurance, credit.</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the volume of Suspiciou transaction reports (STRs) generated, including for MSMEs by the owner's gender? Is there a correlation between the volume of these reports and the composition of the FSP customer base by gender? For example, do FSPs with a higher proportion of women in their customer base report a lower volume of STR? Are there disparities in STR statistics across FSPs with different levels of gender diversity?</t>
+          <t>How do take-up rates vary by gender? Do any genders have higher take-up rates than the overall market average? How do FSPs compare in terms of take-up rates by gender?</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9098,49 +9058,59 @@
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Uptake (account ownership)</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Product type</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Stability, safety and soundness</t>
+          <t>Consumer protection</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>AML/CFT</t>
+          <t>Fair treatment</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Savings</t>
         </is>
       </c>
       <c r="D162">
-        <v>65</v>
+        <v>162</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Systematic reporting to financial intelligence unit/office (FIU)</t>
+          <t>Account closure costs paid by customers</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Number of transactions reported (excluding suspicious transaction reports) to FIU</t>
+          <t>Average customer-paid account closure charges</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>This indicator counts all objective anti-money-laundering (AML) disclosures that reporting institutions file with the FIU other than Suspicious Transaction Reports (STRs)—for example Cash / Large-Value Transaction Reports (CTRs/LCTRs), Cross-Border Currency Reports (CBCRs), Electronic Funds Transfer Reports (EFTIs), and threshold-based filings. Tracking the volume highlights how much potentially risky activity flows through the regulated system, tests the reach and effectiveness of automated monitoring engines, and helps the FIU size analytical workloads and allocate investigative resources. When combined with STR counts and outcome statistics, this indicator offers a comprehensive perspective on the preventive arm of the AML/CFT framework. !- Definitions and concepts: Objective reports: filings triggered automatically when a transaction exceeds a statutory threshold or meets a predefined typology—irrespective of suspicion. Thresholds are set at national level and vary across countries. Reporting entities: all AML-obliged financial institutions. Optional denominator metrics to enable intensity ratios: total transactions processed or number of active customers. !- Data requirements: FIU registry of objective-report filings with unique identifiers. Data-quality variance: Missing customer identifiers or incorrect codes hinder FIU analytics; robust validation routines are essential.</t>
+          <t>This indicator captures the out-of-pocket costs borne by customers when they close their transaction account(s). It focuses on fees directly tied to the closure process (not ongoing usage fees). High averages or wide dispersion can signal unfair fee structures, poor process design (e.g., costly payout rails), or weak disclosures—issues that draw conduct-risk scrutiny and harm inclusion goals. Tracking this metric alongside complaints upheld about closure, time to close, and payout failure/return rates gives a rounded view of off-boarding fairness and efficiency. !- Definitions and concepts: Transaction accounts are broadly defined as an account held with a bank or other authorised and/or regulated service provider (including a non-bank) which can be used to make and receive payments. Transaction accounts can be further differentiated into deposit transaction accounts and e-money accounts. Customer-paid closure charges: amounts debited to the customer because of closure, including: explicit closure fees, final statement/document fees, card/cheque deactivation fees, balance-refund/payout charges (e.g., wire/RTGS, cheque issuance, e-money cash-out), account package early-termination fees, statutory taxes/levies linked to these items, and FX/transfer margins if required to remit funds. Exclusions: regular monthly maintenance already charged prior to the closure request, penalty interest on unrelated lending, and third-party fees not passed through. !- Data requirements: Event log with closure request date and closure completion date; customer ID (deduplicated), number of accounts closed, channel, reason code. Transaction-level fee taxonomy to flag closure-related charges; payout transactions (method, amount, fees, FX). Reversal/waiver flags and timestamps to net back rescinded charges. Recommended charge window: from request date through T+30 days after completion to catch settlement/payout fees. Number of customers who closed at least 1 account in period. !- Limitations and considerations: Attribution: define the fee list upfront to avoid counting routine usage fees; publish the measurement window.</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Are there customer gender disparities in the volume of systematic transaction reports (transactions that are not suspicious but reach regulatory thresholds for reporting) to the FIU, including for MSMEs by the owner's gender? Is there a correlation between the volume of these reports and the composition of the FSP customer base by gender? For example, do FSPs with a higher proportion of women in their customer base report a lower volume of systematic transaction reports, including those involving women? How do FSPs with different levels of gender diversity differ in the patterns of systematic reporting to the FIU?</t>
+          <t>How do relevant FSPs rank in terms of closing costs (from highest to lowest), and does this ranking change when the average is computed by gender? Are women and men equally likely to incur account closure fees, or are there gendered patterns in the types of financial service providers (FSPs) they use that influence the likelihood or amount of such fees? How might account closure costs act as a barrier to financial flexibility or mobility? Are women more likely to avoid formal financial services due to concerns over the cost of exiting the system? Additionally, are FSPs that charge lower or no closure fees more accessible to certain gender groups, and does this vary by geography or provider type?</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -9148,49 +9118,59 @@
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Market development</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Outcomes, Capital markets development</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Transaction type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Stability, safety and soundness</t>
+          <t>Consumer protection</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Credit risk</t>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D163">
-        <v>26</v>
+        <v>389</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Gender composition of loan guarantors</t>
+          <t>Insurance claims (number)</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Gender composition of guarantors in the retail loan portfolio</t>
+          <t>Number of insurance claims</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Measures the representation of different genders among the individuals who act as loan guarantors--pledge to repay a loan if the borrower defaults. It offers a sophisticated lens through which to view credit risk, gender-based economic disparities, and the social dynamics that underpin a loan portfolio. It can reveal hidden concentration risks. For example, if a large portion of a bank's small business loans are guaranteed by the male spouses of female entrepreneurs, the portfolio's risk profile becomes heavily correlated with the financial health and stability of that specific demographic.  This metric also provides insights into the structural barriers different genders face when seeking credit. If the data shows that female borrowers disproportionately require male guarantors (while the reverse is not true), it can signal underlying biases in credit assessment or a disparity in asset ownership. Prudential supervisors may also be interested in finding out whether the different permutations of borrower's and guarantor's gender could relate to loan performance. Conduct supervisors would use it to scrutinize lending practices for fairness and equity.</t>
+          <t>The total count of insurance claims formally submitted by policyholders, beneficiaries, or authorized third parties to an insurer within a defined reporting period, regardless of whether the claims are accepted, rejected, paid, or still under review. Denominator for several key inclusion, consumer protection and prudential insurance ratios. !- Data requirements: Claim identifier, (unique ID per claim), Policyholder identifier, Date of claim submission.</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the representation of loan guarantors? What types of loans and borrowers, across different FSP types, are more likely to show gender disparities in the use of guarantors? Are there disparities in loan performance (NPLs, delinquency, interest income) depending on the gender of the guarantor?</t>
+          <t>How do claim numbers vary by gender? Are there any gender groups logging fewer claims compared to the market average? Are there FSPs with particularly low or high claim numbers for certain genders? How do claim statistics intersect with policy type and customer demographics?</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -9200,57 +9180,57 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Consumer protection</t>
+          <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Fair treatment</t>
+          <t>Usage, Soundness</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Product type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Stability, safety and soundness</t>
+          <t>Consumer protection</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Credit risk</t>
+          <t>Fair treatment</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D164">
-        <v>24</v>
+        <v>390</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Delinquency rate in the loan portfolio</t>
+          <t>Insurance claims paid</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Volume and value of delinquent retail loans as a proportion of total retail portfolio</t>
+          <t>Value of insurance claims paid</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>The delinquency rate tracks the share of consumer loans—mortgages, credit-cards, instalment loans, auto, buy-now-pay-later, qualifying MSMEs—that have fallen past due but have not yet crossed the “non-performing” threshold or been written off. Rising early-stage arrears are an early-warning signal of household stress and of future spikes in non-performing loans (NPLs), provisions and write-offs. Paired with NPL, restructuring and write-off metrics, the delinquency rate provides a forward-looking barometer of retail credit health. Supervisors and risk managers use the metric to test the effectiveness of underwriting standards, consumer disclosure, customer interfaces (for digital loans), and pricing for credit risk. !- Definitions and concepts: Loan delinquency refers to a situation in which borrowed money is not paid back as agreed. A loan becomes delinquent when a borrower misses a regular installment payment. A delinquent loan is any kind of loan that has past due payments but has yet to go into default. On a value basis, this indicator measures the total outstanding balances past due (for example greater than 1 day past due) as a share of gross retail loan balances at the end of a specified period. Operational cut-offs: Inconsistent days past due calculation (calendar days vs. business days, partial payments) hinders cross-lender comparability.</t>
+          <t>"Claims paid" represents the total cash outflow or settled obligations by an insurer to policyholders or beneficiaries for claims events during a reporting period. It includes only claims for which payment has been disbursed, regardless of whether additional claims are still outstanding or whether reserves were previously established. Tracking claims paid helps supervisors monitor liquidity, operational efficiency, and consumer protection outcomes. It provides a concrete measure of the insurer’s fulfillment of contractual obligations and complements other claims indicators (e.g., claims incurred, claims outstanding, unpaid approved claims). !- Data requirements: Claim identifier, (unique ID per claim), Policyholder identifier, Date of claim submission, Date of payment, Amount paid (full or partial), Product / policy type; . !- Limitations and considerations: paid claims may lag claims incurred due to reporting delays or extended claims handling processes; some claims are paid in installments, methodology must specify whether to include full or partial amounts; severe events can cause sudden increases in paid claims, interpretation should consider context. Segmentation by product line or policy type is recommended for supervisory analysis.</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Are there gender disparities (including for MSMEs based on the gender of ownership) in delinquency rates (also considering the number of unpaid installments) for loans of different types, terms and sizes? Do smaller loans have lower delinquency rates and how does this vary across genders? Do FSPs with higher levels of gender diversity present lower delinquency rates?</t>
+          <t>How do claim payments vary by gender? Are there any gender groups receiving fewer/lower payments compared to the market average? Are there FSPs with particularly low or high payment rate for certain genders? How do claim payment statistics intersect with policy type and customer demographics?</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -9260,17 +9240,17 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection</t>
+          <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Outcomes, Suitability</t>
+          <t>Usage, Soundness</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Financial service provider (FSP) type; Financial service provider (FSP) gender diversity; Product type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -9282,35 +9262,35 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Credit risk</t>
+          <t>AML/CFT</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D165">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Non performing loans (NPLs)</t>
+          <t>Suspicious transaction reports</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Non performing loans rate in the retail loan portfolio</t>
+          <t>Number of suspicious transaction reports</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>The NPL indicator for the retail loan portfolio quantifies the share (or absolute value) of consumer and MSME loans that are unlikely to be fully repaid. Because retail credit typically involves high volumes of granular, often unsecured exposures, a build-up of NPLs signals mounting credit risk costs, pressure on provisioning, and potential stress. Supervisors track this metric to assess lenders' underwriting standards, resilience to economic shocks, and the effectiveness of arrears management. !- Definitions and concepts: An NPL is defined as a loan that is past-due for a minimum amount of days (e.g., 90 days). The definition can vary across countries but the Basel Committee has set common standards. The retail portfolio encompasses exposures to individuals and qualifying MSMEs treated under the retail asset class. The most common ratio is Gross NPLs ÷ Gross retail loans. Aggressive charge-offs or “evergreening” can temporarily lower the NPL ratio without improving underlying asset quality. Seasonality and relief measures: Payment holidays or pandemic moratoria may defer delinquencies, masking latent credit risk.</t>
+          <t>The indicator tallies the suspicious transaction reports (STRs)  financial service providers file with the Financial Intelligence Unit (FIU) when they suspect financial crimes such as money-laundering and terrorism financing. A rising count can signal stronger transaction monitoring systems or higher level of potentially criminal activities. Policymakers use STR volumes, in combination with other data (e.g., investigations), to allocate investigative resources. !- Definitions and concepts: Suspicious Transaction Report (STR): a mandatory report filed when a transaction is known, suspected, or has reasonable grounds to be suspected of involving criminal proceeds or terrorist funds (FATF Rec. 20). Reporting entities: broadly, all institutions covered by the AML/CFT law, including all finacial financial service providers. !- Data requirements: FIU registry of incoming STRs, ideally tagged by date, reporting institution, sector, transaction channel, predicate crime category, and outcome (e.g., disseminated to law-enforcement), and customer gender. Data quality: Duplicate submissions, incomplete narratives, or vague suspicion reasons hamper analysis and inflate reported numbers without real value. Confidentiality constraints: Detailed STR data including customer gender may be restricted.</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the rates of non-performing loans (NPL) within retail/MSME portfolios, and how do these differences vary by age, income levels, geographic location, and types of financial service providers? Do women or other gender groups exhibit different patterns of loan repayment and default compared to men, and what factors might explain these variations? How do NPL rates differ across loan types, and are portfolios with higher female borrower participation associated with lower or higher NPL ratios? Are financial service providers with greater gender diversity in their workforce or leadership more effective at managing NPLs equitably across genders? What insights do gender-disaggregated NPL data provide regarding credit risk, financial resilience, and inclusion of vulnerable or underserved gender groups?</t>
+          <t>Are there gender disparities in the volume of Suspiciou transaction reports (STRs) generated, including for MSMEs by the owner's gender? Is there a correlation between the volume of these reports and the composition of the FSP customer base by gender? For example, do FSPs with a higher proportion of women in their customer base report a lower volume of STR? Are there disparities in STR statistics across FSPs with different levels of gender diversity?</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -9318,19 +9298,9 @@
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>Quality, Suitability</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -9342,35 +9312,35 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Credit risk</t>
+          <t>AML/CFT</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D166">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Restructured loans</t>
+          <t>Systematic reporting to financial intelligence unit/office (FIU)</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Volume and value of restructured loans as a proportion of total retail/MSME portfolio</t>
+          <t>Number of transactions reported (excluding suspicious transaction reports) to FIU</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>The restructured loans indicator tracks the portion of a lender's credit portfolio whose contractual terms have been modified to relieve a borrower in financial difficulty—by lowering the interest rate, extending maturity, granting grace periods, converting currency, or partially forgiving principal, or a mix of these. A rising stock signals mounting credit stress, latent loss risk, or even internal frauds or mismagement. While restructurings can help viable borrowers bridge a temporary shock, they may defer recognition of non-performing loans (NPLs). Supervisors watch both the level and the flow of restructurings to detect “ever-greening”. !- Definitions and concepts: Restructured (or renegotiated / forborne) loan: an exposure whose cash-flow terms have been modified for credit risk reasons and would not have been granted under comparable market conditions. Local definitions vary, while standard setting bodies such as the Basel Committe and IFRS have provided common standards. Indicator formula: Restructured loans ÷ Gross loans (stock measure). !- Limitations and considerations: Regulatory divergence: Some jurisdictions treat any concession as a restructuring; others exclude purely administrative changes, hampering cross-country comparisons. Forbearance episodes: Crisis-era moratoria or government-mandated payment holidays may inflate restructuring volumes temporarily, masking true borrower weakness. Portfolio mix effects: High-yield consumer portfolios often show higher restructuring rates than collateralised mortgages; segment analysis is essential.</t>
+          <t>This indicator counts all objective anti-money-laundering (AML) disclosures that reporting institutions file with the FIU other than Suspicious Transaction Reports (STRs)—for example Cash / Large-Value Transaction Reports (CTRs/LCTRs), Cross-Border Currency Reports (CBCRs), Electronic Funds Transfer Reports (EFTIs), and threshold-based filings. Tracking the volume highlights how much potentially risky activity flows through the regulated system, tests the reach and effectiveness of automated monitoring engines, and helps the FIU size analytical workloads and allocate investigative resources. When combined with STR counts and outcome statistics, this indicator offers a comprehensive perspective on the preventive arm of the AML/CFT framework. !- Definitions and concepts: Objective reports: filings triggered automatically when a transaction exceeds a statutory threshold or meets a predefined typology—irrespective of suspicion. Thresholds are set at national level and vary across countries. Reporting entities: all AML-obliged financial institutions. Optional denominator metrics to enable intensity ratios: total transactions processed or number of active customers. !- Data requirements: FIU registry of objective-report filings with unique identifiers. Data-quality variance: Missing customer identifiers or incorrect codes hinder FIU analytics; robust validation routines are essential.</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of restructured loans within retail/MSME loan portfolios, and how do these differences vary by age, income levels, and geographic location? Are women or other gender groups more likely to have loans restructured, potentially reflecting differences in financial vulnerability or repayment capacity? How do patterns of loan restructuring differ across loan types and sectors by gender? Do financial service providers with greater gender diversity in their workforce or leadership demonstrate more equitable practices in loan restructuring across gender groups? What do gender-disaggregated data on restructured loans reveal about the resilience and support available to borrowers facing financial stress?</t>
+          <t>Are there customer gender disparities in the volume of systematic transaction reports (transactions that are not suspicious but reach regulatory thresholds for reporting) to the FIU, including for MSMEs by the owner's gender? Is there a correlation between the volume of these reports and the composition of the FSP customer base by gender? For example, do FSPs with a higher proportion of women in their customer base report a lower volume of systematic transaction reports, including those involving women? How do FSPs with different levels of gender diversity differ in the patterns of systematic reporting to the FIU?</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -9378,19 +9348,9 @@
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>Quality, Suitability</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Transaction type</t>
         </is>
       </c>
     </row>
@@ -9411,26 +9371,31 @@
         </is>
       </c>
       <c r="D167">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Large exposures</t>
+          <t>Gender composition of loan guarantors</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Large exposures as % of total capital</t>
+          <t>Gender composition of guarantors in the retail loan portfolio</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Tracks a lender's credit exposures to single counterparties or groups that exceed a threshold (e.g., a % of capital) and ensures none breach the regulatory cap. !- Definitions and concepts: Exposure includes on- and off-balance-sheet items. !- Data requirements: Counterparty-level exposure data, eligible capital base.</t>
+          <t>Measures the representation of different genders among the individuals who act as loan guarantors--pledge to repay a loan if the borrower defaults. It offers a sophisticated lens through which to view credit risk, gender-based economic disparities, and the social dynamics that underpin a loan portfolio. It can reveal hidden concentration risks. For example, if a large portion of a bank's small business loans are guaranteed by the male spouses of female entrepreneurs, the portfolio's risk profile becomes heavily correlated with the financial health and stability of that specific demographic.  This metric also provides insights into the structural barriers different genders face when seeking credit. If the data shows that female borrowers disproportionately require male guarantors (while the reverse is not true), it can signal underlying biases in credit assessment or a disparity in asset ownership. Prudential supervisors may also be interested in finding out whether the different permutations of borrower's and guarantor's gender could relate to loan performance. Conduct supervisors would use it to scrutinize lending practices for fairness and equity.</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Are higher levels of gender diversity at FSPs and in their customer base correlated with lower levels of large exposures in loan operations? How are large exposures distributed across different products, gender, and locations? Do large exposures show different delinquency and NPL levels based on gender?</t>
+          <t>Are there gender disparities in the representation of loan guarantors? What types of loans and borrowers, across different FSP types, are more likely to show gender disparities in the use of guarantors? Are there disparities in loan performance (NPLs, delinquency, interest income) depending on the gender of the guarantor?</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -9440,12 +9405,12 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Safety and security</t>
+          <t>Fair treatment</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type</t>
+          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Product type</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9422,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Credit risk, Soundness</t>
+          <t>Credit risk</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9466,26 +9431,31 @@
         </is>
       </c>
       <c r="D168">
-        <v>262</v>
+        <v>24</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Write-offs ratio</t>
+          <t>Delinquency rate in the loan portfolio</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Volume and value of written off retail loans as a proportion of retail/MSME portfolio</t>
+          <t>Volume and value of delinquent retail loans as a proportion of total retail portfolio</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>The write-offs ratio tracks the portion of the retail loan portfolio that a lender permanently removes from its balance sheet within a period because collection is deemed impossible or uneconomic. It is a forward-looking credit-risk barometer: rising write-offs shrink the loan book, erode earnings through higher impairment charges, and may reveal weaknesses in underwriting or collections. Supervisors examine the indicator alongside NPL and provisioning coverage to judge whether lenders are recognising losses promptly or postponing them through restructurings. !- Definitions and concepts: Write-offs ratio is usually expressed as (Gross retail loan write-offs during period ÷ Average gross retail loans outstanding). Write-off: an accounting action that derecognises the unrecoverable portion of a loan’s amortised cost. It does not preclude further collections, which are recognised as recoveries. !- Limitations and considerations:  Timing disparities: Institutions with aggressive 180-day charge-off policies show higher ratios than peers that delay write-offs until legal exhaustion, complicating comparisons..</t>
+          <t>The delinquency rate tracks the share of consumer loans—mortgages, credit-cards, instalment loans, auto, buy-now-pay-later, qualifying MSMEs—that have fallen past due but have not yet crossed the “non-performing” threshold or been written off. Rising early-stage arrears are an early-warning signal of household stress and of future spikes in non-performing loans (NPLs), provisions and write-offs. Paired with NPL, restructuring and write-off metrics, the delinquency rate provides a forward-looking barometer of retail credit health. Supervisors and risk managers use the metric to test the effectiveness of underwriting standards, consumer disclosure, customer interfaces (for digital loans), and pricing for credit risk. !- Definitions and concepts: Loan delinquency refers to a situation in which borrowed money is not paid back as agreed. A loan becomes delinquent when a borrower misses a regular installment payment. A delinquent loan is any kind of loan that has past due payments but has yet to go into default. On a value basis, this indicator measures the total outstanding balances past due (for example greater than 1 day past due) as a share of gross retail loan balances at the end of a specified period. Operational cut-offs: Inconsistent days past due calculation (calendar days vs. business days, partial payments) hinders cross-lender comparability.</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the incidence of loan write-offs among retail/MSME borrowers? How do these disparities shift when further disaggregated by age, income, loan size, and geographic location? Do women or other gender groups experience higher or lower write-off rates compared to men, and what factors might explain these patterns? When analyzed in relation to the gender diversity of financial service providers’ leadership or top management, is higher gender diversity associated with more equitable write-off rates across customer genders? What insights do gender-disaggregated write-off data provide about risk assessment, financial inclusion, and borrower resilience?</t>
+          <t>Are there gender disparities (including for MSMEs based on the gender of ownership) in delinquency rates (also considering the number of unpaid installments) for loans of different types, terms and sizes? Do smaller loans have lower delinquency rates and how does this vary across genders? Do FSPs with higher levels of gender diversity present lower delinquency rates?</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -9500,7 +9470,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Customer type; Customer gender; Financial service provider (FSP) type; Financial service provider (FSP) gender diversity; Product type</t>
         </is>
       </c>
     </row>
@@ -9512,7 +9482,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Credit risk, Soundness</t>
+          <t>Credit risk</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9521,26 +9491,26 @@
         </is>
       </c>
       <c r="D169">
-        <v>263</v>
+        <v>22</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Loan loss provisions</t>
+          <t>Non performing loans (NPLs)</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>% of the outstanding loan portfolio set aside as provisions for expected credit losses</t>
+          <t>Non performing loans rate in the retail loan portfolio</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Loan loss provisions (LLPs) are the expenses a lender records to cover expected credit losses on its loan portfolio. They represent management’s best estimate of future cash shortfalls arising from borrower defaults or deteriorating credit quality. Adequate provisioning is critical for portraying true earnings, maintaining solvency, and sustaining market confidence. Monitoring LLP trends alongside non-performing loan inflows, write-offs, and capital ratios provides a holistic view of a bank’s credit-risk resilience and earnings quality. Definitions &amp; concepts: Loan Loss Provision (expense) – the profit-and-loss charge that increases the Allowance for Expected Credit Losses (ECL) on the balance sheet. !- Data requirements: LLP expenses segmented by product, geography, collateral type. Total loan portfolio value.</t>
+          <t>The NPL indicator for the retail loan portfolio quantifies the share (or absolute value) of consumer and MSME loans that are unlikely to be fully repaid. Because retail credit typically involves high volumes of granular, often unsecured exposures, a build-up of NPLs signals mounting credit risk costs, pressure on provisioning, and potential stress. Supervisors track this metric to assess lenders' underwriting standards, resilience to economic shocks, and the effectiveness of arrears management. !- Definitions and concepts: An NPL is defined as a loan that is past-due for a minimum amount of days (e.g., 90 days). The definition can vary across countries but the Basel Committee has set common standards. The retail portfolio encompasses exposures to individuals and qualifying MSMEs treated under the retail asset class. The most common ratio is Gross NPLs ÷ Gross retail loans. Aggressive charge-offs or “evergreening” can temporarily lower the NPL ratio without improving underlying asset quality. Seasonality and relief measures: Payment holidays or pandemic moratoria may defer delinquencies, masking latent credit risk.</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the provisioning level allocated to customers? When disaggregated by other demographics such as age and location, do the observed gender-based differences change? Do vulnerable customers tend to have loans with higher provisioning levels, and are there gender differences in these patterns? When analyzed in relation to the gender diversity of FSPs' top management, is a higher level of gender diversity associated with differences in provisioning levels? And how does this relationship compare when considering gender diversity across other staff levels?</t>
+          <t>Are there gender disparities in the rates of non-performing loans (NPL) within retail/MSME portfolios, and how do these differences vary by age, income levels, geographic location, and types of financial service providers? Do women or other gender groups exhibit different patterns of loan repayment and default compared to men, and what factors might explain these variations? How do NPL rates differ across loan types, and are portfolios with higher female borrower participation associated with lower or higher NPL ratios? Are financial service providers with greater gender diversity in their workforce or leadership more effective at managing NPLs equitably across genders? What insights do gender-disaggregated NPL data provide regarding credit risk, financial resilience, and inclusion of vulnerable or underserved gender groups?</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -9555,12 +9525,12 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Outcomes, Suitability</t>
+          <t>Quality, Suitability</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Product type; Loan size</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -9581,21 +9551,26 @@
         </is>
       </c>
       <c r="D170">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Physical risk in the credit portfolio</t>
+          <t>Restructured loans</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Exposure of the credit portfolio to customers/industries with high physical risk related to climate change</t>
+          <t>Volume and value of restructured loans as a proportion of total retail/MSME portfolio</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>This indicator quantifies how much of the loan book is exposed to climate-related physical risks, specifically. These risks materialize through direct damage to assets, disruptions in business operations, or negative impacts on local economies, all of which can lead to higher rates of loan defaults and losses for the lender. This indicator should complement the all-encompassing indicator that measures climate-related risks (both physical and transition risks). Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, including physical risks, while the NGFS provides a range of additional defintions, including nature-related financial risks.</t>
+          <t>The restructured loans indicator tracks the portion of a lender's credit portfolio whose contractual terms have been modified to relieve a borrower in financial difficulty—by lowering the interest rate, extending maturity, granting grace periods, converting currency, or partially forgiving principal, or a mix of these. A rising stock signals mounting credit stress, latent loss risk, or even internal frauds or mismagement. While restructurings can help viable borrowers bridge a temporary shock, they may defer recognition of non-performing loans (NPLs). Supervisors watch both the level and the flow of restructurings to detect “ever-greening”. !- Definitions and concepts: Restructured (or renegotiated / forborne) loan: an exposure whose cash-flow terms have been modified for credit risk reasons and would not have been granted under comparable market conditions. Local definitions vary, while standard setting bodies such as the Basel Committe and IFRS have provided common standards. Indicator formula: Restructured loans ÷ Gross loans (stock measure). !- Limitations and considerations: Regulatory divergence: Some jurisdictions treat any concession as a restructuring; others exclude purely administrative changes, hampering cross-country comparisons. Forbearance episodes: Crisis-era moratoria or government-mandated payment holidays may inflate restructuring volumes temporarily, masking true borrower weakness. Portfolio mix effects: High-yield consumer portfolios often show higher restructuring rates than collateralised mortgages; segment analysis is essential.</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in the share of restructured loans within retail/MSME loan portfolios, and how do these differences vary by age, income levels, and geographic location? Are women or other gender groups more likely to have loans restructured, potentially reflecting differences in financial vulnerability or repayment capacity? How do patterns of loan restructuring differ across loan types and sectors by gender? Do financial service providers with greater gender diversity in their workforce or leadership demonstrate more equitable practices in loan restructuring across gender groups? What do gender-disaggregated data on restructured loans reveal about the resilience and support available to borrowers facing financial stress?</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -9603,9 +9578,19 @@
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Quality, Suitability</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>Customer gender; Customer type; Financial service provider (FSP) type; Product type; Loan size; Loan term</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -9617,40 +9602,50 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Liquidity risk</t>
+          <t>Credit risk</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D171">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Liquidity ratio</t>
+          <t>Large exposures</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Liquidity ratio</t>
+          <t>Large exposures as % of total capital</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>The liquidity ratio tests whether an entity holds enough high quality liquid assets to survive a 30-day stress scenario. !- Definitions and concepts: definition of liquidity ratios can vary across countries. The Basel Committee has provided definitions for the Liquidity Coverage Ratio and the Net Stable Funding, but many countries use simpler liquidity ratio definitions. For the insurance sector, the International Association of Insurance Supervisors has also proposed liquidity metrics using an exposure approach (Insurance Liquidity Ratio) and a company projection approach (based on cash flows).</t>
+          <t>Tracks a lender's credit exposures to single counterparties or groups that exceed a threshold (e.g., a % of capital) and ensures none breach the regulatory cap. !- Definitions and concepts: Exposure includes on- and off-balance-sheet items. !- Data requirements: Counterparty-level exposure data, eligible capital base.</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>How are FSP gender diversity and the gender composition of the customer base correlated with liquidity risk?</t>
+          <t>Are higher levels of gender diversity at FSPs and in their customer base correlated with lower levels of large exposures in loan operations? How are large exposures distributed across different products, gender, and locations? Do large exposures show different delinquency and NPL levels based on gender?</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Safety and security</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity</t>
+          <t>Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -9662,40 +9657,50 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Market risk</t>
+          <t>Credit risk, Soundness</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Insurance, Pensions, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D172">
-        <v>52</v>
+        <v>262</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Value at Risk (VaR)</t>
+          <t>Write-offs ratio</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Exposure to market risk (value volatility in the trading book)</t>
+          <t>Volume and value of written off retail loans as a proportion of retail/MSME portfolio</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>VaR estimates the maximum potential trading-book loss over a specified horizon at a given confidence level (e.g., one-day 99%). It informs market risk limits and capital requirements for market risk. !- Definitions and concepts: market risk definition and standardized calculations vary across jurisdictions. Standards are provided by international standard setting bodies such as the Basel Committee.</t>
+          <t>The write-offs ratio tracks the portion of the retail loan portfolio that a lender permanently removes from its balance sheet within a period because collection is deemed impossible or uneconomic. It is a forward-looking credit-risk barometer: rising write-offs shrink the loan book, erode earnings through higher impairment charges, and may reveal weaknesses in underwriting or collections. Supervisors examine the indicator alongside NPL and provisioning coverage to judge whether lenders are recognising losses promptly or postponing them through restructurings. !- Definitions and concepts: Write-offs ratio is usually expressed as (Gross retail loan write-offs during period ÷ Average gross retail loans outstanding). Write-off: an accounting action that derecognises the unrecoverable portion of a loan’s amortised cost. It does not preclude further collections, which are recognised as recoveries. !- Limitations and considerations:  Timing disparities: Institutions with aggressive 180-day charge-off policies show higher ratios than peers that delay write-offs until legal exhaustion, complicating comparisons..</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Is there a correlation between higher levels of gender diversity in FSPs and lower risk levels?</t>
+          <t>Are there gender disparities in the incidence of loan write-offs among retail/MSME borrowers? How do these disparities shift when further disaggregated by age, income, loan size, and geographic location? Do women or other gender groups experience higher or lower write-off rates compared to men, and what factors might explain these patterns? When analyzed in relation to the gender diversity of financial service providers’ leadership or top management, is higher gender diversity associated with more equitable write-off rates across customer genders? What insights do gender-disaggregated write-off data provide about risk assessment, financial inclusion, and borrower resilience?</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Outcomes, Suitability</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -9707,35 +9712,40 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Operational risk</t>
+          <t>Credit risk, Soundness</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Payments, Savings</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D173">
-        <v>31</v>
+        <v>263</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Balance of suspense accounts</t>
+          <t>Loan loss provisions</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Value of balances of suspense accounts</t>
+          <t>% of the outstanding loan portfolio set aside as provisions for expected credit losses</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Suspense accounts are temporary holding ledgers used when a transaction cannot be posted to its final customer account because critical details are missing or disputed or due to any technical issues. The balance of suspense accounts aggregates the outstanding debit or credit amounts awaiting resolution. Persistently high or growing balances signal weaknesses in reconciliation, client on-boarding, Know-Your-Customer (KYC) data quality, payment-processing controls, or even internal fraud. Ageing buckets: some regulators require ageing of reported balances (0-30, 31-90, 91-180, &gt;180 days) to identify balances that exceed tolerance windows. !- Limitations and considerations: Accounting practices vary: some institutions clear items by moving them to internal “parking” accounts that may not be labelled suspense, understating the indicator. Standardization is needed to ensure reporting of balances in similar accounts that are not labelled "suspense accounts". Regulatory treatment: in certain jurisdictions, long-dated unresolved credits are treated as unclaimed funds.</t>
+          <t>Loan loss provisions (LLPs) are the expenses a lender records to cover expected credit losses on its loan portfolio. They represent management’s best estimate of future cash shortfalls arising from borrower defaults or deteriorating credit quality. Adequate provisioning is critical for portraying true earnings, maintaining solvency, and sustaining market confidence. Monitoring LLP trends alongside non-performing loan inflows, write-offs, and capital ratios provides a holistic view of a bank’s credit-risk resilience and earnings quality. Definitions &amp; concepts: Loan Loss Provision (expense) – the profit-and-loss charge that increases the Allowance for Expected Credit Losses (ECL) on the balance sheet. !- Data requirements: LLP expenses segmented by product, geography, collateral type. Total loan portfolio value.</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the average amount of funds in suspense accounts, including for low-income customers and MSMEs based on the ownership gender? Are there gender disparities in the distribution of low-income customers with suspense accounts (and for which types of accounts?) compared to the whole customer base? Comparing this indicator with failed transactions and customer losses (if available), are there gender disparities in financial losses after funds remain in suspense or temporary accounts, which could indicate potential internal frauds? Comparing this indicator with FSP gender diversity, does higher gender diversity correlate with lower amounts in suspense accounts or customer losses after funds are temporarily placed in suspense accounts?</t>
+          <t>Are there gender disparities in the provisioning level allocated to customers? When disaggregated by other demographics such as age and location, do the observed gender-based differences change? Do vulnerable customers tend to have loans with higher provisioning levels, and are there gender differences in these patterns? When analyzed in relation to the gender diversity of FSPs' top management, is a higher level of gender diversity associated with differences in provisioning levels? And how does this relationship compare when considering gender diversity across other staff levels?</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -9745,12 +9755,12 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Usage, Suitability</t>
+          <t>Outcomes, Suitability</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Product type; Loan size</t>
         </is>
       </c>
     </row>
@@ -9762,50 +9772,40 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Operational risk</t>
+          <t>Credit risk</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D174">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Incomplete/failed transactions</t>
+          <t>Physical risk in the credit portfolio</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>% of all initiated transactions that are incomplete or failed</t>
+          <t>Exposure of the credit portfolio to customers/industries with high physical risk related to climate change</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Measures the percentage of transactions that users initiate but that do not successfully complete as intended. It's a metric for assessing the reliability, usability, and accessibility of a digital financial service. A high rate of incomplete or failed transactions points to a poor user experience, and may lead to financial loss if funds are temporarily held and not returned. A sudden spike in this indicator can be an early warning of technical problems, cybersecurity attacks, or capacity issues. Incomplete transactions: transactions that are started by the user but are never fully processed to a conclusion. They are often "timed out" or abandoned. Failed transactions: transactions that are fully processed by the system but are ultimately rejected. The system actively returns an error message confirming the failure.</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Do incomplete/failed transactions impact different genders differently, including low-income customers and MSMEs based on the ownership gender? Comparing this indicator with the amount of losses suffered by customers (if available), are there gender disparities in financial losses due to failed transactions? How does this indicator compare with indicators on values maintained in suspense accounts and their variation by gender? Do different types of FSPs and accounts perform differently across the gender in terms of failed transactions? Comparing this indicator with gender diversity, does higher gender diversity correlate with a lower prevalence of failed transactions?</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>Usage, Suitability</t>
+          <t>This indicator quantifies how much of the loan book is exposed to climate-related physical risks, specifically. These risks materialize through direct damage to assets, disruptions in business operations, or negative impacts on local economies, all of which can lead to higher rates of loan defaults and losses for the lender. This indicator should complement the all-encompassing indicator that measures climate-related risks (both physical and transition risks). Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, including physical risks, while the NGFS provides a range of additional defintions, including nature-related financial risks.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Transaction type</t>
+          <t>Customer gender; Customer type; Financial service provider (FSP) type; Product type; Loan size; Loan term</t>
         </is>
       </c>
     </row>
@@ -9817,272 +9817,252 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
+          <t>Liquidity risk</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Investments</t>
+        </is>
+      </c>
+      <c r="D175">
+        <v>110</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Liquidity ratio</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Liquidity ratio</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>The liquidity ratio tests whether an entity holds enough high quality liquid assets to survive a 30-day stress scenario. !- Definitions and concepts: definition of liquidity ratios can vary across countries. The Basel Committee has provided definitions for the Liquidity Coverage Ratio and the Net Stable Funding, but many countries use simpler liquidity ratio definitions. For the insurance sector, the International Association of Insurance Supervisors has also proposed liquidity metrics using an exposure approach (Insurance Liquidity Ratio) and a company projection approach (based on cash flows).</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>How are FSP gender diversity and the gender composition of the customer base correlated with liquidity risk?</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Market risk</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D176">
+        <v>52</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Value at Risk (VaR)</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Exposure to market risk (value volatility in the trading book)</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>VaR estimates the maximum potential trading-book loss over a specified horizon at a given confidence level (e.g., one-day 99%). It informs market risk limits and capital requirements for market risk. !- Definitions and concepts: market risk definition and standardized calculations vary across jurisdictions. Standards are provided by international standard setting bodies such as the Basel Committee.</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Is there a correlation between higher levels of gender diversity in FSPs and lower risk levels?</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
           <t>Operational risk</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Payments, Savings</t>
+        </is>
+      </c>
+      <c r="D177">
+        <v>31</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Balance of suspense accounts</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Value of balances of suspense accounts</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Suspense accounts are temporary holding ledgers used when a transaction cannot be posted to its final customer account because critical details are missing or disputed or due to any technical issues. The balance of suspense accounts aggregates the outstanding debit or credit amounts awaiting resolution. Persistently high or growing balances signal weaknesses in reconciliation, client on-boarding, Know-Your-Customer (KYC) data quality, payment-processing controls, or even internal fraud. Ageing buckets: some regulators require ageing of reported balances (0-30, 31-90, 91-180, &gt;180 days) to identify balances that exceed tolerance windows. !- Limitations and considerations: Accounting practices vary: some institutions clear items by moving them to internal “parking” accounts that may not be labelled suspense, understating the indicator. Standardization is needed to ensure reporting of balances in similar accounts that are not labelled "suspense accounts". Regulatory treatment: in certain jurisdictions, long-dated unresolved credits are treated as unclaimed funds.</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in the average amount of funds in suspense accounts, including for low-income customers and MSMEs based on the ownership gender? Are there gender disparities in the distribution of low-income customers with suspense accounts (and for which types of accounts?) compared to the whole customer base? Comparing this indicator with failed transactions and customer losses (if available), are there gender disparities in financial losses after funds remain in suspense or temporary accounts, which could indicate potential internal frauds? Comparing this indicator with FSP gender diversity, does higher gender diversity correlate with lower amounts in suspense accounts or customer losses after funds are temporarily placed in suspense accounts?</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Usage, Suitability</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
         <is>
           <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
-      <c r="D175">
+      <c r="D178">
+        <v>29</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Incomplete/failed transactions</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>% of all initiated transactions that are incomplete or failed</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Measures the percentage of transactions that users initiate but that do not successfully complete as intended. It's a metric for assessing the reliability, usability, and accessibility of a digital financial service. A high rate of incomplete or failed transactions points to a poor user experience, and may lead to financial loss if funds are temporarily held and not returned. A sudden spike in this indicator can be an early warning of technical problems, cybersecurity attacks, or capacity issues. Incomplete transactions: transactions that are started by the user but are never fully processed to a conclusion. They are often "timed out" or abandoned. Failed transactions: transactions that are fully processed by the system but are ultimately rejected. The system actively returns an error message confirming the failure.</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Do incomplete/failed transactions impact different genders differently, including low-income customers and MSMEs based on the ownership gender? Comparing this indicator with the amount of losses suffered by customers (if available), are there gender disparities in financial losses due to failed transactions? How does this indicator compare with indicators on values maintained in suspense accounts and their variation by gender? Do different types of FSPs and accounts perform differently across the gender in terms of failed transactions? Comparing this indicator with gender diversity, does higher gender diversity correlate with a lower prevalence of failed transactions?</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Usage, Suitability</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Transaction type</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D179">
         <v>106</v>
       </c>
-      <c r="E175" t="inlineStr">
+      <c r="E179" t="inlineStr">
         <is>
           <t>Operational disruption incidents</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
+      <c r="F179" t="inlineStr">
         <is>
           <t>Number of operational disruption incidents</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
+      <c r="G179" t="inlineStr">
         <is>
           <t>This indicator counts and classifies events that interrupt an institution’s ability to deliver financial services—whether due to IT failures, cyber-attacks, power outages, third-party breakdowns, or physical events (e.g., fire, pandemic lockdowns). Regulators track both the frequency and severity (e.g., service-unavailable minutes, customers affected, monetary losses) to judge the resilience of regulated services. A rising trend can erode confidence and expose the system to contagion if multiple firms rely on the same outsourced providers or infrastructure.
 !- Definitions and concepts: Operational disruption incident: an unplanned event that prevents or materially degrades the delivery of a critical business service beyond a defined tolerance. Definitions, including of critical services, vary across countries. Standard setting bodies including the Basel Committee provide standardized definitions that can be used. 
 Impact metrics: duration, peak concurrent users affected, transaction backlog, financial loss, data-integrity impact, customer detriment, others. Root-cause categories: hardware/software failure, cyber-intrusion, third-party outage, human error, environmental event, others. !- Limitations and considerations: Firms may fear reputational damage so there is a risk of under-reporting. Heterogeneous critical-service definitions may be used across firm, so regulatory standardization is needed.</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
+      <c r="H179" t="inlineStr">
         <is>
           <t>How are FSP gender diversity and gender composition of customer base correlated with the frequency of operational disruption incidents?</t>
         </is>
       </c>
-      <c r="J175" t="inlineStr">
+      <c r="J179" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
+      <c r="K179" t="inlineStr">
         <is>
           <t>Quality, Data privacy and protection</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
+      <c r="L179" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity; Transaction type</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Operational risk</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D176">
-        <v>107</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Successful cyber attacks</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Number of successful cyber attacks</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>A measure of the frequency of cyberattacks on regulated financial institutions over a specified period. !- Definitions and concepts: A cyberattack is any intentional effort to steal, expose, alter, disable, or destroy data, applications, or other assets through unauthorized access to a network, computer system or digital device. Cyberattacks can disrupt and damage businesses and often carry high costs, including the costs of discovering and responding to the violation, downtime and lost revenue, and the long-term reputational damage to a business and its brand. Data requirement: Self-reporting of the number of successful cyberattacks by FSPs or data from other parties that track the incidence and severity of cyberattacks.</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Are higher levels of gender diversity at FSPs correlated with the frequency of successful cyber attacks?</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>Outcomes, Safety and security</t>
-        </is>
-      </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type; Transaction type</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Soundness</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D177">
-        <v>122</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Cost of reinsurance</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Premiums ceded to reinsurers as % of gross premium written</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>The cost of reinsurance indicator quantifies the price an insurer pays to transfer part of its underwriting risk to reinsurers. Tracked as either an absolute expense or as a ratio—most often Reinsurance premium ceded ÷ Gross premiums written (GPW)—it shows how much earnings capacity the insurer surrenders for balance-sheet protection. Rising costs may stem from hardening global reinsurance markets, high catastrophe exposures, deteriorating loss experience or weakened credit quality of the insurer. Supervisors and rating agencies watch for excessive reliance on expensive reinsurance cover which can compress margins, while under-spending may leave the insurer over-exposed to shocks. Evaluated over time and in tandem with retention ratios, claims ratio and solvency coverage, the cost of reinsurance reveals whether an insurer’s risk transfer strategy is adequate. !- Definitions and concepts: Reinsurance premium ceded: contractual payments (net of commissions) made to reinsurers for proportional (quota-share, surplus) or non-proportional (excess-of-loss, stop-loss) treaties, booked at treaty inception. Net cost of reinsurance: ceded premium minus ceding commission plus profit-commission adjustments and reinstatement premiums. Timing mismatches: Premiums are typically paid up-front, while recoveries occur post-loss, so annual cost ratios can spike in growth years and dip after large events.</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>How do FSPs’ gender diversity and the gender composition of their customer base correlate with the costs incurred from reinsurance? Are there gendered patterns in how reinsurance expenses impact insurers and their customers?</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>Quality, Suitability</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Soundness</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D178">
-        <v>56</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Insurance claims (loss) ratio</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>% of total premium income paid out as claims</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>The claims paid ratio compares the amount of benefits and claims an insurer actually disburses during a period with the premium income it records for the same portfolio. It answers a basic question for supervisors, policy-holders, and analysts: How much of each premium dollar flows back to customers in the form of claims? Persistently low ratios may flag overly aggressive pricing, onerous exclusions, or servicing bottlenecks, while very high ratios can foreshadow reserve inadequacy, under-pricing, or a spike in catastrophe losses. In combination with the expense ratio, the indicator feeds into the overall loss or combined ratio that underpins solvency and profitability assessments. !- Definitions and concepts: Claims paid: cash actually settled with policy-holders and claimants in the accounting period, including partial payments and salvage recoveries netted where local GAAP allows. It excludes outstanding claims reserves and IBNR, which are captured by “claims incurred.” Gross vs. net basis: gross claims ignore reinsurance recoveries; net claims deduct them, better reflecting the insurer’s retained risk. Segmented ratios (e.g., motor, health, property) pinpoint product-level profitability. !- Data requirements: Extracts from the claims-management system showing paid amounts, dates, line of business, and reinsurance cessions. Premium registers (written or earned, depending on supervisory preference) reconciled to the general ledger. Catastrophe tags, legal-settlement flags, and large-loss registers to isolate one-off distortions. Limitations &amp; considerations: Timing mismatch: annual premiums are often received up-front, whereas claim payments can lag; using earned premiums mitigates, but does not eliminate, this distortion. Claims-handling practices: delayed settlement or dispute escalation depresses the ratio without improving true risk experience. Reinsurance structure: quota-share vs. excess-of-loss treaties change the net ratio dramatically; analysts should review both gross and net perspectives. Regulatory definitions: some jurisdictions fold surrenders of savings-type contracts into claims, inflating comparability. Trend analysis should therefore pair the claims paid ratio with claims-incurred and reserve-adequacy metrics, catastrophe-loss disclosures, and expense dynamics to obtain a holistic view of underwriting performance and solvency resilience.</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in claims ratios for insurance products, including for MSMEs based on the owner's gender? Are excessively low claims ratios correlated with low premiums (a proxy for targeting lower-income segments)? Are women more likely to be targeted by products with low claims ratios, potentially indicating lower-value offerings? Are FSPs with higher levels of gender diversity less likely to have excessively low claims ratios for insurance sold to vulnerable segments, such as women and women-owned MSMEs? When comparing with coverage ratios (amount of claims paid relative to the claim value), how do gender disparities in coverage ratios compare with claims paid?</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>Usage, Suitability</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Soundness</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D179">
-        <v>8</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Insurance claims incurred</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Value of insurance claims incurred</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>“Claims incurred” represents the total cost an insurer recognises for claims events during a reporting period, regardless of whether they have been paid yet. Tracking the level and trend of incurred claims helps supervisors monitor the financial health of insurers such as by detecting emerging risk clusters (e.g., climate-driven catastrophes). !- Definitions and concepts: Claims incurred = Claims paid + Change in outstanding claims reserves + Change in IBNR (incurred-but-not-reported) reserves ± Claims-handling expense reserve movements. !- Data requirements: Total claims incurred.  !- Limitations and considerations: Catastrophe volatility: Single severe events cause spikes. Used alongside premium growth, claims-ratio components, and reserve-adequacy studies, “claims incurred” provides a cornerstone view of underwriting performance and balance-sheet resilience.</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>How has the participation of different genders in incurred insurance claims evolved over time, both for individuals and MSMEs by owner’s gender? Are there gender differences in the types of claims incurred? How does the level of gender diversity within FSPs relate to these patterns?</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>Quality, Suitability</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -10094,231 +10074,271 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D180">
+        <v>107</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Successful cyber attacks</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Number of successful cyber attacks</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>A measure of the frequency of cyberattacks on regulated financial institutions over a specified period. !- Definitions and concepts: A cyberattack is any intentional effort to steal, expose, alter, disable, or destroy data, applications, or other assets through unauthorized access to a network, computer system or digital device. Cyberattacks can disrupt and damage businesses and often carry high costs, including the costs of discovering and responding to the violation, downtime and lost revenue, and the long-term reputational damage to a business and its brand. Data requirement: Self-reporting of the number of successful cyberattacks by FSPs or data from other parties that track the incidence and severity of cyberattacks.</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Are higher levels of gender diversity at FSPs correlated with the frequency of successful cyber attacks?</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Outcomes, Safety and security</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type; Transaction type</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
           <t>Soundness</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D180">
+      <c r="D181">
+        <v>122</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Cost of reinsurance</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Premiums ceded to reinsurers as % of gross premium written</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>The cost of reinsurance indicator quantifies the price an insurer pays to transfer part of its underwriting risk to reinsurers. Tracked as either an absolute expense or as a ratio—most often Reinsurance premium ceded ÷ Gross premiums written (GPW)—it shows how much earnings capacity the insurer surrenders for balance-sheet protection. Rising costs may stem from hardening global reinsurance markets, high catastrophe exposures, deteriorating loss experience or weakened credit quality of the insurer. Supervisors and rating agencies watch for excessive reliance on expensive reinsurance cover which can compress margins, while under-spending may leave the insurer over-exposed to shocks. Evaluated over time and in tandem with retention ratios, claims ratio and solvency coverage, the cost of reinsurance reveals whether an insurer’s risk transfer strategy is adequate. !- Definitions and concepts: Reinsurance premium ceded: contractual payments (net of commissions) made to reinsurers for proportional (quota-share, surplus) or non-proportional (excess-of-loss, stop-loss) treaties, booked at treaty inception. Net cost of reinsurance: ceded premium minus ceding commission plus profit-commission adjustments and reinstatement premiums. Timing mismatches: Premiums are typically paid up-front, while recoveries occur post-loss, so annual cost ratios can spike in growth years and dip after large events.</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>How do FSPs’ gender diversity and the gender composition of their customer base correlate with the costs incurred from reinsurance? Are there gendered patterns in how reinsurance expenses impact insurers and their customers?</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Quality, Suitability</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Soundness</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D182">
+        <v>56</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Insurance claims (loss) ratio</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>% of total premium income paid out as claims</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>The claims paid ratio compares the amount of benefits and claims an insurer actually disburses during a period with the premium income it records for the same portfolio. It answers a basic question for supervisors, policy-holders, and analysts: How much of each premium dollar flows back to customers in the form of claims? Persistently low ratios may flag overly aggressive pricing, onerous exclusions, or servicing bottlenecks, while very high ratios can foreshadow reserve inadequacy, under-pricing, or a spike in catastrophe losses. In combination with the expense ratio, the indicator feeds into the overall loss or combined ratio that underpins solvency and profitability assessments. !- Definitions and concepts: Claims paid: cash actually settled with policy-holders and claimants in the accounting period, including partial payments and salvage recoveries netted where local GAAP allows. It excludes outstanding claims reserves and IBNR, which are captured by “claims incurred.” Gross vs. net basis: gross claims ignore reinsurance recoveries; net claims deduct them, better reflecting the insurer’s retained risk. Segmented ratios (e.g., motor, health, property) pinpoint product-level profitability. !- Data requirements: Extracts from the claims-management system showing paid amounts, dates, line of business, and reinsurance cessions. Premium registers (written or earned, depending on supervisory preference) reconciled to the general ledger. Catastrophe tags, legal-settlement flags, and large-loss registers to isolate one-off distortions. Limitations &amp; considerations: Timing mismatch: annual premiums are often received up-front, whereas claim payments can lag; using earned premiums mitigates, but does not eliminate, this distortion. Claims-handling practices: delayed settlement or dispute escalation depresses the ratio without improving true risk experience. Reinsurance structure: quota-share vs. excess-of-loss treaties change the net ratio dramatically; analysts should review both gross and net perspectives. Regulatory definitions: some jurisdictions fold surrenders of savings-type contracts into claims, inflating comparability. Trend analysis should therefore pair the claims paid ratio with claims-incurred and reserve-adequacy metrics, catastrophe-loss disclosures, and expense dynamics to obtain a holistic view of underwriting performance and solvency resilience.</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in claims ratios for insurance products, including for MSMEs based on the owner's gender? Are excessively low claims ratios correlated with low premiums (a proxy for targeting lower-income segments)? Are women more likely to be targeted by products with low claims ratios, potentially indicating lower-value offerings? Are FSPs with higher levels of gender diversity less likely to have excessively low claims ratios for insurance sold to vulnerable segments, such as women and women-owned MSMEs? When comparing with coverage ratios (amount of claims paid relative to the claim value), how do gender disparities in coverage ratios compare with claims paid?</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Usage, Suitability</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Soundness</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D183">
+        <v>8</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Insurance claims incurred</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Value of insurance claims incurred</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>“Claims incurred” represents the total cost an insurer recognises for claims events during a reporting period, regardless of whether they have been paid yet. Tracking the level and trend of incurred claims helps supervisors monitor the financial health of insurers such as by detecting emerging risk clusters (e.g., climate-driven catastrophes). !- Definitions and concepts: Claims incurred = Claims paid + Change in outstanding claims reserves + Change in IBNR (incurred-but-not-reported) reserves ± Claims-handling expense reserve movements. !- Data requirements: Total claims incurred.  !- Limitations and considerations: Catastrophe volatility: Single severe events cause spikes. Used alongside premium growth, claims-ratio components, and reserve-adequacy studies, “claims incurred” provides a cornerstone view of underwriting performance and balance-sheet resilience.</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>How has the participation of different genders in incurred insurance claims evolved over time, both for individuals and MSMEs by owner’s gender? Are there gender differences in the types of claims incurred? How does the level of gender diversity within FSPs relate to these patterns?</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Quality, Suitability</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Soundness</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D184">
         <v>57</v>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="E184" t="inlineStr">
         <is>
           <t>Insurance policy renewal (persistency) ratio</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>% of all policies up for renewal that are renewed</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
+      <c r="G184" t="inlineStr">
         <is>
           <t>The renewal- or persistency-ratio gauges the proportion of in-force insurance policies (or premium) that remain active after a specified period—typically the 13th, 25th, or 61st month following issuance. High persistency signals strong customer satisfaction, effective servicing, and accurate underwriting assumptions; it underpins stable cash-flow projections, lowers acquisition-cost amortisation strain, and enhances embedded value. Conversely, rapid lapses may expose product-design weaknesses or mis-selling. Supervisors review persistency alongside surrender-value payouts and complaint levels to detect conduct risk and solvency concerns. !- Definitions and concepts: Persistency ratio (policy-count basis) = Policies renewed at month t / Policies eligible for renewal at month t
 Premium-weighted persistency uses renewal premium divided by original premium to capture face-amount shifts. Cohort vs. calendar method: Cohort traces a single issue-year block through time; calendar aggregates all cohorts renewing in a given period. !- Limitations and considerations: Measurement horizon: 13-month persistency suits annual-premium life products; short-tailed general-insurance policies need annual or shorter retention ratios. Channel mix: Bancassurance and digital pathways often show different lapse behaviours—segment analysis is essential.</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
+      <c r="H184" t="inlineStr">
         <is>
           <t>Are there gender disparities in insurance policy renewal rates, including among MSMEs by owner gender? Do certain policy types have lower renewal rates among specific gender groups? Could these differences signal mismatches between products and customer needs, posing strategic risks for insurers?</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr">
+      <c r="J184" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="K184" t="inlineStr">
         <is>
           <t>Quality, Suitability</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
+      <c r="L184" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Soundness</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D181">
-        <v>114</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Risk retention ratio (dependency on reinsurance)</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>% of gross written premium that is net (as a measure of the level of dependency on reinsurance)</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Also known as the net retention ratio, this indicator shows the proportion of insurance risk an insurer keeps on its own balance sheet after ceding portions to reinsurers. It is usually expressed as Net premiums written ÷ Gross premiums written. A high ratio signals greater self-reliance (and potentially higher earnings volatility), while a low ratio points to heavy dependence on reinsurance, which may reduce earnings swings but create counter-party risks. Supervisors monitor the metric to ensure that ceded volumes are commensurate with the insurer’s capital strength, product mix, and risk appetite. !- Definitions and concepts: Gross premiums written (GPW): Total premium income before reinsurance ceded. Net premiums written (NPW): GPW minus premiums ceded plus reinsurance recoveries on ceded unearned premiums. !- Data requirements: Line-of-business breakdown of GPW and NPW for the period. Details of outward reinsurance treaties. Counter-party concentration: high concentration risk may offset the benefits of resinsurance.</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>What is the relationship between FSP gender diversity, customer gender composition, and the degree of dependency on reinsurance? Are there gender-based patterns in insurers’ risk retention strategies?</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Soundness</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D182">
-        <v>115</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Technical provisions</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Level of technical provisions to cover actuarial liabilities</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>Technical provisions represent the present-value estimate of all future cash outflows that an insurer expects to incur on written policies, including claims not yet reported (IBNR), claims reported but not settled, and future policyholder benefits. Adequate provisions are the cornerstone of insurance solvency and a key indicator for prudential supervisors. Definitions &amp; concepts: Technical provisions comprise two main blocks: Best-Estimate Liabilities (BEL), the probability-weighted expected value of future cash flows (claims, benefits, expenses) discounted using risk-free or prescribed curves; and Risk Margins, an additional amount reflecting the cost of holding capital to run off the liabilities (Solvency II) or a prudential margin (IFRS 17, LAT).</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in the adequacy of technical provisions maintained by FSPs? How do FSPs with higher gender diversity in management and governance compare in maintaining technical provisions that fairly reflect risks associated with serving diverse gender groups? Are provisions sufficiently accounting for potential differences in claims or defaults related to gender segments in the portfolio?</t>
-        </is>
-      </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Soundness</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D183">
-        <v>127</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Physical risk in the insurance portfolio</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>Exposure of the insurance portfolio to written policies to physical risk related to climate change</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Metric used to quantify an insurer's financial exposure to losses caused by the direct physical impacts of climate change. This includes both event-driven acute risks and longer-term chronic risks. This indicator is essential for measuring an insurer's vulnerability to climate-related claims, which can impact its profitability, solvency, and ability to provide affordable coverage. Hence, it is an important metric for prudential supervisors from the perspective of capital adequacy, solvency and risk management. Definitions and concepts of climate-related risks vary across countries. The NGFS provides a range of additional defintions, including nature-related financial risks.</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>How do FSP gender diversity and customer gender composition correlate with exposure to climate-related physical risks in insurance portfolios? Are there gender disparities in financial risk exposure due to climate impacts, including among MSMEs by owner gender?</t>
-        </is>
-      </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Soundness</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Investments</t>
-        </is>
-      </c>
-      <c r="D184">
-        <v>108</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Capital adequacy ratio (CAR)</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>Total regulatory capital relative as % of risk weighted assets (RWAs)</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>Capital Adequacy Rario (CAR) shows the total qualifying capital relative to risk-weighted assets (RWA). It captures the full loss-absorbing cushion. !-Definitions and concepts: Capital tiers to include in the CAR formula are provided by the Basel Capital Accords and adapted in each jurisdiction. !- Data requirements: Full breakdown of regulatory capital components, and total RWA. For the insurance sector, the equivalent is the Solvency Ratio calculated as own funds divided by the minimum capital that insurers are required to hold to cover unexpected losses.</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>How are FSP gender diversity and the gender composition of the customer base correlated with CAR levels?</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity</t>
         </is>
       </c>
     </row>
@@ -10335,35 +10355,35 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D185">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Tier 1 capital ratio</t>
+          <t>Risk retention ratio (dependency on reinsurance)</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tier 1 regulatory capital as % of risk weighted assets (RWAs)</t>
+          <t>% of gross written premium that is net (as a measure of the level of dependency on reinsurance)</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>The Tier 1 ratio shows the core loss-absorbing capital relative to risk-weighted assets (RWA). It is a cornerstone of the Basel Capital Accords and a trigger point for supervisory intervention. !- Definitions and concepts: Tier 1 capital comprises common equity tier 1 (CET1) plus additional tier 1 (perpetual, non-cumulative instruments). RWA adjust asset values for credit, market, and operational risk weights. Local definitions vary, but the Basel Committee has provided common standards.</t>
+          <t>Also known as the net retention ratio, this indicator shows the proportion of insurance risk an insurer keeps on its own balance sheet after ceding portions to reinsurers. It is usually expressed as Net premiums written ÷ Gross premiums written. A high ratio signals greater self-reliance (and potentially higher earnings volatility), while a low ratio points to heavy dependence on reinsurance, which may reduce earnings swings but create counter-party risks. Supervisors monitor the metric to ensure that ceded volumes are commensurate with the insurer’s capital strength, product mix, and risk appetite. !- Definitions and concepts: Gross premiums written (GPW): Total premium income before reinsurance ceded. Net premiums written (NPW): GPW minus premiums ceded plus reinsurance recoveries on ceded unearned premiums. !- Data requirements: Line-of-business breakdown of GPW and NPW for the period. Details of outward reinsurance treaties. Counter-party concentration: high concentration risk may offset the benefits of resinsurance.</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Do FSPs with greater gender diversity in leadership and customer base tend to maintain stronger Tier 1 capital ratios? Is there any evidence that gender-inclusive governance correlates with improved capital adequacy and financial resilience? How might gender-related risk factors influence the calculation or management of Tier 1 capital?</t>
+          <t>What is the relationship between FSP gender diversity, customer gender composition, and the degree of dependency on reinsurance? Are there gender-based patterns in insurers’ risk retention strategies?</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -10380,35 +10400,35 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D186">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Interest margin ratio</t>
+          <t>Technical provisions</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Net interest income as % of total earning assets</t>
+          <t>Level of technical provisions to cover actuarial liabilities</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Also known as Net Interest Margin (NIM), is a metric that measures a lender's profitability by calculating difference between the interest it earns on its assets (like loans) and the interest it pays on liabilities, divided by the total earning assets. !- Definitions and concepts: NIM = (Net Interest income – Interest expense) ÷ Average earning assets. !- Data requirements: Total interest income, total interest expenses, total earning assets.</t>
+          <t>Technical provisions represent the present-value estimate of all future cash outflows that an insurer expects to incur on written policies, including claims not yet reported (IBNR), claims reported but not settled, and future policyholder benefits. Adequate provisions are the cornerstone of insurance solvency and a key indicator for prudential supervisors. Definitions &amp; concepts: Technical provisions comprise two main blocks: Best-Estimate Liabilities (BEL), the probability-weighted expected value of future cash flows (claims, benefits, expenses) discounted using risk-free or prescribed curves; and Risk Margins, an additional amount reflecting the cost of holding capital to run off the liabilities (Solvency II) or a prudential margin (IFRS 17, LAT).</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Do financial service providers (FSPs) with higher gender diversity in leadership or governance report different interest margin ratios compared to less gender‑diverse peers? Are there associations between the gender composition of the customer base (e.g. share of women borrowers/depositors) and margin outcomes? Could gendered pricing—such as differential rates offered to male vs. female clients—impact FSP interest margins? Over time, do changes in margin ratios correlate with shifts in gender inclusion (e.g. more women customers or staff)?</t>
+          <t>Are there gender disparities in the adequacy of technical provisions maintained by FSPs? How do FSPs with higher gender diversity in management and governance compare in maintaining technical provisions that fairly reflect risks associated with serving diverse gender groups? Are provisions sufficiently accounting for potential differences in claims or defaults related to gender segments in the portfolio?</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -10429,41 +10449,31 @@
         </is>
       </c>
       <c r="D187">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Insurance premiums written</t>
+          <t>Physical risk in the insurance portfolio</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Value of insurance premiums writen in the insurance sector</t>
+          <t>Exposure of the insurance portfolio to written policies to physical risk related to climate change</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Premiums written represent the contractual revenue an insurer books when it underwrites new or renewal policies during a given period, irrespective of when coverage is provided or cash is received. Rising written-premium volumes can indicate growth, improved pricing power, or inflation-driven sum-assured increases; declining volumes may flag competitive pressures or tighter underwriting standards. !- Definitions and concepts: Gross premiums written (GPW): All premiums on policies incepted or renewed during the period before ceding to reinsurers. Net premiums written (NPW): GPW minus premiums ceded plus any reinsurance assumed—reflects the risk the insurer retains. Earned premiums: Portion of written premiums recognised as revenue in proportion to expired coverage—crucial for claims-ratio analysis. !- Data requirements: total premium written. For granular data: Policy-level underwriting feeds: issue/renewal dates, premium amounts, payment mode, product line, distribution channel, currency.</t>
+          <t>Metric used to quantify an insurer's financial exposure to losses caused by the direct physical impacts of climate change. This includes both event-driven acute risks and longer-term chronic risks. This indicator is essential for measuring an insurer's vulnerability to climate-related claims, which can impact its profitability, solvency, and ability to provide affordable coverage. Hence, it is an important metric for prudential supervisors from the perspective of capital adequacy, solvency and risk management. Definitions and concepts of climate-related risks vary across countries. The NGFS provides a range of additional defintions, including nature-related financial risks.</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>How do insurance premiums written vary by gender of the policyholder, including for individuals and MSMEs based on owner gender? Are there gender disparities in the types and values of insurance products purchased, reflected in premiums collected? Do women or other gender groups pay systematically higher or lower premiums, and what might this indicate about risk assessment or product suitability? How do FSPs with higher gender diversity compare in the total premiums written to different gender segments? Are trends in premiums written by gender evolving over time, and do these trends vary by product type or geographic region?</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>Outcomes</t>
+          <t>How do FSP gender diversity and customer gender composition correlate with exposure to climate-related physical risks in insurance portfolios? Are there gender disparities in financial risk exposure due to climate impacts, including among MSMEs by owner gender?</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -10480,35 +10490,35 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Payments, Savings, Credit, Insurance, Investments</t>
         </is>
       </c>
       <c r="D188">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Efficiency ratio</t>
+          <t>Capital adequacy ratio (CAR)</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Effciency ratio</t>
+          <t>Total regulatory capital relative as % of risk weighted assets (RWAs)</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Indicates operating efficiency by comparing non-interest expenses to operating income. Lower ratios signal better cost control, a key driver of sustainable profitability, especially in low-margin environments. Definitions &amp; concepts – Efficiency Ratio = Operating expenses ÷ (Net interest income + Non-interest income). Some variants exclude litigation or restructuring charges. !- Data requirements: Detailed income statement with breakdowns of personnel, IT, and occupancy costs; segment reporting helps pinpoint inefficiencies. !- Limitations and considerations: Cost cuts that impair risk management or customer service may improve the ratio temporarily but raise long-run risks. Cross-country comparisons should adjust for labour cost levels and digitalisation stages. One-off income (e.g., asset sales) can distort the denominator.</t>
+          <t>Capital Adequacy Rario (CAR) shows the total qualifying capital relative to risk-weighted assets (RWA). It captures the full loss-absorbing cushion. !-Definitions and concepts: Capital tiers to include in the CAR formula are provided by the Basel Capital Accords and adapted in each jurisdiction. !- Data requirements: Full breakdown of regulatory capital components, and total RWA. For the insurance sector, the equivalent is the Solvency Ratio calculated as own funds divided by the minimum capital that insurers are required to hold to cover unexpected losses.</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Are there gender-related differences in the efficiency of FSP operations, for example, in cost-to-income ratios? Do FSPs with more gender-diverse teams or client bases demonstrate better operational efficiency? How do gender dynamics in product design, customer service, and outreach impact overall institutional efficiency?</t>
+          <t>How are FSP gender diversity and the gender composition of the customer base correlated with CAR levels?</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity</t>
         </is>
       </c>
     </row>
@@ -10529,31 +10539,31 @@
         </is>
       </c>
       <c r="D189">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Personnel expenses per customer/contract</t>
+          <t>Tier 1 capital ratio</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Total personnel expenses per customer or contract</t>
+          <t>Tier 1 regulatory capital as % of risk weighted assets (RWAs)</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>This indicator measures the total cost of personnel (wages, salaries, benefits, etc.) divided by the total number of customers a financial service provider serves, revealing how much is spent on staff to support each individual customer. This metric helps assess a company's operational efficiency and cost-effectiveness in managing its customer base, with a lower figure typically indicating better efficiency.</t>
+          <t>The Tier 1 ratio shows the core loss-absorbing capital relative to risk-weighted assets (RWA). It is a cornerstone of the Basel Capital Accords and a trigger point for supervisory intervention. !- Definitions and concepts: Tier 1 capital comprises common equity tier 1 (CET1) plus additional tier 1 (perpetual, non-cumulative instruments). RWA adjust asset values for credit, market, and operational risk weights. Local definitions vary, but the Basel Committee has provided common standards.</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Is there a gender dimension in personnel cost efficiency—that is, do FSPs with more balanced or female‑inclusive staff structures show lower personnel expenses per customer or contract? Are personnel expense ratios correlated with the gender composition of staff and how services are delivered to different gender groups? Do FSPs serving a higher proportion of women customers incur different per-customer personnel costs (e.g. due to agent outreach, financial literacy support)? How does this metric evolve over time in relation to efforts to promote gender inclusion in staffing and service models?</t>
+          <t>Do FSPs with greater gender diversity in leadership and customer base tend to maintain stronger Tier 1 capital ratios? Is there any evidence that gender-inclusive governance correlates with improved capital adequacy and financial resilience? How might gender-related risk factors influence the calculation or management of Tier 1 capital?</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -10570,35 +10580,35 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D190">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>ROA</t>
+          <t>Interest margin ratio</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Return on assets</t>
+          <t>Net interest income as % of total earning assets</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>ROA gauges how efficiently a financial service provider turns every unit of assets under its control into net profit. !- Definitions and concepts: ROA = Net income after tax ÷ Average total assets (opening + closing assets ÷ 2). !- Data requirements: net income and total assets at two balance-sheet dates, preferably quarterly to smooth seasonality. !- Limitations and considerations: ROA ignores off-balance-sheet exposures such as guarantees or derivatives.</t>
+          <t>Also known as Net Interest Margin (NIM), is a metric that measures a lender's profitability by calculating difference between the interest it earns on its assets (like loans) and the interest it pays on liabilities, divided by the total earning assets. !- Definitions and concepts: NIM = (Net Interest income – Interest expense) ÷ Average earning assets. !- Data requirements: Total interest income, total interest expenses, total earning assets.</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Do FSPs with greater gender diversity in their workforce, management, or boards tend to achieve higher or more stable ROA? Is there evidence that the gender composition of the customer base (e.g. more female clients) affects asset returns, for instance through differences in risk, lending, or deposit behaviors? When comparing across FSPs, does ROA differ systematically in institutions with stronger gender inclusion strategies? How have ROA trends shifted over time relative to changes in gender diversity (staffing or customer composition)?</t>
+          <t>Do financial service providers (FSPs) with higher gender diversity in leadership or governance report different interest margin ratios compared to less gender‑diverse peers? Are there associations between the gender composition of the customer base (e.g. share of women borrowers/depositors) and margin outcomes? Could gendered pricing—such as differential rates offered to male vs. female clients—impact FSP interest margins? Over time, do changes in margin ratios correlate with shifts in gender inclusion (e.g. more women customers or staff)?</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -10610,40 +10620,50 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Soundness, Credit risk</t>
+          <t>Soundness</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D191">
-        <v>116</v>
+        <v>7</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>ROE</t>
+          <t>Insurance premiums written</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Return on equity</t>
+          <t>Value of insurance premiums writen in the insurance sector</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>ROE indicates the earnings available to common shareholders per unit of book equity. !- Definitions and concepts: ROE = Net income ÷ Average shareholders’ equity. !- Data requirements: Consolidated net income and shareholders’ equity.</t>
+          <t>Premiums written represent the contractual revenue an insurer books when it underwrites new or renewal policies during a given period, irrespective of when coverage is provided or cash is received. Rising written-premium volumes can indicate growth, improved pricing power, or inflation-driven sum-assured increases; declining volumes may flag competitive pressures or tighter underwriting standards. !- Definitions and concepts: Gross premiums written (GPW): All premiums on policies incepted or renewed during the period before ceding to reinsurers. Net premiums written (NPW): GPW minus premiums ceded plus any reinsurance assumed—reflects the risk the insurer retains. Earned premiums: Portion of written premiums recognised as revenue in proportion to expired coverage—crucial for claims-ratio analysis. !- Data requirements: total premium written. For granular data: Policy-level underwriting feeds: issue/renewal dates, premium amounts, payment mode, product line, distribution channel, currency.</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Is there a relationship between gender diversity in leadership or equity ownership and ROE performance across FSPs? Are FSPs that prioritize gender inclusion more likely to achieve higher equity returns, possibly through broader market reach or more balanced risk management? How does the gender mix of customers, especially depositors and borrowers, relate to ROE outcomes? Over time, do improvements in gender inclusion (in staffing or customer base) precede or follow changes in ROE?</t>
+          <t>How do insurance premiums written vary by gender of the policyholder, including for individuals and MSMEs based on owner gender? Are there gender disparities in the types and values of insurance products purchased, reflected in premiums collected? Do women or other gender groups pay systematically higher or lower premiums, and what might this indicate about risk assessment or product suitability? How do FSPs with higher gender diversity compare in the total premiums written to different gender segments? Are trends in premiums written by gender evolving over time, and do these trends vary by product type or geographic region?</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Outcomes</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -10655,50 +10675,40 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Credit risk</t>
+          <t>Soundness</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D192">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Financial system credit operations</t>
+          <t>Efficiency ratio</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Volume and value of credit operations in the total financial sector portfolio</t>
+          <t>Effciency ratio</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>This indicator captures the breadth of formal lending with two perspectives: the number of credit contracts (volume) and their aggregate outstanding balance (value) across all regulated lenders. Tracking it offers a panoramic view of credit provision, enabling supervisors to (i) gauge financial deepening, (ii) assess systemic leverage of the banking sector, (iii) monitor shifts in portfolio composition (e.g., rise of consumer or MSME lending), and (iv) feed macro-prudential stress tests and monetary policy models. Sharp expansions may indicate rapid financial inclusion or overheating; contractions can herald credit crunches that dampen growth. !- Definitions and concepts: Credit operation – any legally binding loan, line of credit, hire-purchase, lease, or other. Off-balance-sheet commitments (e.g., undrawn credit lines, guarantees) are usually excluded or reported separately. Volume (count): unique credit contracts outstanding at the reporting date; renewals/extensions count as new operations if a fresh contract is signed. Segmentation by sector (household, corporate, government), product type, currency, and residual maturity enriches analysis. !- Data requirements: Supervisory returns or call-reports detailing credit operations contract count by institution and product. Standardised product and sector taxononies to avoid double counting.</t>
+          <t>Indicates operating efficiency by comparing non-interest expenses to operating income. Lower ratios signal better cost control, a key driver of sustainable profitability, especially in low-margin environments. Definitions &amp; concepts – Efficiency Ratio = Operating expenses ÷ (Net interest income + Non-interest income). Some variants exclude litigation or restructuring charges. !- Data requirements: Detailed income statement with breakdowns of personnel, IT, and occupancy costs; segment reporting helps pinpoint inefficiencies. !- Limitations and considerations: Cost cuts that impair risk management or customer service may improve the ratio temporarily but raise long-run risks. Cross-country comparisons should adjust for labour cost levels and digitalisation stages. One-off income (e.g., asset sales) can distort the denominator.</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>How does the gender composition of borrowers in the total financial sector credit portfolio compare across the number and value of outstanding credit operations? Are there gender disparities in both the frequency (number) of credit operations and the total credit amounts extended? How do these disparities vary by loan type, sector, or borrower demographics such as age, income, and location? Are women or other gender groups underrepresented in certain types of credit or regions within the overall portfolio? How do FSPs with higher levels of gender diversity compare in terms of the balance and number of credit operations granted to different genders? Are portfolios with more balanced gender representation associated with differences in credit performance, such as lower default rates or more stable repayment patterns?</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>Usage</t>
+          <t>Are there gender-related differences in the efficiency of FSP operations, for example, in cost-to-income ratios? Do FSPs with more gender-diverse teams or client bases demonstrate better operational efficiency? How do gender dynamics in product design, customer service, and outreach impact overall institutional efficiency?</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -10710,74 +10720,264 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
+          <t>Soundness</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D193">
+        <v>123</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Personnel expenses per customer/contract</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Total personnel expenses per customer or contract</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>This indicator measures the total cost of personnel (wages, salaries, benefits, etc.) divided by the total number of customers a financial service provider serves, revealing how much is spent on staff to support each individual customer. This metric helps assess a company's operational efficiency and cost-effectiveness in managing its customer base, with a lower figure typically indicating better efficiency.</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Is there a gender dimension in personnel cost efficiency—that is, do FSPs with more balanced or female‑inclusive staff structures show lower personnel expenses per customer or contract? Are personnel expense ratios correlated with the gender composition of staff and how services are delivered to different gender groups? Do FSPs serving a higher proportion of women customers incur different per-customer personnel costs (e.g. due to agent outreach, financial literacy support)? How does this metric evolve over time in relation to efforts to promote gender inclusion in staffing and service models?</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Soundness</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D194">
+        <v>117</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>ROA</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Return on assets</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>ROA gauges how efficiently a financial service provider turns every unit of assets under its control into net profit. !- Definitions and concepts: ROA = Net income after tax ÷ Average total assets (opening + closing assets ÷ 2). !- Data requirements: net income and total assets at two balance-sheet dates, preferably quarterly to smooth seasonality. !- Limitations and considerations: ROA ignores off-balance-sheet exposures such as guarantees or derivatives.</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Do FSPs with greater gender diversity in their workforce, management, or boards tend to achieve higher or more stable ROA? Is there evidence that the gender composition of the customer base (e.g. more female clients) affects asset returns, for instance through differences in risk, lending, or deposit behaviors? When comparing across FSPs, does ROA differ systematically in institutions with stronger gender inclusion strategies? How have ROA trends shifted over time relative to changes in gender diversity (staffing or customer composition)?</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Soundness, Credit risk</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D195">
+        <v>116</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>ROE</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Return on equity</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>ROE indicates the earnings available to common shareholders per unit of book equity. !- Definitions and concepts: ROE = Net income ÷ Average shareholders’ equity. !- Data requirements: Consolidated net income and shareholders’ equity.</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Is there a relationship between gender diversity in leadership or equity ownership and ROE performance across FSPs? Are FSPs that prioritize gender inclusion more likely to achieve higher equity returns, possibly through broader market reach or more balanced risk management? How does the gender mix of customers, especially depositors and borrowers, relate to ROE outcomes? Over time, do improvements in gender inclusion (in staffing or customer base) precede or follow changes in ROE?</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Credit risk</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="D196">
+        <v>6</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Financial system credit operations</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Volume and value of credit operations in the total financial sector portfolio</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>This indicator captures the breadth of formal lending with two perspectives: the number of credit contracts (volume) and their aggregate outstanding balance (value) across all regulated lenders. Tracking it offers a panoramic view of credit provision, enabling supervisors to (i) gauge financial deepening, (ii) assess systemic leverage of the banking sector, (iii) monitor shifts in portfolio composition (e.g., rise of consumer or MSME lending), and (iv) feed macro-prudential stress tests and monetary policy models. Sharp expansions may indicate rapid financial inclusion or overheating; contractions can herald credit crunches that dampen growth. !- Definitions and concepts: Credit operation – any legally binding loan, line of credit, hire-purchase, lease, or other. Off-balance-sheet commitments (e.g., undrawn credit lines, guarantees) are usually excluded or reported separately. Volume (count): unique credit contracts outstanding at the reporting date; renewals/extensions count as new operations if a fresh contract is signed. Segmentation by sector (household, corporate, government), product type, currency, and residual maturity enriches analysis. !- Data requirements: Supervisory returns or call-reports detailing credit operations contract count by institution and product. Standardised product and sector taxononies to avoid double counting.</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>How does the gender composition of borrowers in the total financial sector credit portfolio compare across the number and value of outstanding credit operations? Are there gender disparities in both the frequency (number) of credit operations and the total credit amounts extended? How do these disparities vary by loan type, sector, or borrower demographics such as age, income, and location? Are women or other gender groups underrepresented in certain types of credit or regions within the overall portfolio? How do FSPs with higher levels of gender diversity compare in terms of the balance and number of credit operations granted to different genders? Are portfolios with more balanced gender representation associated with differences in credit performance, such as lower default rates or more stable repayment patterns?</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
           <t>Liquidity risk</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
+      <c r="C197" t="inlineStr">
         <is>
           <t>Savings</t>
         </is>
       </c>
-      <c r="D193">
+      <c r="D197">
         <v>17</v>
       </c>
-      <c r="E193" t="inlineStr">
+      <c r="E197" t="inlineStr">
         <is>
           <t>Deposit stability/volatility</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
+      <c r="F197" t="inlineStr">
         <is>
           <t>Stability/volatility of retail deposits (deposit stickness, deposit stability, deposit flows)</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
+      <c r="G197" t="inlineStr">
         <is>
           <t>The deposit stability (or deposit-volatility) indicator assesses how predictable an FSP's funding base is by tracking the fluctuation and “stickiness” of customer deposits over time. Sudden, correlated outflows—whether triggered by market rumours, rate competition or digital bank runs—can force a bank to liquidate assets at fire-sale prices or draw on emergency facilities. Prudential supervisors monitor deposit volatility alongside liquidity ratios to judge an institution’s ability to withstand funding shocks and to calibrate run-off assumptions in stress tests and the Liquidity Coverage Ratio (LCR). Definitions &amp; concepts: Core / stable deposits: retail balances judged unlikely to flee under stress; often defined by balance size, relationship depth, and whether the account is transactional rather than rate-sensitive. Volatility metrics: standard deviation of daily balances divided by the mean (coefficient of variation), maximum one-day net outflow over a look-back window, or elasticity (beta) to market rates. Calculation methods vary across countries. !- Data requirements: High-frequency (daily or intraday) deposit-balance time series, tagged by customer type, product, and currency. Interest-rate history to estimate betas. Customer identifiers for relationship tenure, cross-selling, and concentration analysis. 
 Digital channel dynamics: mobile app withdrawals can accelerate run speed beyond historical norms; backward-looking volatility measures may understate future risk.</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
+      <c r="H197" t="inlineStr">
         <is>
           <t>Are there gender disparities in deposit stability or volatility, and do accounts held by different gender groups show distinct patterns in the frequency or magnitude of balance fluctuations? Could these differences reflect varying income regularity, saving habits, or financial resilience? How do these patterns vary across age, income level, or geographic location? Are there notable differences in deposit stability between FSPs with higher or lower levels of gender diversity in their customer base? Do FSPs with greater gender diversity among their clients tend to experience greater deposit stickiness overall?</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
+      <c r="L197" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
+    <row r="198">
+      <c r="A198" t="inlineStr">
         <is>
           <t>Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="B198" t="inlineStr">
         <is>
           <t>Soundness</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
+      <c r="C198" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D194">
+      <c r="D198">
         <v>392</v>
       </c>
-      <c r="E194" t="inlineStr">
+      <c r="E198" t="inlineStr">
         <is>
           <t>Combined ratio</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
+      <c r="F198" t="inlineStr">
         <is>
           <t>% of total premium income used in paying expenses and claims</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
+      <c r="G198" t="inlineStr">
         <is>
           <t>The combined ratio is a key measure of underwriting profitability in the insurance industry. It indicates the proportion of each unit of premium earned that an insurer uses to cover claims-related losses and operating expenses. A combined ratio below 100% signals an underwriting profit, meaning the insurer is collecting more in premiums than it pays out in claims and expenses, while a ratio above 100% indicates an underwriting loss. This indicator is widely used by insurance supervisors as an early warning signal for assessing the financial health and operational efficiency of insurers, and it supports prudential oversight by helping to identify companies that may be underpricing risk or operating with excessive costs. Monitoring this indicator over time and across different types of insurers can reveal structural patterns in the sustainability of insurance business models and inform supervisory responses.
 !-Definitions and concepts: The combined ratio is calculated as the sum of two components: the loss ratio and the expense ratio. The loss ratio measures claims-related costs (incurred losses plus loss adjustment expenses) as a proportion of earned premiums. The expense ratio measures underwriting and administrative expenses (such as commissions, salaries, and other operational costs) as a proportion of earned or written premiums. The general formula is: Combined Ratio = Loss Ratio + Expense Ratio, or equivalently, Combined Ratio = (Incurred Losses + Loss Adjustment Expenses + Underwriting Expenses) / Earned Premiums. Earned premiums refer to the portion of written premiums corresponding to the coverage period that has elapsed, ensuring proper matching between income recognized and associated claims obligations. A combined ratio of exactly 100% represents the break-even point for underwriting operations.
@@ -10786,36 +10986,36 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
+    <row r="199">
+      <c r="A199" t="inlineStr">
         <is>
           <t>Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B199" t="inlineStr">
         <is>
           <t>Soundness</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
+      <c r="C199" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D195">
+      <c r="D199">
         <v>394</v>
       </c>
-      <c r="E195" t="inlineStr">
+      <c r="E199" t="inlineStr">
         <is>
           <t>Expense ratio</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>% of earned premiums that an insurance company spends on underwriting and administrative expenses (excluding claims)</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
+      <c r="G199" t="inlineStr">
         <is>
           <t>The expense ratio measures the proportion of earned premiums that an insurance company spends on underwriting and administrative expenses, excluding claims-related costs. It is a key indicator of operational efficiency, reflecting how effectively an insurer manages the costs associated with acquiring, underwriting, and servicing insurance policies. Financial sector authorities use this indicator to assess whether insurers are operating within sustainable cost structures and to identify potential inefficiencies that could affect policyholder value or long-term solvency. Together with the loss ratio, the expense ratio is one of the two components of the combined ratio, providing a complementary view that isolates operational cost management from claims experience. Monitoring the expense ratio across providers and over time can help supervisors detect trends in market competitiveness, evaluate the impact of new distribution models (such as digital or agent-based channels) on cost structures, and assess whether high acquisition or administrative costs may be eroding the value delivered to policyholders.
 !-Definitions and concepts: The expense ratio is calculated by dividing total underwriting and administrative expenses by premiums for a given reporting period. The formula is: Expense Ratio (%) = (Underwriting and Administrative Expenses / Premiums) × 100. Underwriting and administrative expenses typically include acquisition costs (such as agent and broker commissions, marketing expenses, and premium taxes), as well as operational costs associated with policy administration, underwriting staff salaries, technology, licensing fees, and general overhead. These expenses exclude claims payments and loss adjustment expenses, which are captured separately in the loss ratio. An important distinction exists in the choice of denominator: under statutory accounting conventions, the expense ratio often uses written premiums, since acquisition costs are recognized at the time a policy is written rather than spread over its duration. Under other accounting frameworks, earned premiums may be used. This difference can affect comparability across jurisdictions and should be noted when interpreting the ratio.
@@ -10824,231 +11024,6 @@
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Sustainability</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Climate and environmental objectives</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D196">
-        <v>330</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Rural credit (volume)</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>Number of loans in the retail loan portfolio designated as rural credit</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector, such as the volume of loans disbursed as a % of the total loan portfolio. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis.</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in participation in the rural credit portfolio, when measured by number of loans and disaggregated by loan type and type of borrower (individual or MSME)? Are these disparities more pronounced in certain types of financial service providers or geographic regions? Do FSPs with higher levels of gender diversity tend to allocate a greater share of loan volume to rural women or women-led MSMEs? Does the proportion of rural credit within the total number of loans granted to women differ significantly from that of men, and what does this reveal about access to credit by gender and location?</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>Usage</t>
-        </is>
-      </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Sustainability</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Climate and environmental objectives</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D197">
-        <v>124</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Climate and other environmental risk in the credit portfolio</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>Exposure of the credit portfolio to customers or industries with high climate (physical and transition risks) and other environmental risk</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>This indicator quantifies how much of the loan book is exposed to climate-related risks (physical and transition) and broader environmental risks (e.g., water stress, biodiversity loss, pollution). It helps firms and supervisors judge vulnerability to asset impairment, collateral devaluation, cash-flow shocks, and regulatory change. It also informs pricing, sector limits, and strategic portfolio alignment. Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, while the NGFS provides a range of additional defintions, including nature-related financial risks.</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>How is FSP gender diversity and the gender composition of the customer base correlated with climate-related financial risks (physical and transition) and other environmental risks?</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>Credit risk, Stability</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Sustainability</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Climate and environmental objectives</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D198">
-        <v>130</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Exposure to polluting firms/industries</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>Number of loans and total exposure of the credit portfolio to pollutting firms/industries</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>This indicator quantifies how much of the loan book is exposed to borrowers classified as big polluters (e.g., fossil fuel industry). The definition of polluting borrowers or activity varies widely across countries and the indicator should be aligned with national definitions. The EU uses a range of similar indicators: https://www.ecb.europa.eu/stats/all-key-statistics/horizontal-indicators/sustainability-indicators/data/html/ecb.climate_indicators_carbon_emissions.en.html</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>How is FSP gender diversity correlated with lending to high polluters?</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>Credit risk, Stability</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Sustainability</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Climate and environmental objectives</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D199">
-        <v>129</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Financed emissions (Carbon footprint of credit portfolio)</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>Contribution of the financial sector to emissions (debtor's emissions financed by the financial sector via loan and securities portfolios)</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>This indicator, also known as carbon footprint, quantifies how much carbon emission the loan book is financing, by estimating the carbon emissions of financed activities and clients. The standardized calculations of emissions vary across countries and the indicator should align with national practices. In the EU, ther financed emissions (FE) indicator provides information on the financing of high-emitting economic activities. It tracks the amount of total carbon emissions from non-financial corporations (borrowers) that can be linked to funding from financial institutions, based on a set of identifiable securities and loan portfolios. See https://www.ecb.europa.eu/stats/all-key-statistics/horizontal-indicators/sustainability-indicators/data/html/ecb.climate_indicators_carbon_emissions.en.html</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>How is FSP gender diversity correlated with financed emissions of the loan and securities portfolio?</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>Credit risk, Stability</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
@@ -11066,26 +11041,31 @@
         </is>
       </c>
       <c r="D200">
-        <v>21</v>
+        <v>330</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Green/sustainable loans</t>
+          <t>Rural credit (volume)</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>% of all loans labelled as green or sustainable</t>
+          <t>Number of loans in the retail loan portfolio designated as rural credit</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>This indicator shows the share of a regulated lender’s aggregate loan book that is formally designated green, social, or sustainable. A higher percentage signals that credit is being channelled toward activities aligned with climate-transition and inclusive-growth objectives, helping regulators gauge progress against national or international sustainable-finance targets and identify institutions with elevated exposure to taxonomy-related reputation or compliance risks. The indicator is an input for green-asset-ratio disclosures and climate-stress-testing frameworks. !- Definitions and concepts: definition of green / sustainable loan varies widely across countries and should align with local frameworks. !- Data requirements: Loan-level tagging for use-of-proceeds or sustainability-performance targets, mapped to the applicable taxonomy code. Up-to-date balances to build the numerator and denominator. Dynamic criteria: Ongoing revisions to reference taxonomies may reclassify loans ex-post, creating series breaks.</t>
+          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector, such as the volume of loans disbursed as a % of the total loan portfolio. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis.</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Are there gender, location, and income disparities in access to green and sustainable loans, including those aimed at climate adaptation and resilience? How do these disparities intersect with factors such as age and sector of activity? Are women or other gender groups underrepresented among borrowers of green loans, and what barriers might contribute to this? Do financial service providers with higher levels of gender diversity tend to have relatively larger and more inclusive green/sustainable loan portfolios? How do repayment patterns and loan terms for green loans differ by gender, and what implications do these have for promoting equitable access to climate finance?</t>
+          <t>Are there gender disparities in participation in the rural credit portfolio, when measured by number of loans and disaggregated by loan type and type of borrower (individual or MSME)? Are these disparities more pronounced in certain types of financial service providers or geographic regions? Do FSPs with higher levels of gender diversity tend to allocate a greater share of loan volume to rural women or women-led MSMEs? Does the proportion of rural credit within the total number of loans granted to women differ significantly from that of men, and what does this reveal about access to credit by gender and location?</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -11095,7 +11075,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Uptake (account ownership)</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -11121,46 +11101,41 @@
         </is>
       </c>
       <c r="D201">
-        <v>331</v>
+        <v>124</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Rural credit (outstanding balance)</t>
+          <t>Climate and other environmental risk in the credit portfolio</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>% of the total retail loan portfolio that is rural credit based on outstanding balance</t>
+          <t>Exposure of the credit portfolio to customers or industries with high climate (physical and transition risks) and other environmental risk</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis. !- Data requirements: Loan account level data, with details on date of disbursements, size of loan, payment schedule and repayments to date. Loan-level detail should have an existing agricultural classification or description of loan to enable classification.</t>
+          <t>This indicator quantifies how much of the loan book is exposed to climate-related risks (physical and transition) and broader environmental risks (e.g., water stress, biodiversity loss, pollution). It helps firms and supervisors judge vulnerability to asset impairment, collateral devaluation, cash-flow shocks, and regulatory change. It also informs pricing, sector limits, and strategic portfolio alignment. Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, while the NGFS provides a range of additional defintions, including nature-related financial risks.</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of the outstanding retail loan portfolio held by rural borrowers, disaggregated by gender and type of borrower? Are these disparities more significant in specific regions or FSP types? Do rural women hold a lower share of outstanding balances, and could this reflect differences in loan size, duration, or repayment behavior? How does the share of rural credit within the total outstanding credit held by women compare to that of men, and what does it suggest about the gendered distribution of long-term credit in rural areas?</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>How is FSP gender diversity and the gender composition of the customer base correlated with climate-related financial risks (physical and transition) and other environmental risks?</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Uptake (account ownership)</t>
+          <t>Credit risk, Stability</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -11181,46 +11156,41 @@
         </is>
       </c>
       <c r="D202">
-        <v>332</v>
+        <v>130</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Rural credit (principal disbursed)</t>
+          <t>Exposure to polluting firms/industries</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>% of the total retail loan portfolio that is rural credit based on principal disbursed</t>
+          <t>Number of loans and total exposure of the credit portfolio to pollutting firms/industries</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis. !- Data requirements: Loan account level data, with details on date of disbursements, size of loan, payment schedule and repayments to date. Loan-level detail should have an existing agricultural classification or description of loan to enable classification.</t>
+          <t>This indicator quantifies how much of the loan book is exposed to borrowers classified as big polluters (e.g., fossil fuel industry). The definition of polluting borrowers or activity varies widely across countries and the indicator should be aligned with national definitions. The EU uses a range of similar indicators: https://www.ecb.europa.eu/stats/all-key-statistics/horizontal-indicators/sustainability-indicators/data/html/ecb.climate_indicators_carbon_emissions.en.html</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the value of new rural credit disbursed to borrowers, disaggregated by gender and borrower type? Are these disparities more evident in certain regions or financial service providers, particularly among those with less gender diversity? Do women in rural areas systematically receive smaller disbursements compared to men in similar loan categories or activities? Does the share of rural credit within the total disbursed credit to women differ significantly from that of men, and what does it indicate about access to productive credit for rural women? Has the share of credit disbursed to rural women changed over time in proportion to their role in the rural economy?</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>How is FSP gender diversity correlated with lending to high polluters?</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>Credit risk, Stability</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -11237,45 +11207,45 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D203">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Green/sustainable insurance</t>
+          <t>Financed emissions (Carbon footprint of credit portfolio)</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>% of all insurance policies that are green or sustainable</t>
+          <t>Contribution of the financial sector to emissions (debtor's emissions financed by the financial sector via loan and securities portfolios)</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>This indicator shows the share of an insurer's aggregate policy portfolio that is formally designated green, social, or sustainable. A higher percentage signals that insurance being channelled toward activities aligned with climate-transition and inclusive-growth objectives (e.g., crop insurance for agroforestry), helping regulators gauge progress against national or international sustainable-finance targets. !- Definitions and concepts: definition of green / sustainable insurance varies widely across countries and should align with local frameworks. !- Data requirements: Policy-level tagging for sustainability-performance targets, mapped to the applicable taxonomy code.</t>
+          <t>This indicator, also known as carbon footprint, quantifies how much carbon emission the loan book is financing, by estimating the carbon emissions of financed activities and clients. The standardized calculations of emissions vary across countries and the indicator should align with national practices. In the EU, ther financed emissions (FE) indicator provides information on the financing of high-emitting economic activities. It tracks the amount of total carbon emissions from non-financial corporations (borrowers) that can be linked to funding from financial institutions, based on a set of identifiable securities and loan portfolios. See https://www.ecb.europa.eu/stats/all-key-statistics/horizontal-indicators/sustainability-indicators/data/html/ecb.climate_indicators_carbon_emissions.en.html</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Are there disparities by gender, income, and location in the likelihood of acquiring green or sustainable insurance products, including climate resilience coverage? Are certain gender groups underserved in this market? Do financial service providers (FSPs) with higher levels of gender diversity tend to maintain larger or more diverse green/sustainable insurance portfolios?</t>
+          <t>How is FSP gender diversity correlated with financed emissions of the loan and securities portfolio?</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>Credit risk, Stability</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -11292,35 +11262,45 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D204">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Holdings of green/sustainable bonds</t>
+          <t>Green/sustainable loans</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Volume (holdings) and value (amount outstanding) of sustainable/green bonds</t>
+          <t>% of all loans labelled as green or sustainable</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>The indicator measures the aggregate value and volume of green and/or sustainability bonds held by investors, reflecting capital directed towards projects and activities with positive environmental or social impacts. It is a measure of sustainable finance. The definition of sustainable or green bond varies widely across countries and the indicator should align with local practices. An example of definition is provided by the Green Bond Principles (GBP), by the International Capital Markets Association (ICMA) https://www.icmagroup.org/sustainable-finance/the-principles-guidelines-and-handbooks/green-bond-principles-gbp/</t>
+          <t>This indicator shows the share of a regulated lender’s aggregate loan book that is formally designated green, social, or sustainable. A higher percentage signals that credit is being channelled toward activities aligned with climate-transition and inclusive-growth objectives, helping regulators gauge progress against national or international sustainable-finance targets and identify institutions with elevated exposure to taxonomy-related reputation or compliance risks. The indicator is an input for green-asset-ratio disclosures and climate-stress-testing frameworks. !- Definitions and concepts: definition of green / sustainable loan varies widely across countries and should align with local frameworks. !- Data requirements: Loan-level tagging for use-of-proceeds or sustainability-performance targets, mapped to the applicable taxonomy code. Up-to-date balances to build the numerator and denominator. Dynamic criteria: Ongoing revisions to reference taxonomies may reclassify loans ex-post, creating series breaks.</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the acquisition/holding of green/sustainable bonds? Are FSPs with higher levels of gender diversity more likely to distribute sustainable or green bonds to a more diverse investor base?  Comparing this with gender diversity at FSPs, are institutions with higher levels of gender diversity more likely to have larger green/sustainable portfolios?</t>
+          <t>Are there gender, location, and income disparities in access to green and sustainable loans, including those aimed at climate adaptation and resilience? How do these disparities intersect with factors such as age and sector of activity? Are women or other gender groups underrepresented among borrowers of green loans, and what barriers might contribute to this? Do financial service providers with higher levels of gender diversity tend to have relatively larger and more inclusive green/sustainable loan portfolios? How do repayment patterns and loan terms for green loans differ by gender, and what implications do these have for promoting equitable access to climate finance?</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Uptake (account ownership)</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -11337,30 +11317,35 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D205">
-        <v>40</v>
+        <v>331</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Issuances of green/sustainable bonds</t>
+          <t>Rural credit (outstanding balance)</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Volume (issuances) and value (amount outstanding) of sustainable/green bonds</t>
+          <t>% of the total retail loan portfolio that is rural credit based on outstanding balance</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>This indicator tracks the number and, more commonly, the face value (in USD, EUR or local currency) of bonds labelled green, social, sustainability or sustainability-linked that reach primary markets in a given period. By capturing how much fresh capital is being channelled explicitly toward environmentally and/or socially beneficial projects, it offers a tangible gauge of the financial sector’s contribution to the transition to a low-carbon, inclusive economy. Policymakers use the series to monitor progress against climate-finance targets, assess the effectiveness of incentives such as tax exemptions or regulatory relief, and spot market slow-downs that could jeopardise net-zero pathways. The definition of sustainable or green bond varies widely across countries and the indicator should align with local practices. An example of definition is provided by the Green Bond Principles (GBP), by the International Capital Markets Association (ICMA) https://www.icmagroup.org/sustainable-finance/the-principles-guidelines-and-handbooks/green-bond-principles-gbp/</t>
+          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis. !- Data requirements: Loan account level data, with details on date of disbursements, size of loan, payment schedule and repayments to date. Loan-level detail should have an existing agricultural classification or description of loan to enable classification.</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Do companies with higher levels of gender diversity issue more green bonds? Are FSPs with higher levels of gender diversity more likely to distribute sustainable or green bonds?</t>
+          <t>Are there gender disparities in the share of the outstanding retail loan portfolio held by rural borrowers, disaggregated by gender and type of borrower? Are these disparities more significant in specific regions or FSP types? Do rural women hold a lower share of outstanding balances, and could this reflect differences in loan size, duration, or repayment behavior? How does the share of rural credit within the total outstanding credit held by women compare to that of men, and what does it suggest about the gendered distribution of long-term credit in rural areas?</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -11370,7 +11355,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>Uptake (account ownership)</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -11392,45 +11377,50 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Savings, Credit, Insurance, Pensions</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D206">
-        <v>126</v>
+        <v>332</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Climate and other environmental risks in the investment portoflio</t>
+          <t>Rural credit (principal disbursed)</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Exposure of the investment portfolio to industries with high climate and other environmental risks</t>
+          <t>% of the total retail loan portfolio that is rural credit based on principal disbursed</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>This indicator quantifies how much of the investment book is exposed to climate-related risks (physical and transition) and broader environmental risks (e.g., water stress, biodiversity loss, pollution). It helps firms and supervisors judge vulnerability to asset impairment and regulatory change. Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, while the NGFS provides a range of additional definitions, including nature-related financial risks.</t>
+          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis. !- Data requirements: Loan account level data, with details on date of disbursements, size of loan, payment schedule and repayments to date. Loan-level detail should have an existing agricultural classification or description of loan to enable classification.</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>How is FSP gender diversity correlated with climate-related financial risks and other environmental risks arising from the investment portfolio of insurers and banks?</t>
+          <t>Are there gender disparities in the value of new rural credit disbursed to borrowers, disaggregated by gender and borrower type? Are these disparities more evident in certain regions or financial service providers, particularly among those with less gender diversity? Do women in rural areas systematically receive smaller disbursements compared to men in similar loan categories or activities? Does the share of rural credit within the total disbursed credit to women differ significantly from that of men, and what does it indicate about access to productive credit for rural women? Has the share of credit disbursed to rural women changed over time in proportion to their role in the rural economy?</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>Stability, safety and soundness</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Market risk, Credit risk</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -11442,40 +11432,50 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Gender equality</t>
+          <t>Climate and environmental objectives</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D207">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Gender diversity at FSP (by reference workforce group)</t>
+          <t>Green/sustainable insurance</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Gender composition of FSP workforce by level of responsibility (Board, management, staff)</t>
+          <t>% of all insurance policies that are green or sustainable</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Measure used to assess the representation of different genders within a financial institution. It serves as a critical tool for evaluating a firm's commitment to inclusivity and is increasingly correlated with enhanced financial performance, risk management, and innovation. This indicator is not a single metric but a suite of measurements that can be applied across various levels of an organization. Ideally, it would be calculated at the board level, the senior management level (C suite), and the staff level. In some occasions, it can also be useful to calculate it for specific roles within the financial institution, such as branch managers, or agents, when analyzing differences in performance related to specific issues, such as consumer protection and conduct issues. In addition to being useful to monitor diversity at the system level, and its alignment with national gender equality policies, this indicator can also be used by prudential and conduct supervisors, as a growing body of knowledge points to improved financial and conduct performance of financial institutions that have a greater level of diversity. For prudential supervisors, this indicator serves as a valuable proxy for assessing a firm's health, as greater gender diversity is often correlated with stronger corporate governance, more prudent risk management, and enhanced financial stability.</t>
+          <t>This indicator shows the share of an insurer's aggregate policy portfolio that is formally designated green, social, or sustainable. A higher percentage signals that insurance being channelled toward activities aligned with climate-transition and inclusive-growth objectives (e.g., crop insurance for agroforestry), helping regulators gauge progress against national or international sustainable-finance targets. !- Definitions and concepts: definition of green / sustainable insurance varies widely across countries and should align with local frameworks. !- Data requirements: Policy-level tagging for sustainability-performance targets, mapped to the applicable taxonomy code.</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Are there gender disparities in workforce participation across different types of FSPs? At what responsibility levels? How does gender diversity in FSP management correlate with key financial indicators (e.g., Stability, Financial Inclusion, Customer Protection, Sustainability)? Comparing with climate-related financial data (e.g., green loan portfolios, green insurance), does gender diversity in FSPs correlate with the growth of these portfolios? If legal or regulatory gender equity requirements exist for FSPs, are they being met? Does gender diversity correlate with variations in supervisory risk scores? How does gender diversity correlate with staff turnover (if data is available)? How does gender diversity correlate with enforcement and other supervisory actions?</t>
+          <t>Are there disparities by gender, income, and location in the likelihood of acquiring green or sustainable insurance products, including climate resilience coverage? Are certain gender groups underserved in this market? Do financial service providers (FSPs) with higher levels of gender diversity tend to maintain larger or more diverse green/sustainable insurance portfolios?</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Usage</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -11487,40 +11487,40 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Gender equality</t>
+          <t>Climate and environmental objectives</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="D208">
-        <v>341</v>
+        <v>41</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Gender diversity of customer base</t>
+          <t>Holdings of green/sustainable bonds</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Gender composition of FSP customer base</t>
+          <t>Volume (holdings) and value (amount outstanding) of sustainable/green bonds</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Measures the representation of different genders—women, men, and non-binary individuals—among a financial institution's clients. This metric provides insights into a firm's market reach, product inclusiveness, and potential exposure to social and economic trends. This indicator can be used to monitor implementaton of gender equality targets and national policies, but also by prudential and conduct supervisors, to compare performance in other metrics, such as basic consumer risk indicators and prudential risk indicators, with the level of gender diversity of the customer base, with the purpose of finding any possible correlation.</t>
+          <t>The indicator measures the aggregate value and volume of green and/or sustainability bonds held by investors, reflecting capital directed towards projects and activities with positive environmental or social impacts. It is a measure of sustainable finance. The definition of sustainable or green bond varies widely across countries and the indicator should align with local practices. An example of definition is provided by the Green Bond Principles (GBP), by the International Capital Markets Association (ICMA) https://www.icmagroup.org/sustainable-finance/the-principles-guidelines-and-handbooks/green-bond-principles-gbp/</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Are there significant gender disparities in the composition of customers across different types of financial service providers (FSPs)? How does the gender diversity of the FSP customer base vary by institution size, sector, and geographic region? What correlations exist between the gender diversity of the customer base and key financial inclusion metrics such as account ownership, loan uptake, and insurance coverage? How does greater gender diversity among customers relate to customer protection outcomes, including complaint resolution and fair treatment? Are FSPs with more gender-diverse customer bases also demonstrating stronger prudential performance and sustainability indicators? How do gender disparities in the customer base influencefinancila outcomes such as Financial Health? And broader social and economic outcomes, such as women's economic empowerment, MSME growth, climate change, jobs creation or poverty reduction?</t>
+          <t>Are there gender disparities in the acquisition/holding of green/sustainable bonds? Are FSPs with higher levels of gender diversity more likely to distribute sustainable or green bonds to a more diverse investor base?  Comparing this with gender diversity at FSPs, are institutions with higher levels of gender diversity more likely to have larger green/sustainable portfolios?</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -11532,40 +11532,50 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Gender equality</t>
+          <t>Climate and environmental objectives</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="D209">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Gender pay gap at FSPs</t>
+          <t>Issuances of green/sustainable bonds</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Gender pay gap at FSPs</t>
+          <t>Volume (issuances) and value (amount outstanding) of sustainable/green bonds</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Metric that measures the difference in average (or median) earnings between genders across similar functions and roles at financial institutions. Typically calculated to spot differences across men and women, but it could be expanded to include other genders. It's typically expressed as a percentage of the higher earner gender (usually men's earnings), for a given role or hierarchical level at the financial institution. Prudential supervisors can use this indicator with a focus on the safety and soundness of financial institutions. A significant gender pay gap can be an indicator of underlying governance and operational risks. for conduct supervisors, a significant gender pay gap could be an indication of potential misconduct and unfairness that could affect customers. The gender pay gap is most commonly calculated as the mean or median difference in gross earnings between all male and female employees, expressed as a percentage of the male earnings.</t>
+          <t>This indicator tracks the number and, more commonly, the face value (in USD, EUR or local currency) of bonds labelled green, social, sustainability or sustainability-linked that reach primary markets in a given period. By capturing how much fresh capital is being channelled explicitly toward environmentally and/or socially beneficial projects, it offers a tangible gauge of the financial sector’s contribution to the transition to a low-carbon, inclusive economy. Policymakers use the series to monitor progress against climate-finance targets, assess the effectiveness of incentives such as tax exemptions or regulatory relief, and spot market slow-downs that could jeopardise net-zero pathways. The definition of sustainable or green bond varies widely across countries and the indicator should align with local practices. An example of definition is provided by the Green Bond Principles (GBP), by the International Capital Markets Association (ICMA) https://www.icmagroup.org/sustainable-finance/the-principles-guidelines-and-handbooks/green-bond-principles-gbp/</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Are there gender disparities in compensation for similar positions or responsibilities (Board, management, staff)? How does this compare with other macro indicators related to financial stability and portfolio performance across FSPs (credit, insurance, investment funds, pensions)? Are FSPs with greater gender diversity in the Board more likely to present lower gender pay gap?</t>
+          <t>Do companies with higher levels of gender diversity issue more green bonds? Are FSPs with higher levels of gender diversity more likely to distribute sustainable or green bonds?</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Usage</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -11577,286 +11587,276 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
+          <t>Climate and environmental objectives</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Savings, Credit, Insurance, Pensions</t>
+        </is>
+      </c>
+      <c r="D210">
+        <v>126</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Climate and other environmental risks in the investment portoflio</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Exposure of the investment portfolio to industries with high climate and other environmental risks</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>This indicator quantifies how much of the investment book is exposed to climate-related risks (physical and transition) and broader environmental risks (e.g., water stress, biodiversity loss, pollution). It helps firms and supervisors judge vulnerability to asset impairment and regulatory change. Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, while the NGFS provides a range of additional definitions, including nature-related financial risks.</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>How is FSP gender diversity correlated with climate-related financial risks and other environmental risks arising from the investment portfolio of insurers and banks?</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Market risk, Credit risk</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Sustainability</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
           <t>Gender equality</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
+      <c r="C211" t="inlineStr">
         <is>
           <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
-      <c r="D210">
+      <c r="D211">
+        <v>11</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Gender diversity at FSP (by reference workforce group)</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Gender composition of FSP workforce by level of responsibility (Board, management, staff)</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Measure used to assess the representation of different genders within a financial institution. It serves as a critical tool for evaluating a firm's commitment to inclusivity and is increasingly correlated with enhanced financial performance, risk management, and innovation. This indicator is not a single metric but a suite of measurements that can be applied across various levels of an organization. Ideally, it would be calculated at the board level, the senior management level (C suite), and the staff level. In some occasions, it can also be useful to calculate it for specific roles within the financial institution, such as branch managers, or agents, when analyzing differences in performance related to specific issues, such as consumer protection and conduct issues. In addition to being useful to monitor diversity at the system level, and its alignment with national gender equality policies, this indicator can also be used by prudential and conduct supervisors, as a growing body of knowledge points to improved financial and conduct performance of financial institutions that have a greater level of diversity. For prudential supervisors, this indicator serves as a valuable proxy for assessing a firm's health, as greater gender diversity is often correlated with stronger corporate governance, more prudent risk management, and enhanced financial stability.</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in workforce participation across different types of FSPs? At what responsibility levels? How does gender diversity in FSP management correlate with key financial indicators (e.g., Stability, Financial Inclusion, Customer Protection, Sustainability)? Comparing with climate-related financial data (e.g., green loan portfolios, green insurance), does gender diversity in FSPs correlate with the growth of these portfolios? If legal or regulatory gender equity requirements exist for FSPs, are they being met? Does gender diversity correlate with variations in supervisory risk scores? How does gender diversity correlate with staff turnover (if data is available)? How does gender diversity correlate with enforcement and other supervisory actions?</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Sustainability</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Gender equality</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D212">
+        <v>341</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Gender diversity of customer base</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Gender composition of FSP customer base</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Measures the representation of different genders—women, men, and non-binary individuals—among a financial institution's clients. This metric provides insights into a firm's market reach, product inclusiveness, and potential exposure to social and economic trends. This indicator can be used to monitor implementaton of gender equality targets and national policies, but also by prudential and conduct supervisors, to compare performance in other metrics, such as basic consumer risk indicators and prudential risk indicators, with the level of gender diversity of the customer base, with the purpose of finding any possible correlation.</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Are there significant gender disparities in the composition of customers across different types of financial service providers (FSPs)? How does the gender diversity of the FSP customer base vary by institution size, sector, and geographic region? What correlations exist between the gender diversity of the customer base and key financial inclusion metrics such as account ownership, loan uptake, and insurance coverage? How does greater gender diversity among customers relate to customer protection outcomes, including complaint resolution and fair treatment? Are FSPs with more gender-diverse customer bases also demonstrating stronger prudential performance and sustainability indicators? How do gender disparities in the customer base influencefinancila outcomes such as Financial Health? And broader social and economic outcomes, such as women's economic empowerment, MSME growth, climate change, jobs creation or poverty reduction?</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Sustainability</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Gender equality</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D213">
+        <v>131</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Gender pay gap at FSPs</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Gender pay gap at FSPs</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Metric that measures the difference in average (or median) earnings between genders across similar functions and roles at financial institutions. Typically calculated to spot differences across men and women, but it could be expanded to include other genders. It's typically expressed as a percentage of the higher earner gender (usually men's earnings), for a given role or hierarchical level at the financial institution. Prudential supervisors can use this indicator with a focus on the safety and soundness of financial institutions. A significant gender pay gap can be an indicator of underlying governance and operational risks. for conduct supervisors, a significant gender pay gap could be an indication of potential misconduct and unfairness that could affect customers. The gender pay gap is most commonly calculated as the mean or median difference in gross earnings between all male and female employees, expressed as a percentage of the male earnings.</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in compensation for similar positions or responsibilities (Board, management, staff)? How does this compare with other macro indicators related to financial stability and portfolio performance across FSPs (credit, insurance, investment funds, pensions)? Are FSPs with greater gender diversity in the Board more likely to present lower gender pay gap?</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Sustainability</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Gender equality</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D214">
         <v>18</v>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="E214" t="inlineStr">
         <is>
           <t>Human Resources Gender Index (HRGI)</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
+      <c r="F214" t="inlineStr">
         <is>
           <t>Index based on FSPs' gender diversity policies, covering gender and employment, gender earnings, leave and work arrangements, childcare, and other benefits</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
+      <c r="G214" t="inlineStr">
         <is>
           <t>The Human Resources Gender Index (HRGI) is a composite index that consolidates multiple HR data points to provide a holistic score of gender equality within an institution, throughout the employee lifecycle. It is not a standardized indicator. It can be defined as a weighted score that measures a financial institution's gender equality across key HR areas, including representation, remuneration, recruitment, promotion, and retention, going way beyond headcount. Potential indicator components include: representation score (gender diversity at different corporate levels), pay equality score (mean and median pay gap), gender gap in performance-based bonuses, progression score (promotion rate gender gap, recruitment score (% of women among new hires, especially at senior levels), retention score (gender gap in turnover rate).  This indicator can be used to monitor implementaton of gender equality targets and national policies, but also by prudential and conduct supervisors, to compare performance in other metrics, such as basic consumer risk indicators and prudential risk indicators, with the level of gender diversity of the customer base, with the purpose of finding any possible correlation. https://www.elibrary.imf.org/view/journals/001/2023/091/article-A001-en.xml
 .</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
+      <c r="H214" t="inlineStr">
         <is>
           <t>How do financial service providers (FSPs) compare in their Human Resources Gender Index (HRGI) scores? Are FSPs with higher levels of gender diversity in their workforce more likely to perform better across the various HRGI dimensions, such as recruitment, retention, promotion, and leadership representation? When comparing HRGI scores with key performance indicators (e.g., capital and liquidity, profitability, efficiency, customer satisfaction, innovation), is there evidence of a positive correlation? How do HRGI scores vary by FSP type, size, or region, and what best practices can be identified from top performers? How does HRGI performance relate to gender-related outcomes, such as gender-balanced customer bases or inclusive product offerings?</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
+      <c r="L214" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Sustainability</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Gender equality</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D211">
-        <v>13</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>Success rate of license applications by diverse FSPs</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>% of all license applications by diverse FSPs that are issued</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>This indicator is a measure of potential gender biases in licensing decisions by the financial authority. It helps authorities analyze the success rate of license pplications by segmenting applications by their final oucome (rejection/approval), and the gender of the lead sponsor of the application (e.g., the majority individual shareholder). The definition of lead sponsor will vary across countries and the indicator should align with local practices.</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>To what extent does the gender of individuals in leadership or control positions within the proposed FSPs influence the likelihood of obtaining a license from the regulatory authority?</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Market development</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Capital markets development</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Investments</t>
-        </is>
-      </c>
-      <c r="D212">
-        <v>45</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>Crowdfunding - Differential rate of return (equity)</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>Difference between the advertised/promised rate of return and the actual rate of return of equity in crowdfunding projects</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>Measures the gap between the projected or advertised rate of return presented to investors before a project is funded and the actual rate of return realized after the project is completed. This is a critical conduct indicator that measures the accuracy of a project's promises versus its real-world performance. For investors, this metric is a tool for due diligence. For conduct supervisors, it can be used to detect mis-selling and fraud. A large and persistent negative differential (where actual returns are consistently far below promised returns) is a red flag. it could flag issues such as inadequate risk disclosure and fraud. When gender disaggregated by the gender of the main sponsor or lead executive, the indicator can provide additional information. If projects led by women consistently show a smaller negative "reality gap" (meaning their actual returns are closer to their promised returns), it could suggest they are more conservative or accurate in their financial projections. This would be a crucial data point in assessing risk and investor protection. Using this indicator together with the indicator on rejected crowddfunding projects could strenghten the identification of gender bias inside the securities authority. Return Differential (%) = Actual Rate of Return - Advertised/Promised Rate of Return.</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Are there differences in the rates of return for crowdfunding projects depending on the gender assigned to the MSME seeking funding?</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>Uptake (account ownership)</t>
-        </is>
-      </c>
-      <c r="L212" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Market development</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Capital markets development</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Investments</t>
-        </is>
-      </c>
-      <c r="D213">
-        <v>44</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>Crowdfunding - Authorization rejection rate</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>% of all crowfunding applications that are rejected (not authorized by the securities authority)</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>Measures the percentage of all crowdfunding applications submitted to a securities authority that are denied or not authorized to proceed with fundraising. This is a key regulatory indicator that reflects the quality of applications being submitted and the stringency of the regulator's vetting process, which is designed to protect investors from fraud and non-viable projects. When disaggregated by the gender of the main sponsor, the lead executive of the company, it could draw insights into potential gender biases working within the securities authority.</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in the rejection rates and the reasons for rejection of crowdfunding projects presented for authorization by the securities regulator?</t>
-        </is>
-      </c>
-      <c r="L213" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Market development</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Capital markets development</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Investments</t>
-        </is>
-      </c>
-      <c r="D214">
-        <v>43</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>Crowdfunding - Success rate</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>% of all crowfunding projects that are successful in raising the asked amount</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>The indicator is a metric that measures the proportion of projects on a crowdfunding platform (or the sum of all crowdfunding platforms) that successfully reach their predetermined funding goal within a specified timeframe. This indicator is a vital sign of a platform's effectiveness, credibility, and the overall health of its ecosystem. It helps gauge the ability of a platform to connect viable projects with interested backers. For MSMEs, crowdfunding can be a viable and less onerous funding source, so the indicator provids important information for monitoring development of MSME finance markets. From a market conduct perspective, while a high success rate is generally positive, an unusually high or artificially inflated rate could be a red flag for misconduct. Platforms could be setting trivially low funding goals to boost statistics,  failing to conduct proper due diligence on projects, or not being transparent about how the success rate is calculated. Successful projects is the number of projects that met or exceeded their funding target during a specific period (e.g., a month, quarter, or year).</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in the success rates of crowdfunding projects? Are smaller or younger MSMEs headed by women more likely to face challenges in crowdfunding?</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>Usage</t>
-        </is>
-      </c>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Market development</t>
+          <t>Sustainability</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Capital markets development</t>
+          <t>Gender equality</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D215">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Crowdfunding - Transactions</t>
+          <t>Success rate of license applications by diverse FSPs</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Volume (number of offerings) and value (amount raised) of crowdfunding transactions</t>
+          <t>% of all license applications by diverse FSPs that are issued</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Metric that measures the total volume of individual investments or pledges made across all projects on a crowdfunding platform or in the entire market (across multiple platforms) over a specific period. This indicator is a direct measure of market activity and investor engagement with crowdfunding, which is increasingly important for MSME finance.</t>
+          <t>This indicator is a measure of potential gender biases in licensing decisions by the financial authority. It helps authorities analyze the success rate of license pplications by segmenting applications by their final oucome (rejection/approval), and the gender of the lead sponsor of the application (e.g., the majority individual shareholder). The definition of lead sponsor will vary across countries and the indicator should align with local practices.</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Are there disparities in crowdfunding volumes and values raised, according to the gender of the MSMEs asking for funds? Are there disparities in terms of funding periods? Among women-owned MSMEs, which types and ages (years in operation) are driving growth in crowdfunding transactions? Are crowdfunding platforms operated by diverse management more likely to attract women-owned MSMEs, and young MSMEs headed by women?</t>
+          <t>To what extent does the gender of individuals in leadership or control positions within the proposed FSPs influence the likelihood of obtaining a license from the regulatory authority?</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -11877,26 +11877,36 @@
         </is>
       </c>
       <c r="D216">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>P2P - Investors</t>
+          <t>Crowdfunding - Differential rate of return (equity)</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Number of P2P investors</t>
+          <t>Difference between the advertised/promised rate of return and the actual rate of return of equity in crowdfunding projects</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>This indicator counts the number of investors registered in P2P lending platforms, as a measure of development of digital finance, and specifically P2P lending, which can potentially benefit MSMEs. It is a key metric to monitor market development in platform lending. It helps assess the effectiveness of marketing campaigns, measure market reach, and forecast potential loan demand or the ability of platforms to meet demand. A growing investor base indicates increased trust and interest, enabling the business to scale and optimize revenue generation. The indicator should be segmented by type of investor (e.g., retail investor, institutional investor), according to local regulatory definitions.</t>
+          <t>Measures the gap between the projected or advertised rate of return presented to investors before a project is funded and the actual rate of return realized after the project is completed. This is a critical conduct indicator that measures the accuracy of a project's promises versus its real-world performance. For investors, this metric is a tool for due diligence. For conduct supervisors, it can be used to detect mis-selling and fraud. A large and persistent negative differential (where actual returns are consistently far below promised returns) is a red flag. it could flag issues such as inadequate risk disclosure and fraud. When gender disaggregated by the gender of the main sponsor or lead executive, the indicator can provide additional information. If projects led by women consistently show a smaller negative "reality gap" (meaning their actual returns are closer to their promised returns), it could suggest they are more conservative or accurate in their financial projections. This would be a crucial data point in assessing risk and investor protection. Using this indicator together with the indicator on rejected crowddfunding projects could strenghten the identification of gender bias inside the securities authority. Return Differential (%) = Actual Rate of Return - Advertised/Promised Rate of Return.</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the growth of reatil investors in P2P lending platforms? How do invested amounts and types vary by investor gender and other demographics? For example, do women prefer to invest in women-led MSMEs, smaller projects, or younger enterprises? Do P2P platforms operated by diverse management more likely to attract a more diverse investor base?</t>
+          <t>Are there differences in the rates of return for crowdfunding projects depending on the gender assigned to the MSME seeking funding?</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Uptake (account ownership)</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -11922,36 +11932,26 @@
         </is>
       </c>
       <c r="D217">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Total investment fund shares</t>
+          <t>Crowdfunding - Authorization rejection rate</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Number of investment fund shares held by retail investors in the system</t>
+          <t>% of all crowfunding applications that are rejected (not authorized by the securities authority)</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Market-wide metric that quantifies the volume of investment fund shares owned by individual, non-professional investors within a financial system. This market develoment indicator serves as a crucial gauge of retail investor participation in the capital markets, and their overall exposure to market risks. Companion indicators include the share of investment fund shares held by retail investors as percentage of total investment fund shares, and the average holding size by retail investors.</t>
+          <t>Measures the percentage of all crowdfunding applications submitted to a securities authority that are denied or not authorized to proceed with fundraising. This is a key regulatory indicator that reflects the quality of applications being submitted and the stringency of the regulator's vetting process, which is designed to protect investors from fraud and non-viable projects. When disaggregated by the gender of the main sponsor, the lead executive of the company, it could draw insights into potential gender biases working within the securities authority.</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>How has participation in investment funds evolved by gender, both for individuals and MSMEs considering the gender of their owners? What types of investment funds show growing participation by women?</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>Uptake (account ownership)</t>
+          <t>Are there gender disparities in the rejection rates and the reasons for rejection of crowdfunding projects presented for authorization by the securities regulator?</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -11968,55 +11968,50 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Capital markets development</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Savings, Credit</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="D218">
-        <v>267</v>
+        <v>43</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Interest rate spreads (loans)</t>
+          <t>Crowdfunding - Success rate</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Difference between the average lending rate and a reference rate (e.g. deposit rate or external reference rate)</t>
+          <t>% of all crowfunding projects that are successful in raising the asked amount</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>The interest-rate spread on loans captures the margin between the average contractual rate a lender charges borrowers and an external reference rate—typically the policy rate. It is a concise gauge of (i) lenders’ credit-risk pricing, (ii) competitive conditions in the lending market, and (iii) monetary-policy transmission. Wider spreads may reflect higher perceived borrower risk, limited competition, or funding-cost pressures; persistently narrow spreads can point to aggressive underwriting or excess liquidity that may undermine future asset quality. Tracked over time and across peer institutions, interest-rate spreads provide insights into credit-cycle turning points, profitability dynamics, and the effectiveness of monetary-policy signals reaching the real economy. !- Definitions and concepts:  Loan interest rate spread (simple): Average contractual loan rate minus Reference rate measured for new originations or for the stock of loans. Net lending spread: average loan rate minus average deposit rate, often used when policy benchmarks are volatile. Segmented spreads: calculated by product (e.g., mortgages, MSMEs, credit cards). Non-interest charges: fees and cross-selling income are excluded; the true all-in lending margin may be higher.</t>
+          <t>The indicator is a metric that measures the proportion of projects on a crowdfunding platform (or the sum of all crowdfunding platforms) that successfully reach their predetermined funding goal within a specified timeframe. This indicator is a vital sign of a platform's effectiveness, credibility, and the overall health of its ecosystem. It helps gauge the ability of a platform to connect viable projects with interested backers. For MSMEs, crowdfunding can be a viable and less onerous funding source, so the indicator provids important information for monitoring development of MSME finance markets. From a market conduct perspective, while a high success rate is generally positive, an unusually high or artificially inflated rate could be a red flag for misconduct. Platforms could be setting trivially low funding goals to boost statistics,  failing to conduct proper due diligence on projects, or not being transparent about how the success rate is calculated. Successful projects is the number of projects that met or exceeded their funding target during a specific period (e.g., a month, quarter, or year).</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Are there gender disparities in interest rate spreads offered to borrowers, and how do these differences vary across regions, income levels, and types of financial service providers? Do women or other gender groups consistently face higher lending rates relative to reference rates compared to men, potentially indicating unequal credit costs? How do interest rate spreads differ by loan type or sector, and are there gender patterns in these variations? Are financial service providers with higher gender diversity more likely to offer more equitable interest rate spreads across gender groups? How do differences in interest rate spreads impact borrowing behavior and access to credit for different gender groups?</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>Are there gender disparities in the success rates of crowdfunding projects? Are smaller or younger MSMEs headed by women more likely to face challenges in crowdfunding?</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Quality, Fair treatment</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -12028,55 +12023,40 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Capital markets development</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="D219">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Open finance - % of customers that have given data sharing consent to FSPs</t>
+          <t>Crowdfunding - Transactions</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>% of all customers that have given consent to participate in the open finance scheme</t>
+          <t>Volume (number of offerings) and value (amount raised) of crowdfunding transactions</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>The indicator shows how many customers have actively opted in to share their data via the open finance rails (e.g., with account information service providers or payment initiation service providers). A higher share signals trust, clear value propositions, and mature consent customer interfaces (mobile apps); a low or falling rate may reflect friction in UX or Strong Customer Authentication (SCA), poor messaging, or privacy concerns. It’s a headline adoption KPI for open finance schemes. !- Definitions and concepts: Explicit consent: a clear, affirmative action tied to a specific purpose with the ability to manage and withdraw. Active consent: valid as of the reference date (not expired/withdrawn). Open finance consenting customers (%) = [# unique customers with at least 1 open finance consent / # eligible customers] x 100%. Denominator options: all active retail/MSME customers (preferred) or customers with eligible accounts (state choice). Segment by purpose of consent, scope (accounts included), and channel (mobile/web). Duplication &amp; scope: a customer may hold multiple consents across TPPs; count unique customers, and compare with total count of consents. Lawful-basis nuance: exclude sharing done under contractual necessity or legal obligation (e.g., consultation to credit bureaus for a loan application)—this metric is about explicit consent only.</t>
+          <t>Metric that measures the total volume of individual investments or pledges made across all projects on a crowdfunding platform or in the entire market (across multiple platforms) over a specific period. This indicator is a direct measure of market activity and investor engagement with crowdfunding, which is increasingly important for MSME finance.</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Are there gender disparities in data-sharing consent within the open finance scheme, including for MSMEs based on the ownership gender and low-value accounts? What types of accounts are more commonly subject to data-sharing consents? Which types of FSPs have a higher percentage of customers who have given data-sharing consent, and do these percentages vary by gender? If the information is available, what are the most common types and terms for these consents?</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>Consumer protection; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>Data privacy and protection, Reputational and legal risk</t>
+          <t>Are there disparities in crowdfunding volumes and values raised, according to the gender of the MSMEs asking for funds? Are there disparities in terms of funding periods? Among women-owned MSMEs, which types and ages (years in operation) are driving growth in crowdfunding transactions? Are crowdfunding platforms operated by diverse management more likely to attract women-owned MSMEs, and young MSMEs headed by women?</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -12088,55 +12068,40 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Capital markets development</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="D220">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Open finance - API availability</t>
+          <t>P2P - Investors</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Average % of time APIs are available</t>
+          <t>Number of P2P investors</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Shows the proportion of clock time that open finance endpoints can successfully serve requests. High availability is critical for data users such as third-party providers (TPPs) to deliver reliable account information and payment initiation; poor uptime breaks customer journeys, breaches SLAs/SLOs, and can trigger regulatory scrutiny in open finance schemes. !- Definitions and concepts: Availability (uptime):  time-weighted share of intervals in which an endpoint meets both reachability and success criteria. Scope — include account information service, payment initiation service, consent/token endpoints, and webhooks if they’re required for completion. Planned vs. unplanned:  exclude planned maintenance time; report maintenance windows separately. SLO period: availability is usually measured monthly/quarterly (e.g., 99.9% per calendar month), but preferably in shorter periods (e.g., weekly, daily). Granularity: overall availability, by endpoint family, region/zone, and time of day. Example indicator: Availability = 1 - [Downtime / Total scheduled time] where Downtime aggregates intervals failing the success criterion (5xx gateway/network timeouts, auth outages, or latency breaches). !- Limitations and considerations: Including latency SLOs will lower availability vs. status-only measurements. Publish thresholds.</t>
+          <t>This indicator counts the number of investors registered in P2P lending platforms, as a measure of development of digital finance, and specifically P2P lending, which can potentially benefit MSMEs. It is a key metric to monitor market development in platform lending. It helps assess the effectiveness of marketing campaigns, measure market reach, and forecast potential loan demand or the ability of platforms to meet demand. A growing investor base indicates increased trust and interest, enabling the business to scale and optimize revenue generation. The indicator should be segmented by type of investor (e.g., retail investor, institutional investor), according to local regulatory definitions.</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Open finance performance will vary across FSPs for a range of reasons such as their current data architecture and other firm-specific aspects. The objective of looking into this indicator from a gender perspective is to identify whether FSPs that concentrate underserved, low-income women and women-led MSMEs also present poor open finance performance. This indicator can be analyzed together with other open finance performance indicators (Unsuccessful API calls, API response time), and open finance adoption indicators (% customer that have given consent, payment initiation transactions)</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>Quality, Operational risk</t>
+          <t>Are there gender disparities in the growth of reatil investors in P2P lending platforms? How do invested amounts and types vary by investor gender and other demographics? For example, do women prefer to invest in women-led MSMEs, smaller projects, or younger enterprises? Do P2P platforms operated by diverse management more likely to attract a more diverse investor base?</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -12148,55 +12113,50 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Capital markets development</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="D221">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Open finance - API error rate</t>
+          <t>Total investment fund shares</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>% of all API calls that are unsuccessful</t>
+          <t>Number of investment fund shares held by retail investors in the system</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>This indicator tracks the reliability of open-finance interfaces by showing what share of API requests do not complete successfully due to errors. It is a key API performance indicator monitored by financial authorities implementing open finance. High failure rates degrade customer journeys (consent, data retrieval, payment initiation), inflate support costs, and can breach SLA/SLO commitments. !- Definitions and concepts: API call (request): one HTTP request to a documented endpoint, for example: Account Information Services (AIS) data, Payment Initiatiion Services (PIS) payment, consent, token, webhook, etc. Unsuccessful call: define as per local regulation. This indicator can be collected segmented by types of errors, to be defined as per local regulation (e.g., gateway/network timeouts, invalid/expired token/consent, error in validation, authentication failures. It should also be segmented by type of endpoint, as per local categorization (e.g., account information request, payment initiation request, other). Example indicator: [# of errors  /  # total API calls] x 100%.</t>
+          <t>Market-wide metric that quantifies the volume of investment fund shares owned by individual, non-professional investors within a financial system. This market develoment indicator serves as a crucial gauge of retail investor participation in the capital markets, and their overall exposure to market risks. Companion indicators include the share of investment fund shares held by retail investors as percentage of total investment fund shares, and the average holding size by retail investors.</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Open finance performance will vary across FSPs for a range of reasons such as their current data architecture and other firm-specific aspects. The objective of looking into this indicator from a gender perspective is to identify whether FSPs that concentrate underserved, low-income women and women-led MSMEs also present poor open finance performance. This indicator can be analyzed together with other open finance performance indicators (Unsuccessful API calls, API response time), and open finance adoption indicators (% customer that have given consent, payment initiation transactions)</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>How has participation in investment funds evolved by gender, both for individuals and MSMEs considering the gender of their owners? What types of investment funds show growing participation by women?</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Quality, Operational risk</t>
+          <t>Uptake (account ownership)</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -12213,30 +12173,30 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Savings, Credit</t>
         </is>
       </c>
       <c r="D222">
-        <v>69</v>
+        <v>267</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Open finance - API response time</t>
+          <t>Interest rate spreads (loans)</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Average API response time</t>
+          <t>Difference between the average lending rate and a reference rate (e.g. deposit rate or external reference rate)</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Shows how quickly open-finance endpoints answer requests. Faster responses improve user experience during consent, account-information retrieval, and payment initiation, reducing frictions and drop-offs. Response time is a core performance KPI that complements availability and error rate. !- Definitions and concepts: Response time (latency): elapsed time between request start and final byte received (client-observed) or gateway in → gateway out (server-observed). Track both when possible. Averages vs. tails: report p50/median, p95, p99, and the mean; tails (p95/p99) best reflect user pain. Track both. Granularity: report by endpoint family (types of APIs), potentially segmented into priority levels (see https://www.cdr.gov.au/performance). Units &amp; window: milliseconds, by calendar month (preferably shorter SLO period, such as weekly or daily).</t>
+          <t>The interest-rate spread on loans captures the margin between the average contractual rate a lender charges borrowers and an external reference rate—typically the policy rate. It is a concise gauge of (i) lenders’ credit-risk pricing, (ii) competitive conditions in the lending market, and (iii) monetary-policy transmission. Wider spreads may reflect higher perceived borrower risk, limited competition, or funding-cost pressures; persistently narrow spreads can point to aggressive underwriting or excess liquidity that may undermine future asset quality. Tracked over time and across peer institutions, interest-rate spreads provide insights into credit-cycle turning points, profitability dynamics, and the effectiveness of monetary-policy signals reaching the real economy. !- Definitions and concepts:  Loan interest rate spread (simple): Average contractual loan rate minus Reference rate measured for new originations or for the stock of loans. Net lending spread: average loan rate minus average deposit rate, often used when policy benchmarks are volatile. Segmented spreads: calculated by product (e.g., mortgages, MSMEs, credit cards). Non-interest charges: fees and cross-selling income are excluded; the true all-in lending margin may be higher.</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Open finance performance will vary across FSPs for a range of reasons such as their current data architecture and other firm-specific aspects. The objective of looking into this indicator from a gender perspective is to identify whether FSPs that concentrate underserved, low-income women and women-led MSMEs also present poor open finance performance. This indicator can be analyzed together with other open finance performance indicators (Unsuccessful API calls, API response time), and open finance adoption indicators (% customer that have given consent, payment initiation transactions)</t>
+          <t>Are there gender disparities in interest rate spreads offered to borrowers, and how do these differences vary across regions, income levels, and types of financial service providers? Do women or other gender groups consistently face higher lending rates relative to reference rates compared to men, potentially indicating unequal credit costs? How do interest rate spreads differ by loan type or sector, and are there gender patterns in these variations? Are financial service providers with higher gender diversity more likely to offer more equitable interest rate spreads across gender groups? How do differences in interest rate spreads impact borrowing behavior and access to credit for different gender groups?</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -12246,17 +12206,17 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
+          <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Quality, Operational risk</t>
+          <t>Quality, Fair treatment</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -12277,31 +12237,41 @@
         </is>
       </c>
       <c r="D223">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Open finance - Payment initiation transactions</t>
+          <t>Open finance - % of customers that have given data sharing consent to FSPs</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Number of payment initiation transactions conducted in the open finance scheme</t>
+          <t>% of all customers that have given consent to participate in the open finance scheme</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Counts how many account-to-account (A2A) payment orders were successfully initiated via open-finance rails in the period. It’s a core adoption and usage KPI for Payment Initiation Services (PIS): more transactions imply growing merchant and P2P acceptance of openb finance, customer trust, and TPP–bank interoperability. !- Definitions and concepts: Payment initiation transaction (PIT): a payment order created via an authorized PISP/TPP and accepted by the ASPSP (account holder) for processing. Companion counts: Failed payment initiation transactions. Refunds/returns/chargebacks tracked separately. Sub-types: single immediate payments, scheduled payments, recurring/VRP (variable recurring payments), instant vs. ACH/batch. !- Data requirements: Total number of successful payment initiation transactions. !- Limitations and considerations: Duplicates: avoid double counting by using operation IDs.</t>
+          <t>The indicator shows how many customers have actively opted in to share their data via the open finance rails (e.g., with account information service providers or payment initiation service providers). A higher share signals trust, clear value propositions, and mature consent customer interfaces (mobile apps); a low or falling rate may reflect friction in UX or Strong Customer Authentication (SCA), poor messaging, or privacy concerns. It’s a headline adoption KPI for open finance schemes. !- Definitions and concepts: Explicit consent: a clear, affirmative action tied to a specific purpose with the ability to manage and withdraw. Active consent: valid as of the reference date (not expired/withdrawn). Open finance consenting customers (%) = [# unique customers with at least 1 open finance consent / # eligible customers] x 100%. Denominator options: all active retail/MSME customers (preferred) or customers with eligible accounts (state choice). Segment by purpose of consent, scope (accounts included), and channel (mobile/web). Duplication &amp; scope: a customer may hold multiple consents across TPPs; count unique customers, and compare with total count of consents. Lawful-basis nuance: exclude sharing done under contractual necessity or legal obligation (e.g., consultation to credit bureaus for a loan application)—this metric is about explicit consent only.</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the adoption of payment initiation transactions within the open finance scheme, including for MSMEs by the owner's gender? Do FSPs with higher levels of gender diversity tend to have a larger share of diverse customers conducting payment initiation transactions?</t>
+          <t>Are there gender disparities in data-sharing consent within the open finance scheme, including for MSMEs based on the ownership gender and low-value accounts? What types of accounts are more commonly subject to data-sharing consents? Which types of FSPs have a higher percentage of customers who have given data-sharing consent, and do these percentages vary by gender? If the information is available, what are the most common types and terms for these consents?</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
           <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Consumer protection; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Data privacy and protection, Reputational and legal risk</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -12327,165 +12297,395 @@
         </is>
       </c>
       <c r="D224">
+        <v>36</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Open finance - API availability</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Average % of time APIs are available</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Shows the proportion of clock time that open finance endpoints can successfully serve requests. High availability is critical for data users such as third-party providers (TPPs) to deliver reliable account information and payment initiation; poor uptime breaks customer journeys, breaches SLAs/SLOs, and can trigger regulatory scrutiny in open finance schemes. !- Definitions and concepts: Availability (uptime):  time-weighted share of intervals in which an endpoint meets both reachability and success criteria. Scope — include account information service, payment initiation service, consent/token endpoints, and webhooks if they’re required for completion. Planned vs. unplanned:  exclude planned maintenance time; report maintenance windows separately. SLO period: availability is usually measured monthly/quarterly (e.g., 99.9% per calendar month), but preferably in shorter periods (e.g., weekly, daily). Granularity: overall availability, by endpoint family, region/zone, and time of day. Example indicator: Availability = 1 - [Downtime / Total scheduled time] where Downtime aggregates intervals failing the success criterion (5xx gateway/network timeouts, auth outages, or latency breaches). !- Limitations and considerations: Including latency SLOs will lower availability vs. status-only measurements. Publish thresholds.</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Open finance performance will vary across FSPs for a range of reasons such as their current data architecture and other firm-specific aspects. The objective of looking into this indicator from a gender perspective is to identify whether FSPs that concentrate underserved, low-income women and women-led MSMEs also present poor open finance performance. This indicator can be analyzed together with other open finance performance indicators (Unsuccessful API calls, API response time), and open finance adoption indicators (% customer that have given consent, payment initiation transactions)</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Quality, Operational risk</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Market development</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D225">
+        <v>37</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Open finance - API error rate</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>% of all API calls that are unsuccessful</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>This indicator tracks the reliability of open-finance interfaces by showing what share of API requests do not complete successfully due to errors. It is a key API performance indicator monitored by financial authorities implementing open finance. High failure rates degrade customer journeys (consent, data retrieval, payment initiation), inflate support costs, and can breach SLA/SLO commitments. !- Definitions and concepts: API call (request): one HTTP request to a documented endpoint, for example: Account Information Services (AIS) data, Payment Initiatiion Services (PIS) payment, consent, token, webhook, etc. Unsuccessful call: define as per local regulation. This indicator can be collected segmented by types of errors, to be defined as per local regulation (e.g., gateway/network timeouts, invalid/expired token/consent, error in validation, authentication failures. It should also be segmented by type of endpoint, as per local categorization (e.g., account information request, payment initiation request, other). Example indicator: [# of errors  /  # total API calls] x 100%.</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Open finance performance will vary across FSPs for a range of reasons such as their current data architecture and other firm-specific aspects. The objective of looking into this indicator from a gender perspective is to identify whether FSPs that concentrate underserved, low-income women and women-led MSMEs also present poor open finance performance. This indicator can be analyzed together with other open finance performance indicators (Unsuccessful API calls, API response time), and open finance adoption indicators (% customer that have given consent, payment initiation transactions)</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Quality, Operational risk</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Market development</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D226">
+        <v>69</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Open finance - API response time</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Average API response time</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Shows how quickly open-finance endpoints answer requests. Faster responses improve user experience during consent, account-information retrieval, and payment initiation, reducing frictions and drop-offs. Response time is a core performance KPI that complements availability and error rate. !- Definitions and concepts: Response time (latency): elapsed time between request start and final byte received (client-observed) or gateway in → gateway out (server-observed). Track both when possible. Averages vs. tails: report p50/median, p95, p99, and the mean; tails (p95/p99) best reflect user pain. Track both. Granularity: report by endpoint family (types of APIs), potentially segmented into priority levels (see https://www.cdr.gov.au/performance). Units &amp; window: milliseconds, by calendar month (preferably shorter SLO period, such as weekly or daily).</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Open finance performance will vary across FSPs for a range of reasons such as their current data architecture and other firm-specific aspects. The objective of looking into this indicator from a gender perspective is to identify whether FSPs that concentrate underserved, low-income women and women-led MSMEs also present poor open finance performance. This indicator can be analyzed together with other open finance performance indicators (Unsuccessful API calls, API response time), and open finance adoption indicators (% customer that have given consent, payment initiation transactions)</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Quality, Operational risk</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Market development</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D227">
+        <v>68</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Open finance - Payment initiation transactions</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Number of payment initiation transactions conducted in the open finance scheme</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Counts how many account-to-account (A2A) payment orders were successfully initiated via open-finance rails in the period. It’s a core adoption and usage KPI for Payment Initiation Services (PIS): more transactions imply growing merchant and P2P acceptance of openb finance, customer trust, and TPP–bank interoperability. !- Definitions and concepts: Payment initiation transaction (PIT): a payment order created via an authorized PISP/TPP and accepted by the ASPSP (account holder) for processing. Companion counts: Failed payment initiation transactions. Refunds/returns/chargebacks tracked separately. Sub-types: single immediate payments, scheduled payments, recurring/VRP (variable recurring payments), instant vs. ACH/batch. !- Data requirements: Total number of successful payment initiation transactions. !- Limitations and considerations: Duplicates: avoid double counting by using operation IDs.</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in the adoption of payment initiation transactions within the open finance scheme, including for MSMEs by the owner's gender? Do FSPs with higher levels of gender diversity tend to have a larger share of diverse customers conducting payment initiation transactions?</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Market development</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D228">
         <v>150</v>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="E228" t="inlineStr">
         <is>
           <t>Bundled product uptake rate</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
+      <c r="F228" t="inlineStr">
         <is>
           <t>% of customers taking up additional products during onboarding</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
+      <c r="G228" t="inlineStr">
         <is>
           <t>Measures the percentage of customers who acquire one or more additional financial products or services at the time of onboarding (i.e., when opening their primary account or initiating a new relationship with a financial service provider). These additional products may include insurance, savings, credit, or investment add-ons linked to the initial product. Captures the prevalence of product bundling and cross-selling practices during customer onboarding. It provides insight into market behavior, product integration, and the extent to which customers are being offered or encouraged to take multiple products simultaneously. Monitoring product bundling helps regulators and providers:
 Assess consumer choice and informed consent during onboarding; Identify potential coercive or mis-selling practices; Evaluate financial literacy and customer understanding of product combinations; Analyze the integration of complementary services (e.g., savings plus micro-insurance); Support efforts to ensure responsible cross-selling and transparent disclosure. Bundling can enhance value and convenience when responsibly designed, but may also raise conduct or affordability risks if customers are not well-informed. High bundling rates may reflect integrated product offerings or effective cross-selling, but warrant review for consent and suitability. Low rates may indicate limited product integration or narrow customer engagement at onboarding. Trends can reveal shifts in market strategy, regulatory compliance, or consumer protection outcomes. !- Definitions and concepts: Bundled product: A package of two or more financial services offered together at onboarding (e.g., transaction account + insurance or credit line). Onboarding: The process of establishing a new customer relationship, including account opening and KYC verification. Cross-selling: Offering additional, often related, financial products to a new or existing customer. Informed consent: The customer’s clear understanding and voluntary acceptance of each product taken. !- Data requirements: Bundled product uptake rate (%)=Number of customers who acquired ≥1 additional product at onboarding​/Total number of new customers onboarded. Administrative or CRM data from financial institutions on new customer onboarding and product uptake. Disaggregation by institution type, customer segment (individual, MSMEs), region, and product category. !- Derivable indicators: Average number of products per new customer; Distribution of additional products (e.g., % taking insurance, credit, savings add-ons)</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
+      <c r="H228" t="inlineStr">
         <is>
           <t>How many products does each gender take up on average during the onboarding stage, and how do these numbers compare? What are the gender disparities in the likelihood of adopting multiple products? Which FSPs stand out in multi-product onboarding, and does their ranking change when analyzed by gender? Note: Active usage of products should also be assessed for multiple products taken up during onboarding.</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr">
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
         <is>
           <t>Uptake (account ownership)</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr">
+      <c r="L228" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
+    <row r="229">
+      <c r="A229" t="inlineStr">
         <is>
           <t>Market development</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B229" t="inlineStr">
         <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
+      <c r="C229" t="inlineStr">
         <is>
           <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
-      <c r="D225">
+      <c r="D229">
         <v>32</v>
       </c>
-      <c r="E225" t="inlineStr">
+      <c r="E229" t="inlineStr">
         <is>
           <t>Product portability requests</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
+      <c r="F229" t="inlineStr">
         <is>
           <t>Number of product portability requests</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
+      <c r="G229" t="inlineStr">
         <is>
           <t>Measures the volume of formal requests initiated by customers to transfer their financial product or relationship from one provider to another within a specific period. This includes activities like switching a mortgage, transferring a loan to a new lender, or moving a current account to a new bank. This indicator is a gauge of market competition, consumer empowerment, and potential frictions or risks within the financial system. Very low switching rates can indicate significant barriers to entry or anti-competitive behavior, suggesting that customers are "trapped" with their current providers due to high exit fees, complex processes, or a lack of clear alternatives. This indicator is even more important in countries where product switching platforms or open finance exist and whose effectiveness should be monitored. A companion indicator to the total number of product switch requests is the total number of switches effected in the period, in comparison to the total number of requests. Another companion indicator is the total number of requests (or successful requests) relative to the number of active customers. The central bank of Brazil has calculated the number of loan portability requests relative to the number of loans with an interest rate above the market average rates, using the number of loans with above-market interest rates as a proxy for the untapped potential of the portability system. https://www.bcb.gov.br/content/publicacoes/Documents/reb/boxesreb2020/boxe_2_evolucao_portabilidade_credito_brasil.pdf</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
+      <c r="H229" t="inlineStr">
         <is>
           <t>Are there customer gender, income and location disparities in account and loan portability or FSP switching requests? Are FSPs with higher levels of gender diversity more likely to receive portability or switching requests or be the destination FSP (rather than the origin) for such requests?</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
+      <c r="K229" t="inlineStr">
         <is>
           <t>Usage, Suitability</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr">
+      <c r="L229" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
+    <row r="230">
+      <c r="A230" t="inlineStr">
         <is>
           <t>Market development</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B230" t="inlineStr">
         <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
+      <c r="C230" t="inlineStr">
         <is>
           <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
-      <c r="D226">
+      <c r="D230">
         <v>33</v>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="E230" t="inlineStr">
         <is>
           <t>Rejected product portability requests</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
+      <c r="F230" t="inlineStr">
         <is>
           <t>% of all product portability requests that are rejected</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
+      <c r="G230" t="inlineStr">
         <is>
           <t>Measures the volume of formal portability requests initiated by customers to transfer their financial product or relationship from one provider to another within a specific period, which are rejected by the financial service provider. Product portability includes activities like switching a mortgage, transferring a loan to a new lender, or moving a current account to a new bank. This indicator is a gauge of market competition, consumer empowerment, and potential frictions or risks within the financial system. Very low switching rates can indicate significant barriers to entry or anti-competitive behavior, suggesting that customers are "trapped" with their current providers due to high exit fees, complex processes, or a lack of clear alternatives. This indicator is even more important in countries where product switching platforms or open finance exist and whose effectiveness should be monitored. When providers reject too many portability requests, this could be a sign of anti-competitive practices. This indicator should be analyzed together with the indicator on the total number of portability requests.</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
+      <c r="H230" t="inlineStr">
         <is>
           <t>Are there customer gender, income, and location disparities in the approval of portability requests? Are FSPs with higher levels of gender diversity more likely to approve portability requests?</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
+      <c r="K230" t="inlineStr">
         <is>
           <t>Usage, Suitability</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
+      <c r="L230" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
         </is>

--- a/www/LENS_INDICATORS_DB.xlsx
+++ b/www/LENS_INDICATORS_DB.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L230"/>
+  <dimension ref="A1:L231"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -592,7 +592,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mobile money accounts</t>
+          <t>Mobile money accounts (number)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1356,13 +1356,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique savings account holders, and how do these vary by age group, income level, and rural vs. urban location? Do certain gender and age groups, particularly low-income individuals or those in remote areas, face greater barriers to opening or maintaining savings accounts? Among MSMEs, are savings accounts equally held by businesses led by individuals of different genders and ages?
-Does greater gender diversity within financial service providers correlate with more equitable savings account ownership across demographic groups?</t>
+          <t>Are there gender disparities in the number of unique savings account holders, and how do these vary by age group, income level, and rural vs. urban location? Do certain gender and age groups, particularly low-income individuals or those in remote areas, face greater barriers to opening or maintaining savings accounts? Does greater gender diversity within financial service providers correlate with more equitable savings account ownership across demographic groups?</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1408,13 +1407,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Are there differences across gender, age, and income groups in the number of savings accounts held, including multiple accounts per individual? Do specific demographic groups tend to maintain more savings accounts, and how does this relate to financial goals or access to different types of savings products? Among MSMEs, does the number of savings accounts vary by the gender and age of the business owner, and what does this suggest about business savings behavior?
-Are financial institutions with gender-diverse teams or inclusive policies more likely to support broader savings account ownership among underserved groups?</t>
+          <t>Are there differences across gender, age, and income groups in the number of savings accounts held, including multiple accounts per individual? Do specific demographic groups tend to maintain more savings accounts, and how does this relate to financial goals or access to different types of savings products? Are financial institutions with gender-diverse teams or inclusive policies more likely to support broader savings account ownership among underserved groups?</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1460,13 +1458,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique term deposit account holders, and how do these vary by age group, income level, and urban versus rural location? Do women or other gender groups face particular barriers in accessing term deposit products, such as minimum balance requirements or lack of tailored products? Among MSMEs, is term deposit ownership influenced by the gender and age of the business owner?
-Do financial institutions with higher gender diversity in management or customer-facing roles show more balanced term deposit ownership across demographic groups?</t>
+          <t>Are there gender disparities in the number of unique term deposit account holders, and how do these vary by age group, income level, and urban versus rural location? Do women or other gender groups face particular barriers in accessing term deposit products, such as minimum balance requirements or lack of tailored products? Do financial institutions with higher gender diversity in management or customer-facing roles show more balanced term deposit ownership across demographic groups?</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1511,13 +1508,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Are there differences by gender, age, and income in the number of term deposit accounts held, including multiple accounts per individual or business? Do certain gender or age groups tend to maintain more term deposits, possibly reflecting differing savings strategies or access to credit alternatives? Among MSMEs, how does the number of term deposit accounts vary by the gender and age of the owner?
-Are providers with greater gender diversity more effective in expanding term deposit ownership among underrepresented gender and demographic groups?</t>
+          <t>Are there differences by gender, age, and income in the number of term deposit accounts held, including multiple accounts per individual or business? Do certain gender or age groups tend to maintain more term deposits, possibly reflecting differing savings strategies or access to credit alternatives? Are providers with greater gender diversity more effective in expanding term deposit ownership among underrepresented gender and demographic groups?</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1562,12 +1558,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of unique pension account holders, and how do these vary by age group, income level, and urban versus rural location? Are women or other gender groups underrepresented in pension coverage, particularly among informal sector workers or MSMEs? Do pension providers or administrators with higher gender diversity in governance or management correlate with more inclusive pension account ownership across gender, age, and income groups?</t>
+          <t>Are there gender disparities in the number of unique pension account holders, and how do these vary by age group, income level, and urban versus rural location? Are women or other gender groups underrepresented in pension coverage, particularly among informal sector workers or MSMEs owners? Do pension providers or administrators with higher gender diversity in governance or management correlate with more inclusive pension account ownership across gender, age, and income groups?</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1617,7 +1613,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1667,7 +1663,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1728,7 +1724,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1788,7 +1784,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -1838,7 +1834,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -1878,7 +1874,8 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>An aggregate measure of the uptake of credit cards. When expressed in per capita terms, it measures the prevalence of uptake in a population and facilitates cross-country comparisons. !- Definitions and concepts: A credit card refers to a type of payment card indicating that the holder has been granted a line of credit. It enables the holder to make purchases and/or withdraw cash up to a prearranged ceiling; the credit granted can be settled in full by the end of a specified period or can be settled in part, with the balance taken as extended credit. Interest is charged on the amount of any extended credit and the holder is sometimes charged an annual fee.(IMF FAS).  !- Data requirements: Unique credit card holders (i.e. an individual or MSME must be counted as one credit card holder irrespective of the number of credit cards held) at the end of a specified period (e.g. quarter or year); Total adult population (count from recent census or estimate from national statistics agency).  !- Limitations and considerations: If individuals or MSMEs own credit cards from multiple different financial institutions, sector or system wide aggregates which add up the number of credit card holders across institutions will, as a result, overstate the number of credit card holders unless a national ID can be used to identify unique card users across institutions. !- Derivable indicators: Credit card holders per 1,000 adults.</t>
+          <t>Are there differences across gender, age, and income groups in the number of savings accounts held, including multiple accounts per individual? Do specific demographic groups tend to maintain more savings accounts, and how does this relate to financial goals or access to different types of savings products?
+Are financial institutions with gender-diverse teams or inclusive policies more likely to support broader savings account ownership among underserved groups?</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1888,7 +1885,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -1938,7 +1935,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -1990,7 +1987,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2045,13 +2042,13 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>How do financial service providers (FSPs), including different types of FSPs, differ in the gender composition of their loan portfolios? Are there gender disparities in loan portfolio participation across various loan types and sectors?  When disaggregated by gender, age, income, and location, how do loan uptake patterns vary? Are women or other gender groups underrepresented as borrowers in specific loan categories or regions? Are there differences in multiple loan holdings by gender or demographic group? 
+          <t>How do financial service providers (FSPs), including different types of FSPs, differ in the gender composition of their loan portfolios? Are there gender disparities in loan portfolio participation across various loan types and sectors?  When disaggregated by gender, age, income, and location, how do loan uptake patterns vary for individuals and MSMEs? Are women, WMSME or other customer groups underrepresented as borrowers in specific loan categories or regions? Are there differences in multiple loan holdings by gender or other sociodemographic group? 
 Comparing this indicator with FSP gender diversity, are lower gender disparities in loan portfolio participation correlated with higher levels of gender diversity within FSPs? How do gender disparities in loan portfolios relate to market-average interest rates or return rates on loan balances? For instance, do FSPs with predominantly female or male loan portfolios offer different rates compared to the market average? Are lower gender disparities in loan portfolio participation correlated with lower non-performing loan (NPL) ratios, and does this correlation vary when women’s representation in the loan portfolio is above or below market averages?</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2112,7 +2109,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2172,7 +2169,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2233,7 +2230,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2293,7 +2290,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2348,7 +2345,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>What is the share of borrowers by gender? Are there gender disparities in borrowing?</t>
+          <t>What is the share of new borrowers by gender?</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2398,19 +2395,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Measures the total number of new retail/MSME loans issued to individuals during the reporting period by regulated financial service providers. Retail loans typically include consumer loans, personal loans, auto loans, credit cards, and residential mortgages granted to households rather than to businesses or government entities. Captures the volume of new credit origination to the household sector, reflecting credit market activity, consumer demand, and lending conditions in the retail segment. Tracking new retail loans helps supervisors and policymakers: Assess trends in household borrowing and credit growth; Monitor potential build-up of consumer debt vulnerabilities; Evaluate the effectiveness of lending standards and access to finance; It serves as a key input to monitoring financial stability, credit risk, and financial inclusion. Higher values indicate expanding credit supply or strong consumer demand, while sharp increases may warrant monitoring for over-indebtedness or lax underwriting standards. Declines may signal tightened credit conditions or weak consumer confidence. !- Data requirements: Total count of newly approved or disbursed retail loans within the reference period derived from: Supervisory returns or administrative data from regulated financial institutions, disaggregation for segmentation analysis, such as by loan type (consumer, mortgage, credit card, etc.), borrower characteristics (gender, region, income group), and institution type. !- Derivable indicators: Loan origination rate = (Number of new retail loans / Number of existing retail borrowers) × 100</t>
+          <t>Measures the total number of new retail loans issued to individuals/MSMEs during the reporting period by regulated financial service providers. Retail loans typically include consumer loans, personal loans, auto loans, credit cards, and residential mortgages granted to households rather than to businesses or government entities. Captures the volume of new credit origination to the household sector, reflecting credit market activity, consumer demand, and lending conditions in the retail segment. Tracking new retail loans helps supervisors and policymakers: Assess trends in household borrowing and credit growth; Monitor potential build-up of consumer debt vulnerabilities; Evaluate the effectiveness of lending standards and access to finance; It serves as a key input to monitoring financial stability, credit risk, and financial inclusion. Higher values indicate expanding credit supply or strong consumer demand, while sharp increases may warrant monitoring for over-indebtedness or lax underwriting standards. Declines may signal tightened credit conditions or weak consumer confidence. !- Data requirements: Total count of newly approved or disbursed retail loans within the reference period derived from: Supervisory returns or administrative data from regulated financial institutions, disaggregation for segmentation analysis, such as by loan type (consumer, mortgage, credit card, etc.), borrower characteristics (gender, region, income group), and institution type. !- Derivable indicators: Loan origination rate = (Number of new retail loans / Number of existing retail borrowers) × 100</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>How do financial service providers (FSPs), including different types of FSPs, differ in the gender composition of their unsecured loan portfolios? Are there gender disparities in unsecured loan portfolio participation across various loan types and sectors?  When disaggregated by gender, age, income, and location, how do unsecured loan uptake patterns vary? Are women or other gender groups underrepresented as borrowers in specific unsecured loan categories or regions? 
-Are there differences in multiple unsecured loan holdings by gender or demographic group? Comparing this indicator with FSP gender diversity, are lower gender disparities in unsecured loan portfolio participation correlated with higher levels of gender diversity within FSPs? How do gender disparities in unsecured loan portfolios relate to market-average interest rates or return rates on loan balances? For instance, do FSPs with predominantly female or male unsecured loan portfolios offer different rates compared to the market average? 
-Are lower gender disparities in unsecured loan portfolio participation correlated with lower non-performing loan (NPL) ratios, and does this correlation vary when women’s representation in the loan portfolio is above or below market averages?</t>
+          <t>How does the gender composition of the new loans disbursed vary by FSP type and FSP loan?  When further disaggregated by age, income, and location, do patterns vary? Are women/WMSE or other customer groups underrepresented as new borrowers in specific loan categories or regions? Comparing this indicator with FSP gender diversity, are lower gender disparities in new loans correlated with higher levels of gender diversity within FSPs?</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2470,7 +2465,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2515,7 +2510,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of retail borrowers holding multiple outstanding credit operations? Do certain gender groups, such as women or non-binary individuals, experience higher rates of potential over-indebtedness compared to others? How does the prevalence of multiple loans vary across age groups, income levels, and geographic locations by gender? Are women or other gender groups more likely to have overlapping loans from different types of financial service providers or loan products, indicating possible gaps in credit assessment? How do financial service providers with higher gender diversity in their workforce or leadership influence the incidence of multiple borrowing among different gender groups? Are there patterns in repayment behavior or default rates among borrowers with multiple loans that differ by gender?</t>
+          <t>Are there gender disparities in the share of retail borrowers holding multiple outstanding credit operations? Do certain gender groups, such as women/WMSME , experience higher rates of potential over-indebtedness compared to others? How does the prevalence of multiple loans vary across age groups, income levels, and geographic locations by gender? Are women or other gender groups more likely to have overlapping loans from different types of financial service providers or loan products, indicating possible gaps in credit assessment? How do financial service providers with higher gender diversity in their workforce or leadership influence the incidence of multiple borrowing among different gender groups? Are there patterns in repayment behavior or default rates among borrowers with multiple loans that differ by gender?</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2575,7 +2570,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2625,7 +2620,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2675,7 +2670,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2725,7 +2720,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2775,7 +2770,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -2825,7 +2820,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -2875,7 +2870,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3070,7 +3065,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3121,7 +3116,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3441,7 +3436,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3601,7 +3596,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3661,7 +3656,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -3711,7 +3706,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -3761,7 +3756,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -3806,12 +3801,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the total outstanding loan balances held by individuals and MSMEs, disaggregated by borrower gender or business owner gender? Do women tend to have lower outstanding balances due to smaller initial loan amounts, shorter loan terms, or faster repayment schedules? How do outstanding loan balances vary across age, income levels, and location for different gender groups? Are portfolios with higher female participation associated with different risk profiles, credit exposure patterns, or lower NPL rates? How does the share of total outstanding balances held by women compare to that held by men, and what does this imply about scale of credit access and usage? Are FSPs with greater gender diversity more likely to have balanced outstanding loan amounts across genders?</t>
+          <t>Are there gender disparities in the total outstanding loan balances held by individuals orMSMEs, disaggregated by borrower gender or business owner gender? Do women tend to have lower outstanding balances due to smaller initial loan amounts, shorter loan terms, or faster repayment schedules? How do outstanding loan balances vary across age, income levels, and location for different gender groups? Are portfolios with higher female participation associated with different risk profiles, credit exposure patterns, or lower NPL rates? How does the share of total outstanding balances held by women compare to that held by men, and what does this imply about scale of credit access and usage? Are FSPs with greater gender diversity more likely to have balanced outstanding loan amounts across genders?</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3866,12 +3861,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the total principal amount of loans disbursed to individuals and MSMEs, disaggregated by borrower or business owner gender? Do women systematically receive smaller loan disbursements than men when controlling for loan type, income level, and sector? Are these disparities more pronounced in certain types of FSPs, geographic regions, or demographic groups? How does the share of total credit disbursed to women compare with their share of total loan applicants or potential borrowers? What does this reveal about credit allocation and approval processes? Are FSPs with higher gender diversity more likely to disburse a larger proportion of credit to women or women-owned MSMEs? How do disbursement patterns by gender relate to broader financial inclusion goals and barriers</t>
+          <t>Are there gender disparities in the total principal amount of loans disbursed to individuals and MSMEs, disaggregated by borrower or business owner gender? Do women systematically receive smaller loan disbursements than men when controlling for loan type, income level, and sector? Are these disparities more pronounced in certain types of FSPs, geographic regions, or demographic groups? How does the share of total credit disbursed to women compare with their share of total loan applicants or potential borrowers? What does this reveal about credit allocation and approval processes? Are FSPs with higher gender diversity more likely to disburse a larger proportion of credit to women or women-owned MSMEs? How do disbursement patterns by gender relate to broader financial inclusion goals and barriers?</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4111,7 +4106,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4162,7 +4157,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4258,7 +4253,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -4353,7 +4348,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -4398,12 +4393,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Are there gender-based disparities in the average balances held in deposit accounts, and how do these vary by age group, income level, location, or provider type? Do certain groups—such as low-income women, youth, or older adults—tend to maintain lower balances, and what factors (e.g., income, financial behavior, limited access to credit) might explain this? Among MSMEs, are deposit account balances different based on the gender and age of the business owner, possibly reflecting liquidity constraints or unequal access to finance? Is there a relationship between the gender composition of FSP leadership or frontline staff and the balance levels maintained by different gender and age groups?</t>
+          <t>Are there gender-based disparities in the average balances held in deposit accounts by individuals or MSMEs, and how do these vary by age group, income level, location, or provider type? Do certain groups—such as low-income women, youth, or older adults—tend to maintain lower balances, and what factors (e.g., income, financial behavior, limited access to credit) might explain this? Among MSMEs, are deposit account balances different based on the gender and age of the business owner, possibly reflecting liquidity constraints or unequal access to finance? Is there a relationship between the gender composition of FSP leadership or frontline staff and the balance levels maintained by different gender and age groups?</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -4592,7 +4587,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -4642,7 +4637,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4702,7 +4697,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4762,7 +4757,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4987,7 +4982,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5047,7 +5042,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5107,7 +5102,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5167,7 +5162,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5227,7 +5222,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5287,7 +5282,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5347,7 +5342,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -5455,7 +5450,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -5506,7 +5501,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -5558,7 +5553,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -5608,7 +5603,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -5656,6 +5651,11 @@
           <t>How does the gender composition of the customer base of the FSPs correlate with the level of access to complaints channels?</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr">
         <is>
           <t>Consumer protection</t>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator, it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -6450,60 +6450,60 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Consumer protection</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Complaints handling, Safety and security</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D118">
-        <v>322</v>
+        <v>401</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Fraud prevalence in complaints</t>
+          <t>New loans (principal disbursed)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Portion and volume of complaints received by providers, regulators, and ombuds that are fraud-related.</t>
+          <t>Value of new loans disbursed in the reference period</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tracks how much of the complaint landscape is driven by fraud—both the count (volume) and the share (portion) of total complaints. Rising prevalence of frauds signals elevated customer harm, control weaknesses (KYC/AML, authentication, data security), or new attack vectors (social engineering). It helps guide supervision, consumer protection responses, reimbursement policies, and investment in fraud controls. !- Definitions and concepts: Fraud-related complaint: a case alleging unauthorised or deceptive activity resulting in loss or attempted loss—e.g., account takeover, card-not-present, phishing/SMiShing, SIM-swap, mule accounts, synthetic identity, merchant fraud, insider abuse, and authorised push payment (APP) scams. Volume: number of fraud-related complaints received in the period. Share: [# of fraud complaints / # of all complaints] x 100%. Intensity companions: fraud complaints per 1,000 customers or per 1 million transactions, value lens using claimed or confirmed loss amounts. Outcome cuts: upheld rate, reimbursement rate, median loss, time-to-resolution. A standard taxonomy for fraud types is needed, including the differentiation between fraud and disputed transaction. !- Limitations and considerations:  Under-reporting: many victims never complain or only contact the bank—triangulate with dispute/chargeback data and incident logs.</t>
+          <t>An aggregate measure of the flow of credit to borrowers over a specified period. On a per loan basis, gives you the average size of loans and on a per borrower basis, give you the average amount of credit accessed per borrower. !- Definitions and concepts: Loans referes to a specific loan account held by resident individuals or MSMEs and could encompass one of many types, such as a mortgage, a revolving line of credit (e.g. credit card), an overdraft account, a personal loan or a loan to purchase a vehicle. MSMEs are defined variably across countries using thresholds of either total number of employees, assets or annual revenue (sales). If none of these characteristics are available, loan size can be used as a proxy for firm size. The International Finance Corporation (IFC) has a standard definition which can be consulted as a guideline if there is no local definition. !- Data requirements: Total principal disbursed to loan accounts from financial institutions (in local currency unit) during a specified period (e.g. quarter, year); Total number of borrowers; Total number of loan accounts. !- Derivable indicators: Average size of loans; Average amount of credit accessed per borrower; Share of all loan disbursements going to MSMEs</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Are there gender differences in the proportion of fraud-related complaints submitted to providers, regulators, or ombuds services?  Do individuals of different genders tend to report different types of fraud, such as identity theft, phishing, or agent misconduct, and are specific delivery channels more commonly associated with these complaints? Is the volume of fraud-related complaints disproportionately high among certain gender groups when compared to their levels of account ownership or usage? Do complaint resolution rates and timeframes differ by gender across various FSP or reporting channels?</t>
+          <t>Are there gender disparities in the total principal amount of loans disbursed to individuals and MSMEs, disaggregated by borrower or business owner gender? Do women systematically receive smaller loan disbursements than men when controlling for loan type, income level, and sector? Are these disparities more pronounced in certain types of FSPs, geographic regions, or demographic groups? How does the share of total credit disbursed to women compare with their share of total loan applicants or potential borrowers? What does this reveal about credit allocation and approval processes? Are FSPs with higher gender diversity more likely to disburse a larger proportion of credit to women or women-owned MSMEs? How do disbursement patterns by gender relate to broader financial inclusion goals and barriers</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Consumer protection; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Suitability, Credit risk</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints resolution outcome; Complaints resolution time</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -6515,55 +6515,55 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Suitability</t>
+          <t>Complaints handling, Safety and security</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D119">
-        <v>103</v>
+        <v>322</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Borrowers whose collateral was seized</t>
+          <t>Fraud prevalence in complaints</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>% of borrowers whose collateral was seized</t>
+          <t>Portion and volume of complaints received by providers, regulators, and ombuds that are fraud-related.</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>A measure of loan portfolio/credit risk assessment quality or financial distress among borrowers. !- Data requirements: Granular data that can yield (1) A count of unique borrowers of secured loans (those with collateral requirements) who subsequently had collateral seized by lender due to default over a specific period of time (e.g. past quarter or past year), (2) Total unique borrowers of secured loans over a specific period of time.</t>
+          <t>Tracks how much of the complaint landscape is driven by fraud—both the count (volume) and the share (portion) of total complaints. Rising prevalence of frauds signals elevated customer harm, control weaknesses (KYC/AML, authentication, data security), or new attack vectors (social engineering). It helps guide supervision, consumer protection responses, reimbursement policies, and investment in fraud controls. !- Definitions and concepts: Fraud-related complaint: a case alleging unauthorised or deceptive activity resulting in loss or attempted loss—e.g., account takeover, card-not-present, phishing/SMiShing, SIM-swap, mule accounts, synthetic identity, merchant fraud, insider abuse, and authorised push payment (APP) scams. Volume: number of fraud-related complaints received in the period. Share: [# of fraud complaints / # of all complaints] x 100%. Intensity companions: fraud complaints per 1,000 customers or per 1 million transactions, value lens using claimed or confirmed loss amounts. Outcome cuts: upheld rate, reimbursement rate, median loss, time-to-resolution. A standard taxonomy for fraud types is needed, including the differentiation between fraud and disputed transaction. !- Limitations and considerations:  Under-reporting: many victims never complain or only contact the bank—triangulate with dispute/chargeback data and incident logs.</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>How does the share of customers whose collateral was seized due to default vary by gender and othe rkey sociodemographics? Are women more or less likely than men to have their collateral seized following loan default? How does the share differ by gender across different loan sizes, loan products,  types of financial service providers (FSP), collateral type (e.g., movable, immovable, alternative)? And how do any of these differences relate to seizure rates? Are women more likely to be subject to stricter collateral requirements or less flexible repayment terms that increase the likelihood of asset seizure?</t>
+          <t>Are there gender differences in the proportion of fraud-related complaints submitted to providers, regulators, or ombuds services?  Do individuals of different genders tend to report different types of fraud, such as identity theft, phishing, or agent misconduct, and are specific delivery channels more commonly associated with these complaints? Is the volume of fraud-related complaints disproportionately high among certain gender groups when compared to their levels of account ownership or usage? Do complaint resolution rates and timeframes differ by gender across various FSP or reporting channels?</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Outcomes, Credit risk</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Loan type; Collateral type; Loan size; Loan term; Interest rate category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints resolution outcome; Complaints resolution time</t>
         </is>
       </c>
     </row>
@@ -6575,55 +6575,55 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Complaints handling</t>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D120">
-        <v>239</v>
+        <v>103</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Customer complaints (number)</t>
+          <t>Borrowers whose collateral was seized</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Number of customer complaints (including processing status, channels, type)</t>
+          <t>% of borrowers whose collateral was seized</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>This indicator tallies the formal expressions of dissatisfaction that retail or MSME clients lodge with a financial-service provider (or an external ombudsman) about products, services, or staff conduct over a specified period and can be normalized by dividing by the customer basis to obtain an intensity metric (e.g. complaints per 1,000 active customers). A rising complaint count can signal service-quality gaps, mis-selling, opaque fees, or inadequate disclosure—issues that erode trust and may escalate into regulatory sanctions or litigation. Supervisors can track both the absolute number and complaint-to-account ratios to test consumer-protection frameworks, prioritise thematic reviews, and assess whether rapid product roll-outs (e.g., digital lending, mobile wallets) are being matched by robust after-sales support. Where granular data or more detailed reporting templates permit, customer complaints can be disaggregated by processing status (e.g. received, accepted/rejected, in process, resolved, escalated/disputed, withdrawn), product (e.g. consumer loan, deposit account, etc), channel (e.g. digital, phone, in-person), issue category (e.g. fraudulent or unauthorized transactions, unfair treatment, unexpected fees, errors on statements,  etc.), resolution status (open, resolved with monetary compensation, resolved without compensation, escalated to ombudsman/regulator, other). Combined with resolution-time, compensation and other metrics, the number of customer complaints provides a critical, early-warning lens on conduct risk and customer-experience health. !- Definitions and concepts:  Complaints are expressions of dissatisfaction by (or on behalf of) customers that are related to their experiences with FSPs and can include any written, digital or recorded verbal statement made through any available channel, such as a branch, call-centre, email, social media, chatbots and other portals. Complaints may relate to the quality of a product or service, treatment by an FSP (including its agents and other third parties), or suspected wrongdoing. Complaints are different from general inquiries (e.g., where can I find an ATM?) or legal disputes between parties that may require formal dispute resolution. For more information, see for example CGAP's toolkit on using complaints data for market conduct supervision: https://www.cgap.org/research/publication/market-monitoring-tool-analysis-complaints-data and the Alliance for Financial Inclusion's framework on 'Complaint handling in Central Banks': https://www.afi-global.org/sites/default/files/publications/2020-04/AFI_CEMC_framework_AW_digital%20v2.pdf. !- Data requirements:  Database or log of customer complaints, detailing date of complaint and additional information, such as channel through which complaint was lodged, associated product or account, details or brief description of the complaint, and resolution status. !- Limitations and considerations: Complaints processes differ across FSPs in terms of steps/levels for routing, hand-over, escalations to higher management levels and to external ombudsman. Customer details and demographics of complainants are not always capture/stored on FSPs' systems, or may be stored in fragmented data bases. Complaints logged at aggregator sites/portals may not request customer demographics. Limited to officially logged complaints and/or maintaining records of inbound customer communications. Dependent on having electronic complaints management system.  Reporting culture: firms with easy‐to‐use channels may record more complaints than peers, even if service quality is similar—benchmark using severity and uphold rates. Under-reporting bias: vulnerable customers may forgo formal complaints; mystery-shopping and survey data can complement administrative counts. Duplicate cases: the same issue voiced through multiple channels can inflate totals unless robust deduplication exists. Product mix effects: complaint propensity varies—e.g., complex investments draw more grievances than basic savings; segment analysis is essential. Regulatory divergence: definitions and mandatory reporting thresholds differ across jurisdictions, complicating cross-border comparisons.</t>
+          <t>A measure of loan portfolio/credit risk assessment quality or financial distress among borrowers. !- Data requirements: Granular data that can yield (1) A count of unique borrowers of secured loans (those with collateral requirements) who subsequently had collateral seized by lender due to default over a specific period of time (e.g. past quarter or past year), (2) Total unique borrowers of secured loans over a specific period of time.</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>How does the number of complaints at each processing stage vary by gender? Are complaints disproportionately concentrated at certain processing stages for any gender? How do FSPs compare to market averages in the number of complaints at each processing stage?"</t>
+          <t>How does the share of customers whose collateral was seized due to default vary by gender and other key sociodemographic of the customer or MSME owner? Are women/WMSME more or less likely than men to have their collateral seized following loan default? How does the share differ by gender across different loan sizes, loan products,  types of financial service providers (FSP), collateral type (e.g., movable, immovable, alternative)? And how do any of these differences relate to seizure rates? Are women more likely to be subject to stricter collateral requirements or less flexible repayment terms that increase the likelihood of asset seizure?</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Outcomes, Credit risk</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints filing channel; Complaints issue category; Complaints processing status; Complaints resolution outcome; Complaints resolution time</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Loan type; Collateral type; Loan size; Loan term; Interest rate category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -6644,31 +6644,31 @@
         </is>
       </c>
       <c r="D121">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Customer complaints resolved in the customer's favor</t>
+          <t>Customer complaints (number)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>% of customer complaints that were solved in the customer's favor in the most recent period</t>
+          <t>Number of customer complaints (including processing status, channels, type)</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>This indicator shows the share of complaints closed in the reference period that were resolved in the customer’s favor. It is a direct outcome metric for fair treatment and service quality. A higher “uphold rate” can indicate strong remediation and customer-centric policies; a very low rate may suggest poor triage, overly narrow eligibility rules, or weak guidance to customers on evidence requirements. Supervisors use it to benchmark conduct outcomes across firms and products; boards track it alongside complaint volumes and resolution times to target root-cause fixes. Tracked with complaint volume, resolution time, and compensation totals, this indicator provides a balanced view of consumer outcomes and conduct risk. !- Definitions and concepts: Resolved in the customer’s favor (upheld): final decision grants redress—monetary (refund/compensation/fee reversal) or non-monetary (policy correction, contract change, apology with tangible remedy). Many firms also count partially upheld cases; disclose whether partials are included. Denominator: all complaints closed in the period. Segment results by product, channel, and severtiy to avoid masking problem areas. !- Data requirements: Central complaint-management records with unique IDs, receipt date, closure date, product, channel, allegation type, decision outcome (upheld/partially/declined), and compensation amount. Deduplication logic across channels; linkages to ombudsman/regulator portals for escalations and reversals. Customer-base denominator (for intensity metrics) and service level agreement (SLA) timestamps for parallel monitoring* (see note below). !- Limitations and considerations: Classification discretion: definitions of “partial uphold” vary; publish inclusion rules. Case mix effects: a surge in low-merit mass claims can depress the percentage; report severity-adjusted or line-of-business cuts. Gaming risk: chasing high uphold rates may encourage paying weak claims; pair with fraud flags, root-cause fixes, and cost-per-case. Timing bias: complex cases close later and differ in uphold propensity; use rolling averages and track median resolution time. External outcomes: include overturned-on-appeal adjustments to reflect true customer outcome. *With granular time-stamped complaints data, timeliness of key milestones in the complaints resolution process can be tracked, for example time to acknowledge complaint, time to first response, time to resolution. With this data, supervisors can track not just outcomes, but also whether providers are meeting required timeframes per their own SLA.</t>
+          <t>This indicator tallies the formal expressions of dissatisfaction that retail or MSME clients lodge with a financial-service provider (or an external ombudsman) about products, services, or staff conduct over a specified period and can be normalized by dividing by the customer basis to obtain an intensity metric (e.g. complaints per 1,000 active customers). A rising complaint count can signal service-quality gaps, mis-selling, opaque fees, or inadequate disclosure—issues that erode trust and may escalate into regulatory sanctions or litigation. Supervisors can track both the absolute number and complaint-to-account ratios to test consumer-protection frameworks, prioritise thematic reviews, and assess whether rapid product roll-outs (e.g., digital lending, mobile wallets) are being matched by robust after-sales support. Where granular data or more detailed reporting templates permit, customer complaints can be disaggregated by processing status (e.g. received, accepted/rejected, in process, resolved, escalated/disputed, withdrawn), product (e.g. consumer loan, deposit account, etc), channel (e.g. digital, phone, in-person), issue category (e.g. fraudulent or unauthorized transactions, unfair treatment, unexpected fees, errors on statements,  etc.), resolution status (open, resolved with monetary compensation, resolved without compensation, escalated to ombudsman/regulator, other). Combined with resolution-time, compensation and other metrics, the number of customer complaints provides a critical, early-warning lens on conduct risk and customer-experience health. !- Definitions and concepts:  Complaints are expressions of dissatisfaction by (or on behalf of) customers that are related to their experiences with FSPs and can include any written, digital or recorded verbal statement made through any available channel, such as a branch, call-centre, email, social media, chatbots and other portals. Complaints may relate to the quality of a product or service, treatment by an FSP (including its agents and other third parties), or suspected wrongdoing. Complaints are different from general inquiries (e.g., where can I find an ATM?) or legal disputes between parties that may require formal dispute resolution. For more information, see for example CGAP's toolkit on using complaints data for market conduct supervision: https://www.cgap.org/research/publication/market-monitoring-tool-analysis-complaints-data and the Alliance for Financial Inclusion's framework on 'Complaint handling in Central Banks': https://www.afi-global.org/sites/default/files/publications/2020-04/AFI_CEMC_framework_AW_digital%20v2.pdf. !- Data requirements:  Database or log of customer complaints, detailing date of complaint and additional information, such as channel through which complaint was lodged, associated product or account, details or brief description of the complaint, and resolution status. !- Limitations and considerations: Complaints processes differ across FSPs in terms of steps/levels for routing, hand-over, escalations to higher management levels and to external ombudsman. Customer details and demographics of complainants are not always capture/stored on FSPs' systems, or may be stored in fragmented data bases. Complaints logged at aggregator sites/portals may not request customer demographics. Limited to officially logged complaints and/or maintaining records of inbound customer communications. Dependent on having electronic complaints management system.  Reporting culture: firms with easy‐to‐use channels may record more complaints than peers, even if service quality is similar—benchmark using severity and uphold rates. Under-reporting bias: vulnerable customers may forgo formal complaints; mystery-shopping and survey data can complement administrative counts. Duplicate cases: the same issue voiced through multiple channels can inflate totals unless robust deduplication exists. Product mix effects: complaint propensity varies—e.g., complex investments draw more grievances than basic savings; segment analysis is essential. Regulatory divergence: definitions and mandatory reporting thresholds differ across jurisdictions, complicating cross-border comparisons.</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>How do the percentages of complaints resolved in favor of customers vary by gender? Are any genders more likely to receive favorable resolutions? How do FSPs rank in terms of favorable resolutions by gender?</t>
+          <t>How does the number of complaints at each processing stage vary by gender? Are complaints disproportionately concentrated at certain processing stages for any gender? How do FSPs compare to market averages in the number of complaints at each processing stage?"</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Data privacy and protection</t>
+          <t>Complaints handling</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6704,31 +6704,31 @@
         </is>
       </c>
       <c r="D122">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Consent rate for FSP contact</t>
+          <t>Customer complaints resolved in the customer's favor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>% of customers who provide consent to be contacted in the future by the FSP for sales, awareness and new offerings</t>
+          <t>% of customer complaints that were solved in the customer's favor in the most recent period</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Measures the percentage of customers who have provided explicit consent to be contacted in the future by their financial service provider (FSP) for purposes such as product marketing, customer awareness campaigns, or information on new offerings. This indicator reflects how institutions manage customer permissions for communication under applicable data privacy and marketing regulations. Captures the extent of customer consent and data-use transparency in the financial system, serving as a proxy for compliance with consent-based communication standards and the balance between customer engagement and data protection. Tracking customer contact consents helps regulators and providers: Monitor compliance with data protection and privacy laws (e.g., GDPR-like frameworks, data protection acts); Assess ethical marketing practices and responsible customer engagement; Evaluate trust and willingness of customers to maintain open communication with FSPs; Understand customer attitudes toward data sharing and digital outreach. For supervisors, it provides a measurable view of market conduct, customer empowerment, and institutional transparency. High consent rates suggest strong customer trust and engagement, but may require close monitoring to ensure non-coercive consent collection and ethical marketing practices. Low consent rates may reflect privacy concerns, limited digital literacy, or overly complex consent processes. Changes over time can signal shifts in consumer sentiment or compliance practices following new regulations. !- Definitions and concepts: Consent: A freely given, informed, and specific agreement by a customer allowing the FSP to contact them for defined purposes. Data privacy regulation: Legal framework governing the collection, storage, and use of personal data, including consent requirements for marketing communications. !- Data requirements: Administrative data from FSP customer relationship management (CRM) or consent-management systems to obtain the number of customers who provided consent to be contact and the total number of customers.</t>
+          <t>This indicator shows the share of complaints closed in the reference period that were resolved in the customer’s favor. It is a direct outcome metric for fair treatment and service quality. A higher “uphold rate” can indicate strong remediation and customer-centric policies; a very low rate may suggest poor triage, overly narrow eligibility rules, or weak guidance to customers on evidence requirements. Supervisors use it to benchmark conduct outcomes across firms and products; boards track it alongside complaint volumes and resolution times to target root-cause fixes. Tracked with complaint volume, resolution time, and compensation totals, this indicator provides a balanced view of consumer outcomes and conduct risk. !- Definitions and concepts: Resolved in the customer’s favor (upheld): final decision grants redress—monetary (refund/compensation/fee reversal) or non-monetary (policy correction, contract change, apology with tangible remedy). Many firms also count partially upheld cases; disclose whether partials are included. Denominator: all complaints closed in the period. Segment results by product, channel, and severtiy to avoid masking problem areas. !- Data requirements: Central complaint-management records with unique IDs, receipt date, closure date, product, channel, allegation type, decision outcome (upheld/partially/declined), and compensation amount. Deduplication logic across channels; linkages to ombudsman/regulator portals for escalations and reversals. Customer-base denominator (for intensity metrics) and service level agreement (SLA) timestamps for parallel monitoring* (see note below). !- Limitations and considerations: Classification discretion: definitions of “partial uphold” vary; publish inclusion rules. Case mix effects: a surge in low-merit mass claims can depress the percentage; report severity-adjusted or line-of-business cuts. Gaming risk: chasing high uphold rates may encourage paying weak claims; pair with fraud flags, root-cause fixes, and cost-per-case. Timing bias: complex cases close later and differ in uphold propensity; use rolling averages and track median resolution time. External outcomes: include overturned-on-appeal adjustments to reflect true customer outcome. *With granular time-stamped complaints data, timeliness of key milestones in the complaints resolution process can be tracked, for example time to acknowledge complaint, time to first response, time to resolution. With this data, supervisors can track not just outcomes, but also whether providers are meeting required timeframes per their own SLA.</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>How do consent rates for customer contact vary by gender? Are any genders more likely to provide consent to be contacted? How do FSPs rank in terms of consent rates by gender?</t>
+          <t>How do the percentages of complaints resolved in favor of customers vary by gender? Are any genders more likely to receive favorable resolutions? How do FSPs rank in terms of favorable resolutions by gender?</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Complaints filing channel; Complaints issue category; Complaints processing status; Complaints resolution outcome; Complaints resolution time</t>
         </is>
       </c>
     </row>
@@ -6755,28 +6755,88 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
+          <t>Data privacy and protection</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D123">
+        <v>234</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Consent rate for FSP contact</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>% of customers who provide consent to be contacted in the future by the FSP for sales, awareness and new offerings</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Measures the percentage of customers who have provided explicit consent to be contacted in the future by their financial service provider (FSP) for purposes such as product marketing, customer awareness campaigns, or information on new offerings. This indicator reflects how institutions manage customer permissions for communication under applicable data privacy and marketing regulations. Captures the extent of customer consent and data-use transparency in the financial system, serving as a proxy for compliance with consent-based communication standards and the balance between customer engagement and data protection. Tracking customer contact consents helps regulators and providers: Monitor compliance with data protection and privacy laws (e.g., GDPR-like frameworks, data protection acts); Assess ethical marketing practices and responsible customer engagement; Evaluate trust and willingness of customers to maintain open communication with FSPs; Understand customer attitudes toward data sharing and digital outreach. For supervisors, it provides a measurable view of market conduct, customer empowerment, and institutional transparency. High consent rates suggest strong customer trust and engagement, but may require close monitoring to ensure non-coercive consent collection and ethical marketing practices. Low consent rates may reflect privacy concerns, limited digital literacy, or overly complex consent processes. Changes over time can signal shifts in consumer sentiment or compliance practices following new regulations. !- Definitions and concepts: Consent: A freely given, informed, and specific agreement by a customer allowing the FSP to contact them for defined purposes. Data privacy regulation: Legal framework governing the collection, storage, and use of personal data, including consent requirements for marketing communications. !- Data requirements: Administrative data from FSP customer relationship management (CRM) or consent-management systems to obtain the number of customers who provided consent to be contact and the total number of customers.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>How do consent rates for customer contact vary by gender? Are any genders more likely to provide consent to be contacted? How do FSPs rank in terms of consent rates by gender?</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D123">
+      <c r="D124">
         <v>284</v>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>Annual percentage rate (APR) for retail credit</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>Average cost of borrowing money, including fees to get the loan, as a% of the loan principal (except for credit cards)</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>APR is the standardized annualized cost of borrowing that incorporates the contractual interest rate plus certain up-front or periodic fees required to obtain and maintain the credit. It lets consumers compare offers across lenders and products on a like-for-like basis, and helps supervisors monitor pricing fairness and market competitiveness. Unlike a simple “nominal” rate, APR reflects timing of cash flows and required charges, so it better approximates the true price of credit. !- Definitions and concepts: Installment credit APR (actuarial method): the internal rate of return (IRR) that equates the amount advanced to the borrower with the present value of all required payments (principal, interest, and included fees), expressed on an annual basis.
 Revolving credit APR (cards/overdrafts): the periodic rate applied to the average daily balance, annualized (e.g., daily rate × 365 or monthly rate × 12), plus disclosure of any mandatory fees as prescribed. Scope of fees: typically includes origination/processing fees and compulsory charges; excludes penalty fees and optional add-ons (unless mandated). APR vs. EIR: APR is a consumer disclosure metric (jurisdiction-specific rules); EIR is an accounting yield used to recognize interest income.!- Data requirements: Contract terms: principal advanced, repayment schedule (dates/amounts), nominal rate, compounding frequency, and variable-rate index/margins. Included fees: origination/processing, mandatory maintenance or platform fees, financed vs. paid-in-cash. For revolving products: periodic rate(s), balance computation method (average daily balance), mandatory annual fees, grace-period rules, promotional/teaser rates.
@@ -6784,89 +6844,29 @@
 Promotions &amp; step-ups: teaser or deferred-interest offers can make snapshot APRs unrepresentative—show lifetime-effective examples when possible. Variable rates: APR at origination may understate future cost if reference rates rise. Loan term effects: fixed fees loom larger on short tenors; present both APR and the fee share of cost for transparency.</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="H124" t="inlineStr">
         <is>
           <t>Are there gender disparities in the APR applied to loans disbursed to women and men, including MSMEs by gender of ownership? Do women borrowers systematically face higher average APRs than men within the same loan type, amount range, or provider category? Are higher APRs for women associated with smaller loan sizes, shorter maturities, or higher perceived credit risk? Do FSPs with greater gender diversity or stronger inclusion policies show smaller gender gaps in average APRs? How do APR differences relate to borrower profiles and do they suggest the presence of gender-based pricing bias or structural credit segmentation?</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
         <is>
           <t>Financial inclusion; Market development</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="K124" t="inlineStr">
         <is>
           <t>Quality, Competition</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Data privacy and protection</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D124">
-        <v>235</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Consents for sharing data with third-parties</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>% of customers who have given explicit consent for their data to be shared by FSPs with third parties, for various purposes</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>This indicator shows how many customers have actively opted in to let a financial service provider (FSP) share their data with external parties—for open-banking/aggregation, credit scoring, fraud prevention, marketing, analytics, etc. A higher share can reflect strong digital adoption and trust; low or falling rates may signal poor consent UX, unclear value propositions, or privacy concerns. It helps compliance teams evidence lawfulness, product teams gauge partner-integration reach, and supervisors assess the maturity of consent-based data-sharing ecosystems. !- Definitions and concepts: Explicit consent: a clear, affirmative action (e.g., checked box, strong-customer-authenticated authorization) tied to a specific purpose, with intelligible notice and the ability to withdraw at any time. Active consent: consent that is valid as of the reference date (not expired, not withdrawn, not superseded). Purpose taxonomy: e.g., account information services (AIS), payment initiation services (PIS), credit decisioning/bureau pulls, fraud/AML tools, personalised marketing, data portability. Metric: % of customer with active consent for purpose p = [# of unique customers with at least 1 active consent for p / # of active customers] x 100%. Indicator companions: Any-purpose consent, consents per consenting customer and revocation rate. !- Data requirements: Consent ledger that includes: customer ID, purpose(s) granted, third-party identity, channel, timestamp, expiry/refresh cycle, version of the privacy notice, proof of consent (hash, audit trail, SCA event). Status events: withdrawals, expiries, scope changes, third-party disconnects. Reference universe: deduplicated active-customer list (define “active”: e.g., ≥1 product in force or ≥1 login/transaction in last 12 months). !- Limitations and considerations: Granularity &amp; fragmentation: a customer may consent per app, per account, and per purpose; avoid double counting by using unique customers and report purpose-level cuts. Expiry &amp; refresh: open-banking tokens often have short authorizations; snapshot dates vs. rolling windows will yield different figures—disclose method. Consumer protection risk: high opt-ins driven by coercive UX can backfire (complaints, revocations); pair with revocation rate, time-to-revocation, and complaints about data sharing. Coverage gaps: legacy channels without digital capture may under-record historical consents; backfill or disclose limitations.</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>How do consent rates for data sharing with third parties vary by gender? Are any genders more likely to provide consent for data sharing? How do FSPs rank in terms of consent rates for data sharing by gender?</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>Market development</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -6878,55 +6878,55 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Fair treatment</t>
+          <t>Data privacy and protection</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D125">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Late penalty charges/fees on retail credit</t>
+          <t>Consents for sharing data with third-parties</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Income from penalty fees as % of total net interest income</t>
+          <t>% of customers who have given explicit consent for their data to be shared by FSPs with third parties, for various purposes</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>This indicator shows how much of a lender is relying on penalty fees for income. Revenue from penalty fees and other charges applied when a loan payment is late is compared with the total gross interest income. A high share could signal borrower stress and potential conduct risk (reliance on punitive pricing). Boards and supervisors use the metric to assess earnings quality, pricing fairness. !- Definitions and concepts: Penalty/default fees and charges: the fees and costs charged once a loan  is past due. Numerator (preferred “incremental” view): Penalty actually recognized as income on retail loans during the period. Denominator: Gross interest income. !- Data requirements: General-ledger mapping that identifies penalty income at product level. Period interest income totals for the denominator.  !- Limitations and considerations: Mix effects: card-heavy books show higher shares of penalty income; segment by product. Conduct lens: pair with % customers incurring penalty charges, related complaints.</t>
+          <t>This indicator shows how many customers have actively opted in to let a financial service provider (FSP) share their data with external parties—for open-banking/aggregation, credit scoring, fraud prevention, marketing, analytics, etc. A higher share can reflect strong digital adoption and trust; low or falling rates may signal poor consent UX, unclear value propositions, or privacy concerns. It helps compliance teams evidence lawfulness, product teams gauge partner-integration reach, and supervisors assess the maturity of consent-based data-sharing ecosystems. !- Definitions and concepts: Explicit consent: a clear, affirmative action (e.g., checked box, strong-customer-authenticated authorization) tied to a specific purpose, with intelligible notice and the ability to withdraw at any time. Active consent: consent that is valid as of the reference date (not expired, not withdrawn, not superseded). Purpose taxonomy: e.g., account information services (AIS), payment initiation services (PIS), credit decisioning/bureau pulls, fraud/AML tools, personalised marketing, data portability. Metric: % of customer with active consent for purpose p = [# of unique customers with at least 1 active consent for p / # of active customers] x 100%. Indicator companions: Any-purpose consent, consents per consenting customer and revocation rate. !- Data requirements: Consent ledger that includes: customer ID, purpose(s) granted, third-party identity, channel, timestamp, expiry/refresh cycle, version of the privacy notice, proof of consent (hash, audit trail, SCA event). Status events: withdrawals, expiries, scope changes, third-party disconnects. Reference universe: deduplicated active-customer list (define “active”: e.g., ≥1 product in force or ≥1 login/transaction in last 12 months). !- Limitations and considerations: Granularity &amp; fragmentation: a customer may consent per app, per account, and per purpose; avoid double counting by using unique customers and report purpose-level cuts. Expiry &amp; refresh: open-banking tokens often have short authorizations; snapshot dates vs. rolling windows will yield different figures—disclose method. Consumer protection risk: high opt-ins driven by coercive UX can backfire (complaints, revocations); pair with revocation rate, time-to-revocation, and complaints about data sharing. Coverage gaps: legacy channels without digital capture may under-record historical consents; backfill or disclose limitations.</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>What percentages of net interest income are attributable to penalties and other punitive charges earned from borrowers of unsecured loans/lines of credit, and how do these vary by gender across age bands and location types, at a total market level and by relevant FSP/type? How do these percentages compare across relevant FSPs/types and against market norms across age bands and location types? How do gender disparities manifest in these percentages at a total market level and by relevant FSP/type?</t>
+          <t>How do consent rates for data sharing with third parties vary by gender? Are any genders more likely to provide consent for data sharing? How do FSPs rank in terms of consent rates for data sharing by gender?</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Market development</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -6947,108 +6947,108 @@
         </is>
       </c>
       <c r="D126">
+        <v>260</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Late penalty charges/fees on retail credit</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Income from penalty fees as % of total net interest income</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>This indicator shows how much of a lender is relying on penalty fees for income. Revenue from penalty fees and other charges applied when a loan payment is late is compared with the total gross interest income. A high share could signal borrower stress and potential conduct risk (reliance on punitive pricing). Boards and supervisors use the metric to assess earnings quality, pricing fairness. !- Definitions and concepts: Penalty/default fees and charges: the fees and costs charged once a loan  is past due. Numerator (preferred “incremental” view): Penalty actually recognized as income on retail loans during the period. Denominator: Gross interest income. !- Data requirements: General-ledger mapping that identifies penalty income at product level. Period interest income totals for the denominator.  !- Limitations and considerations: Mix effects: card-heavy books show higher shares of penalty income; segment by product. Conduct lens: pair with % customers incurring penalty charges, related complaints.</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>What percentages of net interest income are attributable to penalties and other punitive charges earned from borrowers of unsecured loans/lines of credit, and how do these vary by gender across age bands and location types, at a total market level and by relevant FSP/type? How do these percentages compare across relevant FSPs/types and against market norms across age bands and location types? How do gender disparities manifest in these percentages at a total market level and by relevant FSP/type?</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Fair treatment</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="D127">
         <v>185</v>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E127" t="inlineStr">
         <is>
           <t>Processing and application fees or PAF (as % of loan principal)</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>PAF as % of loan principal in unsecured credit operations</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>This indicator expresses the total up-front charges borrowers pay to originate an unsecured loan—processing fees, application fees, documentation charges—as a percentage of the loan’s principal amount. Because unsecured credit often targets price-sensitive segments and carries higher risk-based interest rates, excessive PAFs can materially raise the all-in cost of borrowing, undermine affordability tests, and trigger consumer-protection scrutiny. Tracking the ratio helps regulators detect predatory pricing, compare lenders’ transparency practices, and gauge competition in loan-origination services. For lenders, it is a barometer of non-interest revenue reliance and a lever for recouping acquisition costs. Processing &amp; Application Fees (PAF): any non-refundable charge levied at or before disbursement for administrative tasks (credit checks, KYC, documentation, platform usage). Late-payment or insurance fees are excluded.
 PAF ratio (simple): [Total PAF charged/Gross loan principal]×100%
 Where multiple partial disbursements occur, use the aggregate principal amount. Annualised impact: when PAFs are capitalised into the Effective Annual Percentage Rate (APR), their weight declines as term length rises—monitor both absolute and APR-embedded views. !- Data requirements: Loan-level records capturing principal, disbursement date, PAF amount, and any rebates for cancellations. Product codes distinguishing personal instalment loans, credit-card cash advances, payday/BNPL equivalents. Borrower demographics and channel identifiers (branch, mobile app, marketplace) for segmentation. Accounting entries showing whether fees are recognised up-front (IFRS 15 “contract costs”) or amortised via the effective-interest-rate (EIR) method. !- Limitations and considerations: Amortisation differences: Lenders using EIR spread PAFs over the loan’s life; comparing ratios on a cash basis versus amortised income can mislead. Bundled products: Cross-selling (e.g., credit-life insurance) may shift income from PAF to commissions, understating the ratio. Regulatory caps &amp; disclosures: Jurisdictions with fee ceilings or mandatory APR disclosures compress PAF ratios; cross-country benchmarking must control for such rules. Loan term effects: Short-tenor payday or BNPL loans show high PAF percentages even when absolute fees are small; interpret in context of maturity profile and APR. Waivers &amp; promotions: Temporary fee holidays for marketing campaigns can distort time-series trends—flag promotional periods separately. Should FSPs not be allowed/willing to share sensitive revenue data, ratios/percentages can be performed in-house and then shared with regulator.</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>What are the origination fee percentages as a share of loan principal by gender? Are there gender disparities in the origination fee percentages incurred? How do FSPs rank in terms of origination fee percentages by gender?</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
+      <c r="L127" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Data privacy and protection</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D127">
-        <v>232</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Data breaches</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>% of customers affected by data breaches</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>A measure of the depth of cyberattacks or other data security breach that result in unauthorized access to customer data. Definitions and concept: A data breach is any security incident in which unauthorized parties access sensitive or confidential information, including personal data (tax numbers, ID information, bank account numbers, healthcare data) and corporate data (customer records, intellectual property, financial information). Data requirement: Number of customers whose data was accessed without authorization during a specified period of time (e.g. quarter or year); Total number of customers at the beginning of the specified period (e.g. quarter or year).</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>How does the percentage of customers affected by data breaches vary by gender? Are any genders disproportionately affected by data breaches? Are data breaches more frequent in certain types of FSPs? Are data breaches more common in specific channels or interfaces?"</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>Quality, Operational risk</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -7060,55 +7060,55 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Depositor protection</t>
+          <t>Data privacy and protection</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Savings</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D128">
-        <v>15</v>
+        <v>232</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Deposit accounts covered by direct deposit insurance</t>
+          <t>Data breaches</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Volume and value (balances) of deposit accounts covered by direct deposit insurance</t>
+          <t>% of customers affected by data breaches</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>This indicator counts (or expresses as a percentage) the deposit accounts that fall within the scope of an explicit, statutory deposit insurance scheme (DIS) or deposit guarantee fund. It helps supervisors gauge how much of the retail/MSME funding base is protected against bank failure. This is key for financial stability monitoring, payout readiness, and for calibrating the deposit insurance/guarantee fund. High coverage supports confidence and can dampen run dynamics. Source: https://www.iadi.org/uploads/cprevised2014nov.pdf. !- Definitions and concepts: Covered (eligible) account: a deposit type included by law. Fully insured vs. partially insured: “Fully insured” balances are ≤ the coverage limit per depositor, per bank, per ownership category; “covered/eligible” may include accounts whose balances exceed the cap (partially insured). Ownership categories: individual, joint, trust/fiduciary, retirement—rules vary by jurisdiction and affect aggregation across accounts. Indicator variants: % Eligible accounts = eligible deposit accounts ÷ total deposit accounts. Insured balance share = insured amounts in eligible accounts ÷ total deposit balances in eligible accounts. Dormancy: dormant accounts may be treated differently in coverage statistics.</t>
+          <t>A measure of the depth of cyberattacks or other data security breach that result in unauthorized access to customer data. Definitions and concept: A data breach is any security incident in which unauthorized parties access sensitive or confidential information, including personal data (tax numbers, ID information, bank account numbers, healthcare data) and corporate data (customer records, intellectual property, financial information). Data requirement: Number of customers whose data was accessed without authorization during a specified period of time (e.g. quarter or year); Total number of customers at the beginning of the specified period (e.g. quarter or year).</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the number of deposit accounts covered by direct deposit insurance? How do these disparities vary by age, income level, and geographic location? Are certain gender groups, especially within vulnerable or low-income populations, less likely to hold insured deposit accounts? How do the average insured deposit account balances differ across genders, and what might this indicate about savings behavior, access to financial protection, or economic security? Do financial service providers with higher levels of gender diversity in leadership or staff tend to offer more equitable access to insured deposit accounts and balanced coverage across genders? Additionally, how do gender differences in insured deposit accounts relate to broader financial inclusion and resilience against financial shocks?</t>
+          <t>How does the percentage of customers affected by data breaches vary by gender? Are any genders disproportionately affected by data breaches? Are data breaches more frequent in certain types of FSPs? Are data breaches more common in specific channels or interfaces?"</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection</t>
+          <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Quality, Suitability</t>
+          <t>Quality, Operational risk</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Deposit account type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -7129,19 +7129,79 @@
         </is>
       </c>
       <c r="D129">
+        <v>15</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Deposit accounts covered by direct deposit insurance</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Volume and value (balances) of deposit accounts covered by direct deposit insurance</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>This indicator counts (or expresses as a percentage) the deposit accounts that fall within the scope of an explicit, statutory deposit insurance scheme (DIS) or deposit guarantee fund. It helps supervisors gauge how much of the retail/MSME funding base is protected against bank failure. This is key for financial stability monitoring, payout readiness, and for calibrating the deposit insurance/guarantee fund. High coverage supports confidence and can dampen run dynamics. Source: https://www.iadi.org/uploads/cprevised2014nov.pdf. !- Definitions and concepts: Covered (eligible) account: a deposit type included by law. Fully insured vs. partially insured: “Fully insured” balances are ≤ the coverage limit per depositor, per bank, per ownership category; “covered/eligible” may include accounts whose balances exceed the cap (partially insured). Ownership categories: individual, joint, trust/fiduciary, retirement—rules vary by jurisdiction and affect aggregation across accounts. Indicator variants: % Eligible accounts = eligible deposit accounts ÷ total deposit accounts. Insured balance share = insured amounts in eligible accounts ÷ total deposit balances in eligible accounts. Dormancy: dormant accounts may be treated differently in coverage statistics.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in the number of deposit accounts covered by direct deposit insurance? How do these disparities vary by age, income level, and geographic location? Are certain gender groups, especially within vulnerable or low-income populations, less likely to hold insured deposit accounts? How do the average insured deposit account balances differ across genders, and what might this indicate about savings behavior, access to financial protection, or economic security? Do financial service providers with higher levels of gender diversity in leadership or staff tend to offer more equitable access to insured deposit accounts and balanced coverage across genders? Additionally, how do gender differences in insured deposit accounts relate to broader financial inclusion and resilience against financial shocks?</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Quality, Suitability</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Deposit account type</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Depositor protection</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Savings</t>
+        </is>
+      </c>
+      <c r="D130">
         <v>16</v>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>G2P accounts covered by deposit insurance</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>% of all accounts receiving G2P payments that are covered by deposit protection</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>This indicator helps analyze the extent to which low-value accounts are covered by deposit insurance or other protection. It focuses on account holders who are recipients of G2P programs. It quantifies how many of the government-to-person (G2P) payments recipients are protected by an explicit deposit insurance scheme or guarantee fund. It can be shown as (a) the share of G2P accounts that are eligible/fully insured and/or (b) the insured share of G2P balances. This indicator informs strategies for insurance/coverage payouts and the calibration of the deposit insurance fund. Definitions  and concepts: G2P account: an account that receives social transfers, government pensions, subsidies, or cash-benefit programs.
 Covered (eligible) vs. fully insured: “Eligible” products fall within the deposit insurance scope; “fully insured” means the balance per beneficiary per insured bank does not exceed the coverage cap. 
@@ -7150,197 +7210,137 @@
 Core-banking (and, where applicable, e-money) extracts: product code, ownership category, end-of-day balance, currency. Rules engine encoding national deposit-insurance scope, limits, and aggregation logic (per depositor—per bank). Sub-ledger data for pooled/FBO accounts to support pass-through eligibility. Timing sensitivity: balances spike on disbursement days; define the snapshot (e.g., month-end vs. T+2 after payout).</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="H130" t="inlineStr">
         <is>
           <t>Are there gender disparities in the number of G2P accounts covered by deposit insurance? How do these disparities vary across different age groups, income levels, and geographic locations? Are women and other gender groups within vulnerable populations less likely to have G2P accounts that are insured, potentially affecting their financial security? How do the average balances of insured G2P accounts compare across genders, and what does this imply about economic empowerment and financial resilience? Do government programs and financial service providers with greater gender diversity in design or delivery show more equitable insurance coverage of G2P accounts? Additionally, how do gender differences in insured G2P accounts influence overall inclusion and access to social safety nets?</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="K130" t="inlineStr">
         <is>
           <t>Quality, Suitability, Stability</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="L130" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D130">
+      <c r="D131">
         <v>183</v>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>Average cost-to-borrower for unsecured lending</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>Average topline revenue earned from unsecured retail credit operations (as percentage of the average outstanding unsecured credit)</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>This indicator is a portfolio-level proxy for the all-in price actually paid by customers on unsecured retail credit during the period. It answers: How many currency units of revenue did the lender earn for each 100 units of average unpaid balance? Rising values may reflect higher base rates, heavier fee reliance (e.g., late/over-limit charges), or a shift toward shorter-tenor/high-yield products; falling values can indicate competitive pressure, promotional pricing, or relief programs. Boards, supervisors, and consumer-protection teams use it to benchmark pricing fairness, earnings quality, and sensitivity to interest-rate cycles. !- Definitions and concepts: Recommended numerator (topline revenue, P&amp;L-recognized): Interest income (EIR basis) + contractual fees (origination, servicing) + penalty/default interest actually recognized + punitive fees (late, over-limit, returned-payment) − waivers/reversals. Denominator: Average outstanding unsecured retail balances (use Average Daily Balance - ADB). Formula: Cost-to-customer yield = Topline revenue from unsecured retail credit divded by Average outstanding unsecured retail balances. This indicator can be reported separately for interest, contractual fees and penalities if the data is available and when the period is less than 12 months, report an annualized figure. !- Data requirements: General ledger and product-level revenue broken into interest, contractual fees, penalty interest, punitive fees; flags for waivers/reversals and non-accrual. Loan/card-level balances to compute ADB, segmented by product (cards, instalment, overdraft, BNPL), channel, and risk bucket. Accounting policies: EIR vs. cash, Stage-3/non-accrual treatment, capitalization rules.
 FX mapping for multi-currency portfolios. !- Limitations and considerations: Comparability: EIR vs. cash accounting and non-accrual practices differ; disclose methodology. Mix effects: more revolving/short-tenor loans inflate yields; always segment. Penalty bias: high ratios may be driven by a small cohort repeatedly paying fees—track % customers incurring penalties. Promotions/teasers: intro 0% and fee holidays distort short periods—show trailing-12-month and cohort views. Scope creep: exclude bundled insurance premiums or merchant discounts (BNPL) unless consistently included and disclosed.</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="H131" t="inlineStr">
         <is>
           <t>Are there gender disparities in the percentage of topline revenue relative to outstanding loan balances? Is there any gender paying comparatively more than market percentages for the same account types? How do FSPs rank in terms of these percentages by gender?</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="L131" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D131">
+      <c r="D132">
         <v>181</v>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>Revenue generated by unsecured credit</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>% of total topline revenue attributable to unsecured credit operations and interest and non-interest revenue proportions</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>This indicator captures the total income that a lending institution earns from unsecured credit products—credit cards, personal instalment loans, overdrafts, payday and buy-now-pay-later (BNPL) facilities—over a reporting period. Because unsecured lending is typically high-yield and high-risk, tracking its revenue helps supervisors and management understand how much of the institution’s top line depends on products that are more sensitive to economic downturns, job-market shocks and aggressive competition. A rising share can boost short-term profitability, but it may also presage higher future credit losses and conduct-risk concerns if underwriting standards slip. !- Definitions and concepts: Unsecured credit – loans that are not backed by collateral; repayment relies on the borrower’s cash flow and creditworthiness.
 Revenue components – Interest income (accrued and collected) from outstanding balances. Fee income: annual fees, origination fees, late-payment charges, interchange on card transactions, BNPL merchant discount rates. Net insurance or payment-protection premiums (if bundled) may be included subject to local accounting rules.
 Revenue share metric: Unsecured-credit revenue ÷ Total lending revenue expresses concentration risk. Risk-adjusted yield – revenue net of credit-loss provisions gives a clearer view of economic profitability. !- Data requirements: Product-level general-ledger extracts segregating interest, fees and other income. Loan-level flags identifying collateral status (secured vs. unsecured). Average daily or month-end balances to compute effective yields. Associated credit-loss provisions and write-offs for risk-adjusted analysis. !- Limitations and considerations: Mixed products: Some personal loans are partially secured (e.g., salary-linked) or carry optional collateral; clear taxonomy is essential. Fee recognition rules: Capitalised origination fees amortised under effective-interest-rate (EIR) accounting may blur timing comparisons across banks or jurisdictions. Regulatory caps: Interest-rate or fee ceilings (e.g., usury limits) affect revenue potential and comparability. Promotional pricing: Introductory 0 % card offers or BNPL “pay-in-4” models generate deferred revenue; headline figures may understate future income. Economic cyclicality: Unsecured-credit revenue can fall sharply in recessions as balances contract and charge-offs rise; pairing with delinquency and provision metrics is crucial for a full risk-return picture.</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="H132" t="inlineStr">
         <is>
           <t>What proportion of total topline revenue comes from unsecured credit operations, and are there gender disparities in this distribution? How do FSPs rank in their reliance on unsecured credit revenue by gender?</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Fair treatment</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D132">
-        <v>198</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Insurance approved claims not paid</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>% of approved/accepted claims that remain unpaid to customers</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>This indicator shows the share of claims that have been approved (final liability accepted) but not yet disbursed to the claimant. A high rate flags operational bottlenecks or weak payout controls, directly impacting customer outcomes. Track alongside claims turnaround time, claims rejection rates, and complaints, to get a full picture of payout effectiveness and customer fairness. !- Definitions and concepts: Approved / accepted claim: a claim with a final decision to pay (post-analysis), a recorded payable, and no outstanding dispute. Unpaid status: no successful settlement to the beneficiary by period end. Formula: Amount weighted (unpaid approved amount ÷ approved amount) reveal economic impact. Count basis (# approved claims not paid by cut-off ÷ # claims approved in teh period). SLA variant: % not paid within X days of approval (e.g., 5/10/30 days) to neutralize end-period timing bias. Treatment of partial payments: disclose whether partially paid claims are counted as unpaid or excluded. The indicator may also track the reasons for non-payment, if these are standardized for reporting. !- Limitations and considerations: Cut-off effects: approvals late in the period will naturally be unpaid—use the SLA variant and report both snapshot and flow views. Reopened claims / appeals: specify whether reversals after approval are removed from both numerator and denominator. Segmentation: monitor by line of business, payment method, channel, and claim size to target fixes.</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>How do the average values of outstanding insurance claims compare by gender? Is there a gender group with consistently higher average unpaid claims? How do different FSPs rank in terms of outstanding claims by gender? Are vulnerable gender groups disproportionately affected by delayed or unpaid claims?</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>Quality, Reputational and legal risk</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -7361,164 +7361,164 @@
         </is>
       </c>
       <c r="D133">
+        <v>198</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Insurance approved claims not paid</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>% of approved/accepted claims that remain unpaid to customers</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>This indicator shows the share of claims that have been approved (final liability accepted) but not yet disbursed to the claimant. A high rate flags operational bottlenecks or weak payout controls, directly impacting customer outcomes. Track alongside claims turnaround time, claims rejection rates, and complaints, to get a full picture of payout effectiveness and customer fairness. !- Definitions and concepts: Approved / accepted claim: a claim with a final decision to pay (post-analysis), a recorded payable, and no outstanding dispute. Unpaid status: no successful settlement to the beneficiary by period end. Formula: Amount weighted (unpaid approved amount ÷ approved amount) reveal economic impact. Count basis (# approved claims not paid by cut-off ÷ # claims approved in teh period). SLA variant: % not paid within X days of approval (e.g., 5/10/30 days) to neutralize end-period timing bias. Treatment of partial payments: disclose whether partially paid claims are counted as unpaid or excluded. The indicator may also track the reasons for non-payment, if these are standardized for reporting. !- Limitations and considerations: Cut-off effects: approvals late in the period will naturally be unpaid—use the SLA variant and report both snapshot and flow views. Reopened claims / appeals: specify whether reversals after approval are removed from both numerator and denominator. Segmentation: monitor by line of business, payment method, channel, and claim size to target fixes.</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>How do the average values of outstanding insurance claims compare by gender? Is there a gender group with consistently higher average unpaid claims? How do different FSPs rank in terms of outstanding claims by gender? Are vulnerable gender groups disproportionately affected by delayed or unpaid claims?</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Quality, Reputational and legal risk</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Fair treatment</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D134">
         <v>256</v>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>Insurance claims declined</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>% of claims logged by policyholders that are declined prior to substantive analysis</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>This indicator captures the share of claim notifications the insurer does not accept for assessment at the front door—typically during first notice of loss (FNOL)/triage—because they are ineligible or incomplete. A high intake-decline rate can point to unclear policy wording, poor customer guidance, data-capture frictions, or overly strict gatekeeping. It is a key conduct-risk and customer-experience signal and, operationally, helps size avoidable workload versus genuinely assessable claims. Claim logged / FNOL: the moment a policyholder submits a claim or loss notice. Declined at intake (non-acceptance): the insurer refuses to open an assessable claim before investigation (e.g., policy not in force, peril not covered, waiting period, duplicate claim, claim below deductible/threshold, incomplete mandatory data not cured within a set window). Indicator formula (count basis): # claims declined at intake in period divided by # claim notifications received in period . Variants: exclude cured cases later resubmitted; report by product/channel. !- Data requirements: Claims-intake system fields: FNOL timestamp, policy ID/status at loss date, coverage/peril checks, deductible, mandatory-document checklist, triage outcome. Standardised reason codes (e.g., not covered, lapsed, duplicate, below excess, incomplete info). Deduplication logic (policyholder ID + incident date + peril). Linkage to resubmissions/appeals and to complaint records for outcome tracking. !- Limitations and considerations: Definition variance: what counts as “prior to analysis” differs; some firms place incomplete cases in “pending info” instead of “declined,” affecting comparability.
 Gaming risk: shifting cases to “withdrawn” or “pending” to improve this metric; require audit trails and age-off rules. Mix effects: products with low deductibles or mandatory documents (e.g., health) have different baseline rates—segment results. Customer fairness: high early declines may reflect confusing onboarding or exclusion wording; monitor alongside claims rejection rate (post-assessment), turnaround time, and complaints upheld. Resubmission policy: disclose whether cured resubmissions are excluded from the numerator to avoid double counting.</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="H134" t="inlineStr">
         <is>
           <t>What percentage of claims logged by policyholders are declined, disaggregated by gender? How do these decline rates vary across FSPs, policy types, age groups, and locations? Are there notable gender disparities in claim declines at the market level or within specific providers? Are women or other gender groups more likely to face claim denial?</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="L134" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D134">
+      <c r="D135">
         <v>60</v>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>Insurance claims rejection rate</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>% of all insurance claims that are rejected by insurers (post-analysis)</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>The claims rejection rate shows the share of claims that an insurer declines to pay—fully or partially—relative to the total number (or value) of claims submitted in a period. Because denial directly affects customer trust, supervisors use the metric to monitor fair treatment outcomes, detect aggressive underwriting or opaque policy wording, and flag operational shortcomings. A sudden rise may presage reputational damage, regulatory sanctions, or litigation costs, while an unusually low rate can hint at lax fraud controls or inadequate claims processing. !- Definitions and concepts: Claims rejected (denied): claims for which the insurer issues a final communication refusing payment on contractual grounds (e.g., policy exclusions, lapsed cover, misrepresentation) or on fraud findings. !- Limitations and considerations: Definition divergence: Some regimes class “claims closed without payment” (due to missing documents) as rejections; others record them as pending, complicating cross-market comparison. Fraud vs. technical denial: Combining fraud rejections with contractual exclusions can blur very different issues. Separate reporting is best practice. Volume vs. value: A single large, legitimately denied loss can distort amount-based ratios; analysts should monitor both count and value metrics.
 Appeals and reversals: Denials overturned on review lower true rejection rates; timely data updates are essential.
 Incentive effects: Over-emphasis on low rejection rates may weaken fraud vigilance, whereas strict targets can push staff toward technical denials—pair the indicator with complaint ratios, turnaround times, and fraud-detection statistics for balanced oversight.</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="H135" t="inlineStr">
         <is>
           <t>Are there gender disparities in the rejection rates of insurance claims, including for MSMEs by owner gender? Which types of policies or claims see higher rejection rates, and do these differ by gender? How does claim rejection relate to coverage levels and turnaround times? Do FSPs with higher gender diversity have lower rejection rates for vulnerable gender groups?</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
         <is>
           <t>Quality</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Fair treatment</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D135">
-        <v>201</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Insurance claims settlement ratio</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>% of insurance claims logged by policyholders that have been paid by insurers</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Measures the percentage of insurance claims settled by an insurer out of the total claims it receives. It is a direct measure of an insurer's reliability and its commitment to fulfilling its primary promise to policyholders. This indicator is a cornerstone of conduct supervision, as it provides a quantitative view of how an insurer treats its customers at their most critical moment of need. For prudential supervisors, it could help analysis of operational and reputational risk. This indicator should be used together with other indicators on the performance of the claims process in the insurance sector.</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>How do claim settlement ratios vary by gender? Are any gender groups receiving lower settlement ratios compared to the market average? Are there FSPs with particularly low or high settlement ratios for certain genders? How do these ratios intersect with policy type and customer demographics?</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>Outcomes, Reputational and legal risk</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -7544,215 +7544,215 @@
         </is>
       </c>
       <c r="D136">
+        <v>201</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Insurance claims settlement ratio</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>% of insurance claims logged by policyholders that have been paid by insurers</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Measures the percentage of insurance claims settled by an insurer out of the total claims it receives. It is a direct measure of an insurer's reliability and its commitment to fulfilling its primary promise to policyholders. This indicator is a cornerstone of conduct supervision, as it provides a quantitative view of how an insurer treats its customers at their most critical moment of need. For prudential supervisors, it could help analysis of operational and reputational risk. This indicator should be used together with other indicators on the performance of the claims process in the insurance sector.</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>How do claim settlement ratios vary by gender? Are any gender groups receiving lower settlement ratios compared to the market average? Are there FSPs with particularly low or high settlement ratios for certain genders? How do these ratios intersect with policy type and customer demographics?</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Outcomes, Reputational and legal risk</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Fair treatment</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D137">
         <v>59</v>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="E137" t="inlineStr">
         <is>
           <t>Insurance claims turnaround time</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>Average number of days to process insurance claims</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>This indicator captures the average calendar days an insurer takes to settle a claim—from the claim filing date to the final payment or formal denial. It is a direct yard-stick of operational efficiency and customer experience. Shorter turnaround times (TATs) enhance policy-holder trust, limit reputational risk, and can lower claims handling expenses. Supervisors use the metric to enforce fair-treatment rules, while actuaries and underwriters link it to reserving accuracy—prolonged settlement can signal documentation bottlenecks, fraud investigations, policy transparency issues, or catastrophic complexity that may keep outstanding reserves elevated. !- Definitions and concepts:  Start point – the timestamp when the insurer first receives the claim request. End point – the date the insurer issues full payment, partial final payment, or a written denial. Average turnaround time (TAT) – arithmetic mean; many firms also monitor median and 90th-percentile to limit outlier masking.
 Segmented TATs – tracked by line of business, claim severity band, and distribution channel to isolate problem areas.
 !- Limitations and considerations: Partial settlements: Recording the date of first partial payment can understate full-and-final completion time. Dispute and litigation pauses: Regulatory or court‐mandated suspensions inflate TAT yet lie outside managerial control.</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
+      <c r="H137" t="inlineStr">
         <is>
           <t>Are there gender disparities in the average time taken to process and settle insurance claims? How does processing time vary by policy type, premium, claim amount, and customer demographics? Are insurers with lower gender diversity more likely to have longer turnaround times? Are vulnerable gender groups disproportionately affected by delays?</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>Investments</t>
         </is>
       </c>
-      <c r="D137">
+      <c r="D138">
         <v>207</v>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="E138" t="inlineStr">
         <is>
           <t>Net rate of return on investments</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>% point differential between the average rates of returns on investments and the average performance/administration fees charged</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t>Measures the profitability of a financial institution's own investment portfolio after accounting for all associated costs. It reveals the actual, bottom-line gain or loss generated by the institution's securities, real estate, or other investments. This is a fundamental indicator of an institution's ability to effectively manage its own capital and generate profit from non-lending activities, of particular importance to prudential supervisors, including supervisors of insurance and pension administrators. Net Rate of Return (%)= 
 [(Market Value final-Market Value initial+Income−Expenses)/Market Value initial]×100</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="H138" t="inlineStr">
         <is>
           <t>How do net returns (% returns minus % performance fees and charges) on longer-term investments compare by gender? Do net returns for any gender differ from the overall market average for similar investment products? How do FSPs compare in terms of net returns earned by gender?</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr">
+      <c r="J138" t="inlineStr">
         <is>
           <t>Market development</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
+      <c r="K138" t="inlineStr">
         <is>
           <t>Capital markets development</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
+      <c r="L138" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
+    <row r="139">
+      <c r="A139" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>Fair treatment</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>Savings</t>
         </is>
       </c>
-      <c r="D138">
+      <c r="D139">
         <v>159</v>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E139" t="inlineStr">
         <is>
           <t>Average cost-to-customer for transaction accounts</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>Average topline revenue earned per account holder as % of average account balances</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t>This indicator estimates the effective price of holding and using a transaction account, expressed as a yield on the customer’s average balance. By computing it for each account type (e.g., basic/no-frills, standard retail, premium, MSMEs, e-money wallet), it reveals where pricing and usage frictions are highest. It helps supervisors assess fairness, inclusion quality, and reliance on fee income. !- Definitions and concepts: Non-interest fees: maintenance/inactivity, ATM/network, FX/transfer, statement/card fees, overdraft &amp; returned-payment fees tied to the account. 
 Per account-holder basis: aggregate all accounts of the same type per customer, then average (also show balance-weighted results). !- Data requirements: Core-banking data: customer ID, account type tags, average daily balance by customer for each account type, interest credited, revenue by fee code linked to accounts; flags for waivers/refunds/chargebacks. Channel/product hierarchies (basic vs. premium, retail vs. MSMEs, wallet vs. bank account) and currency/FX mapping. Optional: usage indicators (transactions per month) to explain differences across types.</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
+      <c r="H139" t="inlineStr">
         <is>
           <t>Are there gender disparities in the costs (fees, charges) borne by account holders of transaction accounts? Do women tend to hold transaction accounts with higher fee burdens (relative to income or transaction frequency) than men, particularly in certain regions or among lower‐income groups? How do costs compare across FSPs with different levels of gender diversity? Is fee structure or cost‐to‐customer a barrier to transaction usage for some gender/age/income cohorts?</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
+      <c r="L139" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Financial service provider (FSP) type; Account type</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Fair treatment</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D139">
-        <v>226</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Rejections of product applications</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>% of all applications that are rejected by product type</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Measures the proportion of customer applications for financial products that are rejected by regulated financial institutions during the reporting period. The indicator is calculated as the percentage of total applications received—across products such as loans, credit cards, deposit accounts, or insurance policies—that were not approved or accepted. Captures the extent of unmet demand or access barriers in financial markets, as well as aspects of market conduct, underwriting practices, and risk appetite among providers. It provides insight into how easily consumers and businesses can obtain financial products. Monitoring rejection rates helps authorities: Identify potential access constraints or discriminatory lending or sales practices; Evaluate the tightness of credit or account-opening standards; Assess consumer protection outcomes and fair treatment; Detect sudden shifts in provider risk tolerance or macro-prudential conditions (e.g., post-crisis credit tightening). High rejection rates may indicate stringent eligibility criteria, weak applicant creditworthiness, or barriers to financial access. Declining rates may suggest improving inclusion or relaxation of underwriting standards. Cross-product comparisons reveal whether certain markets (e.g., credit vs. deposits) are more exclusionary. !- Definitions and concepts: Application: A formal request by a customer to obtain a financial product or service. Rejection: A decision by the provider not to approve, issue, or open the requested product, whether automated or manual. Product type: Category of financial service applied for (loan, deposit, insurance, card, etc.). !- Data requirements: Product application records from regulated financail institutions that can yield the total number of applications rejected and the total number of applications received during the reference period. Disaggregation variables for segmentation analysis: product type, applicant type (individual, MSME), gender etc.</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>How do rejection rates vary by gender? Are rejection rates higher for any gender in specific channels? How do rejection rates in physical channels compare to those in digital channels by gender? How do FSPs rank in terms of rejection rates by gender across available channels? For loans, when analyzed alongside the indicator "Customers by credit score," are there gender disparities in rejection rates by credit score?</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
         </is>
       </c>
     </row>
@@ -7764,55 +7764,55 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Suitability</t>
+          <t>Fair treatment</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D140">
-        <v>171</v>
+        <v>226</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Unsecured credit facilities per borrower</t>
+          <t>Rejections of product applications</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Average volume and value (outstanding amount) of unsecured credit operations per borrower</t>
+          <t>% of all applications that are rejected by product type</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>This indicator shows, for each unsecured credit type (e.g., credit cards, personal instalment loans, overdrafts/lines, BNPL/pay-in-4, microcredit), how many active facilities the typical borrower holds (volume) and how much they owe on average (value). It reveals product stacking, utilisation intensity, and pockets of affordability risk. Rising volumes with flat values can indicate product fragmentation (e.g., multiple small BNPL plans), while high values per borrower point to concentration risk and potential loss severity. !- Definitions and concepts: Borrower universe per type (t): unique customers with ≥1 active unsecured facility of type (t) during the period. Average volume (holders-only) = [Total number of active contracts of type t for borrow b] / [Total number of unique borrowers with facility of type t]. Average value (holders only) = [Average daily outstanding balance across all of borrower b's facility of type t] / [Total number of unique borrowers with facility of type t]. Outstanding amount: Gross carrying amount before prvisions, exclude undrawn limits. Attribution rules: Define treatment of joint borrowers (full vs. proportional), refinances/restructures and charged-off accounts (exclude once written off, unless still on-book). !- Data requirements: Loan/line-level records with borrower ID, product/credit-type tag, status, origination date, limit (revolving), currency, and daily balances. Deduped customer master across subsidiaries/channels; joint-borrower flags. FX rates for multi-currency portfolios; calendar to compute ADB over the period. !- Limitations and considerations: Seasonality: cards/overdrafts spike around holidays—use ADB and rolling windows. Mix effects: comparing cards (revolving) with instalments needs a utilisation companion metric. Policy choices: inclusion of dormant but open lines, re-aged accounts, or post-charge-off recoveries changes results—document choices. Distribution matters: report median and percentiles per type alongside means to avoid high-balance skew.</t>
+          <t>Measures the proportion of customer applications for financial products that are rejected by regulated financial institutions during the reporting period. The indicator is calculated as the percentage of total applications received—across products such as loans, credit cards, deposit accounts, or insurance policies—that were not approved or accepted. Captures the extent of unmet demand or access barriers in financial markets, as well as aspects of market conduct, underwriting practices, and risk appetite among providers. It provides insight into how easily consumers and businesses can obtain financial products. Monitoring rejection rates helps authorities: Identify potential access constraints or discriminatory lending or sales practices; Evaluate the tightness of credit or account-opening standards; Assess consumer protection outcomes and fair treatment; Detect sudden shifts in provider risk tolerance or macro-prudential conditions (e.g., post-crisis credit tightening). High rejection rates may indicate stringent eligibility criteria, weak applicant creditworthiness, or barriers to financial access. Declining rates may suggest improving inclusion or relaxation of underwriting standards. Cross-product comparisons reveal whether certain markets (e.g., credit vs. deposits) are more exclusionary. !- Definitions and concepts: Application: A formal request by a customer to obtain a financial product or service. Rejection: A decision by the provider not to approve, issue, or open the requested product, whether automated or manual. Product type: Category of financial service applied for (loan, deposit, insurance, card, etc.). !- Data requirements: Product application records from regulated financail institutions that can yield the total number of applications rejected and the total number of applications received during the reference period. Disaggregation variables for segmentation analysis: product type, applicant type (individual, MSME), gender etc.</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>How does the average number of outstanding loans per borrower vary by gender? Are outstanding balances more concentrated in long- or short-term loans, and does this differ by gender? Have gender disparities in loan terms evolved over time?</t>
+          <t>How do rejection rates vary by gender for individuasl and MSME? Are rejection rates higher for any gender in specific channels? How do rejection rates in physical channels compare to those in digital channels by gender? How do FSPs rank in terms of rejection rates by gender across available channels, by type of customer (individuals, MSME)?</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Outcomes, Credit risk</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Product type</t>
         </is>
       </c>
     </row>
@@ -7824,55 +7824,55 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Safety and security</t>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D141">
-        <v>231</v>
+        <v>171</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Frauds faced by customers</t>
+          <t>Unsecured credit facilities per borrower</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>% of customers affected by fraud</t>
+          <t>Average volume and value (outstanding amount) of unsecured credit operations per borrower</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Fraud directly erodes consumer confidence, trust in financial institutions and can trigger liquidity or solvency stress for institutions, tracking its incidence lets supervisors spot emerging threats before they undermine financial stability. Consistent monitoring also reveals control weaknesses, helping authorities direct enforcement, bolster preventive regulation, and keep the payments and deposit system trusted and resilient. This indicator measures the share of customers of financial services that have been victims of fraud over a specific period. !- Definitions and concepts: Several definitions of fraud exist and vary depending on the jurisdiction, local definitions of fraud for statistical reporting purposes should be used. For example, the European Banking Authority splits fraudelent payment transactions into two categories: (1) Unauthorised payment transactions: transfers made “as a result of the loss, theft or misappropriation of sensitive payment data or a payment instrument … executed in the absence of consent by the payer.” and (2) Manipulation of the payer: transactions “made as a result of the payer being manipulated … to issue a payment order … in good faith, to a payment account it believes belongs to a legitimate payee.” This definition anchors EU-wide fraud statistics and stresses both technical compromise (e.g., stolen credentials) and social-engineering scams (e.g., authorised push-payment fraud). !- Data requirements: Transactions initiated and executed during a specified period that are flagged as fraudulent linked to a unique customer ID; Total number of customer at the beginning of the specified period.</t>
+          <t>This indicator shows, for each unsecured credit type (e.g., credit cards, personal instalment loans, overdrafts/lines, BNPL/pay-in-4, microcredit), how many active facilities the typical borrower holds (volume) and how much they owe on average (value). It reveals product stacking, utilisation intensity, and pockets of affordability risk. Rising volumes with flat values can indicate product fragmentation (e.g., multiple small BNPL plans), while high values per borrower point to concentration risk and potential loss severity. !- Definitions and concepts: Borrower universe per type (t): unique customers with ≥1 active unsecured facility of type (t) during the period. Average volume (holders-only) = [Total number of active contracts of type t for borrow b] / [Total number of unique borrowers with facility of type t]. Average value (holders only) = [Average daily outstanding balance across all of borrower b's facility of type t] / [Total number of unique borrowers with facility of type t]. Outstanding amount: Gross carrying amount before prvisions, exclude undrawn limits. Attribution rules: Define treatment of joint borrowers (full vs. proportional), refinances/restructures and charged-off accounts (exclude once written off, unless still on-book). !- Data requirements: Loan/line-level records with borrower ID, product/credit-type tag, status, origination date, limit (revolving), currency, and daily balances. Deduped customer master across subsidiaries/channels; joint-borrower flags. FX rates for multi-currency portfolios; calendar to compute ADB over the period. !- Limitations and considerations: Seasonality: cards/overdrafts spike around holidays—use ADB and rolling windows. Mix effects: comparing cards (revolving) with instalments needs a utilisation companion metric. Policy choices: inclusion of dormant but open lines, re-aged accounts, or post-charge-off recoveries changes results—document choices. Distribution matters: report median and percentiles per type alongside means to avoid high-balance skew.</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>How does the number of fraud cases vary by gender? Are any genders disproportionately affected by fraud? Are fraud cases more frequent in certain types of FSPs?</t>
+          <t>How does the average number of outstanding loans per borrower vary by gender? Are outstanding balances more concentrated in long- or short-term loans, and does this differ by gender? Have gender disparities in loan terms evolved over time?</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Outcomes, Credit risk</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
         </is>
       </c>
     </row>
@@ -7893,31 +7893,31 @@
         </is>
       </c>
       <c r="D142">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Frauds resulting in costumer losses</t>
+          <t>Frauds faced by customers</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Average volume and value (losses incurred) of frauds experienced by customers</t>
+          <t>% of customers affected by fraud</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Fraud directly erodes consumer confidence, trust in financial institutions and can trigger liquidity or solvency stress for institutions, tracking its incidence lets supervisors spot emerging threats before they undermine financial stability. Consistent monitoring also reveals control weaknesses, helping authorities direct enforcement, bolster preventive regulation, and keep the payments and deposit system trusted and resilient. This indicator measures the number of transactions that have been flagged as fraudulent and their corresponding value in currency.  !- Definitions and concepts: Several definitions of fraud exist and vary depending on the jurisdiction, local definitions of fraud for statistical reporting purposes should be used. For example, the European Banking Authority splits fraudelent payment transactions into two categories: (1) Unauthorised payment transactions: transfers made “as a result of the loss, theft or misappropriation of sensitive payment data or a payment instrument … executed in the absence of consent by the payer.” and (2) Manipulation of the payer: transactions “made as a result of the payer being manipulated … to issue a payment order … in good faith, to a payment account it believes belongs to a legitimate payee.” This definition anchors EU-wide fraud statistics and stresses both technical compromise (e.g., stolen credentials) and social-engineering scams (e.g., authorised push-payment fraud). !- Data requirements: Total number of transactions initiated and executed during a specified period that are flagged as fraudulent;  Total value of transactions initiated and executed during a specified period that are flagged as fraudulent.</t>
+          <t>Fraud directly erodes consumer confidence, trust in financial institutions and can trigger liquidity or solvency stress for institutions, tracking its incidence lets supervisors spot emerging threats before they undermine financial stability. Consistent monitoring also reveals control weaknesses, helping authorities direct enforcement, bolster preventive regulation, and keep the payments and deposit system trusted and resilient. This indicator measures the share of customers of financial services that have been victims of fraud over a specific period. !- Definitions and concepts: Several definitions of fraud exist and vary depending on the jurisdiction, local definitions of fraud for statistical reporting purposes should be used. For example, the European Banking Authority splits fraudelent payment transactions into two categories: (1) Unauthorised payment transactions: transfers made “as a result of the loss, theft or misappropriation of sensitive payment data or a payment instrument … executed in the absence of consent by the payer.” and (2) Manipulation of the payer: transactions “made as a result of the payer being manipulated … to issue a payment order … in good faith, to a payment account it believes belongs to a legitimate payee.” This definition anchors EU-wide fraud statistics and stresses both technical compromise (e.g., stolen credentials) and social-engineering scams (e.g., authorised push-payment fraud). !- Data requirements: Transactions initiated and executed during a specified period that are flagged as fraudulent linked to a unique customer ID; Total number of customer at the beginning of the specified period.</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>How do financial loss-related fraud cases impact genders differently? Are any genders disproportionately affected by frauds that result in financial losses? Are fraud cases involving financial losses more common in certain types of FSPs?</t>
+          <t>How does the number of fraud cases vary by gender? Are any genders disproportionately affected by fraud? Are fraud cases more frequent in certain types of FSPs?</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -7953,102 +7953,102 @@
         </is>
       </c>
       <c r="D143">
+        <v>233</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Frauds resulting in costumer losses</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Average volume and value (losses incurred) of frauds experienced by customers</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Fraud directly erodes consumer confidence, trust in financial institutions and can trigger liquidity or solvency stress for institutions, tracking its incidence lets supervisors spot emerging threats before they undermine financial stability. Consistent monitoring also reveals control weaknesses, helping authorities direct enforcement, bolster preventive regulation, and keep the payments and deposit system trusted and resilient. This indicator measures the number of transactions that have been flagged as fraudulent and their corresponding value in currency.  !- Definitions and concepts: Several definitions of fraud exist and vary depending on the jurisdiction, local definitions of fraud for statistical reporting purposes should be used. For example, the European Banking Authority splits fraudelent payment transactions into two categories: (1) Unauthorised payment transactions: transfers made “as a result of the loss, theft or misappropriation of sensitive payment data or a payment instrument … executed in the absence of consent by the payer.” and (2) Manipulation of the payer: transactions “made as a result of the payer being manipulated … to issue a payment order … in good faith, to a payment account it believes belongs to a legitimate payee.” This definition anchors EU-wide fraud statistics and stresses both technical compromise (e.g., stolen credentials) and social-engineering scams (e.g., authorised push-payment fraud). !- Data requirements: Total number of transactions initiated and executed during a specified period that are flagged as fraudulent;  Total value of transactions initiated and executed during a specified period that are flagged as fraudulent.</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>How do financial loss-related fraud cases impact genders differently? Are any genders disproportionately affected by frauds that result in financial losses? Are fraud cases involving financial losses more common in certain types of FSPs?</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Safety and security</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D144">
         <v>230</v>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>Physical safety</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>Number of physical security incidents and number of customers affected</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t>This indicator captures the total number of reported physical security incidents that occur in connection with the operations of financial service providers (FSPs) — including banks, microfinance institutions, payment service providers, and other regulated entities — as well as the number of customers directly affected by such incidents. Physical security incidents include events such as armed robberies, thefts, assaults, vandalism, or damage to property occurring at branches, ATMs, cash-in-transit vehicles, or other service delivery points. The “number of customers affected” reflects individuals who have experienced harm, loss, or disruption of service as a result of these events.This indicator measures the operational risk exposure of the financial sector to physical threats and criminal activity, and the extent to which such incidents impact customers and public trust. It forms part of the broader construct of operational resilience and consumer protection, providing insights into the safety of physical access points within the financial system. Supervisory reporting could record:
 Number of incidents = Total count of reported physical security incidents during the reference period (e.g., quarterly or annually). Number of customers affected = Total number of customers who suffered loss, injury, or service disruption due to those incidents. !- Derivable indicators: Incident rate = (Number of incidents / Total number of service points) × 1,000; Customer impact rate = (Number of customers affected / Total number of customers) × 100</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="H144" t="inlineStr">
         <is>
           <t>How does the number of physical security incidents vary by gender? Are any genders disproportionately affected? Are physical security incidents more common in certain types of FSPs?</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr">
+      <c r="J144" t="inlineStr">
         <is>
           <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
+      <c r="K144" t="inlineStr">
         <is>
           <t>Outcomes, Reputational and legal risk</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Suitability</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D144">
-        <v>152</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Deposit account holders qualifying for credit</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>% of all deposit account holders that meet the minimum qualifying criteria for a loan or line of credit</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>A measure of the assessed creditworthiness of depositors. Digital financial tools such as mobile money and e-wallets have opened up access to financal services to millions around the world. This indicator tries to measure the degree to which users of accounts can unlock access to addiitonal services, in the case credit. !- Definitions and concepts: Deposit accounts include transaction and non-transaction deposit accounts, for example: Checking/demand, savings, time/term deposit accounts, pensions. !- Data requirements: Total number of unique deposit account holders that also either have (1) an open loan account, (2) do not have an open loan account but would be approved for a loan or line of credit given their current credit history, credit score or other basic requirements (such as minimum balance or savings history); Total number of unique deposit account holders (i.e. an individual must be counted as one depositor irrespective of the number of deposit accounts held) at the end of a specified period (e.g. quarter or year).  !- Limitations and considerations: If individuals or MSMEs own deposit accounts across multiple different financial institutions, sector or system wide aggregates which add up accounts across institutions will, as a result, overstate the degree of financial inclusion unless granular data and unique national IDs can be used to identify individuals with multiple accounts across financial institutions.</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>What are the credit-qualifying rates for transaction account holders by gender? How do these rates compare? Which FSPs rank highest and lowest in credit-qualifying rates for typically underserved groups, and does this ranking change when analyzed by gender?</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>Outcomes, Credit risk</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
         </is>
       </c>
     </row>
@@ -8069,31 +8069,31 @@
         </is>
       </c>
       <c r="D145">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Early loan payoff</t>
+          <t>Deposit account holders qualifying for credit</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>% of borrowers who paid loans in full before due date</t>
+          <t>% of all deposit account holders that meet the minimum qualifying criteria for a loan or line of credit</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>The early-loan-payoff (or prepayment) indicator tracks the share of outstanding loans that borrowers settle—partly or fully—before the contractually scheduled maturity. High prepayment activity can squeeze interest income, change expected cash-flow profiles that underpin asset-liability management, and distort credit-loss models. For lenders, rising early payoffs may flag aggressive refinancing campaigns by competitors, interest rate declines that make refinancing attractive, or borrowers’ improved liquidity. Supervisors and investors monitor the metric to evaluate revenue volatility, among others. !- Definitions and concepts: Early payoff / prepayment: any unscheduled principal reduction exceeding the contractual amortisation, including full settlement (loan closed) and partial prepayments (lump-sum curtailments).</t>
+          <t>A measure of the assessed creditworthiness of depositors. Digital financial tools such as mobile money and e-wallets have opened up access to financal services to millions around the world. This indicator tries to measure the degree to which users of accounts can unlock access to addiitonal services, in the case credit. !- Definitions and concepts: Deposit accounts include transaction and non-transaction deposit accounts, for example: Checking/demand, savings, time/term deposit accounts, pensions. !- Data requirements: Total number of unique deposit account holders that also either have (1) an open loan account, (2) do not have an open loan account but would be approved for a loan or line of credit given their current credit history, credit score or other basic requirements (such as minimum balance or savings history); Total number of unique deposit account holders (i.e. an individual must be counted as one depositor irrespective of the number of deposit accounts held) at the end of a specified period (e.g. quarter or year).  !- Limitations and considerations: If individuals or MSMEs own deposit accounts across multiple different financial institutions, sector or system wide aggregates which add up accounts across institutions will, as a result, overstate the degree of financial inclusion unless granular data and unique national IDs can be used to identify individuals with multiple accounts across financial institutions.</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the likelihood of making early payments before due dates? Which credit products are most frequently paid early by each gender?</t>
+          <t>What are the credit-qualifying rates for transaction account holders by gender? How do these rates compare? Which FSPs rank highest and lowest in credit-qualifying rates for typically underserved groups, and does this ranking change when analyzed by gender?</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8129,31 +8129,31 @@
         </is>
       </c>
       <c r="D146">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Grace period/payment leeway</t>
+          <t>Early loan payoff</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>% of borrowers using payment holidays, grace periods and other relief measures</t>
+          <t>% of borrowers who paid loans in full before due date</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Shows how many borrowers are under temporary repayment relief, signalling household stress, policy effectiveness, and potential payment cliffs when relief ends. Rising usage can reduce near-term delinquencies but may defer (not eliminate) credit risk and revenue. !- Definitions and concepts: Relief measures (forbearance): payment holiday/deferral, interest-only period, reduced instalment, term extension, fee/penalty waiver, capitalization of arrears, hardship programs.Borrower-based indicator: % of borrowers on relief = [Total unique borrowers with at least 1 active relief measure in period]/[Total unique active borrowing customers] x 100%. Account-based variant uses loan count instead of borrowers. Status: Active (relief in effect), Approved but not started, Expired. Intensity companions: % of balances under relief, avg. relief days used, new entrants to relief ÷ active borrowers. !- Data requirements: Loan-level flags: relief type, start/end dates, approval date, terms (interest accrual, capitalization), reason code (income loss, disaster, medical), product type. Borrower ID (deduplicated across products/entities). !- Limitations and considerations: Definition variance: some programs auto-enrol; others require hardship evidence—harmful to cross-bank comparisons. Double counting: a borrower may receive multiple reliefs across loans—use borrower-level dedupe and report per-loan as a companion. Masking effect: relief suppresses DPD/NPL temporarily; pair with balances under relief and post-exit performance. Cohort effects &amp; timing: shocks (e.g., disasters) create spikes; use cohort tracking (by approval month) and rolling windows. Conduct risk: prolonged or opaque relief terms can mislead customers; monitor complaints and repeat relief rates. Segment by product (mortgage, card, personal, MSMEs), risk grade, tenure, and demographics to pinpoint vulnerability and program effectiveness.</t>
+          <t>The early-loan-payoff (or prepayment) indicator tracks the share of outstanding loans that borrowers settle—partly or fully—before the contractually scheduled maturity. High prepayment activity can squeeze interest income, change expected cash-flow profiles that underpin asset-liability management, and distort credit-loss models. For lenders, rising early payoffs may flag aggressive refinancing campaigns by competitors, interest rate declines that make refinancing attractive, or borrowers’ improved liquidity. Supervisors and investors monitor the metric to evaluate revenue volatility, among others. !- Definitions and concepts: Early payoff / prepayment: any unscheduled principal reduction exceeding the contractual amortisation, including full settlement (loan closed) and partial prepayments (lump-sum curtailments).</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>How do the percentages of borrowers using grace periods or payment leeways compare by gender? Is there any gender more likely to use them? How does the use of grace periods or payment leeways vary by credit product and gender?</t>
+          <t>Are there gender disparities in the likelihood of making early payments before due dates? Which credit products are most frequently paid early by each gender?</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8189,102 +8189,102 @@
         </is>
       </c>
       <c r="D147">
+        <v>189</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Grace period/payment leeway</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>% of borrowers using payment holidays, grace periods and other relief measures</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Shows how many borrowers are under temporary repayment relief, signalling household stress, policy effectiveness, and potential payment cliffs when relief ends. Rising usage can reduce near-term delinquencies but may defer (not eliminate) credit risk and revenue. !- Definitions and concepts: Relief measures (forbearance): payment holiday/deferral, interest-only period, reduced instalment, term extension, fee/penalty waiver, capitalization of arrears, hardship programs.Borrower-based indicator: % of borrowers on relief = [Total unique borrowers with at least 1 active relief measure in period]/[Total unique active borrowing customers] x 100%. Account-based variant uses loan count instead of borrowers. Status: Active (relief in effect), Approved but not started, Expired. Intensity companions: % of balances under relief, avg. relief days used, new entrants to relief ÷ active borrowers. !- Data requirements: Loan-level flags: relief type, start/end dates, approval date, terms (interest accrual, capitalization), reason code (income loss, disaster, medical), product type. Borrower ID (deduplicated across products/entities). !- Limitations and considerations: Definition variance: some programs auto-enrol; others require hardship evidence—harmful to cross-bank comparisons. Double counting: a borrower may receive multiple reliefs across loans—use borrower-level dedupe and report per-loan as a companion. Masking effect: relief suppresses DPD/NPL temporarily; pair with balances under relief and post-exit performance. Cohort effects &amp; timing: shocks (e.g., disasters) create spikes; use cohort tracking (by approval month) and rolling windows. Conduct risk: prolonged or opaque relief terms can mislead customers; monitor complaints and repeat relief rates. Segment by product (mortgage, card, personal, MSMEs), risk grade, tenure, and demographics to pinpoint vulnerability and program effectiveness.</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>How do the percentages of borrowers using grace periods or payment leeways compare by gender? Is there any gender more likely to use them? How does the use of grace periods or payment leeways vary by credit product and gender?</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Outcomes, Credit risk</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Suitability</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="D148">
         <v>190</v>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="E148" t="inlineStr">
         <is>
           <t>Borrowers in debt counselling and rehabilitation</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="F148" t="inlineStr">
         <is>
           <t>% of borrowers participating in debt counselling and/or debt rehabilitation progams</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="G148" t="inlineStr">
         <is>
           <t>This indicator tracks the prevalence of individuals formally enrolled in debt-counselling or rehabilitation programmes: legal or contractual processes that restructure debt, impose spending plans, or provide financial-literacy support. A rising level signals household over-indebtedness pressures, tighter monetary or labour-market conditions, or aggressive credit expansion in the recent past. Regulators, consumer-protection agencies, and lenders track the metric to gauge systemic consumer-credit risk, calibrate responsible-lending rules and supervision, and anticipate write-off or provisioning needs. !- Definitions and concepts: Borrowers refers to individuals that have obtained any type of credit from financial institutions. Individuals are counted as one borrower, irrespective of the number of loan accounts held. Debt-counselling / debt-review: A court-sanctioned or regulator-approved process (e.g., South Africa’s National Credit Act, UK Debt Management Plans) where a certified counsellor assesses affordability, negotiates new payment schedules with all creditors, and disburses consolidated instalments. Debt rehabilitation / discharge: The stage at which the borrower has completed the plan, obtained a clearance certificate, or been legally discharged from remaining obligations (analogous to Chapter 13 completion in the US). Indicator forms:
 Stock measure: number of active borrowers under counselling ÷ total number of retail borrowers. Flow measure: new counselling entrants during the period ÷ new defaults. !- Data requirements: Registry or court filings identifying unique borrowers, start and end dates, original and restructured debt balances, and counsellor accreditation. Credit-bureau data to link counselling status with credit scores, delinquency buckets, and new credit enquiries. !- Limitations and considerations: Coverage gaps: Informal or NGO-led advice services may not report centrally, understating prevalence. Regime differences: Some jurisdictions treat insolvency, debt management, and bankruptcy as separate processes; harmonising counts is non-trivial. Multiple enrolments: Borrowers can exit and re-enter counselling; deduplicating unique individuals is essential for accurate stock figures. Moral-hazard concerns: Easy access to rehabilitation might weaken repayment discipline; analysts pair this indicator with post-rehabilitation re-default rates.Privacy restrictions: Personally identifiable data are often masked, limiting segmentation by income, gender, or geography unless aggregated extracts are provided. Used alongside delinquency trends, restructuring volumes, and loan-loss provisions, the “borrowers in debt counselling and rehabilitation” metric offers a forward-looking lens on household financial stress and the effectiveness of consumer-protection frameworks.</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="H148" t="inlineStr">
         <is>
           <t>How do the percentages of borrowers in debt counseling or rehabilitation compare by gender? Is there any gender more likely to enroll in debt counseling or rehabilitation? How do FSPs compare in terms of debt counseling or rehabilitation enrollment by gender?</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
         <is>
           <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
+      <c r="K148" t="inlineStr">
         <is>
           <t>Outcomes, Credit risk</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Suitability</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D148">
-        <v>27</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Borrowers in risky indebtedness (risk of over-indebtedness)</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Number of borrowers classified as at risk of over-indebtedness, as per risk-indebtedness calculation</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Tracking over-indebtedness gives authorities a measure of systemic distress: when large segments of retail borrowers can’t meet their obligations, it highlights consumer-protection gaps. Persistent debt burdens signal predatory lending or inadequate affordability assessments. The indicator helps calibrate market-conduct supervision and regulation. This particular indicator that identifies borrowers at risk of overindebtedness was developed by the Central Bank of Brazil: https://www.bcb.gov.br/content/cidadaniafinanceira/documentos_cidadania/serie_cidadania/serie_cidadania_financeira_8_endividamento_risco_2ed.pdf ad https://www.researchgate.net/publication/376634051_Risky_Indebtedness_Behavior_Impacts_on_Financial_Preparation_for_Retirement_and_Perceived_Financial_Well-Being. It is a composite of four components. A borrower is flagged as being in "risky indebtedness" when any two of the following four criteria are met: (1) Has defaulted on credit installments, that is, has had payment delays of more than 90 days in meeting credit obligations, (2) Monthly income devoted to debt-service payments exceeds 50 percent, (3) Has simultaneous exposure to the following forms of credit: overdraft, unsecured personal loan, and revolving credit card debt, (4) Monthly disposable income (after debt-service payments) that falls below the poverty line. Generating this indicator at the system level requires a unique national ID in order to match granular loan data to unique borrowers. The indicator also requires access to income data. !- Derivable indicators: Percent of borrowers in risky indebtendess; Percent of adults in risky indebtedness.</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in the classification of risky indebtedness? Are low-income borrowers more at risk of risky indebtedness and how does it compare across genders? Comparing this indicator with gender diversity, do FSPs with higher levels of gender diversity present lower levels of risky indebtedness?</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>Credit risk</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -8310,41 +8310,41 @@
         </is>
       </c>
       <c r="D149">
-        <v>285</v>
+        <v>27</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Debt service-to-income ratio</t>
+          <t>Borrowers in risky indebtedness (risk of over-indebtedness)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>% of income allocated to retail credit debt repayment</t>
+          <t>Number of borrowers classified as at risk of over-indebtedness, as per risk-indebtedness calculation</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>The debt service-to-Income ratio,  sometimes referred to more concisely as the debt service ratio (DSR) expresses a borrower’s (or household’s) total debt-service burden relative to recurring income, answering a simple question: How much of each income unit is already pledged to repay existing debt? At the micro level, lenders use DSR to assess repayment capacity, price credit, and comply with responsible-lending rules. At the macro level, supervisors track average or distributional DSR to gauge household vulnerability to interest-rate shocks and to calibrate macro-prudential tools such as loan-to-income caps. !- Definitions and concepts: Debt payments include principal, interest, mandatory insurance on retail credit facilities;  Income can be defined in gross terms (pre-tax income (salary) plus verifiable recurring earning) or net terms (income after taxes and social-security contributions). !- Data requirements: Current loan statements or credit-bureau/registry reports detailing payment amounts, remaiming term, and interest rate for all obligations; Recent payslips, audited financial statements (self-fmployed), tax returns, and verified rental or pension income. !- Limitations and considerations: Income volatility: informal or gig-economy or commission-based earnings make future cash flows uncertain; Undisclosed liabilities: informal or unreported debts escape bureau coverage, understating true DSR. Household composition: shared living expenses and co-borrower support can distort individual ratios; some frameworks use household disposable income instead. Interest-rate path: fixed-rate loans keep payments stable, while floating-rate debt can raise DSR sharply when policy rates rise. Cross-country comparability: tax structures, social-welfare benefits, and healthcare costs influence disposable income, so identical DSR thresholds may imply different real affordability across jurisdictions.</t>
+          <t>Tracking over-indebtedness gives authorities a measure of systemic distress: when large segments of retail borrowers can’t meet their obligations, it highlights consumer-protection gaps. Persistent debt burdens signal predatory lending or inadequate affordability assessments. The indicator helps calibrate market-conduct supervision and regulation. This particular indicator that identifies borrowers at risk of overindebtedness was developed by the Central Bank of Brazil: https://www.bcb.gov.br/content/cidadaniafinanceira/documentos_cidadania/serie_cidadania/serie_cidadania_financeira_8_endividamento_risco_2ed.pdf ad https://www.researchgate.net/publication/376634051_Risky_Indebtedness_Behavior_Impacts_on_Financial_Preparation_for_Retirement_and_Perceived_Financial_Well-Being. It is a composite of four components. A borrower is flagged as being in "risky indebtedness" when any two of the following four criteria are met: (1) Has defaulted on credit installments, that is, has had payment delays of more than 90 days in meeting credit obligations, (2) Monthly income devoted to debt-service payments exceeds 50 percent, (3) Has simultaneous exposure to the following forms of credit: overdraft, unsecured personal loan, and revolving credit card debt, (4) Monthly disposable income (after debt-service payments) that falls below the poverty line. Generating this indicator at the system level requires a unique national ID in order to match granular loan data to unique borrowers. The indicator also requires access to income data. !- Derivable indicators: Percent of borrowers in risky indebtendess; Percent of adults in risky indebtedness.</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>How do debt service-to-income ratios vary by gender and across different loan sizes and terms? Do loans with higher rates and shorter terms show gender disparities in ratios? Comparing this indicator with gender diversity, do FSPs with higher levels of gender diversity present lower debt-service to income ratios?</t>
+          <t>Are there gender disparities in the classification of risky indebtedness? Are low-income borrowers more at risk of risky indebtedness and how does it compare across genders? Comparing this indicator with gender diversity, do FSPs with higher levels of gender diversity present lower levels of risky indebtedness?</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
+          <t>Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Quality, Credit risk</t>
+          <t>Credit risk</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -8366,35 +8366,35 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D150">
-        <v>194</v>
+        <v>285</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Insurance lapse rates</t>
+          <t>Debt service-to-income ratio</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>% of all insurance policies (or policyholders) that have lapsed</t>
+          <t>% of income allocated to retail credit debt repayment</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>This indicator measures the number of policies discontinued due to non-payment of premiums by the policyholder relative to the total number of policies at the beginning of the period. It is a key indicator to assess quality of advice, quality of service, product appropriateness, and mis-selling risk in the insurance sector. https://www.iais.org/uploads/2022/06/Report-on-Supervisors-Use-of-Key-Indicators-to-Assess-Insurer-Conduct.pdf</t>
+          <t>The debt service-to-Income ratio,  sometimes referred to more concisely as the debt service ratio (DSR) expresses a borrower’s (or household’s) total debt-service burden relative to recurring income, answering a simple question: How much of each income unit is already pledged to repay existing debt? At the micro level, lenders use DSR to assess repayment capacity, price credit, and comply with responsible-lending rules. At the macro level, supervisors track average or distributional DSR to gauge household vulnerability to interest-rate shocks and to calibrate macro-prudential tools such as loan-to-income caps. !- Definitions and concepts: Debt payments include principal, interest, mandatory insurance on retail credit facilities;  Income can be defined in gross terms (pre-tax income (salary) plus verifiable recurring earning) or net terms (income after taxes and social-security contributions). !- Data requirements: Current loan statements or credit-bureau/registry reports detailing payment amounts, remaiming term, and interest rate for all obligations; Recent payslips, audited financial statements (self-fmployed), tax returns, and verified rental or pension income. !- Limitations and considerations: Income volatility: informal or gig-economy or commission-based earnings make future cash flows uncertain; Undisclosed liabilities: informal or unreported debts escape bureau coverage, understating true DSR. Household composition: shared living expenses and co-borrower support can distort individual ratios; some frameworks use household disposable income instead. Interest-rate path: fixed-rate loans keep payments stable, while floating-rate debt can raise DSR sharply when policy rates rise. Cross-country comparability: tax structures, social-welfare benefits, and healthcare costs influence disposable income, so identical DSR thresholds may imply different real affordability across jurisdictions.</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>How do insurance lapse rates differ by gender? Are certain types of insurance policies associated with higher lapse rates among specific genders, suggesting potential issues with product suitability? How do different financial service providers (FSPs) compare in terms of lapse rates across genders? Are there notable differences when considering age, location, or income alongside gender?</t>
+          <t>How do debt service-to-income ratios vary by gender and across different loan sizes and terms? Do loans with higher rates and shorter terms show gender disparities in ratios? Comparing this indicator with gender diversity, do FSPs with higher levels of gender diversity present lower debt-service to income ratios?</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Outcomes, Credit risk</t>
+          <t>Quality, Credit risk</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -8430,41 +8430,41 @@
         </is>
       </c>
       <c r="D151">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Reinstatement of lapsed insurance policies</t>
+          <t>Insurance lapse rates</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>% of lapsed insurance policies that have been re-instated after customer made back-payments</t>
+          <t>% of all insurance policies (or policyholders) that have lapsed</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>This indicator shows the share of policies that lapsed for non-payment and were later reinstated after the customer cleared arrears (and, where required, satisfied evidence-of-insurability). A higher reinstatement rate can indicate effective retention outreach and product value to customers; very low rates may signal affordability stress, weak follow-up, or poor customer experience. From a risk perspective, reinstatements affect cash flows, reserve dynamics, and anti-selection (customers may reinstate when risk has increased). Pair this indicator with persistency, tenure of cancellations, and complaint metrics to diagnose retention quality and customer outcomes. !- Definitions and concepts: Lapse (non-payment): policy terminated after the grace period due to unpaid premium (distinct from surrender, maturity, or death). Reinstatement: restoration of coverage after lapse once back-premiums (and any interest/fees) are paid and underwriting/administrative conditions are met. Coverage may be backdated or resume prospectively per policy terms. Measurement window: define a fixed look-back (e.g., reinstated within 90/180 days of lapse). Formula (cohort basis): # policies that lapsed in period and were reinstated within {days} divided by the # policies that lapsed in period. Variants: policyholder-level (deduplicated), premium-weighted share, and calendar-period “reinstatements ÷ lapses” with a stated window. !- Data requirements: Policy-level: product/LOB, activation date, lapse date, grace-period end, arrears amount, reinstatement date, back-payment amount, underwriting outcome (medical/financial), and whether coverage backdated. Channel, geography, tenure at lapse, and prior claims/loan status. Cohort tags (issue or lapse month) for like-for-like tracking. !- Limitations and considerations: Window sensitivity: longer window raises the rate; disclose and keep constant. Classification noise: grace-period statuses mis-tagged as lapses depress apparent reinstatement. Anti-selection: reinstated policies may have higher subsequent claims—monitor post-reinstatement loss experience. Operational variance: some firms “rewrite” new policies rather than reinstate, understating the metric. Coverage basis: backdated vs. prospective reinstatement changes exposure and reserve treatment—report the split if material.</t>
+          <t>This indicator measures the number of policies discontinued due to non-payment of premiums by the policyholder relative to the total number of policies at the beginning of the period. It is a key indicator to assess quality of advice, quality of service, product appropriateness, and mis-selling risk in the insurance sector. https://www.iais.org/uploads/2022/06/Report-on-Supervisors-Use-of-Key-Indicators-to-Assess-Insurer-Conduct.pdf</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>How do rates of reinstating lapsed insurance policies vary by gender? Is any gender more likely to make back payments and reinstate their policies? How do these reinstatement patterns differ across FSPs, policy types, and demographic groups such as age or income? What might these patterns indicate about barriers to maintaining continuous coverage?</t>
+          <t>How do insurance lapse rates differ by gender? Are certain types of insurance policies associated with higher lapse rates among specific genders, suggesting potential issues with product suitability? How do different financial service providers (FSPs) compare in terms of lapse rates across genders? Are there notable differences when considering age, location, or income alongside gender?</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Financial inclusion; Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Outcomes, Credit risk</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -8490,31 +8490,31 @@
         </is>
       </c>
       <c r="D152">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Risk of insurance coverage lapse</t>
+          <t>Reinstatement of lapsed insurance policies</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>% of all insurance policies (or policyholders) that missed one or more premium payments (depending on product rules and polcies) but are still within the grace period</t>
+          <t>% of lapsed insurance policies that have been re-instated after customer made back-payments</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Measures the percentage of active insurance policies (or policyholders) that have missed one or more scheduled premium payments but remain within the contractual grace period before formal lapse or cancellation takes effect. It reflects the proportion of insurance coverage that is at risk of lapsing due to non-payment but still eligible for reinstatement under product rules. Captures policyholder payment continuity risk and the vulnerability of insurance coverage within a given portfolio. It serves as an early-warning measure of potential lapse rates, affordability pressures, and retention dynamics in insurance markets. Monitoring the risk of coverage lapse helps regulators, supervisors, and insurers to: Identify emerging risks to policy continuity and financial protection coverage; Assess household liquidity stress and premium affordability; Evaluate insurer risk management practices regarding collections and grace-period handling; Strengthen consumer protection and financial health monitoring, especially in low-income or microinsurance segments. It provides an early signal of future lapse or surrender trends, which can affect both household resilience and insurer liquidity. Higher values indicate rising vulnerability to policy lapse, which may reflect household financial strain, ineffective premium collection, or weak payment reminders.Persistent high rates suggest potential issues in affordability or product suitability. Declining values reflect improved payment discipline, automatic premium collection mechanisms, or targeted retention strategies. !- Definitions and concepts: Grace period: A contractually defined period after a missed premium during which coverage remains active and can be reinstated upon payment. Lapse: Termination of an insurance policy due to non-payment of premiums after the grace period expires. !- Data requirements: Administrative data from licensed insurance companies or supervisory reporting systems. Disaggregation by product type (life, health, motor, microinsurance, etc.), customer segment (individual, group), and insurer type. Definition of grace period based on product category (e.g., 30 days for life insurance, 7–15 days for general insurance).</t>
+          <t>This indicator shows the share of policies that lapsed for non-payment and were later reinstated after the customer cleared arrears (and, where required, satisfied evidence-of-insurability). A higher reinstatement rate can indicate effective retention outreach and product value to customers; very low rates may signal affordability stress, weak follow-up, or poor customer experience. From a risk perspective, reinstatements affect cash flows, reserve dynamics, and anti-selection (customers may reinstate when risk has increased). Pair this indicator with persistency, tenure of cancellations, and complaint metrics to diagnose retention quality and customer outcomes. !- Definitions and concepts: Lapse (non-payment): policy terminated after the grace period due to unpaid premium (distinct from surrender, maturity, or death). Reinstatement: restoration of coverage after lapse once back-premiums (and any interest/fees) are paid and underwriting/administrative conditions are met. Coverage may be backdated or resume prospectively per policy terms. Measurement window: define a fixed look-back (e.g., reinstated within 90/180 days of lapse). Formula (cohort basis): # policies that lapsed in period and were reinstated within {days} divided by the # policies that lapsed in period. Variants: policyholder-level (deduplicated), premium-weighted share, and calendar-period “reinstatements ÷ lapses” with a stated window. !- Data requirements: Policy-level: product/LOB, activation date, lapse date, grace-period end, arrears amount, reinstatement date, back-payment amount, underwriting outcome (medical/financial), and whether coverage backdated. Channel, geography, tenure at lapse, and prior claims/loan status. Cohort tags (issue or lapse month) for like-for-like tracking. !- Limitations and considerations: Window sensitivity: longer window raises the rate; disclose and keep constant. Classification noise: grace-period statuses mis-tagged as lapses depress apparent reinstatement. Anti-selection: reinstated policies may have higher subsequent claims—monitor post-reinstatement loss experience. Operational variance: some firms “rewrite” new policies rather than reinstate, understating the metric. Coverage basis: backdated vs. prospective reinstatement changes exposure and reserve treatment—report the split if material.</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>How well does the non-life insurance policy market reflect gender-based differences in policyholding and insured benefits? How do the types of non-life insurance policies held compare by gender? How are gender disparities evolving in the distribution of non-life insurance policies across different FSPs?</t>
+          <t>How do rates of reinstating lapsed insurance policies vary by gender? Is any gender more likely to make back payments and reinstate their policies? How do these reinstatement patterns differ across FSPs, policy types, and demographic groups such as age or income? What might these patterns indicate about barriers to maintaining continuous coverage?</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Outcomes</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -8550,19 +8550,79 @@
         </is>
       </c>
       <c r="D153">
+        <v>193</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Risk of insurance coverage lapse</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>% of all insurance policies (or policyholders) that missed one or more premium payments (depending on product rules and polcies) but are still within the grace period</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Measures the percentage of active insurance policies (or policyholders) that have missed one or more scheduled premium payments but remain within the contractual grace period before formal lapse or cancellation takes effect. It reflects the proportion of insurance coverage that is at risk of lapsing due to non-payment but still eligible for reinstatement under product rules. Captures policyholder payment continuity risk and the vulnerability of insurance coverage within a given portfolio. It serves as an early-warning measure of potential lapse rates, affordability pressures, and retention dynamics in insurance markets. Monitoring the risk of coverage lapse helps regulators, supervisors, and insurers to: Identify emerging risks to policy continuity and financial protection coverage; Assess household liquidity stress and premium affordability; Evaluate insurer risk management practices regarding collections and grace-period handling; Strengthen consumer protection and financial health monitoring, especially in low-income or microinsurance segments. It provides an early signal of future lapse or surrender trends, which can affect both household resilience and insurer liquidity. Higher values indicate rising vulnerability to policy lapse, which may reflect household financial strain, ineffective premium collection, or weak payment reminders.Persistent high rates suggest potential issues in affordability or product suitability. Declining values reflect improved payment discipline, automatic premium collection mechanisms, or targeted retention strategies. !- Definitions and concepts: Grace period: A contractually defined period after a missed premium during which coverage remains active and can be reinstated upon payment. Lapse: Termination of an insurance policy due to non-payment of premiums after the grace period expires. !- Data requirements: Administrative data from licensed insurance companies or supervisory reporting systems. Disaggregation by product type (life, health, motor, microinsurance, etc.), customer segment (individual, group), and insurer type. Definition of grace period based on product category (e.g., 30 days for life insurance, 7–15 days for general insurance).</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>How well does the non-life insurance policy market reflect gender-based differences in policyholding and insured benefits? How do the types of non-life insurance policies held compare by gender? How are gender disparities evolving in the distribution of non-life insurance policies across different FSPs?</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Outcomes</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Suitability</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D154">
         <v>196</v>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="E154" t="inlineStr">
         <is>
           <t>Surrendered insurance policies</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>% of eligible insurance policies (or policyholders) de-activated/lapsed that paid-out surrender values</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t>This indicator shows the share of terminated policies that generated a cash surrender payout. It helps distinguish benign expiries or non-cash lapses from value-bearing exits that can strain liquidity, depress embedded value, and signal product-fit or conduct issues (e.g., early surrenders after aggressive sales). Supervisors and boards use it to gauge customer outcomes, the health of savings-type books, and potential mis-selling or affordability problems. !- Definitions and concepts: Eligible policy: contracts with a cash value (e.g., whole life, endowment, unit-linked). Pure risk covers (term, many GI lines) are ineligible. Surrender vs. lapse: a surrender pays cash value on termination; a lapse ends cover without payout. De-activatd here excludes natural maturaties and deaths. Full vs. partial surrender: count full surrenders tied to termination; report partial withdrawals separately unless they trigger de-activation.
 Indicator (count basis): Policies terminated in period with a surrender payout divided by the number of eligible policies terminated (non-maturity) in period. Variants: policyholder-based (unique customers), and amount-based (surrender amounts ÷ cash values of terminated policies). Segment by tenure (&lt;1y, 1–3y, &gt;3y), product, and channel. Data requirements
@@ -8570,136 +8630,76 @@
 Data granularity: partial withdrawals that don’t terminate cover should be excluded or separately disclosed. Conduct lens: high early-tenure surrender shares point to mis-selling or affordability issues—pair with complaints, persistency, and tenure-of-cancellation indicators.</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
+      <c r="H154" t="inlineStr">
         <is>
           <t>Are surrender values and payouts equitably distributed by gender among eligible policyholders? Is there any gender that is less likely to receive surrender payouts, and does this vary by policy type or FSP? How do surrender rates differ by gender when combined with other demographics like income or location?</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
+      <c r="L154" t="inlineStr">
         <is>
           <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
+    <row r="155">
+      <c r="A155" t="inlineStr">
         <is>
           <t>Consumer protection</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>Suitability</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D154">
+      <c r="D155">
         <v>195</v>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E155" t="inlineStr">
         <is>
           <t>Tenure of  insurance policies</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>Average time elapsed since policy activation, by chosen time periods (e.g., &lt;3 months, 3-6 months, 6-12 months, etc)</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t>This indicator measures how long policies have stayed in force -including policies that were cancelled or lapsed mid-term. It captures the stability, maturity, and longevity of customer relationships with insurers, distinguishing recently opened accounts from those that have remained active and in use over time, and identifying which policies were cancelled after a short period of activity. A concentration of early-tenure cancellations is a red flag for mis-selling, poor onboarding, pricing/friction issues, or product-fit problems. It also matters for economics: early lapses strand acquisition costs, depress embedded value, and erode persistency. Tracking tenure helps regulators and financial institutions to: Assess policyholder retention and churn rates; Identify short-lived policies that may inflate access statistics; Evaluate the depth and continuity of customer engagement; Analyze cancellations by product and channel to target remediation measures (e.g., agent training, cooling-off disclosures, claim-time communications). From a supervisory perspective, it provides insights into stability, consumer loyalty, and the effectiveness of insurance acquisition campaigns. A longer average tenure indicates stable customer relationships, active usage, and mature market penetration. A high share of new policies may suggest recent inclusion initiatives, but also potential fragility if those policies are cancelled quickly. Monitoring shifts over time can reveal trends in account retention and digital adoption maturity !- Definitions and concepts: Activation (policy start): the in-force date (not the issue date, if different). Cancellation: termination of cover before the natural renewal/expiry date—may be customer-initiated (voluntary), insurer-initiated (non-payment, underwriting, fraud), or regulatory. Tenure of active policies (days/months) = date at the end of the reference period – activation date. Tenure of cancelled policies (days/months) = cancelation date – activation date.
 Buckets: choose stable, business-meaningful bands (e.g., &lt;3m, 3–6m, 6–12m, 12–24m, &gt;24m). Report count-weighted and premium-weighted shares. Scope: life and non-life.  Clarify whether non-renewals at anniversary are counted (usually not) and how cooling-off/free-look rescissions are treated (often reported separately). Data requirements: Policy-level fields: policy ID, product/LOB, distribution channel, activation date, cancellation date, cancellation reason code, written premium/sum assured, payment mode, and claim history. Status logic to exclude simple expiries and to de-duplicate reinstated policies (see below). Calendar and cohort views (by issue month/quarter) to remove seasonality. !- Limitations and considerations: Selection bias: averaging only cancelled policies ignores still-active ones. For a fuller view of lifetime behaviour, complement with survival analysis (e.g., Kaplan–Meier) and standard persistency ratios (13/25/61-month). Reinstatements: define whether a reinstated policy’s earlier cancellation is (a) ignored, (b) treated as a separate episode, or (c) measured to the first cancellation only.
 For cancelled policies, consider including reason codes and analyze results by product type (voluntary, non-payment, underwriting, fraud). Early non-payment suggests billing/channel issues; early voluntary points to product fit. Channel &amp; product mix: bancassurance, digital, and agency books have distinct early-tenure profiles—always segment. Cooling-off: report &lt;30-day rescissions separately to avoid overstating issues that are procedural rather than structural.</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
+      <c r="H155" t="inlineStr">
         <is>
           <t>Do genders differ in how long they hold their policies? Are there disproportionate gender differences in longer, medium, or shorter tenures? Does any gender show higher loyalty across different insurers/types? At what tenure points do insurance policies tend to be canceled, and do these patterns vary by gender? Is there a gender more likely to cancel policies earlier? How do cancellation patterns differ across policy types, age groups, locations, or income levels? What might early cancellations suggest about policy suitability or customer experience for different genders?</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Suitability, Fair treatment</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D155">
-        <v>61</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Insurance policy downgrade rate</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>% of policies downgraded at the customer's request (e.g.,  lower coverage, higher deductiblees, removal of riders, switch to a lower tier plan)</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>This indicator tracks the share of in-force policies that customers voluntarily reduce in coverage during the period. Elevated downgrade activity can signal affordability stress, product misfit, or competitive pressure (customers trading down to cheaper plans). It affects revenue (lower premiums), risk mix (higher deductibles shift loss ratios), and persistency (downgrades may precede lapses or surrenders). Supervisors and boards use the metric to monitor customer outcomes and pricing adequacy, and to gauge the effectiveness of retention strategies that preserve cover while easing budgets. !- Definitions and concepts: Downgrade (customer-initiated): a mid-term endorsement or renewal change that reduces coverage level—e.g., lower sum assured/benefit limits, higher deductibles/co-pays, downgrade of plan tier. Formula (count basis): # policies with customer-requested downgrades in period divided by # active (or renewing) policies in period. !- Limitations and considerations: Multiple events: the same policy may downgrade more than once—decide event vs. policy-unique counting. Product mapping: ensure consistent tier/benefit taxonomy across products. Group policies: member-level downgrades may not map cleanly to master policy counts—state scope.</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in policy downgrade rates, including for MSMEs based on owner gender? Which types of policies experience higher downgrade rates, and could this reflect issues like unsuitable product features or unfavorable premium-to-coverage ratios? How might these downgrade rates relate to claims rejection rates and coverage ratios? Could poor claims experiences or misunderstandings about coverage terms contribute to downgrades? Do FSPs with greater gender diversity exhibit lower downgrade rates?</t>
-        </is>
-      </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -8726,50 +8726,55 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Suitability</t>
+          <t>Suitability, Fair treatment</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D156">
-        <v>206</v>
+        <v>61</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Unpaid matured long-term investments</t>
+          <t>Insurance policy downgrade rate</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>% of long-term investments that have matured but have not yet been paid to investors</t>
+          <t>% of policies downgraded at the customer's request (e.g.,  lower coverage, higher deductiblees, removal of riders, switch to a lower tier plan)</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>This indicator tracks the share of in-force policies that customers voluntarily reduce in coverage during the period. Elevated downgrade activity can signal affordability stress, product misfit, or competitive pressure (customers trading down to cheaper plans). It affects revenue (lower premiums), risk mix (higher deductibles shift loss ratios), and persistency (downgrades may precede lapses or surrenders). Supervisors and boards use the metric to monitor customer outcomes and pricing adequacy, and to gauge the effectiveness of retention strategies that preserve cover while easing budgets. !- Definitions and concepts: Downgrade (customer-initiated): a mid-term endorsement or renewal change that reduces coverage level—e.g., lower sum assured/benefit limits, higher deductibles/co-pays, downgrade of plan tier. Formula (count basis): # policies with customer-requested downgrades in period divided by # active (or renewing) policies in period. !- Limitations and considerations: Multiple events: the same policy may downgrade more than once—decide event vs. policy-unique counting. Product mapping: ensure consistent tier/benefit taxonomy across products. Group policies: member-level downgrades may not map cleanly to master policy counts—state scope.</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>What percentage of unpaid matured longer-term investments is attributable to each gender? Are unpaid amounts disproportionately concentrated in any gender? How do FSPs rank in terms of unpaid proportions of matured longer-term investments by gender?</t>
+          <t>Are there gender disparities in policy downgrade rates, including for MSMEs based on owner gender? Which types of policies experience higher downgrade rates, and could this reflect issues like unsuitable product features or unfavorable premium-to-coverage ratios? How might these downgrade rates relate to claims rejection rates and coverage ratios? Could poor claims experiences or misunderstandings about coverage terms contribute to downgrades? Do FSPs with greater gender diversity exhibit lower downgrade rates?</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Market development</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Capital markets development</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -8781,55 +8786,50 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Suitability, Fair treatment</t>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Pensions</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="D157">
-        <v>34</v>
+        <v>206</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Pension fund switching rate</t>
+          <t>Unpaid matured long-term investments</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>% of all pension accounts that have switched to another pension fund administrator</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>An indicator of switching rates among pension recipients is a metric used to measure the frequency or volume of pension fund members who transfer their accumulated savings from one pension fund administrator (PFA) to another within a specific timeframe. This indicator can be used in countries where there is a private pension fund adminsitration industry, but not in countries where the entirety of the pension system is publicly-funded. This indicator serves as a key barometer of competition, customer satisfaction, and market dynamics within the pension industry. It can signal trends to administrators, regulators, and members themselves.  Switching Rate (%) = Total average number of members in the system / number of members who switched pension fund administrators  ×100</t>
+          <t>% of long-term investments that have matured but have not yet been paid to investors</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>How do transfers of pension fund balances to a different pension fund administrator vary by gender? Does this vary according to the level of FSP gender diversity? What percentage of contributors transferred funds compared to all customers, and are there gender disparities in this proportion? Are certain customer segments, such as women, women-owned MSMEs, and low-value accounts, more likely to make high-to-low transfers (switching to a fund administrator that has been paying lower returns)? Are FSPs with higher levels of gender diversity less likely to receive savers coming from an administrator that previously paid higher returns?</t>
+          <t>What percentage of unpaid matured longer-term investments is attributable to each gender? Are unpaid amounts disproportionately concentrated in any gender? How do FSPs rank in terms of unpaid proportions of matured longer-term investments by gender?</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Market development</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Capital markets development</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Pension type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -8841,55 +8841,55 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Suitability</t>
+          <t>Suitability, Fair treatment</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Savings</t>
+          <t>Pensions</t>
         </is>
       </c>
       <c r="D158">
-        <v>151</v>
+        <v>34</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Tenure of deposit and payment accounts</t>
+          <t>Pension fund switching rate</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Average time elapsed since account opening</t>
+          <t>% of all pension accounts that have switched to another pension fund administrator</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Measures the length of time that deposit and payment accounts have been open, can be expressed as an average or as the share of accounts in tenure categories such as &lt;3 months, 3–6 months, 6–12 months, 1–3 years, &gt;3 years, etc. It reflects the age profile of active accounts held by customers at regulated financial institutions and payment service providers. Captures the stability, maturity, and longevity of customer relationships with financial institutions. It is a key behavioral measure of financial inclusion sustainability, distinguishing recently opened accounts from those that have remained active and in use over time. Tracking account tenure helps regulators and financial institutions to: Assess account retention and churn rates in deposit and payment systems; Monitor sustained usage versus one-off account openings, especially under inclusion programs; Identify short-lived or dormant accounts that may inflate access statistics; Evaluate the depth and continuity of customer engagement with the financial system. From a supervisory perspective, it provides insights into financial system stability, consumer loyalty, and the effectiveness of account-opening campaigns. A longer average tenure indicates stable customer relationships, active usage, and mature market penetration. A high share of newly opened accounts may suggest recent inclusion initiatives, but also potential fragility if those accounts become inactive. Monitoring shifts over time can reveal trends in account retention and digital adoption maturity. !- Definitions and concepts: Deposit accounts: Savings, current, or term accounts offered by regulated deposit-taking institutions. Payment accounts: Accounts used to execute payment transactions or access funds on demand, including e-money and digital wallets. !- Data requirements: Account-level data from administrative records containing the account opening date; Total number of accounts. The tenure is calculated as the difference between the data of the end of the reference period and the account opening data (expressed in years or months).</t>
+          <t>An indicator of switching rates among pension recipients is a metric used to measure the frequency or volume of pension fund members who transfer their accumulated savings from one pension fund administrator (PFA) to another within a specific timeframe. This indicator can be used in countries where there is a private pension fund adminsitration industry, but not in countries where the entirety of the pension system is publicly-funded. This indicator serves as a key barometer of competition, customer satisfaction, and market dynamics within the pension industry. It can signal trends to administrators, regulators, and members themselves.  Switching Rate (%) = Total average number of members in the system / number of members who switched pension fund administrators  ×100</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Do genders differ in how long they hold their transaction accounts? Are some genders disproportionately represented in longer, medium, or shorter account tenures? Which genders show higher account loyalty across different FSPs/types, and which tend to close accounts sooner?</t>
+          <t>How do transfers of pension fund balances to a different pension fund administrator vary by gender? Does this vary according to the level of FSP gender diversity? What percentage of contributors transferred funds compared to all customers, and are there gender disparities in this proportion? Are certain customer segments, such as women, women-owned MSMEs owners, and low-value accounts, more likely to make high-to-low transfers (switching to a fund administrator that has been paying lower returns)? Are FSPs with higher levels of gender diversity less likely to receive savers coming from an administrator that previously paid higher returns?</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Stability, safety and soundness</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Liquidity risk</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Pension type</t>
         </is>
       </c>
     </row>
@@ -8906,96 +8906,96 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
+          <t>Savings</t>
+        </is>
+      </c>
+      <c r="D159">
+        <v>151</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Tenure of deposit and payment accounts</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Average time elapsed since account opening</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Measures the length of time that deposit and payment accounts have been open, can be expressed as an average or as the share of accounts in tenure categories such as &lt;3 months, 3–6 months, 6–12 months, 1–3 years, &gt;3 years, etc. It reflects the age profile of active accounts held by customers at regulated financial institutions and payment service providers. Captures the stability, maturity, and longevity of customer relationships with financial institutions. It is a key behavioral measure of financial inclusion sustainability, distinguishing recently opened accounts from those that have remained active and in use over time. Tracking account tenure helps regulators and financial institutions to: Assess account retention and churn rates in deposit and payment systems; Monitor sustained usage versus one-off account openings, especially under inclusion programs; Identify short-lived or dormant accounts that may inflate access statistics; Evaluate the depth and continuity of customer engagement with the financial system. From a supervisory perspective, it provides insights into financial system stability, consumer loyalty, and the effectiveness of account-opening campaigns. A longer average tenure indicates stable customer relationships, active usage, and mature market penetration. A high share of newly opened accounts may suggest recent inclusion initiatives, but also potential fragility if those accounts become inactive. Monitoring shifts over time can reveal trends in account retention and digital adoption maturity. !- Definitions and concepts: Deposit accounts: Savings, current, or term accounts offered by regulated deposit-taking institutions. Payment accounts: Accounts used to execute payment transactions or access funds on demand, including e-money and digital wallets. !- Data requirements: Account-level data from administrative records containing the account opening date; Total number of accounts. The tenure is calculated as the difference between the data of the end of the reference period and the account opening data (expressed in years or months).</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Do genders differ in how long they hold their transaction accounts? Are some genders disproportionately represented in longer, medium, or shorter account tenures? Which genders show higher account loyalty across different FSPs/types, and which tend to close accounts sooner?</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Liquidity risk</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Consumer protection</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Suitability</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
           <t>Payments, Savings, Pensions, Investments</t>
         </is>
       </c>
-      <c r="D159">
+      <c r="D160">
         <v>158</v>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="E160" t="inlineStr">
         <is>
           <t>Inactive and dormant accounts (balance)</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>% of total account balances that are held in inactive and dormant accounts</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="G160" t="inlineStr">
         <is>
           <t>This indicator shows the share of funds sitting in deposit and payment accounts (excluding term deposits) that are not actively used by customers. High concentrations of idle balances can signal weak customer engagement, poor product fit, or frictions in account usage—important for financial-inclusion quality, liquidity management, and conduct risk. From a prudential angle, large dormant balances may look “stable” but can reverse if reactivation drives or policy changes prompt withdrawals. For consumer protection, persistent dormancy raises risks around unclaimed funds, fees, and fraud. Recommended to analyze of this indicator by product type (e.g. current/checking, mobile money, etc). !- Definitions and concepts: Accounts: demand/current accounts and other payment-capable deposit accounts. Inactive account: no customer-initiated debit/credit (card use, cash withdrawal/deposit, transfer) for a defined window (e.g., ≥90 or 180 days). System entries (interest, fees, bank corrections) don’t count. Dormant account: extended inactivity beyond a longer threshold (commonly ≥12 months) that may trigger special handling (restricted access, outreach, escheatment). Indicator formula: Balances in inactive + dormant transaction accounts divided by total transaction-account balances. Reporting the split (inactive vs. dormant) can provide further detail. !- Data requirements: Core-banking ledger with end-of-day balances, product codes, and last customer-initiated activity timestamp per account. Classification rules reflecting local definitions (inactive/dormant thresholds; treatment of standing orders/auto-debits). Ownership segment (retail/MSMEs), currency, and insured/uninsured flags. Optional: outreach attempts, reactivation outcomes, and fee assessments to monitor conduct risk. Limitations &amp; considerations: Definition divergence: thresholds and what counts as “activity” vary by jurisdiction and even by institution—state methodology clearly. Data quality: some channels (agents, fintech front-ends) may not update the core “last activity” field, overstating dormancy.
 Seasonality &amp; cycles: balances can spike around payroll/tax periods; use consistent month-end or averages. Policy effects: dormancy fees, auto-closures, and unclaimed-funds rules materially affect trends. Coverage scope: exclude escrow, trust, and suspense ledgers to avoid inflating inactive balances.</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
+      <c r="H160" t="inlineStr">
         <is>
           <t>What proportion of balances held in inactive/dormant/suspense accounts is attributable to each gender? Are these balances disproportionately skewed by gender? Which FSPs have notable skews (higher than market averages) in balances held in inactive/dormant/suspense accounts by gender?</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Account type</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Suitability</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D160">
-        <v>161</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Revenue from inactive and dormant accounts</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Average non-interest revenue earned on inactive and dormant accounts per account holder</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>This indicator estimates how much fee income a provider earns, on average, from customers whose transaction accounts are inactive or dormant. It highlights potential conduct-risk hotspots (“junk fees”), tests whether inclusion policies translate into active use, and helps gauge earnings reliance on non-usage charges. Regulators often scrutinize such revenue because it may disproportionately affect vulnerable or low-balance customers and can conflict with fair-treatment principles or local dormancy rules. Used alongside % balances in inactive/dormant accounts, reactivation rates, and complaints upheld about fees, this metric provides a balanced view of inclusion quality and earnings fairness. !- Definitions and concepts: Inactive account: no customer-initiated transaction over a defined window (e.g., ≥90/180 days). Dormant account: extended inactivity (e.g., ≥12 months) triggering special handling (restricted access, outreach, or escheatment). Non-interest revenue: maintenance/inactivity fees, SMS/statement charges, card fees, ATM/network fees, account closure fees—exclude interest, FX spreads, and lending-related fees. Metric (per holder): Avg. fee per inactive/dormant holder = [Non interest fees charged to inactive+dormant accounts in period (net of waivers/refunds)] divided by unique customers with ≥1 inactive or dormant account in period. Report per-account as a companion view, and show inactive vs dormant separately. !- Data requirements: Core-banking extracts: account status, last customer-initiated activity timestamp, balances, product code. General-ledger fee income by fee code with identifiers to tie fees to specific accounts/customers; flags for waivers/refunds/chargebacks. Customer master data to deduplicate holders with multiple accounts. Policy tables: inactivity/dormancy thresholds, fee schedules, and escheatment rules; time-at-risk (days classified as inactive/dormant). !- Limitations and considerations: Definition variance: thresholds and what counts as “activity” differ—state methodology. Partial-period bias: accounts turning dormant late in the period face fewer fee days; consider normalizing by days inactive/dormant. Outliers &amp; distribution: averages can be skewed; also report median, 90th percentile, and % of affected customers. Conduct/regulatory constraints: some jurisdictions cap or ban dormancy fees or require fee cessation before escheatment—track compliance and annotate series breaks after rule changes. Mix effects: product/channel mixes (e.g., basic accounts, youth or social-transfer accounts) drive fee propensity—segment results by product and customer segment.</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>How does the average revenue earned from inactive and dormant accounts compare by gender? Are there gender disparities in the charges applied to these accounts compared to the overall market average? How do relevant FSPs rank in terms of the average revenue earned from these accounts, and does this ranking change when analyzed by gender?</t>
-        </is>
-      </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9027,35 +9027,35 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Payments, Savings, Pensions, Investments</t>
         </is>
       </c>
       <c r="D161">
-        <v>229</v>
+        <v>161</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Product take-up ratio</t>
+          <t>Revenue from inactive and dormant accounts</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>% of approved applicants who take-up the approved products by product type</t>
+          <t>Average non-interest revenue earned on inactive and dormant accounts per account holder</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Share of applicants that are approved for a specific product type that take-up the product. This indicator can be viewed together with the product application indicator to allow for a more comprehensive analysis of the demand for financial products. Product categoreis to consider for analysis include: deposits, investments, insurance, credit.</t>
+          <t>This indicator estimates how much fee income a provider earns, on average, from customers whose transaction accounts are inactive or dormant. It highlights potential conduct-risk hotspots (“junk fees”), tests whether inclusion policies translate into active use, and helps gauge earnings reliance on non-usage charges. Regulators often scrutinize such revenue because it may disproportionately affect vulnerable or low-balance customers and can conflict with fair-treatment principles or local dormancy rules. Used alongside % balances in inactive/dormant accounts, reactivation rates, and complaints upheld about fees, this metric provides a balanced view of inclusion quality and earnings fairness. !- Definitions and concepts: Inactive account: no customer-initiated transaction over a defined window (e.g., ≥90/180 days). Dormant account: extended inactivity (e.g., ≥12 months) triggering special handling (restricted access, outreach, or escheatment). Non-interest revenue: maintenance/inactivity fees, SMS/statement charges, card fees, ATM/network fees, account closure fees—exclude interest, FX spreads, and lending-related fees. Metric (per holder): Avg. fee per inactive/dormant holder = [Non interest fees charged to inactive+dormant accounts in period (net of waivers/refunds)] divided by unique customers with ≥1 inactive or dormant account in period. Report per-account as a companion view, and show inactive vs dormant separately. !- Data requirements: Core-banking extracts: account status, last customer-initiated activity timestamp, balances, product code. General-ledger fee income by fee code with identifiers to tie fees to specific accounts/customers; flags for waivers/refunds/chargebacks. Customer master data to deduplicate holders with multiple accounts. Policy tables: inactivity/dormancy thresholds, fee schedules, and escheatment rules; time-at-risk (days classified as inactive/dormant). !- Limitations and considerations: Definition variance: thresholds and what counts as “activity” differ—state methodology. Partial-period bias: accounts turning dormant late in the period face fewer fee days; consider normalizing by days inactive/dormant. Outliers &amp; distribution: averages can be skewed; also report median, 90th percentile, and % of affected customers. Conduct/regulatory constraints: some jurisdictions cap or ban dormancy fees or require fee cessation before escheatment—track compliance and annotate series breaks after rule changes. Mix effects: product/channel mixes (e.g., basic accounts, youth or social-transfer accounts) drive fee propensity—segment results by product and customer segment.</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>How do take-up rates vary by gender? Do any genders have higher take-up rates than the overall market average? How do FSPs compare in terms of take-up rates by gender?</t>
+          <t>How does the average revenue earned from inactive and dormant accounts compare by gender? Are there gender disparities in the charges applied to these accounts compared to the overall market average? How do relevant FSPs rank in terms of the average revenue earned from these accounts, and does this ranking change when analyzed by gender?</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Uptake (account ownership)</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Product type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Account type</t>
         </is>
       </c>
     </row>
@@ -9082,55 +9082,55 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Fair treatment</t>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Savings</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D162">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Account closure costs paid by customers</t>
+          <t>Product take-up ratio</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Average customer-paid account closure charges</t>
+          <t>% of approved applicants who take-up the approved products by product type</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>This indicator captures the out-of-pocket costs borne by customers when they close their transaction account(s). It focuses on fees directly tied to the closure process (not ongoing usage fees). High averages or wide dispersion can signal unfair fee structures, poor process design (e.g., costly payout rails), or weak disclosures—issues that draw conduct-risk scrutiny and harm inclusion goals. Tracking this metric alongside complaints upheld about closure, time to close, and payout failure/return rates gives a rounded view of off-boarding fairness and efficiency. !- Definitions and concepts: Transaction accounts are broadly defined as an account held with a bank or other authorised and/or regulated service provider (including a non-bank) which can be used to make and receive payments. Transaction accounts can be further differentiated into deposit transaction accounts and e-money accounts. Customer-paid closure charges: amounts debited to the customer because of closure, including: explicit closure fees, final statement/document fees, card/cheque deactivation fees, balance-refund/payout charges (e.g., wire/RTGS, cheque issuance, e-money cash-out), account package early-termination fees, statutory taxes/levies linked to these items, and FX/transfer margins if required to remit funds. Exclusions: regular monthly maintenance already charged prior to the closure request, penalty interest on unrelated lending, and third-party fees not passed through. !- Data requirements: Event log with closure request date and closure completion date; customer ID (deduplicated), number of accounts closed, channel, reason code. Transaction-level fee taxonomy to flag closure-related charges; payout transactions (method, amount, fees, FX). Reversal/waiver flags and timestamps to net back rescinded charges. Recommended charge window: from request date through T+30 days after completion to catch settlement/payout fees. Number of customers who closed at least 1 account in period. !- Limitations and considerations: Attribution: define the fee list upfront to avoid counting routine usage fees; publish the measurement window.</t>
+          <t>Share of applicants that are approved for a specific product type that take-up the product. This indicator can be viewed together with the product application indicator to allow for a more comprehensive analysis of the demand for financial products. Product categoreis to consider for analysis include: deposits, investments, insurance, credit.</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>How do relevant FSPs rank in terms of closing costs (from highest to lowest), and does this ranking change when the average is computed by gender? Are women and men equally likely to incur account closure fees, or are there gendered patterns in the types of financial service providers (FSPs) they use that influence the likelihood or amount of such fees? How might account closure costs act as a barrier to financial flexibility or mobility? Are women more likely to avoid formal financial services due to concerns over the cost of exiting the system? Additionally, are FSPs that charge lower or no closure fees more accessible to certain gender groups, and does this vary by geography or provider type?</t>
+          <t>How do take-up rates vary by gender? Do any genders have higher take-up rates than the overall market average? How do FSPs compare in terms of take-up rates by gender?</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Financial inclusion; Market development</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Outcomes, Capital markets development</t>
+          <t>Uptake (account ownership)</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Product type</t>
         </is>
       </c>
     </row>
@@ -9142,55 +9142,55 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Suitability</t>
+          <t>Fair treatment</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Savings</t>
         </is>
       </c>
       <c r="D163">
-        <v>389</v>
+        <v>162</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Insurance claims (number)</t>
+          <t>Account closure costs paid by customers</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Number of insurance claims</t>
+          <t>Average customer-paid account closure charges</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>The total count of insurance claims formally submitted by policyholders, beneficiaries, or authorized third parties to an insurer within a defined reporting period, regardless of whether the claims are accepted, rejected, paid, or still under review. Denominator for several key inclusion, consumer protection and prudential insurance ratios. !- Data requirements: Claim identifier, (unique ID per claim), Policyholder identifier, Date of claim submission.</t>
+          <t>This indicator captures the out-of-pocket costs borne by customers when they close their transaction account(s). It focuses on fees directly tied to the closure process (not ongoing usage fees). High averages or wide dispersion can signal unfair fee structures, poor process design (e.g., costly payout rails), or weak disclosures—issues that draw conduct-risk scrutiny and harm inclusion goals. Tracking this metric alongside complaints upheld about closure, time to close, and payout failure/return rates gives a rounded view of off-boarding fairness and efficiency. !- Definitions and concepts: Transaction accounts are broadly defined as an account held with a bank or other authorised and/or regulated service provider (including a non-bank) which can be used to make and receive payments. Transaction accounts can be further differentiated into deposit transaction accounts and e-money accounts. Customer-paid closure charges: amounts debited to the customer because of closure, including: explicit closure fees, final statement/document fees, card/cheque deactivation fees, balance-refund/payout charges (e.g., wire/RTGS, cheque issuance, e-money cash-out), account package early-termination fees, statutory taxes/levies linked to these items, and FX/transfer margins if required to remit funds. Exclusions: regular monthly maintenance already charged prior to the closure request, penalty interest on unrelated lending, and third-party fees not passed through. !- Data requirements: Event log with closure request date and closure completion date; customer ID (deduplicated), number of accounts closed, channel, reason code. Transaction-level fee taxonomy to flag closure-related charges; payout transactions (method, amount, fees, FX). Reversal/waiver flags and timestamps to net back rescinded charges. Recommended charge window: from request date through T+30 days after completion to catch settlement/payout fees. Number of customers who closed at least 1 account in period. !- Limitations and considerations: Attribution: define the fee list upfront to avoid counting routine usage fees; publish the measurement window.</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>How do claim numbers vary by gender? Are there any gender groups logging fewer claims compared to the market average? Are there FSPs with particularly low or high claim numbers for certain genders? How do claim statistics intersect with policy type and customer demographics?</t>
+          <t>How do relevant FSPs rank in terms of closing costs (from highest to lowest), and does this ranking change when the average is computed by gender? Are women and men equally likely to incur account closure fees, or are there gendered patterns in the types of financial service providers (FSPs) they use that influence the likelihood or amount of such fees? How might account closure costs act as a barrier to financial flexibility or mobility? Are women more likely to avoid formal financial services due to concerns over the cost of exiting the system? Additionally, are FSPs that charge lower or no closure fees more accessible to certain gender groups, and does this vary by geography or provider type?</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Financial inclusion; Stability, safety and soundness</t>
+          <t>Financial inclusion; Market development</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Usage, Soundness</t>
+          <t>Outcomes, Capital markets development</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Fair treatment</t>
+          <t>Suitability</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9211,31 +9211,31 @@
         </is>
       </c>
       <c r="D164">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Insurance claims paid</t>
+          <t>Insurance claims (number)</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Value of insurance claims paid</t>
+          <t>Number of insurance claims</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>"Claims paid" represents the total cash outflow or settled obligations by an insurer to policyholders or beneficiaries for claims events during a reporting period. It includes only claims for which payment has been disbursed, regardless of whether additional claims are still outstanding or whether reserves were previously established. Tracking claims paid helps supervisors monitor liquidity, operational efficiency, and consumer protection outcomes. It provides a concrete measure of the insurer’s fulfillment of contractual obligations and complements other claims indicators (e.g., claims incurred, claims outstanding, unpaid approved claims). !- Data requirements: Claim identifier, (unique ID per claim), Policyholder identifier, Date of claim submission, Date of payment, Amount paid (full or partial), Product / policy type; . !- Limitations and considerations: paid claims may lag claims incurred due to reporting delays or extended claims handling processes; some claims are paid in installments, methodology must specify whether to include full or partial amounts; severe events can cause sudden increases in paid claims, interpretation should consider context. Segmentation by product line or policy type is recommended for supervisory analysis.</t>
+          <t>The total count of insurance claims formally submitted by policyholders, beneficiaries, or authorized third parties to an insurer within a defined reporting period, regardless of whether the claims are accepted, rejected, paid, or still under review. Denominator for several key inclusion, consumer protection and prudential insurance ratios. !- Data requirements: Claim identifier, (unique ID per claim), Policyholder identifier, Date of claim submission.</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>How do claim payments vary by gender? Are there any gender groups receiving fewer/lower payments compared to the market average? Are there FSPs with particularly low or high payment rate for certain genders? How do claim payment statistics intersect with policy type and customer demographics?</t>
+          <t>How do claim numbers vary by gender? Are there any gender groups logging fewer claims compared to the market average? Are there FSPs with particularly low or high claim numbers for certain genders? How do claim statistics intersect with policy type and customer demographics?</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9257,50 +9257,60 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Stability, safety and soundness</t>
+          <t>Consumer protection</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>AML/CFT</t>
+          <t>Fair treatment</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D165">
-        <v>64</v>
+        <v>390</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Suspicious transaction reports</t>
+          <t>Insurance claims paid</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Number of suspicious transaction reports</t>
+          <t>Value of insurance claims paid</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>The indicator tallies the suspicious transaction reports (STRs)  financial service providers file with the Financial Intelligence Unit (FIU) when they suspect financial crimes such as money-laundering and terrorism financing. A rising count can signal stronger transaction monitoring systems or higher level of potentially criminal activities. Policymakers use STR volumes, in combination with other data (e.g., investigations), to allocate investigative resources. !- Definitions and concepts: Suspicious Transaction Report (STR): a mandatory report filed when a transaction is known, suspected, or has reasonable grounds to be suspected of involving criminal proceeds or terrorist funds (FATF Rec. 20). Reporting entities: broadly, all institutions covered by the AML/CFT law, including all finacial financial service providers. !- Data requirements: FIU registry of incoming STRs, ideally tagged by date, reporting institution, sector, transaction channel, predicate crime category, and outcome (e.g., disseminated to law-enforcement), and customer gender. Data quality: Duplicate submissions, incomplete narratives, or vague suspicion reasons hamper analysis and inflate reported numbers without real value. Confidentiality constraints: Detailed STR data including customer gender may be restricted.</t>
+          <t>"Claims paid" represents the total cash outflow or settled obligations by an insurer to policyholders or beneficiaries for claims events during a reporting period. It includes only claims for which payment has been disbursed, regardless of whether additional claims are still outstanding or whether reserves were previously established. Tracking claims paid helps supervisors monitor liquidity, operational efficiency, and consumer protection outcomes. It provides a concrete measure of the insurer’s fulfillment of contractual obligations and complements other claims indicators (e.g., claims incurred, claims outstanding, unpaid approved claims). !- Data requirements: Claim identifier, (unique ID per claim), Policyholder identifier, Date of claim submission, Date of payment, Amount paid (full or partial), Product / policy type; . !- Limitations and considerations: paid claims may lag claims incurred due to reporting delays or extended claims handling processes; some claims are paid in installments, methodology must specify whether to include full or partial amounts; severe events can cause sudden increases in paid claims, interpretation should consider context. Segmentation by product line or policy type is recommended for supervisory analysis.</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the volume of Suspiciou transaction reports (STRs) generated, including for MSMEs by the owner's gender? Is there a correlation between the volume of these reports and the composition of the FSP customer base by gender? For example, do FSPs with a higher proportion of women in their customer base report a lower volume of STR? Are there disparities in STR statistics across FSPs with different levels of gender diversity?</t>
+          <t>How do claim payments vary by gender? Are there any gender groups receiving fewer/lower payments compared to the market average? Are there FSPs with particularly low or high payment rate for certain genders? How do claim payment statistics intersect with policy type and customer demographics?</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Usage, Soundness</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -9321,36 +9331,36 @@
         </is>
       </c>
       <c r="D166">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Systematic reporting to financial intelligence unit/office (FIU)</t>
+          <t>Suspicious transaction reports</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Number of transactions reported (excluding suspicious transaction reports) to FIU</t>
+          <t>Number of suspicious transaction reports</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>This indicator counts all objective anti-money-laundering (AML) disclosures that reporting institutions file with the FIU other than Suspicious Transaction Reports (STRs)—for example Cash / Large-Value Transaction Reports (CTRs/LCTRs), Cross-Border Currency Reports (CBCRs), Electronic Funds Transfer Reports (EFTIs), and threshold-based filings. Tracking the volume highlights how much potentially risky activity flows through the regulated system, tests the reach and effectiveness of automated monitoring engines, and helps the FIU size analytical workloads and allocate investigative resources. When combined with STR counts and outcome statistics, this indicator offers a comprehensive perspective on the preventive arm of the AML/CFT framework. !- Definitions and concepts: Objective reports: filings triggered automatically when a transaction exceeds a statutory threshold or meets a predefined typology—irrespective of suspicion. Thresholds are set at national level and vary across countries. Reporting entities: all AML-obliged financial institutions. Optional denominator metrics to enable intensity ratios: total transactions processed or number of active customers. !- Data requirements: FIU registry of objective-report filings with unique identifiers. Data-quality variance: Missing customer identifiers or incorrect codes hinder FIU analytics; robust validation routines are essential.</t>
+          <t>The indicator tallies the suspicious transaction reports (STRs)  financial service providers file with the Financial Intelligence Unit (FIU) when they suspect financial crimes such as money-laundering and terrorism financing. A rising count can signal stronger transaction monitoring systems or higher level of potentially criminal activities. Policymakers use STR volumes, in combination with other data (e.g., investigations), to allocate investigative resources. !- Definitions and concepts: Suspicious Transaction Report (STR): a mandatory report filed when a transaction is known, suspected, or has reasonable grounds to be suspected of involving criminal proceeds or terrorist funds (FATF Rec. 20). Reporting entities: broadly, all institutions covered by the AML/CFT law, including all finacial financial service providers. !- Data requirements: FIU registry of incoming STRs, ideally tagged by date, reporting institution, sector, transaction channel, predicate crime category, and outcome (e.g., disseminated to law-enforcement), and customer gender. Data quality: Duplicate submissions, incomplete narratives, or vague suspicion reasons hamper analysis and inflate reported numbers without real value. Confidentiality constraints: Detailed STR data including customer gender may be restricted.</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Are there customer gender disparities in the volume of systematic transaction reports (transactions that are not suspicious but reach regulatory thresholds for reporting) to the FIU, including for MSMEs by the owner's gender? Is there a correlation between the volume of these reports and the composition of the FSP customer base by gender? For example, do FSPs with a higher proportion of women in their customer base report a lower volume of systematic transaction reports, including those involving women? How do FSPs with different levels of gender diversity differ in the patterns of systematic reporting to the FIU?</t>
+          <t>Are there gender disparities in the volume of Suspiciou transaction reports (STRs) generated, including for MSMEs by the owner's gender? Is there a correlation between the volume of these reports and the composition of the FSP customer base by gender? For example, do FSPs with a higher proportion of women in their customer base report a lower volume of STR? Are there disparities in STR statistics across FSPs with different levels of gender diversity?</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Transaction type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -9362,55 +9372,45 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Credit risk</t>
+          <t>AML/CFT</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D167">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Gender composition of loan guarantors</t>
+          <t>Systematic reporting to financial intelligence unit/office (FIU)</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Gender composition of guarantors in the retail loan portfolio</t>
+          <t>Number of transactions reported (excluding suspicious transaction reports) to FIU</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Measures the representation of different genders among the individuals who act as loan guarantors--pledge to repay a loan if the borrower defaults. It offers a sophisticated lens through which to view credit risk, gender-based economic disparities, and the social dynamics that underpin a loan portfolio. It can reveal hidden concentration risks. For example, if a large portion of a bank's small business loans are guaranteed by the male spouses of female entrepreneurs, the portfolio's risk profile becomes heavily correlated with the financial health and stability of that specific demographic.  This metric also provides insights into the structural barriers different genders face when seeking credit. If the data shows that female borrowers disproportionately require male guarantors (while the reverse is not true), it can signal underlying biases in credit assessment or a disparity in asset ownership. Prudential supervisors may also be interested in finding out whether the different permutations of borrower's and guarantor's gender could relate to loan performance. Conduct supervisors would use it to scrutinize lending practices for fairness and equity.</t>
+          <t>This indicator counts all objective anti-money-laundering (AML) disclosures that reporting institutions file with the FIU other than Suspicious Transaction Reports (STRs)—for example Cash / Large-Value Transaction Reports (CTRs/LCTRs), Cross-Border Currency Reports (CBCRs), Electronic Funds Transfer Reports (EFTIs), and threshold-based filings. Tracking the volume highlights how much potentially risky activity flows through the regulated system, tests the reach and effectiveness of automated monitoring engines, and helps the FIU size analytical workloads and allocate investigative resources. When combined with STR counts and outcome statistics, this indicator offers a comprehensive perspective on the preventive arm of the AML/CFT framework. !- Definitions and concepts: Objective reports: filings triggered automatically when a transaction exceeds a statutory threshold or meets a predefined typology—irrespective of suspicion. Thresholds are set at national level and vary across countries. Reporting entities: all AML-obliged financial institutions. Optional denominator metrics to enable intensity ratios: total transactions processed or number of active customers. !- Data requirements: FIU registry of objective-report filings with unique identifiers. Data-quality variance: Missing customer identifiers or incorrect codes hinder FIU analytics; robust validation routines are essential.</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the representation of loan guarantors? What types of loans and borrowers, across different FSP types, are more likely to show gender disparities in the use of guarantors? Are there disparities in loan performance (NPLs, delinquency, interest income) depending on the gender of the guarantor?</t>
+          <t>Are there customer gender disparities in the volume of systematic transaction reports (transactions that are not suspicious but reach regulatory thresholds for reporting) to the FIU, including for MSMEs by the owner's gender? Is there a correlation between the volume of these reports and the composition of the FSP customer base by gender? For example, do FSPs with a higher proportion of women in their customer base report a lower volume of systematic transaction reports, including those involving women? How do FSPs with different levels of gender diversity differ in the patterns of systematic reporting to the FIU?</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>Consumer protection</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>Fair treatment</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Product type</t>
+          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Transaction type</t>
         </is>
       </c>
     </row>
@@ -9431,46 +9431,46 @@
         </is>
       </c>
       <c r="D168">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Delinquency rate in the loan portfolio</t>
+          <t>Gender composition of loan guarantors</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Volume and value of delinquent retail loans as a proportion of total retail portfolio</t>
+          <t>Gender composition of guarantors in the retail loan portfolio</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>The delinquency rate tracks the share of consumer loans—mortgages, credit-cards, instalment loans, auto, buy-now-pay-later, qualifying MSMEs—that have fallen past due but have not yet crossed the “non-performing” threshold or been written off. Rising early-stage arrears are an early-warning signal of household stress and of future spikes in non-performing loans (NPLs), provisions and write-offs. Paired with NPL, restructuring and write-off metrics, the delinquency rate provides a forward-looking barometer of retail credit health. Supervisors and risk managers use the metric to test the effectiveness of underwriting standards, consumer disclosure, customer interfaces (for digital loans), and pricing for credit risk. !- Definitions and concepts: Loan delinquency refers to a situation in which borrowed money is not paid back as agreed. A loan becomes delinquent when a borrower misses a regular installment payment. A delinquent loan is any kind of loan that has past due payments but has yet to go into default. On a value basis, this indicator measures the total outstanding balances past due (for example greater than 1 day past due) as a share of gross retail loan balances at the end of a specified period. Operational cut-offs: Inconsistent days past due calculation (calendar days vs. business days, partial payments) hinders cross-lender comparability.</t>
+          <t>Measures the representation of different genders among the individuals who act as loan guarantors--pledge to repay a loan if the borrower defaults. It offers a sophisticated lens through which to view credit risk, gender-based economic disparities, and the social dynamics that underpin a loan portfolio. It can reveal hidden concentration risks. For example, if a large portion of a bank's small business loans are guaranteed by the male spouses of female entrepreneurs, the portfolio's risk profile becomes heavily correlated with the financial health and stability of that specific demographic.  This metric also provides insights into the structural barriers different genders face when seeking credit. If the data shows that female borrowers disproportionately require male guarantors (while the reverse is not true), it can signal underlying biases in credit assessment or a disparity in asset ownership. Prudential supervisors may also be interested in finding out whether the different permutations of borrower's and guarantor's gender could relate to loan performance. Conduct supervisors would use it to scrutinize lending practices for fairness and equity.</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Are there gender disparities (including for MSMEs based on the gender of ownership) in delinquency rates (also considering the number of unpaid installments) for loans of different types, terms and sizes? Do smaller loans have lower delinquency rates and how does this vary across genders? Do FSPs with higher levels of gender diversity present lower delinquency rates?</t>
+          <t>Are there gender disparities in the representation of loan guarantors? What types of loans and borrowers, across different FSP types, are more likely to show gender disparities in the use of guarantors? Are there disparities in loan performance (NPLs, delinquency, interest income) depending on the gender of the guarantor?</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection</t>
+          <t>Consumer protection</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Outcomes, Suitability</t>
+          <t>Fair treatment</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Financial service provider (FSP) type; Financial service provider (FSP) gender diversity; Product type</t>
+          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Product type</t>
         </is>
       </c>
     </row>
@@ -9491,31 +9491,31 @@
         </is>
       </c>
       <c r="D169">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Non performing loans (NPLs)</t>
+          <t>Delinquency rate in the loan portfolio</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Non performing loans rate in the retail loan portfolio</t>
+          <t>Volume and value of delinquent retail loans as a proportion of total retail portfolio</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>The NPL indicator for the retail loan portfolio quantifies the share (or absolute value) of consumer and MSME loans that are unlikely to be fully repaid. Because retail credit typically involves high volumes of granular, often unsecured exposures, a build-up of NPLs signals mounting credit risk costs, pressure on provisioning, and potential stress. Supervisors track this metric to assess lenders' underwriting standards, resilience to economic shocks, and the effectiveness of arrears management. !- Definitions and concepts: An NPL is defined as a loan that is past-due for a minimum amount of days (e.g., 90 days). The definition can vary across countries but the Basel Committee has set common standards. The retail portfolio encompasses exposures to individuals and qualifying MSMEs treated under the retail asset class. The most common ratio is Gross NPLs ÷ Gross retail loans. Aggressive charge-offs or “evergreening” can temporarily lower the NPL ratio without improving underlying asset quality. Seasonality and relief measures: Payment holidays or pandemic moratoria may defer delinquencies, masking latent credit risk.</t>
+          <t>The delinquency rate tracks the share of consumer loans—mortgages, credit-cards, instalment loans, auto, buy-now-pay-later, qualifying MSMEs—that have fallen past due but have not yet crossed the “non-performing” threshold or been written off. Rising early-stage arrears are an early-warning signal of household stress and of future spikes in non-performing loans (NPLs), provisions and write-offs. Paired with NPL, restructuring and write-off metrics, the delinquency rate provides a forward-looking barometer of retail credit health. Supervisors and risk managers use the metric to test the effectiveness of underwriting standards, consumer disclosure, customer interfaces (for digital loans), and pricing for credit risk. !- Definitions and concepts: Loan delinquency refers to a situation in which borrowed money is not paid back as agreed. A loan becomes delinquent when a borrower misses a regular installment payment. A delinquent loan is any kind of loan that has past due payments but has yet to go into default. On a value basis, this indicator measures the total outstanding balances past due (for example greater than 1 day past due) as a share of gross retail loan balances at the end of a specified period. Operational cut-offs: Inconsistent days past due calculation (calendar days vs. business days, partial payments) hinders cross-lender comparability.</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the rates of non-performing loans (NPL) within retail/MSME portfolios, and how do these differences vary by age, income levels, geographic location, and types of financial service providers? Do women or other gender groups exhibit different patterns of loan repayment and default compared to men, and what factors might explain these variations? How do NPL rates differ across loan types, and are portfolios with higher female borrower participation associated with lower or higher NPL ratios? Are financial service providers with greater gender diversity in their workforce or leadership more effective at managing NPLs equitably across genders? What insights do gender-disaggregated NPL data provide regarding credit risk, financial resilience, and inclusion of vulnerable or underserved gender groups?</t>
+          <t>Are there gender disparities (including for MSMEs based on the gender of ownership) in delinquency rates (also considering the number of unpaid installments) for loans of different types, terms and sizes? Do smaller loans have lower delinquency rates and how does this vary across genders? Do FSPs with higher levels of gender diversity present lower delinquency rates?</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Quality, Suitability</t>
+          <t>Outcomes, Suitability</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Customer type; Customer gender; Financial service provider (FSP) type; Financial service provider (FSP) gender diversity; Product type</t>
         </is>
       </c>
     </row>
@@ -9551,31 +9551,31 @@
         </is>
       </c>
       <c r="D170">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Restructured loans</t>
+          <t>Non performing loans (NPLs)</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Volume and value of restructured loans as a proportion of total retail/MSME portfolio</t>
+          <t>Non performing loans rate in the retail loan portfolio</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>The restructured loans indicator tracks the portion of a lender's credit portfolio whose contractual terms have been modified to relieve a borrower in financial difficulty—by lowering the interest rate, extending maturity, granting grace periods, converting currency, or partially forgiving principal, or a mix of these. A rising stock signals mounting credit stress, latent loss risk, or even internal frauds or mismagement. While restructurings can help viable borrowers bridge a temporary shock, they may defer recognition of non-performing loans (NPLs). Supervisors watch both the level and the flow of restructurings to detect “ever-greening”. !- Definitions and concepts: Restructured (or renegotiated / forborne) loan: an exposure whose cash-flow terms have been modified for credit risk reasons and would not have been granted under comparable market conditions. Local definitions vary, while standard setting bodies such as the Basel Committe and IFRS have provided common standards. Indicator formula: Restructured loans ÷ Gross loans (stock measure). !- Limitations and considerations: Regulatory divergence: Some jurisdictions treat any concession as a restructuring; others exclude purely administrative changes, hampering cross-country comparisons. Forbearance episodes: Crisis-era moratoria or government-mandated payment holidays may inflate restructuring volumes temporarily, masking true borrower weakness. Portfolio mix effects: High-yield consumer portfolios often show higher restructuring rates than collateralised mortgages; segment analysis is essential.</t>
+          <t>The NPL indicator for the retail loan portfolio quantifies the share (or absolute value) of consumer and MSME loans that are unlikely to be fully repaid. Because retail credit typically involves high volumes of granular, often unsecured exposures, a build-up of NPLs signals mounting credit risk costs, pressure on provisioning, and potential stress. Supervisors track this metric to assess lenders' underwriting standards, resilience to economic shocks, and the effectiveness of arrears management. !- Definitions and concepts: An NPL is defined as a loan that is past-due for a minimum amount of days (e.g., 90 days). The definition can vary across countries but the Basel Committee has set common standards. The retail portfolio encompasses exposures to individuals and qualifying MSMEs treated under the retail asset class. The most common ratio is Gross NPLs ÷ Gross retail loans. Aggressive charge-offs or “evergreening” can temporarily lower the NPL ratio without improving underlying asset quality. Seasonality and relief measures: Payment holidays or pandemic moratoria may defer delinquencies, masking latent credit risk.</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of restructured loans within retail/MSME loan portfolios, and how do these differences vary by age, income levels, and geographic location? Are women or other gender groups more likely to have loans restructured, potentially reflecting differences in financial vulnerability or repayment capacity? How do patterns of loan restructuring differ across loan types and sectors by gender? Do financial service providers with greater gender diversity in their workforce or leadership demonstrate more equitable practices in loan restructuring across gender groups? What do gender-disaggregated data on restructured loans reveal about the resilience and support available to borrowers facing financial stress?</t>
+          <t>Are there gender disparities in the rates of non-performing loans (NPL) within retail/MSME portfolios, and how do these differences vary by age, income levels, geographic location, and types of financial service providers? Do women or WMSME exhibit different patterns of loan repayment and default compared to men, and what factors might explain these variations? How do NPL rates differ across loan types, and are portfolios with higher female borrower participation associated with lower or higher NPL ratios? Are financial service providers with greater gender diversity in their workforce or leadership more effective at managing NPLs equitably across genders? What insights do gender-disaggregated NPL data provide regarding credit risk, financial resilience, and inclusion of vulnerable or underserved gender groups?</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -9611,41 +9611,46 @@
         </is>
       </c>
       <c r="D171">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Large exposures</t>
+          <t>Restructured loans</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Large exposures as % of total capital</t>
+          <t>Volume and value of restructured loans as a proportion of total retail/MSME portfolio</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tracks a lender's credit exposures to single counterparties or groups that exceed a threshold (e.g., a % of capital) and ensures none breach the regulatory cap. !- Definitions and concepts: Exposure includes on- and off-balance-sheet items. !- Data requirements: Counterparty-level exposure data, eligible capital base.</t>
+          <t>The restructured loans indicator tracks the portion of a lender's credit portfolio whose contractual terms have been modified to relieve a borrower in financial difficulty—by lowering the interest rate, extending maturity, granting grace periods, converting currency, or partially forgiving principal, or a mix of these. A rising stock signals mounting credit stress, latent loss risk, or even internal frauds or mismagement. While restructurings can help viable borrowers bridge a temporary shock, they may defer recognition of non-performing loans (NPLs). Supervisors watch both the level and the flow of restructurings to detect “ever-greening”. !- Definitions and concepts: Restructured (or renegotiated / forborne) loan: an exposure whose cash-flow terms have been modified for credit risk reasons and would not have been granted under comparable market conditions. Local definitions vary, while standard setting bodies such as the Basel Committe and IFRS have provided common standards. Indicator formula: Restructured loans ÷ Gross loans (stock measure). !- Limitations and considerations: Regulatory divergence: Some jurisdictions treat any concession as a restructuring; others exclude purely administrative changes, hampering cross-country comparisons. Forbearance episodes: Crisis-era moratoria or government-mandated payment holidays may inflate restructuring volumes temporarily, masking true borrower weakness. Portfolio mix effects: High-yield consumer portfolios often show higher restructuring rates than collateralised mortgages; segment analysis is essential.</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Are higher levels of gender diversity at FSPs and in their customer base correlated with lower levels of large exposures in loan operations? How are large exposures distributed across different products, gender, and locations? Do large exposures show different delinquency and NPL levels based on gender?</t>
+          <t>Are there gender disparities in the share of restructured loans within retail/MSME loan portfolios, and how do these differences vary by age, income levels, and geographic location? Are women or other gender groups more likely to have loans restructured, potentially reflecting differences in financial vulnerability or repayment capacity? How do patterns of loan restructuring differ across loan types and sectors by gender? Do financial service providers with greater gender diversity in their workforce or leadership demonstrate more equitable practices in loan restructuring across gender groups? What do gender-disaggregated data on restructured loans reveal about the resilience and support available to borrowers facing financial stress?</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Consumer protection</t>
+          <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Safety and security</t>
+          <t>Quality, Suitability</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -9657,7 +9662,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Credit risk, Soundness</t>
+          <t>Credit risk</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -9666,41 +9671,41 @@
         </is>
       </c>
       <c r="D172">
-        <v>262</v>
+        <v>118</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Write-offs ratio</t>
+          <t>Large exposures</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Volume and value of written off retail loans as a proportion of retail/MSME portfolio</t>
+          <t>Large exposures as % of total capital</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>The write-offs ratio tracks the portion of the retail loan portfolio that a lender permanently removes from its balance sheet within a period because collection is deemed impossible or uneconomic. It is a forward-looking credit-risk barometer: rising write-offs shrink the loan book, erode earnings through higher impairment charges, and may reveal weaknesses in underwriting or collections. Supervisors examine the indicator alongside NPL and provisioning coverage to judge whether lenders are recognising losses promptly or postponing them through restructurings. !- Definitions and concepts: Write-offs ratio is usually expressed as (Gross retail loan write-offs during period ÷ Average gross retail loans outstanding). Write-off: an accounting action that derecognises the unrecoverable portion of a loan’s amortised cost. It does not preclude further collections, which are recognised as recoveries. !- Limitations and considerations:  Timing disparities: Institutions with aggressive 180-day charge-off policies show higher ratios than peers that delay write-offs until legal exhaustion, complicating comparisons..</t>
+          <t>Tracks a lender's credit exposures to single counterparties or groups that exceed a threshold (e.g., a % of capital) and ensures none breach the regulatory cap. !- Definitions and concepts: Exposure includes on- and off-balance-sheet items. !- Data requirements: Counterparty-level exposure data, eligible capital base.</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the incidence of loan write-offs among retail/MSME borrowers? How do these disparities shift when further disaggregated by age, income, loan size, and geographic location? Do women or other gender groups experience higher or lower write-off rates compared to men, and what factors might explain these patterns? When analyzed in relation to the gender diversity of financial service providers’ leadership or top management, is higher gender diversity associated with more equitable write-off rates across customer genders? What insights do gender-disaggregated write-off data provide about risk assessment, financial inclusion, and borrower resilience?</t>
+          <t>Are higher levels of gender diversity at FSPs and in their customer base correlated with lower levels of large exposures in loan operations? How are large exposures distributed across different products, gender, and locations? Do large exposures show different delinquency and NPL levels based on gender?</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Financial inclusion; Consumer protection</t>
+          <t>Consumer protection</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Outcomes, Suitability</t>
+          <t>Safety and security</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -9721,31 +9726,26 @@
         </is>
       </c>
       <c r="D173">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Loan loss provisions</t>
+          <t>Write-offs ratio</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>% of the outstanding loan portfolio set aside as provisions for expected credit losses</t>
+          <t>Volume and value of written off retail loans as a proportion of retail/MSME portfolio</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Loan loss provisions (LLPs) are the expenses a lender records to cover expected credit losses on its loan portfolio. They represent management’s best estimate of future cash shortfalls arising from borrower defaults or deteriorating credit quality. Adequate provisioning is critical for portraying true earnings, maintaining solvency, and sustaining market confidence. Monitoring LLP trends alongside non-performing loan inflows, write-offs, and capital ratios provides a holistic view of a bank’s credit-risk resilience and earnings quality. Definitions &amp; concepts: Loan Loss Provision (expense) – the profit-and-loss charge that increases the Allowance for Expected Credit Losses (ECL) on the balance sheet. !- Data requirements: LLP expenses segmented by product, geography, collateral type. Total loan portfolio value.</t>
+          <t>The write-offs ratio tracks the portion of the retail loan portfolio that a lender permanently removes from its balance sheet within a period because collection is deemed impossible or uneconomic. It is a forward-looking credit-risk barometer: rising write-offs shrink the loan book, erode earnings through higher impairment charges, and may reveal weaknesses in underwriting or collections. Supervisors examine the indicator alongside NPL and provisioning coverage to judge whether lenders are recognising losses promptly or postponing them through restructurings. !- Definitions and concepts: Write-offs ratio is usually expressed as (Gross retail loan write-offs during period ÷ Average gross retail loans outstanding). Write-off: an accounting action that derecognises the unrecoverable portion of a loan’s amortised cost. It does not preclude further collections, which are recognised as recoveries. !- Limitations and considerations:  Timing disparities: Institutions with aggressive 180-day charge-off policies show higher ratios than peers that delay write-offs until legal exhaustion, complicating comparisons..</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the provisioning level allocated to customers? When disaggregated by other demographics such as age and location, do the observed gender-based differences change? Do vulnerable customers tend to have loans with higher provisioning levels, and are there gender differences in these patterns? When analyzed in relation to the gender diversity of FSPs' top management, is a higher level of gender diversity associated with differences in provisioning levels? And how does this relationship compare when considering gender diversity across other staff levels?</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>Are there gender disparities in the incidence of loan write-offs among retail/MSME borrowers? How do these disparities shift when further disaggregated by age, income, loan size, and geographic location? Do women or other gender groups experience higher or lower write-off rates compared to men, and what factors might explain these patterns? When analyzed in relation to the gender diversity of financial service providers’ leadership or top management, is higher gender diversity associated with more equitable write-off rates across customer genders? What insights do gender-disaggregated write-off data provide about risk assessment, financial inclusion, and borrower resilience?</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Product type; Loan size</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Credit risk</t>
+          <t>Credit risk, Soundness</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9781,31 +9781,46 @@
         </is>
       </c>
       <c r="D174">
-        <v>125</v>
+        <v>263</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Physical risk in the credit portfolio</t>
+          <t>Loan loss provisions</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Exposure of the credit portfolio to customers/industries with high physical risk related to climate change</t>
+          <t>% of the outstanding loan portfolio set aside as provisions for expected credit losses</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>This indicator quantifies how much of the loan book is exposed to climate-related physical risks, specifically. These risks materialize through direct damage to assets, disruptions in business operations, or negative impacts on local economies, all of which can lead to higher rates of loan defaults and losses for the lender. This indicator should complement the all-encompassing indicator that measures climate-related risks (both physical and transition risks). Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, including physical risks, while the NGFS provides a range of additional defintions, including nature-related financial risks.</t>
+          <t>Loan loss provisions (LLPs) are the expenses a lender records to cover expected credit losses on its loan portfolio. They represent management’s best estimate of future cash shortfalls arising from borrower defaults or deteriorating credit quality. Adequate provisioning is critical for portraying true earnings, maintaining solvency, and sustaining market confidence. Monitoring LLP trends alongside non-performing loan inflows, write-offs, and capital ratios provides a holistic view of a bank’s credit-risk resilience and earnings quality. Definitions &amp; concepts: Loan Loss Provision (expense) – the profit-and-loss charge that increases the Allowance for Expected Credit Losses (ECL) on the balance sheet. !- Data requirements: LLP expenses segmented by product, geography, collateral type. Total loan portfolio value.</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Are there gender disparities in the provisioning level allocated to customers? When disaggregated by other demographics such as age and location, do the observed gender-based differences change? Do vulnerable customers tend to have loans with higher provisioning levels, and are there gender differences in these patterns? When analyzed in relation to the gender diversity of FSPs' top management, is a higher level of gender diversity associated with differences in provisioning levels? And how does this relationship compare when considering gender diversity across other staff levels?</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Outcomes, Suitability</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Customer gender; Customer type; Financial service provider (FSP) type; Product type; Loan size; Loan term</t>
+          <t>Customer gender; Financial service provider (FSP) gender diversity; Customer type; Financial service provider (FSP) type; Product type; Loan size</t>
         </is>
       </c>
     </row>
@@ -9817,40 +9832,40 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Liquidity risk</t>
+          <t>Credit risk</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Investments</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D175">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Liquidity ratio</t>
+          <t>Physical risk in the credit portfolio</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Liquidity ratio</t>
+          <t>Exposure of the credit portfolio to customers/industries with high physical risk related to climate change</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>The liquidity ratio tests whether an entity holds enough high quality liquid assets to survive a 30-day stress scenario. !- Definitions and concepts: definition of liquidity ratios can vary across countries. The Basel Committee has provided definitions for the Liquidity Coverage Ratio and the Net Stable Funding, but many countries use simpler liquidity ratio definitions. For the insurance sector, the International Association of Insurance Supervisors has also proposed liquidity metrics using an exposure approach (Insurance Liquidity Ratio) and a company projection approach (based on cash flows).</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>How are FSP gender diversity and the gender composition of the customer base correlated with liquidity risk?</t>
+          <t>This indicator quantifies how much of the loan book is exposed to climate-related physical risks, specifically. These risks materialize through direct damage to assets, disruptions in business operations, or negative impacts on local economies, all of which can lead to higher rates of loan defaults and losses for the lender. This indicator should complement the all-encompassing indicator that measures climate-related risks (both physical and transition risks). Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, including physical risks, while the NGFS provides a range of additional defintions, including nature-related financial risks.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity</t>
+          <t>Customer gender; Customer type; Financial service provider (FSP) type; Product type; Loan size; Loan term</t>
         </is>
       </c>
     </row>
@@ -9862,40 +9877,40 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Market risk</t>
+          <t>Liquidity risk</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Insurance, Pensions, Investments</t>
+          <t>Payments, Savings, Credit, Insurance, Investments</t>
         </is>
       </c>
       <c r="D176">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Value at Risk (VaR)</t>
+          <t>Liquidity ratio</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Exposure to market risk (value volatility in the trading book)</t>
+          <t>Liquidity ratio</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>VaR estimates the maximum potential trading-book loss over a specified horizon at a given confidence level (e.g., one-day 99%). It informs market risk limits and capital requirements for market risk. !- Definitions and concepts: market risk definition and standardized calculations vary across jurisdictions. Standards are provided by international standard setting bodies such as the Basel Committee.</t>
+          <t>The liquidity ratio tests whether an entity holds enough high quality liquid assets to survive a 30-day stress scenario. !- Definitions and concepts: definition of liquidity ratios can vary across countries. The Basel Committee has provided definitions for the Liquidity Coverage Ratio and the Net Stable Funding, but many countries use simpler liquidity ratio definitions. For the insurance sector, the International Association of Insurance Supervisors has also proposed liquidity metrics using an exposure approach (Insurance Liquidity Ratio) and a company projection approach (based on cash flows).</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Is there a correlation between higher levels of gender diversity in FSPs and lower risk levels?</t>
+          <t>How are FSP gender diversity and the gender composition of the customer base correlated with liquidity risk?</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity</t>
         </is>
       </c>
     </row>
@@ -9907,50 +9922,40 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Operational risk</t>
+          <t>Market risk</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Payments, Savings</t>
+          <t>Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D177">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Balance of suspense accounts</t>
+          <t>Value at Risk (VaR)</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Value of balances of suspense accounts</t>
+          <t>Exposure to market risk (value volatility in the trading book)</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Suspense accounts are temporary holding ledgers used when a transaction cannot be posted to its final customer account because critical details are missing or disputed or due to any technical issues. The balance of suspense accounts aggregates the outstanding debit or credit amounts awaiting resolution. Persistently high or growing balances signal weaknesses in reconciliation, client on-boarding, Know-Your-Customer (KYC) data quality, payment-processing controls, or even internal fraud. Ageing buckets: some regulators require ageing of reported balances (0-30, 31-90, 91-180, &gt;180 days) to identify balances that exceed tolerance windows. !- Limitations and considerations: Accounting practices vary: some institutions clear items by moving them to internal “parking” accounts that may not be labelled suspense, understating the indicator. Standardization is needed to ensure reporting of balances in similar accounts that are not labelled "suspense accounts". Regulatory treatment: in certain jurisdictions, long-dated unresolved credits are treated as unclaimed funds.</t>
+          <t>VaR estimates the maximum potential trading-book loss over a specified horizon at a given confidence level (e.g., one-day 99%). It informs market risk limits and capital requirements for market risk. !- Definitions and concepts: market risk definition and standardized calculations vary across jurisdictions. Standards are provided by international standard setting bodies such as the Basel Committee.</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the average amount of funds in suspense accounts, including for low-income customers and MSMEs based on the ownership gender? Are there gender disparities in the distribution of low-income customers with suspense accounts (and for which types of accounts?) compared to the whole customer base? Comparing this indicator with failed transactions and customer losses (if available), are there gender disparities in financial losses after funds remain in suspense or temporary accounts, which could indicate potential internal frauds? Comparing this indicator with FSP gender diversity, does higher gender diversity correlate with lower amounts in suspense accounts or customer losses after funds are temporarily placed in suspense accounts?</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>Usage, Suitability</t>
+          <t>Is there a correlation between higher levels of gender diversity in FSPs and lower risk levels?</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -9967,30 +9972,30 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Payments, Savings</t>
         </is>
       </c>
       <c r="D178">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Incomplete/failed transactions</t>
+          <t>Balance of suspense accounts</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>% of all initiated transactions that are incomplete or failed</t>
+          <t>Value of balances of suspense accounts</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Measures the percentage of transactions that users initiate but that do not successfully complete as intended. It's a metric for assessing the reliability, usability, and accessibility of a digital financial service. A high rate of incomplete or failed transactions points to a poor user experience, and may lead to financial loss if funds are temporarily held and not returned. A sudden spike in this indicator can be an early warning of technical problems, cybersecurity attacks, or capacity issues. Incomplete transactions: transactions that are started by the user but are never fully processed to a conclusion. They are often "timed out" or abandoned. Failed transactions: transactions that are fully processed by the system but are ultimately rejected. The system actively returns an error message confirming the failure.</t>
+          <t>Suspense accounts are temporary holding ledgers used when a transaction cannot be posted to its final customer account because critical details are missing or disputed or due to any technical issues. The balance of suspense accounts aggregates the outstanding debit or credit amounts awaiting resolution. Persistently high or growing balances signal weaknesses in reconciliation, client on-boarding, Know-Your-Customer (KYC) data quality, payment-processing controls, or even internal fraud. Ageing buckets: some regulators require ageing of reported balances (0-30, 31-90, 91-180, &gt;180 days) to identify balances that exceed tolerance windows. !- Limitations and considerations: Accounting practices vary: some institutions clear items by moving them to internal “parking” accounts that may not be labelled suspense, understating the indicator. Standardization is needed to ensure reporting of balances in similar accounts that are not labelled "suspense accounts". Regulatory treatment: in certain jurisdictions, long-dated unresolved credits are treated as unclaimed funds.</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Do incomplete/failed transactions impact different genders differently, including low-income customers and MSMEs based on the ownership gender? Comparing this indicator with the amount of losses suffered by customers (if available), are there gender disparities in financial losses due to failed transactions? How does this indicator compare with indicators on values maintained in suspense accounts and their variation by gender? Do different types of FSPs and accounts perform differently across the gender in terms of failed transactions? Comparing this indicator with gender diversity, does higher gender diversity correlate with a lower prevalence of failed transactions?</t>
+          <t>Are there gender disparities in the average amount of funds in suspense accounts, including for low-income customers and MSMEs based on the ownership gender? Are there gender disparities in the distribution of low-income customers with suspense accounts (and for which types of accounts?) compared to the whole customer base? Comparing this indicator with failed transactions and customer losses (if available), are there gender disparities in financial losses after funds remain in suspense or temporary accounts, which could indicate potential internal frauds? Comparing this indicator with FSP gender diversity, does higher gender diversity correlate with lower amounts in suspense accounts or customer losses after funds are temporarily placed in suspense accounts?</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10005,7 +10010,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Transaction type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -10026,98 +10031,98 @@
         </is>
       </c>
       <c r="D179">
+        <v>29</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Incomplete/failed transactions</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>% of all initiated transactions that are incomplete or failed</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Measures the percentage of transactions that users initiate but that do not successfully complete as intended. It's a metric for assessing the reliability, usability, and accessibility of a digital financial service. A high rate of incomplete or failed transactions points to a poor user experience, and may lead to financial loss if funds are temporarily held and not returned. A sudden spike in this indicator can be an early warning of technical problems, cybersecurity attacks, or capacity issues. Incomplete transactions: transactions that are started by the user but are never fully processed to a conclusion. They are often "timed out" or abandoned. Failed transactions: transactions that are fully processed by the system but are ultimately rejected. The system actively returns an error message confirming the failure.</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Do incomplete/failed transactions impact different genders differently, including low-income customers and MSMEs based on the ownership gender? Comparing this indicator with the amount of losses suffered by customers (if available), are there gender disparities in financial losses due to failed transactions? How does this indicator compare with indicators on values maintained in suspense accounts and their variation by gender? Do different types of FSPs and accounts perform differently across the gender in terms of failed transactions? Comparing this indicator with gender diversity, does higher gender diversity correlate with a lower prevalence of failed transactions?</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Usage, Suitability</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Transaction type</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+        </is>
+      </c>
+      <c r="D180">
         <v>106</v>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="E180" t="inlineStr">
         <is>
           <t>Operational disruption incidents</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>Number of operational disruption incidents</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
+      <c r="G180" t="inlineStr">
         <is>
           <t>This indicator counts and classifies events that interrupt an institution’s ability to deliver financial services—whether due to IT failures, cyber-attacks, power outages, third-party breakdowns, or physical events (e.g., fire, pandemic lockdowns). Regulators track both the frequency and severity (e.g., service-unavailable minutes, customers affected, monetary losses) to judge the resilience of regulated services. A rising trend can erode confidence and expose the system to contagion if multiple firms rely on the same outsourced providers or infrastructure.
 !- Definitions and concepts: Operational disruption incident: an unplanned event that prevents or materially degrades the delivery of a critical business service beyond a defined tolerance. Definitions, including of critical services, vary across countries. Standard setting bodies including the Basel Committee provide standardized definitions that can be used. 
 Impact metrics: duration, peak concurrent users affected, transaction backlog, financial loss, data-integrity impact, customer detriment, others. Root-cause categories: hardware/software failure, cyber-intrusion, third-party outage, human error, environmental event, others. !- Limitations and considerations: Firms may fear reputational damage so there is a risk of under-reporting. Heterogeneous critical-service definitions may be used across firm, so regulatory standardization is needed.</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
+      <c r="H180" t="inlineStr">
         <is>
           <t>How are FSP gender diversity and gender composition of customer base correlated with the frequency of operational disruption incidents?</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr">
+      <c r="J180" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="K180" t="inlineStr">
         <is>
           <t>Quality, Data privacy and protection</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
+      <c r="L180" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity; Transaction type</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Operational risk</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
-        </is>
-      </c>
-      <c r="D180">
-        <v>107</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Successful cyber attacks</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>Number of successful cyber attacks</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>A measure of the frequency of cyberattacks on regulated financial institutions over a specified period. !- Definitions and concepts: A cyberattack is any intentional effort to steal, expose, alter, disable, or destroy data, applications, or other assets through unauthorized access to a network, computer system or digital device. Cyberattacks can disrupt and damage businesses and often carry high costs, including the costs of discovering and responding to the violation, downtime and lost revenue, and the long-term reputational damage to a business and its brand. Data requirement: Self-reporting of the number of successful cyberattacks by FSPs or data from other parties that track the incidence and severity of cyberattacks.</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Are higher levels of gender diversity at FSPs correlated with the frequency of successful cyber attacks?</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>Financial inclusion; Consumer protection</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>Outcomes, Safety and security</t>
-        </is>
-      </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type; Transaction type</t>
         </is>
       </c>
     </row>
@@ -10129,35 +10134,35 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Soundness</t>
+          <t>Operational risk</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D181">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Cost of reinsurance</t>
+          <t>Successful cyber attacks</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Premiums ceded to reinsurers as % of gross premium written</t>
+          <t>Number of successful cyber attacks</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>The cost of reinsurance indicator quantifies the price an insurer pays to transfer part of its underwriting risk to reinsurers. Tracked as either an absolute expense or as a ratio—most often Reinsurance premium ceded ÷ Gross premiums written (GPW)—it shows how much earnings capacity the insurer surrenders for balance-sheet protection. Rising costs may stem from hardening global reinsurance markets, high catastrophe exposures, deteriorating loss experience or weakened credit quality of the insurer. Supervisors and rating agencies watch for excessive reliance on expensive reinsurance cover which can compress margins, while under-spending may leave the insurer over-exposed to shocks. Evaluated over time and in tandem with retention ratios, claims ratio and solvency coverage, the cost of reinsurance reveals whether an insurer’s risk transfer strategy is adequate. !- Definitions and concepts: Reinsurance premium ceded: contractual payments (net of commissions) made to reinsurers for proportional (quota-share, surplus) or non-proportional (excess-of-loss, stop-loss) treaties, booked at treaty inception. Net cost of reinsurance: ceded premium minus ceding commission plus profit-commission adjustments and reinstatement premiums. Timing mismatches: Premiums are typically paid up-front, while recoveries occur post-loss, so annual cost ratios can spike in growth years and dip after large events.</t>
+          <t>A measure of the frequency of cyberattacks on regulated financial institutions over a specified period. !- Definitions and concepts: A cyberattack is any intentional effort to steal, expose, alter, disable, or destroy data, applications, or other assets through unauthorized access to a network, computer system or digital device. Cyberattacks can disrupt and damage businesses and often carry high costs, including the costs of discovering and responding to the violation, downtime and lost revenue, and the long-term reputational damage to a business and its brand. Data requirement: Self-reporting of the number of successful cyberattacks by FSPs or data from other parties that track the incidence and severity of cyberattacks.</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>How do FSPs’ gender diversity and the gender composition of their customer base correlate with the costs incurred from reinsurance? Are there gendered patterns in how reinsurance expenses impact insurers and their customers?</t>
+          <t>Are higher levels of gender diversity at FSPs correlated with the frequency of successful cyber attacks?</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10167,12 +10172,12 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Quality, Suitability</t>
+          <t>Outcomes, Safety and security</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type; Transaction type</t>
         </is>
       </c>
     </row>
@@ -10193,26 +10198,26 @@
         </is>
       </c>
       <c r="D182">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Insurance claims (loss) ratio</t>
+          <t>Cost of reinsurance</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>% of total premium income paid out as claims</t>
+          <t>Premiums ceded to reinsurers as % of gross premium written</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>The claims paid ratio compares the amount of benefits and claims an insurer actually disburses during a period with the premium income it records for the same portfolio. It answers a basic question for supervisors, policy-holders, and analysts: How much of each premium dollar flows back to customers in the form of claims? Persistently low ratios may flag overly aggressive pricing, onerous exclusions, or servicing bottlenecks, while very high ratios can foreshadow reserve inadequacy, under-pricing, or a spike in catastrophe losses. In combination with the expense ratio, the indicator feeds into the overall loss or combined ratio that underpins solvency and profitability assessments. !- Definitions and concepts: Claims paid: cash actually settled with policy-holders and claimants in the accounting period, including partial payments and salvage recoveries netted where local GAAP allows. It excludes outstanding claims reserves and IBNR, which are captured by “claims incurred.” Gross vs. net basis: gross claims ignore reinsurance recoveries; net claims deduct them, better reflecting the insurer’s retained risk. Segmented ratios (e.g., motor, health, property) pinpoint product-level profitability. !- Data requirements: Extracts from the claims-management system showing paid amounts, dates, line of business, and reinsurance cessions. Premium registers (written or earned, depending on supervisory preference) reconciled to the general ledger. Catastrophe tags, legal-settlement flags, and large-loss registers to isolate one-off distortions. Limitations &amp; considerations: Timing mismatch: annual premiums are often received up-front, whereas claim payments can lag; using earned premiums mitigates, but does not eliminate, this distortion. Claims-handling practices: delayed settlement or dispute escalation depresses the ratio without improving true risk experience. Reinsurance structure: quota-share vs. excess-of-loss treaties change the net ratio dramatically; analysts should review both gross and net perspectives. Regulatory definitions: some jurisdictions fold surrenders of savings-type contracts into claims, inflating comparability. Trend analysis should therefore pair the claims paid ratio with claims-incurred and reserve-adequacy metrics, catastrophe-loss disclosures, and expense dynamics to obtain a holistic view of underwriting performance and solvency resilience.</t>
+          <t>The cost of reinsurance indicator quantifies the price an insurer pays to transfer part of its underwriting risk to reinsurers. Tracked as either an absolute expense or as a ratio—most often Reinsurance premium ceded ÷ Gross premiums written (GPW)—it shows how much earnings capacity the insurer surrenders for balance-sheet protection. Rising costs may stem from hardening global reinsurance markets, high catastrophe exposures, deteriorating loss experience or weakened credit quality of the insurer. Supervisors and rating agencies watch for excessive reliance on expensive reinsurance cover which can compress margins, while under-spending may leave the insurer over-exposed to shocks. Evaluated over time and in tandem with retention ratios, claims ratio and solvency coverage, the cost of reinsurance reveals whether an insurer’s risk transfer strategy is adequate. !- Definitions and concepts: Reinsurance premium ceded: contractual payments (net of commissions) made to reinsurers for proportional (quota-share, surplus) or non-proportional (excess-of-loss, stop-loss) treaties, booked at treaty inception. Net cost of reinsurance: ceded premium minus ceding commission plus profit-commission adjustments and reinstatement premiums. Timing mismatches: Premiums are typically paid up-front, while recoveries occur post-loss, so annual cost ratios can spike in growth years and dip after large events.</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Are there gender disparities in claims ratios for insurance products, including for MSMEs based on the owner's gender? Are excessively low claims ratios correlated with low premiums (a proxy for targeting lower-income segments)? Are women more likely to be targeted by products with low claims ratios, potentially indicating lower-value offerings? Are FSPs with higher levels of gender diversity less likely to have excessively low claims ratios for insurance sold to vulnerable segments, such as women and women-owned MSMEs? When comparing with coverage ratios (amount of claims paid relative to the claim value), how do gender disparities in coverage ratios compare with claims paid?</t>
+          <t>How do FSPs’ gender diversity and the gender composition of their customer base correlate with the costs incurred from reinsurance? Are there gendered patterns in how reinsurance expenses impact insurers and their customers?</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10222,7 +10227,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Usage, Suitability</t>
+          <t>Quality, Suitability</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -10248,26 +10253,26 @@
         </is>
       </c>
       <c r="D183">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Insurance claims incurred</t>
+          <t>Insurance claims (loss) ratio</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Value of insurance claims incurred</t>
+          <t>% of total premium income paid out as claims</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>“Claims incurred” represents the total cost an insurer recognises for claims events during a reporting period, regardless of whether they have been paid yet. Tracking the level and trend of incurred claims helps supervisors monitor the financial health of insurers such as by detecting emerging risk clusters (e.g., climate-driven catastrophes). !- Definitions and concepts: Claims incurred = Claims paid + Change in outstanding claims reserves + Change in IBNR (incurred-but-not-reported) reserves ± Claims-handling expense reserve movements. !- Data requirements: Total claims incurred.  !- Limitations and considerations: Catastrophe volatility: Single severe events cause spikes. Used alongside premium growth, claims-ratio components, and reserve-adequacy studies, “claims incurred” provides a cornerstone view of underwriting performance and balance-sheet resilience.</t>
+          <t>The claims paid ratio compares the amount of benefits and claims an insurer actually disburses during a period with the premium income it records for the same portfolio. It answers a basic question for supervisors, policy-holders, and analysts: How much of each premium dollar flows back to customers in the form of claims? Persistently low ratios may flag overly aggressive pricing, onerous exclusions, or servicing bottlenecks, while very high ratios can foreshadow reserve inadequacy, under-pricing, or a spike in catastrophe losses. In combination with the expense ratio, the indicator feeds into the overall loss or combined ratio that underpins solvency and profitability assessments. !- Definitions and concepts: Claims paid: cash actually settled with policy-holders and claimants in the accounting period, including partial payments and salvage recoveries netted where local GAAP allows. It excludes outstanding claims reserves and IBNR, which are captured by “claims incurred.” Gross vs. net basis: gross claims ignore reinsurance recoveries; net claims deduct them, better reflecting the insurer’s retained risk. Segmented ratios (e.g., motor, health, property) pinpoint product-level profitability. !- Data requirements: Extracts from the claims-management system showing paid amounts, dates, line of business, and reinsurance cessions. Premium registers (written or earned, depending on supervisory preference) reconciled to the general ledger. Catastrophe tags, legal-settlement flags, and large-loss registers to isolate one-off distortions. Limitations &amp; considerations: Timing mismatch: annual premiums are often received up-front, whereas claim payments can lag; using earned premiums mitigates, but does not eliminate, this distortion. Claims-handling practices: delayed settlement or dispute escalation depresses the ratio without improving true risk experience. Reinsurance structure: quota-share vs. excess-of-loss treaties change the net ratio dramatically; analysts should review both gross and net perspectives. Regulatory definitions: some jurisdictions fold surrenders of savings-type contracts into claims, inflating comparability. Trend analysis should therefore pair the claims paid ratio with claims-incurred and reserve-adequacy metrics, catastrophe-loss disclosures, and expense dynamics to obtain a holistic view of underwriting performance and solvency resilience.</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>How has the participation of different genders in incurred insurance claims evolved over time, both for individuals and MSMEs by owner’s gender? Are there gender differences in the types of claims incurred? How does the level of gender diversity within FSPs relate to these patterns?</t>
+          <t>Are there gender disparities in claims ratios for insurance products, including for MSMEs based on the owner's gender? Are excessively low claims ratios correlated with low premiums (a proxy for targeting lower-income segments)? Are women more likely to be targeted by products with low claims ratios, potentially indicating lower-value offerings? Are FSPs with higher levels of gender diversity less likely to have excessively low claims ratios for insurance sold to vulnerable segments, such as women and women-owned MSMEs? When comparing with coverage ratios (amount of claims paid relative to the claim value), how do gender disparities in coverage ratios compare with claims paid?</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -10277,7 +10282,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Quality, Suitability</t>
+          <t>Usage, Suitability</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -10303,82 +10308,92 @@
         </is>
       </c>
       <c r="D184">
+        <v>8</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Insurance claims incurred</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Value of insurance claims incurred</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>“Claims incurred” represents the total cost an insurer recognises for claims events during a reporting period, regardless of whether they have been paid yet. Tracking the level and trend of incurred claims helps supervisors monitor the financial health of insurers such as by detecting emerging risk clusters (e.g., climate-driven catastrophes). !- Definitions and concepts: Claims incurred = Claims paid + Change in outstanding claims reserves + Change in IBNR (incurred-but-not-reported) reserves ± Claims-handling expense reserve movements. !- Data requirements: Total claims incurred.  !- Limitations and considerations: Catastrophe volatility: Single severe events cause spikes. Used alongside premium growth, claims-ratio components, and reserve-adequacy studies, “claims incurred” provides a cornerstone view of underwriting performance and balance-sheet resilience.</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>How has the participation of different genders in incurred insurance claims evolved over time, both for individuals and MSMEs by owner’s gender? Are there gender differences in the types of claims incurred? How does the level of gender diversity within FSPs relate to these patterns?</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Financial inclusion; Consumer protection</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Quality, Suitability</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Soundness</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D185">
         <v>57</v>
       </c>
-      <c r="E184" t="inlineStr">
+      <c r="E185" t="inlineStr">
         <is>
           <t>Insurance policy renewal (persistency) ratio</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>% of all policies up for renewal that are renewed</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
+      <c r="G185" t="inlineStr">
         <is>
           <t>The renewal- or persistency-ratio gauges the proportion of in-force insurance policies (or premium) that remain active after a specified period—typically the 13th, 25th, or 61st month following issuance. High persistency signals strong customer satisfaction, effective servicing, and accurate underwriting assumptions; it underpins stable cash-flow projections, lowers acquisition-cost amortisation strain, and enhances embedded value. Conversely, rapid lapses may expose product-design weaknesses or mis-selling. Supervisors review persistency alongside surrender-value payouts and complaint levels to detect conduct risk and solvency concerns. !- Definitions and concepts: Persistency ratio (policy-count basis) = Policies renewed at month t / Policies eligible for renewal at month t
 Premium-weighted persistency uses renewal premium divided by original premium to capture face-amount shifts. Cohort vs. calendar method: Cohort traces a single issue-year block through time; calendar aggregates all cohorts renewing in a given period. !- Limitations and considerations: Measurement horizon: 13-month persistency suits annual-premium life products; short-tailed general-insurance policies need annual or shorter retention ratios. Channel mix: Bancassurance and digital pathways often show different lapse behaviours—segment analysis is essential.</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
+      <c r="H185" t="inlineStr">
         <is>
           <t>Are there gender disparities in insurance policy renewal rates, including among MSMEs by owner gender? Do certain policy types have lower renewal rates among specific gender groups? Could these differences signal mismatches between products and customer needs, posing strategic risks for insurers?</t>
         </is>
       </c>
-      <c r="J184" t="inlineStr">
+      <c r="J185" t="inlineStr">
         <is>
           <t>Financial inclusion; Consumer protection</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
+      <c r="K185" t="inlineStr">
         <is>
           <t>Quality, Suitability</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Stability, safety and soundness</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Soundness</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D185">
-        <v>114</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Risk retention ratio (dependency on reinsurance)</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>% of gross written premium that is net (as a measure of the level of dependency on reinsurance)</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>Also known as the net retention ratio, this indicator shows the proportion of insurance risk an insurer keeps on its own balance sheet after ceding portions to reinsurers. It is usually expressed as Net premiums written ÷ Gross premiums written. A high ratio signals greater self-reliance (and potentially higher earnings volatility), while a low ratio points to heavy dependence on reinsurance, which may reduce earnings swings but create counter-party risks. Supervisors monitor the metric to ensure that ceded volumes are commensurate with the insurer’s capital strength, product mix, and risk appetite. !- Definitions and concepts: Gross premiums written (GPW): Total premium income before reinsurance ceded. Net premiums written (NPW): GPW minus premiums ceded plus reinsurance recoveries on ceded unearned premiums. !- Data requirements: Line-of-business breakdown of GPW and NPW for the period. Details of outward reinsurance treaties. Counter-party concentration: high concentration risk may offset the benefits of resinsurance.</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>What is the relationship between FSP gender diversity, customer gender composition, and the degree of dependency on reinsurance? Are there gender-based patterns in insurers’ risk retention strategies?</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -10404,31 +10419,31 @@
         </is>
       </c>
       <c r="D186">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Technical provisions</t>
+          <t>Risk retention ratio (dependency on reinsurance)</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Level of technical provisions to cover actuarial liabilities</t>
+          <t>% of gross written premium that is net (as a measure of the level of dependency on reinsurance)</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Technical provisions represent the present-value estimate of all future cash outflows that an insurer expects to incur on written policies, including claims not yet reported (IBNR), claims reported but not settled, and future policyholder benefits. Adequate provisions are the cornerstone of insurance solvency and a key indicator for prudential supervisors. Definitions &amp; concepts: Technical provisions comprise two main blocks: Best-Estimate Liabilities (BEL), the probability-weighted expected value of future cash flows (claims, benefits, expenses) discounted using risk-free or prescribed curves; and Risk Margins, an additional amount reflecting the cost of holding capital to run off the liabilities (Solvency II) or a prudential margin (IFRS 17, LAT).</t>
+          <t>Also known as the net retention ratio, this indicator shows the proportion of insurance risk an insurer keeps on its own balance sheet after ceding portions to reinsurers. It is usually expressed as Net premiums written ÷ Gross premiums written. A high ratio signals greater self-reliance (and potentially higher earnings volatility), while a low ratio points to heavy dependence on reinsurance, which may reduce earnings swings but create counter-party risks. Supervisors monitor the metric to ensure that ceded volumes are commensurate with the insurer’s capital strength, product mix, and risk appetite. !- Definitions and concepts: Gross premiums written (GPW): Total premium income before reinsurance ceded. Net premiums written (NPW): GPW minus premiums ceded plus reinsurance recoveries on ceded unearned premiums. !- Data requirements: Line-of-business breakdown of GPW and NPW for the period. Details of outward reinsurance treaties. Counter-party concentration: high concentration risk may offset the benefits of resinsurance.</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the adequacy of technical provisions maintained by FSPs? How do FSPs with higher gender diversity in management and governance compare in maintaining technical provisions that fairly reflect risks associated with serving diverse gender groups? Are provisions sufficiently accounting for potential differences in claims or defaults related to gender segments in the portfolio?</t>
+          <t>What is the relationship between FSP gender diversity, customer gender composition, and the degree of dependency on reinsurance? Are there gender-based patterns in insurers’ risk retention strategies?</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -10449,31 +10464,31 @@
         </is>
       </c>
       <c r="D187">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Physical risk in the insurance portfolio</t>
+          <t>Technical provisions</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Exposure of the insurance portfolio to written policies to physical risk related to climate change</t>
+          <t>Level of technical provisions to cover actuarial liabilities</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Metric used to quantify an insurer's financial exposure to losses caused by the direct physical impacts of climate change. This includes both event-driven acute risks and longer-term chronic risks. This indicator is essential for measuring an insurer's vulnerability to climate-related claims, which can impact its profitability, solvency, and ability to provide affordable coverage. Hence, it is an important metric for prudential supervisors from the perspective of capital adequacy, solvency and risk management. Definitions and concepts of climate-related risks vary across countries. The NGFS provides a range of additional defintions, including nature-related financial risks.</t>
+          <t>Technical provisions represent the present-value estimate of all future cash outflows that an insurer expects to incur on written policies, including claims not yet reported (IBNR), claims reported but not settled, and future policyholder benefits. Adequate provisions are the cornerstone of insurance solvency and a key indicator for prudential supervisors. Definitions &amp; concepts: Technical provisions comprise two main blocks: Best-Estimate Liabilities (BEL), the probability-weighted expected value of future cash flows (claims, benefits, expenses) discounted using risk-free or prescribed curves; and Risk Margins, an additional amount reflecting the cost of holding capital to run off the liabilities (Solvency II) or a prudential margin (IFRS 17, LAT).</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>How do FSP gender diversity and customer gender composition correlate with exposure to climate-related physical risks in insurance portfolios? Are there gender disparities in financial risk exposure due to climate impacts, including among MSMEs by owner gender?</t>
+          <t>Are there gender disparities in the adequacy of technical provisions maintained by FSPs? How do FSPs with higher gender diversity in management and governance compare in maintaining technical provisions that fairly reflect risks associated with serving diverse gender groups? Are provisions sufficiently accounting for potential differences in claims or defaults related to gender segments in the portfolio?</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -10490,35 +10505,35 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Investments</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D188">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Capital adequacy ratio (CAR)</t>
+          <t>Physical risk in the insurance portfolio</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Total regulatory capital relative as % of risk weighted assets (RWAs)</t>
+          <t>Exposure of the insurance portfolio to written policies to physical risk related to climate change</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Capital Adequacy Rario (CAR) shows the total qualifying capital relative to risk-weighted assets (RWA). It captures the full loss-absorbing cushion. !-Definitions and concepts: Capital tiers to include in the CAR formula are provided by the Basel Capital Accords and adapted in each jurisdiction. !- Data requirements: Full breakdown of regulatory capital components, and total RWA. For the insurance sector, the equivalent is the Solvency Ratio calculated as own funds divided by the minimum capital that insurers are required to hold to cover unexpected losses.</t>
+          <t>Metric used to quantify an insurer's financial exposure to losses caused by the direct physical impacts of climate change. This includes both event-driven acute risks and longer-term chronic risks. This indicator is essential for measuring an insurer's vulnerability to climate-related claims, which can impact its profitability, solvency, and ability to provide affordable coverage. Hence, it is an important metric for prudential supervisors from the perspective of capital adequacy, solvency and risk management. Definitions and concepts of climate-related risks vary across countries. The NGFS provides a range of additional defintions, including nature-related financial risks.</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>How are FSP gender diversity and the gender composition of the customer base correlated with CAR levels?</t>
+          <t>How do FSP gender diversity and customer gender composition correlate with exposure to climate-related physical risks in insurance portfolios? Are there gender disparities in financial risk exposure due to climate impacts, including among MSMEs by owner gender?</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -10535,35 +10550,35 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Payments, Savings, Credit, Insurance, Investments</t>
         </is>
       </c>
       <c r="D189">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Tier 1 capital ratio</t>
+          <t>Capital adequacy ratio (CAR)</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tier 1 regulatory capital as % of risk weighted assets (RWAs)</t>
+          <t>Total regulatory capital relative as % of risk weighted assets (RWAs)</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>The Tier 1 ratio shows the core loss-absorbing capital relative to risk-weighted assets (RWA). It is a cornerstone of the Basel Capital Accords and a trigger point for supervisory intervention. !- Definitions and concepts: Tier 1 capital comprises common equity tier 1 (CET1) plus additional tier 1 (perpetual, non-cumulative instruments). RWA adjust asset values for credit, market, and operational risk weights. Local definitions vary, but the Basel Committee has provided common standards.</t>
+          <t>Capital Adequacy Rario (CAR) shows the total qualifying capital relative to risk-weighted assets (RWA). It captures the full loss-absorbing cushion. !-Definitions and concepts: Capital tiers to include in the CAR formula are provided by the Basel Capital Accords and adapted in each jurisdiction. !- Data requirements: Full breakdown of regulatory capital components, and total RWA. For the insurance sector, the equivalent is the Solvency Ratio calculated as own funds divided by the minimum capital that insurers are required to hold to cover unexpected losses.</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Do FSPs with greater gender diversity in leadership and customer base tend to maintain stronger Tier 1 capital ratios? Is there any evidence that gender-inclusive governance correlates with improved capital adequacy and financial resilience? How might gender-related risk factors influence the calculation or management of Tier 1 capital?</t>
+          <t>How are FSP gender diversity and the gender composition of the customer base correlated with CAR levels?</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) gender diversity</t>
         </is>
       </c>
     </row>
@@ -10580,35 +10595,35 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D190">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Interest margin ratio</t>
+          <t>Tier 1 capital ratio</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Net interest income as % of total earning assets</t>
+          <t>Tier 1 regulatory capital as % of risk weighted assets (RWAs)</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Also known as Net Interest Margin (NIM), is a metric that measures a lender's profitability by calculating difference between the interest it earns on its assets (like loans) and the interest it pays on liabilities, divided by the total earning assets. !- Definitions and concepts: NIM = (Net Interest income – Interest expense) ÷ Average earning assets. !- Data requirements: Total interest income, total interest expenses, total earning assets.</t>
+          <t>The Tier 1 ratio shows the core loss-absorbing capital relative to risk-weighted assets (RWA). It is a cornerstone of the Basel Capital Accords and a trigger point for supervisory intervention. !- Definitions and concepts: Tier 1 capital comprises common equity tier 1 (CET1) plus additional tier 1 (perpetual, non-cumulative instruments). RWA adjust asset values for credit, market, and operational risk weights. Local definitions vary, but the Basel Committee has provided common standards.</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Do financial service providers (FSPs) with higher gender diversity in leadership or governance report different interest margin ratios compared to less gender‑diverse peers? Are there associations between the gender composition of the customer base (e.g. share of women borrowers/depositors) and margin outcomes? Could gendered pricing—such as differential rates offered to male vs. female clients—impact FSP interest margins? Over time, do changes in margin ratios correlate with shifts in gender inclusion (e.g. more women customers or staff)?</t>
+          <t>Do FSPs with greater gender diversity in leadership and customer base tend to maintain stronger Tier 1 capital ratios? Is there any evidence that gender-inclusive governance correlates with improved capital adequacy and financial resilience? How might gender-related risk factors influence the calculation or management of Tier 1 capital?</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -10625,45 +10640,35 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D191">
-        <v>7</v>
+        <v>113</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Insurance premiums written</t>
+          <t>Interest margin ratio</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Value of insurance premiums writen in the insurance sector</t>
+          <t>Net interest income as % of total earning assets</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Premiums written represent the contractual revenue an insurer books when it underwrites new or renewal policies during a given period, irrespective of when coverage is provided or cash is received. Rising written-premium volumes can indicate growth, improved pricing power, or inflation-driven sum-assured increases; declining volumes may flag competitive pressures or tighter underwriting standards. !- Definitions and concepts: Gross premiums written (GPW): All premiums on policies incepted or renewed during the period before ceding to reinsurers. Net premiums written (NPW): GPW minus premiums ceded plus any reinsurance assumed—reflects the risk the insurer retains. Earned premiums: Portion of written premiums recognised as revenue in proportion to expired coverage—crucial for claims-ratio analysis. !- Data requirements: total premium written. For granular data: Policy-level underwriting feeds: issue/renewal dates, premium amounts, payment mode, product line, distribution channel, currency.</t>
+          <t>Also known as Net Interest Margin (NIM), is a metric that measures a lender's profitability by calculating difference between the interest it earns on its assets (like loans) and the interest it pays on liabilities, divided by the total earning assets. !- Definitions and concepts: NIM = (Net Interest income – Interest expense) ÷ Average earning assets. !- Data requirements: Total interest income, total interest expenses, total earning assets.</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>How do insurance premiums written vary by gender of the policyholder, including for individuals and MSMEs based on owner gender? Are there gender disparities in the types and values of insurance products purchased, reflected in premiums collected? Do women or other gender groups pay systematically higher or lower premiums, and what might this indicate about risk assessment or product suitability? How do FSPs with higher gender diversity compare in the total premiums written to different gender segments? Are trends in premiums written by gender evolving over time, and do these trends vary by product type or geographic region?</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>Outcomes</t>
+          <t>Do financial service providers (FSPs) with higher gender diversity in leadership or governance report different interest margin ratios compared to less gender‑diverse peers? Are there associations between the gender composition of the customer base (e.g. share of women borrowers/depositors) and margin outcomes? Could gendered pricing—such as differential rates offered to male vs. female clients—impact FSP interest margins? Over time, do changes in margin ratios correlate with shifts in gender inclusion (e.g. more women customers or staff)?</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -10680,35 +10685,45 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D192">
-        <v>112</v>
+        <v>7</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Efficiency ratio</t>
+          <t>Insurance premiums written</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Effciency ratio</t>
+          <t>Value of insurance premiums writen in the insurance sector</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Indicates operating efficiency by comparing non-interest expenses to operating income. Lower ratios signal better cost control, a key driver of sustainable profitability, especially in low-margin environments. Definitions &amp; concepts – Efficiency Ratio = Operating expenses ÷ (Net interest income + Non-interest income). Some variants exclude litigation or restructuring charges. !- Data requirements: Detailed income statement with breakdowns of personnel, IT, and occupancy costs; segment reporting helps pinpoint inefficiencies. !- Limitations and considerations: Cost cuts that impair risk management or customer service may improve the ratio temporarily but raise long-run risks. Cross-country comparisons should adjust for labour cost levels and digitalisation stages. One-off income (e.g., asset sales) can distort the denominator.</t>
+          <t>Premiums written represent the contractual revenue an insurer books when it underwrites new or renewal policies during a given period, irrespective of when coverage is provided or cash is received. Rising written-premium volumes can indicate growth, improved pricing power, or inflation-driven sum-assured increases; declining volumes may flag competitive pressures or tighter underwriting standards. !- Definitions and concepts: Gross premiums written (GPW): All premiums on policies incepted or renewed during the period before ceding to reinsurers. Net premiums written (NPW): GPW minus premiums ceded plus any reinsurance assumed—reflects the risk the insurer retains. Earned premiums: Portion of written premiums recognised as revenue in proportion to expired coverage—crucial for claims-ratio analysis. !- Data requirements: total premium written. For granular data: Policy-level underwriting feeds: issue/renewal dates, premium amounts, payment mode, product line, distribution channel, currency.</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Are there gender-related differences in the efficiency of FSP operations, for example, in cost-to-income ratios? Do FSPs with more gender-diverse teams or client bases demonstrate better operational efficiency? How do gender dynamics in product design, customer service, and outreach impact overall institutional efficiency?</t>
+          <t>How do insurance premiums written vary by gender of the policyholder, including for individuals and MSMEs based on owner gender? Are there gender disparities in the types and values of insurance products purchased, reflected in premiums collected? Do women or other gender groups pay systematically higher or lower premiums, and what might this indicate about risk assessment or product suitability? How do FSPs with higher gender diversity compare in the total premiums written to different gender segments? Are trends in premiums written by gender evolving over time, and do these trends vary by product type or geographic region?</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Outcomes</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -10729,31 +10744,31 @@
         </is>
       </c>
       <c r="D193">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Personnel expenses per customer/contract</t>
+          <t>Efficiency ratio</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Total personnel expenses per customer or contract</t>
+          <t>Effciency ratio</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>This indicator measures the total cost of personnel (wages, salaries, benefits, etc.) divided by the total number of customers a financial service provider serves, revealing how much is spent on staff to support each individual customer. This metric helps assess a company's operational efficiency and cost-effectiveness in managing its customer base, with a lower figure typically indicating better efficiency.</t>
+          <t>Indicates operating efficiency by comparing non-interest expenses to operating income. Lower ratios signal better cost control, a key driver of sustainable profitability, especially in low-margin environments. Definitions &amp; concepts – Efficiency Ratio = Operating expenses ÷ (Net interest income + Non-interest income). Some variants exclude litigation or restructuring charges. !- Data requirements: Detailed income statement with breakdowns of personnel, IT, and occupancy costs; segment reporting helps pinpoint inefficiencies. !- Limitations and considerations: Cost cuts that impair risk management or customer service may improve the ratio temporarily but raise long-run risks. Cross-country comparisons should adjust for labour cost levels and digitalisation stages. One-off income (e.g., asset sales) can distort the denominator.</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Is there a gender dimension in personnel cost efficiency—that is, do FSPs with more balanced or female‑inclusive staff structures show lower personnel expenses per customer or contract? Are personnel expense ratios correlated with the gender composition of staff and how services are delivered to different gender groups? Do FSPs serving a higher proportion of women customers incur different per-customer personnel costs (e.g. due to agent outreach, financial literacy support)? How does this metric evolve over time in relation to efforts to promote gender inclusion in staffing and service models?</t>
+          <t>Are there gender-related differences in the efficiency of FSP operations, for example, in cost-to-income ratios? Do FSPs with more gender-diverse teams or client bases demonstrate better operational efficiency? How do gender dynamics in product design, customer service, and outreach impact overall institutional efficiency?</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Financial service provider (FSP) gender diversity; Financial service provider (FSP) type</t>
         </is>
       </c>
     </row>
@@ -10774,31 +10789,31 @@
         </is>
       </c>
       <c r="D194">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>ROA</t>
+          <t>Personnel expenses per customer/contract</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Return on assets</t>
+          <t>Total personnel expenses per customer or contract</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>ROA gauges how efficiently a financial service provider turns every unit of assets under its control into net profit. !- Definitions and concepts: ROA = Net income after tax ÷ Average total assets (opening + closing assets ÷ 2). !- Data requirements: net income and total assets at two balance-sheet dates, preferably quarterly to smooth seasonality. !- Limitations and considerations: ROA ignores off-balance-sheet exposures such as guarantees or derivatives.</t>
+          <t>This indicator measures the total cost of personnel (wages, salaries, benefits, etc.) divided by the total number of customers a financial service provider serves, revealing how much is spent on staff to support each individual customer. This metric helps assess a company's operational efficiency and cost-effectiveness in managing its customer base, with a lower figure typically indicating better efficiency.</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Do FSPs with greater gender diversity in their workforce, management, or boards tend to achieve higher or more stable ROA? Is there evidence that the gender composition of the customer base (e.g. more female clients) affects asset returns, for instance through differences in risk, lending, or deposit behaviors? When comparing across FSPs, does ROA differ systematically in institutions with stronger gender inclusion strategies? How have ROA trends shifted over time relative to changes in gender diversity (staffing or customer composition)?</t>
+          <t>Is there a gender dimension in personnel cost efficiency—that is, do FSPs with more balanced or female‑inclusive staff structures show lower personnel expenses per customer or contract? Are personnel expense ratios correlated with the gender composition of staff and how services are delivered to different gender groups? Do FSPs serving a higher proportion of women customers incur different per-customer personnel costs (e.g. due to agent outreach, financial literacy support)? How does this metric evolve over time in relation to efforts to promote gender inclusion in staffing and service models?</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -10810,7 +10825,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Soundness, Credit risk</t>
+          <t>Soundness</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -10819,26 +10834,26 @@
         </is>
       </c>
       <c r="D195">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>ROE</t>
+          <t>ROA</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Return on equity</t>
+          <t>Return on assets</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>ROE indicates the earnings available to common shareholders per unit of book equity. !- Definitions and concepts: ROE = Net income ÷ Average shareholders’ equity. !- Data requirements: Consolidated net income and shareholders’ equity.</t>
+          <t>ROA gauges how efficiently a financial service provider turns every unit of assets under its control into net profit. !- Definitions and concepts: ROA = Net income after tax ÷ Average total assets (opening + closing assets ÷ 2). !- Data requirements: net income and total assets at two balance-sheet dates, preferably quarterly to smooth seasonality. !- Limitations and considerations: ROA ignores off-balance-sheet exposures such as guarantees or derivatives.</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Is there a relationship between gender diversity in leadership or equity ownership and ROE performance across FSPs? Are FSPs that prioritize gender inclusion more likely to achieve higher equity returns, possibly through broader market reach or more balanced risk management? How does the gender mix of customers, especially depositors and borrowers, relate to ROE outcomes? Over time, do improvements in gender inclusion (in staffing or customer base) precede or follow changes in ROE?</t>
+          <t>Do FSPs with greater gender diversity in their workforce, management, or boards tend to achieve higher or more stable ROA? Is there evidence that the gender composition of the customer base (e.g. more female clients) affects asset returns, for instance through differences in risk, lending, or deposit behaviors? When comparing across FSPs, does ROA differ systematically in institutions with stronger gender inclusion strategies? How have ROA trends shifted over time relative to changes in gender diversity (staffing or customer composition)?</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -10855,50 +10870,40 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Credit risk</t>
+          <t>Soundness, Credit risk</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Payments, Savings, Credit, Insurance, Pensions, Investments</t>
         </is>
       </c>
       <c r="D196">
-        <v>6</v>
+        <v>116</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Financial system credit operations</t>
+          <t>ROE</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Volume and value of credit operations in the total financial sector portfolio</t>
+          <t>Return on equity</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>This indicator captures the breadth of formal lending with two perspectives: the number of credit contracts (volume) and their aggregate outstanding balance (value) across all regulated lenders. Tracking it offers a panoramic view of credit provision, enabling supervisors to (i) gauge financial deepening, (ii) assess systemic leverage of the banking sector, (iii) monitor shifts in portfolio composition (e.g., rise of consumer or MSME lending), and (iv) feed macro-prudential stress tests and monetary policy models. Sharp expansions may indicate rapid financial inclusion or overheating; contractions can herald credit crunches that dampen growth. !- Definitions and concepts: Credit operation – any legally binding loan, line of credit, hire-purchase, lease, or other. Off-balance-sheet commitments (e.g., undrawn credit lines, guarantees) are usually excluded or reported separately. Volume (count): unique credit contracts outstanding at the reporting date; renewals/extensions count as new operations if a fresh contract is signed. Segmentation by sector (household, corporate, government), product type, currency, and residual maturity enriches analysis. !- Data requirements: Supervisory returns or call-reports detailing credit operations contract count by institution and product. Standardised product and sector taxononies to avoid double counting.</t>
+          <t>ROE indicates the earnings available to common shareholders per unit of book equity. !- Definitions and concepts: ROE = Net income ÷ Average shareholders’ equity. !- Data requirements: Consolidated net income and shareholders’ equity.</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>How does the gender composition of borrowers in the total financial sector credit portfolio compare across the number and value of outstanding credit operations? Are there gender disparities in both the frequency (number) of credit operations and the total credit amounts extended? How do these disparities vary by loan type, sector, or borrower demographics such as age, income, and location? Are women or other gender groups underrepresented in certain types of credit or regions within the overall portfolio? How do FSPs with higher levels of gender diversity compare in terms of the balance and number of credit operations granted to different genders? Are portfolios with more balanced gender representation associated with differences in credit performance, such as lower default rates or more stable repayment patterns?</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>Usage</t>
+          <t>Is there a relationship between gender diversity in leadership or equity ownership and ROE performance across FSPs? Are FSPs that prioritize gender inclusion more likely to achieve higher equity returns, possibly through broader market reach or more balanced risk management? How does the gender mix of customers, especially depositors and borrowers, relate to ROE outcomes? Over time, do improvements in gender inclusion (in staffing or customer base) precede or follow changes in ROE?</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
@@ -10910,74 +10915,129 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
+          <t>Credit risk</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="D197">
+        <v>6</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Financial system credit operations</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Volume and value of credit operations in the total financial sector portfolio</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>This indicator captures the breadth of formal lending with two perspectives: the number of credit contracts (volume) and their aggregate outstanding balance (value) across all regulated lenders. Tracking it offers a panoramic view of credit provision, enabling supervisors to (i) gauge financial deepening, (ii) assess systemic leverage of the banking sector, (iii) monitor shifts in portfolio composition (e.g., rise of consumer or MSME lending), and (iv) feed macro-prudential stress tests and monetary policy models. Sharp expansions may indicate rapid financial inclusion or overheating; contractions can herald credit crunches that dampen growth. !- Definitions and concepts: Credit operation – any legally binding loan, line of credit, hire-purchase, lease, or other. Off-balance-sheet commitments (e.g., undrawn credit lines, guarantees) are usually excluded or reported separately. Volume (count): unique credit contracts outstanding at the reporting date; renewals/extensions count as new operations if a fresh contract is signed. Segmentation by sector (household, corporate, government), product type, currency, and residual maturity enriches analysis. !- Data requirements: Supervisory returns or call-reports detailing credit operations contract count by institution and product. Standardised product and sector taxononies to avoid double counting.</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>How does the gender composition of borrowers in the total financial sector credit portfolio compare across the number and value of outstanding credit operations? Are there gender disparities in both the frequency (number) of credit operations and the total credit amounts extended? How do these disparities vary by loan type, sector, or borrower demographics such as age, income, and location? Are women or other gender groups underrepresented in certain types of credit or regions within the overall portfolio? How do FSPs with higher levels of gender diversity compare in terms of the balance and number of credit operations granted to different genders? Are portfolios with more balanced gender representation associated with differences in credit performance, such as lower default rates or more stable repayment patterns?</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Financial inclusion</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Stability, safety and soundness</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
           <t>Liquidity risk</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
+      <c r="C198" t="inlineStr">
         <is>
           <t>Savings</t>
         </is>
       </c>
-      <c r="D197">
+      <c r="D198">
         <v>17</v>
       </c>
-      <c r="E197" t="inlineStr">
+      <c r="E198" t="inlineStr">
         <is>
           <t>Deposit stability/volatility</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
+      <c r="F198" t="inlineStr">
         <is>
           <t>Stability/volatility of retail deposits (deposit stickness, deposit stability, deposit flows)</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
+      <c r="G198" t="inlineStr">
         <is>
           <t>The deposit stability (or deposit-volatility) indicator assesses how predictable an FSP's funding base is by tracking the fluctuation and “stickiness” of customer deposits over time. Sudden, correlated outflows—whether triggered by market rumours, rate competition or digital bank runs—can force a bank to liquidate assets at fire-sale prices or draw on emergency facilities. Prudential supervisors monitor deposit volatility alongside liquidity ratios to judge an institution’s ability to withstand funding shocks and to calibrate run-off assumptions in stress tests and the Liquidity Coverage Ratio (LCR). Definitions &amp; concepts: Core / stable deposits: retail balances judged unlikely to flee under stress; often defined by balance size, relationship depth, and whether the account is transactional rather than rate-sensitive. Volatility metrics: standard deviation of daily balances divided by the mean (coefficient of variation), maximum one-day net outflow over a look-back window, or elasticity (beta) to market rates. Calculation methods vary across countries. !- Data requirements: High-frequency (daily or intraday) deposit-balance time series, tagged by customer type, product, and currency. Interest-rate history to estimate betas. Customer identifiers for relationship tenure, cross-selling, and concentration analysis. 
 Digital channel dynamics: mobile app withdrawals can accelerate run speed beyond historical norms; backward-looking volatility measures may understate future risk.</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
+      <c r="H198" t="inlineStr">
         <is>
           <t>Are there gender disparities in deposit stability or volatility, and do accounts held by different gender groups show distinct patterns in the frequency or magnitude of balance fluctuations? Could these differences reflect varying income regularity, saving habits, or financial resilience? How do these patterns vary across age, income level, or geographic location? Are there notable differences in deposit stability between FSPs with higher or lower levels of gender diversity in their customer base? Do FSPs with greater gender diversity among their clients tend to experience greater deposit stickiness overall?</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
+      <c r="L198" t="inlineStr">
         <is>
           <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity; Insurance type</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
+    <row r="199">
+      <c r="A199" t="inlineStr">
         <is>
           <t>Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="B199" t="inlineStr">
         <is>
           <t>Soundness</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
+      <c r="C199" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D198">
+      <c r="D199">
         <v>392</v>
       </c>
-      <c r="E198" t="inlineStr">
+      <c r="E199" t="inlineStr">
         <is>
           <t>Combined ratio</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>% of total premium income used in paying expenses and claims</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
+      <c r="G199" t="inlineStr">
         <is>
           <t>The combined ratio is a key measure of underwriting profitability in the insurance industry. It indicates the proportion of each unit of premium earned that an insurer uses to cover claims-related losses and operating expenses. A combined ratio below 100% signals an underwriting profit, meaning the insurer is collecting more in premiums than it pays out in claims and expenses, while a ratio above 100% indicates an underwriting loss. This indicator is widely used by insurance supervisors as an early warning signal for assessing the financial health and operational efficiency of insurers, and it supports prudential oversight by helping to identify companies that may be underpricing risk or operating with excessive costs. Monitoring this indicator over time and across different types of insurers can reveal structural patterns in the sustainability of insurance business models and inform supervisory responses.
 !-Definitions and concepts: The combined ratio is calculated as the sum of two components: the loss ratio and the expense ratio. The loss ratio measures claims-related costs (incurred losses plus loss adjustment expenses) as a proportion of earned premiums. The expense ratio measures underwriting and administrative expenses (such as commissions, salaries, and other operational costs) as a proportion of earned or written premiums. The general formula is: Combined Ratio = Loss Ratio + Expense Ratio, or equivalently, Combined Ratio = (Incurred Losses + Loss Adjustment Expenses + Underwriting Expenses) / Earned Premiums. Earned premiums refer to the portion of written premiums corresponding to the coverage period that has elapsed, ensuring proper matching between income recognized and associated claims obligations. A combined ratio of exactly 100% represents the break-even point for underwriting operations.
@@ -10986,36 +11046,36 @@
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
+    <row r="200">
+      <c r="A200" t="inlineStr">
         <is>
           <t>Stability, safety and soundness</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B200" t="inlineStr">
         <is>
           <t>Soundness</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
+      <c r="C200" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D199">
+      <c r="D200">
         <v>394</v>
       </c>
-      <c r="E199" t="inlineStr">
+      <c r="E200" t="inlineStr">
         <is>
           <t>Expense ratio</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
+      <c r="F200" t="inlineStr">
         <is>
           <t>% of earned premiums that an insurance company spends on underwriting and administrative expenses (excluding claims)</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
+      <c r="G200" t="inlineStr">
         <is>
           <t>The expense ratio measures the proportion of earned premiums that an insurance company spends on underwriting and administrative expenses, excluding claims-related costs. It is a key indicator of operational efficiency, reflecting how effectively an insurer manages the costs associated with acquiring, underwriting, and servicing insurance policies. Financial sector authorities use this indicator to assess whether insurers are operating within sustainable cost structures and to identify potential inefficiencies that could affect policyholder value or long-term solvency. Together with the loss ratio, the expense ratio is one of the two components of the combined ratio, providing a complementary view that isolates operational cost management from claims experience. Monitoring the expense ratio across providers and over time can help supervisors detect trends in market competitiveness, evaluate the impact of new distribution models (such as digital or agent-based channels) on cost structures, and assess whether high acquisition or administrative costs may be eroding the value delivered to policyholders.
 !-Definitions and concepts: The expense ratio is calculated by dividing total underwriting and administrative expenses by premiums for a given reporting period. The formula is: Expense Ratio (%) = (Underwriting and Administrative Expenses / Premiums) × 100. Underwriting and administrative expenses typically include acquisition costs (such as agent and broker commissions, marketing expenses, and premium taxes), as well as operational costs associated with policy administration, underwriting staff salaries, technology, licensing fees, and general overhead. These expenses exclude claims payments and loss adjustment expenses, which are captured separately in the loss ratio. An important distinction exists in the choice of denominator: under statutory accounting conventions, the expense ratio often uses written premiums, since acquisition costs are recognized at the time a policy is written rather than spread over its duration. Under other accounting frameworks, earned premiums may be used. This difference can affect comparability across jurisdictions and should be noted when interpreting the ratio.
@@ -11024,66 +11084,6 @@
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Sustainability</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Climate and environmental objectives</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D200">
-        <v>330</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>Rural credit (volume)</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>Number of loans in the retail loan portfolio designated as rural credit</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector, such as the volume of loans disbursed as a % of the total loan portfolio. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis.</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Are there gender disparities in participation in the rural credit portfolio, when measured by number of loans and disaggregated by loan type and type of borrower (individual or MSME)? Are these disparities more pronounced in certain types of financial service providers or geographic regions? Do FSPs with higher levels of gender diversity tend to allocate a greater share of loan volume to rural women or women-led MSMEs? Does the proportion of rural credit within the total number of loans granted to women differ significantly from that of men, and what does this reveal about access to credit by gender and location?</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>Financial inclusion</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>Usage</t>
-        </is>
-      </c>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
-        </is>
-      </c>
-    </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
@@ -11101,41 +11101,46 @@
         </is>
       </c>
       <c r="D201">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Climate and other environmental risk in the credit portfolio</t>
+          <t>Rural credit (volume)</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Exposure of the credit portfolio to customers or industries with high climate (physical and transition risks) and other environmental risk</t>
+          <t>Number of loans in the retail loan portfolio designated as rural credit</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>This indicator quantifies how much of the loan book is exposed to climate-related risks (physical and transition) and broader environmental risks (e.g., water stress, biodiversity loss, pollution). It helps firms and supervisors judge vulnerability to asset impairment, collateral devaluation, cash-flow shocks, and regulatory change. It also informs pricing, sector limits, and strategic portfolio alignment. Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, while the NGFS provides a range of additional defintions, including nature-related financial risks.</t>
+          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector, such as the volume of loans disbursed as a % of the total loan portfolio. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis.</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>How is FSP gender diversity and the gender composition of the customer base correlated with climate-related financial risks (physical and transition) and other environmental risks?</t>
+          <t>Are there gender disparities in participation in the rural credit portfolio, when measured by number of loans and disaggregated by loan type and type of borrower (individual or MSME)? Are these disparities more pronounced in certain types of financial service providers or geographic regions? Do FSPs with higher levels of gender diversity tend to allocate a greater share of loan volume to rural women or women-led MSMEs? Does the proportion of rural credit within the total number of loans granted to women differ significantly from that of men, and what does this reveal about access to credit by gender and location?</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Stability, safety and soundness</t>
+          <t>Financial inclusion</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Credit risk, Stability</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -11156,26 +11161,26 @@
         </is>
       </c>
       <c r="D202">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Exposure to polluting firms/industries</t>
+          <t>Climate and other environmental risk in the credit portfolio</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Number of loans and total exposure of the credit portfolio to pollutting firms/industries</t>
+          <t>Exposure of the credit portfolio to customers or industries with high climate (physical and transition risks) and other environmental risk</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>This indicator quantifies how much of the loan book is exposed to borrowers classified as big polluters (e.g., fossil fuel industry). The definition of polluting borrowers or activity varies widely across countries and the indicator should be aligned with national definitions. The EU uses a range of similar indicators: https://www.ecb.europa.eu/stats/all-key-statistics/horizontal-indicators/sustainability-indicators/data/html/ecb.climate_indicators_carbon_emissions.en.html</t>
+          <t>This indicator quantifies how much of the loan book is exposed to climate-related risks (physical and transition) and broader environmental risks (e.g., water stress, biodiversity loss, pollution). It helps firms and supervisors judge vulnerability to asset impairment, collateral devaluation, cash-flow shocks, and regulatory change. It also informs pricing, sector limits, and strategic portfolio alignment. Definitions and concepts of climate-related risks vary across countries. The Basel Committee has defined climate-related financial risks, while the NGFS provides a range of additional defintions, including nature-related financial risks.</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>How is FSP gender diversity correlated with lending to high polluters?</t>
+          <t>How is FSP gender diversity and the gender composition of the customer base correlated with climate-related financial risks (physical and transition) and other environmental risks?</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -11211,26 +11216,26 @@
         </is>
       </c>
       <c r="D203">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Financed emissions (Carbon footprint of credit portfolio)</t>
+          <t>Exposure to polluting firms/industries</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Contribution of the financial sector to emissions (debtor's emissions financed by the financial sector via loan and securities portfolios)</t>
+          <t>Number of loans and total exposure of the credit portfolio to pollutting firms/industries</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>This indicator, also known as carbon footprint, quantifies how much carbon emission the loan book is financing, by estimating the carbon emissions of financed activities and clients. The standardized calculations of emissions vary across countries and the indicator should align with national practices. In the EU, ther financed emissions (FE) indicator provides information on the financing of high-emitting economic activities. It tracks the amount of total carbon emissions from non-financial corporations (borrowers) that can be linked to funding from financial institutions, based on a set of identifiable securities and loan portfolios. See https://www.ecb.europa.eu/stats/all-key-statistics/horizontal-indicators/sustainability-indicators/data/html/ecb.climate_indicators_carbon_emissions.en.html</t>
+          <t>This indicator quantifies how much of the loan book is exposed to borrowers classified as big polluters (e.g., fossil fuel industry). The definition of polluting borrowers or activity varies widely across countries and the indicator should be aligned with national definitions. The EU uses a range of similar indicators: https://www.ecb.europa.eu/stats/all-key-statistics/horizontal-indicators/sustainability-indicators/data/html/ecb.climate_indicators_carbon_emissions.en.html</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>How is FSP gender diversity correlated with financed emissions of the loan and securities portfolio?</t>
+          <t>How is FSP gender diversity correlated with lending to high polluters?</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -11266,41 +11271,41 @@
         </is>
       </c>
       <c r="D204">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Green/sustainable loans</t>
+          <t>Financed emissions (Carbon footprint of credit portfolio)</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>% of all loans labelled as green or sustainable</t>
+          <t>Contribution of the financial sector to emissions (debtor's emissions financed by the financial sector via loan and securities portfolios)</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>This indicator shows the share of a regulated lender’s aggregate loan book that is formally designated green, social, or sustainable. A higher percentage signals that credit is being channelled toward activities aligned with climate-transition and inclusive-growth objectives, helping regulators gauge progress against national or international sustainable-finance targets and identify institutions with elevated exposure to taxonomy-related reputation or compliance risks. The indicator is an input for green-asset-ratio disclosures and climate-stress-testing frameworks. !- Definitions and concepts: definition of green / sustainable loan varies widely across countries and should align with local frameworks. !- Data requirements: Loan-level tagging for use-of-proceeds or sustainability-performance targets, mapped to the applicable taxonomy code. Up-to-date balances to build the numerator and denominator. Dynamic criteria: Ongoing revisions to reference taxonomies may reclassify loans ex-post, creating series breaks.</t>
+          <t>This indicator, also known as carbon footprint, quantifies how much carbon emission the loan book is financing, by estimating the carbon emissions of financed activities and clients. The standardized calculations of emissions vary across countries and the indicator should align with national practices. In the EU, ther financed emissions (FE) indicator provides information on the financing of high-emitting economic activities. It tracks the amount of total carbon emissions from non-financial corporations (borrowers) that can be linked to funding from financial institutions, based on a set of identifiable securities and loan portfolios. See https://www.ecb.europa.eu/stats/all-key-statistics/horizontal-indicators/sustainability-indicators/data/html/ecb.climate_indicators_carbon_emissions.en.html</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Are there gender, location, and income disparities in access to green and sustainable loans, including those aimed at climate adaptation and resilience? How do these disparities intersect with factors such as age and sector of activity? Are women or other gender groups underrepresented among borrowers of green loans, and what barriers might contribute to this? Do financial service providers with higher levels of gender diversity tend to have relatively larger and more inclusive green/sustainable loan portfolios? How do repayment patterns and loan terms for green loans differ by gender, and what implications do these have for promoting equitable access to climate finance?</t>
+          <t>How is FSP gender diversity correlated with financed emissions of the loan and securities portfolio?</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>Financial inclusion</t>
+          <t>Stability, safety and soundness</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Uptake (account ownership)</t>
+          <t>Credit risk, Stability</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
+          <t>Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
         </is>
       </c>
     </row>
@@ -11321,31 +11326,26 @@
         </is>
       </c>
       <c r="D205">
-        <v>331</v>
+        <v>21</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Rural credit (outstanding balance)</t>
+          <t>Green/sustainable loans</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>% of the total retail loan portfolio that is rural credit based on outstanding balance</t>
+          <t>% of all loans labelled as green or sustainable</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis. !- Data requirements: Loan account level data, with details on date of disbursements, size of loan, payment schedule and repayments to date. Loan-level detail should have an existing agricultural classification or description of loan to enable classification.</t>
+          <t>This indicator shows the share of a regulated lender’s aggregate loan book that is formally designated green, social, or sustainable. A higher percentage signals that credit is being channelled toward activities aligned with climate-transition and inclusive-growth objectives, helping regulators gauge progress against national or international sustainable-finance targets and identify institutions with elevated exposure to taxonomy-related reputation or compliance risks. The indicator is an input for green-asset-ratio disclosures and climate-stress-testing frameworks. !- Definitions and concepts: definition of green / sustainable loan varies widely across countries and should align with local frameworks. !- Data requirements: Loan-level tagging for use-of-proceeds or sustainability-performance targets, mapped to the applicable taxonomy code. Up-to-date balances to build the numerator and denominator. Dynamic criteria: Ongoing revisions to reference taxonomies may reclassify loans ex-post, creating series breaks.</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the share of the outstanding retail loan portfolio held by rural borrowers, disaggregated by gender and type of borrower? Are these disparities more significant in specific regions or FSP types? Do rural women hold a lower share of outstanding balances, and could this reflect differences in loan size, duration, or repayment behavior? How does the share of rural credit within the total outstanding credit held by women compare to that of men, and what does it suggest about the gendered distribution of long-term credit in rural areas?</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers (i.e., natural persons) and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
+          <t>Are there gender, location, and income disparities in access to green and sustainable loans, including those aimed at climate adaptation and resilience? How do these disparities intersect with factors such as age and sector of activity? Are women or other gender groups underrepresented among borrowers of green loans, and what barriers might contribute to this? Do financial service providers with higher levels of gender diversity tend to have relatively larger and more inclusive green/sustainable loan portfolios? How do repayment patterns and loan terms for green loans differ by gender, and what implications do these have for promoting equitable access to climate finance?</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -11381,16 +11381,16 @@
         </is>
       </c>
       <c r="D206">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Rural credit (principal disbursed)</t>
+          <t>Rural credit (outstanding balance)</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>% of the total retail loan portfolio that is rural credit based on principal disbursed</t>
+          <t>% of the total retail loan portfolio that is rural credit based on outstanding balance</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Are there gender disparities in the value of new rural credit disbursed to borrowers, disaggregated by gender and borrower type? Are these disparities more evident in certain regions or financial service providers, particularly among those with less gender diversity? Do women in rural areas systematically receive smaller disbursements compared to men in similar loan categories or activities? Does the share of rural credit within the total disbursed credit to women differ significantly from that of men, and what does it indicate about access to productive credit for rural women? Has the share of credit disbursed to rural women changed over time in proportion to their role in the rural economy?</t>
+          <t>Are there gender disparities in the share of the outstanding retail loan portfolio held by rural borrowers, disaggregated by gender and type of borrower? Are these disparities more significant in specific regions or FSP types? Do rural women hold a lower share of outstanding balances, and could this reflect differences in loan size, duration, or repayment behavior? How does the share of rural credit within the total outstanding credit held by women compare to that of men, and what does it suggest about the gendered distribution of long-term credit in rural areas?</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>Uptake (account ownership)</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -11437,30 +11437,35 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D207">
-        <v>58</v>
+        <v>332</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Green/sustainable insurance</t>
+          <t>Rural credit (principal disbursed)</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>% of all insurance policies that are green or sustainable</t>
+          <t>% of the total retail loan portfolio that is rural credit based on principal disbursed</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>This indicator shows the share of an insurer's aggregate policy portfolio that is formally designated green, social, or sustainable. A higher percentage signals that insurance being channelled toward activities aligned with climate-transition and inclusive-growth objectives (e.g., crop insurance for agroforestry), helping regulators gauge progress against national or international sustainable-finance targets. !- Definitions and concepts: definition of green / sustainable insurance varies widely across countries and should align with local frameworks. !- Data requirements: Policy-level tagging for sustainability-performance targets, mapped to the applicable taxonomy code.</t>
+          <t>An indicator of rural credit is a metric used to analyze and quantify the performance, accessibility, and impact of lending to the agricultural sector. In many countries, this indicator is essential to monitor compliance with minimum lending targets imposed on the financial or the banking sector. This indicator helps in assessing the effectiveness of national agricultural finance policies, including subsidies made available to lenders. It should be analyzed together with other indicators such as total number of rural credit contracts, average size of rural credit operations and, when data is available, indicators that highlight which types of clients are benefiting from rural credit, such as farmers classified as smallholders or family farmers. Segmentation by sector and geographic location enrich the analysis. !- Data requirements: Loan account level data, with details on date of disbursements, size of loan, payment schedule and repayments to date. Loan-level detail should have an existing agricultural classification or description of loan to enable classification.</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Are there disparities by gender, income, and location in the likelihood of acquiring green or sustainable insurance products, including climate resilience coverage? Are certain gender groups underserved in this market? Do financial service providers (FSPs) with higher levels of gender diversity tend to maintain larger or more diverse green/sustainable insurance portfolios?</t>
+          <t>Are there gender disparities in the value of new rural credit disbursed to borrowers, disaggregated by gender and borrower type? Are these disparities more evident in certain regions or financial service providers, particularly among those with less gender diversity? Do women in rural areas systematically receive smaller disbursements compared to men in similar loan categories or activities? Does the share of rural credit within the total disbursed credit to women differ significantly from that of men, and what does it indicate about access to productive credit for rural women? Has the share of credit disbursed to rural women changed over time in proportion to their role in the rural economy?</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>For analyses with a primary focus on financial inclusion, for this indicator it is recommended that only retail customers and/or financial products held by retail customers are considered. Where data permits, this indicator can be examined separately for MSMEs.</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -11475,7 +11480,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity</t>
+          <t>Customer type; Customer gender; Customer age; Customer location; Customer income category; Financial service provider (FSP) type; Financial service provider (FSP) main activity; Loan type; Loan size; Loan term; Interest rate category</t>
         </is>
       </c>
     </row>
@@ -11492,30 +11497,40 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D208">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Holdings of green/sustainable bonds</t>
+          <t>Green/sustainable insurance</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Volume (holdings) and value (amount outstanding) of sustainable/green bonds</t>
+          <t>% of all insurance policies that are green or sustainable</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>The indicator measures the aggregate value and volume of green and/or sustainability bonds held by investors, reflecting capital directed towards projects and activities with positive environmental or social impacts. It is a measure of sustainable finance. The definition of sustainable or green bond varies widely across countries and the indicator should align with local practices. An example of definition is provided by the Green Bond Principles (GBP), by the International Capital Markets Association (ICMA) https://www.icmagroup.org/sustainable-finance/the-principles-guidelines-and-handbooks/green-bond-principles-gbp/</t>
+          <t>This indicator shows the share of an insurer's aggregate policy portfolio that is formally designated green, social, or sustainable. A higher percentage signals that insurance being channelled toward activities aligned with climate-transition and inclusive-growth objectives (e.g., crop insurance for agroforestry), helping regulators gauge progress against national or international sustainable-finance targets. !- Definitions and concepts: definition of green / sustainable insurance varies widely across countries and should align with local frameworks. !- Dat